--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>شهریه + £1,171 × ۹ = £10,539 خارج لندن / £13,761 لندن؛ از ۳۰ نوامبر ۲۰۲۶: £10,827 / £14,130؛ ۲۸ روز متوالی در حساب؛ + IHS £1,035/سال + ویزا £524.</t>
+          <t>شهریه + £1,171 × ۹ = £10,539 خارج لندن / £13,761 لندن؛ از ۳۰ نوامبر ۲۰۲۶: £10,827 / £14,130؛ ۲۸ روز متوالی در حساب؛ + ویزای دانشجویی £524 + IHS با نرخ دانشجویی £776/سال (برای ۱۶ ماه اقامت ≈ £1,164).</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>بریتانیا (UK) 🇬🇧</t>
+          <t>انگلستان (England) 🇬🇧</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -587,9 +587,13 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Swansea – MSc Advanced Computer Science (2:2) → Safe
-Brunel – MSc AI / Data Science (2:2) → Safe
-Strathclyde – MSc Advanced Computer Science (2:2) → Target</t>
+          <t>Teesside (Middlesbrough) – MSc Computer Science (2:2، IELTS 6.0) → Safe
+Northumbria (Newcastle) – MSc Advanced Computer Science (2:2 در رشته کامپیوتری) → Safe
+Essex (Colchester) – MSc Advanced Computer Science (2:2؛ Computer Engineering پذیرفته می‌شود) → Safe/Target
+Brunel (London) – MSc AI / Data Science (2:2) → Safe/Target
+Leicester – MSc Advanced Computer Science (2:1؛ سابقه کار مرتبط جبران می‌کند) → Target
+York – MSc Advanced Computer Science (2:2 با پیش‌زمینه قوی، IELTS 6.5) → Reach
+فقط انگلستان — Strathclyde (اسکاتلند) و Swansea (ولز) حذف شدند</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -636,7 +640,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Strathclyde =230 · Swansea ≈ 300 · Brunel 353</t>
+          <t>Newcastle 149 · York =158 · Leicester =314 · Brunel 353 · Essex =438 · Northumbria =528 · Teesside در فهرست اصلی QS نیست (THE 601–800)</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -737,15 +741,18 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Swansea: £24,200
+          <t>Teesside: £17,000
+Northumbria: £21,500
+Leicester: £24,250
+Essex: £24,675
 Brunel: £24,795
-Strathclyde: £31,900
-بورس‌ها (Strathclyde ۱۵٪، Brunel £6,000) جدا حساب شوند، تضمینی نیستند</t>
+York: £32,900 (Newcastle ≈ £31,700)
+کف قیمت انگلستان: Chester £15,500 (بدون رتبه). بورس‌ها (مثلاً Brunel تا £6,000) جدا حساب شوند، تضمینی نیستند</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>utwente.nl؛ liu.se؛ bth.se؛ sdu.dk؛ studyindenmark.dk؛ ul.ie؛ maynoothuniversity.ie؛ brunel.ac.uk؛ strath.ac.uk؛ swansea.ac.uk</t>
+          <t>utwente.nl؛ liu.se؛ bth.se؛ sdu.dk؛ studyindenmark.dk؛ ul.ie؛ maynoothuniversity.ie؛ brunel.ac.uk؛ tees.ac.uk؛ northumbria.ac.uk؛ le.ac.uk؛ essex.ac.uk؛ york.ac.uk</t>
         </is>
       </c>
     </row>
@@ -787,7 +794,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>$32,100–42,300</t>
+          <t>$22,500–43,600 (Teesside $22,500 · Northumbria $28,500 · Leicester/Essex/Brunel ≈ $32,100–32,900 · York $43,600)</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -840,7 +847,8 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Glasgow/Swansea: £1,000–1,300
+          <t>شمال انگلستان (Middlesbrough/Newcastle): £950–1,250
+Leicester/Colchester/York: £1,000–1,350
 London (Brunel): £1,400–1,800
 حداقل ویزا: £1,171 / £1,529 در ماه (× ۹)؛ از ۳۰ نوامبر ۲۰۲۶: £1,203 / £1,570</t>
         </is>
@@ -889,7 +897,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>$48,000–71,000 (Swansea: $48,000–53,000)</t>
+          <t>$38,000–65,000 (Teesside $38–42k · Northumbria $44–48k · Leicester/Essex $48–54k · Brunel/London $55–61k · York $60–65k)</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -936,7 +944,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>$48,000–71,000 (۱ سال)</t>
+          <t>$38,000–65,000 (۱ سال)</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -983,7 +991,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>❌ کسری $16,000–39,000</t>
+          <t>❌ کسری $6,000–33,000 (کمترین: Teesside ≈ $6–10k؛ Northumbria ≈ $12–16k)</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1368,7 +1376,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>£28,000–35,000 خارج لندن؛ London £32,000–45,000 — اغلب زیر کف اسپانسری £38,290</t>
+          <t>£28,000–35,000 خارج لندن (Manchester/Leeds/Newcastle)؛ London £32,000–45,000 — اغلب زیر کف اسپانسری £38,290</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1839,7 +1847,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>بسیار بالا: Graduate visa ۱۸ ماه، B2، طرح PR ۱۰ ساله، عوارض £925/دانشجو/سال از 2028-29 (فقط دانشگاه‌های انگلستان: Brunel بله، Strathclyde/Swansea خیر)</t>
+          <t>بسیار بالا: Graduate visa ۱۸ ماه، B2، طرح PR ۱۰ ساله، عوارض £925/دانشجو/سال از اوت ۲۰۲۸ فقط برای دانشگاه‌های انگلستان — یعنی همهٔ گزینه‌های شما (ورودی ۲۰۲۸)؛ احتمالاً به شهریه اضافه می‌شود</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -1886,12 +1894,12 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>3 / 10 / 4 = ۱۷</t>
+          <t>5 / 10 / 4 = ۱۹</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>وزن برابر. اگر «انگلیسی» وزن بیشتری دارد → ایرلند با فاصله؛ اگر «هزینه» وزن بیشتری دارد و B1 آلمانی را می‌پذیرید → آلمان.</t>
+          <t>وزن برابر. اگر «انگلیسی» وزن بیشتری دارد → ایرلند با فاصله؛ اگر «هزینه» وزن بیشتری دارد و B1 آلمانی را می‌پذیرید → آلمان. انگلستان با گزینه‌های ارزان شمال (Teesside/Northumbria) از ۱۷ به ۱۹ رسید (هم‌امتیاز سوئد) ولی هنوز از بودجهٔ سالانه $32k بیرون است.</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1954,7 +1962,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>آلمان $27–36k  &lt;  ایرلند $32–48k  &lt;  بریتانیا $48–71k  &lt;  سوئد $54–65k  &lt;  دانمارک $61–71k  &lt;  هلند $75–90k</t>
+          <t>آلمان $27–36k  &lt;  ایرلند $32–48k  &lt;  انگلستان $38–65k  &lt;  سوئد $54–65k  &lt;  دانمارک $61–71k  &lt;  هلند $75–90k</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1974,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ایرلند و بریتانیا کامل؛ هلند و سوئد برای زندگی/کار خوب ولی برای اقامت دائم/تابعیت زبان می‌خواهند (هلند B1 در راه، سوئد آزمون تابعیت)؛ دانمارک و آلمان بدون زبان محلی هم بازار کار و هم PR محدود.</t>
+          <t>ایرلند و انگلستان کامل؛ هلند و سوئد برای زندگی/کار خوب ولی برای اقامت دائم/تابعیت زبان می‌خواهند (هلند B1 در راه، سوئد آزمون تابعیت)؛ دانمارک و آلمان بدون زبان محلی هم بازار کار و هم PR محدود.</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1986,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>حقوق ناخالص: دانمارک &gt; آلمان &gt; هلند ≈ سوئد &gt; ایرلند &gt; بریتانیا. دسترسی برای جونیورِ فقط‌انگلیسی: ایرلند ≈ هلند &gt; آلمان &gt; سوئد ≈ دانمارک ≈ بریتانیا.</t>
+          <t>حقوق ناخالص: دانمارک &gt; آلمان &gt; هلند ≈ سوئد &gt; ایرلند &gt; انگلستان. دسترسی برای جونیورِ فقط‌انگلیسی: ایرلند ≈ هلند &gt; آلمان &gt; سوئد ≈ دانمارک ≈ انگلستان.</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1998,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ایرلند ۲۵ › آلمان ۲۲ › سوئد ۱۹ › هلند ۱۸ › بریتانیا ۱۷ › دانمارک ۱۶.  پیشنهاد: اپلای هم‌زمان به ۲–۳ برنامه ایرلند (UL، Maynooth، TU Dublin) + ۲ برنامه آلمان (Stuttgart، FAU یا یک گزینه Safe)؛ تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در ۲۰۲۸.</t>
+          <t>ایرلند ۲۵ › آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ › دانمارک ۱۶.  پیشنهاد: اپلای هم‌زمان به ۲–۳ برنامه ایرلند (UL، Maynooth، TU Dublin) + ۲ برنامه آلمان (Stuttgart، FAU یا یک گزینه Safe)؛ تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در ۲۰۲۸.</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2022,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>تا بهار ۲۰۲۷: IELTS 7.0 (هر بخش ≥ 6.5) · تابستان ۲۰۲۷: ریزنمرات رسمی + تأییدیه‌ها + VPD uni-assist · پاییز ۲۰۲۷ تا زمستان ۲۰۲۸: اپلای (ایرلند rolling از اکتبر؛ سوئد ۱۵ ژانویه؛ هلند تا ۱ می؛ آلمان ۱۵ ژانویه–۱۵ ژوئیه؛ بریتانیا rolling) · بهار ۲۰۲۸: شهریه/تمکن → خوابگاه → ویزا یا برنامه B.</t>
+          <t>تا بهار ۲۰۲۷: IELTS 7.0 (هر بخش ≥ 6.5) · تابستان ۲۰۲۷: ریزنمرات رسمی + تأییدیه‌ها + VPD uni-assist · پاییز ۲۰۲۷ تا زمستان ۲۰۲۸: اپلای (ایرلند rolling از اکتبر؛ سوئد ۱۵ ژانویه؛ هلند تا ۱ می؛ آلمان ۱۵ ژانویه–۱۵ ژوئیه؛ انگلستان rolling) · بهار ۲۰۲۸: شهریه/تمکن → خوابگاه → ویزا یا برنامه B.</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2035,7 @@
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>• هزینه کل دوره اضافه شد (هلند از «نیاز به تأمین سال دوم» به گران‌ترین گزینه تبدیل شد)
-• بریتانیا: Graduate visa ۱۸ ماه؛ کف اسپانسری £54,700 / £38,290؛ طرح PR ۱۰ ساله؛ شهریه Strathclyde £31,900
+• فقط انگلستان (به خواست شما): Strathclyde و Swansea حذف شدند؛ گزینه‌ها Teesside £17,000 · Northumbria £21,500 · Leicester £24,250 · Essex £24,675 · Brunel £24,795 · York £32,900؛ Graduate visa ۱۸ ماه؛ کف اسپانسری £54,700 / £38,290؛ طرح PR ۱۰ ساله؛ عوارض £925 از ۲۰۲۸ شامل همهٔ گزینه‌ها
 • کف حقوق ۲۰۲۶ همه کشورها به‌روز شد (آلمان €50,700/€45,934؛ هلند €3,122/ماه؛ سوئد SEK 34,470؛ ایرلند €40,904)
 • ایرلند: ۲ سال CSEP = Stamp 4 نه PR؛ تمکن €10,000
 • سوئد: کار دانشجویی ۱۵ ساعت/هفته (ژوئن ۲۰۲۶)؛ شهروندی ۸ سال؛ «BTH یک‌ساله» حذف شد؛ خوابگاه فقط LiU
@@ -2040,22 +2048,34 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>نکته پروفایل</t>
+          <t>چرا «انگلستان» و نه «بریتانیا»</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>معدل (۱۵.۷۷ طبق جدول اول؛ ۱۵.۷۰ طبق نقد دوم — تفاوتی در نتیجه ندارد) برای همه برنامه‌های بالا بالاتر از حداقل است. مهم‌تر از معدل، تطابق ریزنمرات با پیش‌نیازها (ریاضی، الگوریتم، CS نظری) و SOP با تکیه بر ۲ سال سابقه کار + بازی‌سازی + پروژه‌های گیت‌هاب است.</t>
+          <t>به خواست شما فقط دانشگاه‌های انگلستان مقایسه شده‌اند. قوانین ویزا، کار و اقامت در کل بریتانیا یکسان است؛ سه تفاوت عملی: (۱) ارزان‌ترین گزینه‌های انگلستان (Teesside £17,000، Northumbria £21,500) از Swansea/Strathclyde ارزان‌ترند → کل دوره از $48–71k به $38–65k رسید؛ (۲) عوارض £925 به ازای هر دانشجو از اوت ۲۰۲۸ فقط دانشگاه‌های انگلستان را می‌گیرد — یعنی همهٔ گزینه‌های شما؛ (۳) بازار کار فناوری بریتانیا عملاً در انگلستان است (London، Manchester، Cambridge، Bristol، Leeds) — حذف اسکاتلند/ولز به فرصت شغلی لطمه نمی‌زند. برای شهریهٔ کمتر باید رتبهٔ پایین‌تر را بپذیرید: Teesside/Chester بدون رتبه QS، Northumbria ≈ ۵۲۸، Essex ≈ ۴۳۸؛ York (۱۵۸) و Newcastle (۱۴۹) تقریباً دوبرابر گران‌ترند.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>نکته پروفایل</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>معدل (۱۵.۷۷ طبق جدول اول؛ ۱۵.۷۰ طبق نقد دوم — تفاوتی در نتیجه ندارد) برای همه برنامه‌های بالا بالاتر از حداقل است. مهم‌تر از معدل، تطابق ریزنمرات با پیش‌نیازها (ریاضی، الگوریتم، CS نظری) و SOP با تکیه بر ۲ سال سابقه کار + بازی‌سازی + پروژه‌های گیت‌هاب است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>اعداد را چگونه بخوانم</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>همه مبالغ سطح 2026/27 هستند؛ برای ۲۰۲۸ سالانه ۳–۵٪ (شهریه ۵–۱۰٪) اضافه کنید. نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55</t>
         </is>
@@ -2072,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2682,130 +2702,238 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Strathclyde شهریه PG 2026-27</t>
+          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>https://www.strath.ac.uk/media/1newwebsite/documents/tuitionfees/PG_Fees_2026-2027_Entry_v0.7.pdf</t>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Swansea MSc Advanced Computer Science</t>
+          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>https://www.swansea.ac.uk/postgraduate/taught/maths-comp-sci/computer-science/msc-advanced-computer-science/</t>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
+          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
+          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
+          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
+          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – وضعیت VAC تهران</t>
+          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – TU Dresden</t>
+          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
+          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Stuttgart</t>
+          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
+          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Brunel</t>
+          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
+          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – سایر</t>
+          <t>بریتانیا – وضعیت VAC تهران</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/world-university-rankings</t>
+          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
+          <t>QS WUR 2027 – TU Dresden</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
+          <t>QS WUR 2027 – Stuttgart</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>QS WUR 2027 – Newcastle 149</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>QS WUR 2027 – York =158</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/about/rankings/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>QS WUR 2027 – Leicester =314</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/university-leicester</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>QS WUR 2027 – Essex =438</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/essex-university</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>QS WUR 2027 – Northumbria =528</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>QS WUR 2027 – Brunel</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>QS WUR 2027 – سایر</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/world-university-rankings</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
           <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>https://www.xe.com/</t>
         </is>
@@ -2873,6 +3001,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -8,10 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جدول نهایی ۲۰۲۶" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جمع‌بندی" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منابع" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه‌ها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="حوزه‌ها و بازار کار" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جمع‌بندی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منابع" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$O$103</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,10 +45,15 @@
     </font>
     <font>
       <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +68,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAF1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF5E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
@@ -106,7 +140,31 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -474,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -598,7 +656,8 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>سایت برنامه‌ها؛ utwente.nl (Iran 15/20)؛ bth.se؛ «۷۵٪ قبولی» جدول اول حذف شد — چنین آماری وجود ندارد</t>
+          <t>سایت برنامه‌ها؛ utwente.nl (Iran 15/20)؛ bth.se؛ «۷۵٪ قبولی» جدول اول حذف شد — چنین آماری وجود ندارد.
+➜ فهرست کامل ≈۱۰۰ برنامه در ۸ حوزه (AI، امنیت، داده، نرم‌افزار، ابری، نهفته/رباتیک، HCI، بازی) با شهریه و شرط ورود: شیت «برنامه‌ها»؛ مقایسهٔ بازار کار حوزه‌ها: شیت «حوزه‌ها و بازار کار»</t>
         </is>
       </c>
     </row>
@@ -630,7 +689,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Aalborg 329 · SDU ≈ 329</t>
+          <t>SDU =283 · Aalborg =329</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -728,8 +787,8 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>SDU: €13,900 (DKK 104,000)
-AAU: €14,910 (7,455 در ترم)</t>
+          <t>AAU: €14,910 (7,455 در ترم)
+SDU: €17,300 (نرخ رسمی برای ورودی سپتامبر ۲۰۲۶ به بعد — رقم قدیمی €13,900 دیگر معتبر نیست)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -784,7 +843,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>$15,800–17,000</t>
+          <t>$17,000–19,700</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -887,7 +946,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>$30,500–35,500</t>
+          <t>$31,500–38,000</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -934,7 +993,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>$61,000–71,000 (۲ سال)</t>
+          <t>$63,000–76,000 (۲ سال)</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -981,7 +1040,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ مرزی؛ کسری تا ≈ $3,500 در سال</t>
+          <t>⚠️ مرزی؛ AAU تقریباً در بودجه، SDU کسری تا ≈ $6,000 در سال</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1921,6 +1980,13 @@
       <c r="B33" t="inlineStr">
         <is>
           <t>جدول اولیه (Table.xlsx) برای مقایسه دست‌نخورده مانده است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>شیت «برنامه‌ها»: ≈۱۰۰ برنامهٔ انگلیسی‌زبان در ۸ حوزهٔ کامپیوتری (نه فقط CS) برای هر ۶ کشور؛ شیت «حوزه‌ها و بازار کار»: کدام حوزه برای شما بازار و پذیرش بهتری دارد.</t>
         </is>
       </c>
     </row>
@@ -1930,6 +1996,8175 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>کشور</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>دانشگاه (شهر)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>برنامه</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>حوزه</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>مدت</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>شهریهٔ سالانه 2026/27 (ارز محلی)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>≈ شهریهٔ سالانه به دلار</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>شرط ورود</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>IELTS</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>QS 2027</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Safe / Target / Reach (معدل ۱۵.۷۷)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>بازار کار حوزه (۱–۵) و نکته</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>نکتهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>منبع (صفحهٔ رسمی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Teesside (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>£17,000</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>$22,500</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2:2 در رشتهٔ مرتبط</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>— (THE 601–800)</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>ارزان‌ترین گزینهٔ معتبر انگلستان؛ Middlesbrough ارزان ولی بازار کار محلی کوچک</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Teesside (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>£17,000</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>$22,500</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>2:2 در رشتهٔ مرتبط</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>همان باند شهریهٔ Teesside</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_artificial_intelligence.cfm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Teesside (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cyber Security (BCS accredited)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>£17,000</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>$22,500</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2:2 در رشتهٔ مرتبط</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>اعتبار BCS؛ بدون NCSC</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_cyber_security.cfm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Northumbria (Newcastle)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>MSc Advanced Computer Science</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>£21,500</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>$28,500</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2:2 در رشتهٔ کامپیوتری</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K5" s="4">
+        <f>528</f>
+        <v/>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Newcastle: شهر دانشجویی ارزان با بازار فناوری متوسط</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Northumbria (Newcastle)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>£21,500</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>$28,500</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2:2 در رشتهٔ کامپیوتری/ریاضی</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K6" s="4">
+        <f>528</f>
+        <v/>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-artificial-intelligence-dtfari6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Nottingham Trent (Nottingham)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>≈ £19,900</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>$26,400</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2:2 (≈ ۵۵٪)</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K7" s="4">
+        <f>639</f>
+        <v/>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>رقم از دو مرجع ثانویه؛ صفحهٔ رسمی 2026/27 را قبل از اقدام چک کنید</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ntu.ac.uk/study-and-courses/courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Nottingham Trent (Nottingham)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cyber Security</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>≈ £19,900</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>$26,400</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K8" s="4">
+        <f>639</f>
+        <v/>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>همان باند NTU (≈)</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ntu.ac.uk/study-and-courses/courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Manchester Metropolitan (Manchester)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cyber Security</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>£21,000</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>$27,800</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>2:2 در رشتهٔ کامپیوتری</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>≈ 600–650</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Manchester دومین قطب فناوری انگلستان؛ شهریهٔ رسمی overseas 2026/27</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Essex (Colchester)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>MSc Advanced Computer Science</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>£24,675</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>$32,700</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>2:2؛ Computer Engineering پذیرفته می‌شود</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K10" s="4">
+        <f>438</f>
+        <v/>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>۵۰ دقیقه تا لندن؛ دانشکدهٔ CSEE قوی در AI</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Essex (Colchester)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>£24,675</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>$32,700</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>2:2 در رشتهٔ کامپیوتری/ریاضی</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K11" s="4">
+        <f>438</f>
+        <v/>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>ورودی اکتبر ۲۰۲۶ تأیید شده</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.essex.ac.uk/courses/pg00457/1/msc-artificial-intelligence</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>MSc Advanced Computer Science</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>£24,250</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>$32,100</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>2:1 (سابقهٔ کار مرتبط جبران می‌کند)</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K12" s="4">
+        <f>314</f>
+        <v/>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>رتبهٔ بهتر با شهریهٔ نزدیک Essex</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>£24,250</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>$32,100</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K13" s="4">
+        <f>314</f>
+        <v/>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>https://le.ac.uk/courses/artificial-intelligence-msc/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cloud Computing</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>£24,250</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>$32,100</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K14" s="4">
+        <f>314</f>
+        <v/>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>یکی از معدود ارشدهای خالص Cloud در انگلستان</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>https://le.ac.uk/courses/cloud-computing-msc/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Brunel (London)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>£24,795</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>$32,900</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>لندن = بازار کار بزرگ ولی زندگی £1,400–1,800/ماه؛ بورس تا £6,000 تضمینی نیست</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Brunel (London)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science and Analytics</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>£24,795</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>$32,900</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.brunel.ac.uk/study/courses/data-science-and-analytics-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Kent (Canterbury)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cyber Security (NCSC fully certified + BCS)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>≈ £23,500</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>$31,100</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>«good 2:2»</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>گواهی کامل NCSC = معتبرترین برچسب امنیت در بریتانیا؛ رقم شهریه از مرجع ثانویه</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Royal Holloway (Egham، حومهٔ لندن)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>MSc Information and Cyber Security</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>£25,500</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>$33,800</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K18" s="4">
+        <f>485</f>
+        <v/>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>قدیمی‌ترین گروه امنیت اطلاعات بریتانیا (ISG)؛ NCSC certified</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Goldsmiths (London)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Games Programming</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>£22,000</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>$29,200</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>مدرک second-class در رشتهٔ برنامه‌نویسی</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>6.5 (6.0)</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>≈ 800–1000</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>پورتفولیوی Unity/C# شما اینجا مستقیماً به کار می‌آید؛ بازار بازی ۲۰۲۲–۲۵ ضعیف</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Surrey (Guildford)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>≈ £26,900–27,500</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>$35,600–36,400</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K20" s="4">
+        <f>246</f>
+        <v/>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Guildford قطب بازی‌سازی و امنیت بریتانیا (نزدیک لندن)؛ رقم 2025/26 + برآورد 2026/27</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>https://www.surrey.ac.uk/postgraduate/artificial-intelligence-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Surrey (Guildford)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cyber Security (NCSC)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>£25,900</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>$34,300</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>6.5 (W 6.0)</t>
+        </is>
+      </c>
+      <c r="K21" s="4">
+        <f>246</f>
+        <v/>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>MSc Advanced Computer Science</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>£32,900</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>$43,600</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>2:2 با پیش‌زمینهٔ قوی</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K22" s="4">
+        <f>158</f>
+        <v/>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Russell Group؛ گران</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>MSc Human-Centred Interactive Technologies</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>HCI / طراحی تعامل / UX</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>£32,900</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>$43,600</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K23" s="4">
+        <f>158</f>
+        <v/>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>بهترین برنامهٔ HCI انگلستان برای معدل شما؛ ولی بازار UX ضعیف</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Game Engineering</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>£32,300</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>$42,800</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>2:1 (2:2 با سابقه بررسی می‌شود)</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>معتبرترین ارشد مهندسی بازی انگلستان؛ گران</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ncl.ac.uk/postgraduate/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cyber Security</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>£30,000 (بورس خودکار £4,500 با 2:1)</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>$39,800</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>NCSC-certified؛ شرط 2:1 برای معدل شما سخت است</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>£34,340</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>$45,500</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>رتبهٔ بالا، شهریه و شرط ورود بالا</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sheffield.ac.uk/postgraduate/taught/courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>TU Dublin (Blanchardstown)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computing in Applied Cyber Security</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال (حضوری + آنلاین)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>€14,500 (کل دوره)</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>$16,500</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>2:2 (GPA 2.5) در Computing</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>6.5 (6.0)</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>791–800</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>ارزان‌ترین ارشد امنیت ایرلند در یک دانشگاه دولتی</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tudublin.ie/study/postgraduate/courses/applied-cyber-security/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>TU Dublin (Grangegorman)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science (Data Science)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>۱–۱.۵ سال</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>€21,750 (کل دوره)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>$24,800</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>2:1، یا 2:2 + ۲ سال سابقهٔ توسعهٔ نرم‌افزار</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>6.5 (6.0)</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>791–800</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال سابقهٔ کار شما اینجا شرط ورود را جبران می‌کند</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tudublin.ie/study/postgraduate/courses/computing-data-science/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>TU Dublin (Grangegorman)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computing (Advanced Software Development)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>≈ €15,000–15,500</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>$17,100–17,700</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>791–800</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Safe جدول اصلی</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tudublin.ie/study/postgraduate/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Maynooth</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science and Analytics (۱۲ ماهه، conversion)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>≈ €17,000</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>$19,400</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>مدرک Level 8 با محتوای ریاضی</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>721–730</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>ورود آسان؛ ولی حوزهٔ اشباع جونیور</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.maynoothuniversity.ie/study-maynooth/postgraduate-studies/courses/msc-data-science-and-analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Maynooth</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>MSc (Computer Science) Software Engineering</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>€18,000 (2025/26) → ≈ €18,500</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>$21,100</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>721–730</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>۲۵ دقیقه تا Dublin با قطار؛ اجاره کمتر از Dublin</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>https://www.maynoothuniversity.ie/study-maynooth/postgraduate-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>University of Limerick</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>€20,800</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>$23,700</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>first یا second class honours در CS/Computer Engineering</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27؛ Limerick ارزان‌تر از Dublin</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ul.ie/study/postgraduate/artificial-intelligence-and-machine-learning-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>University of Limerick</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>MSc Software Engineering</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>€20,800</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>$23,700</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ul.ie/study/postgraduate</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Munster TU – MTU (Cork)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>≈ €12,000–15,000</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>$13,700–17,100</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>مدرک Level 8 honours در Computing</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Cork: مقر اروپایی Apple و ده‌ها شرکت امنیت؛ رقم از مراجع ثانویه</t>
+        </is>
+      </c>
+      <c r="O34" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mtu.ie/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Munster TU – MTU (Cork)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>≈ €15,000</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Level 8 honours در CS/Eng + ریاضی و کدنویسی قوی</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mtu.ie/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Dublin City University (Dublin)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>MSc in Computing — Majors: AI with NLP / Data Analytics / Secure Software Engineering / Cloud Computing</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>چندحوزه‌ای (انتخاب گرایش)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>€25,000 (−€5,000 بورس دانشکده برای غیر-EU ⇒ €20,000)</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>$22,800–28,500</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>2:1 در CS/Computing</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>شرط 2:1؛ ورودی ژانویه ۲۰۲۷ هم دارد</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dcu.ie/courses/postgraduate/school-computing/msc-computing-major-options</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>University of Galway</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science (Artificial Intelligence)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>€28,000</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>$31,900</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>First Class (یا 2:1 خوب با تأیید مدیر برنامه)</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>شرط ورود بالا؛ گران</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>http://cs.universityofgalway.ie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>University College Cork (Cork)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>€28,000</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>$31,900</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>2:1 در CS/ریاضی</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>UCD (QS 100) و TCD (QS 75) هم ≈ €30k و 2:1 → برای معدل شما Reach</t>
+        </is>
+      </c>
+      <c r="O38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ucc.ie/en/study/postgrad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Universität Stuttgart</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Computer Science (انگلیسی، بدون NC)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>€1,500 در ترم + ≈ €200 سهم ترم = ≈ €3,400/سال</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>$3,900</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>7.0 (C1)</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ بادن-وورتمبرگ برای غیر-EU</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Universität Stuttgart</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Information Technology (INFOTECH)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>€1,500 در ترم + سهم ترم ≈ €3,400/سال</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>$3,900</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی EE/CS/Computer Engineering؛ گزینش</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>7.0 (C1)</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>گرایش‌های Embedded/Communication؛ Bosch و Daimler همان شهر</t>
+        </is>
+      </c>
+      <c r="O40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mygermanuniversity.com/master/information-technology-infotech/678</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>FAU Erlangen-Nürnberg</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €130 سهم ترم (≈ €260/سال)</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/مرتبط؛ بررسی ریزنمرات</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>B2 (IELTS 6.0)</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Siemens/adidas/Schaeffler در منطقه</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.fau.eu/degree-program/artificial-intelligence-m-sc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>FAU Erlangen-Nürnberg</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Autonomy Technologies</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €130 سهم ترم</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی مرتبط؛ آلمانی لازم نیست</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>B2 (IELTS 6.0)</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>رباتیک/خودران؛ صفحهٔ رسمی سپتامبر ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="O42" s="8" t="inlineStr">
+        <is>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>TU Darmstadt</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Distributed Software Systems (انگلیسی)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €300 سهم ترم (≈ €600/سال)</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>$700</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS با پیش‌نیازهای مشخص</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>≈ 7.0 (C1) — چک شود</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>منطقهٔ Rhein-Main (SAP، Deutsche Bank، Software AG)</t>
+        </is>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tu-darmstadt.de/studieren/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>TU Dresden</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Computer Science (انگلیسی)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €300 سهم ترم</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>$700</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS؛ ارزیابی استعداد</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>Dresden ارزان‌ترین شهر جدول؛ GlobalFoundries/Infineon/Bosch</t>
+        </is>
+      </c>
+      <c r="O44" s="8" t="inlineStr">
+        <is>
+          <t>https://tu-dresden.de/studium/vor-dem-studium/studienangebot</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Saarland University (Saarbrücken)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €394 سهم ترم (≈ €790/سال)</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>$900</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS + اثبات دروس پایه + ۲ توصیه‌نامه؛ بدون NC</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>7.0 (C1؛ MOI پذیرفته نمی‌شود)</t>
+        </is>
+      </c>
+      <c r="K45" s="4">
+        <f>588 (CS ≈ 251)</f>
+        <v/>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>CISPA — بهترین مرکز امنیت آلمان؛ IELTS 7 شرط سخت شماست</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Saarland University (Saarbrücken)</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Data Science and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €394 سهم ترم</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>$900</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>7.0 (C1)</t>
+        </is>
+      </c>
+      <c r="K46" s="4">
+        <f>588 (CS ≈ 251)</f>
+        <v/>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>MPI Informatics و DFKI در همان کمپوس</t>
+        </is>
+      </c>
+      <c r="O46" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/data-science.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>TU Chemnitz</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Automotive Software Engineering</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €320 سهم ترم (≈ €640/سال)</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>$700</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/مرتبط؛ بدون محدودیت پذیرش</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>B2 (IELTS 5.5)</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>آسان‌ترین ورود؛ شهر ارزان؛ ولی صنعت خودرو ۲۰۲۴–۲۵ ضعیف و آلمانی در کارفرمایان محلی</t>
+        </is>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mygermanuniversity.com/master/automotive-software-engineering/91</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Universität Passau</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Artificial Intelligence Engineering</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €100–200 سهم ترم</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>معدل آلمانی ≤ 2.7 (معدل شما ≈ 2.3 ✓)؛ ۳۵ ECTS ریاضی + ۴۰ ECTS CS</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>B2؛ + آلمانی A1 تا پایان سال اول (کلاس رایگان)</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان</t>
+        </is>
+      </c>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>OVGU Magdeburg</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Data and Knowledge Engineering</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €311 سهم ترم</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>$700</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>معدل آلمانی ≤ 2.3 (معدل شما ≈ 2.27 — دقیقاً مرزی)؛ کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>6.0–7.0 (منابع متناقض؛ رسمی را چک کنید)</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dke.ovgu.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>TH Köln – Cologne Game Lab</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>M.A. Game Development and Research</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>€2,500 در ترم (غیر-EU) + €277 سهم ترم ≈ €5,550/سال</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>$6,300</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>هر کارشناسی + ≥ ۱۲ ماه سابقهٔ مرتبط + آزمون استعداد (مهلت ۳۱ مارس)</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>معتبرترین مدرسهٔ بازی آلمان؛ ۷ ماه Unity + ۲ سال IT شما احتمالاً شرط ۱۲ ماه را می‌پوشاند — بپرسید</t>
+        </is>
+      </c>
+      <c r="O50" s="8" t="inlineStr">
+        <is>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Universität Siegen</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Human Computer Interaction</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>HCI / طراحی تعامل / UX</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €372 سهم ترم</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>معدل آلمانی ≤ 2.5؛ کارشناسی CS/IS/Design/Psychology</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>شروع زمستان و تابستان؛ شهر کوچک</t>
+        </is>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Hochschule Bonn-Rhein-Sieg (Sankt Augustin)</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>€0 + €349 سهم ترم</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>معدل آلمانی ≤ 2.5؛ ۲۵ جای محدود؛ آزمون استعداد؛ uni-assist</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>6.5 (B2+)</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>رباتیک کاربردی با Fraunhofer؛ نزدیک Bonn/Köln</t>
+        </is>
+      </c>
+      <c r="O52" s="8" t="inlineStr">
+        <is>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>RWTH Aachen</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Software Systems Engineering</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>€0 + ≈ €330 سهم ترم</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS، معدل ≥ ۶۵٪ (شما ۷۹٪ ✓)؛ ۲ درس پیشرفتهٔ سیستم؛ مهلت ۱ مارس</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>B2 (IELTS 5.5)</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>TU9؛ رقابتی — معدل شما حداقل را رد می‌کند ولی متقاضیان قوی‌ترند</t>
+        </is>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Universität Tübingen</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Machine Learning</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>€1,500 در ترم + ≈ €200 = ≈ €3,400/سال</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>$3,900</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/ریاضی؛ آزمون توانایی؛ مهلت ۳۰ آوریل</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="K54" s="4">
+        <f>230</f>
+        <v/>
+      </c>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>Cyber Valley — بهترین ML آلمان؛ پذیرش بسیار سخت</t>
+        </is>
+      </c>
+      <c r="O54" s="8" t="inlineStr">
+        <is>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>TU München (Garching)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>M.Sc. Informatics</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>€6,000 در ترم برای غیر-EU (€12,000/سال) + €97</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>$13,900</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS؛ ارزیابی استعداد؛ بسیار رقابتی</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>≈ 25</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ TUM از ۲۰۲۴ شهریهٔ غیر-EU می‌گیرد — دیگر «رایگان» نیست؛ Munich گران‌ترین شهر آلمان</t>
+        </is>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>University of Twente (Enschede)</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science (گرایش‌ها: Cyber Security، Data Science، Software Tech، ...)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>€21,700</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>$24,700</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>حداقل رسمی برای مدرک ایرانی ۱۵/۲۰</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی</t>
+        </is>
+      </c>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/education/master/programmes/computer-science/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>University of Twente (Enschede)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>MSc Embedded Systems</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>€21,700</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>$24,700</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>CGPA ≥ ۷۰–۷۵٪؛ کارشناسی CS/EE/Computer Eng</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27؛ مهلت غیر-EU ۱ مه</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>University of Twente (Enschede)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>MSc Interaction Technology</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>HCI / طراحی تعامل / UX</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>€21,700</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>$24,700</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/مرتبط</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>HCI فنی (نه طراحی صرف)</t>
+        </is>
+      </c>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/education/master/programmes/interaction-technology/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Radboud (Nijmegen)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computing Science (گرایش‌ها: Cyber Security، Data Science، Software Science)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>€19,714 (2025/26) → ≈ €20,500</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>$23,400</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS با ریاضی/الگوریتم کافی</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی</t>
+        </is>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/education/masters/computing-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Radboud (Nijmegen)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>€19,714 (2025/26) → ≈ €20,500</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>$23,400</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/AI/مرتبط</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>AI شناختی (Donders Institute)</t>
+        </is>
+      </c>
+      <c r="O60" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/education/masters/artificial-intelligence</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Leiden</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science (گرایش‌ها: Artificial Intelligence، Data Science، ...)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>چندحوزه‌ای (انتخاب گرایش)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>€22,500</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>$25,600</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27؛ نزدیک Den Haag/Amsterdam</t>
+        </is>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>€24,900</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>$28,400</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی AI/CS با ریاضی</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27؛ بورس ASML €5k</t>
+        </is>
+      </c>
+      <c r="O62" s="8" t="inlineStr">
+        <is>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computing Science</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>≈ €21,400 (2025) → ≈ €22,500</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>$25,600</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="L63" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="8" t="inlineStr">
+        <is>
+          <t>https://www.rug.nl/masters/computing-science/?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>MSc Game and Media Technology</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>€25,306</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>$28,800</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS؛ ارشد پژوهشی گزینشی</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L64" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>تنها ارشد پژوهشی بازی هلند؛ Utrecht قطب استودیوهای بازی</t>
+        </is>
+      </c>
+      <c r="O64" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>€25,306</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>$28,800</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/AI؛ گزینشی</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>همان باند شهریهٔ Utrecht 2026/27</t>
+        </is>
+      </c>
+      <c r="O65" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uu.nl/en/masters/artificial-intelligence</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Universiteit van Amsterdam (UvA)</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>MSc Software Engineering (۱ ساله!)</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>≈ €23,540</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>$26,800</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>تنها ارشد ۱ سالهٔ معتبر هلند → کل هزینه نصف؛ اما اجارهٔ Amsterdam €900–1,300</t>
+        </is>
+      </c>
+      <c r="O66" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uva.nl/en/programmes/masters/software-engineering/software-engineering.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Universiteit van Amsterdam (UvA)</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>≈ €26,000</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>$29,600</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی AI/CS با ریاضی قوی؛ بسیار رقابتی</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr"/>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uva.nl/en/programmes/masters/artificial-intelligence/artificial-intelligence.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>TU Eindhoven</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>€21,700</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>$24,700</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/ریاضی؛ گزینش بر اساس معدل</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="L68" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>Brainport (ASML، Philips، NXP)</t>
+        </is>
+      </c>
+      <c r="O68" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tue.nl/en/education/graduate-school/master-data-science-and-artificial-intelligence</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>TU Eindhoven</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>MSc Embedded Systems</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>€21,700</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>$24,700</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/EE؛ گزینش</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="L69" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>ASML/NXP بزرگ‌ترین کارفرمایان Embedded اروپا</t>
+        </is>
+      </c>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tue.nl/en/education/graduate-school/master-embedded-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>TU Delft</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science / MSc Computer &amp; Embedded Systems Engineering</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>€22,290 (2025/26) → ≈ €23,000</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>$26,200</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>معدل ≥ ۷۵٪ / ۲۰٪ برتر</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L70" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>معتبرترین، ولی برای معدل ۱۵.۷۷ دور از دسترس</t>
+        </is>
+      </c>
+      <c r="O70" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tudelft.nl/onderwijs/opleidingen/masters/cs/msc-computer-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Breda University of Applied Sciences (BUas)</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Master Game Technology (۱ ساله)</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>۱ سال</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>≈ €15,200</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>$17,300</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی IT/برنامه‌نویسی/بازی + پیشنهاد پروژه</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>برنامهٔ بازی BUas در اروپا شناخته‌شده است؛ مدرک UAS (نه پژوهشی)</t>
+        </is>
+      </c>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/breda-university-applied-sciences/postgrad/master-game-technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Linköping (LiU)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>SEK 166,000</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>$16,800</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>گزینش بر اساس گروه معدل</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی</t>
+        </is>
+      </c>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>https://liu.se/en/education/program/6mics</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Linköping (LiU)</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>MSc Statistics and Machine Learning</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>≈ SEK 166,000 (همان باند)</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>$16,800</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی با ≥ ۳۰ واحد ریاضی/آمار + برنامه‌نویسی</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>https://liu.se/en/education/program/f7msl</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>MSc Embedded and Intelligent Systems (120 cr)</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>≈ SEK 151,000</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>$15,300</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/EE</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>Volvo/HMS در منطقه؛ بدون رتبهٔ QS</t>
+        </is>
+      </c>
+      <c r="O74" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hh.se/english/education/programmes.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Blekinge Tekniska Högskola – BTH (Karlskrona)</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>MSc Software Engineering (120 cr)</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>SEK 140,000</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>$14,100</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>≥ ۹۰ واحد CS/SE</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>Ericsson و Telenor در Karlskrona؛ ⚠️ نسخهٔ ۶۰ واحدی از راه دور است</t>
+        </is>
+      </c>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bth.se/eng/programmes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>KTH (Stockholm)</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>MSc Machine Learning</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>SEK 190,000</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>$19,200</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/ریاضی قوی؛ بسیار رقابتی</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L76" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>Stockholm گران (اتاق SEK 7–10k)</t>
+        </is>
+      </c>
+      <c r="O76" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>KTH (Stockholm)</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>MSc Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>SEK 190,000</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>$19,200</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr"/>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kth.se/en/studies/master/cybersecurity</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>KTH (Stockholm – Kista)</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>MSc Software Engineering of Distributed Systems</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>SEK 180,000–190,000</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>$18,200–19,200</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>Kista = قطب ICT سوئد (Ericsson)</t>
+        </is>
+      </c>
+      <c r="O78" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kth.se/en/studies/master/software-engineering-of-distributed-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Chalmers (Gothenburg)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science and AI</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>SEK 160,000</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>$16,200</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/ریاضی</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه</t>
+        </is>
+      </c>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/data-science-and-ai-msc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Chalmers (Gothenburg)</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>MSc Software Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>SEK 160,000</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>$16,200</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/SE</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="inlineStr"/>
+      <c r="O80" s="8" t="inlineStr">
+        <is>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/software-engineering-and-technology-msc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Chalmers (Gothenburg)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>MSc Interaction Design and Technologies</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>HCI / طراحی تعامل / UX</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>SEK 160,000</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>$16,200</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/Design</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M81" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="inlineStr"/>
+      <c r="O81" s="8" t="inlineStr">
+        <is>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/interaction-design-and-technologies-msc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>University of Gothenburg (با Chalmers)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>MSc Game Design &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>SEK 145,000 (کل ۲۹۰k؛ ورودی ۲۰۲۷: ۲۹۴k)</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>$14,600–14,800</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/Design/Media</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>Gothenburg: استودیوهای EA DICE/Ghost؛ بازار بازی ضعیف</t>
+        </is>
+      </c>
+      <c r="O82" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>≈ SEK 145,000–150,000</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>$14,600–15,200</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>رتبهٔ بالا با شهریهٔ پایین‌تر از KTH</t>
+        </is>
+      </c>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>https://www.uu.se/en/study/programme/masters-programme-in-computer-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>SEK 152,300</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>$15,400</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/ریاضی</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>شمال سوئد، شهر دانشجویی ارزان؛ کل دوره SEK 304,600</t>
+        </is>
+      </c>
+      <c r="O84" s="8" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science (120 cr)</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>SEK 135,000</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>$13,600</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/مرتبط</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M85" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>ارزان؛ Skövde قطب بازی سوئد (Sweden Game Arena)</t>
+        </is>
+      </c>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>https://www.his.se/en/education/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Mälardalen – MDU (Västerås)</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>MSc Intelligent Embedded Systems</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>≈ SEK 135,000</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>$13,600</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/EE</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>ABB و Westinghouse در Västerås؛ رقم 2024/25</t>
+        </is>
+      </c>
+      <c r="O86" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mdu.se/en/malardalen-university/education</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Mälardalen – MDU (Västerås)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>MSc Software Engineering</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>≈ SEK 135,000</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>$13,600</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/SE</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr"/>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mdu.se/en/malardalen-university/education</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Aalborg University (Aalborg)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science (IT)</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>€14,910 (€7,455 در ترم)</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>$17,000</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/SE</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K88" s="4">
+        <f>329</f>
+        <v/>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)</t>
+        </is>
+      </c>
+      <c r="O88" s="8" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Aalborg University (Aalborg)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>MSc Software</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>€14,910</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>$17,000</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی SE/CS</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K89" s="4">
+        <f>329</f>
+        <v/>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr"/>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/master/software</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Aalborg University (Copenhagen)</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Cyber Security</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>€14,910</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>$17,000</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/EE مرتبط؛ مهلت ۱ مارس</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K90" s="4">
+        <f>329</f>
+        <v/>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>کمپوس کپنهاگ: اجاره بالاتر ولی بازار کار بزرگ</t>
+        </is>
+      </c>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/master/cyber-security/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Aalborg University (Aalborg / Copenhagen)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>MSc Medialogy</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>HCI / طراحی تعامل / UX</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>€14,910</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>$17,000</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی مرتبط (Medialogy، CS، Media Tech)</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K91" s="4">
+        <f>329</f>
+        <v/>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>تعامل، AR/VR، بازی؛ بین HCI و Game</t>
+        </is>
+      </c>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/master/medialogy-aal</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>SDU (Odense)</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>€17,300 (از ورودی سپتامبر ۲۰۲۶؛ قبلاً €13,900)</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>$19,700</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>≥ ۱۰۰ ECTS دروس CS؛ ظرفیت محدود + آزمون</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K92" s="4">
+        <f>283</f>
+        <v/>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ افزایش شهریهٔ ۲۰۲۶ — جدول اصلی اصلاح شد</t>
+        </is>
+      </c>
+      <c r="O92" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>SDU (Odense)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Software Engineering</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>€17,300</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>$19,700</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی SE/CS</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K93" s="4">
+        <f>283</f>
+        <v/>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>گرایش‌های Interactive Tech &amp; Games، Cyber-security &amp; Data Intelligence</t>
+        </is>
+      </c>
+      <c r="O93" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/softwareengineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>SDU (Odense)</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>MSc Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>€17,300</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>$19,700</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/AI</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K94" s="4">
+        <f>283</f>
+        <v/>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>شروع سپتامبر و فوریه</t>
+        </is>
+      </c>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/studyscience</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>SDU (Odense)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Robot Systems</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>€17,300</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>$19,700</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی مرتبط (CS/EE/Mechatronics)</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K95" s="4">
+        <f>283</f>
+        <v/>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>Odense Robotics cluster (Universal Robots، MiR)</t>
+        </is>
+      </c>
+      <c r="O95" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>SDU (Kolding)</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>€17,300</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>$19,700</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی با محتوای کمی/برنامه‌نویسی</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K96" s="4">
+        <f>283</f>
+        <v/>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="inlineStr"/>
+      <c r="O96" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>IT University of Copenhagen (ITU)</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>MSc Games — track Game Technology</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>€13,400 (€6,700 در ترم)</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>$15,300</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>برای track فنی: کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>— (تخصصی)</t>
+        </is>
+      </c>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M97" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>شناخته‌شده‌ترین ارشد بازی اسکاندیناوی؛ Copenhagen (IO Interactive، Unity Copenhagen)</t>
+        </is>
+      </c>
+      <c r="O97" s="8" t="inlineStr">
+        <is>
+          <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/games</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>IT University of Copenhagen (ITU)</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>€13,400</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>$15,300</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/SE با برنامه‌نویسی قابل توجه</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>— (تخصصی)</t>
+        </is>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>ارزان‌ترین شهریهٔ کپنهاگ</t>
+        </is>
+      </c>
+      <c r="O98" s="8" t="inlineStr">
+        <is>
+          <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/computer-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>IT University of Copenhagen (ITU)</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>€13,400</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>$15,300</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی مرتبط با داده/CS</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>— (تخصصی)</t>
+        </is>
+      </c>
+      <c r="L99" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M99" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="inlineStr"/>
+      <c r="O99" s="8" t="inlineStr">
+        <is>
+          <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/data-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>DTU (Kgs. Lyngby)</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Human-Centered Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>€15,000</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>ظرفیت محدود؛ امتیازدهی: معدل ۶۰٪ + سابقهٔ کار ۱۰٪</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>معدل ۱۵.۷۷ در رقابت DTU ضعیف است</t>
+        </is>
+      </c>
+      <c r="O100" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/human-centered-artificial-intelligence</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>DTU (Kgs. Lyngby)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>€15,000</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>۸۰–۹۰ ECTS دروس مرتبط؛ ظرفیت محدود</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="L101" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M101" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr"/>
+      <c r="O101" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>DTU (Kgs. Lyngby)</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>€15,000</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>ظرفیت محدود؛ گزینش با معدل</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="L102" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="M102" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="inlineStr"/>
+      <c r="O102" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/computer-science-and-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>€17,300</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>$19,700</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS با واحدهای مشخص</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
+        </is>
+      </c>
+      <c r="M103" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>Aarhus: دومین شهر، ارزان‌تر از کپنهاگ</t>
+        </is>
+      </c>
+      <c r="O103" s="8" t="inlineStr">
+        <is>
+          <t>https://masters.au.dk/computerscience</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="34" customHeight="1">
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>راهنما: هر ردیف یک برنامهٔ انگلیسی‌زبان است. Safe/Target/Reach نسبت به معدل ۱۵.۷۷/۲۰ (≈ 2:2 بریتانیا / ≈ 2.3 آلمانی / ≈ ۷۹٪) و IELTS ≈ 7 سنجیده شده و پیش‌بینی پذیرش نیست. «≈» یعنی رقم از منبع ثانویه یا سال قبل است — قبل از اقدام صفحهٔ رسمی را چک کنید.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="34" customHeight="1">
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>شهریهٔ دلاری با نرخ نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 و گرد شده به $100. برای ورودی ۲۰۲۸ شهریه‌ها را ۵–۱۰٪ در سال بالاتر فرض کنید. آلمان: عدد فقط سهم ترم (Semesterbeitrag) است که بلیت حمل‌ونقل را هم شامل می‌شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="34" customHeight="1">
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>امتیاز بازار کار (۱–۵) ارزیابی من بر پایهٔ منابع شیت «حوزه‌ها و بازار کار» است، نه آمار رسمی؛ برای هر برنامه فقط حوزه را نشان می‌دهد، نه کیفیت آن دانشگاه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="34" customHeight="1">
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>حذف‌شده‌ها: Essex MSc Computer Games (برای 2025/26 و 2026/27 تعلیق شده)، Hull AI &amp; Data Science (سه رقم متناقض شهریه)، UCD/TCD (2:1 و ≈ €30k → Reach، بررسی نشد)، KU Copenhagen (شهریه تأیید نشد)، NCI/DBS ایرلند (کالج خصوصی، اعتبار کمتر).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O103"/>
+  <mergeCells count="4">
+    <mergeCell ref="B107:O107"/>
+    <mergeCell ref="B105:O105"/>
+    <mergeCell ref="B106:O106"/>
+    <mergeCell ref="B108:O108"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId102"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>حوزه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تقاضای بازار ۲۰۲۶ (۱–۵)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>حقوق شروع نسبت به CS عمومی</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>سازگاری با «فقط انگلیسی»</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>تناسب با پروفایل شایان (Computer Eng، معدل ۱۵.۷۷، ۲ سال IT + ۷ ماه Unity/C#)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ریسک‌ها / واقعیت بازار</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>منابع</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>۵ — قوی‌ترین رشد</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>بالاتر (+۱۰ تا +۲۵٪؛ در آلمان €52–60k، انگلستان £35–45k خارج لندن)</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>بسیار خوب — تیم‌های AI/ML در همهٔ ۶ کشور انگلیسی‌زبان‌اند</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>خوب: پیش‌زمینهٔ Computer Engineering + Python؛ ولی برای برنامه‌های Reach (Tübingen، UvA، KTH، Sheffield) معدل ۱۵.۷۷ کافی نیست — برنامه‌های کاربردی (Passau AI Eng، FAU، Northumbria/Teesside AI، UL AI&amp;ML، Umeå) هدف بگیرید</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>رقابت ورودی شدید؛ بخشی از آگهی‌ها «AI» در عنوان دارند ولی کار مهندسی نرم‌افزار معمولی است؛ مدرک به‌تنهایی بدون پورتفولیو/پروژه کافی نیست</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn/WEF ژانویه ۲۰۲۶ (۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد)؛ Bitkom 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>۴ — بیشترین حجم</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>مرجع (آلمان €48–55k · هلند €40–50k · سوئد SEK 420–540k · دانمارک DKK 500–540k · ایرلند €35–45k · انگلستان £28–35k)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>بسیار خوب</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>بهترین تناسب با سابقهٔ شما (۲ سال IT + Unity/C#)؛ پذیرش ساده‌تر (2:2)؛ در همهٔ کشورها گزینهٔ Safe دارد</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>آگهی‌های جونیور از ۲۰۲۳ کم شده (اثر GenAI)؛ در بریتانیا ۶–۷٪ بیکاری فارغ‌التحصیلان CS — سابقهٔ کار واقعی شما را از این گروه جدا می‌کند</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Bitkom 2025 (۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن)؛ IW 2024 (آگهی‌ها ۲۶٪ کمتر از ۲۰۲۳)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>امنیت سایبری</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>۴ — کمبود ساختاری</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>مساوی تا کمی بالاتر؛ در انگلستان (NCSC-certified) و ایرلند (مراکز امنیت شرکت‌های آمریکایی) خوب</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>خوب — ولی مشاغل دولتی/دفاعی معمولاً به تابعیت یا اقامت بلندمدت نیاز دارند</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>خوب: MSc Cyber با 2:2 در Teesside/Northumbria/MMU/Kent/Royal Holloway/TU Dublin؛ Saarland (رایگان ولی IELTS 7)؛ AAU کپنهاگ</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>عدد «۴.۸ میلیون کمبود» ISC2 در گزارش ۲۰۲۵ حذف شد (نیاز اعلام‌شده بود نه آگهی واقعی)؛ کمبود بودجه دلیل اول جای خالی؛ ۳۱٪ تیم‌ها صفر جونیور دارند → برای اولین شغل، کارآموزی + گواهی (Security+، AZ-500) لازم است</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>ISC2 Workforce Study 2024/2025؛ Kent/Surrey NCSC certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>۴ — پایدار</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>بالاتر از توسعه‌دهندهٔ عمومی (+۵ تا +۱۵٪)؛ DevOps/SRE در دانمارک و سوئد پرتقاضا</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>بسیار خوب</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>خوب: Leicester Cloud Computing، TU Darmstadt DSS، KTH SEDS، DCU Cloud major؛ گواهی AWS/Azure کنار مدرک</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>کمتر «مدرک‌محور» است؛ برنامه‌های خالص Cloud کم‌اند — معمولاً گرایشِ CS/SE است</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>tribexyz 2026 (Data/Cloud Engineer پرجست‌وجوترین در UK/DE)؛ آگهی‌های شرکت‌ها</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>۳ — جونیور اشباع</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>مساوی CS در سطح جونیور؛ بالاتر بعد از ۲–۳ سال</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>بسیار خوب</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>متوسط: مدرک‌های ارزان و Safe زیاد است (Maynooth €17k، Skövde، Brunel، ITU) ولی رقابت جونیور بالاست؛ اگر می‌روید، Data Engineering را انتخاب کنید</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>تعداد فارغ‌التحصیل خیلی بیشتر از جای خالی جونیور؛ آگهی جونیور Data Engineering هم ↓۶۷٪؛ مسیر رایج: تحلیلگر/بک‌اند → مهندس داده</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>research.com 2026؛ careery.pro 2026؛ datadriven.io 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>۴ در آلمان/سوئد؛ ۳ در بقیه</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>مساوی تا کمی بالاتر در صنعت (Bosch، Continental، ABB، Volvo)؛ پایین‌تر در بریتانیا/ایرلند</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>متوسط ⚠️ — تیم‌های R&amp;D انگلیسی‌اند ولی شرکت‌های صنعتی متوسط آلمان/سوئد در عمل زبان محلی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>خوب از نظر پیش‌زمینه (Computer Engineering)؛ گزینه‌ها: Twente ES، Stuttgart INFOTECH، H-BRS Autonomous Systems، FAU Autonomy Tech، Halmstad، MDU، SDU Robot Systems، DTU Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>با معیار «فقط انگلیسی» شما ضعیف‌تر از AI/SE/Cyber؛ وابسته به صنعت خودرو که در ۲۰۲۴–۲۵ آگهی‌هایش کم شد</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Bitkom/IW 2024–25؛ Twente/H-BRS/FAU program pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>HCI / طراحی تعامل / UX</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>۲ — رو به کاهش</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>پایین‌تر از توسعه‌دهنده (−۱۰ تا −۲۵٪)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>خوب</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>ضعیف برای هدف «حقوق شروع بالا»؛ فقط اگر واقعاً به طراحی علاقه دارید (Siegen رایگان، Twente I-Tech، York HCIT، Chalmers IxD، AAU Medialogy)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>آگهی UX ↓۷۱٪ و UXR ↓۷۳٪ نسبت به ۲۰۲۲ و از ۲۰۲۳ ثابت؛ متقاضی به ازای هر آگهی دو برابر شده</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Indeed Hiring Lab تا Q4 2025 (thevoiceofuser, 2026)؛ uxdesigninstitute 2024؛ academyux Q1 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>۲ — کوچک و پرنوسان</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>پایین‌تر از نرم‌افزار عمومی (−۲۰ تا −۴۰٪)؛ استودیوهای بزرگ استثنا</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>خوب (استودیوهای بزرگ انگلیسی‌زبان: لندن، Guildford، Stockholm، Malmö، Copenhagen، Cologne)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>تنها حوزه‌ای که سابقهٔ Unity/C# شما در آن مستقیماً مزیت است؛ اما بازار ۲۰۲۲–۲۵ بدترین دورهٔ خود را داشت — پیشنهاد: ارشد Software/AI بگیرید و بازی را به‌عنوان تخصص/پورتفولیو نگه دارید، مگر Goldsmiths (£22k) یا Cologne Game Lab را با چشم باز انتخاب کنید</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>≈۴۵ هزار اخراج ۲۰۲۲–ژوئیهٔ ۲۰۲۵؛ بیش از ۳۰ استودیو کاملاً بسته شد؛ حقوق برنامه‌نویس Unity ≈۵۰٪ افت؛ Unity Technologies شش دور اخراج</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Wikipedia «2022–2026 video game industry layoffs» (GDC State of the Industry 2026؛ 80.lv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>جمع‌بندی برای شما: (۱) هوش مصنوعی/ML و (۲) مهندسی نرم‌افزار بهترین ترکیب «بازار + پذیرش‌پذیری + انگلیسی» را دارند؛ (۳) امنیت سایبری اگر حاضر به گرفتن گواهی و کارآموزی باشید؛ ابری/DevOps به‌عنوان گرایش داخل CS/SE. علم داده فقط با تمرکز Data Engineering. نهفته/رباتیک قوی است ولی با شرط «فقط انگلیسی» شما نمی‌خواند (کارفرمایان صنعتی آلمان/سوئد). HCI/UX و بازی‌سازی با معیار «حقوق شروع بالا» شما در تضادند — سابقهٔ Unity را به‌عنوان پورتفولیو کنار یک ارشد Software/AI نگه دارید.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:G11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1962,7 +10197,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>آلمان $27–36k  &lt;  ایرلند $32–48k  &lt;  انگلستان $38–65k  &lt;  سوئد $54–65k  &lt;  دانمارک $61–71k  &lt;  هلند $75–90k</t>
+          <t>آلمان $27–36k  &lt;  ایرلند $32–48k  &lt;  انگلستان $38–65k  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k</t>
         </is>
       </c>
     </row>
@@ -2086,13 +10321,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2117,7 +10352,7 @@
           <t>آلمان – EU Blue Card 2026 (€50,700 / €45,934.20)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/visa-residence/types/eu-blue-card</t>
         </is>
@@ -2129,7 +10364,7 @@
           <t>آلمان – Sperrkonto €992/ماه (2026)</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/study-training/study/financing</t>
         </is>
@@ -2141,7 +10376,7 @@
           <t>آلمان – Niederlassungserlaubnis §18c (فارغ‌التحصیلان، ۲ سال، B1)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/visa-residence/living-permanently/permanent-residence</t>
         </is>
@@ -2153,7 +10388,7 @@
           <t>آلمان – Stuttgart MSc Computer Science (انگلیسی، IELTS 7، €1,500/ترم)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc./</t>
         </is>
@@ -2165,7 +10400,7 @@
           <t>آلمان – FAU MSc Artificial Intelligence (انگلیسی، B2)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>https://www.ai.study.fau.eu/prospective-students/living-studying-in-germany/language-proficiency/</t>
         </is>
@@ -2177,7 +10412,7 @@
           <t>آلمان – TU Darmstadt MSc Computer Science</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>https://www.informatik.tu-darmstadt.de/studium_fb20/im_studium/studiengaenge_liste/computer_science_msc.en.jsp</t>
         </is>
@@ -2189,7 +10424,7 @@
           <t>آلمان – TU Dresden MSc Computer Science admission</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>https://tu-dresden.de/ing/informatik/studium/studienangebot/master-studiengaenge/m-sc-computer-science/admission?set_language=en</t>
         </is>
@@ -2201,7 +10436,7 @@
           <t>آلمان – TLScontact Tehran (لیست انتظار دانشجویی)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>https://visas-de.tlscontact.com/en-us/country/ir/vac/irTHR2de</t>
         </is>
@@ -2213,7 +10448,7 @@
           <t>آلمان – وضعیت سفارت تهران (Iran International، اوت ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>https://www.iranintl.com/en/202608115899</t>
         </is>
@@ -2225,7 +10460,7 @@
           <t>آلمان – Fintiba: ساکنان ایران پذیرفته نمی‌شوند</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>https://www.simplegermany.com/best-blocked-account-germany/</t>
         </is>
@@ -2237,7 +10472,7 @@
           <t>آلمان – حقوق توسعه‌دهنده (StepStone)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>https://www.stepstone.de/gehalt/Software-Entwickler-in.html</t>
         </is>
@@ -2249,7 +10484,7 @@
           <t>هلند – IND مبالغ ۲۰۲۶ (HSM €3,122 / €4,357؛ دانشجو €1,130.77)</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>https://ind.nl/en/required-amounts-income-requirements</t>
         </is>
@@ -2261,7 +10496,7 @@
           <t>هلند – Twente شهریه 2026/27 €21,700</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/computer-science/finance/</t>
         </is>
@@ -2273,7 +10508,7 @@
           <t>هلند – Twente حداقل معدل برای مدرک ایرانی (۱۵/۲۰)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/european-studies/admission/international/</t>
         </is>
@@ -2285,7 +10520,7 @@
           <t>هلند – Twente QS 2027 = 223</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/about-us/impact-ambitions/rankings/</t>
         </is>
@@ -2297,7 +10532,7 @@
           <t>هلند – Radboud Computing Science شهریه</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>https://www.mastersportal.com/studies/8984/computing-science.html</t>
         </is>
@@ -2309,7 +10544,7 @@
           <t>هلند – MVV در ایران (سفارت در باکو)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>https://www.netherlandsworldwide.nl/visa-the-netherlands/mvv-long-stay/apply-iran</t>
         </is>
@@ -2321,7 +10556,7 @@
           <t>هلند – B1 برای PR/تابعیت (تصمیم کابینه ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>https://thedutchdaily.nl/dutch-citizenship-b1-language-requirement-confirmed-2026/</t>
         </is>
@@ -2333,7 +10568,7 @@
           <t>سوئد – قوانین جدید اقامت تحصیلی از ۱۱ ژوئن ۲۰۲۶ (۱۵ ساعت/هفته)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/nyheter/news-archive/2026-05-25-new-rules-for-residence-permits-for-studies-in-higher-education.html</t>
         </is>
@@ -2345,7 +10580,7 @@
           <t>سوئد – قوانین جدید مجوز کار از ۱ ژوئن ۲۰۲۶ (SEK 34,470)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/nyheter/news-archive/2026-04-17-new-rules-for-work-permits-from-1-june-2026.html</t>
         </is>
@@ -2357,7 +10592,7 @@
           <t>سوئد – گروه‌های معاف (فارغ‌التحصیلان ۷۵٪)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>https://eiglaw.com/sweden-publishes-exempt-occupations-for-new-salary-rule/</t>
         </is>
@@ -2369,7 +10604,7 @@
           <t>سوئد – مجوز ۱۲ ماهه جست‌وجوی کار و تمکن SEK 10,656</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/en/you-want-to-extend/study/look-for-work-after-completing-your-studies-in-sweden.html</t>
         </is>
@@ -2381,7 +10616,7 @@
           <t>سوئد – Linköping MSc CS شهریه SEK 332,000 (کل)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>https://liu.se/en/education/program/6mics</t>
         </is>
@@ -2393,7 +10628,7 @@
           <t>سوئد – BTH MSc Software Engineering 120 credits (SEK 70,000/ترم)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>https://www.bth.se/english/education/programmes/masters-programme-in-software-engineering-120-credits</t>
         </is>
@@ -2405,7 +10640,7 @@
           <t>سوئد – BTH برنامه ۶۰ واحدی (از راه دور، نیمه‌وقت، ۲ سال سابقه)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>https://www.bth.se/english/education/programmes/masters-programme-in-software-engineering-60-credits</t>
         </is>
@@ -2417,7 +10652,7 @@
           <t>سوئد – Halmstad MSc Information Technology شهریه</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>https://www.mastersportal.com/studies/22787/information-technology.html</t>
         </is>
@@ -2429,7 +10664,7 @@
           <t>سوئد – Halmstad مسکن (بدون تضمین)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>https://www.hh.se/english/education/student-life/find-accommodation.html</t>
         </is>
@@ -2441,7 +10676,7 @@
           <t>سوئد – شهروندی ۸ ساله از ژوئن ۲۰۲۶</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>https://www.imidaily.com/europe/sweden-passes-law-curtailing-naturalization-8-year-wait-income-floor/</t>
         </is>
@@ -2453,7 +10688,7 @@
           <t>سوئد – اطلاعیه مهاجرتی سفارت تهران</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>https://www.swedenabroad.se/globalassets/ambassader/iran-teheran/documents/migration-issues/new-folder/english-versin.pdf</t>
         </is>
@@ -2465,7 +10700,7 @@
           <t>دانمارک – Pay Limit Scheme 2026</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/pl-PL/You-want-to-apply/Work/Pay-limit-scheme</t>
         </is>
@@ -2477,7 +10712,7 @@
           <t>دانمارک – برنامه‌های آموزش عالی: ۹۰ ساعت/ماه، ۶ ماه یا ۳ سال جست‌وجوی کار</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/en-GB/You-want-to-apply/Study/Higher-Education</t>
         </is>
@@ -2489,7 +10724,7 @@
           <t>دانمارک – مجوز ۳ ساله جست‌وجوی کار</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/de-DE/You-want-to-apply/Study/Study---job-seeking/Study---3-years-job-seeking</t>
         </is>
@@ -2501,7 +10736,7 @@
           <t>دانمارک – اقامت دائم</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/de-DE/You-want-to-apply/Permanent-residence-permit/Permanent-residence</t>
         </is>
@@ -2513,7 +10748,7 @@
           <t>دانمارک – تمکن DKK 7,426 (2026)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>https://nyidanmark.dk/en-GB/Words-and-concepts/SIRI/Self-support---SIRI</t>
         </is>
@@ -2525,7 +10760,7 @@
           <t>دانمارک – AAU Computer Science (IT) شهریه €7,455/ترم</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>https://studyindenmark.dk/portal/aalborg-university-aau/aalborg/computer-science-it-msc</t>
         </is>
@@ -2534,408 +10769,912 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – SDU Computer Science شهریه</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi/adgangskrav</t>
+          <t>دانمارک – SDU شهریهٔ رسمی از ورودی ۲۰۲۶: Science/Engineering €17,300 در سال</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – سفارت تهران (درخواست از ایران ممکن نیست)</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>https://iran.um.dk/en</t>
+          <t>دانمارک – SDU MSc Computer Science (ظرفیت محدود، €17,300)</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi/adgangskrav</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – IDA حقوق شروع ۲۰۲۶</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>https://studerende.ida.dk/snart-nyuddannet/loen/softwareingenioer-loen-saa-meget-kommer-du-til-at-tjene/</t>
+          <t>دانمارک – سفارت تهران (درخواست از ایران ممکن نیست)</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>https://iran.um.dk/en</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – کف حقوق مجوز کار از ۱ مارس ۲۰۲۶ (€40,904 / €36,848 / €36,605)</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>https://kodlyons.ie/critical-skills-employment-permit-changes/</t>
+          <t>دانمارک – IDA حقوق شروع ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>https://studerende.ida.dk/snart-nyuddannet/loen/softwareingenioer-loen-saa-meget-kommer-du-til-at-tjene/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – نقشه راه DETE تا ۲۰۳۰</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>https://www.visahq.com/news/2025-12-12/ie/ireland-sets-phased-salary-threshold-hikes-for-all-work-permit-categories-first-rise-due-1-march-2026/</t>
+          <t>ایرلند – کف حقوق مجوز کار از ۱ مارس ۲۰۲۶ (€40,904 / €36,848 / €36,605)</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>https://kodlyons.ie/critical-skills-employment-permit-changes/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – ISD تمکن دانشجویی €10,000</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>https://www.irishimmigration.ie/coming-to-study-in-ireland/what-are-my-study-options/a-fee-paying-private-primary-or-secondary-school/information-on-student-finances/</t>
+          <t>ایرلند – نقشه راه DETE تا ۲۰۳۰</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>https://www.visahq.com/news/2025-12-12/ie/ireland-sets-phased-salary-threshold-hikes-for-all-work-permit-categories-first-rise-due-1-march-2026/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – UL MSc Software Engineering €20,800</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>https://www.ul.ie/study/postgraduate/software-engineering-msc</t>
+          <t>ایرلند – ISD تمکن دانشجویی €10,000</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>https://www.irishimmigration.ie/coming-to-study-in-ireland/what-are-my-study-options/a-fee-paying-private-primary-or-secondary-school/information-on-student-finances/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – Maynooth فهرست شهریه 2025/26</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>https://www.maynoothuniversity.ie/sites/default/files/assets/document/2025.26%20Postgraduate%20EU%20&amp;%20International%20Fees%20List%20(24.02.25)%20V.4%20CHR.pdf</t>
+          <t>ایرلند – UL MSc Software Engineering €20,800</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>https://www.ul.ie/study/postgraduate/software-engineering-msc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – سفارت/کنسول افتخاری تهران</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>https://www.ireland.ie/en/tehran/</t>
+          <t>ایرلند – Maynooth فهرست شهریه 2025/26</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>https://www.maynoothuniversity.ie/sites/default/files/assets/document/2025.26%20Postgraduate%20EU%20&amp;%20International%20Fees%20List%20(24.02.25)%20V.4%20CHR.pdf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – QS 2027 دانشگاه‌های ایرلند</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>https://www.thejournal.ie/irish-universities-qs-world-university-rankings-2027-7073948-Jun2026/</t>
+          <t>ایرلند – سفارت/کنسول افتخاری تهران</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>https://www.ireland.ie/en/tehran/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
+          <t>ایرلند – QS 2027 دانشگاه‌های ایرلند</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>https://www.thejournal.ie/irish-universities-qs-world-university-rankings-2027-7073948-Jun2026/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
+          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
+          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
+          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
+          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
+          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
+          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
+          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
+          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
+          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
+          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
+          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – وضعیت VAC تهران</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
+          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – TU Dresden</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
+          <t>بریتانیا – وضعیت VAC تهران</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Stuttgart</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
+          <t>QS WUR 2027 – TU Dresden</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Newcastle 149</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
+          <t>QS WUR 2027 – Stuttgart</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – York =158</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>https://www.york.ac.uk/about/rankings/</t>
+          <t>QS WUR 2027 – Newcastle 149</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Leicester =314</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/university-leicester</t>
+          <t>QS WUR 2027 – York =158</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/about/rankings/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Essex =438</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/essex-university</t>
+          <t>QS WUR 2027 – Leicester =314</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/university-leicester</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Northumbria =528</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
+          <t>QS WUR 2027 – Essex =438</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/essex-university</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Brunel</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
+          <t>QS WUR 2027 – Northumbria =528</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – سایر</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/world-university-rankings</t>
+          <t>QS WUR 2027 – Brunel</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+          <t>QS WUR 2027 – سایر</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/world-university-rankings</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
+          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
           <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>https://www.xe.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>https://www.isc2.org/research</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند – UL MSc AI &amp; ML: €20,800</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>https://www.ul.ie/study/postgraduate/artificial-intelligence-and-machine-learning-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند – TU Dublin MSc Applied Cyber Security: €14,500، 2:2</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>https://www.tudublin.ie/study/postgraduate/courses/applied-cyber-security/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند – TU Dublin MSc CS (Data Science): €21,750، 2:2 + ۲ سال سابقه</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>https://www.tudublin.ie/study/postgraduate/courses/computing-data-science/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند – DCU MSc Computing majors: €25,000، 2:1، بورس €5,000</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>https://www.dcu.ie/courses/postgraduate/school-computing/msc-computing-major-options</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند – Galway MSc CS (AI) €28,000 / SDD €18,440، 2026/27</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>http://cs.universityofgalway.ie/science-engineering/postgraduateprogrammes/taught-postgraduate-courses/software-design-development.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Siegen MSc HCI (DAAD)</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – RWTH MSc Software Systems Engineering</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Leiden CS 2026/27: €22,500</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Groningen AI 2026/27: €24,900</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – KTH Machine Learning: SEK 190,000</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – Umeå AI: SEK 152,300</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>https://www.study.eu/best-universities/sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – ITU شهریه €6,700 در ترم (Games / CS / Data Science)</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/games</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – Aarhus CS €17,300</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>https://masters.au.dk/computerscience</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
+        </is>
+      </c>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – NTU QS 2027 =639</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
         </is>
       </c>
     </row>
@@ -3010,6 +11749,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منابع" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -606,40 +606,40 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Stuttgart – MSc Computer Science (انگلیسی، بدون NC، IELTS 7) → Target
-FAU – MSc Artificial Intelligence (انگلیسی، B2) → Target
-TU Darmstadt – MSc Computer Science (انگلیسی، IELTS 7) → Target/Reach
-TU Dresden – MSc Computer Science (انگلیسی، IELTS 7، ارزیابی استعداد) → Reach
-Safe: RPTU Kaiserslautern، Passau، Saarland، TU Chemnitz، OVGU Magdeburg</t>
+          <t>Stuttgart (اشتوتگارت) – MSc Computer Science (انگلیسی، بدون NC، IELTS 7) → Target
+FAU (Erlangen/Nürnberg) – MSc Artificial Intelligence (انگلیسی، B2) → Target
+TU Darmstadt (دارمشتات) – MSc Computer Science (انگلیسی، IELTS 7) → Target/Reach
+TU Dresden (درسدن) – MSc Computer Science (انگلیسی، IELTS 7، ارزیابی استعداد) → Reach
+Safe: RPTU Kaiserslautern، Passau، Saarland (Saarbrücken)، TU Chemnitz، OVGU Magdeburg</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Twente – MSc Computer Science (حداقل رسمی برای مدرک ایرانی: ۱۵/۲۰) → Target
-Radboud – MSc Computing Science → Target
+          <t>Twente (Enschede) – MSc Computer Science (حداقل رسمی برای مدرک ایرانی: ۱۵/۲۰) → Target
+Radboud (Nijmegen) – MSc Computing Science → Target
 (هر دو روی واحدهای ریاضی/الگوریتم/CS نظری در ریزنمرات حساس‌اند)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Linköping – MSc Computer Science (گزینش بر اساس گروه معدل) → Target
+          <t>Linköping (لینشوپینگ) – MSc Computer Science (گزینش بر اساس گروه معدل) → Target
 BTH – MSc Software Engineering 120 واحدی، Karlskrona (≥ ۹۰ واحد CS/SE در کارشناسی) → Safe/Target
-Halmstad – MSc Information Technology 120 واحدی → Safe
+Halmstad (هالمستاد) – MSc Information Technology 120 واحدی → Safe
 ⚠️ برنامه ۶۰ واحدی BTH از راه دور/نیمه‌وقت است و برای ویزا کاربرد ندارد</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>AAU – MSc Computer Science (IT) (انگلیسی؛ نه برنامه Computer Science دانمارکی‌زبان) → Target
-SDU Odense – MSc Computer Science → Target
+          <t>AAU (Aalborg) – MSc Computer Science (IT) (انگلیسی؛ نه برنامه Computer Science دانمارکی‌زبان) → Target
+SDU (Odense) – MSc Computer Science → Target
 (پذیرش بر اساس داشتن ≥ ۱۰۰ ECTS دروس کامپیوتر)</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin – MSc Computing (Advanced Software Development) → Safe
-Maynooth – MSc (CS) Software Engineering، ۱ ساله → Safe/Target
-UL – MSc Software Engineering → Target
+          <t>TU Dublin (Dublin) – MSc Computing (Advanced Software Development) → Safe
+Maynooth (۲۵ km از Dublin) – MSc (CS) Software Engineering، ۱ ساله → Safe/Target
+UL (Limerick) – MSc Software Engineering → Target
 (شرط 2.2 honours ≈ معدل شما OK)</t>
         </is>
       </c>
@@ -649,8 +649,8 @@
 Northumbria (Newcastle) – MSc Advanced Computer Science (2:2 در رشته کامپیوتری) → Safe
 Essex (Colchester) – MSc Advanced Computer Science (2:2؛ Computer Engineering پذیرفته می‌شود) → Safe/Target
 Brunel (London) – MSc AI / Data Science (2:2) → Safe/Target
-Leicester – MSc Advanced Computer Science (2:1؛ سابقه کار مرتبط جبران می‌کند) → Target
-York – MSc Advanced Computer Science (2:2 با پیش‌زمینه قوی، IELTS 6.5) → Reach
+Leicester (لستر) – MSc Advanced Computer Science (2:1؛ سابقه کار مرتبط جبران می‌کند) → Target
+York (یورک) – MSc Advanced Computer Science (2:2 با پیش‌زمینه قوی، IELTS 6.5) → Reach
 فقط انگلستان — Strathclyde (اسکاتلند) و Swansea (ولز) حذف شدند</t>
         </is>
       </c>
@@ -2001,24 +2001,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="44" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
@@ -2034,65 +2036,75 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>دانشگاه (شهر)</t>
+          <t>دانشگاه</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>شهر</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>هزینهٔ زندگی شهر (تقریبی، ماهانه با اجاره)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>برنامه</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>حوزه</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>مدت</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>شهریهٔ سالانه 2026/27 (ارز محلی)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>≈ شهریهٔ سالانه به دلار</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>شرط ورود</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>IELTS</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>QS 2027</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Safe / Target / Reach (معدل ۱۵.۷۷)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>بازار کار حوزه (۱–۵) و نکته</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>نکتهٔ برنامه</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>منبع (صفحهٔ رسمی)</t>
         </is>
@@ -2109,65 +2121,75 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Teesside (Middlesbrough)</t>
+          <t>Teesside University</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
+          <t>Middlesbrough (میدلزبرو) — شمال شرق انگلستان</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>ارزان — £950–1,150</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>£17,000</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>$22,500</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>2:2 در رشتهٔ مرتبط</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>— (THE 601–800)</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>ارزان‌ترین گزینهٔ معتبر انگلستان؛ Middlesbrough ارزان ولی بازار کار محلی کوچک</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="Q2" s="8" t="inlineStr">
         <is>
           <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
@@ -2184,65 +2206,75 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Teesside (Middlesbrough)</t>
+          <t>Teesside University</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>Middlesbrough (میدلزبرو) — شمال شرق انگلستان</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>ارزان — £950–1,150</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>£17,000</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>$22,500</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>2:2 در رشتهٔ مرتبط</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>همان باند شهریهٔ Teesside</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_artificial_intelligence.cfm</t>
         </is>
@@ -2259,65 +2291,75 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Teesside (Middlesbrough)</t>
+          <t>Teesside University</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>Middlesbrough (میدلزبرو) — شمال شرق انگلستان</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>ارزان — £950–1,150</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>MSc Cyber Security (BCS accredited)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>£17,000</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>$22,500</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>2:2 در رشتهٔ مرتبط</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>اعتبار BCS؛ بدون NCSC</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_cyber_security.cfm</t>
         </is>
@@ -2334,64 +2376,74 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Northumbria (Newcastle)</t>
+          <t>Northumbria University</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>Newcastle upon Tyne (نیوکاسل) — شمال شرق</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>ارزان تا متوسط — £950–1,250</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>MSc Advanced Computer Science</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>£21,500</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>$28,500</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>2:2 در رشتهٔ کامپیوتری</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K5" s="4">
+      <c r="M5" s="4">
         <f>528</f>
         <v/>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Newcastle: شهر دانشجویی ارزان با بازار فناوری متوسط</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="Q5" s="8" t="inlineStr">
         <is>
           <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
@@ -2408,64 +2460,74 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Northumbria (Newcastle)</t>
+          <t>Northumbria University</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
+          <t>Newcastle upon Tyne (نیوکاسل) — شمال شرق</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>ارزان تا متوسط — £950–1,250</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>£21,500</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>$28,500</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>2:2 در رشتهٔ کامپیوتری/ریاضی</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K6" s="4">
+      <c r="M6" s="4">
         <f>528</f>
         <v/>
       </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>شهریهٔ رسمی 2026/27</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="Q6" s="8" t="inlineStr">
         <is>
           <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-artificial-intelligence-dtfari6/</t>
         </is>
@@ -2482,64 +2544,74 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Nottingham Trent (Nottingham)</t>
+          <t>Nottingham Trent University (NTU)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>Nottingham (ناتینگهام) — میدلندز</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>≈ £19,900</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>$26,400</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>2:2 (≈ ۵۵٪)</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K7" s="4">
+      <c r="M7" s="4">
         <f>639</f>
         <v/>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>رقم از دو مرجع ثانویه؛ صفحهٔ رسمی 2026/27 را قبل از اقدام چک کنید</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>https://www.ntu.ac.uk/study-and-courses/courses</t>
         </is>
@@ -2556,64 +2628,74 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Nottingham Trent (Nottingham)</t>
+          <t>Nottingham Trent University (NTU)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>Nottingham (ناتینگهام) — میدلندز</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>MSc Cyber Security</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>≈ £19,900</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>$26,400</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K8" s="4">
+      <c r="M8" s="4">
         <f>639</f>
         <v/>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>همان باند NTU (≈)</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="Q8" s="8" t="inlineStr">
         <is>
           <t>https://www.ntu.ac.uk/study-and-courses/courses</t>
         </is>
@@ -2630,65 +2712,75 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Manchester Metropolitan (Manchester)</t>
+          <t>Manchester Metropolitan University (MMU)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>Manchester (منچستر) — دومین قطب فناوری انگلستان</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,050–1,350</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>MSc Cyber Security</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>£21,000</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>$27,800</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>2:2 در رشتهٔ کامپیوتری</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>≈ 600–650</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>Manchester دومین قطب فناوری انگلستان؛ شهریهٔ رسمی overseas 2026/27</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="Q9" s="8" t="inlineStr">
         <is>
           <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
         </is>
@@ -2705,64 +2797,74 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Essex (Colchester)</t>
+          <t>University of Essex</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
+          <t>Colchester (کولچستر) — Essex، ۵۰ دقیقه تا لندن</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,350</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
           <t>MSc Advanced Computer Science</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>£24,675</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>$32,700</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>2:2؛ Computer Engineering پذیرفته می‌شود</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="K10" s="4">
+      <c r="M10" s="4">
         <f>438</f>
         <v/>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>۵۰ دقیقه تا لندن؛ دانشکدهٔ CSEE قوی در AI</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="Q10" s="8" t="inlineStr">
         <is>
           <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
@@ -2779,64 +2881,74 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Essex (Colchester)</t>
+          <t>University of Essex</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>Colchester (کولچستر) — Essex، ۵۰ دقیقه تا لندن</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,350</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>£24,675</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>$32,700</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>2:2 در رشتهٔ کامپیوتری/ریاضی</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="K11" s="4">
+      <c r="M11" s="4">
         <f>438</f>
         <v/>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>ورودی اکتبر ۲۰۲۶ تأیید شده</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="Q11" s="8" t="inlineStr">
         <is>
           <t>https://www.essex.ac.uk/courses/pg00457/1/msc-artificial-intelligence</t>
         </is>
@@ -2853,64 +2965,74 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>University of Leicester</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
+          <t>Leicester (لستر) — میدلندز</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>MSc Advanced Computer Science</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>£24,250</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>$32,100</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>2:1 (سابقهٔ کار مرتبط جبران می‌کند)</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K12" s="4">
+      <c r="M12" s="4">
         <f>314</f>
         <v/>
       </c>
-      <c r="L12" s="10" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>رتبهٔ بهتر با شهریهٔ نزدیک Essex</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="Q12" s="8" t="inlineStr">
         <is>
           <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
@@ -2927,60 +3049,70 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>University of Leicester</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
+          <t>Leicester (لستر) — میدلندز</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>£24,250</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>$32,100</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K13" s="4">
+      <c r="M13" s="4">
         <f>314</f>
         <v/>
       </c>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>https://le.ac.uk/courses/artificial-intelligence-msc/2026</t>
         </is>
@@ -2997,64 +3129,74 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>University of Leicester</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
+          <t>Leicester (لستر) — میدلندز</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>MSc Cloud Computing</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>£24,250</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>$32,100</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K14" s="4">
+      <c r="M14" s="4">
         <f>314</f>
         <v/>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>یکی از معدود ارشدهای خالص Cloud در انگلستان</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>https://le.ac.uk/courses/cloud-computing-msc/2026</t>
         </is>
@@ -3071,65 +3213,75 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Brunel (London)</t>
+          <t>Brunel University London</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
+          <t>London – Uxbridge (لندن، غرب؛ کمپوس Brunel)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — £1,400–1,800</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>£24,795</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>$32,900</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>لندن = بازار کار بزرگ ولی زندگی £1,400–1,800/ماه؛ بورس تا £6,000 تضمینی نیست</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
@@ -3146,61 +3298,71 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Brunel (London)</t>
+          <t>Brunel University London</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
+          <t>London – Uxbridge (لندن، غرب؛ کمپوس Brunel)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — £1,400–1,800</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
           <t>MSc Data Science and Analytics</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>£24,795</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>$32,900</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="8" t="inlineStr">
         <is>
           <t>https://www.brunel.ac.uk/study/courses/data-science-and-analytics-msc</t>
         </is>
@@ -3217,65 +3379,75 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Kent (Canterbury)</t>
+          <t>University of Kent</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
+          <t>Canterbury (کنتربری) — Kent</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,350</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>MSc Cyber Security (NCSC fully certified + BCS)</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>≈ £23,500</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>$31,100</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>«good 2:2»</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>415</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>گواهی کامل NCSC = معتبرترین برچسب امنیت در بریتانیا؛ رقم شهریه از مرجع ثانویه</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="Q17" s="8" t="inlineStr">
         <is>
           <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
         </is>
@@ -3292,64 +3464,74 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Royal Holloway (Egham، حومهٔ لندن)</t>
+          <t>Royal Holloway, University of London</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
+          <t>Egham، Surrey (اگام؛ ۴۰ دقیقه تا لندن)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>گران — £1,300–1,600</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
           <t>MSc Information and Cyber Security</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>£25,500</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>$33,800</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K18" s="4">
+      <c r="M18" s="4">
         <f>485</f>
         <v/>
       </c>
-      <c r="L18" s="10" t="inlineStr">
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>قدیمی‌ترین گروه امنیت اطلاعات بریتانیا (ISG)؛ NCSC certified</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="Q18" s="8" t="inlineStr">
         <is>
           <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
         </is>
@@ -3366,65 +3548,75 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Goldsmiths (London)</t>
+          <t>Goldsmiths, University of London</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
+          <t>London – New Cross (لندن، جنوب شرق؛ Goldsmiths)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — £1,400–1,800</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Games Programming</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>توسعه بازی</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>£22,000</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>$29,200</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>مدرک second-class در رشتهٔ برنامه‌نویسی</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>6.5 (6.0)</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>≈ 800–1000</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>پورتفولیوی Unity/C# شما اینجا مستقیماً به کار می‌آید؛ بازار بازی ۲۰۲۲–۲۵ ضعیف</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="Q19" s="8" t="inlineStr">
         <is>
           <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
         </is>
@@ -3441,64 +3633,74 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Surrey (Guildford)</t>
+          <t>University of Surrey</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
+          <t>Guildford (گیلفورد) — Surrey، ۳۵ دقیقه تا لندن؛ قطب بازی‌سازی</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>گران — £1,300–1,600</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>≈ £26,900–27,500</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>$35,600–36,400</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K20" s="4">
+      <c r="M20" s="4">
         <f>246</f>
         <v/>
       </c>
-      <c r="L20" s="10" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>Guildford قطب بازی‌سازی و امنیت بریتانیا (نزدیک لندن)؛ رقم 2025/26 + برآورد 2026/27</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="Q20" s="8" t="inlineStr">
         <is>
           <t>https://www.surrey.ac.uk/postgraduate/artificial-intelligence-msc</t>
         </is>
@@ -3515,60 +3717,70 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Surrey (Guildford)</t>
+          <t>University of Surrey</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
+          <t>Guildford (گیلفورد) — Surrey، ۳۵ دقیقه تا لندن؛ قطب بازی‌سازی</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>گران — £1,300–1,600</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
           <t>MSc Cyber Security (NCSC)</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>£25,900</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>$34,300</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>6.5 (W 6.0)</t>
         </is>
       </c>
-      <c r="K21" s="4">
+      <c r="M21" s="4">
         <f>246</f>
         <v/>
       </c>
-      <c r="L21" s="10" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr"/>
+      <c r="Q21" s="8" t="inlineStr">
         <is>
           <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
         </is>
@@ -3585,64 +3797,74 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>University of York</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
+          <t>York (یورک) — شمال انگلستان</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,350</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
           <t>MSc Advanced Computer Science</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>£32,900</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>$43,600</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>2:2 با پیش‌زمینهٔ قوی</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K22" s="4">
+      <c r="M22" s="4">
         <f>158</f>
         <v/>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>Russell Group؛ گران</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="Q22" s="8" t="inlineStr">
         <is>
           <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
@@ -3659,64 +3881,74 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>University of York</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
+          <t>York (یورک) — شمال انگلستان</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — £1,000–1,350</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
           <t>MSc Human-Centred Interactive Technologies</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>£32,900</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>$43,600</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K23" s="4">
+      <c r="M23" s="4">
         <f>158</f>
         <v/>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>بهترین برنامهٔ HCI انگلستان برای معدل شما؛ ولی بازار UX ضعیف</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="Q23" s="8" t="inlineStr">
         <is>
           <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
         </is>
@@ -3733,65 +3965,75 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Newcastle University (Russell Group)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
+          <t>Newcastle upon Tyne (نیوکاسل) — شمال شرق</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>ارزان تا متوسط — £950–1,250</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Game Engineering</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>توسعه بازی</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>£32,300</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>$42,800</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>2:1 (2:2 با سابقه بررسی می‌شود)</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="N24" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>معتبرترین ارشد مهندسی بازی انگلستان؛ گران</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="Q24" s="8" t="inlineStr">
         <is>
           <t>https://www.ncl.ac.uk/postgraduate/</t>
         </is>
@@ -3808,65 +4050,75 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Lancaster University</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
+          <t>Lancaster (لنکستر) — شمال غرب</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ارزان تا متوسط — £950–1,250</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
           <t>MSc Cyber Security</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>£30,000 (بورس خودکار £4,500 با 2:1)</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>$39,800</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>164</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="N25" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>NCSC-certified؛ شرط 2:1 برای معدل شما سخت است</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="Q25" s="8" t="inlineStr">
         <is>
           <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
         </is>
@@ -3883,65 +4135,75 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>University of Sheffield (Russell Group)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
+          <t>Sheffield (شفیلد) — یورکشایر</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>ارزان تا متوسط — £950–1,250</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>£34,340</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>$45,500</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="N26" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>رتبهٔ بالا، شهریه و شرط ورود بالا</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="Q26" s="8" t="inlineStr">
         <is>
           <t>https://www.sheffield.ac.uk/postgraduate/taught/courses</t>
         </is>
@@ -3958,65 +4220,75 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin (Blanchardstown)</t>
+          <t>TU Dublin</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>Dublin – Blanchardstown (دوبلین، حومهٔ غربی)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — €1,300–1,700</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
           <t>MSc Computing in Applied Cyber Security</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>۱ سال (حضوری + آنلاین)</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>€14,500 (کل دوره)</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>$16,500</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>2:2 (GPA 2.5) در Computing</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>6.5 (6.0)</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>791–800</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>ارزان‌ترین ارشد امنیت ایرلند در یک دانشگاه دولتی</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t>https://www.tudublin.ie/study/postgraduate/courses/applied-cyber-security/</t>
         </is>
@@ -4033,65 +4305,75 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin (Grangegorman)</t>
+          <t>TU Dublin</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
+          <t>Dublin – Grangegorman (دوبلین، مرکز شهر)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — €1,400–1,800</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science (Data Science)</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>۱–۱.۵ سال</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>€21,750 (کل دوره)</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>$24,800</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>2:1، یا 2:2 + ۲ سال سابقهٔ توسعهٔ نرم‌افزار</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>6.5 (6.0)</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>791–800</t>
         </is>
       </c>
-      <c r="L28" s="10" t="inlineStr">
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>۲ سال سابقهٔ کار شما اینجا شرط ورود را جبران می‌کند</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="Q28" s="8" t="inlineStr">
         <is>
           <t>https://www.tudublin.ie/study/postgraduate/courses/computing-data-science/</t>
         </is>
@@ -4108,65 +4390,75 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin (Grangegorman)</t>
+          <t>TU Dublin</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
+          <t>Dublin – Grangegorman (دوبلین، مرکز شهر)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — €1,400–1,800</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
           <t>MSc Computing (Advanced Software Development)</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>≈ €15,000–15,500</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>$17,100–17,700</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>791–800</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>گزینهٔ Safe جدول اصلی</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="Q29" s="8" t="inlineStr">
         <is>
           <t>https://www.tudublin.ie/study/postgraduate/</t>
         </is>
@@ -4183,65 +4475,75 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Maynooth</t>
+          <t>Maynooth University</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
+          <t>Maynooth (مینوث) — ۲۵ کیلومتری دوبلین</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,100–1,400</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
           <t>MSc Data Science and Analytics (۱۲ ماهه، conversion)</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>≈ €17,000</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>$19,400</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>مدرک Level 8 با محتوای ریاضی</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>721–730</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>ورود آسان؛ ولی حوزهٔ اشباع جونیور</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="Q30" s="8" t="inlineStr">
         <is>
           <t>https://www.maynoothuniversity.ie/study-maynooth/postgraduate-studies/courses/msc-data-science-and-analytics</t>
         </is>
@@ -4258,65 +4560,75 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Maynooth</t>
+          <t>Maynooth University</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
+          <t>Maynooth (مینوث) — ۲۵ کیلومتری دوبلین</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,100–1,400</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
           <t>MSc (Computer Science) Software Engineering</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>€18,000 (2025/26) → ≈ €18,500</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>$21,100</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>721–730</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>۲۵ دقیقه تا Dublin با قطار؛ اجاره کمتر از Dublin</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="Q31" s="8" t="inlineStr">
         <is>
           <t>https://www.maynoothuniversity.ie/study-maynooth/postgraduate-studies</t>
         </is>
@@ -4333,65 +4645,75 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>University of Limerick</t>
+          <t>University of Limerick (UL)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>Limerick (لیمریک) — سومین شهر ایرلند</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,100–1,400</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence and Machine Learning</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>€20,800</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>$23,700</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>first یا second class honours در CS/Computer Engineering</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="L32" s="10" t="inlineStr">
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>شهریهٔ رسمی 2026/27؛ Limerick ارزان‌تر از Dublin</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="Q32" s="8" t="inlineStr">
         <is>
           <t>https://www.ul.ie/study/postgraduate/artificial-intelligence-and-machine-learning-msc</t>
         </is>
@@ -4408,65 +4730,75 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>University of Limerick</t>
+          <t>University of Limerick (UL)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
+          <t>Limerick (لیمریک) — سومین شهر ایرلند</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,100–1,400</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
           <t>MSc Software Engineering</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>€20,800</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>$23,700</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="Q33" s="8" t="inlineStr">
         <is>
           <t>https://www.ul.ie/study/postgraduate</t>
         </is>
@@ -4483,65 +4815,75 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Munster TU – MTU (Cork)</t>
+          <t>Munster Technological University (MTU)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
+          <t>Cork (کورک) — دومین شهر؛ مقر اروپایی Apple</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,200–1,500</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
           <t>MSc Cybersecurity</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>≈ €12,000–15,000</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>$13,700–17,100</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>مدرک Level 8 honours در Computing</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>Cork: مقر اروپایی Apple و ده‌ها شرکت امنیت؛ رقم از مراجع ثانویه</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="Q34" s="8" t="inlineStr">
         <is>
           <t>https://www.mtu.ie/courses/</t>
         </is>
@@ -4558,61 +4900,71 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Munster TU – MTU (Cork)</t>
+          <t>Munster Technological University (MTU)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
+          <t>Cork (کورک) — دومین شهر؛ مقر اروپایی Apple</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,200–1,500</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>≈ €15,000</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>$17,100</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Level 8 honours در CS/Eng + ریاضی و کدنویسی قوی</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr"/>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr"/>
+      <c r="Q35" s="8" t="inlineStr">
         <is>
           <t>https://www.mtu.ie/courses/</t>
         </is>
@@ -4629,65 +4981,75 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Dublin City University (Dublin)</t>
+          <t>Dublin City University (DCU)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
+          <t>Dublin – Glasnevin (دوبلین، شمال شهر؛ DCU)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — €1,400–1,800</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
           <t>MSc in Computing — Majors: AI with NLP / Data Analytics / Secure Software Engineering / Cloud Computing</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>چندحوزه‌ای (انتخاب گرایش)</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>€25,000 (−€5,000 بورس دانشکده برای غیر-EU ⇒ €20,000)</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>$22,800–28,500</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>2:1 در CS/Computing</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="N36" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>شرط 2:1؛ ورودی ژانویه ۲۰۲۷ هم دارد</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="Q36" s="8" t="inlineStr">
         <is>
           <t>https://www.dcu.ie/courses/postgraduate/school-computing/msc-computing-major-options</t>
         </is>
@@ -4709,60 +5071,70 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>Galway (گالوی) — غرب ایرلند</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,150–1,450</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>€28,000</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>$31,900</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>First Class (یا 2:1 خوب با تأیید مدیر برنامه)</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>275</t>
         </is>
       </c>
-      <c r="L37" s="12" t="inlineStr">
+      <c r="N37" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>شرط ورود بالا؛ گران</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="Q37" s="8" t="inlineStr">
         <is>
           <t>http://cs.universityofgalway.ie/</t>
         </is>
@@ -4779,65 +5151,75 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>University College Cork (Cork)</t>
+          <t>University College Cork (UCC)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
+          <t>Cork (کورک) — دومین شهر؛ مقر اروپایی Apple</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,200–1,500</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
           <t>MSc Data Science and Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>€28,000</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>$31,900</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>2:1 در CS/ریاضی</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="L38" s="12" t="inlineStr">
+      <c r="N38" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>UCD (QS 100) و TCD (QS 75) هم ≈ €30k و 2:1 → برای معدل شما Reach</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="Q38" s="8" t="inlineStr">
         <is>
           <t>https://www.ucc.ie/en/study/postgrad/</t>
         </is>
@@ -4859,60 +5241,70 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
+          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,100–1,350</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Computer Science (انگلیسی، بدون NC)</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>€1,500 در ترم + ≈ €200 سهم ترم = ≈ €3,400/سال</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>$3,900</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/مرتبط؛ بدون NC</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>7.0 (C1)</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="L39" s="10" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>شهریهٔ بادن-وورتمبرگ برای غیر-EU</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="Q39" s="8" t="inlineStr">
         <is>
           <t>https://www.uni-stuttgart.de/en/study/study-programs/</t>
         </is>
@@ -4934,60 +5326,70 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
+          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,100–1,350</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Information Technology (INFOTECH)</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>€1,500 در ترم + سهم ترم ≈ €3,400/سال</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>$3,900</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>کارشناسی EE/CS/Computer Engineering؛ گزینش</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>7.0 (C1)</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="L40" s="10" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>گرایش‌های Embedded/Communication؛ Bosch و Daimler همان شهر</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="Q40" s="8" t="inlineStr">
         <is>
           <t>https://www.mygermanuniversity.com/master/information-technology-infotech/678</t>
         </is>
@@ -5009,60 +5411,70 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
+          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €950–1,150</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €130 سهم ترم (≈ €260/سال)</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>$300</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/مرتبط؛ بررسی ریزنمرات</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>B2 (IELTS 6.0)</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>218</t>
         </is>
       </c>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>Siemens/adidas/Schaeffler در منطقه</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="Q41" s="8" t="inlineStr">
         <is>
           <t>https://www.fau.eu/degree-program/artificial-intelligence-m-sc/</t>
         </is>
@@ -5084,60 +5496,70 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
+          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €950–1,150</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Autonomy Technologies</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €130 سهم ترم</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>$300</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>کارشناسی مرتبط؛ آلمانی لازم نیست</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>B2 (IELTS 6.0)</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>218</t>
         </is>
       </c>
-      <c r="L42" s="10" t="inlineStr">
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>رباتیک/خودران؛ صفحهٔ رسمی سپتامبر ۲۰۲۶</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="Q42" s="8" t="inlineStr">
         <is>
           <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
@@ -5159,60 +5581,70 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
+          <t>Darmstadt (دارمشتات) — ۲۵ دقیقه تا فرانکفورت</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,050–1,300</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Distributed Software Systems (انگلیسی)</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €300 سهم ترم (≈ €600/سال)</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>$700</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS با پیش‌نیازهای مشخص</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
         <is>
           <t>≈ 7.0 (C1) — چک شود</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="L43" s="11" t="inlineStr">
+      <c r="N43" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>منطقهٔ Rhein-Main (SAP، Deutsche Bank، Software AG)</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="Q43" s="8" t="inlineStr">
         <is>
           <t>https://www.tu-darmstadt.de/studieren/</t>
         </is>
@@ -5234,60 +5666,70 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
+          <t>Dresden (درسدن) — «سیلیکون ساکسونی»</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>ارزان — €850–1,050</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Computer Science (انگلیسی)</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €300 سهم ترم</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>$700</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS؛ ارزیابی استعداد</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="N44" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>Dresden ارزان‌ترین شهر جدول؛ GlobalFoundries/Infineon/Bosch</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="Q44" s="8" t="inlineStr">
         <is>
           <t>https://tu-dresden.de/studium/vor-dem-studium/studienangebot</t>
         </is>
@@ -5304,64 +5746,74 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Saarland University (Saarbrücken)</t>
+          <t>Saarland University (UdS)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
+          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €900–1,100</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Cybersecurity</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €394 سهم ترم (≈ €790/سال)</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>$900</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS + اثبات دروس پایه + ۲ توصیه‌نامه؛ بدون NC</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
         <is>
           <t>7.0 (C1؛ MOI پذیرفته نمی‌شود)</t>
         </is>
       </c>
-      <c r="K45" s="4">
+      <c r="M45" s="4">
         <f>588 (CS ≈ 251)</f>
         <v/>
       </c>
-      <c r="L45" s="10" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>CISPA — بهترین مرکز امنیت آلمان؛ IELTS 7 شرط سخت شماست</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="Q45" s="8" t="inlineStr">
         <is>
           <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
@@ -5378,64 +5830,74 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Saarland University (Saarbrücken)</t>
+          <t>Saarland University (UdS)</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
+          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €900–1,100</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Data Science and Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €394 سهم ترم</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>$900</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/مرتبط؛ بدون NC</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
         <is>
           <t>7.0 (C1)</t>
         </is>
       </c>
-      <c r="K46" s="4">
+      <c r="M46" s="4">
         <f>588 (CS ≈ 251)</f>
         <v/>
       </c>
-      <c r="L46" s="10" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>MPI Informatics و DFKI در همان کمپوس</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="Q46" s="8" t="inlineStr">
         <is>
           <t>https://www.uni-saarland.de/en/study/programmes/master/data-science.html</t>
         </is>
@@ -5457,60 +5919,70 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
+          <t>Chemnitz (کمنیتس) — ساکسونی</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>ارزان — €800–1,000</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Automotive Software Engineering</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €320 سهم ترم (≈ €640/سال)</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>$700</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/مرتبط؛ بدون محدودیت پذیرش</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>B2 (IELTS 5.5)</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="N47" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>آسان‌ترین ورود؛ شهر ارزان؛ ولی صنعت خودرو ۲۰۲۴–۲۵ ضعیف و آلمانی در کارفرمایان محلی</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="Q47" s="8" t="inlineStr">
         <is>
           <t>https://www.mygermanuniversity.com/master/automotive-software-engineering/91</t>
         </is>
@@ -5532,60 +6004,70 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
+          <t>Passau (پاساو) — شهر کوچک، مرز اتریش</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €900–1,100</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Artificial Intelligence Engineering</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €100–200 سهم ترم</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>$300</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>معدل آلمانی ≤ 2.7 (معدل شما ≈ 2.3 ✓)؛ ۳۵ ECTS ریاضی + ۴۰ ECTS CS</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>B2؛ + آلمانی A1 تا پایان سال اول (کلاس رایگان)</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="N48" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>کاملاً انگلیسی؛ شهر کوچک و ارزان</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="Q48" s="8" t="inlineStr">
         <is>
           <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
@@ -5602,61 +6084,71 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>OVGU Magdeburg</t>
+          <t>Otto-von-Guericke-Universität (OVGU)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
+          <t>Magdeburg (ماگدبورگ) — ساکسونی-آنهالت</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>ارزان — €850–1,000</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Data and Knowledge Engineering</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €311 سهم ترم</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>$700</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>معدل آلمانی ≤ 2.3 (معدل شما ≈ 2.27 — دقیقاً مرزی)؛ کارشناسی CS</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
         <is>
           <t>6.0–7.0 (منابع متناقض؛ رسمی را چک کنید)</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L49" s="9" t="inlineStr">
+      <c r="N49" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr"/>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="P49" s="4" t="inlineStr"/>
+      <c r="Q49" s="8" t="inlineStr">
         <is>
           <t>https://www.dke.ovgu.de/</t>
         </is>
@@ -5678,60 +6170,70 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
+          <t>Köln / Cologne (کلن) — چهارمین شهر آلمان</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,050–1,300</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
           <t>M.A. Game Development and Research</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>توسعه بازی</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>€2,500 در ترم (غیر-EU) + €277 سهم ترم ≈ €5,550/سال</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>$6,300</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>هر کارشناسی + ≥ ۱۲ ماه سابقهٔ مرتبط + آزمون استعداد (مهلت ۳۱ مارس)</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>— (UAS)</t>
         </is>
       </c>
-      <c r="L50" s="10" t="inlineStr">
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>معتبرترین مدرسهٔ بازی آلمان؛ ۷ ماه Unity + ۲ سال IT شما احتمالاً شرط ۱۲ ماه را می‌پوشاند — بپرسید</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="Q50" s="8" t="inlineStr">
         <is>
           <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
@@ -5753,60 +6255,70 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
+          <t>Siegen (زیگن) — شهر کوچک، NRW</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €900–1,100</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Human Computer Interaction</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €372 سهم ترم</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>$800</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>معدل آلمانی ≤ 2.5؛ کارشناسی CS/IS/Design/Psychology</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
+      <c r="P51" s="4" t="inlineStr">
         <is>
           <t>شروع زمستان و تابستان؛ شهر کوچک</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="Q51" s="8" t="inlineStr">
         <is>
           <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
@@ -5823,65 +6335,75 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Hochschule Bonn-Rhein-Sieg (Sankt Augustin)</t>
+          <t>Hochschule Bonn-Rhein-Sieg (H-BRS)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
+          <t>Sankt Augustin (زانکت آگوستین) — حومهٔ Bonn</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €950–1,200</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Autonomous Systems</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>€0 + €349 سهم ترم</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>$800</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>معدل آلمانی ≤ 2.5؛ ۲۵ جای محدود؛ آزمون استعداد؛ uni-assist</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>6.5 (B2+)</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>— (UAS)</t>
         </is>
       </c>
-      <c r="L52" s="10" t="inlineStr">
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="P52" s="4" t="inlineStr">
         <is>
           <t>رباتیک کاربردی با Fraunhofer؛ نزدیک Bonn/Köln</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="Q52" s="8" t="inlineStr">
         <is>
           <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
@@ -5903,60 +6425,70 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
+          <t>Aachen (آخن) — مرز هلند/بلژیک</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €950–1,200</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Software Systems Engineering</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>€0 + ≈ €330 سهم ترم</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>$800</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS، معدل ≥ ۶۵٪ (شما ۷۹٪ ✓)؛ ۲ درس پیشرفتهٔ سیستم؛ مهلت ۱ مارس</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="L53" s="4" t="inlineStr">
         <is>
           <t>B2 (IELTS 5.5)</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="L53" s="12" t="inlineStr">
+      <c r="N53" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M53" s="4" t="inlineStr">
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr">
+      <c r="P53" s="4" t="inlineStr">
         <is>
           <t>TU9؛ رقابتی — معدل شما حداقل را رد می‌کند ولی متقاضیان قوی‌ترند</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="Q53" s="8" t="inlineStr">
         <is>
           <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
@@ -5978,59 +6510,69 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
+          <t>Tübingen (توبینگن) — شهر دانشگاهی کوچک؛ Cyber Valley</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,050–1,300</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Machine Learning</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>€1,500 در ترم + ≈ €200 = ≈ €3,400/سال</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>$3,900</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/ریاضی؛ آزمون توانایی؛ مهلت ۳۰ آوریل</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="L54" s="4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="K54" s="4">
+      <c r="M54" s="4">
         <f>230</f>
         <v/>
       </c>
-      <c r="L54" s="12" t="inlineStr">
+      <c r="N54" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="P54" s="4" t="inlineStr">
         <is>
           <t>Cyber Valley — بهترین ML آلمان؛ پذیرش بسیار سخت</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="Q54" s="8" t="inlineStr">
         <is>
           <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
@@ -6047,65 +6589,75 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>TU München (Garching)</t>
+          <t>TU München (TUM)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
+          <t>München – Garching (مونیخ، کمپوس گارشینگ)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — €1,300–1,600</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
           <t>M.Sc. Informatics</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>€6,000 در ترم برای غیر-EU (€12,000/سال) + €97</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>$13,900</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS؛ ارزیابی استعداد؛ بسیار رقابتی</t>
         </is>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>≈ 25</t>
         </is>
       </c>
-      <c r="L55" s="12" t="inlineStr">
+      <c r="N55" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M55" s="4" t="inlineStr">
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N55" s="4" t="inlineStr">
+      <c r="P55" s="4" t="inlineStr">
         <is>
           <t>⚠️ TUM از ۲۰۲۴ شهریهٔ غیر-EU می‌گیرد — دیگر «رایگان» نیست؛ Munich گران‌ترین شهر آلمان</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="Q55" s="8" t="inlineStr">
         <is>
           <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
@@ -6122,65 +6674,75 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>University of Twente (Enschede)</t>
+          <t>University of Twente (UT)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
+          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science (گرایش‌ها: Cyber Security، Data Science، Software Tech، ...)</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>€21,700</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>$24,700</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>حداقل رسمی برای مدرک ایرانی ۱۵/۲۰</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="L56" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
+      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="L56" s="10" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="P56" s="4" t="inlineStr">
         <is>
           <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="Q56" s="8" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/computer-science/</t>
         </is>
@@ -6197,65 +6759,75 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>University of Twente (Enschede)</t>
+          <t>University of Twente (UT)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
+          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
           <t>MSc Embedded Systems</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>€21,700</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>$24,700</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>CGPA ≥ ۷۰–۷۵٪؛ کارشناسی CS/EE/Computer Eng</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="L57" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="L57" s="10" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="P57" s="4" t="inlineStr">
         <is>
           <t>شهریهٔ رسمی 2026/27؛ مهلت غیر-EU ۱ مه</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="Q57" s="8" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
@@ -6272,65 +6844,75 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>University of Twente (Enschede)</t>
+          <t>University of Twente (UT)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
+          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
           <t>MSc Interaction Technology</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>€21,700</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>$24,700</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr">
+      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="L58" s="10" t="inlineStr">
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="P58" s="4" t="inlineStr">
         <is>
           <t>HCI فنی (نه طراحی صرف)</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="Q58" s="8" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/interaction-technology/</t>
         </is>
@@ -6347,65 +6929,75 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Radboud (Nijmegen)</t>
+          <t>Radboud University</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
+          <t>Nijmegen (نایمخن) — شرق هلند</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,050–1,350</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
           <t>MSc Computing Science (گرایش‌ها: Cyber Security، Data Science، Software Science)</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>€19,714 (2025/26) → ≈ €20,500</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>$23,400</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="K59" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS با ریاضی/الگوریتم کافی</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="L59" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="L59" s="10" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="P59" s="4" t="inlineStr">
         <is>
           <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="Q59" s="8" t="inlineStr">
         <is>
           <t>https://www.ru.nl/en/education/masters/computing-science</t>
         </is>
@@ -6422,65 +7014,75 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Radboud (Nijmegen)</t>
+          <t>Radboud University</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
+          <t>Nijmegen (نایمخن) — شرق هلند</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,050–1,350</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>€19,714 (2025/26) → ≈ €20,500</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>$23,400</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/AI/مرتبط</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="L60" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="L60" s="10" t="inlineStr">
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="P60" s="4" t="inlineStr">
         <is>
           <t>AI شناختی (Donders Institute)</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="Q60" s="8" t="inlineStr">
         <is>
           <t>https://www.ru.nl/en/education/masters/artificial-intelligence</t>
         </is>
@@ -6497,65 +7099,75 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Leiden</t>
+          <t>Leiden University</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
+          <t>Leiden (لایدن) — بین Den Haag و Amsterdam</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,200–1,500</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science (گرایش‌ها: Artificial Intelligence، Data Science، ...)</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>چندحوزه‌ای (انتخاب گرایش)</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>€22,500</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>$25,600</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="L61" s="11" t="inlineStr">
+      <c r="N61" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="O61" s="4" t="inlineStr">
         <is>
           <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="P61" s="4" t="inlineStr">
         <is>
           <t>شهریهٔ رسمی 2026/27؛ نزدیک Den Haag/Amsterdam</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="Q61" s="8" t="inlineStr">
         <is>
           <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
@@ -6572,65 +7184,75 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>University of Groningen (RUG)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
+          <t>Groningen (خرونینگن) — شمال هلند</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,050–1,350</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>€24,900</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>$28,400</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>کارشناسی AI/CS با ریاضی</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="L62" s="11" t="inlineStr">
+      <c r="N62" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>شهریهٔ رسمی 2026/27؛ بورس ASML €5k</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="Q62" s="8" t="inlineStr">
         <is>
           <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
@@ -6647,61 +7269,71 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>University of Groningen (RUG)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
+          <t>Groningen (خرونینگن) — شمال هلند</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,050–1,350</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
           <t>MSc Computing Science</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>≈ €21,400 (2025) → ≈ €22,500</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>$25,600</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr">
+      <c r="K63" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="L63" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="O63" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr"/>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="P63" s="4" t="inlineStr"/>
+      <c r="Q63" s="8" t="inlineStr">
         <is>
           <t>https://www.rug.nl/masters/computing-science/?lang=en</t>
         </is>
@@ -6718,65 +7350,75 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Utrecht University</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
+          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,200–1,500</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
           <t>MSc Game and Media Technology</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>توسعه بازی</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>€25,306</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>$28,800</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS؛ ارشد پژوهشی گزینشی</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="L64" s="12" t="inlineStr">
+      <c r="N64" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M64" s="4" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>تنها ارشد پژوهشی بازی هلند؛ Utrecht قطب استودیوهای بازی</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="Q64" s="8" t="inlineStr">
         <is>
           <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
@@ -6793,65 +7435,75 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Utrecht University</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
+          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,200–1,500</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>€25,306</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>$28,800</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="K65" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/AI؛ گزینشی</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="L65" s="12" t="inlineStr">
+      <c r="N65" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr">
+      <c r="O65" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N65" s="4" t="inlineStr">
+      <c r="P65" s="4" t="inlineStr">
         <is>
           <t>همان باند شهریهٔ Utrecht 2026/27</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="Q65" s="8" t="inlineStr">
         <is>
           <t>https://www.uu.nl/en/masters/artificial-intelligence</t>
         </is>
@@ -6868,65 +7520,75 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Universiteit van Amsterdam (UvA)</t>
+          <t>University of Amsterdam (UvA)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
+          <t>Amsterdam (آمستردام)</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — €1,300–1,700</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
           <t>MSc Software Engineering (۱ ساله!)</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>≈ €23,540</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
         <is>
           <t>$26,800</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="K66" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr">
+      <c r="M66" s="4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L66" s="11" t="inlineStr">
+      <c r="N66" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr">
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="P66" s="4" t="inlineStr">
         <is>
           <t>تنها ارشد ۱ سالهٔ معتبر هلند → کل هزینه نصف؛ اما اجارهٔ Amsterdam €900–1,300</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="Q66" s="8" t="inlineStr">
         <is>
           <t>https://www.uva.nl/en/programmes/masters/software-engineering/software-engineering.html</t>
         </is>
@@ -6943,61 +7605,71 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Universiteit van Amsterdam (UvA)</t>
+          <t>University of Amsterdam (UvA)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
+          <t>Amsterdam (آمستردام)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — €1,300–1,700</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>≈ €26,000</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>$29,600</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="K67" s="4" t="inlineStr">
         <is>
           <t>کارشناسی AI/CS با ریاضی قوی؛ بسیار رقابتی</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L67" s="12" t="inlineStr">
+      <c r="N67" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M67" s="4" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N67" s="4" t="inlineStr"/>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="P67" s="4" t="inlineStr"/>
+      <c r="Q67" s="8" t="inlineStr">
         <is>
           <t>https://www.uva.nl/en/programmes/masters/artificial-intelligence/artificial-intelligence.html</t>
         </is>
@@ -7014,65 +7686,75 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>TU Eindhoven</t>
+          <t>TU Eindhoven (TU/e)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
+          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,100–1,400</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
           <t>MSc Data Science and Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>€21,700</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>$24,700</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="K68" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/ریاضی؛ گزینش بر اساس معدل</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K68" s="4" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="L68" s="12" t="inlineStr">
+      <c r="N68" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="P68" s="4" t="inlineStr">
         <is>
           <t>Brainport (ASML، Philips، NXP)</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="Q68" s="8" t="inlineStr">
         <is>
           <t>https://www.tue.nl/en/education/graduate-school/master-data-science-and-artificial-intelligence</t>
         </is>
@@ -7089,65 +7771,75 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>TU Eindhoven</t>
+          <t>TU Eindhoven (TU/e)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
+          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,100–1,400</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
           <t>MSc Embedded Systems</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
         <is>
           <t>€21,700</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>$24,700</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="K69" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/EE؛ گزینش</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="L69" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="L69" s="12" t="inlineStr">
+      <c r="N69" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M69" s="4" t="inlineStr">
+      <c r="O69" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="P69" s="4" t="inlineStr">
         <is>
           <t>ASML/NXP بزرگ‌ترین کارفرمایان Embedded اروپا</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="Q69" s="8" t="inlineStr">
         <is>
           <t>https://www.tue.nl/en/education/graduate-school/master-embedded-systems</t>
         </is>
@@ -7169,60 +7861,70 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
+          <t>Delft (دلفت) — کنار Den Haag/Rotterdam</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>گران — €1,200–1,500</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science / MSc Computer &amp; Embedded Systems Engineering</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>€22,290 (2025/26) → ≈ €23,000</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>$26,200</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="K70" s="4" t="inlineStr">
         <is>
           <t>معدل ≥ ۷۵٪ / ۲۰٪ برتر</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="L70" s="4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
+      <c r="M70" s="4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="L70" s="12" t="inlineStr">
+      <c r="N70" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M70" s="4" t="inlineStr">
+      <c r="O70" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="P70" s="4" t="inlineStr">
         <is>
           <t>معتبرترین، ولی برای معدل ۱۵.۷۷ دور از دسترس</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="Q70" s="8" t="inlineStr">
         <is>
           <t>https://www.tudelft.nl/onderwijs/opleidingen/masters/cs/msc-computer-science</t>
         </is>
@@ -7244,60 +7946,70 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
+          <t>Breda (بردا) — جنوب هلند</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — €1,000–1,300</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
           <t>Master Game Technology (۱ ساله)</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>توسعه بازی</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t>۱ سال</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="I71" s="4" t="inlineStr">
         <is>
           <t>≈ €15,200</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
         <is>
           <t>$17,300</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr">
+      <c r="K71" s="4" t="inlineStr">
         <is>
           <t>کارشناسی IT/برنامه‌نویسی/بازی + پیشنهاد پروژه</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="L71" s="4" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr">
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>— (UAS)</t>
         </is>
       </c>
-      <c r="L71" s="9" t="inlineStr">
+      <c r="N71" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="O71" s="4" t="inlineStr">
         <is>
           <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="P71" s="4" t="inlineStr">
         <is>
           <t>برنامهٔ بازی BUas در اروپا شناخته‌شده است؛ مدرک UAS (نه پژوهشی)</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="Q71" s="8" t="inlineStr">
         <is>
           <t>https://www.topuniversities.com/universities/breda-university-applied-sciences/postgrad/master-game-technology</t>
         </is>
@@ -7314,65 +8026,75 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Linköping (LiU)</t>
+          <t>Linköping University (LiU)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
+          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — SEK 10,500–12,500</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="I72" s="4" t="inlineStr">
         <is>
           <t>SEK 166,000</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>$16,800</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
+      <c r="K72" s="4" t="inlineStr">
         <is>
           <t>گزینش بر اساس گروه معدل</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="L72" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K72" s="4" t="inlineStr">
+      <c r="M72" s="4" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="L72" s="10" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr">
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="P72" s="4" t="inlineStr">
         <is>
           <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="Q72" s="8" t="inlineStr">
         <is>
           <t>https://liu.se/en/education/program/6mics</t>
         </is>
@@ -7389,61 +8111,71 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Linköping (LiU)</t>
+          <t>Linköping University (LiU)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
+          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — SEK 10,500–12,500</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
           <t>MSc Statistics and Machine Learning</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="I73" s="4" t="inlineStr">
         <is>
           <t>≈ SEK 166,000 (همان باند)</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr">
         <is>
           <t>$16,800</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr">
+      <c r="K73" s="4" t="inlineStr">
         <is>
           <t>کارشناسی با ≥ ۳۰ واحد ریاضی/آمار + برنامه‌نویسی</t>
         </is>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="L73" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
+      <c r="M73" s="4" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="L73" s="10" t="inlineStr">
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M73" s="4" t="inlineStr">
+      <c r="O73" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N73" s="4" t="inlineStr"/>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="P73" s="4" t="inlineStr"/>
+      <c r="Q73" s="8" t="inlineStr">
         <is>
           <t>https://liu.se/en/education/program/f7msl</t>
         </is>
@@ -7460,65 +8192,75 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Halmstad University</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
+          <t>Halmstad (هالمستاد) — غرب سوئد</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — SEK 10,000–12,000</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
           <t>MSc Embedded and Intelligent Systems (120 cr)</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>≈ SEK 151,000</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>$15,300</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="K74" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/EE</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="M74" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="N74" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="P74" s="4" t="inlineStr">
         <is>
           <t>Volvo/HMS در منطقه؛ بدون رتبهٔ QS</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="Q74" s="8" t="inlineStr">
         <is>
           <t>https://www.hh.se/english/education/programmes.html</t>
         </is>
@@ -7535,65 +8277,75 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Blekinge Tekniska Högskola – BTH (Karlskrona)</t>
+          <t>Blekinge Institute of Technology (BTH)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
+          <t>Karlskrona (کارلسکرونا) — Ericsson، Telenor</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>ارزان — SEK 9,500–11,500</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
           <t>MSc Software Engineering (120 cr)</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="I75" s="4" t="inlineStr">
         <is>
           <t>SEK 140,000</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>$14,100</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>≥ ۹۰ واحد CS/SE</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="N75" s="9" t="inlineStr">
         <is>
           <t>Safe/Target</t>
         </is>
       </c>
-      <c r="M75" s="4" t="inlineStr">
+      <c r="O75" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N75" s="4" t="inlineStr">
+      <c r="P75" s="4" t="inlineStr">
         <is>
           <t>Ericsson و Telenor در Karlskrona؛ ⚠️ نسخهٔ ۶۰ واحدی از راه دور است</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="Q75" s="8" t="inlineStr">
         <is>
           <t>https://www.bth.se/eng/programmes/</t>
         </is>
@@ -7610,65 +8362,75 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>KTH (Stockholm)</t>
+          <t>KTH Royal Institute of Technology</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
+          <t>Stockholm (استکهلم)</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>گران — SEK 12,500–15,000</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
           <t>MSc Machine Learning</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>SEK 190,000</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>$19,200</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/ریاضی قوی؛ بسیار رقابتی</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="M76" s="4" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="L76" s="12" t="inlineStr">
+      <c r="N76" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M76" s="4" t="inlineStr">
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="P76" s="4" t="inlineStr">
         <is>
           <t>Stockholm گران (اتاق SEK 7–10k)</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="Q76" s="8" t="inlineStr">
         <is>
           <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
@@ -7685,61 +8447,71 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>KTH (Stockholm)</t>
+          <t>KTH Royal Institute of Technology</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
+          <t>Stockholm (استکهلم)</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>گران — SEK 12,500–15,000</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
           <t>MSc Cybersecurity</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>SEK 190,000</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>$19,200</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="K77" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="L77" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
+      <c r="M77" s="4" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="L77" s="12" t="inlineStr">
+      <c r="N77" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M77" s="4" t="inlineStr">
+      <c r="O77" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N77" s="4" t="inlineStr"/>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="P77" s="4" t="inlineStr"/>
+      <c r="Q77" s="8" t="inlineStr">
         <is>
           <t>https://www.kth.se/en/studies/master/cybersecurity</t>
         </is>
@@ -7756,65 +8528,75 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>KTH (Stockholm – Kista)</t>
+          <t>KTH Royal Institute of Technology</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
+          <t>Stockholm – Kista (استکهلم، شیستا؛ قطب ICT)</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>گران — SEK 12,500–15,000</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
           <t>MSc Software Engineering of Distributed Systems</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>SEK 180,000–190,000</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>$18,200–19,200</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="L78" s="11" t="inlineStr">
+      <c r="N78" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M78" s="4" t="inlineStr">
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
         </is>
       </c>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="P78" s="4" t="inlineStr">
         <is>
           <t>Kista = قطب ICT سوئد (Ericsson)</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="Q78" s="8" t="inlineStr">
         <is>
           <t>https://www.kth.se/en/studies/master/software-engineering-of-distributed-systems</t>
         </is>
@@ -7831,65 +8613,75 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Chalmers (Gothenburg)</t>
+          <t>Chalmers University of Technology</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
           <t>MSc Data Science and AI</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>SEK 160,000</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
         <is>
           <t>$16,200</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="K79" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/ریاضی</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="L79" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="L79" s="11" t="inlineStr">
+      <c r="N79" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M79" s="4" t="inlineStr">
+      <c r="O79" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
+      <c r="P79" s="4" t="inlineStr">
         <is>
           <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="Q79" s="8" t="inlineStr">
         <is>
           <t>https://www.chalmers.se/en/education/find-masters-programme/data-science-and-ai-msc/</t>
         </is>
@@ -7906,61 +8698,71 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Chalmers (Gothenburg)</t>
+          <t>Chalmers University of Technology</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
           <t>MSc Software Engineering and Technology</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>SEK 160,000</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>$16,200</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/SE</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="L80" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="L80" s="10" t="inlineStr">
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N80" s="4" t="inlineStr"/>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="P80" s="4" t="inlineStr"/>
+      <c r="Q80" s="8" t="inlineStr">
         <is>
           <t>https://www.chalmers.se/en/education/find-masters-programme/software-engineering-and-technology-msc/</t>
         </is>
@@ -7977,61 +8779,71 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Chalmers (Gothenburg)</t>
+          <t>Chalmers University of Technology</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
           <t>MSc Interaction Design and Technologies</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>SEK 160,000</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
+      <c r="J81" s="4" t="inlineStr">
         <is>
           <t>$16,200</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr">
+      <c r="K81" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/Design</t>
         </is>
       </c>
-      <c r="J81" s="4" t="inlineStr">
+      <c r="L81" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K81" s="4" t="inlineStr">
+      <c r="M81" s="4" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="L81" s="10" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M81" s="4" t="inlineStr">
+      <c r="O81" s="4" t="inlineStr">
         <is>
           <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
-      <c r="N81" s="4" t="inlineStr"/>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="P81" s="4" t="inlineStr"/>
+      <c r="Q81" s="8" t="inlineStr">
         <is>
           <t>https://www.chalmers.se/en/education/find-masters-programme/interaction-design-and-technologies-msc/</t>
         </is>
@@ -8048,65 +8860,75 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>University of Gothenburg (با Chalmers)</t>
+          <t>University of Gothenburg (مشترک با Chalmers)</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
           <t>MSc Game Design &amp; Technology</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>توسعه بازی</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>SEK 145,000 (کل ۲۹۰k؛ ورودی ۲۰۲۷: ۲۹۴k)</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>$14,600–14,800</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/Design/Media</t>
         </is>
       </c>
-      <c r="J82" s="4" t="inlineStr">
+      <c r="L82" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr">
+      <c r="M82" s="4" t="inlineStr">
         <is>
           <t>225</t>
         </is>
       </c>
-      <c r="L82" s="10" t="inlineStr">
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M82" s="4" t="inlineStr">
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="P82" s="4" t="inlineStr">
         <is>
           <t>Gothenburg: استودیوهای EA DICE/Ghost؛ بازار بازی ضعیف</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="Q82" s="8" t="inlineStr">
         <is>
           <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
@@ -8123,65 +8945,75 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Uppsala University</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
+          <t>Uppsala (اوپسالا) — ۴۰ دقیقه تا استکهلم</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>متوسط تا گران — SEK 11,000–13,000</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="I83" s="4" t="inlineStr">
         <is>
           <t>≈ SEK 145,000–150,000</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr">
         <is>
           <t>$14,600–15,200</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="K83" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="L83" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="M83" s="4" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="L83" s="11" t="inlineStr">
+      <c r="N83" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M83" s="4" t="inlineStr">
+      <c r="O83" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N83" s="4" t="inlineStr">
+      <c r="P83" s="4" t="inlineStr">
         <is>
           <t>رتبهٔ بالا با شهریهٔ پایین‌تر از KTH</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="Q83" s="8" t="inlineStr">
         <is>
           <t>https://www.uu.se/en/study/programme/masters-programme-in-computer-science</t>
         </is>
@@ -8198,65 +9030,75 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Umeå University</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
+          <t>Umeå (اومئو) — شمال سوئد</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>ارزان تا متوسط — SEK 10,000–12,000</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>SEK 152,300</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>$15,400</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/ریاضی</t>
         </is>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="L84" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K84" s="4" t="inlineStr">
+      <c r="M84" s="4" t="inlineStr">
         <is>
           <t>438</t>
         </is>
       </c>
-      <c r="L84" s="10" t="inlineStr">
+      <c r="N84" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M84" s="4" t="inlineStr">
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="P84" s="4" t="inlineStr">
         <is>
           <t>شمال سوئد، شهر دانشجویی ارزان؛ کل دوره SEK 304,600</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="Q84" s="8" t="inlineStr">
         <is>
           <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
@@ -8273,65 +9115,75 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Skövde</t>
+          <t>University of Skövde</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
+          <t>Skövde (شوده) — Sweden Game Arena</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>ارزان — SEK 9,500–11,500</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
           <t>MSc Data Science (120 cr)</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="H85" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="I85" s="4" t="inlineStr">
         <is>
           <t>SEK 135,000</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
+      <c r="J85" s="4" t="inlineStr">
         <is>
           <t>$13,600</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr">
+      <c r="K85" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
-      <c r="J85" s="4" t="inlineStr">
+      <c r="L85" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K85" s="4" t="inlineStr">
+      <c r="M85" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="N85" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M85" s="4" t="inlineStr">
+      <c r="O85" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N85" s="4" t="inlineStr">
+      <c r="P85" s="4" t="inlineStr">
         <is>
           <t>ارزان؛ Skövde قطب بازی سوئد (Sweden Game Arena)</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="Q85" s="8" t="inlineStr">
         <is>
           <t>https://www.his.se/en/education/</t>
         </is>
@@ -8348,65 +9200,75 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Mälardalen – MDU (Västerås)</t>
+          <t>Mälardalen University (MDU)</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
+          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — SEK 10,000–12,000</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
           <t>MSc Intelligent Embedded Systems</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>≈ SEK 135,000</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr">
+      <c r="J86" s="4" t="inlineStr">
         <is>
           <t>$13,600</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
+      <c r="K86" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/EE</t>
         </is>
       </c>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="L86" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K86" s="4" t="inlineStr">
+      <c r="M86" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="N86" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M86" s="4" t="inlineStr">
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="P86" s="4" t="inlineStr">
         <is>
           <t>ABB و Westinghouse در Västerås؛ رقم 2024/25</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="Q86" s="8" t="inlineStr">
         <is>
           <t>https://www.mdu.se/en/malardalen-university/education</t>
         </is>
@@ -8423,61 +9285,71 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Mälardalen – MDU (Västerås)</t>
+          <t>Mälardalen University (MDU)</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
+          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — SEK 10,000–12,000</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
           <t>MSc Software Engineering</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>≈ SEK 135,000</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>$13,600</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr">
+      <c r="K87" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/SE</t>
         </is>
       </c>
-      <c r="J87" s="4" t="inlineStr">
+      <c r="L87" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K87" s="4" t="inlineStr">
+      <c r="M87" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="N87" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="M87" s="4" t="inlineStr">
+      <c r="O87" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N87" s="4" t="inlineStr"/>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="P87" s="4" t="inlineStr"/>
+      <c r="Q87" s="8" t="inlineStr">
         <is>
           <t>https://www.mdu.se/en/malardalen-university/education</t>
         </is>
@@ -8494,64 +9366,74 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (Aalborg)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
+          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — DKK 8,000–9,500</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science (IT)</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>€14,910 (€7,455 در ترم)</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
+      <c r="J88" s="4" t="inlineStr">
         <is>
           <t>$17,000</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
+      <c r="K88" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/SE</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="L88" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K88" s="4">
+      <c r="M88" s="4">
         <f>329</f>
         <v/>
       </c>
-      <c r="L88" s="10" t="inlineStr">
+      <c r="N88" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M88" s="4" t="inlineStr">
+      <c r="O88" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="P88" s="4" t="inlineStr">
         <is>
           <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="Q88" s="8" t="inlineStr">
         <is>
           <t>https://www.en.aau.dk/education/master/computer-science-it</t>
         </is>
@@ -8568,60 +9450,70 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (Aalborg)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
+          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — DKK 8,000–9,500</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
           <t>MSc Software</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="I89" s="4" t="inlineStr">
         <is>
           <t>€14,910</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
+      <c r="J89" s="4" t="inlineStr">
         <is>
           <t>$17,000</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr">
+      <c r="K89" s="4" t="inlineStr">
         <is>
           <t>کارشناسی SE/CS</t>
         </is>
       </c>
-      <c r="J89" s="4" t="inlineStr">
+      <c r="L89" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K89" s="4">
+      <c r="M89" s="4">
         <f>329</f>
         <v/>
       </c>
-      <c r="L89" s="10" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M89" s="4" t="inlineStr">
+      <c r="O89" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N89" s="4" t="inlineStr"/>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="P89" s="4" t="inlineStr"/>
+      <c r="Q89" s="8" t="inlineStr">
         <is>
           <t>https://www.en.aau.dk/education/master/software</t>
         </is>
@@ -8638,64 +9530,74 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (Copenhagen)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
+          <t>Copenhagen – Sydhavn (کپنهاگ؛ کمپوس AAU)</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 10,000–12,500</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
           <t>MSc Eng Cyber Security</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>امنیت سایبری</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="I90" s="4" t="inlineStr">
         <is>
           <t>€14,910</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="J90" s="4" t="inlineStr">
         <is>
           <t>$17,000</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="K90" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/EE مرتبط؛ مهلت ۱ مارس</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="L90" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K90" s="4">
+      <c r="M90" s="4">
         <f>329</f>
         <v/>
       </c>
-      <c r="L90" s="10" t="inlineStr">
+      <c r="N90" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M90" s="4" t="inlineStr">
+      <c r="O90" s="4" t="inlineStr">
         <is>
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="P90" s="4" t="inlineStr">
         <is>
           <t>کمپوس کپنهاگ: اجاره بالاتر ولی بازار کار بزرگ</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="Q90" s="8" t="inlineStr">
         <is>
           <t>https://www.en.aau.dk/education/master/cyber-security/</t>
         </is>
@@ -8712,64 +9614,74 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (Aalborg / Copenhagen)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
+          <t>Aalborg یا Copenhagen (هر دو کمپوس)</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>متوسط (Aalborg) تا خیلی گران (Copenhagen)</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
           <t>MSc Medialogy</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="G91" s="4" t="inlineStr">
         <is>
           <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="H91" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="I91" s="4" t="inlineStr">
         <is>
           <t>€14,910</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
+      <c r="J91" s="4" t="inlineStr">
         <is>
           <t>$17,000</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr">
+      <c r="K91" s="4" t="inlineStr">
         <is>
           <t>کارشناسی مرتبط (Medialogy، CS، Media Tech)</t>
         </is>
       </c>
-      <c r="J91" s="4" t="inlineStr">
+      <c r="L91" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K91" s="4">
+      <c r="M91" s="4">
         <f>329</f>
         <v/>
       </c>
-      <c r="L91" s="10" t="inlineStr">
+      <c r="N91" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M91" s="4" t="inlineStr">
+      <c r="O91" s="4" t="inlineStr">
         <is>
           <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
-      <c r="N91" s="4" t="inlineStr">
+      <c r="P91" s="4" t="inlineStr">
         <is>
           <t>تعامل، AR/VR، بازی؛ بین HCI و Game</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="Q91" s="8" t="inlineStr">
         <is>
           <t>https://www.en.aau.dk/education/master/medialogy-aal</t>
         </is>
@@ -8786,64 +9698,74 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>SDU (Odense)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — DKK 8,000–10,000</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>€17,300 (از ورودی سپتامبر ۲۰۲۶؛ قبلاً €13,900)</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="J92" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr">
+      <c r="K92" s="4" t="inlineStr">
         <is>
           <t>≥ ۱۰۰ ECTS دروس CS؛ ظرفیت محدود + آزمون</t>
         </is>
       </c>
-      <c r="J92" s="4" t="inlineStr">
+      <c r="L92" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K92" s="4">
+      <c r="M92" s="4">
         <f>283</f>
         <v/>
       </c>
-      <c r="L92" s="10" t="inlineStr">
+      <c r="N92" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M92" s="4" t="inlineStr">
+      <c r="O92" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="P92" s="4" t="inlineStr">
         <is>
           <t>⚠️ افزایش شهریهٔ ۲۰۲۶ — جدول اصلی اصلاح شد</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="Q92" s="8" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
         </is>
@@ -8860,64 +9782,74 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>SDU (Odense)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — DKK 8,000–10,000</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
           <t>MSc Eng Software Engineering</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="H93" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G93" s="4" t="inlineStr">
+      <c r="I93" s="4" t="inlineStr">
         <is>
           <t>€17,300</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr">
+      <c r="J93" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr">
+      <c r="K93" s="4" t="inlineStr">
         <is>
           <t>کارشناسی SE/CS</t>
         </is>
       </c>
-      <c r="J93" s="4" t="inlineStr">
+      <c r="L93" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K93" s="4">
+      <c r="M93" s="4">
         <f>283</f>
         <v/>
       </c>
-      <c r="L93" s="10" t="inlineStr">
+      <c r="N93" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M93" s="4" t="inlineStr">
+      <c r="O93" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N93" s="4" t="inlineStr">
+      <c r="P93" s="4" t="inlineStr">
         <is>
           <t>گرایش‌های Interactive Tech &amp; Games، Cyber-security &amp; Data Intelligence</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="Q93" s="8" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/kandidat/softwareengineering</t>
         </is>
@@ -8934,64 +9866,74 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>SDU (Odense)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — DKK 8,000–10,000</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
           <t>MSc Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr">
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t>€17,300</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr">
+      <c r="K94" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/AI</t>
         </is>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="L94" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K94" s="4">
+      <c r="M94" s="4">
         <f>283</f>
         <v/>
       </c>
-      <c r="L94" s="10" t="inlineStr">
+      <c r="N94" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M94" s="4" t="inlineStr">
+      <c r="O94" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="P94" s="4" t="inlineStr">
         <is>
           <t>شروع سپتامبر و فوریه</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="Q94" s="8" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/studyscience</t>
         </is>
@@ -9008,64 +9950,74 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>SDU (Odense)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>متوسط — DKK 8,000–10,000</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
           <t>MSc Eng Robot Systems</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="H95" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="I95" s="4" t="inlineStr">
         <is>
           <t>€17,300</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr">
+      <c r="J95" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="K95" s="4" t="inlineStr">
         <is>
           <t>کارشناسی مرتبط (CS/EE/Mechatronics)</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr">
+      <c r="L95" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K95" s="4">
+      <c r="M95" s="4">
         <f>283</f>
         <v/>
       </c>
-      <c r="L95" s="10" t="inlineStr">
+      <c r="N95" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M95" s="4" t="inlineStr">
+      <c r="O95" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N95" s="4" t="inlineStr">
+      <c r="P95" s="4" t="inlineStr">
         <is>
           <t>Odense Robotics cluster (Universal Robots، MiR)</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="Q95" s="8" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
         </is>
@@ -9082,60 +10034,70 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>SDU (Kolding)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
+          <t>Kolding (کولدینگ) — جنوب یوتلند</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>ارزان تا متوسط — DKK 7,500–9,000</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
           <t>MSc Data Science</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr">
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>€17,300</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr">
+      <c r="J96" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="I96" s="4" t="inlineStr">
+      <c r="K96" s="4" t="inlineStr">
         <is>
           <t>کارشناسی با محتوای کمی/برنامه‌نویسی</t>
         </is>
       </c>
-      <c r="J96" s="4" t="inlineStr">
+      <c r="L96" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K96" s="4">
+      <c r="M96" s="4">
         <f>283</f>
         <v/>
       </c>
-      <c r="L96" s="10" t="inlineStr">
+      <c r="N96" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M96" s="4" t="inlineStr">
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N96" s="4" t="inlineStr"/>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="P96" s="4" t="inlineStr"/>
+      <c r="Q96" s="8" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
         </is>
@@ -9157,60 +10119,70 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
+          <t>Copenhagen (کپنهاگ)</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 10,000–12,500</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
           <t>MSc Games — track Game Technology</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>توسعه بازی</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>€13,400 (€6,700 در ترم)</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
         <is>
           <t>$15,300</t>
         </is>
       </c>
-      <c r="I97" s="4" t="inlineStr">
+      <c r="K97" s="4" t="inlineStr">
         <is>
           <t>برای track فنی: کارشناسی CS</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr">
+      <c r="L97" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K97" s="4" t="inlineStr">
+      <c r="M97" s="4" t="inlineStr">
         <is>
           <t>— (تخصصی)</t>
         </is>
       </c>
-      <c r="L97" s="10" t="inlineStr">
+      <c r="N97" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M97" s="4" t="inlineStr">
+      <c r="O97" s="4" t="inlineStr">
         <is>
           <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
-      <c r="N97" s="4" t="inlineStr">
+      <c r="P97" s="4" t="inlineStr">
         <is>
           <t>شناخته‌شده‌ترین ارشد بازی اسکاندیناوی؛ Copenhagen (IO Interactive، Unity Copenhagen)</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="Q97" s="8" t="inlineStr">
         <is>
           <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/games</t>
         </is>
@@ -9232,60 +10204,70 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
+          <t>Copenhagen (کپنهاگ)</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 10,000–12,500</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G98" s="4" t="inlineStr">
+      <c r="I98" s="4" t="inlineStr">
         <is>
           <t>€13,400</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
         <is>
           <t>$15,300</t>
         </is>
       </c>
-      <c r="I98" s="4" t="inlineStr">
+      <c r="K98" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS/SE با برنامه‌نویسی قابل توجه</t>
         </is>
       </c>
-      <c r="J98" s="4" t="inlineStr">
+      <c r="L98" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K98" s="4" t="inlineStr">
+      <c r="M98" s="4" t="inlineStr">
         <is>
           <t>— (تخصصی)</t>
         </is>
       </c>
-      <c r="L98" s="10" t="inlineStr">
+      <c r="N98" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M98" s="4" t="inlineStr">
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="P98" s="4" t="inlineStr">
         <is>
           <t>ارزان‌ترین شهریهٔ کپنهاگ</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="Q98" s="8" t="inlineStr">
         <is>
           <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/computer-science</t>
         </is>
@@ -9307,56 +10289,66 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
+          <t>Copenhagen (کپنهاگ)</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 10,000–12,500</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
           <t>MSc Data Science</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t>علم داده / تحلیل داده</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="H99" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
+      <c r="I99" s="4" t="inlineStr">
         <is>
           <t>€13,400</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr">
+      <c r="J99" s="4" t="inlineStr">
         <is>
           <t>$15,300</t>
         </is>
       </c>
-      <c r="I99" s="4" t="inlineStr">
+      <c r="K99" s="4" t="inlineStr">
         <is>
           <t>کارشناسی مرتبط با داده/CS</t>
         </is>
       </c>
-      <c r="J99" s="4" t="inlineStr">
+      <c r="L99" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K99" s="4" t="inlineStr">
+      <c r="M99" s="4" t="inlineStr">
         <is>
           <t>— (تخصصی)</t>
         </is>
       </c>
-      <c r="L99" s="10" t="inlineStr">
+      <c r="N99" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M99" s="4" t="inlineStr">
+      <c r="O99" s="4" t="inlineStr">
         <is>
           <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
-      <c r="N99" s="4" t="inlineStr"/>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="P99" s="4" t="inlineStr"/>
+      <c r="Q99" s="8" t="inlineStr">
         <is>
           <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/data-science</t>
         </is>
@@ -9373,65 +10365,75 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>DTU (Kgs. Lyngby)</t>
+          <t>Technical University of Denmark (DTU)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
+          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 9,500–12,000</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
           <t>MSc Eng Human-Centered Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="G100" s="4" t="inlineStr">
         <is>
           <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G100" s="4" t="inlineStr">
+      <c r="I100" s="4" t="inlineStr">
         <is>
           <t>€15,000</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr">
+      <c r="J100" s="4" t="inlineStr">
         <is>
           <t>$17,100</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr">
+      <c r="K100" s="4" t="inlineStr">
         <is>
           <t>ظرفیت محدود؛ امتیازدهی: معدل ۶۰٪ + سابقهٔ کار ۱۰٪</t>
         </is>
       </c>
-      <c r="J100" s="4" t="inlineStr">
+      <c r="L100" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K100" s="4" t="inlineStr">
+      <c r="M100" s="4" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="L100" s="12" t="inlineStr">
+      <c r="N100" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M100" s="4" t="inlineStr">
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="P100" s="4" t="inlineStr">
         <is>
           <t>معدل ۱۵.۷۷ در رقابت DTU ضعیف است</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="Q100" s="8" t="inlineStr">
         <is>
           <t>https://www.dtu.dk/english/education/graduate/msc-programmes/human-centered-artificial-intelligence</t>
         </is>
@@ -9448,61 +10450,71 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>DTU (Kgs. Lyngby)</t>
+          <t>Technical University of Denmark (DTU)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
+          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 9,500–12,000</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
           <t>MSc Eng Autonomous Systems</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="H101" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr">
+      <c r="I101" s="4" t="inlineStr">
         <is>
           <t>€15,000</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
+      <c r="J101" s="4" t="inlineStr">
         <is>
           <t>$17,100</t>
         </is>
       </c>
-      <c r="I101" s="4" t="inlineStr">
+      <c r="K101" s="4" t="inlineStr">
         <is>
           <t>۸۰–۹۰ ECTS دروس مرتبط؛ ظرفیت محدود</t>
         </is>
       </c>
-      <c r="J101" s="4" t="inlineStr">
+      <c r="L101" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K101" s="4" t="inlineStr">
+      <c r="M101" s="4" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="L101" s="12" t="inlineStr">
+      <c r="N101" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M101" s="4" t="inlineStr">
+      <c r="O101" s="4" t="inlineStr">
         <is>
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr"/>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="P101" s="4" t="inlineStr"/>
+      <c r="Q101" s="8" t="inlineStr">
         <is>
           <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
@@ -9519,61 +10531,71 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>DTU (Kgs. Lyngby)</t>
+          <t>Technical University of Denmark (DTU)</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
+          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 9,500–12,000</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
           <t>MSc Eng Computer Science and Engineering</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G102" s="4" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>€15,000</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr">
+      <c r="J102" s="4" t="inlineStr">
         <is>
           <t>$17,100</t>
         </is>
       </c>
-      <c r="I102" s="4" t="inlineStr">
+      <c r="K102" s="4" t="inlineStr">
         <is>
           <t>ظرفیت محدود؛ گزینش با معدل</t>
         </is>
       </c>
-      <c r="J102" s="4" t="inlineStr">
+      <c r="L102" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K102" s="4" t="inlineStr">
+      <c r="M102" s="4" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="L102" s="12" t="inlineStr">
+      <c r="N102" s="12" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="M102" s="4" t="inlineStr">
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N102" s="4" t="inlineStr"/>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="P102" s="4" t="inlineStr"/>
+      <c r="Q102" s="8" t="inlineStr">
         <is>
           <t>https://www.dtu.dk/english/education/graduate/msc-programmes/computer-science-and-engineering</t>
         </is>
@@ -9590,65 +10612,75 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Aarhus University</t>
+          <t>Aarhus University (AU)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
+          <t>Aarhus (آرهوس) — دومین شهر دانمارک</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>گران — DKK 9,000–11,000</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="I103" s="4" t="inlineStr">
         <is>
           <t>€17,300</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
+      <c r="J103" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr">
+      <c r="K103" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS با واحدهای مشخص</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr">
+      <c r="L103" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K103" s="4" t="inlineStr">
+      <c r="M103" s="4" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="L103" s="11" t="inlineStr">
+      <c r="N103" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="M103" s="4" t="inlineStr">
+      <c r="O103" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="N103" s="4" t="inlineStr">
+      <c r="P103" s="4" t="inlineStr">
         <is>
           <t>Aarhus: دومین شهر، ارزان‌تر از کپنهاگ</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="Q103" s="8" t="inlineStr">
         <is>
           <t>https://masters.au.dk/computerscience</t>
         </is>
@@ -9678,121 +10710,129 @@
     <row r="108" ht="34" customHeight="1">
       <c r="B108" s="13" t="inlineStr">
         <is>
+          <t>ستون «هزینهٔ زندگی شهر» برآورد تقریبی هزینهٔ ماهانهٔ دانشجو با اجارهٔ اتاق در همان شهر است (سازگار با ردیف ۶ جدول اصلی)؛ برچسب‌ها: ارزان / متوسط / گران / خیلی گران. برای مقایسهٔ کشورها همچنان ردیف‌های ۶–۸ جدول اصلی معیار است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="34" customHeight="1">
+      <c r="B109" s="13" t="inlineStr">
+        <is>
           <t>حذف‌شده‌ها: Essex MSc Computer Games (برای 2025/26 و 2026/27 تعلیق شده)، Hull AI &amp; Data Science (سه رقم متناقض شهریه)، UCD/TCD (2:1 و ≈ €30k → Reach، بررسی نشد)، KU Copenhagen (شهریه تأیید نشد)، NCI/DBS ایرلند (کالج خصوصی، اعتبار کمتر).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
-  <mergeCells count="4">
-    <mergeCell ref="B107:O107"/>
-    <mergeCell ref="B105:O105"/>
-    <mergeCell ref="B106:O106"/>
-    <mergeCell ref="B108:O108"/>
+  <autoFilter ref="A1:Q103"/>
+  <mergeCells count="5">
+    <mergeCell ref="B107:Q107"/>
+    <mergeCell ref="B108:Q108"/>
+    <mergeCell ref="B105:Q105"/>
+    <mergeCell ref="B106:Q106"/>
+    <mergeCell ref="B109:Q109"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -607,7 +607,7 @@
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Stuttgart (اشتوتگارت) – MSc Computer Science (انگلیسی، بدون NC، IELTS 7) → Target
-FAU (Erlangen/Nürnberg) – MSc Artificial Intelligence (انگلیسی، B2) → Target
+FAU (Erlangen/Nürnberg) – MSc Artificial Intelligence (انگلیسی، B2؛ ⚠️ از تابستان ۲۰۲۷ شهریهٔ €4,000/ترم برای غیر-EU) → Target
 TU Darmstadt (دارمشتات) – MSc Computer Science (انگلیسی، IELTS 7) → Target/Reach
 TU Dresden (درسدن) – MSc Computer Science (انگلیسی، IELTS 7، ارزیابی استعداد) → Reach
 Safe: RPTU Kaiserslautern، Passau، Saarland (Saarbrücken)، TU Chemnitz، OVGU Magdeburg</t>
@@ -632,7 +632,7 @@
         <is>
           <t>AAU (Aalborg) – MSc Computer Science (IT) (انگلیسی؛ نه برنامه Computer Science دانمارکی‌زبان) → Target
 SDU (Odense) – MSc Computer Science → Target
-(پذیرش بر اساس داشتن ≥ ۱۰۰ ECTS دروس کامپیوتر)</t>
+(AAU رسماً حداقل ۱۵۰ ECTS دروس مرتبط با CS می‌خواهد و از ۲۰۲۷ سابقهٔ کار را هم در رتبه‌بندی حساب می‌کند؛ SDU هم واحدهای CS ریزنمرات را ارزیابی می‌کند)</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -769,13 +769,14 @@
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>€0 + سهم ترمی €150–400 (≈ €300–800 در سال)
-Stuttgart: €1,500 در ترم = €3,000 در سال (بادن-وورتمبرگ)</t>
+Stuttgart: €1,500 در ترم = €3,000 در سال (بادن-وورتمبرگ)
+⚠️ FAU: از ترم تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU €4,000 در ترم (AI/CS) = €8,000 در سال (BayHIG §13)؛ Passau فعلاً بدون شهریه</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Twente: €21,700
-Radboud: ≈ €19,700 (2025/26) → 2026/27 ≈ €20,500</t>
+Radboud: €19,714 (2026/27، رسمی)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -787,7 +788,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>AAU: €14,910 (7,455 در ترم)
+          <t>AAU: ≈ €14,910 (2025/26: 7,455 در ترم؛ نرخ ۲۰۲۶ هنوز روی سایت AAU نیست)
 SDU: €17,300 (نرخ رسمی برای ورودی سپتامبر ۲۰۲۶ به بعد — رقم قدیمی €13,900 دیگر معتبر نیست)</t>
         </is>
       </c>
@@ -828,7 +829,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>$350–900 (Stuttgart ≈ $3,400)</t>
+          <t>$350–900 (Stuttgart ≈ $3,400؛ FAU از ۲۰۲۷ ≈ $9,300)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -931,7 +932,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>$13,000–18,000 (Stuttgart تا $20,500)</t>
+          <t>$13,000–18,000 (Stuttgart تا $20,500؛ FAU از ۲۰۲۷ تا ≈ $26,000)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -978,7 +979,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$27,000–36,000 (۲ سال؛ Stuttgart تا $41,000) — ارزان‌ترین</t>
+          <t>$27,000–36,000 (۲ سال؛ Stuttgart تا $41,000؛ FAU از ۲۰۲۷ تا ≈ $53,000) — ارزان‌ترین</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -2001,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3697,7 +3698,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>Guildford قطب بازی‌سازی و امنیت بریتانیا (نزدیک لندن)؛ رقم 2025/26 + برآورد 2026/27</t>
+          <t>Guildford قطب بازی‌سازی و امنیت بریتانیا (نزدیک لندن)؛ رقم AI برآورد است (Cyber همین دانشگاه: £26,900 برای سپتامبر ۲۰۲۷ رسمی)</t>
         </is>
       </c>
       <c r="Q20" s="8" t="inlineStr">
@@ -3747,12 +3748,12 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>£25,900</t>
+          <t>£25,900 (ورودی فوریه ۲۰۲۷) / £26,900 (سپتامبر ۲۰۲۷)</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>$34,300</t>
+          <t>$34,300–35,600</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -3779,7 +3780,11 @@
           <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>صفحهٔ رسمی الان ورودی ۲۰۲۷ را نشان می‌دهد (رقم رسمی)؛ برای ۲۰۲۸ ≈ £27,900 انتظار داشته باشید</t>
+        </is>
+      </c>
       <c r="Q21" s="8" t="inlineStr">
         <is>
           <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
@@ -3995,7 +4000,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>£32,300</t>
+          <t>£32,300 (2026)</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -4005,7 +4010,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2:1 (2:2 با سابقه بررسی می‌شود)</t>
+          <t>2:2 در رشتهٔ کامپیوتری/ریاضی‌محور (طبق QS TopUniversities و IDP — صفحهٔ رسمی را چک کنید)</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -4018,9 +4023,9 @@
           <t>149</t>
         </is>
       </c>
-      <c r="N24" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -4165,12 +4170,12 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>£34,340</t>
+          <t>≈ £32,900–34,340 (2026؛ MSc AI for Engineering همین دانشگاه رسماً £32,905)</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>$45,500</t>
+          <t>$43,600–45,500</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -4200,7 +4205,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>رتبهٔ بالا، شهریه و شرط ورود بالا</t>
+          <t>رتبهٔ بالا، شهریه و شرط ورود بالا؛ رقم دقیق MSc AI را از صفحهٔ رسمی بگیرید</t>
         </is>
       </c>
       <c r="Q26" s="8" t="inlineStr">
@@ -5096,7 +5101,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>€28,000</t>
+          <t>≈ €28,000 (IDP/collegedunia 2025–26؛ صفحهٔ رسمی چک شود)</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -5436,12 +5441,12 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €130 سهم ترم (≈ €260/سال)</t>
+          <t>€4,000 در ترم برای غیر-EU از ترم تابستان ۲۰۲۷ (€8,000/سال) + €82 سهم ترم</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>$9,300</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -5471,7 +5476,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>Siemens/adidas/Schaeffler در منطقه</t>
+          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی ۲۰۲۸ مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
         </is>
       </c>
       <c r="Q41" s="8" t="inlineStr">
@@ -5521,12 +5526,12 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €130 سهم ترم</t>
+          <t>€2,000 در ترم از تابستان ۲۰۲۷ (€4,000/سال) + €82 سهم ترم</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>$4,700</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -5556,7 +5561,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>رباتیک/خودران؛ صفحهٔ رسمی سپتامبر ۲۰۲۶</t>
+          <t>رباتیک/خودران؛ ⚠️ مشمول شهریهٔ جدید FAU از ۲۰۲۷ (صفحهٔ رسمی شهریه، ۲۰۲۶)</t>
         </is>
       </c>
       <c r="Q42" s="8" t="inlineStr">
@@ -6064,7 +6069,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان</t>
+          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان؛ Passau رسماً اعلام کرده «فعلاً» شهریهٔ غیر-EU نمی‌گیرد (برخلاف FAU/TUM) ولی طبق قانون باواریا می‌تواند — قبل از اپلای چک کنید</t>
         </is>
       </c>
       <c r="Q48" s="8" t="inlineStr">
@@ -6959,12 +6964,12 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>€19,714 (2025/26) → ≈ €20,500</t>
+          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>$23,400</t>
+          <t>$22,500</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -7044,12 +7049,12 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>€19,714 (2025/26) → ≈ €20,500</t>
+          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>$23,400</t>
+          <t>$22,500</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -8392,12 +8397,12 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>SEK 190,000</t>
+          <t>≈ SEK 180,000–190,000 (کل دوره ≈ 360k–380k)</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>$19,200</t>
+          <t>$18,200–19,200</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -8427,7 +8432,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>Stockholm گران (اتاق SEK 7–10k)</t>
+          <t>Stockholm گران (اتاق SEK 7–10k)؛ رقم دقیق روی kth.se فقط در سامانهٔ اپلای نمایش داده می‌شود</t>
         </is>
       </c>
       <c r="Q76" s="8" t="inlineStr">
@@ -8477,12 +8482,12 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>SEK 190,000</t>
+          <t>≈ SEK 180,000–190,000</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>$19,200</t>
+          <t>$18,200–19,200</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -8643,12 +8648,12 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>SEK 160,000</t>
+          <t>≈ SEK 175,000 (2026/27؛ 2025/26: 160,000)</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>$16,200</t>
+          <t>$17,700</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
@@ -8678,7 +8683,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه</t>
+          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه؛ ⚠️ طبق صفحهٔ شهریهٔ Chalmers دانشگاه‌های سوئد فعلاً نمی‌توانند از ایران پول دریافت کنند (تحریم بانکی) — پرداخت از کشور ثالث</t>
         </is>
       </c>
       <c r="Q79" s="8" t="inlineStr">
@@ -8728,12 +8733,12 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>SEK 160,000</t>
+          <t>≈ SEK 175,000 (2026/27)</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>$16,200</t>
+          <t>$17,700</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -8809,12 +8814,12 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>SEK 160,000</t>
+          <t>≈ SEK 175,000 (2026/27)</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>$16,200</t>
+          <t>$17,700</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -9396,22 +9401,22 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>€14,910 (€7,455 در ترم)</t>
+          <t>≈ €14,910 (2025/26: €7,455 در ترم؛ نرخ ۲۰۲۶ روی سایت AAU منتشر نشده — mastersportal: €15,340)</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>$17,000</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE</t>
+          <t>رسمی: حداقل ۱۵۰ ECTS دروس مرتبط با CS (برنامه‌نویسی ۱۵، مهندسی نرم‌افزار ۵، الگوریتم ۵، پایگاه داده ۵، ریاضیات گسسته ۵)؛ از ورودی ۲۰۲۷ سابقهٔ کار و انگیزه‌نامه هم در رتبه‌بندی حساب می‌شود</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5 (هر بخش ≥ 6.0)</t>
         </is>
       </c>
       <c r="M88" s="4">
@@ -9430,7 +9435,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)</t>
+          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)؛ ظرفیت محدود</t>
         </is>
       </c>
       <c r="Q88" s="8" t="inlineStr">
@@ -9480,12 +9485,12 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>€14,910</t>
+          <t>≈ €14,910–15,340</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>$17,000</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -9560,12 +9565,12 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>€14,910</t>
+          <t>≈ €14,910–15,340</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>$17,000</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -9644,12 +9649,12 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>€14,910</t>
+          <t>≈ €14,910–15,340</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>$17,000</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -10144,12 +10149,12 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>€13,400 (€6,700 در ترم)</t>
+          <t>€16,500 (€8,250 در ترم؛ ورودی ۲۰۲۶ — رسمی)</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>$15,300</t>
+          <t>$18,800</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -10184,7 +10189,7 @@
       </c>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/games</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
@@ -10229,12 +10234,12 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>€13,400</t>
+          <t>€16,500 (€8,250 در ترم)</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>$15,300</t>
+          <t>$18,800</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
@@ -10264,12 +10269,12 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌ترین شهریهٔ کپنهاگ</t>
+          <t>ارزان‌تر از DTU/KU در کپنهاگ؛ رقم قدیمی €13,400 (پورتال studyindenmark) منسوخ است</t>
         </is>
       </c>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/computer-science</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
@@ -10314,12 +10319,12 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>€13,400</t>
+          <t>€16,500 (€8,250 در ترم)</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>$15,300</t>
+          <t>$18,800</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -10350,7 +10355,7 @@
       <c r="P99" s="4" t="inlineStr"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/data-science</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
@@ -10717,15 +10722,23 @@
     <row r="109" ht="34" customHeight="1">
       <c r="B109" s="13" t="inlineStr">
         <is>
+          <t>بازبینی صحت اعداد (۲۷ سپتامبر ۲۰۲۶): ≈۷۰٪ شهریه‌ها مستقیماً از صفحهٔ رسمی 2026/27 است؛ ردیف‌های «≈» از منبع ثانویه یا سال قبل‌اند. اصلاح‌های این بازبینی: FAU از تابستان ۲۰۲۷ شهریه می‌گیرد (AI/CS €4,000/ترم)؛ ITU €16,500 (نه €13,400)؛ Radboud €19,714 رسمی؛ Chalmers ≈ SEK 175k (نه 160k)؛ KTH ≈ 180–190k؛ AAU شرط ≥ ۱۵۰ ECTS؛ Surrey Cyber ورودی ۲۰۲۷؛ Newcastle Games 2:2؛ Sheffield AI ≈ £32.9–34.3k. رتبه‌بندی Safe/Target/Reach، امتیاز بازار و ردهٔ هزینهٔ شهر ارزیابی‌اند، نه دادهٔ رسمی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="34" customHeight="1">
+      <c r="B110" s="13" t="inlineStr">
+        <is>
           <t>حذف‌شده‌ها: Essex MSc Computer Games (برای 2025/26 و 2026/27 تعلیق شده)، Hull AI &amp; Data Science (سه رقم متناقض شهریه)، UCD/TCD (2:1 و ≈ €30k → Reach، بررسی نشد)، KU Copenhagen (شهریه تأیید نشد)، NCI/DBS ایرلند (کالج خصوصی، اعتبار کمتر).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q103"/>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B107:Q107"/>
     <mergeCell ref="B108:Q108"/>
+    <mergeCell ref="B110:Q110"/>
     <mergeCell ref="B105:Q105"/>
     <mergeCell ref="B106:Q106"/>
     <mergeCell ref="B109:Q109"/>
@@ -11064,7 +11077,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>متوسط: مدرک‌های ارزان و Safe زیاد است (Maynooth €17k، Skövde، Brunel، ITU) ولی رقابت جونیور بالاست؛ اگر می‌روید، Data Engineering را انتخاب کنید</t>
+          <t>متوسط: مدرک‌های ارزان و Safe زیاد است (Maynooth €17k، Skövde، Brunel، ITU €16.5k) ولی رقابت جونیور بالاست؛ اگر می‌روید، Data Engineering را انتخاب کنید</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11273,7 +11286,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ایرلند ۲۵ › آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ › دانمارک ۱۶.  پیشنهاد: اپلای هم‌زمان به ۲–۳ برنامه ایرلند (UL، Maynooth، TU Dublin) + ۲ برنامه آلمان (Stuttgart، FAU یا یک گزینه Safe)؛ تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در ۲۰۲۸.</t>
+          <t>ایرلند ۲۵ › آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ › دانمارک ۱۶.  پیشنهاد: اپلای هم‌زمان به ۲–۳ برنامه ایرلند (UL، Maynooth، TU Dublin) + ۲ برنامه آلمان (Stuttgart + یک گزینه Safe مثل Passau/Saarland؛ FAU فقط اگر شهریهٔ جدید €8,000/سال را می‌پذیرید)؛ تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در ۲۰۲۸.</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -11569,12 +11582,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>هلند – Radboud Computing Science شهریه</t>
+          <t>هلند – Radboud شهریهٔ رسمی 2026/27 غیر-EEA €19,714 (Data Science and AI؛ دانشکدهٔ علوم)</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>https://www.mastersportal.com/studies/8984/computing-science.html</t>
+          <t>https://www.ru.nl/en/education/masters/data-science-and-ai/tuition</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12554,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>سوئد – KTH Machine Learning: SEK 190,000</t>
+          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -12577,12 +12590,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – ITU شهریه €6,700 در ترم (Games / CS / Data Science)</t>
+          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>https://studyindenmark.dk/portal/it-university-of-copenhagen-itu/kobenhavn/games</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
@@ -12715,6 +12728,102 @@
       <c r="B112" s="15" t="inlineStr">
         <is>
           <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
+        </is>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
+        </is>
+      </c>
+      <c r="B118" s="15" t="inlineStr">
+        <is>
+          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="inlineStr">
+        <is>
+          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
         </is>
       </c>
     </row>
@@ -12831,6 +12940,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جدول نهایی ۲۰۲۶" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه‌ها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="حوزه‌ها و بازار کار" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جمع‌بندی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منابع" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="جدول نهایی ۲۰۲۶" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="برنامه‌ها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="حوزه‌ها و بازار کار" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="برنامهٔ زمانی ۲۰۲۷" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="جمع‌بندی" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="منابع" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$103</definedName>
@@ -122,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
@@ -162,6 +163,9 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1771,7 +1775,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>سایت برنامه‌ها — IELTS معمولاً ۲ سال اعتبار دارد؛ زمان امتحان را با اقدام ۲۰۲۸ هماهنگ کنید</t>
+          <t>سایت برنامه‌ها — ⚠️ IELTS از ۳۱ ژانویه ۲۰۲۶ و TOEFL از ۱۴۰۵ در ایران برگزار نمی‌شوند؛ آزمون را در استانبول/ایروان/دبی/تفلیس بدهید (نتیجهٔ کامپیوتری ۳–۵ روزه). برای مهلت ۱۵ ژانویهٔ ۲۰۲۷ (سوئد/دانمارک/Stuttgart) نتیجه باید تا اوایل ژانویه در دست باشد</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1911,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>بسیار بالا: Graduate visa ۱۸ ماه، B2، طرح PR ۱۰ ساله، عوارض £925/دانشجو/سال از اوت ۲۰۲۸ فقط برای دانشگاه‌های انگلستان — یعنی همهٔ گزینه‌های شما (ورودی ۲۰۲۸)؛ احتمالاً به شهریه اضافه می‌شود</t>
+          <t>بسیار بالا: Graduate visa ۱۸ ماه، B2، طرح PR ۱۰ ساله، عوارض £925/دانشجو/سال از اوت ۲۰۲۸ فقط برای دانشگاه‌های انگلستان — دورهٔ یک‌سالهٔ شما (سپتامبر ۲۰۲۷ تا سپتامبر ۲۰۲۸) عملاً از آن رد می‌شود، ولی بعضی دانشگاه‌ها ممکن است از ۲۰۲۷ در شهریه پیش‌خور کنند</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -1973,7 +1977,7 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>همه ارقام سطح 2026/27 و از منابع رسمی (شیت «منابع»)؛ برای ورودی ۲۰۲۸ سالانه ۳–۵٪ (شهریه ۵–۱۰٪) اضافه کنید. ردیف‌های ۱۳، ۱۴، ۱۷–۱۹، ۲۶ برآورد/ارزیابی هستند و در ستون منبع مشخص شده‌اند.</t>
+          <t>همه ارقام سطح 2026/27 و از منابع رسمی (شیت «منابع»)؛ برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 را بگیرید (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪). ردیف‌های ۱۳، ۱۴، ۱۷–۱۹، ۲۶ برآورد/ارزیابی هستند و در ستون منبع مشخص شده‌اند.</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2071,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>شهریهٔ سالانه 2026/27 (ارز محلی)</t>
+          <t>شهریهٔ سالانه (2026/27؛ اگر نرخ 2027/28 منتشر شده، ذکر شده) — ارز محلی</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -3748,12 +3752,12 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>£25,900 (ورودی فوریه ۲۰۲۷) / £26,900 (سپتامبر ۲۰۲۷)</t>
+          <t>£26,900 (ورودی سپتامبر ۲۰۲۷ — رسمی؛ فوریه ۲۰۲۷: £25,900)</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>$34,300–35,600</t>
+          <t>$35,600</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -3782,7 +3786,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>صفحهٔ رسمی الان ورودی ۲۰۲۷ را نشان می‌دهد (رقم رسمی)؛ برای ۲۰۲۸ ≈ £27,900 انتظار داشته باشید</t>
+          <t>رقم رسمی دقیقاً برای سال ورود شما (سپتامبر ۲۰۲۷)</t>
         </is>
       </c>
       <c r="Q21" s="8" t="inlineStr">
@@ -5476,7 +5480,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی ۲۰۲۸ مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
+          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی اکتبر ۲۰۲۷ شما مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
         </is>
       </c>
       <c r="Q41" s="8" t="inlineStr">
@@ -7721,12 +7725,12 @@
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>€21,700</t>
+          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>$24,700</t>
+          <t>$25,500</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -7806,12 +7810,12 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>€21,700</t>
+          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>$24,700</t>
+          <t>$25,500</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -8895,12 +8899,12 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>SEK 145,000 (کل ۲۹۰k؛ ورودی ۲۰۲۷: ۲۹۴k)</t>
+          <t>SEK 147,000 (ورودی ۲۰۲۷: کل دوره SEK 294,000 رسمی)</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>$14,600–14,800</t>
+          <t>$14,800</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -10701,7 +10705,7 @@
     <row r="106" ht="34" customHeight="1">
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>شهریهٔ دلاری با نرخ نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 و گرد شده به $100. برای ورودی ۲۰۲۸ شهریه‌ها را ۵–۱۰٪ در سال بالاتر فرض کنید. آلمان: عدد فقط سهم ترم (Semesterbeitrag) است که بلیت حمل‌ونقل را هم شامل می‌شود.</t>
+          <t>شهریهٔ دلاری با نرخ نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 و گرد شده به $100. برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 ملاک است (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪؛ TU/e و Surrey و Gothenburg همین حالا رسمی‌اند). آلمان: عدد فقط سهم ترم (Semesterbeitrag) است که بلیت حمل‌ونقل را هم شامل می‌شود.</t>
         </is>
       </c>
     </row>
@@ -11223,153 +11227,648 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="130" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>موضوع</t>
+          <t>تاریخ / مهلت</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>جمع‌بندی</t>
+          <t>اقدام</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>کشور / برنامه</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>جزئیات</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>منبع</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>رتبه‌بندی هزینه کل تا فارغ‌التحصیلی</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>همین هفته (اکتبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>آلمان $27–36k  &lt;  ایرلند $32–48k  &lt;  انگلستان $38–65k  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k</t>
+          <t>تعیین تکلیف نظام‌وظیفه</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>اگر کارت پایان خدمت یا معافیت دائم ندارید: خروج تحصیلی مشمولانِ بدون غیبت فقط با مجوز سامانهٔ «سخا»، وثیقهٔ ۲۰۰ میلیون تومان (از خرداد/تیر ۱۴۰۵؛ قبلاً ۸۰ میلیون) و پذیرش از دانشگاه مورد تأیید وزارت علوم ممکن است؛ مدت مجوز = طول دوره. این را قبل از هر هزینه‌ای روشن کنید.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>sakha.epolice.ir؛ زومیت/فرارو تیر ۱۴۰۵</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>فقط با انگلیسی (تحصیل + کار + اداری + اقامت)</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>اکتبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ایرلند و انگلستان کامل؛ هلند و سوئد برای زندگی/کار خوب ولی برای اقامت دائم/تابعیت زبان می‌خواهند (هلند B1 در راه، سوئد آزمون تابعیت)؛ دانمارک و آلمان بدون زبان محلی هم بازار کار و هم PR محدود.</t>
+          <t>رزرو آزمون زبان — خارج از ایران</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>IELTS از ۳۱ ژانویه ۲۰۲۶ و TOEFL از ۱۴۰۵ در ایران برگزار نمی‌شوند. IELTS Academic کامپیوتری در استانبول/ایروان/دبی/تفلیس برای نوامبر تا اوایل دسامبر ۲۰۲۶ رزرو کنید (نتیجه ۳–۵ روزه؛ ≈ $250–300 + سفر). هدف 7.0 با هر بخش ≥ 6.5 (Stuttgart C1، Saarland 7.0). Duolingo فقط بعضی دانشگاه‌های انگلستان/ایرلند را باز می‌کند، نه سوئد/دانمارک/هلند/آلمان.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>اعلام IDP (دسامبر ۲۰۲۵)؛ وضعیت ETS/سنجش شهریور ۱۴۰۵</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>بازار کار و حقوق جونیور</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>اکتبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>حقوق ناخالص: دانمارک &gt; آلمان &gt; هلند ≈ سوئد &gt; ایرلند &gt; انگلستان. دسترسی برای جونیورِ فقط‌انگلیسی: ایرلند ≈ هلند &gt; آلمان &gt; سوئد ≈ دانمارک ≈ انگلستان.</t>
+          <t>مدارک پایه</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ریزنمرات و دانشنامهٔ انگلیسی رسمی (دانشگاه سمنان + تأییدیه‌ها)؛ گواهی رتبه/میانگین کلاس اگر می‌دهند؛ ۲ توصیه‌نامه (استاد + کارفرما)؛ SOP با تکیه بر ۲ سال IT + Unity؛ CV؛ گیت‌هاب مرتب؛ گواهی سابقهٔ کار (AAU از ورودی ۲۰۲۷ برایش امتیاز می‌دهد).</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>نتیجه با وزن برابر برای ۳ معیار</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>۱۴–۱۶ اکتبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ایرلند ۲۵ › آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ › دانمارک ۱۶.  پیشنهاد: اپلای هم‌زمان به ۲–۳ برنامه ایرلند (UL، Maynooth، TU Dublin) + ۲ برنامه آلمان (Stuttgart + یک گزینه Safe مثل Passau/Saarland؛ FAU فقط اگر شهریهٔ جدید €8,000/سال را می‌پذیرید)؛ تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در ۲۰۲۸.</t>
+          <t>باز شدن پورتال‌ها</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند، هلند، سوئد</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Maynooth (۱۴ اکتبر)، UL (۱۵ اکتبر)، فرم بورس UTS Twente (۱۵ اکتبر)، سوئد universityadmissions.se (۱۶ اکتبر — تا ۴ برنامه با یک درخواست، SEK 900).</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>maynoothuniversity.ie؛ ul.ie؛ utwente.nl؛ universityadmissions.se</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ریسک شماره یک</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>نوامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>دسترسی به سفارت‌ها از داخل ایران (ردیف ۲۳): در سپتامبر ۲۰۲۶ هیچ‌کدام از ۶ کشور خدمات عادی ویزای دانشجویی در تهران ندارند. از الان هزینه «برنامه B» (اقدام از ترکیه/ارمنستان/امارات) را در بودجه ببینید.</t>
+          <t>VPD از uni-assist</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>برای TU Darmstadt، TU Dresden، Saarland، RPTU، Chemnitz، OVGU و Passau (uni-assist) ۴–۶ هفته زمان و €75 هزینه؛ Stuttgart مستقیم در C@MPUS اپلای می‌گیرد (۱۵ نوامبر – ۱۵ ژانویه).</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>uni-assist.de؛ uni-stuttgart.de</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>برنامه زمانی ورودی سپتامبر ۲۰۲۸</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>نوامبر – اوایل دسامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>تا بهار ۲۰۲۷: IELTS 7.0 (هر بخش ≥ 6.5) · تابستان ۲۰۲۷: ریزنمرات رسمی + تأییدیه‌ها + VPD uni-assist · پاییز ۲۰۲۷ تا زمستان ۲۰۲۸: اپلای (ایرلند rolling از اکتبر؛ سوئد ۱۵ ژانویه؛ هلند تا ۱ می؛ آلمان ۱۵ ژانویه–۱۵ ژوئیه؛ انگلستان rolling) · بهار ۲۰۲۸: شهریه/تمکن → خوابگاه → ویزا یا برنامه B.</t>
+          <t>آزمون IELTS</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>نتیجه باید تا اوایل ژانویه ۲۰۲۷ در دست باشد (سوئد، دانمارک، Stuttgart). یک تاریخ ذخیره در دسامبر رزرو کنید.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>تغییرات اصلی نسبت به جدول اول</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>اواسط دسامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>• هزینه کل دوره اضافه شد (هلند از «نیاز به تأمین سال دوم» به گران‌ترین گزینه تبدیل شد)
-• فقط انگلستان (به خواست شما): Strathclyde و Swansea حذف شدند؛ گزینه‌ها Teesside £17,000 · Northumbria £21,500 · Leicester £24,250 · Essex £24,675 · Brunel £24,795 · York £32,900؛ Graduate visa ۱۸ ماه؛ کف اسپانسری £54,700 / £38,290؛ طرح PR ۱۰ ساله؛ عوارض £925 از ۲۰۲۸ شامل همهٔ گزینه‌ها
-• کف حقوق ۲۰۲۶ همه کشورها به‌روز شد (آلمان €50,700/€45,934؛ هلند €3,122/ماه؛ سوئد SEK 34,470؛ ایرلند €40,904)
-• ایرلند: ۲ سال CSEP = Stamp 4 نه PR؛ تمکن €10,000
-• سوئد: کار دانشجویی ۱۵ ساعت/هفته (ژوئن ۲۰۲۶)؛ شهروندی ۸ سال؛ «BTH یک‌ساله» حذف شد؛ خوابگاه فقط LiU
-• QS 2027؛ شهریه‌های واقعی 2026/27؛ «۷۵٪ قبولی» حذف شد
-• «۱۰۰٪ انگلیسی» برای هلند/سوئد/دانمارک تعدیل شد؛ دانمارک PD2/PD3 تفکیک شد
-• ردیف ویزا برای وضعیت ۲۰۲۶ بازنویسی شد؛ ردیف‌های IELTS، تمکن مالی، پس‌انداز، شهروندی و امتیاز اضافه شد</t>
+          <t>پورتال AAU باز می‌شود</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>برای شهریه‌پردازها مهلت ۱۵ ژانویه است (۱ مارس فقط برای EU).</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>en.aau.dk/how-and-when-to-apply</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>چرا «انگلستان» و نه «بریتانیا»</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>به خواست شما فقط دانشگاه‌های انگلستان مقایسه شده‌اند. قوانین ویزا، کار و اقامت در کل بریتانیا یکسان است؛ سه تفاوت عملی: (۱) ارزان‌ترین گزینه‌های انگلستان (Teesside £17,000، Northumbria £21,500) از Swansea/Strathclyde ارزان‌ترند → کل دوره از $48–71k به $38–65k رسید؛ (۲) عوارض £925 به ازای هر دانشجو از اوت ۲۰۲۸ فقط دانشگاه‌های انگلستان را می‌گیرد — یعنی همهٔ گزینه‌های شما؛ (۳) بازار کار فناوری بریتانیا عملاً در انگلستان است (London، Manchester، Cambridge، Bristol، Leeds) — حذف اسکاتلند/ولز به فرصت شغلی لطمه نمی‌زند. برای شهریهٔ کمتر باید رتبهٔ پایین‌تر را بپذیرید: Teesside/Chester بدون رتبه QS، Northumbria ≈ ۵۲۸، Essex ≈ ۴۳۸؛ York (۱۵۸) و Newcastle (۱۴۹) تقریباً دوبرابر گران‌ترند.</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>۱۵ ژانویه ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>⛔ مهلت اصلی ۱: سوئد + دانمارک + Stuttgart</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>سوئد، دانمارک، آلمان</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>سوئد (همهٔ دانشگاه‌ها: Linköping، Halmstad، BTH، Chalmers، KTH، Uppsala، Umeå، Skövde)؛ AAU (fee-paying)، Aarhus، DTU (الگوی ۱۵ ژانویه برای غیر-EU)؛ Stuttgart MSc Computer Science / INFOTECH.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>umu.se و uu.se key dates؛ en.aau.dk؛ uni-stuttgart.de</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>نکته پروفایل</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>۳۱ ژانویه ۲۰۲۷</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>معدل (۱۵.۷۷ طبق جدول اول؛ ۱۵.۷۰ طبق نقد دوم — تفاوتی در نتیجه ندارد) برای همه برنامه‌های بالا بالاتر از حداقل است. مهم‌تر از معدل، تطابق ریزنمرات با پیش‌نیازها (ریاضی، الگوریتم، CS نظری) و SOP با تکیه بر ۲ سال سابقه کار + بازی‌سازی + پروژه‌های گیت‌هاب است.</t>
+          <t>مهلت بورس Radboud</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Radboud Scholarship Programme (≈۳۳ نفر؛ شهریه به €2,694 می‌رسد) — اپلای اصلی هم باید تا این تاریخ کامل باشد.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>ru.nl deadlines</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>اعداد را چگونه بخوانم</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>همه مبالغ سطح 2026/27 هستند؛ برای ۲۰۲۸ سالانه ۳–۵٪ (شهریه ۵–۱۰٪) اضافه کنید. نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>۱ فوریه ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>⛔ مهلت اصلی ۲</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>سوئد، دانمارک، هلند</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>سوئد: مدارک + SEK 900 روی universityadmissions.se؛ SDU (غیر-EU)؛ Twente: برای بورس UTS (۱ آوریل) اپلای را تا اوایل فوریه بفرستید.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>universityadmissions.se؛ sdu.dk/datalogi؛ utwente.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>فوریه – مارس ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>اپلای ایرلند و انگلستان</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند، انگلستان</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>همه rolling هستند ولی زود اپلای کنید: بورس‌ها (Brunel، DCU، Northumbria) و ظرفیت‌ها زود پر می‌شود؛ TU Dublin بین‌المللی ≈ ۳۱ می، Maynooth غیر-EU ≈ ۱۵ می تا ژوئن، UL غیر-EU ویزایی ۱ ژوئیه.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>studyinireland.app؛ ul.ie/gps/applications-faq</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>۳۰ مارس – ۱ آوریل ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>نتایج سوئد</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>پاسخ به پیشنهاد در مهلت؛ قسط اول شهریه قبل از درخواست اقامت تحصیلی.</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>universityadmissions.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>۱ آوریل ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>⛔ مهلت اصلی ۳</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>هلند، آلمان</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Radboud غیر-EU (اپلای اصلی)؛ بورس UTS Twente؛ پنجرهٔ Passau AI Engineering باز می‌شود (۱ آوریل – ۳۱ می).</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>ru.nl؛ utwente.nl؛ uni-passau.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>۱۵ آوریل ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>دور دوم سوئد (فقط پشتیبان)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>۱۵ مارس – ۱۵ آوریل؛ مدارک تا ۲۱ ژوئن؛ نتیجه ۹ ژوئیه — برای اقامت و خوابگاه دیر است.</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>umu.se key dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>۱ می ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>⛔ مهلت Twente (غیر-EEA)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science / Embedded Systems / Interaction Technology.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>utwente.nl (به نقل از collegedunia، اوت ۲۰۲۶)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>۱۵ – ۳۱ می ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>مهلت‌های ایرلند و آلمان</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند، آلمان</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Maynooth غیر-EU ≈ ۱۵ می؛ TU Dublin بین‌المللی ≈ ۳۱ می؛ Passau AI Eng ۳۱ می؛ بقیهٔ آلمان (TU Darmstadt، TU Dresden، Saarland، RPTU، Chemnitz، OVGU، FAU) بیشتر بین ۱۵ می تا ۱۵ ژوئیه — هر کدام را جدا چک کنید.</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>studyinireland.app؛ uni-passau.de؛ سایت دانشگاه‌ها</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>می – ژوئن ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>💰 پول باید نقد و قابل انتقال باشد</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>SDU: یک سال شهریه پیش‌پرداخت (€17,300)؛ سوئد: قسط ترم اول + تمکن SEK 10,656 × ماه‌ها؛ هلند: شهریه + €13,569 زندگی به حساب دانشگاه (Radboud تا ۱ ژوئن)؛ آلمان: حساب مسدود €11,904 (Fintiba ایران را نمی‌پذیرد → Expatrio/Coracle) + Stuttgart €1,500؛ ایرلند: €10,000 + حداقل €6,000 شهریه؛ انگلستان: ودیعه → CAS + £1,203 × ۹ ماه. انتقال از کشور ثالث/صرافی ۳–۶٪ هزینه.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>ردیف ۲۵ جدول اصلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>۱ ژوئن ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>مهلت ثبت‌نام/ویزای Radboud</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>برای شروع سپتامبر (غیر-EU)؛ درخواست MVV را دانشگاه از طرف شما به IND می‌دهد.</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>ru.nl deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>۱ ژوئیه ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>⛔ مهلت UL (غیر-EU ویزایی)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>الگوی ۲۰۲۶: ۱ ژوئیه ساعت ۱۲؛ بعد از آن بررسی نمی‌شود.</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>ul.ie/gps/applications-faq</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ژوئن – ژوئیه ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>🛂 ویزا / برنامهٔ B</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>وضعیت تهران (سپتامبر ۲۰۲۶): آلمان حالت اضطراری، هلند از باکو، دانمارک «از ایران ممکن نیست»، ایرلند کنسول بسته، انگلستان VFS متناوب؛ سوئد بدون بیومتریک (آنلاین). یعنی برای DE/DK/IE/UK سفر به ترکیه/ارمنستان/امارات را (۲–۶ هفته) در بودجه و تقویم بگذارید.</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>ردیف ۲۳ جدول اصلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>ژوئیه ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Twente/Radboud اتاق رزروشده برای بین‌المللی‌ها (مهلت‌دار)؛ Linköping یک پیشنهاد اتاق برای شهریه‌پردازها؛ آلمان لیست Studierendenwerk بلافاصله بعد از پذیرش؛ ایرلند/انگلستان خوابگاه دانشگاه زود پر می‌شود.</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>ردیف‌های ۹–۱۰ جدول اصلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>اوت – اکتبر ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>شروع</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>سوئد ≈ ۳۰ اوت؛ دانمارک ۱ سپتامبر؛ هلند اوایل سپتامبر؛ ایرلند/انگلستان اواسط تا اواخر سپتامبر؛ آلمان ترم زمستان از ۱ اکتبر (کلاس‌ها ≈ اواسط اکتبر).</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>جمع‌بندی: ورودی سپتامبر ۲۰۲۷ شدنی است، فقط اگر (۱) IELTS تا دسامبر ۲۰۲۶ خارج از ایران گرفته شود، (۲) پول سال اول تا می ۲۰۲۷ نقد و قابل انتقال باشد، (۳) وضعیت نظام‌وظیفه/مجوز خروج روشن باشد. سوئد، دانمارک و Stuttgart با مهلت ۱۵ ژانویه سخت‌ترین‌اند؛ ایرلند، انگلستان، هلند و بیشتر آلمان تا بهار ۲۰۲۷ وقت دارند — اگر IELTS به ژانویه نرسید، تمرکز را روی این‌ها بگذارید. مهلت‌های علامت «≈» از منابع ثانویه‌اند؛ تاریخ دقیق را از صفحهٔ برنامه بگیرید.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A25:E25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11380,7 +11879,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>موضوع</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>جمع‌بندی</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>رتبه‌بندی هزینه کل تا فارغ‌التحصیلی</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>آلمان $27–36k  &lt;  ایرلند $32–48k  &lt;  انگلستان $38–65k  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>فقط با انگلیسی (تحصیل + کار + اداری + اقامت)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند و انگلستان کامل؛ هلند و سوئد برای زندگی/کار خوب ولی برای اقامت دائم/تابعیت زبان می‌خواهند (هلند B1 در راه، سوئد آزمون تابعیت)؛ دانمارک و آلمان بدون زبان محلی هم بازار کار و هم PR محدود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>بازار کار و حقوق جونیور</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>حقوق ناخالص: دانمارک &gt; آلمان &gt; هلند ≈ سوئد &gt; ایرلند &gt; انگلستان. دسترسی برای جونیورِ فقط‌انگلیسی: ایرلند ≈ هلند &gt; آلمان &gt; سوئد ≈ دانمارک ≈ انگلستان.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>نتیجه با وزن برابر برای ۳ معیار</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند ۲۵ › آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ › دانمارک ۱۶.  پیشنهاد: اپلای هم‌زمان به ۲–۳ برنامه ایرلند (UL، Maynooth، TU Dublin) + ۲ برنامه آلمان (Stuttgart + یک گزینه Safe مثل Passau/Saarland؛ FAU فقط اگر شهریهٔ جدید €8,000/سال را می‌پذیرید)؛ تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در بهار ۲۰۲۷.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ریسک شماره یک</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>دسترسی به سفارت‌ها از داخل ایران (ردیف ۲۳): در سپتامبر ۲۰۲۶ هیچ‌کدام از ۶ کشور خدمات عادی ویزای دانشجویی در تهران ندارند. از الان هزینه «برنامه B» (اقدام از ترکیه/ارمنستان/امارات) را در بودجه ببینید.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>برنامه زمانی ورودی سپتامبر ۲۰۲۷ (فشرده — جزئیات در شیت «برنامهٔ زمانی ۲۰۲۷»)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>اکتبر ۲۰۲۶: نظام‌وظیفه + رزرو IELTS خارج از ایران + مدارک · ۱۶ اکتبر: باز شدن سوئد · نوامبر–دسامبر: IELTS + VPD uni-assist · ۱۵ ژانویه ۲۰۲۷: مهلت سوئد / AAU / Stuttgart · ۱ فوریه: مدارک سوئد + SDU · فوریه–مارس: ایرلند و انگلستان · ۱ آوریل: Radboud · ۱ می: Twente · ۳۱ می: Passau / TU Dublin · می–ژوئن: پول + ویزا یا برنامهٔ B · ۱ ژوئیه: UL · اوت–اکتبر: شروع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>سه پیش‌نیاز عملی ورودی ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>(۱) آزمون زبان: IELTS و TOEFL در ایران برگزار نمی‌شوند → سفر به ترکیه/ارمنستان/امارات/گرجستان تا دسامبر ۲۰۲۶. (۲) نظام‌وظیفه: بدون کارت/معافیت، خروج تحصیلی فقط با مجوز سخا + وثیقهٔ ۲۰۰ میلیون تومان + پذیرش از دانشگاه مورد تأیید وزارت علوم. (۳) نقدینگی: شهریه/تمکن سال اول باید تا می–ژوئن ۲۰۲۷ قابل انتقال باشد (SDU یک سال کامل پیش‌پرداخت). اگر یکی از این سه تا ژانویه ۲۰۲۷ حل نشود، هدف واقع‌بینانه ایرلند/انگلستان/هلند/آلمان با مهلت‌های بهار ۲۰۲۷ است — یا ورودی ۲۰۲۸.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>تغییرات اصلی نسبت به جدول اول</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>• هزینه کل دوره اضافه شد (هلند از «نیاز به تأمین سال دوم» به گران‌ترین گزینه تبدیل شد)
+• فقط انگلستان (به خواست شما): Strathclyde و Swansea حذف شدند؛ گزینه‌ها Teesside £17,000 · Northumbria £21,500 · Leicester £24,250 · Essex £24,675 · Brunel £24,795 · York £32,900؛ Graduate visa ۱۸ ماه؛ کف اسپانسری £54,700 / £38,290؛ طرح PR ۱۰ ساله؛ عوارض £925 از ۲۰۲۸ شامل همهٔ گزینه‌ها
+• کف حقوق ۲۰۲۶ همه کشورها به‌روز شد (آلمان €50,700/€45,934؛ هلند €3,122/ماه؛ سوئد SEK 34,470؛ ایرلند €40,904)
+• ایرلند: ۲ سال CSEP = Stamp 4 نه PR؛ تمکن €10,000
+• سوئد: کار دانشجویی ۱۵ ساعت/هفته (ژوئن ۲۰۲۶)؛ شهروندی ۸ سال؛ «BTH یک‌ساله» حذف شد؛ خوابگاه فقط LiU
+• QS 2027؛ شهریه‌های واقعی 2026/27؛ «۷۵٪ قبولی» حذف شد
+• «۱۰۰٪ انگلیسی» برای هلند/سوئد/دانمارک تعدیل شد؛ دانمارک PD2/PD3 تفکیک شد
+• ردیف ویزا برای وضعیت ۲۰۲۶ بازنویسی شد؛ ردیف‌های IELTS، تمکن مالی، پس‌انداز، شهروندی و امتیاز اضافه شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>چرا «انگلستان» و نه «بریتانیا»</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>به خواست شما فقط دانشگاه‌های انگلستان مقایسه شده‌اند. قوانین ویزا، کار و اقامت در کل بریتانیا یکسان است؛ سه تفاوت عملی: (۱) ارزان‌ترین گزینه‌های انگلستان (Teesside £17,000، Northumbria £21,500) از Swansea/Strathclyde ارزان‌ترند → کل دوره از $48–71k به $38–65k رسید؛ (۲) عوارض £925 به ازای هر دانشجو از اوت ۲۰۲۸ فقط دانشگاه‌های انگلستان را می‌گیرد — یعنی همهٔ گزینه‌های شما؛ (۳) بازار کار فناوری بریتانیا عملاً در انگلستان است (London، Manchester، Cambridge، Bristol، Leeds) — حذف اسکاتلند/ولز به فرصت شغلی لطمه نمی‌زند. برای شهریهٔ کمتر باید رتبهٔ پایین‌تر را بپذیرید: Teesside/Chester بدون رتبه QS، Northumbria ≈ ۵۲۸، Essex ≈ ۴۳۸؛ York (۱۵۸) و Newcastle (۱۴۹) تقریباً دوبرابر گران‌ترند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>نکته پروفایل</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>معدل (۱۵.۷۷ طبق جدول اول؛ ۱۵.۷۰ طبق نقد دوم — تفاوتی در نتیجه ندارد) برای همه برنامه‌های بالا بالاتر از حداقل است. مهم‌تر از معدل، تطابق ریزنمرات با پیش‌نیازها (ریاضی، الگوریتم، CS نظری) و SOP با تکیه بر ۲ سال سابقه کار + بازی‌سازی + پروژه‌های گیت‌هاب است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>اعداد را چگونه بخوانم</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>مبالغ سطح 2026/27 هستند؛ نرخ 2027/28 (سال ورود شما) بین اکتبر ۲۰۲۶ تا بهار ۲۰۲۷ منتشر می‌شود — جایی که رسمی بود (TU/e €22,400، Surrey £26,900، Gothenburg SEK 294k کل) در جدول آمده؛ برای بقیه فعلاً ۳–۵٪ اضافه کنید. نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -11405,7 +12073,7 @@
           <t>آلمان – EU Blue Card 2026 (€50,700 / €45,934.20)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/visa-residence/types/eu-blue-card</t>
         </is>
@@ -11417,7 +12085,7 @@
           <t>آلمان – Sperrkonto €992/ماه (2026)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/study-training/study/financing</t>
         </is>
@@ -11429,7 +12097,7 @@
           <t>آلمان – Niederlassungserlaubnis §18c (فارغ‌التحصیلان، ۲ سال، B1)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/visa-residence/living-permanently/permanent-residence</t>
         </is>
@@ -11441,7 +12109,7 @@
           <t>آلمان – Stuttgart MSc Computer Science (انگلیسی، IELTS 7، €1,500/ترم)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc./</t>
         </is>
@@ -11453,7 +12121,7 @@
           <t>آلمان – FAU MSc Artificial Intelligence (انگلیسی، B2)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>https://www.ai.study.fau.eu/prospective-students/living-studying-in-germany/language-proficiency/</t>
         </is>
@@ -11465,7 +12133,7 @@
           <t>آلمان – TU Darmstadt MSc Computer Science</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>https://www.informatik.tu-darmstadt.de/studium_fb20/im_studium/studiengaenge_liste/computer_science_msc.en.jsp</t>
         </is>
@@ -11477,7 +12145,7 @@
           <t>آلمان – TU Dresden MSc Computer Science admission</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>https://tu-dresden.de/ing/informatik/studium/studienangebot/master-studiengaenge/m-sc-computer-science/admission?set_language=en</t>
         </is>
@@ -11489,7 +12157,7 @@
           <t>آلمان – TLScontact Tehran (لیست انتظار دانشجویی)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>https://visas-de.tlscontact.com/en-us/country/ir/vac/irTHR2de</t>
         </is>
@@ -11501,7 +12169,7 @@
           <t>آلمان – وضعیت سفارت تهران (Iran International، اوت ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>https://www.iranintl.com/en/202608115899</t>
         </is>
@@ -11513,7 +12181,7 @@
           <t>آلمان – Fintiba: ساکنان ایران پذیرفته نمی‌شوند</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>https://www.simplegermany.com/best-blocked-account-germany/</t>
         </is>
@@ -11525,7 +12193,7 @@
           <t>آلمان – حقوق توسعه‌دهنده (StepStone)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>https://www.stepstone.de/gehalt/Software-Entwickler-in.html</t>
         </is>
@@ -11537,7 +12205,7 @@
           <t>هلند – IND مبالغ ۲۰۲۶ (HSM €3,122 / €4,357؛ دانشجو €1,130.77)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>https://ind.nl/en/required-amounts-income-requirements</t>
         </is>
@@ -11549,7 +12217,7 @@
           <t>هلند – Twente شهریه 2026/27 €21,700</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/computer-science/finance/</t>
         </is>
@@ -11561,7 +12229,7 @@
           <t>هلند – Twente حداقل معدل برای مدرک ایرانی (۱۵/۲۰)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/european-studies/admission/international/</t>
         </is>
@@ -11573,7 +12241,7 @@
           <t>هلند – Twente QS 2027 = 223</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/about-us/impact-ambitions/rankings/</t>
         </is>
@@ -11585,7 +12253,7 @@
           <t>هلند – Radboud شهریهٔ رسمی 2026/27 غیر-EEA €19,714 (Data Science and AI؛ دانشکدهٔ علوم)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>https://www.ru.nl/en/education/masters/data-science-and-ai/tuition</t>
         </is>
@@ -11597,7 +12265,7 @@
           <t>هلند – MVV در ایران (سفارت در باکو)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>https://www.netherlandsworldwide.nl/visa-the-netherlands/mvv-long-stay/apply-iran</t>
         </is>
@@ -11609,7 +12277,7 @@
           <t>هلند – B1 برای PR/تابعیت (تصمیم کابینه ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>https://thedutchdaily.nl/dutch-citizenship-b1-language-requirement-confirmed-2026/</t>
         </is>
@@ -11621,7 +12289,7 @@
           <t>سوئد – قوانین جدید اقامت تحصیلی از ۱۱ ژوئن ۲۰۲۶ (۱۵ ساعت/هفته)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/nyheter/news-archive/2026-05-25-new-rules-for-residence-permits-for-studies-in-higher-education.html</t>
         </is>
@@ -11633,7 +12301,7 @@
           <t>سوئد – قوانین جدید مجوز کار از ۱ ژوئن ۲۰۲۶ (SEK 34,470)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/nyheter/news-archive/2026-04-17-new-rules-for-work-permits-from-1-june-2026.html</t>
         </is>
@@ -11645,7 +12313,7 @@
           <t>سوئد – گروه‌های معاف (فارغ‌التحصیلان ۷۵٪)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>https://eiglaw.com/sweden-publishes-exempt-occupations-for-new-salary-rule/</t>
         </is>
@@ -11657,7 +12325,7 @@
           <t>سوئد – مجوز ۱۲ ماهه جست‌وجوی کار و تمکن SEK 10,656</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/en/you-want-to-extend/study/look-for-work-after-completing-your-studies-in-sweden.html</t>
         </is>
@@ -11669,7 +12337,7 @@
           <t>سوئد – Linköping MSc CS شهریه SEK 332,000 (کل)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>https://liu.se/en/education/program/6mics</t>
         </is>
@@ -11681,7 +12349,7 @@
           <t>سوئد – BTH MSc Software Engineering 120 credits (SEK 70,000/ترم)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>https://www.bth.se/english/education/programmes/masters-programme-in-software-engineering-120-credits</t>
         </is>
@@ -11693,7 +12361,7 @@
           <t>سوئد – BTH برنامه ۶۰ واحدی (از راه دور، نیمه‌وقت، ۲ سال سابقه)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>https://www.bth.se/english/education/programmes/masters-programme-in-software-engineering-60-credits</t>
         </is>
@@ -11705,7 +12373,7 @@
           <t>سوئد – Halmstad MSc Information Technology شهریه</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>https://www.mastersportal.com/studies/22787/information-technology.html</t>
         </is>
@@ -11717,7 +12385,7 @@
           <t>سوئد – Halmstad مسکن (بدون تضمین)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>https://www.hh.se/english/education/student-life/find-accommodation.html</t>
         </is>
@@ -11729,7 +12397,7 @@
           <t>سوئد – شهروندی ۸ ساله از ژوئن ۲۰۲۶</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>https://www.imidaily.com/europe/sweden-passes-law-curtailing-naturalization-8-year-wait-income-floor/</t>
         </is>
@@ -11741,7 +12409,7 @@
           <t>سوئد – اطلاعیه مهاجرتی سفارت تهران</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>https://www.swedenabroad.se/globalassets/ambassader/iran-teheran/documents/migration-issues/new-folder/english-versin.pdf</t>
         </is>
@@ -11753,7 +12421,7 @@
           <t>دانمارک – Pay Limit Scheme 2026</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/pl-PL/You-want-to-apply/Work/Pay-limit-scheme</t>
         </is>
@@ -11765,7 +12433,7 @@
           <t>دانمارک – برنامه‌های آموزش عالی: ۹۰ ساعت/ماه، ۶ ماه یا ۳ سال جست‌وجوی کار</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/en-GB/You-want-to-apply/Study/Higher-Education</t>
         </is>
@@ -11777,7 +12445,7 @@
           <t>دانمارک – مجوز ۳ ساله جست‌وجوی کار</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/de-DE/You-want-to-apply/Study/Study---job-seeking/Study---3-years-job-seeking</t>
         </is>
@@ -11789,7 +12457,7 @@
           <t>دانمارک – اقامت دائم</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/de-DE/You-want-to-apply/Permanent-residence-permit/Permanent-residence</t>
         </is>
@@ -11801,7 +12469,7 @@
           <t>دانمارک – تمکن DKK 7,426 (2026)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>https://nyidanmark.dk/en-GB/Words-and-concepts/SIRI/Self-support---SIRI</t>
         </is>
@@ -11813,7 +12481,7 @@
           <t>دانمارک – AAU Computer Science (IT) شهریه €7,455/ترم</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>https://studyindenmark.dk/portal/aalborg-university-aau/aalborg/computer-science-it-msc</t>
         </is>
@@ -11825,7 +12493,7 @@
           <t>دانمارک – SDU شهریهٔ رسمی از ورودی ۲۰۲۶: Science/Engineering €17,300 در سال</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
         </is>
@@ -11837,7 +12505,7 @@
           <t>دانمارک – SDU MSc Computer Science (ظرفیت محدود، €17,300)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi/adgangskrav</t>
         </is>
@@ -11849,7 +12517,7 @@
           <t>دانمارک – سفارت تهران (درخواست از ایران ممکن نیست)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>https://iran.um.dk/en</t>
         </is>
@@ -11861,7 +12529,7 @@
           <t>دانمارک – IDA حقوق شروع ۲۰۲۶</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>https://studerende.ida.dk/snart-nyuddannet/loen/softwareingenioer-loen-saa-meget-kommer-du-til-at-tjene/</t>
         </is>
@@ -11873,7 +12541,7 @@
           <t>ایرلند – کف حقوق مجوز کار از ۱ مارس ۲۰۲۶ (€40,904 / €36,848 / €36,605)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>https://kodlyons.ie/critical-skills-employment-permit-changes/</t>
         </is>
@@ -11885,7 +12553,7 @@
           <t>ایرلند – نقشه راه DETE تا ۲۰۳۰</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>https://www.visahq.com/news/2025-12-12/ie/ireland-sets-phased-salary-threshold-hikes-for-all-work-permit-categories-first-rise-due-1-march-2026/</t>
         </is>
@@ -11897,7 +12565,7 @@
           <t>ایرلند – ISD تمکن دانشجویی €10,000</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>https://www.irishimmigration.ie/coming-to-study-in-ireland/what-are-my-study-options/a-fee-paying-private-primary-or-secondary-school/information-on-student-finances/</t>
         </is>
@@ -11909,7 +12577,7 @@
           <t>ایرلند – UL MSc Software Engineering €20,800</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>https://www.ul.ie/study/postgraduate/software-engineering-msc</t>
         </is>
@@ -11921,7 +12589,7 @@
           <t>ایرلند – Maynooth فهرست شهریه 2025/26</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>https://www.maynoothuniversity.ie/sites/default/files/assets/document/2025.26%20Postgraduate%20EU%20&amp;%20International%20Fees%20List%20(24.02.25)%20V.4%20CHR.pdf</t>
         </is>
@@ -11933,7 +12601,7 @@
           <t>ایرلند – سفارت/کنسول افتخاری تهران</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>https://www.ireland.ie/en/tehran/</t>
         </is>
@@ -11945,7 +12613,7 @@
           <t>ایرلند – QS 2027 دانشگاه‌های ایرلند</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>https://www.thejournal.ie/irish-universities-qs-world-university-rankings-2027-7073948-Jun2026/</t>
         </is>
@@ -11957,7 +12625,7 @@
           <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
         </is>
@@ -11969,7 +12637,7 @@
           <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
         </is>
@@ -11981,7 +12649,7 @@
           <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
         </is>
@@ -11993,7 +12661,7 @@
           <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
         </is>
@@ -12005,7 +12673,7 @@
           <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
@@ -12017,7 +12685,7 @@
           <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
@@ -12029,7 +12697,7 @@
           <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
@@ -12041,7 +12709,7 @@
           <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
@@ -12053,7 +12721,7 @@
           <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
@@ -12065,7 +12733,7 @@
           <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
         </is>
@@ -12077,7 +12745,7 @@
           <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
@@ -12089,7 +12757,7 @@
           <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
         </is>
@@ -12101,7 +12769,7 @@
           <t>بریتانیا – وضعیت VAC تهران</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
         </is>
@@ -12113,7 +12781,7 @@
           <t>QS WUR 2027 – TU Dresden</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
         </is>
@@ -12125,7 +12793,7 @@
           <t>QS WUR 2027 – Stuttgart</t>
         </is>
       </c>
-      <c r="B62" s="15" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
         </is>
@@ -12137,7 +12805,7 @@
           <t>QS WUR 2027 – Newcastle 149</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
         </is>
@@ -12149,7 +12817,7 @@
           <t>QS WUR 2027 – York =158</t>
         </is>
       </c>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>https://www.york.ac.uk/about/rankings/</t>
         </is>
@@ -12161,7 +12829,7 @@
           <t>QS WUR 2027 – Leicester =314</t>
         </is>
       </c>
-      <c r="B65" s="15" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>https://www.topuniversities.com/universities/university-leicester</t>
         </is>
@@ -12173,7 +12841,7 @@
           <t>QS WUR 2027 – Essex =438</t>
         </is>
       </c>
-      <c r="B66" s="15" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>https://www.topuniversities.com/universities/essex-university</t>
         </is>
@@ -12185,7 +12853,7 @@
           <t>QS WUR 2027 – Northumbria =528</t>
         </is>
       </c>
-      <c r="B67" s="15" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
         </is>
@@ -12197,7 +12865,7 @@
           <t>QS WUR 2027 – Brunel</t>
         </is>
       </c>
-      <c r="B68" s="15" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
         </is>
@@ -12209,7 +12877,7 @@
           <t>QS WUR 2027 – سایر</t>
         </is>
       </c>
-      <c r="B69" s="15" t="inlineStr">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>https://www.topuniversities.com/world-university-rankings</t>
         </is>
@@ -12221,7 +12889,7 @@
           <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
         </is>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
         </is>
@@ -12233,7 +12901,7 @@
           <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>https://www.xe.com/</t>
         </is>
@@ -12245,7 +12913,7 @@
           <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
         </is>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
         </is>
@@ -12257,7 +12925,7 @@
           <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
         </is>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
         </is>
@@ -12269,7 +12937,7 @@
           <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
         </is>
       </c>
-      <c r="B74" s="15" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>https://www.isc2.org/research</t>
         </is>
@@ -12281,7 +12949,7 @@
           <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
         </is>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
         </is>
@@ -12293,7 +12961,7 @@
           <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
         </is>
       </c>
-      <c r="B76" s="15" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
         </is>
@@ -12305,7 +12973,7 @@
           <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
         </is>
       </c>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
         </is>
@@ -12317,7 +12985,7 @@
           <t>ایرلند – UL MSc AI &amp; ML: €20,800</t>
         </is>
       </c>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>https://www.ul.ie/study/postgraduate/artificial-intelligence-and-machine-learning-msc</t>
         </is>
@@ -12329,7 +12997,7 @@
           <t>ایرلند – TU Dublin MSc Applied Cyber Security: €14,500، 2:2</t>
         </is>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>https://www.tudublin.ie/study/postgraduate/courses/applied-cyber-security/</t>
         </is>
@@ -12341,7 +13009,7 @@
           <t>ایرلند – TU Dublin MSc CS (Data Science): €21,750، 2:2 + ۲ سال سابقه</t>
         </is>
       </c>
-      <c r="B80" s="15" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>https://www.tudublin.ie/study/postgraduate/courses/computing-data-science/</t>
         </is>
@@ -12353,7 +13021,7 @@
           <t>ایرلند – DCU MSc Computing majors: €25,000، 2:1، بورس €5,000</t>
         </is>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>https://www.dcu.ie/courses/postgraduate/school-computing/msc-computing-major-options</t>
         </is>
@@ -12365,7 +13033,7 @@
           <t>ایرلند – Galway MSc CS (AI) €28,000 / SDD €18,440، 2026/27</t>
         </is>
       </c>
-      <c r="B82" s="15" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>http://cs.universityofgalway.ie/science-engineering/postgraduateprogrammes/taught-postgraduate-courses/software-design-development.html</t>
         </is>
@@ -12377,7 +13045,7 @@
           <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
         </is>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr">
         <is>
           <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
@@ -12389,7 +13057,7 @@
           <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
         </is>
       </c>
-      <c r="B84" s="15" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
@@ -12401,7 +13069,7 @@
           <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
         </is>
       </c>
-      <c r="B85" s="15" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
@@ -12413,7 +13081,7 @@
           <t>آلمان – Siegen MSc HCI (DAAD)</t>
         </is>
       </c>
-      <c r="B86" s="15" t="inlineStr">
+      <c r="B86" s="16" t="inlineStr">
         <is>
           <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
@@ -12425,7 +13093,7 @@
           <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
         </is>
       </c>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
@@ -12437,7 +13105,7 @@
           <t>آلمان – RWTH MSc Software Systems Engineering</t>
         </is>
       </c>
-      <c r="B88" s="15" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
@@ -12449,7 +13117,7 @@
           <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
         </is>
       </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
@@ -12461,7 +13129,7 @@
           <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
         </is>
       </c>
-      <c r="B90" s="15" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
         <is>
           <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
@@ -12473,7 +13141,7 @@
           <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
         </is>
       </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
@@ -12485,7 +13153,7 @@
           <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
         </is>
       </c>
-      <c r="B92" s="15" t="inlineStr">
+      <c r="B92" s="16" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
@@ -12497,7 +13165,7 @@
           <t>هلند – Leiden CS 2026/27: €22,500</t>
         </is>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
@@ -12509,7 +13177,7 @@
           <t>هلند – Groningen AI 2026/27: €24,900</t>
         </is>
       </c>
-      <c r="B94" s="15" t="inlineStr">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
@@ -12521,7 +13189,7 @@
           <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
         </is>
       </c>
-      <c r="B95" s="15" t="inlineStr">
+      <c r="B95" s="16" t="inlineStr">
         <is>
           <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
@@ -12533,7 +13201,7 @@
           <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
         </is>
       </c>
-      <c r="B96" s="15" t="inlineStr">
+      <c r="B96" s="16" t="inlineStr">
         <is>
           <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
         </is>
@@ -12545,7 +13213,7 @@
           <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
         </is>
       </c>
-      <c r="B97" s="15" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
@@ -12557,7 +13225,7 @@
           <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
         </is>
       </c>
-      <c r="B98" s="15" t="inlineStr">
+      <c r="B98" s="16" t="inlineStr">
         <is>
           <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
@@ -12569,7 +13237,7 @@
           <t>سوئد – Umeå AI: SEK 152,300</t>
         </is>
       </c>
-      <c r="B99" s="15" t="inlineStr">
+      <c r="B99" s="16" t="inlineStr">
         <is>
           <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
@@ -12581,7 +13249,7 @@
           <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
         </is>
       </c>
-      <c r="B100" s="15" t="inlineStr">
+      <c r="B100" s="16" t="inlineStr">
         <is>
           <t>https://www.study.eu/best-universities/sweden</t>
         </is>
@@ -12593,7 +13261,7 @@
           <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
         </is>
       </c>
-      <c r="B101" s="15" t="inlineStr">
+      <c r="B101" s="16" t="inlineStr">
         <is>
           <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
@@ -12605,7 +13273,7 @@
           <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
         </is>
       </c>
-      <c r="B102" s="15" t="inlineStr">
+      <c r="B102" s="16" t="inlineStr">
         <is>
           <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
         </is>
@@ -12617,7 +13285,7 @@
           <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
         </is>
       </c>
-      <c r="B103" s="15" t="inlineStr">
+      <c r="B103" s="16" t="inlineStr">
         <is>
           <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
@@ -12629,7 +13297,7 @@
           <t>دانمارک – Aarhus CS €17,300</t>
         </is>
       </c>
-      <c r="B104" s="15" t="inlineStr">
+      <c r="B104" s="16" t="inlineStr">
         <is>
           <t>https://masters.au.dk/computerscience</t>
         </is>
@@ -12641,7 +13309,7 @@
           <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
         </is>
       </c>
-      <c r="B105" s="15" t="inlineStr">
+      <c r="B105" s="16" t="inlineStr">
         <is>
           <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
         </is>
@@ -12653,7 +13321,7 @@
           <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
         </is>
       </c>
-      <c r="B106" s="15" t="inlineStr">
+      <c r="B106" s="16" t="inlineStr">
         <is>
           <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
         </is>
@@ -12665,7 +13333,7 @@
           <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
         </is>
       </c>
-      <c r="B107" s="15" t="inlineStr">
+      <c r="B107" s="16" t="inlineStr">
         <is>
           <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
         </is>
@@ -12677,7 +13345,7 @@
           <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
         </is>
       </c>
-      <c r="B108" s="15" t="inlineStr">
+      <c r="B108" s="16" t="inlineStr">
         <is>
           <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
         </is>
@@ -12689,7 +13357,7 @@
           <t>انگلستان – MMU MSc Cyber Security £21,000</t>
         </is>
       </c>
-      <c r="B109" s="15" t="inlineStr">
+      <c r="B109" s="16" t="inlineStr">
         <is>
           <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
         </is>
@@ -12701,7 +13369,7 @@
           <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
         </is>
       </c>
-      <c r="B110" s="15" t="inlineStr">
+      <c r="B110" s="16" t="inlineStr">
         <is>
           <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
         </is>
@@ -12713,7 +13381,7 @@
           <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
         </is>
       </c>
-      <c r="B111" s="15" t="inlineStr">
+      <c r="B111" s="16" t="inlineStr">
         <is>
           <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
         </is>
@@ -12725,7 +13393,7 @@
           <t>انگلستان – NTU QS 2027 =639</t>
         </is>
       </c>
-      <c r="B112" s="15" t="inlineStr">
+      <c r="B112" s="16" t="inlineStr">
         <is>
           <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
         </is>
@@ -12737,7 +13405,7 @@
           <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
         </is>
       </c>
-      <c r="B113" s="15" t="inlineStr">
+      <c r="B113" s="16" t="inlineStr">
         <is>
           <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
         </is>
@@ -12749,7 +13417,7 @@
           <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
         </is>
       </c>
-      <c r="B114" s="15" t="inlineStr">
+      <c r="B114" s="16" t="inlineStr">
         <is>
           <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
         </is>
@@ -12761,7 +13429,7 @@
           <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
         </is>
       </c>
-      <c r="B115" s="15" t="inlineStr">
+      <c r="B115" s="16" t="inlineStr">
         <is>
           <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
         </is>
@@ -12773,7 +13441,7 @@
           <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
         </is>
       </c>
-      <c r="B116" s="15" t="inlineStr">
+      <c r="B116" s="16" t="inlineStr">
         <is>
           <t>https://www.en.aau.dk/education/master/computer-science-it</t>
         </is>
@@ -12785,7 +13453,7 @@
           <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
         </is>
       </c>
-      <c r="B117" s="15" t="inlineStr">
+      <c r="B117" s="16" t="inlineStr">
         <is>
           <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
         </is>
@@ -12797,7 +13465,7 @@
           <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
         </is>
       </c>
-      <c r="B118" s="15" t="inlineStr">
+      <c r="B118" s="16" t="inlineStr">
         <is>
           <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
         </is>
@@ -12809,7 +13477,7 @@
           <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
         </is>
       </c>
-      <c r="B119" s="15" t="inlineStr">
+      <c r="B119" s="16" t="inlineStr">
         <is>
           <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
         </is>
@@ -12821,9 +13489,177 @@
           <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
         </is>
       </c>
-      <c r="B120" s="15" t="inlineStr">
+      <c r="B120" s="16" t="inlineStr">
         <is>
           <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>https://zandienglish.ir/toefl-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+        </is>
+      </c>
+      <c r="B125" s="16" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Twente: مهلت غیر-EEA ۱ می ۲۰۲۷؛ بورس UTS ۱۵ اکتبر ۲۰۲۶ – ۱ آوریل ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/netherlands/university/749-university-of-twente-enschede/admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند – UL: مهلت غیر-EU ویزایی ۱ ژوئیه؛ اپلای از ۱۵ اکتبر</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ul.ie/gps/applications-faq</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند – Maynooth: باز شدن اپلای ۲۰۲۷ در ۱۴ اکتبر ۲۰۲۶؛ ودیعهٔ غیر-EU €1,000</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>https://www.maynoothuniversity.ie/study-maynooth/how-apply/postgraduate-applicants</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>ایرلند – مهلت‌های تقریبی TU Dublin (۳۱ می) و Maynooth (۱۵ می) برای غیر-EU</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>https://studyinireland.app/apply/deadlines</t>
         </is>
       </c>
     </row>
@@ -12948,6 +13784,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -15,7 +15,7 @@
     <sheet name="منابع" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -583,7 +583,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ایرلند 🇮🇪</t>
+          <t>سوئیس 🇨🇭</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -641,10 +641,11 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin (Dublin) – MSc Computing (Advanced Software Development) → Safe
-Maynooth (۲۵ km از Dublin) – MSc (CS) Software Engineering، ۱ ساله → Safe/Target
-UL (Limerick) – MSc Software Engineering → Target
-(شرط 2.2 honours ≈ معدل شما OK)</t>
+          <t>USI (Lugano) – MSc Informatics / MSc Artificial Intelligence / MSc Software &amp; Data Engineering (انگلیسی؛ ورود با B2) → Target
+HSLU (Lucerne) – MSc Applied Information and Data Science (انگلیسی؛ C1 یا B2 مشروط؛ بدون آلمانی) → Safe/Target
+Bern یا Fribourg – Swiss Joint MSc Computer Science (90 ECTS، انگلیسی) → Target
+ZHAW (Zürich/Winterthur) – MSE Computer Science / Data Science / Cyber Security (فقط با معدل A/B کارشناسی) → Target/Reach
+ETH Zürich، EPFL، UZH، Basel → Reach (با معدل ۱۵.۷۷ احتمال پذیرش کم)</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -698,7 +699,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>UL 388 · Maynooth 721–730 · TU Dublin 791–800</t>
+          <t>ETH Zürich =8 · EPFL =22 · UZH =98 · Basel =150 · Bern =191 · USI =456 · Fribourg =670 · ZHAW 851–900 · HSLU رتبه ندارد</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -745,7 +746,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>۱ سال (90 ECTS، ۱۲ ماه)</t>
+          <t>۱.۵ سال (90 ECTS: Bern/Fribourg/UZH/Basel/ZHAW) یا ۲ سال (120 ECTS: ETH، EPFL، USI، HSLU)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -798,9 +799,12 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin: ≈ €15,000–15,500
-Maynooth: €18,000 (2025/26) → ≈ €18,500
-UL: €20,800</t>
+          <t>به ازای هر ترم برای غیرمقیم سوئیس (۲ ترم در سال):
+USI: CHF 4,000 (= CHF 8,000/سال)
+ETH: CHF 2,190 + ≈ 74 (≈ CHF 4,530/سال) · EPFL: CHF 2,240 (≈ CHF 4,480/سال)
+HSLU: CHF 1,300 + ≈ 275 (≈ CHF 3,150/سال) · ZHAW: CHF 1,220 + 60 (≈ CHF 2,560/سال)
+Bern: CHF 950 (CHF 1,900/سال) · Fribourg: CHF 870 + 115 (≈ CHF 1,970/سال) · UZH: CHF 879 (≈ CHF 1,760/سال) · Basel: ≈ CHF 850–1,050
+⚠️ ETH/EPFL: افزایش دوباره (تا ≈ CHF 5,840/ترم برای خارجی‌ها) در بستهٔ صرفه‌جویی EP27 مطرح است؛ تصمیم شورای ETH برای ۲۰۲۷ هنوز اعلام نشده</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -816,7 +820,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>utwente.nl؛ liu.se؛ bth.se؛ sdu.dk؛ studyindenmark.dk؛ ul.ie؛ maynoothuniversity.ie؛ brunel.ac.uk؛ tees.ac.uk؛ northumbria.ac.uk؛ le.ac.uk؛ essex.ac.uk؛ york.ac.uk</t>
+          <t>utwente.nl؛ liu.se؛ bth.se؛ sdu.dk؛ studyindenmark.dk؛ ethz.ch؛ epfl.ch؛ uzh.ch؛ usi.ch؛ swissuniversities.ch؛ brunel.ac.uk؛ tees.ac.uk؛ northumbria.ac.uk؛ le.ac.uk؛ essex.ac.uk؛ york.ac.uk</t>
         </is>
       </c>
     </row>
@@ -853,7 +857,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>$17,100–23,700</t>
+          <t>$2,100–2,400 (Bern/UZH/Fribourg) · ≈ $3,100–3,800 (ZHAW/HSLU) · ≈ $5,400–5,500 (ETH/EPFL) · $9,700 (USI) — ارزان‌ترین بعد از آلمان</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -863,7 +867,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55</t>
+          <t>نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21</t>
         </is>
       </c>
     </row>
@@ -904,9 +908,9 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Dublin: €1,400–1,800 (اتاق €800–1,200)
-Limerick/Maynooth: €1,100–1,400
-حداقل رسمی ISD: €10,000 برای یک سال</t>
+          <t>Zürich: CHF 1,900–2,500 (≈ $2,300–3,000؛ اتاق WOKO CHF 500–900، اتاق خصوصی 800–1,200) · Lausanne: CHF 1,700–2,200
+Bern/Basel/Lucerne: CHF 1,550–2,100 · Lugano/Fribourg: CHF 1,400–1,800
+حداقل رسمی: CHF 21,000 در سال (Basel: 24,000)؛ کانتون زوریخ فقط حساب بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم سوئیس را می‌پذیرد</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -919,7 +923,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ irishimmigration.ie؛ gov.uk (HC 584)</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (HC 584)</t>
         </is>
       </c>
     </row>
@@ -956,7 +960,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>$32,000–48,000 (خارج از Dublin: $32,000–40,000)</t>
+          <t>$23,000–42,000 (Bern/Fribourg $23–31k · Lucerne $26–32k · Lugano/Lausanne $30–37k · Zürich $30–42k)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1003,7 +1007,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>$32,000–48,000 (۱ سال)</t>
+          <t>$35,000–84,000 (Bern/Fribourg ۱.۵ سال $35–47k · UZH $45–58k · HSLU $53–64k · USI/EPFL $60–75k · ETH $66–84k) — بعد از هلند گران‌ترین؛ شهریه ناچیز است، هزینهٔ زندگی همه‌چیز را تعیین می‌کند</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1050,7 +1054,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ خارج از Dublin یا با شهریه TU Dublin ✓؛ Dublin کسری</t>
+          <t>⚠️ فقط Bern/Fribourg (و با صرفه‌جویی Lucerne/Lugano) در بودجه؛ Zürich/Lausanne کسری $1,000–10,000 در سال؛ کار دانشجویی در ۶ ماه اول ممنوع → سال اول تماماً از جیب</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Dublin بحرانی و بسیار گران؛ UL دهکده‌های خوابگاهی کمپوس؛ Maynooth خوابگاه کمپوس (قرعه‌کشی).</t>
+          <t>Zürich بحرانی: WOKO/Juwo (CHF 500–900) لیست انتظار ۳–۱۲ ماه، بازار خصوصی بسیار رقابتی؛ Lausanne خوابگاه‌های FMEL (زود پر می‌شود)؛ Lugano/Fribourg/Bern/Lucerne آسان‌تر و ارزان‌تر (CHF 500–800). روز دریافت پذیرش ثبت‌نام کنید.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>۲۰ ساعت/هفته؛ ۴۰ ساعت/هفته در ژوئن–سپتامبر و ۱۵ دسامبر–۱۵ ژانویه</t>
+          <t>غیر-EU: ۶ ماه اول هیچ؛ بعد از آن ۱۵ ساعت/هفته در ترم و تمام‌وقت در تعطیلات؛ کارفرما باید مجوز کانتونی بگیرد؛ کل دورهٔ تحصیل در سوئیس حداکثر ۸ سال</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1154,7 +1158,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se (خبر ۲۵ مه ۲۰۲۶)؛ nyidanmark.dk؛ irishimmigration.ie؛ gov.uk</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se (خبر ۲۵ مه ۲۰۲۶)؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1195,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>تا ≈ €1,200 (۲۰ ساعت × €14.15)</t>
+          <t>بعد از ماه ششم: ≈ CHF 1,300–1,800 (۱۵ ساعت × CHF 22–28؛ دستیاری آموزشی/پژوهشی در ETH/UZH/ZHAW رایج)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1238,7 +1242,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>۱۰۰٪ انگلیسی؛ دفاتر اروپایی Google، Meta، Microsoft، Amazon، Stripe…</t>
+          <t>Zürich: انگلیسی در Big Tech (Google ≈ ۵ هزار نفر، Microsoft، Meta، Apple، Nvidia، OpenAI/Anthropic)، بانک‌ها و استارتاپ‌های ETH کافی؛ Lausanne/Geneva: انگلیسی + فرانسه؛ SMEهای آلمانی‌زبان و Lugano (ایتالیایی) زبان محلی می‌خواهند → بدون آلمانی/فرانسه ≈ نیمی از بازار بسته</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی.</t>
+          <t>رسمی: آلمانی / فرانسه / ایتالیایی بسته به کانتون؛ نامه‌های ادارهٔ مهاجرت، بیمه، اجاره و مالیات به زبان محلی؛ انگلیسی در زوریخ/ژنو/لوزان برای روزمره کافی است، ولی سوئیسی‌آلمانی (گویش) در محیط اجتماعی مانع است</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1332,7 +1336,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>۲۴ ماه Stamp 1G (۱۲ + ۱۲) — کار تمام‌وقت بدون مجوز</t>
+          <t>فقط ۶ ماه (مجوز L برای جست‌وجوی کار، مادهٔ ۲۱ بند ۳ FNIA) — کوتاه‌ترین در بین ۶ کشور؛ کار در این مدت تا ۱۵ ساعت/هفته</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1342,7 +1346,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ irishimmigration.ie؛ gov.uk (Statement of Changes ۱۴ اکتبر ۲۰۲۵)</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (Statement of Changes ۱۴ اکتبر ۲۰۲۵)</t>
         </is>
       </c>
     </row>
@@ -1384,9 +1388,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>CSEP: €40,904 (از ۱ مارس ۲۰۲۶؛ پلکانی تا ۲۰۳۰)
-تخفیف تا ۱۲ ماه بعد از مدرک: €36,848
-GEP: €36,605</t>
+          <t>کف عددی ندارد ولی حقوق باید «متعارف محل/رشته» باشد. فارغ‌التحصیل سوئیس از «اولویت داخلی/EU» معاف است اگر شغل «منفعت علمی/اقتصادی بالا» داشته باشد؛ ⚠️ ولی سهمیهٔ سالانهٔ اتباع غیر-EU (۲۰۲۶: ۴,۵۰۰ مجوز B + ۴,۰۰۰ L؛ معمولاً ≈ ۶۵–۷۰٪ مصرف می‌شود) شامل شما هم می‌شود — طرح معافیت فارغ‌التحصیلان (22.067) از ۲۰۲۳ در پارلمان متوقف مانده</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1398,7 +1400,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ enterprise.gov.ie (DETE)؛ gov.uk Appendix Skilled Occupations</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch (Art. 21 FNIA)؛ gov.uk Appendix Skilled Occupations</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1437,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>€35,000–45,000 (میانه Dublin ≈ €38k؛ Big Tech €50k+)</t>
+          <t>CHF 85,000–105,000 (≈ $103–127k؛ میانهٔ Glassdoor زوریخ CHF 92k؛ ETH/EPFL 90–118k؛ Big Tech CHF 110–165k) — بالاترین در بین ۶ کشور</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1482,7 +1484,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>€2,600–3,000</t>
+          <t>≈ CHF 5,700–6,700 (مالیات + بیمه‌های اجتماعی ≈ ۲۰–۲۵٪ برای مجرد در زوریخ)؛ بیمهٔ درمانی اجباری CHF 350–450/ماه جداگانه از جیب</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1529,7 +1531,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Dublin €400–1,000 · Limerick €800–1,300</t>
+          <t>CHF 1,500–3,000 (≈ $1,800–3,600) در زوریخ (استودیو CHF 1,400–1,900 + بیمه ≈ 400) — بیشترین پس‌انداز مطلق بین ۶ کشور، اگر شغل بگیرید</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1539,7 +1541,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>برآورد؛ هزینه زندگی شاغل: DE €1,400–1,700 · NL €1,700–2,100 · SE €1,300–1,600 · DK €1,900–2,300 · IE €1,800–2,300 · UK £1,300–1,700</t>
+          <t>برآورد؛ هزینه زندگی شاغل: DE €1,400–1,700 · NL €1,700–2,100 · SE €1,300–1,600 · DK €1,900–2,300 · CH CHF 3,200–3,800 · UK £1,300–1,700</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1578,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>۲ سال CSEP → Stamp 4 (کار آزاد؛ PR نیست)؛ اقامت بلندمدت: ۵ سال قابل‌احتساب (Stamp 2 دانشجویی حساب نمی‌شود)</t>
+          <t>اجازهٔ اقامت C: برای ایرانی‌ها ۱۰ سال (۵ سال آخر پیوسته با B)؛ سال‌های دانشجویی فقط اگر بعدش ۲ سال پیوسته اجازهٔ B داشته باشید حساب می‌شود؛ C زودهنگام ۵ ساله فقط با «ادغام موفق» و B1 شفاهی به صلاحدید کانتون — سخت‌ترین مسیر در بین ۶ کشور</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1586,7 +1588,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ irishimmigration.ie؛ gov.uk / Home Affairs Committee</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk / Home Affairs Committee</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1625,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>هیچ</t>
+          <t>A2 شفاهی + A1 کتبی زبان محلی (آزمون fide) برای C ۱۰ ساله؛ B1 شفاهی برای C زودهنگام ۵ ساله → بدون زبان سوم PR نمی‌گیرید</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1633,7 +1635,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>BAMF؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ irishimmigration.ie؛ gov.uk (HC 1691)</t>
+          <t>BAMF؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (HC 1691)</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1672,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>۵ سال قابل‌احتساب (بدون آزمون زبان)</t>
+          <t>۱۰ سال اقامت (سال‌های ۸ تا ۱۸ سالگی دوبرابر) + اجازهٔ C + B1 شفاهی / A2 کتبی + شرایط کانتون و شهرداری (۲–۵ سال اقامت محلی) — سخت‌ترین در اروپا</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1680,7 +1682,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>قوانین تابعیت ۲۰۲۶؛ migrationsverket.se؛ nyidanmark.dk؛ irishimmigration.ie</t>
+          <t>قوانین تابعیت ۲۰۲۶؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1719,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>AVATS آنلاین ✓؛ کنسول افتخاری تهران فعلاً درخواست ویزا نمی‌پذیرد — محل تحویل مدارک را هنگام اقدام بررسی کنید.</t>
+          <t>سفارت سوئیس در تهران باز است: ویزای D (تحصیلی) با وقت قبلی پذیرفته می‌شود، ویزای C فعلاً خیر (اطلاعیهٔ ۳۰ ژانویه ۲۰۲۶؛ در جنگ ژوئن ۲۰۲۵ دو هفته بسته بود). تصمیم را ادارهٔ مهاجرت کانتون می‌گیرد: ۸–۱۲ هفته؛ ETH تأییدیهٔ ثبت‌نام برای ویزا را از می ۲۰۲۷ می‌دهد. ⚠️ گلوگاه اصلی: اثبات تمکن (ردیف ۲۵).</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1727,7 +1729,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>visas-de.tlscontact.com؛ netherlandsworldwide.nl؛ swedenabroad.se؛ iran.um.dk؛ ireland.ie/tehran؛ gov.uk — برنامه B: اقدام از ترکیه/ارمنستان/امارات</t>
+          <t>visas-de.tlscontact.com؛ netherlandsworldwide.nl؛ swedenabroad.se؛ iran.um.dk؛ eda.admin.ch/tehran؛ gov.uk — برنامه B: اقدام از ترکیه/ارمنستان/امارات</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1767,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>IELTS 6.5 (هر بخش ≥ 6.0)</t>
+          <t>USI: B2 در ورود (IELTS 5.5–6.5) و C1 تا فارغ‌التحصیلی · HSLU: C1 (B2 مشروط) · Bern/Fribourg: «انگلیسی خیلی خوب» (معمولاً 6.5) · ZHAW: B2–C1 · UZH و ETH: C1 / IELTS 7.0 · EPFL: مدرک زبان الزامی نیست</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1812,7 +1814,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>€10,000 + شهریه سال اول (حداقل €6,000 پرداخت‌شده)؛ ۶ ماه گردش حساب.</t>
+          <t>CHF 21,000 برای هر سال (Basel 24,000) + شهریه؛ برای هر تمدید سالانه دوباره. زوریخ: فقط حساب بانک سوئیسی/شعبهٔ سوئیسی به نام خودتان (حساب والدین پذیرفته نیست) یا ضامن مقیم سوئیس (B/C)؛ بانک‌های سوئیس برای ساکنان ایران حساب باز نمی‌کنند → عملاً از تهران فقط با ضامن، یا کانتون‌های انعطاف‌پذیرتر (تیچینو، فریبورگ، برن، لوسرن — قبل از اقدام از دفتر بین‌الملل دانشگاه تأیید بگیرید). انتقال پول فقط از مسیر کشور ثالث.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1822,7 +1824,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ irishimmigration.ie؛ gov.uk (HC 584). افتتاح حساب بانکی برای ایرانی‌ها در همه‌جا کندتر است (آلمان و هلند بیشترین گزارش مشکل).</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (HC 584). افتتاح حساب بانکی برای ایرانی‌ها در همه‌جا کندتر است (آلمان و هلند بیشترین گزارش مشکل).</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1861,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐ هاب فناوری اروپا؛ ۲ سال Stamp 1G؛ رقابت جونیور زیاد ولی در باز</t>
+          <t>⭐⭐⭐ بالاترین حقوق اروپا و هاب Big Tech در زوریخ؛ ولی برای غیر-EU فقط ۶ ماه فرصت، سهمیه و شرط «منفعت اقتصادی بالا» → عملاً فقط شرکت‌های بزرگ/اسپین‌آف‌های ETH اسپانسر می‌شوند؛ رقابت با فارغ‌التحصیلان ETH/EPFL و EU؛ بازار ۲۰۲۶ گزینشی‌تر</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1906,7 +1908,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>پایین–متوسط: افزایش پلکانی کف حقوق تا ۲۰۳۰</t>
+          <t>متوسط: ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ رد شد (۵۴.۸٪ نه)؛ ولی بستهٔ صرفه‌جویی EP27 (۲۰۲۷–۲۹) → احتمال افزایش دوبارهٔ شهریهٔ ETH/EPFL برای خارجی‌ها؛ سهمیهٔ غیر-EU ثابت (۸,۵۰۰)؛ بستهٔ قراردادهای جدید با EU (Bilaterals III) در راه رفراندوم</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1953,7 +1955,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>7 / 10 / 8 = ۲۵</t>
+          <t>5 / 6 / 7 = ۱۸</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1963,14 +1965,14 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>وزن برابر. اگر «انگلیسی» وزن بیشتری دارد → ایرلند با فاصله؛ اگر «هزینه» وزن بیشتری دارد و B1 آلمانی را می‌پذیرید → آلمان. انگلستان با گزینه‌های ارزان شمال (Teesside/Northumbria) از ۱۷ به ۱۹ رسید (هم‌امتیاز سوئد) ولی هنوز از بودجهٔ سالانه $32k بیرون است.</t>
+          <t>وزن برابر. اگر «هزینه» وزن بیشتری دارد و B1 آلمانی را می‌پذیرید → آلمان؛ اگر «انگلیسی» وزن بیشتری دارد → انگلستان (کامل) و بعد هلند/سوئد؛ اگر «حقوق» وزن بیشتری دارد → سوئیس، به شرط پذیرش ریسک پنجرهٔ ۶ ماههٔ کار و هزینهٔ زندگی. سوئیس: هزینه ۵ (شهریه ناچیز ولی زندگی گران‌ترین)، انگلیسی ۶ (تحصیل و Big Tech انگلیسی، اداری/PR زبان محلی)، بازار ۷ (بالاترین حقوق، ولی دسترسی محدود برای غیر-EU). انگلستان با گزینه‌های ارزان شمال (Teesside/Northumbria) ۱۹ (هم‌امتیاز سوئد) ولی هنوز از بودجهٔ سالانه $32k بیرون است.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>تاریخ راستی‌آزمایی: ۲۷ سپتامبر ۲۰۲۶ (۵ مهر ۱۴۰۵). نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55</t>
+          <t>تاریخ راستی‌آزمایی: ۲۷ سپتامبر ۲۰۲۶ (۵ مهر ۱۴۰۵). نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q110"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4224,82 +4226,81 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin</t>
+          <t>USI – Università della Svizzera italiana</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Dublin – Blanchardstown (دوبلین، حومهٔ غربی)</t>
+          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,300–1,700</t>
+          <t>گران — CHF 1,400–1,800</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>MSc Computing in Applied Cyber Security</t>
+          <t>MSc Informatics (گرایش‌ها: Artificial Intelligence، Software Development، Systems…)</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>۱ سال (حضوری + آنلاین)</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>€14,500 (کل دوره)</t>
+          <t>CHF 4,000 در ترم برای غیرمقیم سوئیس (CHF 8,000/سال)</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>$16,500</t>
+          <t>$9,700</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2:2 (GPA 2.5) در Computing</t>
+          <t>کارشناسی CS/مرتبط؛ فارغ‌التحصیل UAS با ۳۰–۶۰ ECTS تکمیلی؛ بررسی موردی</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>6.5 (6.0)</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>791–800</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>B2 در ورود (IELTS 5.5) → C1 (7.0) تا فارغ‌التحصیلی</t>
+        </is>
+      </c>
+      <c r="M27" s="4">
+        <f>456</f>
+        <v/>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌ترین ارشد امنیت ایرلند در یک دانشگاه دولتی</t>
+          <t>کم‌شرط‌ترین ورود سوئیس؛ Lugano ارزان‌ترین شهر دانشگاهی سوئیس؛ مهلت غیر-EU ۳۰ آوریل ۲۰۲۷؛ زبان شهر ایتالیایی</t>
         </is>
       </c>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>https://www.tudublin.ie/study/postgraduate/courses/applied-cyber-security/</t>
+          <t>https://www.usi.ch/en/education/master/informatics</t>
         </is>
       </c>
     </row>
@@ -4309,63 +4310,62 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin</t>
+          <t>USI – Università della Svizzera italiana</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Dublin – Grangegorman (دوبلین، مرکز شهر)</t>
+          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,400–1,800</t>
+          <t>گران — CHF 1,400–1,800</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (Data Science)</t>
+          <t>MSc Artificial Intelligence (با IDSIA)</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>۱–۱.۵ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>€21,750 (کل دوره)</t>
+          <t>CHF 4,000 در ترم برای غیرمقیم (CHF 8,000/سال)</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>$24,800</t>
+          <t>$9,700</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2:1، یا 2:2 + ۲ سال سابقهٔ توسعهٔ نرم‌افزار</t>
+          <t>کارشناسی CS/مرتبط با ریاضی و برنامه‌نویسی قوی؛ بررسی موردی</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>6.5 (6.0)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>791–800</t>
-        </is>
+          <t>6.5 (B2؛ C1 تا پایان دوره)</t>
+        </is>
+      </c>
+      <c r="M28" s="4">
+        <f>456</f>
+        <v/>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
@@ -4374,17 +4374,17 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>۲ سال سابقهٔ کار شما اینجا شرط ورود را جبران می‌کند</t>
+          <t>اولین ارشد AI سوئیس؛ IDSIA (آزمایشگاه Schmidhuber/LSTM)؛ رقابتی‌تر از Informatics</t>
         </is>
       </c>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t>https://www.tudublin.ie/study/postgraduate/courses/computing-data-science/</t>
+          <t>https://www.usi.ch/en/education/master/artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -4394,82 +4394,81 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>TU Dublin</t>
+          <t>USI – Università della Svizzera italiana</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Dublin – Grangegorman (دوبلین، مرکز شهر)</t>
+          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,400–1,800</t>
+          <t>گران — CHF 1,400–1,800</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>MSc Computing (Advanced Software Development)</t>
+          <t>MSc Software and Data Engineering</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>≈ €15,000–15,500</t>
+          <t>CHF 4,000 در ترم برای غیرمقیم (CHF 8,000/سال)</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>$17,100–17,700</t>
+          <t>$9,700</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>791–800</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>B2 → C1</t>
+        </is>
+      </c>
+      <c r="M29" s="4">
+        <f>456</f>
+        <v/>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Safe جدول اصلی</t>
+          <t>ترکیب مهندسی نرم‌افزار + مهندسی داده (Data Engineering — همان توصیهٔ شیت حوزه‌ها)؛ کم‌رقابت‌تر از AI</t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>https://www.tudublin.ie/study/postgraduate/</t>
+          <t>https://www.usi.ch/en/education/master/software-and-data-engineering</t>
         </is>
       </c>
     </row>
@@ -4479,27 +4478,27 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Maynooth University</t>
+          <t>Hochschule Luzern (HSLU)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Maynooth (مینوث) — ۲۵ کیلومتری دوبلین</t>
+          <t>Lucerne / Luzern (لوسرن) — مرکز سوئیس، ۴۵ دقیقه تا زوریخ</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,400</t>
+          <t>گران — CHF 1,550–1,950</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science and Analytics (۱۲ ماهه، conversion)</t>
+          <t>MSc Applied Information and Data Science</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -4509,37 +4508,37 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>≈ €17,000</t>
+          <t>CHF 1,300 در ترم (خارجی) + ≈ CHF 275 هزینهٔ جانبی ≈ CHF 3,150/سال</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>$19,400</t>
+          <t>$3,800</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>مدرک Level 8 با محتوای ریاضی</t>
+          <t>هر کارشناسی ۱۸۰ ECTS؛ خوداظهاری + آزمون انگلیسی HSLU + مصاحبه در صورت نیاز</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>C1 (B2 مشروط)</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>721–730</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -4549,12 +4548,12 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>ورود آسان؛ ولی حوزهٔ اشباع جونیور</t>
+          <t>«باز برای تغییر رشته‌ای‌ها»، کاربردی و مدیریتی؛ آلمانی لازم نیست؛ شروع سپتامبر/فوریه؛ مهلت ≈ ۳۰ آوریل (چک شود)</t>
         </is>
       </c>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>https://www.maynoothuniversity.ie/study-maynooth/postgraduate-studies/courses/msc-data-science-and-analytics</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/</t>
         </is>
       </c>
     </row>
@@ -4564,27 +4563,27 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Maynooth University</t>
+          <t>University of Bern</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Maynooth (مینوث) — ۲۵ کیلومتری دوبلین</t>
+          <t>Bern (برن) — پایتخت؛ آلمانی‌زبان</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,400</t>
+          <t>گران — CHF 1,600–2,000</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>MSc (Computer Science) Software Engineering</t>
+          <t>Swiss Joint MSc Computer Science (Bern / Neuchâtel / Fribourg)</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -4594,37 +4593,36 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۱.۵ سال (90 ECTS)</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>€18,000 (2025/26) → ≈ €18,500</t>
+          <t>CHF 750 + 200 (خارجی) = CHF 950 در ترم (CHF 1,900/سال)</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>$21,100</t>
+          <t>$2,300</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>کارشناسی Computer Science (یا معادل با حداکثر ۶۰ ECTS تکمیلی)؛ تأیید ادارهٔ پذیرش برای مدرک خارجی</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>721–730</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+          <t>معمولاً 6.5 (C1 توصیه)</t>
+        </is>
+      </c>
+      <c r="M31" s="4">
+        <f>191</f>
+        <v/>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -4634,12 +4632,12 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>۲۵ دقیقه تا Dublin با قطار؛ اجاره کمتر از Dublin</t>
+          <t>ارزان‌ترین مسیر سوئیس با رتبهٔ زیر ۲۰۰؛ مهلت ۳۰ آوریل — ویزایی‌ها مهلت دیرهنگام ندارند؛ شهریه از mastersportal (≈)</t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>https://www.maynoothuniversity.ie/study-maynooth/postgraduate-studies</t>
+          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
         </is>
       </c>
     </row>
@@ -4649,63 +4647,62 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>University of Limerick (UL)</t>
+          <t>University of Fribourg</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Limerick (لیمریک) — سومین شهر ایرلند</t>
+          <t>Fribourg (فریبورگ) — دوزبانه (آلمانی/فرانسه)</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,100–1,400</t>
+          <t>گران — CHF 1,450–1,800</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence and Machine Learning</t>
+          <t>Swiss Joint MSc Computer Science (ثبت‌نام در Fribourg)</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۱.۵ سال (90 ECTS)</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>€20,800</t>
+          <t>CHF 870 در ترم (خارجی) + CHF 115 = ≈ CHF 1,970/سال</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>$23,700</t>
+          <t>$2,400</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>first یا second class honours در CS/Computer Engineering</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
+          <t>معمولاً 6.5</t>
+        </is>
+      </c>
+      <c r="M32" s="4">
+        <f>670</f>
+        <v/>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
@@ -4714,17 +4711,17 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ Limerick ارزان‌تر از Dublin</t>
+          <t>همان برنامهٔ مشترک Bern؛ شهر دوزبانه و ارزان‌تر؛ ⚠️ مهلت ویزایی‌ها ۲۸ فوریه ۲۰۲۷</t>
         </is>
       </c>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>https://www.ul.ie/study/postgraduate/artificial-intelligence-and-machine-learning-msc</t>
+          <t>https://www.unifr.ch/inf/en/</t>
         </is>
       </c>
     </row>
@@ -4734,27 +4731,27 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>University of Limerick (UL)</t>
+          <t>University of Basel</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Limerick (لیمریک) — سومین شهر ایرلند</t>
+          <t>Basel (بازل) — Roche، Novartis؛ مرز آلمان/فرانسه</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,100–1,400</t>
+          <t>گران — CHF 1,600–2,100</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -4764,37 +4761,36 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۱.۵ سال (90 ECTS)</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>€20,800</t>
+          <t>≈ CHF 850 در ترم (+ هزینهٔ احتمالی خارجی‌ها؛ صفحهٔ رسمی چک شود) ≈ CHF 1,700–2,100/سال</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>$23,700</t>
+          <t>$2,100–2,500</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>کارشناسی CS با نمرات خوب؛ بررسی فردی</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>B2–C1 (چک شود)</t>
+        </is>
+      </c>
+      <c r="M33" s="4">
+        <f>150</f>
+        <v/>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -4804,12 +4800,12 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>رتبهٔ ۱۵۰؛ ⚠️ کانتون Basel تمکن CHF 24,000/سال می‌خواهد؛ مهلت ۳۰ آوریل</t>
         </is>
       </c>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>https://www.ul.ie/study/postgraduate</t>
+          <t>https://www.unibas.ch/en/Studies/Degree-Programs.html</t>
         </is>
       </c>
     </row>
@@ -4819,82 +4815,81 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Munster Technological University (MTU)</t>
+          <t>University of Zurich (UZH)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Cork (کورک) — دومین شهر؛ مقر اروپایی Apple</t>
+          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>خیلی گران — CHF 1,900–2,500</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>MSc Cybersecurity</t>
+          <t>MSc Informatics (گرایش‌ها: Software Systems، Data Science، People-Oriented Computing…)</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۱.۵–۲ سال (90/120 ECTS)</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>≈ €12,000–15,000</t>
+          <t>CHF 720 + 100 (خارجی) + 59 = CHF 879 در ترم (≈ CHF 1,760/سال)</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>$13,700–17,100</t>
+          <t>$2,100</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>مدرک Level 8 honours در Computing</t>
+          <t>کارشناسی Informatics/CS با نمرات بسیار خوب؛ فقط یک درخواست در هر ترم؛ هزینهٔ درخواست CHF 150</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>C1 / IELTS 7.0</t>
+        </is>
+      </c>
+      <c r="M34" s="4">
+        <f>98</f>
+        <v/>
+      </c>
+      <c r="N34" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>Cork: مقر اروپایی Apple و ده‌ها شرکت امنیت؛ رقم از مراجع ثانویه</t>
+          <t>⚠️ مهلت ویزایی‌ها ۲۸ فوریه ۲۰۲۷ (بدون ویزا ۳۰ آوریل)؛ کانتون زوریخ: تمکن CHF 21,000 فقط در بانک سوئیسی به نام خودتان</t>
         </is>
       </c>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>https://www.mtu.ie/courses/</t>
+          <t>https://www.ifi.uzh.ch/en/studies/master.html</t>
         </is>
       </c>
     </row>
@@ -4904,78 +4899,82 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Munster Technological University (MTU)</t>
+          <t>ZHAW School of Engineering</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Cork (کورک) — دومین شهر؛ مقر اروپایی Apple</t>
+          <t>Zürich / Winterthur (زوریخ / وینترتور؛ کمپوس‌های ZHAW)</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>خیلی گران — CHF 1,800–2,400</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc in Engineering (MSE) — پروفایل Computer Science / Data Science / Information &amp; Cyber Security</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>چندحوزه‌ای (انتخاب گرایش)</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۱.۵ سال (90 ECTS؛ پاره‌وقت تا ۳ سال)</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>≈ €15,000</t>
+          <t>CHF 1,220 در ترم (خارجی) + CHF 60 ≈ CHF 2,560/سال</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>$17,100</t>
+          <t>$3,100</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Level 8 honours در CS/Eng + ریاضی و کدنویسی قوی</t>
+          <t>کارشناسی با نمرات A یا B (≈ یک‌سوم بالای کلاس) — گواهی رتبهٔ کلاسی از سمنان بگیرید</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>B2–C1</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N35" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+          <t>851–900</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr"/>
+          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>کاربردی و پروژه‌محور (کار در مؤسسات ZHAW، اغلب با حقوق دستیاری)؛ مهلت پایان آوریل؛ کانتون زوریخ (تمکن در بانک سوئیسی)</t>
+        </is>
+      </c>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>https://www.mtu.ie/courses/</t>
+          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
         </is>
       </c>
     </row>
@@ -4985,82 +4984,81 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Dublin City University (DCU)</t>
+          <t>EPFL</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Dublin – Glasnevin (دوبلین، شمال شهر؛ DCU)</t>
+          <t>Lausanne (لوزان) — کنار دریاچهٔ ژنو؛ فرانسه‌زبان؛ EPFL</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,400–1,800</t>
+          <t>خیلی گران — CHF 1,700–2,200</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>MSc in Computing — Majors: AI with NLP / Data Analytics / Secure Software Engineering / Cloud Computing</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>چندحوزه‌ای (انتخاب گرایش)</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>€25,000 (−€5,000 بورس دانشکده برای غیر-EU ⇒ €20,000)</t>
+          <t>CHF 2,240 در ترم برای خارجی‌های غیرمقیم (از پاییز ۲۰۲۵؛ ≈ CHF 4,480/سال)</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>$22,800–28,500</t>
+          <t>$5,400</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2:1 در CS/Computing</t>
+          <t>کارشناسی CS با نمرات عالی (بالای کلاس)؛ فقط یک برنامه در سال</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="N36" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>مدرک زبان الزامی نیست (C1 عملاً لازم)</t>
+        </is>
+      </c>
+      <c r="M36" s="4">
+        <f>22</f>
+        <v/>
+      </c>
+      <c r="N36" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>شرط 2:1؛ ورودی ژانویه ۲۰۲۷ هم دارد</t>
+          <t>دور اول ۱۵ دسامبر ۲۰۲۶ (توصیه برای ویزایی‌ها؛ پاسخ اوایل آوریل)، دور دوم ۳۱ مارس ۲۰۲۷؛ ⚠️ احتمال افزایش دوبارهٔ شهریه (EP27)</t>
         </is>
       </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>https://www.dcu.ie/courses/postgraduate/school-computing/msc-computing-major-options</t>
+          <t>https://www.epfl.ch/education/master/programs/computer-science/</t>
         </is>
       </c>
     </row>
@@ -5070,63 +5068,62 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>University of Galway</t>
+          <t>EPFL</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Galway (گالوی) — غرب ایرلند</t>
+          <t>Lausanne (لوزان) — کنار دریاچهٔ ژنو؛ فرانسه‌زبان؛ EPFL</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,150–1,450</t>
+          <t>خیلی گران — CHF 1,700–2,200</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (Artificial Intelligence)</t>
+          <t>MSc Data Science</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>≈ €28,000 (IDP/collegedunia 2025–26؛ صفحهٔ رسمی چک شود)</t>
+          <t>CHF 2,240 در ترم (≈ CHF 4,480/سال)</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>$31,900</t>
+          <t>$5,400</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>First Class (یا 2:1 خوب با تأیید مدیر برنامه)</t>
+          <t>کارشناسی CS/ریاضی/مهندسی با نمرات عالی</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
+          <t>مدرک زبان الزامی نیست</t>
+        </is>
+      </c>
+      <c r="M37" s="4">
+        <f>22</f>
+        <v/>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -5135,17 +5132,17 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>شرط ورود بالا؛ گران</t>
+          <t>بسیار رقابتی؛ کارآموزی صنعتی جزو برنامه است</t>
         </is>
       </c>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>http://cs.universityofgalway.ie/</t>
+          <t>https://www.epfl.ch/education/master/programs/data-science/</t>
         </is>
       </c>
     </row>
@@ -5155,63 +5152,62 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>University College Cork (UCC)</t>
+          <t>ETH Zürich</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Cork (کورک) — دومین شهر؛ مقر اروپایی Apple</t>
+          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>خیلی گران — CHF 1,900–2,500</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science and Artificial Intelligence</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>€28,000</t>
+          <t>CHF 2,190 + ≈ CHF 74 = ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>$31,900</t>
+          <t>$5,500</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2:1 در CS/ریاضی</t>
+          <t>کارشناسی CS با نمرات ممتاز (عملاً ۱۰٪ بالای کلاس)؛ هزینهٔ درخواست CHF 150؛ تا ۲ برنامه</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+          <t>C1 / IELTS 7.0</t>
+        </is>
+      </c>
+      <c r="M38" s="4">
+        <f>8</f>
+        <v/>
       </c>
       <c r="N38" s="12" t="inlineStr">
         <is>
@@ -5220,17 +5216,17 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>UCD (QS 100) و TCD (QS 75) هم ≈ €30k و 2:1 → برای معدل شما Reach</t>
+          <t>بهترین دانشگاه قارهٔ اروپا؛ اپلای فقط ۱–۳۰ نوامبر ۲۰۲۶، پاسخ تا پایان مارس ۲۰۲۷، شروع ۲۰ سپتامبر ۲۰۲۷؛ با معدل ۱۵.۷۷ احتمال پذیرش کم</t>
         </is>
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>https://www.ucc.ie/en/study/postgrad/</t>
+          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/computer-science.html</t>
         </is>
       </c>
     </row>
@@ -5240,82 +5236,81 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Universität Stuttgart</t>
+          <t>ETH Zürich + EPFL</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
+          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,350</t>
+          <t>خیلی گران — CHF 1,900–2,500</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Computer Science (انگلیسی، بدون NC)</t>
+          <t>MSc Cyber Security (مشترک ETH–EPFL؛ یک سال در هر کدام)</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + ≈ €200 سهم ترم = ≈ €3,400/سال</t>
+          <t>شهریهٔ ETH: ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>$3,900</t>
+          <t>$5,500</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
+          <t>کارشناسی CS با نمرات ممتاز؛ پیش‌زمینهٔ ریاضی/سیستم قوی</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1)</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="N39" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>C1 / IELTS 7.0</t>
+        </is>
+      </c>
+      <c r="M39" s="4">
+        <f>8</f>
+        <v/>
+      </c>
+      <c r="N39" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ بادن-وورتمبرگ برای غیر-EU</t>
+          <t>قوی‌ترین ارشد امنیت اروپا؛ همان پنجرهٔ نوامبر ETH؛ Reach</t>
         </is>
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/study/study-programs/</t>
+          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/cyber-security.html</t>
         </is>
       </c>
     </row>
@@ -5345,12 +5340,12 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Information Technology (INFOTECH)</t>
+          <t>M.Sc. Computer Science (انگلیسی، بدون NC)</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -5360,7 +5355,7 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + سهم ترم ≈ €3,400/سال</t>
+          <t>€1,500 در ترم + ≈ €200 سهم ترم = ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -5370,7 +5365,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی EE/CS/Computer Engineering؛ گزینش</t>
+          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -5390,17 +5385,17 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>گرایش‌های Embedded/Communication؛ Bosch و Daimler همان شهر</t>
+          <t>شهریهٔ بادن-وورتمبرگ برای غیر-EU</t>
         </is>
       </c>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>https://www.mygermanuniversity.com/master/information-technology-infotech/678</t>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/</t>
         </is>
       </c>
     </row>
@@ -5415,27 +5410,27 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>FAU Erlangen-Nürnberg</t>
+          <t>Universität Stuttgart</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
+          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €950–1,150</t>
+          <t>گران — €1,100–1,350</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Artificial Intelligence</t>
+          <t>M.Sc. Information Technology (INFOTECH)</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -5445,27 +5440,27 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>€4,000 در ترم برای غیر-EU از ترم تابستان ۲۰۲۷ (€8,000/سال) + €82 سهم ترم</t>
+          <t>€1,500 در ترم + سهم ترم ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>$9,300</t>
+          <t>$3,900</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بررسی ریزنمرات</t>
+          <t>کارشناسی EE/CS/Computer Engineering؛ گزینش</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 6.0)</t>
+          <t>7.0 (C1)</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>318</t>
         </is>
       </c>
       <c r="N41" s="10" t="inlineStr">
@@ -5475,17 +5470,17 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی اکتبر ۲۰۲۷ شما مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
+          <t>گرایش‌های Embedded/Communication؛ Bosch و Daimler همان شهر</t>
         </is>
       </c>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/artificial-intelligence-m-sc/</t>
+          <t>https://www.mygermanuniversity.com/master/information-technology-infotech/678</t>
         </is>
       </c>
     </row>
@@ -5515,12 +5510,12 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Autonomy Technologies</t>
+          <t>M.Sc. Artificial Intelligence</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -5530,17 +5525,17 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>€2,000 در ترم از تابستان ۲۰۲۷ (€4,000/سال) + €82 سهم ترم</t>
+          <t>€4,000 در ترم برای غیر-EU از ترم تابستان ۲۰۲۷ (€8,000/سال) + €82 سهم ترم</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>$4,700</t>
+          <t>$9,300</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط؛ آلمانی لازم نیست</t>
+          <t>کارشناسی CS/مرتبط؛ بررسی ریزنمرات</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -5560,17 +5555,17 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>رباتیک/خودران؛ ⚠️ مشمول شهریهٔ جدید FAU از ۲۰۲۷ (صفحهٔ رسمی شهریه، ۲۰۲۶)</t>
+          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی اکتبر ۲۰۲۷ شما مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
         </is>
       </c>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+          <t>https://www.fau.eu/degree-program/artificial-intelligence-m-sc/</t>
         </is>
       </c>
     </row>
@@ -5585,27 +5580,27 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>TU Darmstadt</t>
+          <t>FAU Erlangen-Nürnberg</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Darmstadt (دارمشتات) — ۲۵ دقیقه تا فرانکفورت</t>
+          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>متوسط — €950–1,150</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Distributed Software Systems (انگلیسی)</t>
+          <t>M.Sc. Autonomy Technologies</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -5615,47 +5610,47 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €300 سهم ترم (≈ €600/سال)</t>
+          <t>€2,000 در ترم از تابستان ۲۰۲۷ (€4,000/سال) + €82 سهم ترم</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$4,700</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با پیش‌نیازهای مشخص</t>
+          <t>کارشناسی مرتبط؛ آلمانی لازم نیست</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>≈ 7.0 (C1) — چک شود</t>
+          <t>B2 (IELTS 6.0)</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="N43" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>منطقهٔ Rhein-Main (SAP، Deutsche Bank، Software AG)</t>
+          <t>رباتیک/خودران؛ ⚠️ مشمول شهریهٔ جدید FAU از ۲۰۲۷ (صفحهٔ رسمی شهریه، ۲۰۲۶)</t>
         </is>
       </c>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>https://www.tu-darmstadt.de/studieren/</t>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
       </c>
     </row>
@@ -5670,27 +5665,27 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>TU Dresden</t>
+          <t>TU Darmstadt</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Dresden (درسدن) — «سیلیکون ساکسونی»</t>
+          <t>Darmstadt (دارمشتات) — ۲۵ دقیقه تا فرانکفورت</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €850–1,050</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Computer Science (انگلیسی)</t>
+          <t>M.Sc. Distributed Software Systems (انگلیسی)</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -5700,7 +5695,7 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €300 سهم ترم</t>
+          <t>€0 + ≈ €300 سهم ترم (≈ €600/سال)</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -5710,37 +5705,37 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارزیابی استعداد</t>
+          <t>کارشناسی CS با پیش‌نیازهای مشخص</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>≈ 7.0 (C1) — چک شود</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>Dresden ارزان‌ترین شهر جدول؛ GlobalFoundries/Infineon/Bosch</t>
+          <t>منطقهٔ Rhein-Main (SAP، Deutsche Bank، Software AG)</t>
         </is>
       </c>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de/studium/vor-dem-studium/studienangebot</t>
+          <t>https://www.tu-darmstadt.de/studieren/</t>
         </is>
       </c>
     </row>
@@ -5755,27 +5750,27 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Saarland University (UdS)</t>
+          <t>TU Dresden</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
+          <t>Dresden (درسدن) — «سیلیکون ساکسونی»</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>ارزان — €850–1,050</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Cybersecurity</t>
+          <t>M.Sc. Computer Science (انگلیسی)</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -5785,46 +5780,47 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €394 سهم ترم (≈ €790/سال)</t>
+          <t>€0 + ≈ €300 سهم ترم</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>$900</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS + اثبات دروس پایه + ۲ توصیه‌نامه؛ بدون NC</t>
+          <t>کارشناسی CS؛ ارزیابی استعداد</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1؛ MOI پذیرفته نمی‌شود)</t>
-        </is>
-      </c>
-      <c r="M45" s="4">
-        <f>588 (CS ≈ 251)</f>
-        <v/>
-      </c>
-      <c r="N45" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>CISPA — بهترین مرکز امنیت آلمان؛ IELTS 7 شرط سخت شماست</t>
+          <t>Dresden ارزان‌ترین شهر جدول؛ GlobalFoundries/Infineon/Bosch</t>
         </is>
       </c>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+          <t>https://tu-dresden.de/studium/vor-dem-studium/studienangebot</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5850,12 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Data Science and Artificial Intelligence</t>
+          <t>M.Sc. Cybersecurity</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -5869,7 +5865,7 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €394 سهم ترم</t>
+          <t>€0 + ≈ €394 سهم ترم (≈ €790/سال)</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -5879,12 +5875,12 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
+          <t>کارشناسی CS + اثبات دروس پایه + ۲ توصیه‌نامه؛ بدون NC</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1)</t>
+          <t>7.0 (C1؛ MOI پذیرفته نمی‌شود)</t>
         </is>
       </c>
       <c r="M46" s="4">
@@ -5898,17 +5894,17 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>MPI Informatics و DFKI در همان کمپوس</t>
+          <t>CISPA — بهترین مرکز امنیت آلمان؛ IELTS 7 شرط سخت شماست</t>
         </is>
       </c>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/data-science.html</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
       </c>
     </row>
@@ -5923,27 +5919,27 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>TU Chemnitz</t>
+          <t>Saarland University (UdS)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Chemnitz (کمنیتس) — ساکسونی</t>
+          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €800–1,000</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Automotive Software Engineering</t>
+          <t>M.Sc. Data Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -5953,47 +5949,46 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €320 سهم ترم (≈ €640/سال)</t>
+          <t>€0 + ≈ €394 سهم ترم</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$900</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون محدودیت پذیرش</t>
+          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 5.5)</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>7.0 (C1)</t>
+        </is>
+      </c>
+      <c r="M47" s="4">
+        <f>588 (CS ≈ 251)</f>
+        <v/>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>آسان‌ترین ورود؛ شهر ارزان؛ ولی صنعت خودرو ۲۰۲۴–۲۵ ضعیف و آلمانی در کارفرمایان محلی</t>
+          <t>MPI Informatics و DFKI در همان کمپوس</t>
         </is>
       </c>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>https://www.mygermanuniversity.com/master/automotive-software-engineering/91</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/data-science.html</t>
         </is>
       </c>
     </row>
@@ -6008,27 +6003,27 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Universität Passau</t>
+          <t>TU Chemnitz</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Passau (پاساو) — شهر کوچک، مرز اتریش</t>
+          <t>Chemnitz (کمنیتس) — ساکسونی</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>ارزان — €800–1,000</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Artificial Intelligence Engineering</t>
+          <t>M.Sc. Automotive Software Engineering</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -6038,22 +6033,22 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €100–200 سهم ترم</t>
+          <t>€0 + ≈ €320 سهم ترم (≈ €640/سال)</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.7 (معدل شما ≈ 2.3 ✓)؛ ۳۵ ECTS ریاضی + ۴۰ ECTS CS</t>
+          <t>کارشناسی CS/مرتبط؛ بدون محدودیت پذیرش</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>B2؛ + آلمانی A1 تا پایان سال اول (کلاس رایگان)</t>
+          <t>B2 (IELTS 5.5)</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
@@ -6068,17 +6063,17 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان؛ Passau رسماً اعلام کرده «فعلاً» شهریهٔ غیر-EU نمی‌گیرد (برخلاف FAU/TUM) ولی طبق قانون باواریا می‌تواند — قبل از اپلای چک کنید</t>
+          <t>آسان‌ترین ورود؛ شهر ارزان؛ ولی صنعت خودرو ۲۰۲۴–۲۵ ضعیف و آلمانی در کارفرمایان محلی</t>
         </is>
       </c>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+          <t>https://www.mygermanuniversity.com/master/automotive-software-engineering/91</t>
         </is>
       </c>
     </row>
@@ -6093,27 +6088,27 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Otto-von-Guericke-Universität (OVGU)</t>
+          <t>Universität Passau</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Magdeburg (ماگدبورگ) — ساکسونی-آنهالت</t>
+          <t>Passau (پاساو) — شهر کوچک، مرز اتریش</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €850–1,000</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Data and Knowledge Engineering</t>
+          <t>M.Sc. Artificial Intelligence Engineering</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -6123,22 +6118,22 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €311 سهم ترم</t>
+          <t>€0 + ≈ €100–200 سهم ترم</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$300</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.3 (معدل شما ≈ 2.27 — دقیقاً مرزی)؛ کارشناسی CS</t>
+          <t>معدل آلمانی ≤ 2.7 (معدل شما ≈ 2.3 ✓)؛ ۳۵ ECTS ریاضی + ۴۰ ECTS CS</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>6.0–7.0 (منابع متناقض؛ رسمی را چک کنید)</t>
+          <t>B2؛ + آلمانی A1 تا پایان سال اول (کلاس رایگان)</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -6146,20 +6141,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N49" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P49" s="4" t="inlineStr"/>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان؛ Passau رسماً اعلام کرده «فعلاً» شهریهٔ غیر-EU نمی‌گیرد (برخلاف FAU/TUM) ولی طبق قانون باواریا می‌تواند — قبل از اپلای چک کنید</t>
+        </is>
+      </c>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>https://www.dke.ovgu.de/</t>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
       </c>
     </row>
@@ -6174,27 +6173,27 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>TH Köln – Cologne Game Lab</t>
+          <t>Otto-von-Guericke-Universität (OVGU)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Köln / Cologne (کلن) — چهارمین شهر آلمان</t>
+          <t>Magdeburg (ماگدبورگ) — ساکسونی-آنهالت</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>ارزان — €850–1,000</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>M.A. Game Development and Research</t>
+          <t>M.Sc. Data and Knowledge Engineering</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -6204,47 +6203,43 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>€2,500 در ترم (غیر-EU) + €277 سهم ترم ≈ €5,550/سال</t>
+          <t>€0 + ≈ €311 سهم ترم</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>$6,300</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>هر کارشناسی + ≥ ۱۲ ماه سابقهٔ مرتبط + آزمون استعداد (مهلت ۳۱ مارس)</t>
+          <t>معدل آلمانی ≤ 2.3 (معدل شما ≈ 2.27 — دقیقاً مرزی)؛ کارشناسی CS</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>6.0–7.0 (منابع متناقض؛ رسمی را چک کنید)</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>— (UAS)</t>
-        </is>
-      </c>
-      <c r="N50" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="inlineStr">
-        <is>
-          <t>معتبرترین مدرسهٔ بازی آلمان؛ ۷ ماه Unity + ۲ سال IT شما احتمالاً شرط ۱۲ ماه را می‌پوشاند — بپرسید</t>
-        </is>
-      </c>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+          <t>https://www.dke.ovgu.de/</t>
         </is>
       </c>
     </row>
@@ -6259,27 +6254,27 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Universität Siegen</t>
+          <t>TH Köln – Cologne Game Lab</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Siegen (زیگن) — شهر کوچک، NRW</t>
+          <t>Köln / Cologne (کلن) — چهارمین شهر آلمان</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Human Computer Interaction</t>
+          <t>M.A. Game Development and Research</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -6289,47 +6284,47 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €372 سهم ترم</t>
+          <t>€2,500 در ترم (غیر-EU) + €277 سهم ترم ≈ €5,550/سال</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>$800</t>
+          <t>$6,300</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.5؛ کارشناسی CS/IS/Design/Psychology</t>
+          <t>هر کارشناسی + ≥ ۱۲ ماه سابقهٔ مرتبط + آزمون استعداد (مهلت ۳۱ مارس)</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>شروع زمستان و تابستان؛ شهر کوچک</t>
+          <t>معتبرترین مدرسهٔ بازی آلمان؛ ۷ ماه Unity + ۲ سال IT شما احتمالاً شرط ۱۲ ماه را می‌پوشاند — بپرسید</t>
         </is>
       </c>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
       </c>
     </row>
@@ -6344,27 +6339,27 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Hochschule Bonn-Rhein-Sieg (H-BRS)</t>
+          <t>Universität Siegen</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Sankt Augustin (زانکت آگوستین) — حومهٔ Bonn</t>
+          <t>Siegen (زیگن) — شهر کوچک، NRW</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €950–1,200</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Autonomous Systems</t>
+          <t>M.Sc. Human Computer Interaction</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -6374,7 +6369,7 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>€0 + €349 سهم ترم</t>
+          <t>€0 + ≈ €372 سهم ترم</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -6384,37 +6379,37 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.5؛ ۲۵ جای محدود؛ آزمون استعداد؛ uni-assist</t>
+          <t>معدل آلمانی ≤ 2.5؛ کارشناسی CS/IS/Design/Psychology</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>6.5 (B2+)</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>— (UAS)</t>
-        </is>
-      </c>
-      <c r="N52" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>رباتیک کاربردی با Fraunhofer؛ نزدیک Bonn/Köln</t>
+          <t>شروع زمستان و تابستان؛ شهر کوچک</t>
         </is>
       </c>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6424,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>RWTH Aachen</t>
+          <t>Hochschule Bonn-Rhein-Sieg (H-BRS)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Aachen (آخن) — مرز هلند/بلژیک</t>
+          <t>Sankt Augustin (زانکت آگوستین) — حومهٔ Bonn</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -6444,12 +6439,12 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Software Systems Engineering</t>
+          <t>M.Sc. Autonomous Systems</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -6459,7 +6454,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €330 سهم ترم</t>
+          <t>€0 + €349 سهم ترم</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6469,37 +6464,37 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS، معدل ≥ ۶۵٪ (شما ۷۹٪ ✓)؛ ۲ درس پیشرفتهٔ سیستم؛ مهلت ۱ مارس</t>
+          <t>معدل آلمانی ≤ 2.5؛ ۲۵ جای محدود؛ آزمون استعداد؛ uni-assist</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 5.5)</t>
+          <t>6.5 (B2+)</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="N53" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>TU9؛ رقابتی — معدل شما حداقل را رد می‌کند ولی متقاضیان قوی‌ترند</t>
+          <t>رباتیک کاربردی با Fraunhofer؛ نزدیک Bonn/Köln</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
       </c>
     </row>
@@ -6514,27 +6509,27 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Universität Tübingen</t>
+          <t>RWTH Aachen</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Tübingen (توبینگن) — شهر دانشگاهی کوچک؛ Cyber Valley</t>
+          <t>Aachen (آخن) — مرز هلند/بلژیک</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>متوسط — €950–1,200</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Machine Learning</t>
+          <t>M.Sc. Software Systems Engineering</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -6544,27 +6539,28 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + ≈ €200 = ≈ €3,400/سال</t>
+          <t>€0 + ≈ €330 سهم ترم</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>$3,900</t>
+          <t>$800</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی؛ آزمون توانایی؛ مهلت ۳۰ آوریل</t>
+          <t>کارشناسی CS، معدل ≥ ۶۵٪ (شما ۷۹٪ ✓)؛ ۲ درس پیشرفتهٔ سیستم؛ مهلت ۱ مارس</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="M54" s="4">
-        <f>230</f>
-        <v/>
+          <t>B2 (IELTS 5.5)</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="N54" s="12" t="inlineStr">
         <is>
@@ -6573,17 +6569,17 @@
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>Cyber Valley — بهترین ML آلمان؛ پذیرش بسیار سخت</t>
+          <t>TU9؛ رقابتی — معدل شما حداقل را رد می‌کند ولی متقاضیان قوی‌ترند</t>
         </is>
       </c>
       <c r="Q54" s="8" t="inlineStr">
         <is>
-          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
       </c>
     </row>
@@ -6598,27 +6594,27 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>TU München (TUM)</t>
+          <t>Universität Tübingen</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>München – Garching (مونیخ، کمپوس گارشینگ)</t>
+          <t>Tübingen (توبینگن) — شهر دانشگاهی کوچک؛ Cyber Valley</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,300–1,600</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Informatics</t>
+          <t>M.Sc. Machine Learning</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -6628,28 +6624,27 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>€6,000 در ترم برای غیر-EU (€12,000/سال) + €97</t>
+          <t>€1,500 در ترم + ≈ €200 = ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>$13,900</t>
+          <t>$3,900</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارزیابی استعداد؛ بسیار رقابتی</t>
+          <t>کارشناسی CS/ریاضی؛ آزمون توانایی؛ مهلت ۳۰ آوریل</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="inlineStr">
-        <is>
-          <t>≈ 25</t>
-        </is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M55" s="4">
+        <f>230</f>
+        <v/>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -6658,17 +6653,17 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>⚠️ TUM از ۲۰۲۴ شهریهٔ غیر-EU می‌گیرد — دیگر «رایگان» نیست؛ Munich گران‌ترین شهر آلمان</t>
+          <t>Cyber Valley — بهترین ML آلمان؛ پذیرش بسیار سخت</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr">
         <is>
-          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
       </c>
     </row>
@@ -6678,27 +6673,27 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>University of Twente (UT)</t>
+          <t>TU München (TUM)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
+          <t>München – Garching (مونیخ، کمپوس گارشینگ)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,000–1,300</t>
+          <t>خیلی گران — €1,300–1,600</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (گرایش‌ها: Cyber Security، Data Science، Software Tech، ...)</t>
+          <t>M.Sc. Informatics</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -6713,17 +6708,17 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>€21,700</t>
+          <t>€6,000 در ترم برای غیر-EU (€12,000/سال) + €97</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>$24,700</t>
+          <t>$13,900</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>حداقل رسمی برای مدرک ایرانی ۱۵/۲۰</t>
+          <t>کارشناسی CS؛ ارزیابی استعداد؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -6733,12 +6728,12 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="N56" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>≈ 25</t>
+        </is>
+      </c>
+      <c r="N56" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -6748,12 +6743,12 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>⚠️ TUM از ۲۰۲۴ شهریهٔ غیر-EU می‌گیرد — دیگر «رایگان» نیست؛ Munich گران‌ترین شهر آلمان</t>
         </is>
       </c>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/computer-science/</t>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6778,12 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded Systems</t>
+          <t>MSc Computer Science (گرایش‌ها: Cyber Security، Data Science، Software Tech، ...)</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -6808,7 +6803,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>CGPA ≥ ۷۰–۷۵٪؛ کارشناسی CS/EE/Computer Eng</t>
+          <t>حداقل رسمی برای مدرک ایرانی ۱۵/۲۰</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -6828,17 +6823,17 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ مهلت غیر-EU ۱ مه</t>
+          <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/computer-science/</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6863,12 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>MSc Interaction Technology</t>
+          <t>MSc Embedded Systems</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -6893,7 +6888,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط</t>
+          <t>CGPA ≥ ۷۰–۷۵٪؛ کارشناسی CS/EE/Computer Eng</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -6913,17 +6908,17 @@
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>HCI فنی (نه طراحی صرف)</t>
+          <t>شهریهٔ رسمی 2026/27؛ مهلت غیر-EU ۱ مه</t>
         </is>
       </c>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/interaction-technology/</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
       </c>
     </row>
@@ -6938,27 +6933,27 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Radboud University</t>
+          <t>University of Twente (UT)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Nijmegen (نایمخن) — شرق هلند</t>
+          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,050–1,350</t>
+          <t>متوسط — €1,000–1,300</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>MSc Computing Science (گرایش‌ها: Cyber Security، Data Science، Software Science)</t>
+          <t>MSc Interaction Technology</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -6968,17 +6963,17 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
+          <t>€21,700</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>$22,500</t>
+          <t>$24,700</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با ریاضی/الگوریتم کافی</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -6988,7 +6983,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>223</t>
         </is>
       </c>
       <c r="N59" s="10" t="inlineStr">
@@ -6998,17 +6993,17 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>HCI فنی (نه طراحی صرف)</t>
         </is>
       </c>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/masters/computing-science</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/interaction-technology/</t>
         </is>
       </c>
     </row>
@@ -7038,12 +7033,12 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computing Science (گرایش‌ها: Cyber Security، Data Science، Software Science)</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -7063,7 +7058,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI/مرتبط</t>
+          <t>کارشناسی CS با ریاضی/الگوریتم کافی</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -7083,17 +7078,17 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>AI شناختی (Donders Institute)</t>
+          <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
       <c r="Q60" s="8" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/masters/artificial-intelligence</t>
+          <t>https://www.ru.nl/en/education/masters/computing-science</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7103,27 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Leiden University</t>
+          <t>Radboud University</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Leiden (لایدن) — بین Den Haag و Amsterdam</t>
+          <t>Nijmegen (نایمخن) — شرق هلند</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>متوسط — €1,050–1,350</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (گرایش‌ها: Artificial Intelligence، Data Science، ...)</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>چندحوزه‌ای (انتخاب گرایش)</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -7138,17 +7133,17 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>€22,500</t>
+          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>$25,600</t>
+          <t>$22,500</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/AI/مرتبط</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -7158,27 +7153,27 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="N61" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="N61" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ نزدیک Den Haag/Amsterdam</t>
+          <t>AI شناختی (Donders Institute)</t>
         </is>
       </c>
       <c r="Q61" s="8" t="inlineStr">
         <is>
-          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+          <t>https://www.ru.nl/en/education/masters/artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -7193,27 +7188,27 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>University of Groningen (RUG)</t>
+          <t>Leiden University</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Groningen (خرونینگن) — شمال هلند</t>
+          <t>Leiden (لایدن) — بین Den Haag و Amsterdam</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,050–1,350</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computer Science (گرایش‌ها: Artificial Intelligence، Data Science، ...)</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>چندحوزه‌ای (انتخاب گرایش)</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -7223,17 +7218,17 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>€24,900</t>
+          <t>€22,500</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>$28,400</t>
+          <t>$25,600</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی AI/CS با ریاضی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -7243,7 +7238,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N62" s="11" t="inlineStr">
@@ -7253,17 +7248,17 @@
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ بورس ASML €5k</t>
+          <t>شهریهٔ رسمی 2026/27؛ نزدیک Den Haag/Amsterdam</t>
         </is>
       </c>
       <c r="Q62" s="8" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
       </c>
     </row>
@@ -7293,12 +7288,12 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>MSc Computing Science</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -7308,17 +7303,17 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>≈ €21,400 (2025) → ≈ €22,500</t>
+          <t>€24,900</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>$25,600</t>
+          <t>$28,400</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی AI/CS با ریاضی</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -7331,20 +7326,24 @@
           <t>157</t>
         </is>
       </c>
-      <c r="N63" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="N63" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P63" s="4" t="inlineStr"/>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27؛ بورس ASML €5k</t>
+        </is>
+      </c>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/computing-science/?lang=en</t>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
       </c>
     </row>
@@ -7359,27 +7358,27 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Utrecht University</t>
+          <t>University of Groningen (RUG)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
+          <t>Groningen (خرونینگن) — شمال هلند</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>متوسط — €1,050–1,350</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>MSc Game and Media Technology</t>
+          <t>MSc Computing Science</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -7389,17 +7388,17 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>€25,306</t>
+          <t>≈ €21,400 (2025) → ≈ €22,500</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>$28,800</t>
+          <t>$25,600</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارشد پژوهشی گزینشی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -7409,27 +7408,23 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="N64" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
-        </is>
-      </c>
-      <c r="P64" s="4" t="inlineStr">
-        <is>
-          <t>تنها ارشد پژوهشی بازی هلند؛ Utrecht قطب استودیوهای بازی</t>
-        </is>
-      </c>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="inlineStr"/>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+          <t>https://www.rug.nl/masters/computing-science/?lang=en</t>
         </is>
       </c>
     </row>
@@ -7459,12 +7454,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Game and Media Technology</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -7484,7 +7479,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI؛ گزینشی</t>
+          <t>کارشناسی CS؛ ارشد پژوهشی گزینشی</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -7504,17 +7499,17 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>همان باند شهریهٔ Utrecht 2026/27</t>
+          <t>تنها ارشد پژوهشی بازی هلند؛ Utrecht قطب استودیوهای بازی</t>
         </is>
       </c>
       <c r="Q65" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/artificial-intelligence</t>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
       </c>
     </row>
@@ -7529,47 +7524,47 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA)</t>
+          <t>Utrecht University</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Amsterdam (آمستردام)</t>
+          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,300–1,700</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering (۱ ساله!)</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>≈ €23,540</t>
+          <t>€25,306</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>$26,800</t>
+          <t>$28,800</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/AI؛ گزینشی</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -7579,27 +7574,27 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="N66" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="N66" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>تنها ارشد ۱ سالهٔ معتبر هلند → کل هزینه نصف؛ اما اجارهٔ Amsterdam €900–1,300</t>
+          <t>همان باند شهریهٔ Utrecht 2026/27</t>
         </is>
       </c>
       <c r="Q66" s="8" t="inlineStr">
         <is>
-          <t>https://www.uva.nl/en/programmes/masters/software-engineering/software-engineering.html</t>
+          <t>https://www.uu.nl/en/masters/artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -7629,32 +7624,32 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Software Engineering (۱ ساله!)</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>≈ €26,000</t>
+          <t>≈ €23,540</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>$29,600</t>
+          <t>$26,800</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی AI/CS با ریاضی قوی؛ بسیار رقابتی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -7667,20 +7662,24 @@
           <t>60</t>
         </is>
       </c>
-      <c r="N67" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="N67" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
-        </is>
-      </c>
-      <c r="P67" s="4" t="inlineStr"/>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>تنها ارشد ۱ سالهٔ معتبر هلند → کل هزینه نصف؛ اما اجارهٔ Amsterdam €900–1,300</t>
+        </is>
+      </c>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>https://www.uva.nl/en/programmes/masters/artificial-intelligence/artificial-intelligence.html</t>
+          <t>https://www.uva.nl/en/programmes/masters/software-engineering/software-engineering.html</t>
         </is>
       </c>
     </row>
@@ -7695,27 +7694,27 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>TU Eindhoven (TU/e)</t>
+          <t>University of Amsterdam (UvA)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
+          <t>Amsterdam (آمستردام)</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,400</t>
+          <t>خیلی گران — €1,300–1,700</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science and Artificial Intelligence</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -7725,17 +7724,17 @@
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
+          <t>≈ €26,000</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>$25,500</t>
+          <t>$29,600</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی؛ گزینش بر اساس معدل</t>
+          <t>کارشناسی AI/CS با ریاضی قوی؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -7745,7 +7744,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N68" s="12" t="inlineStr">
@@ -7755,17 +7754,13 @@
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P68" s="4" t="inlineStr">
-        <is>
-          <t>Brainport (ASML، Philips، NXP)</t>
-        </is>
-      </c>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P68" s="4" t="inlineStr"/>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/graduate-school/master-data-science-and-artificial-intelligence</t>
+          <t>https://www.uva.nl/en/programmes/masters/artificial-intelligence/artificial-intelligence.html</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7790,12 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded Systems</t>
+          <t>MSc Data Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -7820,7 +7815,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE؛ گزینش</t>
+          <t>کارشناسی CS/ریاضی؛ گزینش بر اساس معدل</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -7840,17 +7835,17 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>ASML/NXP بزرگ‌ترین کارفرمایان Embedded اروپا</t>
+          <t>Brainport (ASML، Philips، NXP)</t>
         </is>
       </c>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/graduate-school/master-embedded-systems</t>
+          <t>https://www.tue.nl/en/education/graduate-school/master-data-science-and-artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -7865,27 +7860,27 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>TU Delft</t>
+          <t>TU Eindhoven (TU/e)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Delft (دلفت) — کنار Den Haag/Rotterdam</t>
+          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>گران — €1,100–1,400</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science / MSc Computer &amp; Embedded Systems Engineering</t>
+          <t>MSc Embedded Systems</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -7895,27 +7890,27 @@
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>€22,290 (2025/26) → ≈ €23,000</t>
+          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>$26,200</t>
+          <t>$25,500</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>معدل ≥ ۷۵٪ / ۲۰٪ برتر</t>
+          <t>کارشناسی CS/EE؛ گزینش</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N70" s="12" t="inlineStr">
@@ -7925,17 +7920,17 @@
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>معتبرترین، ولی برای معدل ۱۵.۷۷ دور از دسترس</t>
+          <t>ASML/NXP بزرگ‌ترین کارفرمایان Embedded اروپا</t>
         </is>
       </c>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>https://www.tudelft.nl/onderwijs/opleidingen/masters/cs/msc-computer-science</t>
+          <t>https://www.tue.nl/en/education/graduate-school/master-embedded-systems</t>
         </is>
       </c>
     </row>
@@ -7950,77 +7945,77 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Breda University of Applied Sciences (BUas)</t>
+          <t>TU Delft</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Breda (بردا) — جنوب هلند</t>
+          <t>Delft (دلفت) — کنار Den Haag/Rotterdam</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,000–1,300</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Master Game Technology (۱ ساله)</t>
+          <t>MSc Computer Science / MSc Computer &amp; Embedded Systems Engineering</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>≈ €15,200</t>
+          <t>€22,290 (2025/26) → ≈ €23,000</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>$17,300</t>
+          <t>$26,200</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی IT/برنامه‌نویسی/بازی + پیشنهاد پروژه</t>
+          <t>معدل ≥ ۷۵٪ / ۲۰٪ برتر</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>— (UAS)</t>
-        </is>
-      </c>
-      <c r="N71" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N71" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>برنامهٔ بازی BUas در اروپا شناخته‌شده است؛ مدرک UAS (نه پژوهشی)</t>
+          <t>معتبرترین، ولی برای معدل ۱۵.۷۷ دور از دسترس</t>
         </is>
       </c>
       <c r="Q71" s="8" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/breda-university-applied-sciences/postgrad/master-game-technology</t>
+          <t>https://www.tudelft.nl/onderwijs/opleidingen/masters/cs/msc-computer-science</t>
         </is>
       </c>
     </row>
@@ -8030,82 +8025,82 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Linköping University (LiU)</t>
+          <t>Breda University of Applied Sciences (BUas)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
+          <t>Breda (بردا) — جنوب هلند</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,500–12,500</t>
+          <t>متوسط — €1,000–1,300</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>Master Game Technology (۱ ساله)</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>SEK 166,000</t>
+          <t>≈ €15,200</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>$16,800</t>
+          <t>$17,300</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>گزینش بر اساس گروه معدل</t>
+          <t>کارشناسی IT/برنامه‌نویسی/بازی + پیشنهاد پروژه</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="N72" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="N72" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>برنامهٔ بازی BUas در اروپا شناخته‌شده است؛ مدرک UAS (نه پژوهشی)</t>
         </is>
       </c>
       <c r="Q72" s="8" t="inlineStr">
         <is>
-          <t>https://liu.se/en/education/program/6mics</t>
+          <t>https://www.topuniversities.com/universities/breda-university-applied-sciences/postgrad/master-game-technology</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8130,12 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>MSc Statistics and Machine Learning</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -8150,7 +8145,7 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 166,000 (همان باند)</t>
+          <t>SEK 166,000</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -8160,7 +8155,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی با ≥ ۳۰ واحد ریاضی/آمار + برنامه‌نویسی</t>
+          <t>گزینش بر اساس گروه معدل</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -8180,13 +8175,17 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
-        </is>
-      </c>
-      <c r="P73" s="4" t="inlineStr"/>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی</t>
+        </is>
+      </c>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>https://liu.se/en/education/program/f7msl</t>
+          <t>https://liu.se/en/education/program/6mics</t>
         </is>
       </c>
     </row>
@@ -8201,27 +8200,27 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Halmstad University</t>
+          <t>Linköping University (LiU)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Halmstad (هالمستاد) — غرب سوئد</t>
+          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,000–12,000</t>
+          <t>متوسط — SEK 10,500–12,500</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded and Intelligent Systems (120 cr)</t>
+          <t>MSc Statistics and Machine Learning</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -8231,17 +8230,17 @@
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 151,000</t>
+          <t>≈ SEK 166,000 (همان باند)</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>$15,300</t>
+          <t>$16,800</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE</t>
+          <t>کارشناسی با ≥ ۳۰ واحد ریاضی/آمار + برنامه‌نویسی</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -8251,27 +8250,23 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
-        </is>
-      </c>
-      <c r="P74" s="4" t="inlineStr">
-        <is>
-          <t>Volvo/HMS در منطقه؛ بدون رتبهٔ QS</t>
-        </is>
-      </c>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P74" s="4" t="inlineStr"/>
       <c r="Q74" s="8" t="inlineStr">
         <is>
-          <t>https://www.hh.se/english/education/programmes.html</t>
+          <t>https://liu.se/en/education/program/f7msl</t>
         </is>
       </c>
     </row>
@@ -8286,27 +8281,27 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Blekinge Institute of Technology (BTH)</t>
+          <t>Halmstad University</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Karlskrona (کارلسکرونا) — Ericsson، Telenor</t>
+          <t>Halmstad (هالمستاد) — غرب سوئد</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>ارزان — SEK 9,500–11,500</t>
+          <t>متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering (120 cr)</t>
+          <t>MSc Embedded and Intelligent Systems (120 cr)</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -8316,17 +8311,17 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>SEK 140,000</t>
+          <t>≈ SEK 151,000</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>$14,100</t>
+          <t>$15,300</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>≥ ۹۰ واحد CS/SE</t>
+          <t>کارشناسی CS/EE</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -8339,24 +8334,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N75" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Ericsson و Telenor در Karlskrona؛ ⚠️ نسخهٔ ۶۰ واحدی از راه دور است</t>
+          <t>Volvo/HMS در منطقه؛ بدون رتبهٔ QS</t>
         </is>
       </c>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>https://www.bth.se/eng/programmes/</t>
+          <t>https://www.hh.se/english/education/programmes.html</t>
         </is>
       </c>
     </row>
@@ -8371,27 +8366,27 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>KTH Royal Institute of Technology</t>
+          <t>Blekinge Institute of Technology (BTH)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Stockholm (استکهلم)</t>
+          <t>Karlskrona (کارلسکرونا) — Ericsson، Telenor</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>گران — SEK 12,500–15,000</t>
+          <t>ارزان — SEK 9,500–11,500</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>MSc Machine Learning</t>
+          <t>MSc Software Engineering (120 cr)</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -8401,17 +8396,17 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 180,000–190,000 (کل دوره ≈ 360k–380k)</t>
+          <t>SEK 140,000</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>$18,200–19,200</t>
+          <t>$14,100</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی قوی؛ بسیار رقابتی</t>
+          <t>≥ ۹۰ واحد CS/SE</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -8421,27 +8416,27 @@
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="N76" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>Stockholm گران (اتاق SEK 7–10k)؛ رقم دقیق روی kth.se فقط در سامانهٔ اپلای نمایش داده می‌شود</t>
+          <t>Ericsson و Telenor در Karlskrona؛ ⚠️ نسخهٔ ۶۰ واحدی از راه دور است</t>
         </is>
       </c>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+          <t>https://www.bth.se/eng/programmes/</t>
         </is>
       </c>
     </row>
@@ -8471,12 +8466,12 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>MSc Cybersecurity</t>
+          <t>MSc Machine Learning</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -8486,7 +8481,7 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 180,000–190,000</t>
+          <t>≈ SEK 180,000–190,000 (کل دوره ≈ 360k–380k)</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -8496,7 +8491,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/ریاضی قوی؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -8516,13 +8511,17 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
-        </is>
-      </c>
-      <c r="P77" s="4" t="inlineStr"/>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>Stockholm گران (اتاق SEK 7–10k)؛ رقم دقیق روی kth.se فقط در سامانهٔ اپلای نمایش داده می‌شود</t>
+        </is>
+      </c>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/cybersecurity</t>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8541,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Stockholm – Kista (استکهلم، شیستا؛ قطب ICT)</t>
+          <t>Stockholm (استکهلم)</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -8552,12 +8551,12 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering of Distributed Systems</t>
+          <t>MSc Cybersecurity</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -8567,7 +8566,7 @@
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>SEK 180,000–190,000</t>
+          <t>≈ SEK 180,000–190,000</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -8590,24 +8589,20 @@
           <t>82</t>
         </is>
       </c>
-      <c r="N78" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+      <c r="N78" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
-        </is>
-      </c>
-      <c r="P78" s="4" t="inlineStr">
-        <is>
-          <t>Kista = قطب ICT سوئد (Ericsson)</t>
-        </is>
-      </c>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="P78" s="4" t="inlineStr"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/software-engineering-of-distributed-systems</t>
+          <t>https://www.kth.se/en/studies/master/cybersecurity</t>
         </is>
       </c>
     </row>
@@ -8622,27 +8617,27 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Chalmers University of Technology</t>
+          <t>KTH Royal Institute of Technology</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+          <t>Stockholm – Kista (استکهلم، شیستا؛ قطب ICT)</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,500–13,500</t>
+          <t>گران — SEK 12,500–15,000</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science and AI</t>
+          <t>MSc Software Engineering of Distributed Systems</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -8652,17 +8647,17 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 175,000 (2026/27؛ 2025/26: 160,000)</t>
+          <t>SEK 180,000–190,000</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>$17,700</t>
+          <t>$18,200–19,200</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -8672,7 +8667,7 @@
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N79" s="11" t="inlineStr">
@@ -8682,17 +8677,17 @@
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه؛ ⚠️ طبق صفحهٔ شهریهٔ Chalmers دانشگاه‌های سوئد فعلاً نمی‌توانند از ایران پول دریافت کنند (تحریم بانکی) — پرداخت از کشور ثالث</t>
+          <t>Kista = قطب ICT سوئد (Ericsson)</t>
         </is>
       </c>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/data-science-and-ai-msc/</t>
+          <t>https://www.kth.se/en/studies/master/software-engineering-of-distributed-systems</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8717,12 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering and Technology</t>
+          <t>MSc Data Science and AI</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -8737,7 +8732,7 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 175,000 (2026/27)</t>
+          <t>≈ SEK 175,000 (2026/27؛ 2025/26: 160,000)</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -8747,7 +8742,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE</t>
+          <t>کارشناسی CS/ریاضی</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -8760,20 +8755,24 @@
           <t>174</t>
         </is>
       </c>
-      <c r="N80" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="N80" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P80" s="4" t="inlineStr"/>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه؛ ⚠️ طبق صفحهٔ شهریهٔ Chalmers دانشگاه‌های سوئد فعلاً نمی‌توانند از ایران پول دریافت کنند (تحریم بانکی) — پرداخت از کشور ثالث</t>
+        </is>
+      </c>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/software-engineering-and-technology-msc/</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/data-science-and-ai-msc/</t>
         </is>
       </c>
     </row>
@@ -8803,12 +8802,12 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>MSc Interaction Design and Technologies</t>
+          <t>MSc Software Engineering and Technology</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -8828,7 +8827,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/Design</t>
+          <t>کارشناسی CS/SE</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -8848,13 +8847,13 @@
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/interaction-design-and-technologies-msc/</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/software-engineering-and-technology-msc/</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8868,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>University of Gothenburg (مشترک با Chalmers)</t>
+          <t>Chalmers University of Technology</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -8884,12 +8883,12 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>MSc Game Design &amp; Technology</t>
+          <t>MSc Interaction Design and Technologies</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -8899,17 +8898,17 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>SEK 147,000 (ورودی ۲۰۲۷: کل دوره SEK 294,000 رسمی)</t>
+          <t>≈ SEK 175,000 (2026/27)</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>$14,800</t>
+          <t>$17,700</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/Design/Media</t>
+          <t>کارشناسی CS/Design</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -8919,7 +8918,7 @@
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N82" s="10" t="inlineStr">
@@ -8929,17 +8928,13 @@
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
-        </is>
-      </c>
-      <c r="P82" s="4" t="inlineStr">
-        <is>
-          <t>Gothenburg: استودیوهای EA DICE/Ghost؛ بازار بازی ضعیف</t>
-        </is>
-      </c>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+        </is>
+      </c>
+      <c r="P82" s="4" t="inlineStr"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/interaction-design-and-technologies-msc/</t>
         </is>
       </c>
     </row>
@@ -8954,27 +8949,27 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Uppsala University</t>
+          <t>University of Gothenburg (مشترک با Chalmers)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Uppsala (اوپسالا) — ۴۰ دقیقه تا استکهلم</t>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,000–13,000</t>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Game Design &amp; Technology</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -8984,17 +8979,17 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 145,000–150,000</t>
+          <t>SEK 147,000 (ورودی ۲۰۲۷: کل دوره SEK 294,000 رسمی)</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>$14,600–15,200</t>
+          <t>$14,800</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/Design/Media</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -9004,27 +8999,27 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="N83" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="N83" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>رتبهٔ بالا با شهریهٔ پایین‌تر از KTH</t>
+          <t>Gothenburg: استودیوهای EA DICE/Ghost؛ بازار بازی ضعیف</t>
         </is>
       </c>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.se/en/study/programme/masters-programme-in-computer-science</t>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
       </c>
     </row>
@@ -9039,27 +9034,27 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Umeå University</t>
+          <t>Uppsala University</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Umeå (اومئو) — شمال سوئد</t>
+          <t>Uppsala (اوپسالا) — ۴۰ دقیقه تا استکهلم</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>ارزان تا متوسط — SEK 10,000–12,000</t>
+          <t>متوسط تا گران — SEK 11,000–13,000</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -9069,17 +9064,17 @@
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>SEK 152,300</t>
+          <t>≈ SEK 145,000–150,000</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>$15,400</t>
+          <t>$14,600–15,200</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -9089,27 +9084,27 @@
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="N84" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N84" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>شمال سوئد، شهر دانشجویی ارزان؛ کل دوره SEK 304,600</t>
+          <t>رتبهٔ بالا با شهریهٔ پایین‌تر از KTH</t>
         </is>
       </c>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+          <t>https://www.uu.se/en/study/programme/masters-programme-in-computer-science</t>
         </is>
       </c>
     </row>
@@ -9124,27 +9119,27 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>University of Skövde</t>
+          <t>Umeå University</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Skövde (شوده) — Sweden Game Arena</t>
+          <t>Umeå (اومئو) — شمال سوئد</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>ارزان — SEK 9,500–11,500</t>
+          <t>ارزان تا متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science (120 cr)</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -9154,17 +9149,17 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>SEK 135,000</t>
+          <t>SEK 152,300</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>$13,600</t>
+          <t>$15,400</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط</t>
+          <t>کارشناسی CS/ریاضی</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -9174,27 +9169,27 @@
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N85" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>ارزان؛ Skövde قطب بازی سوئد (Sweden Game Arena)</t>
+          <t>شمال سوئد، شهر دانشجویی ارزان؛ کل دوره SEK 304,600</t>
         </is>
       </c>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>https://www.his.se/en/education/</t>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
       </c>
     </row>
@@ -9209,27 +9204,27 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Mälardalen University (MDU)</t>
+          <t>University of Skövde</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
+          <t>Skövde (شوده) — Sweden Game Arena</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,000–12,000</t>
+          <t>ارزان — SEK 9,500–11,500</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>MSc Intelligent Embedded Systems</t>
+          <t>MSc Data Science (120 cr)</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -9239,7 +9234,7 @@
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 135,000</t>
+          <t>SEK 135,000</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -9249,7 +9244,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -9269,17 +9264,17 @@
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>ABB و Westinghouse در Västerås؛ رقم 2024/25</t>
+          <t>ارزان؛ Skövde قطب بازی سوئد (Sweden Game Arena)</t>
         </is>
       </c>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>https://www.mdu.se/en/malardalen-university/education</t>
+          <t>https://www.his.se/en/education/</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9304,12 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering</t>
+          <t>MSc Intelligent Embedded Systems</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -9334,7 +9329,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE</t>
+          <t>کارشناسی CS/EE</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -9354,10 +9349,14 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P87" s="4" t="inlineStr"/>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>ABB و Westinghouse در Västerås؛ رقم 2024/25</t>
+        </is>
+      </c>
       <c r="Q87" s="8" t="inlineStr">
         <is>
           <t>https://www.mdu.se/en/malardalen-university/education</t>
@@ -9370,27 +9369,27 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (AAU)</t>
+          <t>Mälardalen University (MDU)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
+          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–9,500</t>
+          <t>متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (IT)</t>
+          <t>MSc Software Engineering</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -9405,31 +9404,32 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>≈ €14,910 (2025/26: €7,455 در ترم؛ نرخ ۲۰۲۶ روی سایت AAU منتشر نشده — mastersportal: €15,340)</t>
+          <t>≈ SEK 135,000</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>$17,000–17,500</t>
+          <t>$13,600</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>رسمی: حداقل ۱۵۰ ECTS دروس مرتبط با CS (برنامه‌نویسی ۱۵، مهندسی نرم‌افزار ۵، الگوریتم ۵، پایگاه داده ۵، ریاضیات گسسته ۵)؛ از ورودی ۲۰۲۷ سابقهٔ کار و انگیزه‌نامه هم در رتبه‌بندی حساب می‌شود</t>
+          <t>کارشناسی CS/SE</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>6.5 (هر بخش ≥ 6.0)</t>
-        </is>
-      </c>
-      <c r="M88" s="4">
-        <f>329</f>
-        <v/>
-      </c>
-      <c r="N88" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -9437,14 +9437,10 @@
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P88" s="4" t="inlineStr">
-        <is>
-          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)؛ ظرفیت محدود</t>
-        </is>
-      </c>
+      <c r="P88" s="4" t="inlineStr"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+          <t>https://www.mdu.se/en/malardalen-university/education</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9470,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>MSc Software</t>
+          <t>MSc Computer Science (IT)</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -9489,7 +9485,7 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>≈ €14,910–15,340</t>
+          <t>≈ €14,910 (2025/26: €7,455 در ترم؛ نرخ ۲۰۲۶ روی سایت AAU منتشر نشده — mastersportal: €15,340)</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -9499,12 +9495,12 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی SE/CS</t>
+          <t>رسمی: حداقل ۱۵۰ ECTS دروس مرتبط با CS (برنامه‌نویسی ۱۵، مهندسی نرم‌افزار ۵، الگوریتم ۵، پایگاه داده ۵، ریاضیات گسسته ۵)؛ از ورودی ۲۰۲۷ سابقهٔ کار و انگیزه‌نامه هم در رتبه‌بندی حساب می‌شود</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5 (هر بخش ≥ 6.0)</t>
         </is>
       </c>
       <c r="M89" s="4">
@@ -9521,10 +9517,14 @@
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P89" s="4" t="inlineStr"/>
+      <c r="P89" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)؛ ظرفیت محدود</t>
+        </is>
+      </c>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/software</t>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
         </is>
       </c>
     </row>
@@ -9544,22 +9544,22 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen – Sydhavn (کپنهاگ؛ کمپوس AAU)</t>
+          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 10,000–12,500</t>
+          <t>متوسط — DKK 8,000–9,500</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Cyber Security</t>
+          <t>MSc Software</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE مرتبط؛ مهلت ۱ مارس</t>
+          <t>کارشناسی SE/CS</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -9598,17 +9598,13 @@
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
-        </is>
-      </c>
-      <c r="P90" s="4" t="inlineStr">
-        <is>
-          <t>کمپوس کپنهاگ: اجاره بالاتر ولی بازار کار بزرگ</t>
-        </is>
-      </c>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="inlineStr"/>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/cyber-security/</t>
+          <t>https://www.en.aau.dk/education/master/software</t>
         </is>
       </c>
     </row>
@@ -9628,22 +9624,22 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Aalborg یا Copenhagen (هر دو کمپوس)</t>
+          <t>Copenhagen – Sydhavn (کپنهاگ؛ کمپوس AAU)</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>متوسط (Aalborg) تا خیلی گران (Copenhagen)</t>
+          <t>خیلی گران — DKK 10,000–12,500</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>MSc Medialogy</t>
+          <t>MSc Eng Cyber Security</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -9663,7 +9659,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط (Medialogy، CS، Media Tech)</t>
+          <t>کارشناسی CS/EE مرتبط؛ مهلت ۱ مارس</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -9682,17 +9678,17 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>تعامل، AR/VR، بازی؛ بین HCI و Game</t>
+          <t>کمپوس کپنهاگ: اجاره بالاتر ولی بازار کار بزرگ</t>
         </is>
       </c>
       <c r="Q91" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/medialogy-aal</t>
+          <t>https://www.en.aau.dk/education/master/cyber-security/</t>
         </is>
       </c>
     </row>
@@ -9707,27 +9703,27 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+          <t>Aalborg یا Copenhagen (هر دو کمپوس)</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–10,000</t>
+          <t>متوسط (Aalborg) تا خیلی گران (Copenhagen)</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Medialogy</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -9737,17 +9733,17 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>€17,300 (از ورودی سپتامبر ۲۰۲۶؛ قبلاً €13,900)</t>
+          <t>≈ €14,910–15,340</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>$19,700</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>≥ ۱۰۰ ECTS دروس CS؛ ظرفیت محدود + آزمون</t>
+          <t>کارشناسی مرتبط (Medialogy، CS، Media Tech)</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -9756,7 +9752,7 @@
         </is>
       </c>
       <c r="M92" s="4">
-        <f>283</f>
+        <f>329</f>
         <v/>
       </c>
       <c r="N92" s="10" t="inlineStr">
@@ -9766,17 +9762,17 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>⚠️ افزایش شهریهٔ ۲۰۲۶ — جدول اصلی اصلاح شد</t>
+          <t>تعامل، AR/VR، بازی؛ بین HCI و Game</t>
         </is>
       </c>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
+          <t>https://www.en.aau.dk/education/master/medialogy-aal</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9802,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Software Engineering</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -9821,7 +9817,7 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>€17,300</t>
+          <t>€17,300 (از ورودی سپتامبر ۲۰۲۶؛ قبلاً €13,900)</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -9831,7 +9827,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی SE/CS</t>
+          <t>≥ ۱۰۰ ECTS دروس CS؛ ظرفیت محدود + آزمون</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -9855,12 +9851,12 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>گرایش‌های Interactive Tech &amp; Games، Cyber-security &amp; Data Intelligence</t>
+          <t>⚠️ افزایش شهریهٔ ۲۰۲۶ — جدول اصلی اصلاح شد</t>
         </is>
       </c>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/softwareengineering</t>
+          <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
         </is>
       </c>
     </row>
@@ -9890,12 +9886,12 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Eng Software Engineering</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -9915,7 +9911,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI</t>
+          <t>کارشناسی SE/CS</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -9934,17 +9930,17 @@
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>شروع سپتامبر و فوریه</t>
+          <t>گرایش‌های Interactive Tech &amp; Games، Cyber-security &amp; Data Intelligence</t>
         </is>
       </c>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/studyscience</t>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/softwareengineering</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9970,12 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Robot Systems</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -9999,7 +9995,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط (CS/EE/Mechatronics)</t>
+          <t>کارشناسی CS/AI</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -10018,17 +10014,17 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>Odense Robotics cluster (Universal Robots، MiR)</t>
+          <t>شروع سپتامبر و فوریه</t>
         </is>
       </c>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
+          <t>https://www.sdu.dk/en/studyscience</t>
         </is>
       </c>
     </row>
@@ -10048,22 +10044,22 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Kolding (کولدینگ) — جنوب یوتلند</t>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>ارزان تا متوسط — DKK 7,500–9,000</t>
+          <t>متوسط — DKK 8,000–10,000</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science</t>
+          <t>MSc Eng Robot Systems</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -10083,7 +10079,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی با محتوای کمی/برنامه‌نویسی</t>
+          <t>کارشناسی مرتبط (CS/EE/Mechatronics)</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -10102,10 +10098,14 @@
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P96" s="4" t="inlineStr"/>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="P96" s="4" t="inlineStr">
+        <is>
+          <t>Odense Robotics cluster (Universal Robots، MiR)</t>
+        </is>
+      </c>
       <c r="Q96" s="8" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
@@ -10123,27 +10123,27 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen (ITU)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen (کپنهاگ)</t>
+          <t>Kolding (کولدینگ) — جنوب یوتلند</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 10,000–12,500</t>
+          <t>ارزان تا متوسط — DKK 7,500–9,000</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>MSc Games — track Game Technology</t>
+          <t>MSc Data Science</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>€16,500 (€8,250 در ترم؛ ورودی ۲۰۲۶ — رسمی)</t>
+          <t>€17,300</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>$18,800</t>
+          <t>$19,700</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>برای track فنی: کارشناسی CS</t>
+          <t>کارشناسی با محتوای کمی/برنامه‌نویسی</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -10171,10 +10171,9 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M97" s="4" t="inlineStr">
-        <is>
-          <t>— (تخصصی)</t>
-        </is>
+      <c r="M97" s="4">
+        <f>283</f>
+        <v/>
       </c>
       <c r="N97" s="10" t="inlineStr">
         <is>
@@ -10183,17 +10182,13 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
-        </is>
-      </c>
-      <c r="P97" s="4" t="inlineStr">
-        <is>
-          <t>شناخته‌شده‌ترین ارشد بازی اسکاندیناوی؛ Copenhagen (IO Interactive، Unity Copenhagen)</t>
-        </is>
-      </c>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P97" s="4" t="inlineStr"/>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
         </is>
       </c>
     </row>
@@ -10223,12 +10218,12 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Games — track Game Technology</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -10238,7 +10233,7 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>€16,500 (€8,250 در ترم)</t>
+          <t>€16,500 (€8,250 در ترم؛ ورودی ۲۰۲۶ — رسمی)</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -10248,7 +10243,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE با برنامه‌نویسی قابل توجه</t>
+          <t>برای track فنی: کارشناسی CS</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -10268,12 +10263,12 @@
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌تر از DTU/KU در کپنهاگ؛ رقم قدیمی €13,400 (پورتال studyindenmark) منسوخ است</t>
+          <t>شناخته‌شده‌ترین ارشد بازی اسکاندیناوی؛ Copenhagen (IO Interactive، Unity Copenhagen)</t>
         </is>
       </c>
       <c r="Q98" s="8" t="inlineStr">
@@ -10308,12 +10303,12 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -10333,7 +10328,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط با داده/CS</t>
+          <t>کارشناسی CS/SE با برنامه‌نویسی قابل توجه</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -10353,10 +10348,14 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P99" s="4" t="inlineStr"/>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>ارزان‌تر از DTU/KU در کپنهاگ؛ رقم قدیمی €13,400 (پورتال studyindenmark) منسوخ است</t>
+        </is>
+      </c>
       <c r="Q99" s="8" t="inlineStr">
         <is>
           <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
@@ -10374,27 +10373,27 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Technical University of Denmark (DTU)</t>
+          <t>IT University of Copenhagen (ITU)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+          <t>Copenhagen (کپنهاگ)</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 9,500–12,000</t>
+          <t>خیلی گران — DKK 10,000–12,500</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Human-Centered Artificial Intelligence</t>
+          <t>MSc Data Science</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -10404,17 +10403,17 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>€15,000</t>
+          <t>€16,500 (€8,250 در ترم)</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>$17,100</t>
+          <t>$18,800</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>ظرفیت محدود؛ امتیازدهی: معدل ۶۰٪ + سابقهٔ کار ۱۰٪</t>
+          <t>کارشناسی مرتبط با داده/CS</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -10424,27 +10423,23 @@
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="N100" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>— (تخصصی)</t>
+        </is>
+      </c>
+      <c r="N100" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
-        </is>
-      </c>
-      <c r="P100" s="4" t="inlineStr">
-        <is>
-          <t>معدل ۱۵.۷۷ در رقابت DTU ضعیف است</t>
-        </is>
-      </c>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P100" s="4" t="inlineStr"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/human-centered-artificial-intelligence</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
@@ -10474,12 +10469,12 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Autonomous Systems</t>
+          <t>MSc Eng Human-Centered Artificial Intelligence</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -10499,7 +10494,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>۸۰–۹۰ ECTS دروس مرتبط؛ ظرفیت محدود</t>
+          <t>ظرفیت محدود؛ امتیازدهی: معدل ۶۰٪ + سابقهٔ کار ۱۰٪</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -10519,13 +10514,17 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
-        </is>
-      </c>
-      <c r="P101" s="4" t="inlineStr"/>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>معدل ۱۵.۷۷ در رقابت DTU ضعیف است</t>
+        </is>
+      </c>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/human-centered-artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -10555,12 +10554,12 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Computer Science and Engineering</t>
+          <t>MSc Eng Autonomous Systems</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -10580,7 +10579,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>ظرفیت محدود؛ گزینش با معدل</t>
+          <t>۸۰–۹۰ ECTS دروس مرتبط؛ ظرفیت محدود</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -10600,13 +10599,13 @@
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr"/>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/computer-science-and-engineering</t>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
       </c>
     </row>
@@ -10621,129 +10620,210 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
+          <t>Technical University of Denmark (DTU)</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 9,500–12,000</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>€15,000</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>ظرفیت محدود؛ گزینش با معدل</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M103" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N103" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P103" s="4" t="inlineStr"/>
+      <c r="Q103" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/computer-science-and-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
           <t>Aarhus University (AU)</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>Aarhus (آرهوس) — دومین شهر دانمارک</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>گران — DKK 9,000–11,000</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr">
+      <c r="I104" s="4" t="inlineStr">
         <is>
           <t>€17,300</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr">
+      <c r="J104" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="K103" s="4" t="inlineStr">
+      <c r="K104" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS با واحدهای مشخص</t>
         </is>
       </c>
-      <c r="L103" s="4" t="inlineStr">
+      <c r="L104" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="M103" s="4" t="inlineStr">
+      <c r="M104" s="4" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="N103" s="11" t="inlineStr">
+      <c r="N104" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="O103" s="4" t="inlineStr">
+      <c r="O104" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P103" s="4" t="inlineStr">
+      <c r="P104" s="4" t="inlineStr">
         <is>
           <t>Aarhus: دومین شهر، ارزان‌تر از کپنهاگ</t>
         </is>
       </c>
-      <c r="Q103" s="8" t="inlineStr">
+      <c r="Q104" s="8" t="inlineStr">
         <is>
           <t>https://masters.au.dk/computerscience</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="34" customHeight="1">
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>راهنما: هر ردیف یک برنامهٔ انگلیسی‌زبان است. Safe/Target/Reach نسبت به معدل ۱۵.۷۷/۲۰ (≈ 2:2 بریتانیا / ≈ 2.3 آلمانی / ≈ ۷۹٪) و IELTS ≈ 7 سنجیده شده و پیش‌بینی پذیرش نیست. «≈» یعنی رقم از منبع ثانویه یا سال قبل است — قبل از اقدام صفحهٔ رسمی را چک کنید.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="34" customHeight="1">
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>شهریهٔ دلاری با نرخ نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 و گرد شده به $100. برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 ملاک است (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪؛ TU/e و Surrey و Gothenburg همین حالا رسمی‌اند). آلمان: عدد فقط سهم ترم (Semesterbeitrag) است که بلیت حمل‌ونقل را هم شامل می‌شود.</t>
+          <t>راهنما: هر ردیف یک برنامهٔ انگلیسی‌زبان است. Safe/Target/Reach نسبت به معدل ۱۵.۷۷/۲۰ (≈ 2:2 بریتانیا / ≈ 2.3 آلمانی / ≈ ۷۹٪) و IELTS ≈ 7 سنجیده شده و پیش‌بینی پذیرش نیست. «≈» یعنی رقم از منبع ثانویه یا سال قبل است — قبل از اقدام صفحهٔ رسمی را چک کنید.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="34" customHeight="1">
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>امتیاز بازار کار (۱–۵) ارزیابی من بر پایهٔ منابع شیت «حوزه‌ها و بازار کار» است، نه آمار رسمی؛ برای هر برنامه فقط حوزه را نشان می‌دهد، نه کیفیت آن دانشگاه.</t>
+          <t>شهریهٔ دلاری با نرخ نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21 و گرد شده به $100. برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 ملاک است (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪؛ TU/e و Surrey و Gothenburg همین حالا رسمی‌اند). آلمان: عدد فقط سهم ترم (Semesterbeitrag) است که بلیت حمل‌ونقل را هم شامل می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="34" customHeight="1">
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>ستون «هزینهٔ زندگی شهر» برآورد تقریبی هزینهٔ ماهانهٔ دانشجو با اجارهٔ اتاق در همان شهر است (سازگار با ردیف ۶ جدول اصلی)؛ برچسب‌ها: ارزان / متوسط / گران / خیلی گران. برای مقایسهٔ کشورها همچنان ردیف‌های ۶–۸ جدول اصلی معیار است.</t>
+          <t>امتیاز بازار کار (۱–۵) ارزیابی من بر پایهٔ منابع شیت «حوزه‌ها و بازار کار» است، نه آمار رسمی؛ برای هر برنامه فقط حوزه را نشان می‌دهد، نه کیفیت آن دانشگاه.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="34" customHeight="1">
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>بازبینی صحت اعداد (۲۷ سپتامبر ۲۰۲۶): ≈۷۰٪ شهریه‌ها مستقیماً از صفحهٔ رسمی 2026/27 است؛ ردیف‌های «≈» از منبع ثانویه یا سال قبل‌اند. اصلاح‌های این بازبینی: FAU از تابستان ۲۰۲۷ شهریه می‌گیرد (AI/CS €4,000/ترم)؛ ITU €16,500 (نه €13,400)؛ Radboud €19,714 رسمی؛ Chalmers ≈ SEK 175k (نه 160k)؛ KTH ≈ 180–190k؛ AAU شرط ≥ ۱۵۰ ECTS؛ Surrey Cyber ورودی ۲۰۲۷؛ Newcastle Games 2:2؛ Sheffield AI ≈ £32.9–34.3k. رتبه‌بندی Safe/Target/Reach، امتیاز بازار و ردهٔ هزینهٔ شهر ارزیابی‌اند، نه دادهٔ رسمی.</t>
+          <t>ستون «هزینهٔ زندگی شهر» برآورد تقریبی هزینهٔ ماهانهٔ دانشجو با اجارهٔ اتاق در همان شهر است (سازگار با ردیف ۶ جدول اصلی)؛ برچسب‌ها: ارزان / متوسط / گران / خیلی گران. برای مقایسهٔ کشورها همچنان ردیف‌های ۶–۸ جدول اصلی معیار است.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="34" customHeight="1">
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>حذف‌شده‌ها: Essex MSc Computer Games (برای 2025/26 و 2026/27 تعلیق شده)، Hull AI &amp; Data Science (سه رقم متناقض شهریه)، UCD/TCD (2:1 و ≈ €30k → Reach، بررسی نشد)، KU Copenhagen (شهریه تأیید نشد)، NCI/DBS ایرلند (کالج خصوصی، اعتبار کمتر).</t>
+          <t>بازبینی صحت اعداد (۲۷ سپتامبر ۲۰۲۶): ≈۷۰٪ شهریه‌ها مستقیماً از صفحهٔ رسمی 2026/27 است؛ ردیف‌های «≈» از منبع ثانویه یا سال قبل‌اند. اصلاح‌های این بازبینی: FAU از تابستان ۲۰۲۷ شهریه می‌گیرد (AI/CS €4,000/ترم)؛ ITU €16,500 (نه €13,400)؛ Radboud €19,714 رسمی؛ Chalmers ≈ SEK 175k (نه 160k)؛ KTH ≈ 180–190k؛ AAU شرط ≥ ۱۵۰ ECTS؛ Surrey Cyber ورودی ۲۰۲۷؛ Newcastle Games 2:2؛ Sheffield AI ≈ £32.9–34.3k. رتبه‌بندی Safe/Target/Reach، امتیاز بازار و ردهٔ هزینهٔ شهر ارزیابی‌اند، نه دادهٔ رسمی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="34" customHeight="1">
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>حذف‌شده‌ها: Essex MSc Computer Games (برای 2025/26 و 2026/27 تعلیق شده)، Hull AI &amp; Data Science (سه رقم متناقض شهریه)، UCD/TCD (2:1 و ≈ €30k → Reach، بررسی نشد)، KU Copenhagen (شهریه تأیید نشد)؛ ایرلند (۱۲ برنامه) به خواست شما در سپتامبر ۲۰۲۶ کامل حذف و ۱۳ برنامهٔ سوئیس جایگزین شد. سوئیس: شهریه‌های ETH، EPFL، UZH، USI، ZHAW و HSLU از صفحات رسمی 2026/27؛ Bern، Fribourg و Basel از مراجع ثانویه (≈) — و یادتان باشد در سوئیس شهریه عدد کوچک است، هزینهٔ زندگی (CHF 1,400–2,500/ماه) و تمکن CHF 21,000 عدد اصلی‌اند.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q103"/>
+  <autoFilter ref="A1:Q104"/>
   <mergeCells count="6">
+    <mergeCell ref="B111:Q111"/>
     <mergeCell ref="B107:Q107"/>
     <mergeCell ref="B108:Q108"/>
     <mergeCell ref="B110:Q110"/>
-    <mergeCell ref="B105:Q105"/>
     <mergeCell ref="B106:Q106"/>
     <mergeCell ref="B109:Q109"/>
   </mergeCells>
@@ -10850,6 +10930,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q104" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10933,7 +11014,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>خوب: پیش‌زمینهٔ Computer Engineering + Python؛ ولی برای برنامه‌های Reach (Tübingen، UvA، KTH، Sheffield) معدل ۱۵.۷۷ کافی نیست — برنامه‌های کاربردی (Passau AI Eng، FAU، Northumbria/Teesside AI، UL AI&amp;ML، Umeå) هدف بگیرید</t>
+          <t>خوب: پیش‌زمینهٔ Computer Engineering + Python؛ ولی برای برنامه‌های Reach (Tübingen، UvA، KTH، Sheffield) معدل ۱۵.۷۷ کافی نیست — برنامه‌های کاربردی (Passau AI Eng، FAU، Northumbria/Teesside AI، USI AI (Lugano)، Umeå) هدف بگیرید</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10960,7 +11041,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>مرجع (آلمان €48–55k · هلند €40–50k · سوئد SEK 420–540k · دانمارک DKK 500–540k · ایرلند €35–45k · انگلستان £28–35k)</t>
+          <t>مرجع (آلمان €48–55k · هلند €40–50k · سوئد SEK 420–540k · دانمارک DKK 500–540k · سوئیس CHF 85–105k (بالاترین) · انگلستان £28–35k)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -10997,7 +11078,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>مساوی تا کمی بالاتر؛ در انگلستان (NCSC-certified) و ایرلند (مراکز امنیت شرکت‌های آمریکایی) خوب</t>
+          <t>مساوی تا کمی بالاتر؛ در انگلستان (NCSC-certified) و سوئیس (بانک‌ها، بیمه‌ها، ETH/EPFL Cyber؛ حقوق بالا) خوب</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -11007,7 +11088,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>خوب: MSc Cyber با 2:2 در Teesside/Northumbria/MMU/Kent/Royal Holloway/TU Dublin؛ Saarland (رایگان ولی IELTS 7)؛ AAU کپنهاگ</t>
+          <t>خوب: MSc Cyber با 2:2 در Teesside/Northumbria/MMU/Kent/Royal Holloway؛ Saarland (رایگان ولی IELTS 7)؛ AAU کپنهاگ؛ ZHAW MSE Information &amp; Cyber Security (سوئیس، نیاز به معدل A/B)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -11044,7 +11125,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>خوب: Leicester Cloud Computing، TU Darmstadt DSS، KTH SEDS، DCU Cloud major؛ گواهی AWS/Azure کنار مدرک</t>
+          <t>خوب: Leicester Cloud Computing، TU Darmstadt DSS، KTH SEDS، USI Software &amp; Data Engineering؛ گواهی AWS/Azure کنار مدرک</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -11081,7 +11162,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>متوسط: مدرک‌های ارزان و Safe زیاد است (Maynooth €17k، Skövde، Brunel، ITU €16.5k) ولی رقابت جونیور بالاست؛ اگر می‌روید، Data Engineering را انتخاب کنید</t>
+          <t>متوسط: مدرک‌های ارزان و Safe زیاد است (HSLU Lucerne ≈ CHF 3,150/سال، Skövde، Brunel، ITU €16.5k) ولی رقابت جونیور بالاست؛ اگر می‌روید، Data Engineering را انتخاب کنید</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11108,7 +11189,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>مساوی تا کمی بالاتر در صنعت (Bosch، Continental، ABB، Volvo)؛ پایین‌تر در بریتانیا/ایرلند</t>
+          <t>مساوی تا کمی بالاتر در صنعت (Bosch، Continental، ABB، Volvo)؛ پایین‌تر در بریتانیا؛ در سوئیس (ABB، رباتیک ETH) بالا ولی آلمانی‌محور</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -11227,7 +11308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11309,7 +11390,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>IELTS از ۳۱ ژانویه ۲۰۲۶ و TOEFL از ۱۴۰۵ در ایران برگزار نمی‌شوند. IELTS Academic کامپیوتری در استانبول/ایروان/دبی/تفلیس برای نوامبر تا اوایل دسامبر ۲۰۲۶ رزرو کنید (نتیجه ۳–۵ روزه؛ ≈ $250–300 + سفر). هدف 7.0 با هر بخش ≥ 6.5 (Stuttgart C1، Saarland 7.0). Duolingo فقط بعضی دانشگاه‌های انگلستان/ایرلند را باز می‌کند، نه سوئد/دانمارک/هلند/آلمان.</t>
+          <t>IELTS از ۳۱ ژانویه ۲۰۲۶ و TOEFL از ۱۴۰۵ در ایران برگزار نمی‌شوند. IELTS Academic کامپیوتری در استانبول/ایروان/دبی/تفلیس برای نوامبر تا اوایل دسامبر ۲۰۲۶ رزرو کنید (نتیجه ۳–۵ روزه؛ ≈ $250–300 + سفر). هدف 7.0 با هر بخش ≥ 6.5 (Stuttgart C1، Saarland 7.0). Duolingo فقط بعضی دانشگاه‌های انگلستان را باز می‌کند، نه سوئد/دانمارک/هلند/آلمان/سوئیس. برای ETH (۳۰ نوامبر) گواهی باید زودتر آماده باشد.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11348,7 +11429,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>۱۴–۱۶ اکتبر ۲۰۲۶</t>
+          <t>۱۵–۱۶ اکتبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -11358,380 +11439,380 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>ایرلند، هلند، سوئد</t>
+          <t>هلند، سوئد</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Maynooth (۱۴ اکتبر)، UL (۱۵ اکتبر)، فرم بورس UTS Twente (۱۵ اکتبر)، سوئد universityadmissions.se (۱۶ اکتبر — تا ۴ برنامه با یک درخواست، SEK 900).</t>
+          <t>فرم بورس UTS Twente (۱۵ اکتبر)، سوئد universityadmissions.se (۱۶ اکتبر — تا ۴ برنامه با یک درخواست، SEK 900). پورتال‌های سوئیس (USI، Bern، Basel، UZH، ZHAW، HSLU) از حدود اکتبر–ژانویه برای پاییز ۲۰۲۷ باز می‌شوند.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>maynoothuniversity.ie؛ ul.ie؛ utwente.nl؛ universityadmissions.se</t>
+          <t>utwente.nl؛ universityadmissions.se؛ سایت دانشگاه‌های سوئیس</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>نوامبر ۲۰۲۶</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>VPD از uni-assist</t>
+          <t>۱ – ۳۰ نوامبر ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>⛔ پنجرهٔ ETH Zürich (تنها فرصت سال — Reach)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>برای TU Darmstadt، TU Dresden، Saarland، RPTU، Chemnitz، OVGU و Passau (uni-assist) ۴–۶ هفته زمان و €75 هزینه؛ Stuttgart مستقیم در C@MPUS اپلای می‌گیرد (۱۵ نوامبر – ۱۵ ژانویه).</t>
+          <t>اپلای آنلاین ۱ تا ۳۰ نوامبر ۲۰۲۶ (ساعت ۱۱:۵۹ صبح CET)؛ CHF 150؛ گواهی C1/IELTS 7.0 باید تا آن موقع در دست باشد → یعنی آزمون در اکتبر یا اوایل نوامبر. پاسخ تا پایان مارس ۲۰۲۷؛ تأییدیهٔ ثبت‌نام برای ویزا از می ۲۰۲۷؛ شروع ۲۰ سپتامبر ۲۰۲۷. با معدل ۱۵.۷۷ شانس کم است — فقط اگر هزینهٔ آن را می‌پذیرید.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>uni-assist.de؛ uni-stuttgart.de</t>
+          <t>ethz.ch/en/studies/master/application/dates.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>نوامبر – اوایل دسامبر ۲۰۲۶</t>
+          <t>نوامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>آزمون IELTS</t>
+          <t>VPD از uni-assist</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>همه</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>نتیجه باید تا اوایل ژانویه ۲۰۲۷ در دست باشد (سوئد، دانمارک، Stuttgart). یک تاریخ ذخیره در دسامبر رزرو کنید.</t>
+          <t>برای TU Darmstadt، TU Dresden، Saarland، RPTU، Chemnitz، OVGU و Passau (uni-assist) ۴–۶ هفته زمان و €75 هزینه؛ Stuttgart مستقیم در C@MPUS اپلای می‌گیرد (۱۵ نوامبر – ۱۵ ژانویه).</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>uni-assist.de؛ uni-stuttgart.de</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>اواسط دسامبر ۲۰۲۶</t>
+          <t>نوامبر – اوایل دسامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>پورتال AAU باز می‌شود</t>
+          <t>آزمون IELTS</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>همه</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>برای شهریه‌پردازها مهلت ۱۵ ژانویه است (۱ مارس فقط برای EU).</t>
+          <t>نتیجه باید تا اوایل ژانویه ۲۰۲۷ در دست باشد (سوئد، دانمارک، Stuttgart). یک تاریخ ذخیره در دسامبر رزرو کنید.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>en.aau.dk/how-and-when-to-apply</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>۱۵ ژانویه ۲۰۲۷</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>⛔ مهلت اصلی ۱: سوئد + دانمارک + Stuttgart</t>
+          <t>۱۵ دسامبر ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>دور اول EPFL (توصیه برای ویزایی‌ها — Reach)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>سوئد، دانمارک، آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>سوئد (همهٔ دانشگاه‌ها: Linköping، Halmstad، BTH، Chalmers، KTH، Uppsala، Umeå، Skövde)؛ AAU (fee-paying)، Aarhus، DTU (الگوی ۱۵ ژانویه برای غیر-EU)؛ Stuttgart MSc Computer Science / INFOTECH.</t>
+          <t>پنجرهٔ اپلای از اواسط نوامبر تا ۱۵ دسامبر (پاسخ اوایل آوریل)؛ دور دوم ۱۶ دسامبر – ۳۱ مارس ۲۰۲۷ (پاسخ پایان ژوئن — برای ویزای ۸–۱۲ هفته‌ای دیر است). فقط یک برنامه در سال؛ مدرک زبان الزامی نیست؛ CHF 150.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>umu.se و uu.se key dates؛ en.aau.dk؛ uni-stuttgart.de</t>
+          <t>epfl.ch (online application)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>۳۱ ژانویه ۲۰۲۷</t>
+          <t>اواسط دسامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>مهلت بورس Radboud</t>
+          <t>پورتال AAU باز می‌شود</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>دانمارک</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Radboud Scholarship Programme (≈۳۳ نفر؛ شهریه به €2,694 می‌رسد) — اپلای اصلی هم باید تا این تاریخ کامل باشد.</t>
+          <t>برای شهریه‌پردازها مهلت ۱۵ ژانویه است (۱ مارس فقط برای EU).</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>ru.nl deadlines</t>
+          <t>en.aau.dk/how-and-when-to-apply</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>۱ فوریه ۲۰۲۷</t>
+          <t>۱۵ ژانویه ۲۰۲۷</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>⛔ مهلت اصلی ۲</t>
+          <t>⛔ مهلت اصلی ۱: سوئد + دانمارک + Stuttgart</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>سوئد، دانمارک، هلند</t>
+          <t>سوئد، دانمارک، آلمان</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>سوئد: مدارک + SEK 900 روی universityadmissions.se؛ SDU (غیر-EU)؛ Twente: برای بورس UTS (۱ آوریل) اپلای را تا اوایل فوریه بفرستید.</t>
+          <t>سوئد (همهٔ دانشگاه‌ها: Linköping، Halmstad، BTH، Chalmers، KTH، Uppsala، Umeå، Skövde)؛ AAU (fee-paying)، Aarhus، DTU (الگوی ۱۵ ژانویه برای غیر-EU)؛ Stuttgart MSc Computer Science / INFOTECH.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>universityadmissions.se؛ sdu.dk/datalogi؛ utwente.nl</t>
+          <t>umu.se و uu.se key dates؛ en.aau.dk؛ uni-stuttgart.de</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>فوریه – مارس ۲۰۲۷</t>
+          <t>۳۱ ژانویه ۲۰۲۷</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>اپلای ایرلند و انگلستان</t>
+          <t>مهلت بورس Radboud</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>ایرلند، انگلستان</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>همه rolling هستند ولی زود اپلای کنید: بورس‌ها (Brunel، DCU، Northumbria) و ظرفیت‌ها زود پر می‌شود؛ TU Dublin بین‌المللی ≈ ۳۱ می، Maynooth غیر-EU ≈ ۱۵ می تا ژوئن، UL غیر-EU ویزایی ۱ ژوئیه.</t>
+          <t>Radboud Scholarship Programme (≈۳۳ نفر؛ شهریه به €2,694 می‌رسد) — اپلای اصلی هم باید تا این تاریخ کامل باشد.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>studyinireland.app؛ ul.ie/gps/applications-faq</t>
+          <t>ru.nl deadlines</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>۳۰ مارس – ۱ آوریل ۲۰۲۷</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>نتایج سوئد</t>
+          <t>۱ فوریه ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>⛔ مهلت اصلی ۲</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>سوئد، دانمارک، هلند</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>پاسخ به پیشنهاد در مهلت؛ قسط اول شهریه قبل از درخواست اقامت تحصیلی.</t>
+          <t>سوئد: مدارک + SEK 900 روی universityadmissions.se؛ SDU (غیر-EU)؛ Twente: برای بورس UTS (۱ آوریل) اپلای را تا اوایل فوریه بفرستید.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>universityadmissions.se</t>
+          <t>universityadmissions.se؛ sdu.dk/datalogi؛ utwente.nl</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>۱ آوریل ۲۰۲۷</t>
+          <t>۲۸ فوریه ۲۰۲۷</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>⛔ مهلت اصلی ۳</t>
+          <t>⛔ مهلت ویزایی‌ها: UZH و Fribourg</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>هلند، آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Radboud غیر-EU (اپلای اصلی)؛ بورس UTS Twente؛ پنجرهٔ Passau AI Engineering باز می‌شود (۱ آوریل – ۳۱ می).</t>
+          <t>UZH (MSc Informatics — Reach) و Fribourg (Joint MSc CS — Target) برای متقاضیانی که ویزا لازم دارند ۲۸ فوریه می‌بندند (بدون ویزا ۳۰ آوریل). UZH: CHF 150، فقط یک برنامه در هر ترم.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>ru.nl؛ utwente.nl؛ uni-passau.de</t>
+          <t>oec.uzh.ch (FAQ Master's Admission)؛ mastersportal/unifr.ch</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>۱۵ آوریل ۲۰۲۷</t>
+          <t>فوریه – مارس ۲۰۲۷</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>دور دوم سوئد (فقط پشتیبان)</t>
+          <t>اپلای انگلستان + پرونده‌های سوئیس</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>انگلستان، سوئیس</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>۱۵ مارس – ۱۵ آوریل؛ مدارک تا ۲۱ ژوئن؛ نتیجه ۹ ژوئیه — برای اقامت و خوابگاه دیر است.</t>
+          <t>انگلستان rolling است ولی زود اپلای کنید: بورس‌ها (Brunel، Northumbria) و ظرفیت‌ها زود پر می‌شود. سوئیس: پرونده‌های USI (Informatics / AI / Software &amp; Data Eng)، Bern، Basel، HSLU و ZHAW را همین ماه‌ها بفرستید تا قبل از مهلت ۳۰ آوریل بررسی شوند؛ ریزنمرات و دانشنامه باید ترجمهٔ رسمی/تأییدشده باشند.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>umu.se key dates</t>
+          <t>سایت دانشگاه‌ها</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>۱ می ۲۰۲۷</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>⛔ مهلت Twente (غیر-EEA)</t>
+          <t>۳۰ مارس – ۱ آوریل ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>نتایج سوئد</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science / Embedded Systems / Interaction Technology.</t>
+          <t>پاسخ به پیشنهاد در مهلت؛ قسط اول شهریه قبل از درخواست اقامت تحصیلی.</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>utwente.nl (به نقل از collegedunia، اوت ۲۰۲۶)</t>
+          <t>universityadmissions.se</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>۱۵ – ۳۱ می ۲۰۲۷</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>مهلت‌های ایرلند و آلمان</t>
+          <t>۱ آوریل ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>⛔ مهلت اصلی ۳</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>ایرلند، آلمان</t>
+          <t>هلند، آلمان</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Maynooth غیر-EU ≈ ۱۵ می؛ TU Dublin بین‌المللی ≈ ۳۱ می؛ Passau AI Eng ۳۱ می؛ بقیهٔ آلمان (TU Darmstadt، TU Dresden، Saarland، RPTU، Chemnitz، OVGU، FAU) بیشتر بین ۱۵ می تا ۱۵ ژوئیه — هر کدام را جدا چک کنید.</t>
+          <t>Radboud غیر-EU (اپلای اصلی)؛ بورس UTS Twente؛ پنجرهٔ Passau AI Engineering باز می‌شود (۱ آوریل – ۳۱ می).</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>studyinireland.app؛ uni-passau.de؛ سایت دانشگاه‌ها</t>
+          <t>ru.nl؛ utwente.nl؛ uni-passau.de</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>می – ژوئن ۲۰۲۷</t>
+          <t>۱۵ آوریل ۲۰۲۷</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>💰 پول باید نقد و قابل انتقال باشد</t>
+          <t>دور دوم سوئد (فقط پشتیبان)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>همه</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>SDU: یک سال شهریه پیش‌پرداخت (€17,300)؛ سوئد: قسط ترم اول + تمکن SEK 10,656 × ماه‌ها؛ هلند: شهریه + €13,569 زندگی به حساب دانشگاه (Radboud تا ۱ ژوئن)؛ آلمان: حساب مسدود €11,904 (Fintiba ایران را نمی‌پذیرد → Expatrio/Coracle) + Stuttgart €1,500؛ ایرلند: €10,000 + حداقل €6,000 شهریه؛ انگلستان: ودیعه → CAS + £1,203 × ۹ ماه. انتقال از کشور ثالث/صرافی ۳–۶٪ هزینه.</t>
+          <t>۱۵ مارس – ۱۵ آوریل؛ مدارک تا ۲۱ ژوئن؛ نتیجه ۹ ژوئیه — برای اقامت و خوابگاه دیر است.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>ردیف ۲۵ جدول اصلی</t>
+          <t>umu.se key dates</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>۱ ژوئن ۲۰۲۷</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>مهلت ثبت‌نام/ویزای Radboud</t>
+          <t>۱ می ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>⛔ مهلت Twente (غیر-EEA)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11741,78 +11822,78 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>برای شروع سپتامبر (غیر-EU)؛ درخواست MVV را دانشگاه از طرف شما به IND می‌دهد.</t>
+          <t>MSc Computer Science / Embedded Systems / Interaction Technology.</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>ru.nl deadlines</t>
+          <t>utwente.nl (به نقل از collegedunia، اوت ۲۰۲۶)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>۱ ژوئیه ۲۰۲۷</t>
+          <t>۳۰ آوریل ۲۰۲۷</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>⛔ مهلت UL (غیر-EU ویزایی)</t>
+          <t>⛔ مهلت اصلی سوئیس (غیر-EU)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>ایرلند</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>الگوی ۲۰۲۶: ۱ ژوئیه ساعت ۱۲؛ بعد از آن بررسی نمی‌شود.</t>
+          <t>USI (Informatics / AI / Software &amp; Data Engineering — مهلت غیر-EU)، Bern (Joint MSc CS؛ ویزایی‌ها مهلت دیرهنگام ندارند)، Basel، ZHAW MSE (پایان آوریل)؛ HSLU ≈ همین حدود (چک شود). پاسخ‌ها می–ژوئن؛ بلافاصله وقت ویزای D را در سفارت تهران بگیرید — تصمیم با ادارهٔ مهاجرت کانتون، ۸–۱۲ هفته؛ برای Ticino/Bern/Fribourg/Lucerne قبلش نوع مدرک تمکن قابل قبول را بپرسید.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>ul.ie/gps/applications-faq</t>
+          <t>usi.ch؛ unibe.ch؛ zhaw.ch؛ eda.admin.ch/tehran</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ژوئن – ژوئیه ۲۰۲۷</t>
+          <t>۱۵ – ۳۱ می ۲۰۲۷</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>🛂 ویزا / برنامهٔ B</t>
+          <t>مهلت‌های آلمان</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>همه</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>وضعیت تهران (سپتامبر ۲۰۲۶): آلمان حالت اضطراری، هلند از باکو، دانمارک «از ایران ممکن نیست»، ایرلند کنسول بسته، انگلستان VFS متناوب؛ سوئد بدون بیومتریک (آنلاین). یعنی برای DE/DK/IE/UK سفر به ترکیه/ارمنستان/امارات را (۲–۶ هفته) در بودجه و تقویم بگذارید.</t>
+          <t>Passau AI Eng ۳۱ می؛ بقیهٔ آلمان (TU Darmstadt، TU Dresden، Saarland، RPTU، Chemnitz، OVGU، FAU) بیشتر بین ۱۵ می تا ۱۵ ژوئیه — هر کدام را جدا چک کنید.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>ردیف ۲۳ جدول اصلی</t>
+          <t>uni-passau.de؛ سایت دانشگاه‌ها</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ژوئیه ۲۰۲۷</t>
+          <t>می – ژوئن ۲۰۲۷</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه</t>
+          <t>💰 پول باید نقد و قابل انتقال باشد</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11822,52 +11903,133 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Twente/Radboud اتاق رزروشده برای بین‌المللی‌ها (مهلت‌دار)؛ Linköping یک پیشنهاد اتاق برای شهریه‌پردازها؛ آلمان لیست Studierendenwerk بلافاصله بعد از پذیرش؛ ایرلند/انگلستان خوابگاه دانشگاه زود پر می‌شود.</t>
+          <t>SDU: یک سال شهریه پیش‌پرداخت (€17,300)؛ سوئد: قسط ترم اول + تمکن SEK 10,656 × ماه‌ها؛ هلند: شهریه + €13,569 زندگی به حساب دانشگاه (Radboud تا ۱ ژوئن)؛ آلمان: حساب مسدود €11,904 (Fintiba ایران را نمی‌پذیرد → Expatrio/Coracle) + Stuttgart €1,500؛ سوئیس: CHF 21,000 برای سال اول (Basel 24,000) + شهریهٔ ترم اول (USI CHF 4,000؛ ETH/EPFL ≈ 2,240؛ بقیه ≈ 900–1,300) — در کانتون زوریخ فقط در بانک سوئیسی به نام خودتان یا با ضامن مقیم؛ انگلستان: ودیعه → CAS + £1,203 × ۹ ماه. انتقال از کشور ثالث/صرافی ۳–۶٪ هزینه.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>ردیف‌های ۹–۱۰ جدول اصلی</t>
+          <t>ردیف ۲۵ جدول اصلی</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>۱ ژوئن ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>مهلت ثبت‌نام/ویزای Radboud</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>هلند</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>برای شروع سپتامبر (غیر-EU)؛ درخواست MVV را دانشگاه از طرف شما به IND می‌دهد.</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>ru.nl deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ژوئن – ژوئیه ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>🛂 ویزا / برنامهٔ B</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>وضعیت تهران (سپتامبر ۲۰۲۶): آلمان حالت اضطراری، هلند از باکو، دانمارک «از ایران ممکن نیست»، انگلستان VFS متناوب؛ سوئد بدون بیومتریک (آنلاین)؛ سوئیس: سفارت تهران باز و ویزای D با وقت قبلی (تصمیم کانتون ۸–۱۲ هفته — پس درخواست را در می–ژوئن بدهید). یعنی برای DE/DK/UK سفر به ترکیه/ارمنستان/امارات را (۲–۶ هفته) در بودجه و تقویم بگذارید.</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>ردیف ۲۳ جدول اصلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ژوئیه ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Twente/Radboud اتاق رزروشده برای بین‌المللی‌ها (مهلت‌دار)؛ Linköping یک پیشنهاد اتاق برای شهریه‌پردازها؛ آلمان لیست Studierendenwerk بلافاصله بعد از پذیرش؛ انگلستان خوابگاه دانشگاه زود پر می‌شود؛ سوئیس: WOKO/Juwo زوریخ و FMEL لوزان لیست انتظار طولانی — روز پذیرش ثبت‌نام کنید؛ Lugano/Fribourg/Bern/Lucerne آسان‌تر.</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>ردیف‌های ۹–۱۰ جدول اصلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>اوت – اکتبر ۲۰۲۷</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>شروع</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>همه</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>سوئد ≈ ۳۰ اوت؛ دانمارک ۱ سپتامبر؛ هلند اوایل سپتامبر؛ ایرلند/انگلستان اواسط تا اواخر سپتامبر؛ آلمان ترم زمستان از ۱ اکتبر (کلاس‌ها ≈ اواسط اکتبر).</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>سوئد ≈ ۳۰ اوت؛ دانمارک ۱ سپتامبر؛ هلند اوایل سپتامبر؛ سوئیس اواسط سپتامبر (ETH ۲۰ سپتامبر؛ USI/HSLU هفتهٔ ۳۸)؛ انگلستان اواسط تا اواخر سپتامبر؛ آلمان ترم زمستان از ۱ اکتبر (کلاس‌ها ≈ اواسط اکتبر).</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>جمع‌بندی: ورودی سپتامبر ۲۰۲۷ شدنی است، فقط اگر (۱) IELTS تا دسامبر ۲۰۲۶ خارج از ایران گرفته شود، (۲) پول سال اول تا می ۲۰۲۷ نقد و قابل انتقال باشد، (۳) وضعیت نظام‌وظیفه/مجوز خروج روشن باشد. سوئد، دانمارک و Stuttgart با مهلت ۱۵ ژانویه سخت‌ترین‌اند؛ ایرلند، انگلستان، هلند و بیشتر آلمان تا بهار ۲۰۲۷ وقت دارند — اگر IELTS به ژانویه نرسید، تمرکز را روی این‌ها بگذارید. مهلت‌های علامت «≈» از منابع ثانویه‌اند؛ تاریخ دقیق را از صفحهٔ برنامه بگیرید.</t>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>جمع‌بندی: ورودی سپتامبر ۲۰۲۷ شدنی است، فقط اگر (۱) IELTS تا دسامبر ۲۰۲۶ خارج از ایران گرفته شود، (۲) پول سال اول تا می ۲۰۲۷ نقد و قابل انتقال باشد، (۳) وضعیت نظام‌وظیفه/مجوز خروج روشن باشد. ETH (۳۰ نوامبر)، سوئد، دانمارک و Stuttgart (۱۵ ژانویه) سخت‌ترین‌اند؛ سوئیسِ واقع‌بینانه (USI/Bern/Basel/ZHAW تا ۳۰ آوریل؛ UZH/Fribourg ۲۸ فوریه)، انگلستان، هلند و بیشتر آلمان تا بهار ۲۰۲۷ وقت دارند — اگر IELTS به ژانویه نرسید، تمرکز را روی این‌ها بگذارید. مهلت‌های علامت «≈» از منابع ثانویه‌اند؛ تاریخ دقیق را از صفحهٔ برنامه بگیرید.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11906,7 +12068,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>آلمان $27–36k  &lt;  ایرلند $32–48k  &lt;  انگلستان $38–65k  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k</t>
+          <t>آلمان $27–36k  &lt;  انگلستان $38–65k (۱ سال)  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k. سوئیس گسترده‌ترین بازه را دارد: $35–84k — Bern/Fribourg (۱.۵ سال) $35–47k کنار انگلستان، UZH $45–58k، HSLU $53–64k، USI/EPFL $60–75k، ETH $66–84k کنار هلند</t>
         </is>
       </c>
     </row>
@@ -11918,7 +12080,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ایرلند و انگلستان کامل؛ هلند و سوئد برای زندگی/کار خوب ولی برای اقامت دائم/تابعیت زبان می‌خواهند (هلند B1 در راه، سوئد آزمون تابعیت)؛ دانمارک و آلمان بدون زبان محلی هم بازار کار و هم PR محدود.</t>
+          <t>انگلستان کامل؛ هلند و سوئد برای زندگی/کار خوب ولی برای اقامت دائم/تابعیت زبان می‌خواهند (هلند B1 در راه، سوئد آزمون تابعیت)؛ سوئیس: تحصیل و Big Tech زوریخ انگلیسی، ولی اداری به زبان کانتون و PR/تابعیت با A2–B1 زبان محلی (۱۰ سال)؛ دانمارک و آلمان بدون زبان محلی هم بازار کار و هم PR محدود.</t>
         </is>
       </c>
     </row>
@@ -11930,7 +12092,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>حقوق ناخالص: دانمارک &gt; آلمان &gt; هلند ≈ سوئد &gt; ایرلند &gt; انگلستان. دسترسی برای جونیورِ فقط‌انگلیسی: ایرلند ≈ هلند &gt; آلمان &gt; سوئد ≈ دانمارک ≈ انگلستان.</t>
+          <t>حقوق ناخالص: سوئیس (CHF 85–105k) ≫ دانمارک &gt; آلمان &gt; هلند ≈ سوئد &gt; انگلستان. دسترسی برای جونیورِ فقط‌انگلیسی: هلند &gt; آلمان ≈ سوئیس (فقط شرکت‌های بزرگ، ۶ ماه فرصت) &gt; سوئد ≈ دانمارک ≈ انگلستان.</t>
         </is>
       </c>
     </row>
@@ -11942,7 +12104,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ایرلند ۲۵ › آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ › دانمارک ۱۶.  پیشنهاد: اپلای هم‌زمان به ۲–۳ برنامه ایرلند (UL، Maynooth، TU Dublin) + ۲ برنامه آلمان (Stuttgart + یک گزینه Safe مثل Passau/Saarland؛ FAU فقط اگر شهریهٔ جدید €8,000/سال را می‌پذیرید)؛ تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در بهار ۲۰۲۷.</t>
+          <t>آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ = سوئیس ۱۸ › دانمارک ۱۶.  با حذف ایرلند، هیچ کشوری هر سه معیار را با هم نمی‌دهد: آلمان ارزان‌ترین (ولی آلمانی)، انگلستان تنها گزینهٔ کاملاً انگلیسی (ولی گران و بازار جونیور ضعیف)، سوئیس بالاترین حقوق (ولی گران‌ترین زندگی، ۶ ماه فرصت کار، زبان محلی برای PR). پیشنهاد: ۲ برنامه آلمان (Stuttgart + Passau/Saarland) + ۲ برنامه سوئیس با شانس واقعی (USI Lugano + HSLU یا Bern/Fribourg) + ۱–۲ گزینهٔ ارزان انگلستان (Teesside/Northumbria) به‌عنوان مسیر تماماً انگلیسی؛ ETH/EPFL فقط اگر حاضرید CHF 150 را برای یک شانس کم خرج کنید. تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در بهار ۲۰۲۷.</t>
         </is>
       </c>
     </row>
@@ -11954,7 +12116,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>دسترسی به سفارت‌ها از داخل ایران (ردیف ۲۳): در سپتامبر ۲۰۲۶ هیچ‌کدام از ۶ کشور خدمات عادی ویزای دانشجویی در تهران ندارند. از الان هزینه «برنامه B» (اقدام از ترکیه/ارمنستان/امارات) را در بودجه ببینید.</t>
+          <t>دسترسی به سفارت‌ها از داخل ایران (ردیف ۲۳): در سپتامبر ۲۰۲۶ فقط سوئیس (ویزای D با وقت قبلی) و تا حدی سوئد (آنلاین) از تهران قابل اقدام‌اند؛ آلمان، هلند، دانمارک و انگلستان خدمات عادی ندارند. برای سوئیس گلوگاه به‌جای سفارت، اثبات تمکن CHF 21,000 در بانک سوئیسی (کانتون زوریخ) است. از الان هزینه «برنامه B» (اقدام از ترکیه/ارمنستان/امارات) را در بودجه ببینید.</t>
         </is>
       </c>
     </row>
@@ -11966,7 +12128,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>اکتبر ۲۰۲۶: نظام‌وظیفه + رزرو IELTS خارج از ایران + مدارک · ۱۶ اکتبر: باز شدن سوئد · نوامبر–دسامبر: IELTS + VPD uni-assist · ۱۵ ژانویه ۲۰۲۷: مهلت سوئد / AAU / Stuttgart · ۱ فوریه: مدارک سوئد + SDU · فوریه–مارس: ایرلند و انگلستان · ۱ آوریل: Radboud · ۱ می: Twente · ۳۱ می: Passau / TU Dublin · می–ژوئن: پول + ویزا یا برنامهٔ B · ۱ ژوئیه: UL · اوت–اکتبر: شروع.</t>
+          <t>اکتبر ۲۰۲۶: نظام‌وظیفه + رزرو IELTS خارج از ایران + مدارک · ۱۶ اکتبر: باز شدن سوئد · ۱–۳۰ نوامبر: پنجرهٔ ETH (Reach) · نوامبر–دسامبر: IELTS + VPD uni-assist · ۱۵ دسامبر: دور اول EPFL · ۱۵ ژانویه ۲۰۲۷: مهلت سوئد / AAU / Stuttgart · ۱ فوریه: مدارک سوئد + SDU · ۲۸ فوریه: UZH و Fribourg (ویزایی‌ها) · فوریه–مارس: انگلستان + پرونده‌های سوئیس · ۱ آوریل: Radboud · ۳۰ آوریل: USI / Bern / Basel / ZHAW · ۱ می: Twente · ۳۱ می: Passau · می–ژوئن: پول (سوئیس CHF 21,000 + شهریه) + ویزا یا برنامهٔ B · اوت–اکتبر: شروع (سوئیس اواسط سپتامبر).</t>
         </is>
       </c>
     </row>
@@ -11978,7 +12140,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>(۱) آزمون زبان: IELTS و TOEFL در ایران برگزار نمی‌شوند → سفر به ترکیه/ارمنستان/امارات/گرجستان تا دسامبر ۲۰۲۶. (۲) نظام‌وظیفه: بدون کارت/معافیت، خروج تحصیلی فقط با مجوز سخا + وثیقهٔ ۲۰۰ میلیون تومان + پذیرش از دانشگاه مورد تأیید وزارت علوم. (۳) نقدینگی: شهریه/تمکن سال اول باید تا می–ژوئن ۲۰۲۷ قابل انتقال باشد (SDU یک سال کامل پیش‌پرداخت). اگر یکی از این سه تا ژانویه ۲۰۲۷ حل نشود، هدف واقع‌بینانه ایرلند/انگلستان/هلند/آلمان با مهلت‌های بهار ۲۰۲۷ است — یا ورودی ۲۰۲۸.</t>
+          <t>(۱) آزمون زبان: IELTS و TOEFL در ایران برگزار نمی‌شوند → سفر به ترکیه/ارمنستان/امارات/گرجستان تا دسامبر ۲۰۲۶. (۲) نظام‌وظیفه: بدون کارت/معافیت، خروج تحصیلی فقط با مجوز سخا + وثیقهٔ ۲۰۰ میلیون تومان + پذیرش از دانشگاه مورد تأیید وزارت علوم. (۳) نقدینگی: شهریه/تمکن سال اول باید تا می–ژوئن ۲۰۲۷ قابل انتقال باشد (SDU یک سال کامل پیش‌پرداخت). اگر یکی از این سه تا ژانویه ۲۰۲۷ حل نشود، هدف واقع‌بینانه سوئیس (USI/Bern/Basel/ZHAW تا ۳۰ آوریل)، انگلستان، هلند و آلمان با مهلت‌های بهار ۲۰۲۷ است — یا ورودی ۲۰۲۸. برای سوئیس علاوه بر این سه، «ضامن مقیم یا حساب بانکی قابل قبول کانتون» پیش‌نیاز چهارم است.</t>
         </is>
       </c>
     </row>
@@ -11992,8 +12154,8 @@
         <is>
           <t>• هزینه کل دوره اضافه شد (هلند از «نیاز به تأمین سال دوم» به گران‌ترین گزینه تبدیل شد)
 • فقط انگلستان (به خواست شما): Strathclyde و Swansea حذف شدند؛ گزینه‌ها Teesside £17,000 · Northumbria £21,500 · Leicester £24,250 · Essex £24,675 · Brunel £24,795 · York £32,900؛ Graduate visa ۱۸ ماه؛ کف اسپانسری £54,700 / £38,290؛ طرح PR ۱۰ ساله؛ عوارض £925 از ۲۰۲۸ شامل همهٔ گزینه‌ها
-• کف حقوق ۲۰۲۶ همه کشورها به‌روز شد (آلمان €50,700/€45,934؛ هلند €3,122/ماه؛ سوئد SEK 34,470؛ ایرلند €40,904)
-• ایرلند: ۲ سال CSEP = Stamp 4 نه PR؛ تمکن €10,000
+• کف حقوق ۲۰۲۶ همه کشورها به‌روز شد (آلمان €50,700/€45,934؛ هلند €3,122/ماه؛ سوئد SEK 34,470)
+• ایرلند به خواست شما به‌کلی حذف و سوئیس جایگزین شد (سپتامبر ۲۰۲۶): شهریه‌های 2026/27 ETH/EPFL/UZH/USI/ZHAW/HSLU، تمکن CHF 21,000، ۶ ماه جست‌وجوی کار، سهمیهٔ غیر-EU، اجازهٔ C ۱۰ ساله، حقوق جونیور CHF 85–105k، سفارت تهران (ویزای D فعال)
 • سوئد: کار دانشجویی ۱۵ ساعت/هفته (ژوئن ۲۰۲۶)؛ شهروندی ۸ سال؛ «BTH یک‌ساله» حذف شد؛ خوابگاه فقط LiU
 • QS 2027؛ شهریه‌های واقعی 2026/27؛ «۷۵٪ قبولی» حذف شد
 • «۱۰۰٪ انگلیسی» برای هلند/سوئد/دانمارک تعدیل شد؛ دانمارک PD2/PD3 تفکیک شد
@@ -12033,7 +12195,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>مبالغ سطح 2026/27 هستند؛ نرخ 2027/28 (سال ورود شما) بین اکتبر ۲۰۲۶ تا بهار ۲۰۲۷ منتشر می‌شود — جایی که رسمی بود (TU/e €22,400، Surrey £26,900، Gothenburg SEK 294k کل) در جدول آمده؛ برای بقیه فعلاً ۳–۵٪ اضافه کنید. نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55</t>
+          <t>مبالغ سطح 2026/27 هستند؛ نرخ 2027/28 (سال ورود شما) بین اکتبر ۲۰۲۶ تا بهار ۲۰۲۷ منتشر می‌شود — جایی که رسمی بود (TU/e €22,400، Surrey £26,900، Gothenburg SEK 294k کل) در جدول آمده؛ برای بقیه فعلاً ۳–۵٪ اضافه کنید. نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21</t>
         </is>
       </c>
     </row>
@@ -12048,7 +12210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B134"/>
+  <dimension ref="A1:B150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12538,1128 +12700,1320 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – کف حقوق مجوز کار از ۱ مارس ۲۰۲۶ (€40,904 / €36,848 / €36,605)</t>
+          <t>سوئیس – ETH: تاریخ‌های اپلای ارشد پاییز ۲۰۲۷ (۱–۳۰ نوامبر ۲۰۲۶؛ پاسخ تا پایان مارس؛ شروع ۲۰ سپتامبر ۲۰۲۷)</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>https://kodlyons.ie/critical-skills-employment-permit-changes/</t>
+          <t>https://ethz.ch/en/studies/master/application/dates.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – نقشه راه DETE تا ۲۰۳۰</t>
+          <t>سوئیس – EPFL: شهریه CHF 2,240/ترم برای خارجی‌های غیرمقیم از پاییز ۲۰۲۵ (CHF 780 برای بقیه)</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>https://www.visahq.com/news/2025-12-12/ie/ireland-sets-phased-salary-threshold-hikes-for-all-work-permit-categories-first-rise-due-1-march-2026/</t>
+          <t>https://www.epfl.ch/education/studies/en/rules-and-procedures/study-taxes/tuition-fee-other-fees/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – ISD تمکن دانشجویی €10,000</t>
+          <t>سوئیس – EPFL: پنجره‌های اپلای ارشد (۱۵ دسامبر / ۳۱ مارس؛ یک برنامه در سال)</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>https://www.irishimmigration.ie/coming-to-study-in-ireland/what-are-my-study-options/a-fee-paying-private-primary-or-secondary-school/information-on-student-finances/</t>
+          <t>https://www.epfl.ch/education/admission/admission-2/master-admission-criteria-application/online-application/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – UL MSc Software Engineering €20,800</t>
+          <t>سوئیس – UZH: شهریه CHF 720 + 100 (خارجی، ارشد) + 59؛ هزینهٔ درخواست CHF 150</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>https://www.ul.ie/study/postgraduate/software-engineering-msc</t>
+          <t>https://www.uzh.ch/en/studies/application/fees.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – Maynooth فهرست شهریه 2025/26</t>
+          <t>سوئیس – UZH: مهلت ویزایی‌ها ۲۸ فوریه / بدون ویزا ۳۰ آوریل (پاییز)</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>https://www.maynoothuniversity.ie/sites/default/files/assets/document/2025.26%20Postgraduate%20EU%20&amp;%20International%20Fees%20List%20(24.02.25)%20V.4%20CHR.pdf</t>
+          <t>https://www.oec.uzh.ch/en/studies/general/admission/master/faq-master-admission.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – سفارت/کنسول افتخاری تهران</t>
+          <t>سوئیس – USI MSc Informatics: CHF 4,000/ترم غیرمقیم، B2 در ورود → C1، مهلت غیر-EU ۳۰ آوریل</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>https://www.ireland.ie/en/tehran/</t>
+          <t>https://www.usi.ch/en/education/master/informatics</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – QS 2027 دانشگاه‌های ایرلند</t>
+          <t>سوئیس – USI MSc Artificial Intelligence: CHF 4,000/ترم، IELTS 6.5</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>https://www.thejournal.ie/irish-universities-qs-world-university-rankings-2027-7073948-Jun2026/</t>
+          <t>https://www.topuniversities.com/universities/usi-universita-della-svizzera-italiana/postgrad/master-science-artificial-intelligence</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
+          <t>سوئیس – swissuniversities: شهریهٔ دانشگاه‌های علوم کاربردی 2026–27 (ZHAW 1,220؛ HSLU 1,300؛ OST 1,500؛ FHNW 1,000–5,000)</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
+          <t>https://www.swissuniversities.ch/en/themen/lehre-studium/information-on-studies/tuition-fees/tuition-fees-at-uas</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
+          <t>سوئیس – ZHAW MSE: انگلیسی، 90 ECTS، پروفایل‌های CS/Data Science/Cyber، معدل A/B، مهلت پایان آوریل</t>
         </is>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
+          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
+          <t>سوئیس – HSLU MSc Applied Information &amp; Data Science: C1 (B2 مشروط)، آلمانی لازم نیست، هر کارشناسی</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/haeufig-gestellte-fragen/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
+          <t>سوئیس – Bern: Swiss Joint MSc Computer Science (90 ECTS، انگلیسی، شرط کارشناسی CS)</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
+          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
+          <t>سوئیس – Bern شهریه CHF 750 + 200 خارجی (≈)؛ Fribourg CHF 870 + 115، مهلت ویزایی ۲۸ فوریه (≈)</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
+          <t>https://www.mastersportal.com/studies/12191/computer-science.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
+          <t>سوئیس – Bern: مهلت ۳۰ آوریل؛ ویزایی‌ها از مهلت دیرهنگام محروم‌اند (راهنمای ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
+          <t>https://www.libertify.com/universities/university-of-bern-international-admissions-guide/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
+          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
+          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
+          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
+          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
+          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
+          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
+          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
+          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
+          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
+          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
+          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
+          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – وضعیت VAC تهران</t>
+          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
+          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – TU Dresden</t>
+          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
+          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Stuttgart</t>
+          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
+          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Newcastle 149</t>
+          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
+          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – York =158</t>
+          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/about/rankings/</t>
+          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Leicester =314</t>
+          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/university-leicester</t>
+          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Essex =438</t>
+          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/essex-university</t>
+          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Northumbria =528</t>
+          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
+          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Brunel</t>
+          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
+          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – سایر</t>
+          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/world-university-rankings</t>
+          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
+          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
+          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
         </is>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>https://www.xe.com/</t>
+          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
+          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
+          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
+          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
+          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
+          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>https://www.isc2.org/research</t>
+          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
+          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
+          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
+          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
+          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
         </is>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – UL MSc AI &amp; ML: €20,800</t>
+          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>https://www.ul.ie/study/postgraduate/artificial-intelligence-and-machine-learning-msc</t>
+          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – TU Dublin MSc Applied Cyber Security: €14,500، 2:2</t>
+          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
         </is>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>https://www.tudublin.ie/study/postgraduate/courses/applied-cyber-security/</t>
+          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – TU Dublin MSc CS (Data Science): €21,750، 2:2 + ۲ سال سابقه</t>
+          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
         </is>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>https://www.tudublin.ie/study/postgraduate/courses/computing-data-science/</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – DCU MSc Computing majors: €25,000، 2:1، بورس €5,000</t>
+          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
         </is>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>https://www.dcu.ie/courses/postgraduate/school-computing/msc-computing-major-options</t>
+          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – Galway MSc CS (AI) €28,000 / SDD €18,440، 2026/27</t>
+          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>http://cs.universityofgalway.ie/science-engineering/postgraduateprogrammes/taught-postgraduate-courses/software-design-development.html</t>
+          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
+          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
         </is>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
+          <t>بریتانیا – وضعیت VAC تهران</t>
         </is>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
+          <t>QS WUR 2027 – TU Dresden</t>
         </is>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Siegen MSc HCI (DAAD)</t>
+          <t>QS WUR 2027 – Stuttgart</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
+          <t>QS WUR 2027 – Newcastle 149</t>
         </is>
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>آلمان – RWTH MSc Software Systems Engineering</t>
+          <t>QS WUR 2027 – York =158</t>
         </is>
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+          <t>https://www.york.ac.uk/about/rankings/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
+          <t>QS WUR 2027 – Leicester =314</t>
         </is>
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+          <t>https://www.topuniversities.com/universities/university-leicester</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
+          <t>QS WUR 2027 – Essex =438</t>
         </is>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+          <t>https://www.topuniversities.com/universities/essex-university</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
+          <t>QS WUR 2027 – Northumbria =528</t>
         </is>
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
+          <t>QS WUR 2027 – Brunel</t>
         </is>
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>هلند – Leiden CS 2026/27: €22,500</t>
+          <t>QS WUR 2027 – سایر</t>
         </is>
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+          <t>https://www.topuniversities.com/world-university-rankings</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>هلند – Groningen AI 2026/27: €24,900</t>
+          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
         </is>
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
+          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+          <t>https://www.xe.com/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
+          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
         </is>
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
+          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
+          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
         </is>
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
+          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
         </is>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+          <t>https://www.isc2.org/research</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Umeå AI: SEK 152,300</t>
+          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
         </is>
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
+          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
         </is>
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>https://www.study.eu/best-universities/sweden</t>
+          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
+          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
         </is>
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
+          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
         </is>
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
+          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
         </is>
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus CS €17,300</t>
+          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
         </is>
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>https://masters.au.dk/computerscience</t>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
+          <t>آلمان – Siegen MSc HCI (DAAD)</t>
         </is>
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
+          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
         </is>
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
+          <t>آلمان – RWTH MSc Software Systems Engineering</t>
         </is>
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
+          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
         </is>
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
+          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
         </is>
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
+          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
         </is>
       </c>
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
+          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
         </is>
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – NTU QS 2027 =639</t>
+          <t>هلند – Leiden CS 2026/27: €22,500</t>
         </is>
       </c>
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
+          <t>هلند – Groningen AI 2026/27: €24,900</t>
         </is>
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
+          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
         </is>
       </c>
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
+          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
         </is>
       </c>
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
+          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
+          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
         </is>
       </c>
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
+          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
         </is>
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
+          <t>سوئد – Umeå AI: SEK 152,300</t>
         </is>
       </c>
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
+          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
         </is>
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+          <t>https://www.study.eu/best-universities/sweden</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
         </is>
       </c>
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
         </is>
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
         </is>
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+          <t>دانمارک – Aarhus CS €17,300</t>
         </is>
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>https://zandienglish.ir/toefl-in-iran/</t>
+          <t>https://masters.au.dk/computerscience</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
         </is>
       </c>
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
         </is>
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
         </is>
       </c>
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
         </is>
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
         </is>
       </c>
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
         </is>
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
         </is>
       </c>
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>هلند – Twente: مهلت غیر-EEA ۱ می ۲۰۲۷؛ بورس UTS ۱۵ اکتبر ۲۰۲۶ – ۱ آوریل ۲۰۲۷</t>
+          <t>انگلستان – NTU QS 2027 =639</t>
         </is>
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/netherlands/university/749-university-of-twente-enschede/admission</t>
+          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – UL: مهلت غیر-EU ویزایی ۱ ژوئیه؛ اپلای از ۱۵ اکتبر</t>
+          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
         </is>
       </c>
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>https://www.ul.ie/gps/applications-faq</t>
+          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – Maynooth: باز شدن اپلای ۲۰۲۷ در ۱۴ اکتبر ۲۰۲۶؛ ودیعهٔ غیر-EU €1,000</t>
+          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
         </is>
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>https://www.maynoothuniversity.ie/study-maynooth/how-apply/postgraduate-applicants</t>
+          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>ایرلند – مهلت‌های تقریبی TU Dublin (۳۱ می) و Maynooth (۱۵ می) برای غیر-EU</t>
+          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
         </is>
       </c>
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>https://studyinireland.app/apply/deadlines</t>
+          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>https://zandienglish.ir/toefl-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="inlineStr">
+        <is>
+          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Twente: مهلت غیر-EEA ۱ می ۲۰۲۷؛ بورس UTS ۱۵ اکتبر ۲۰۲۶ – ۱ آوریل ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/netherlands/university/749-university-of-twente-enschede/admission</t>
         </is>
       </c>
     </row>
@@ -13798,6 +14152,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -15,7 +15,7 @@
     <sheet name="منابع" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -642,8 +642,8 @@
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>USI (Lugano) – MSc Informatics / MSc Artificial Intelligence / MSc Software &amp; Data Engineering (انگلیسی؛ ورود با B2) → Target
-HSLU (Lucerne) – MSc Applied Information and Data Science (انگلیسی؛ C1 یا B2 مشروط؛ بدون آلمانی) → Safe/Target
-Bern یا Fribourg – Swiss Joint MSc Computer Science (90 ECTS، انگلیسی) → Target
+HSLU (Lucerne) – MSc Applied Data Science and AI (انگلیسی؛ C1 یا B2 مشروط؛ بدون آلمانی؛ مهلت ویزایی‌ها ۱ آوریل) → Safe/Target
+Neuchâtel یا Fribourg (Bern همان مدرک با شهریهٔ ۳ برابر) – Swiss Joint MSc Computer Science (90 ECTS، انگلیسی، بدون آزمون زبان) → Target
 ZHAW (Zürich/Winterthur) – MSE Computer Science / Data Science / Cyber Security (فقط با معدل A/B کارشناسی) → Target/Reach
 ETH Zürich، EPFL، UZH، Basel → Reach (با معدل ۱۵.۷۷ احتمال پذیرش کم)</t>
         </is>
@@ -746,7 +746,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>۱.۵ سال (90 ECTS: Bern/Fribourg/UZH/Basel/ZHAW) یا ۲ سال (120 ECTS: ETH، EPFL، USI، HSLU)</t>
+          <t>۱.۵ سال (90 ECTS: Neuchâtel/Fribourg/Bern/UZH/Basel/ZHAW) یا ۲ سال (120 ECTS: ETH، EPFL، USI، HSLU)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -803,7 +803,8 @@
 USI: CHF 4,000 (= CHF 8,000/سال)
 ETH: CHF 2,190 + ≈ 74 (≈ CHF 4,530/سال) · EPFL: CHF 2,240 (≈ CHF 4,480/سال)
 HSLU: CHF 1,300 + ≈ 275 (≈ CHF 3,150/سال) · ZHAW: CHF 1,220 + 60 (≈ CHF 2,560/سال)
-Bern: CHF 950 (CHF 1,900/سال) · Fribourg: CHF 870 + 115 (≈ CHF 1,970/سال) · UZH: CHF 879 (≈ CHF 1,760/سال) · Basel: ≈ CHF 850–1,050
+Neuchâtel: CHF 790 (CHF 1,580/سال) · Basel: CHF 850 (CHF 1,700/سال) · UZH: CHF 879 (≈ CHF 1,760/سال) · Fribourg: CHF 870 + 115 = 985 (CHF 1,970/سال)
+⚠️ Bern از پاییز ۲۰۲۶: CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها + 59 = CHF 2,609 (≈ CHF 5,200/سال) — همان مدرک مشترک را از Neuchâtel/Fribourg بگیرید
 ⚠️ ETH/EPFL: افزایش دوباره (تا ≈ CHF 5,840/ترم برای خارجی‌ها) در بستهٔ صرفه‌جویی EP27 مطرح است؛ تصمیم شورای ETH برای ۲۰۲۷ هنوز اعلام نشده</t>
         </is>
       </c>
@@ -857,7 +858,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>$2,100–2,400 (Bern/UZH/Fribourg) · ≈ $3,100–3,800 (ZHAW/HSLU) · ≈ $5,400–5,500 (ETH/EPFL) · $9,700 (USI) — ارزان‌ترین بعد از آلمان</t>
+          <t>$1,900–2,400 (Neuchâtel/Basel/UZH/Fribourg) · ≈ $3,100–3,800 (ZHAW/HSLU) · ≈ $5,400–5,500 (ETH/EPFL) · ≈ $6,300 (Bern، از پاییز ۲۰۲۶) · $9,700 (USI) — ارزان‌ترین بعد از آلمان</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -909,7 +910,7 @@
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Zürich: CHF 1,900–2,500 (≈ $2,300–3,000؛ اتاق WOKO CHF 500–900، اتاق خصوصی 800–1,200) · Lausanne: CHF 1,700–2,200
-Bern/Basel/Lucerne: CHF 1,550–2,100 · Lugano/Fribourg: CHF 1,400–1,800
+Bern/Basel/Lucerne: CHF 1,550–2,100 · Lugano/Fribourg/Neuchâtel: CHF 1,350–1,800
 حداقل رسمی: CHF 21,000 در سال (Basel: 24,000)؛ کانتون زوریخ فقط حساب بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم سوئیس را می‌پذیرد</t>
         </is>
       </c>
@@ -960,7 +961,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>$23,000–42,000 (Bern/Fribourg $23–31k · Lucerne $26–32k · Lugano/Lausanne $30–37k · Zürich $30–42k)</t>
+          <t>$23,000–42,000 (Neuchâtel/Fribourg $23–31k · Lucerne $26–32k · Bern $27–35k · Lugano/Lausanne $30–37k · Zürich $30–42k)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1007,7 +1008,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>$35,000–84,000 (Bern/Fribourg ۱.۵ سال $35–47k · UZH $45–58k · HSLU $53–64k · USI/EPFL $60–75k · ETH $66–84k) — بعد از هلند گران‌ترین؛ شهریه ناچیز است، هزینهٔ زندگی همه‌چیز را تعیین می‌کند</t>
+          <t>$35,000–84,000 (Neuchâtel/Fribourg ۱.۵ سال $35–47k · Bern $39–51k · UZH $45–58k · HSLU $53–64k · USI/EPFL $60–75k · ETH $66–84k) — بعد از هلند گران‌ترین؛ شهریه ناچیز است، هزینهٔ زندگی همه‌چیز را تعیین می‌کند</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1054,7 +1055,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ فقط Bern/Fribourg (و با صرفه‌جویی Lucerne/Lugano) در بودجه؛ Zürich/Lausanne کسری $1,000–10,000 در سال؛ کار دانشجویی در ۶ ماه اول ممنوع → سال اول تماماً از جیب</t>
+          <t>⚠️ فقط Neuchâtel/Fribourg (و با صرفه‌جویی Lucerne/Lugano) در بودجه؛ Zürich/Lausanne کسری $1,000–10,000 در سال؛ کار دانشجویی در ۶ ماه اول ممنوع → سال اول تماماً از جیب</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1101,7 +1102,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Zürich بحرانی: WOKO/Juwo (CHF 500–900) لیست انتظار ۳–۱۲ ماه، بازار خصوصی بسیار رقابتی؛ Lausanne خوابگاه‌های FMEL (زود پر می‌شود)؛ Lugano/Fribourg/Bern/Lucerne آسان‌تر و ارزان‌تر (CHF 500–800). روز دریافت پذیرش ثبت‌نام کنید.</t>
+          <t>Zürich بحرانی: WOKO/Juwo (CHF 500–900) لیست انتظار ۳–۱۲ ماه، بازار خصوصی بسیار رقابتی؛ Lausanne خوابگاه‌های FMEL (زود پر می‌شود)؛ Lugano/Fribourg/Neuchâtel/Bern/Lucerne آسان‌تر و ارزان‌تر (CHF 500–800). روز دریافت پذیرش ثبت‌نام کنید.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1767,7 +1768,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>USI: B2 در ورود (IELTS 5.5–6.5) و C1 تا فارغ‌التحصیلی · HSLU: C1 (B2 مشروط) · Bern/Fribourg: «انگلیسی خیلی خوب» (معمولاً 6.5) · ZHAW: B2–C1 · UZH و ETH: C1 / IELTS 7.0 · EPFL: مدرک زبان الزامی نیست</t>
+          <t>USI: B2 در ورود (IELTS 5.5–6.5) و C1 تا فارغ‌التحصیلی · HSLU: C1 (B2 مشروط) · Joint MSc CS (Neuchâtel/Fribourg/Bern): بدون آزمون زبان — B2 توصیه (FAQ رسمی) · ZHAW: B2–C1 · UZH و ETH: C1 / IELTS 7.0 · EPFL: مدرک زبان الزامی نیست</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1814,7 +1815,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>CHF 21,000 برای هر سال (Basel 24,000) + شهریه؛ برای هر تمدید سالانه دوباره. زوریخ: فقط حساب بانک سوئیسی/شعبهٔ سوئیسی به نام خودتان (حساب والدین پذیرفته نیست) یا ضامن مقیم سوئیس (B/C)؛ بانک‌های سوئیس برای ساکنان ایران حساب باز نمی‌کنند → عملاً از تهران فقط با ضامن، یا کانتون‌های انعطاف‌پذیرتر (تیچینو، فریبورگ، برن، لوسرن — قبل از اقدام از دفتر بین‌الملل دانشگاه تأیید بگیرید). انتقال پول فقط از مسیر کشور ثالث.</t>
+          <t>CHF 21,000 برای هر سال (Basel 24,000) + شهریه؛ برای هر تمدید سالانه دوباره. زوریخ: فقط حساب بانک سوئیسی/شعبهٔ سوئیسی به نام خودتان (حساب والدین پذیرفته نیست) یا ضامن مقیم سوئیس (B/C)؛ بانک‌های سوئیس برای ساکنان ایران حساب باز نمی‌کنند → عملاً از تهران فقط با ضامن، یا کانتون‌های انعطاف‌پذیرتر (تیچینو، فریبورگ، نوشاتل، برن، لوسرن — قبل از اقدام از دفتر بین‌الملل دانشگاه تأیید بگیرید). انتقال پول فقط از مسیر کشور ثالث.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2008,7 +2009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q111"/>
+  <dimension ref="A1:Q112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4498,7 +4499,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>MSc Applied Information and Data Science</t>
+          <t>MSc Applied Data Science and AI (نام جدید از اوت ۲۰۲۶؛ قبلاً Applied Information and Data Science)</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -4508,12 +4509,12 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۲ سال (120 ECTS؛ معمولاً ۴ ترم، قابل تمدید تا ۸)</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>CHF 1,300 در ترم (خارجی) + ≈ CHF 275 هزینهٔ جانبی ≈ CHF 3,150/سال</t>
+          <t>CHF 1,300 در ترم (خارجی) + ≈ CHF 275 هزینهٔ جانبی ≈ CHF 3,150/سال؛ هزینهٔ درخواست CHF 250</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -4523,7 +4524,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>هر کارشناسی ۱۸۰ ECTS؛ خوداظهاری + آزمون انگلیسی HSLU + مصاحبه در صورت نیاز</t>
+          <t>هر کارشناسی (دانشگاه یا UAS)؛ آزمون انگلیسی + آزمون استعداد HSLU</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -4548,12 +4549,12 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>«باز برای تغییر رشته‌ای‌ها»، کاربردی و مدیریتی؛ آلمانی لازم نیست؛ شروع سپتامبر/فوریه؛ مهلت ≈ ۳۰ آوریل (چک شود)</t>
+          <t>«باز برای تغییر رشته‌ای‌ها»، کاربردی و مدیریتی؛ ترکیبی (حضوری/آنلاین)؛ آلمانی لازم نیست؛ شروع سپتامبر/فوریه؛ ⚠️ مهلت ویزایی‌ها ۱ آوریل ۲۰۲۷ (رسمی؛ Swiss/EU تا ۱ ژوئن)</t>
         </is>
       </c>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
         </is>
       </c>
     </row>
@@ -4598,22 +4599,22 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>CHF 750 + 200 (خارجی) = CHF 950 در ترم (CHF 1,900/سال)</t>
+          <t>CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها (از پاییز ۲۰۲۶) + 34 + 25 = CHF 2,609 در ترم (≈ CHF 5,200/سال)</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>$2,300</t>
+          <t>$6,300</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی Computer Science (یا معادل با حداکثر ۶۰ ECTS تکمیلی)؛ تأیید ادارهٔ پذیرش برای مدرک خارجی</t>
+          <t>کارشناسی Computer Science یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی — دروس تکمیلی ممکن است آلمانی/فرانسه باشند)</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>معمولاً 6.5 (C1 توصیه)</t>
+          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
         </is>
       </c>
       <c r="M31" s="4">
@@ -4632,7 +4633,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌ترین مسیر سوئیس با رتبهٔ زیر ۲۰۰؛ مهلت ۳۰ آوریل — ویزایی‌ها مهلت دیرهنگام ندارند؛ شهریه از mastersportal (≈)</t>
+          <t>⚠️ شهریهٔ خارجی‌ها از پاییز ۲۰۲۶ سه‌برابر شد (رسمی unibe.ch) → همان مدرک مشترک را از Neuchâtel (CHF 790/ترم) یا Fribourg (CHF 985/ترم) بگیرید؛ مهلت ۳۰ آوریل — ویزایی‌ها مهلت دیرهنگام ندارند</t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
@@ -4652,22 +4653,22 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>University of Fribourg</t>
+          <t>University of Neuchâtel</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Fribourg (فریبورگ) — دوزبانه (آلمانی/فرانسه)</t>
+          <t>Neuchâtel (نوشاتل) — فرانسه‌زبان؛ کنار دریاچه؛ ۳۵ دقیقه تا برن</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,450–1,800</t>
+          <t>متوسط تا گران — CHF 1,350–1,750</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Swiss Joint MSc Computer Science (ثبت‌نام در Fribourg)</t>
+          <t>Swiss Joint MSc Computer Science (ثبت‌نام در Neuchâtel)</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -4682,27 +4683,28 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>CHF 870 در ترم (خارجی) + CHF 115 = ≈ CHF 1,970/سال</t>
+          <t>CHF 790 در ترم (خارجی؛ شامل همهٔ هزینه‌ها) = CHF 1,580/سال</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>$2,400</t>
+          <t>$1,900</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط</t>
+          <t>کارشناسی CS یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی)</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>معمولاً 6.5</t>
-        </is>
-      </c>
-      <c r="M32" s="4">
-        <f>670</f>
-        <v/>
+          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
@@ -4716,12 +4718,12 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>همان برنامهٔ مشترک Bern؛ شهر دوزبانه و ارزان‌تر؛ ⚠️ مهلت ویزایی‌ها ۲۸ فوریه ۲۰۲۷</t>
+          <t>ارزان‌ترین شهریهٔ سوئیس؛ همان مدرک مشترک Bern/Fribourg (دروس در سه شهر، بلیت قطار جبران می‌شود)؛ مهلت ۳۰ آوریل (خارجی‌ها: تا ۳۱ مارس بفرستید)؛ هزینهٔ پرونده CHF 100 از شهریه کم می‌شود؛ شهر فرانسه‌زبان</t>
         </is>
       </c>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>https://www.unifr.ch/inf/en/</t>
+          <t>https://mcs.unibnf.ch/</t>
         </is>
       </c>
     </row>
@@ -4736,22 +4738,22 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>University of Basel</t>
+          <t>University of Fribourg</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Basel (بازل) — Roche، Novartis؛ مرز آلمان/فرانسه</t>
+          <t>Fribourg (فریبورگ) — دوزبانه (آلمانی/فرانسه)</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,600–2,100</t>
+          <t>گران — CHF 1,450–1,800</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>Swiss Joint MSc Computer Science (ثبت‌نام در Fribourg)</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -4766,31 +4768,31 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>≈ CHF 850 در ترم (+ هزینهٔ احتمالی خارجی‌ها؛ صفحهٔ رسمی چک شود) ≈ CHF 1,700–2,100/سال</t>
+          <t>CHF 870 + 115 = CHF 985 در ترم (خارجی؛ رسمی) = CHF 1,970/سال</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>$2,100–2,500</t>
+          <t>$2,400</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با نمرات خوب؛ بررسی فردی</t>
+          <t>کارشناسی CS یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی)</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>B2–C1 (چک شود)</t>
+          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
         </is>
       </c>
       <c r="M33" s="4">
-        <f>150</f>
+        <f>670</f>
         <v/>
       </c>
-      <c r="N33" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -4800,12 +4802,12 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>رتبهٔ ۱۵۰؛ ⚠️ کانتون Basel تمکن CHF 24,000/سال می‌خواهد؛ مهلت ۳۰ آوریل</t>
+          <t>همان برنامهٔ مشترک Bern/Neuchâtel؛ شهر دوزبانه و ارزان‌تر؛ ⚠️ مهلت ویزایی‌ها ۱–۲۸ فوریه ۲۰۲۷ (رسمی unifr.ch)</t>
         </is>
       </c>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>https://www.unibas.ch/en/Studies/Degree-Programs.html</t>
+          <t>https://www.unifr.ch/inf/en/</t>
         </is>
       </c>
     </row>
@@ -4820,22 +4822,22 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>University of Zurich (UZH)</t>
+          <t>University of Basel</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
+          <t>Basel (بازل) — Roche، Novartis؛ مرز آلمان/فرانسه</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,900–2,500</t>
+          <t>گران — CHF 1,600–2,100</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>MSc Informatics (گرایش‌ها: Software Systems، Data Science، People-Oriented Computing…)</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -4845,12 +4847,12 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>۱.۵–۲ سال (90/120 ECTS)</t>
+          <t>۱.۵ سال (90 ECTS)</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>CHF 720 + 100 (خارجی) + 59 = CHF 879 در ترم (≈ CHF 1,760/سال)</t>
+          <t>CHF 850 در ترم (برای همه؛ بدون اضافهٔ خارجی‌ها — رسمی 2026/27) = CHF 1,700/سال</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -4860,21 +4862,21 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی Informatics/CS با نمرات بسیار خوب؛ فقط یک درخواست در هر ترم؛ هزینهٔ درخواست CHF 150</t>
+          <t>کارشناسی CS یا معادل با نمرات خوب؛ بررسی فردی</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>C1 / IELTS 7.0</t>
+          <t>B2–C1 (چک شود)</t>
         </is>
       </c>
       <c r="M34" s="4">
-        <f>98</f>
+        <f>150</f>
         <v/>
       </c>
-      <c r="N34" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="N34" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -4884,12 +4886,12 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>⚠️ مهلت ویزایی‌ها ۲۸ فوریه ۲۰۲۷ (بدون ویزا ۳۰ آوریل)؛ کانتون زوریخ: تمکن CHF 21,000 فقط در بانک سوئیسی به نام خودتان</t>
+          <t>رتبهٔ ۱۵۰؛ 90 ECTS انگلیسی؛ هزینهٔ درخواست CHF 100؛ ⚠️ کانتون Basel تمکن CHF 24,000/سال می‌خواهد؛ مهلت ۳۰ آوریل (رسمی)</t>
         </is>
       </c>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>https://www.ifi.uzh.ch/en/studies/master.html</t>
+          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
         </is>
       </c>
     </row>
@@ -4904,77 +4906,76 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ZHAW School of Engineering</t>
+          <t>University of Zurich (UZH)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Zürich / Winterthur (زوریخ / وینترتور؛ کمپوس‌های ZHAW)</t>
+          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,800–2,400</t>
+          <t>خیلی گران — CHF 1,900–2,500</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>MSc in Engineering (MSE) — پروفایل Computer Science / Data Science / Information &amp; Cyber Security</t>
+          <t>MSc Informatics (گرایش‌ها: Software Systems، Data Science، People-Oriented Computing…)</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>چندحوزه‌ای (انتخاب گرایش)</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>۱.۵ سال (90 ECTS؛ پاره‌وقت تا ۳ سال)</t>
+          <t>۱.۵–۲ سال (90/120 ECTS)</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>CHF 1,220 در ترم (خارجی) + CHF 60 ≈ CHF 2,560/سال</t>
+          <t>CHF 720 + 100 (خارجی) + 59 = CHF 879 در ترم (≈ CHF 1,760/سال)</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>$3,100</t>
+          <t>$2,100</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی با نمرات A یا B (≈ یک‌سوم بالای کلاس) — گواهی رتبهٔ کلاسی از سمنان بگیرید</t>
+          <t>کارشناسی Informatics/CS با نمرات بسیار خوب؛ فقط یک درخواست در هر ترم؛ هزینهٔ درخواست CHF 150</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>B2–C1</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>851–900</t>
-        </is>
-      </c>
-      <c r="N35" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>C1 / IELTS 7.0</t>
+        </is>
+      </c>
+      <c r="M35" s="4">
+        <f>98</f>
+        <v/>
+      </c>
+      <c r="N35" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>کاربردی و پروژه‌محور (کار در مؤسسات ZHAW، اغلب با حقوق دستیاری)؛ مهلت پایان آوریل؛ کانتون زوریخ (تمکن در بانک سوئیسی)</t>
+          <t>⚠️ مهلت ویزایی‌ها ۲۸ فوریه ۲۰۲۷ (بدون ویزا ۳۰ آوریل)؛ کانتون زوریخ: تمکن CHF 21,000 فقط در بانک سوئیسی به نام خودتان</t>
         </is>
       </c>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
+          <t>https://www.ifi.uzh.ch/en/studies/master.html</t>
         </is>
       </c>
     </row>
@@ -4989,76 +4990,77 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>EPFL</t>
+          <t>ZHAW School of Engineering</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Lausanne (لوزان) — کنار دریاچهٔ ژنو؛ فرانسه‌زبان؛ EPFL</t>
+          <t>Zürich / Winterthur (زوریخ / وینترتور؛ کمپوس‌های ZHAW)</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,700–2,200</t>
+          <t>خیلی گران — CHF 1,800–2,400</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc in Engineering (MSE) — پروفایل Computer Science / Data Science / Information &amp; Cyber Security</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>چندحوزه‌ای (انتخاب گرایش)</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۱.۵ سال (90 ECTS؛ پاره‌وقت تا ۳ سال)</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>CHF 2,240 در ترم برای خارجی‌های غیرمقیم (از پاییز ۲۰۲۵؛ ≈ CHF 4,480/سال)</t>
+          <t>CHF 1,220 در ترم (خارجی) + CHF 60 ≈ CHF 2,560/سال</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>$5,400</t>
+          <t>$3,100</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با نمرات عالی (بالای کلاس)؛ فقط یک برنامه در سال</t>
+          <t>کارشناسی با نمرات A یا B (≈ یک‌سوم بالای کلاس) — گواهی رتبهٔ کلاسی از سمنان بگیرید</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>مدرک زبان الزامی نیست (C1 عملاً لازم)</t>
-        </is>
-      </c>
-      <c r="M36" s="4">
-        <f>22</f>
-        <v/>
-      </c>
-      <c r="N36" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>B2–C1</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>851–900</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>دور اول ۱۵ دسامبر ۲۰۲۶ (توصیه برای ویزایی‌ها؛ پاسخ اوایل آوریل)، دور دوم ۳۱ مارس ۲۰۲۷؛ ⚠️ احتمال افزایش دوبارهٔ شهریه (EP27)</t>
+          <t>کاربردی و پروژه‌محور (کار در مؤسسات ZHAW، اغلب با حقوق دستیاری)؛ مهلت پایان آوریل؛ کانتون زوریخ (تمکن در بانک سوئیسی)</t>
         </is>
       </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/education/master/programs/computer-science/</t>
+          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5090,12 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -5103,7 +5105,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>CHF 2,240 در ترم (≈ CHF 4,480/سال)</t>
+          <t>CHF 2,240 در ترم برای خارجی‌های غیرمقیم (از پاییز ۲۰۲۵؛ ≈ CHF 4,480/سال)</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -5113,12 +5115,12 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی/مهندسی با نمرات عالی</t>
+          <t>کارشناسی CS با نمرات عالی (بالای کلاس)؛ فقط یک برنامه در سال</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>مدرک زبان الزامی نیست</t>
+          <t>مدرک زبان الزامی نیست (C1 عملاً لازم)</t>
         </is>
       </c>
       <c r="M37" s="4">
@@ -5132,17 +5134,17 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>بسیار رقابتی؛ کارآموزی صنعتی جزو برنامه است</t>
+          <t>دور اول ۱۵ دسامبر ۲۰۲۶ (توصیه برای ویزایی‌ها؛ پاسخ اوایل آوریل)، دور دوم ۳۱ مارس ۲۰۲۷؛ ⚠️ احتمال افزایش دوبارهٔ شهریه (EP27)</t>
         </is>
       </c>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/education/master/programs/data-science/</t>
+          <t>https://www.epfl.ch/education/master/programs/computer-science/</t>
         </is>
       </c>
     </row>
@@ -5157,27 +5159,27 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>ETH Zürich</t>
+          <t>EPFL</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
+          <t>Lausanne (لوزان) — کنار دریاچهٔ ژنو؛ فرانسه‌زبان؛ EPFL</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,900–2,500</t>
+          <t>خیلی گران — CHF 1,700–2,200</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Data Science</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -5187,26 +5189,26 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>CHF 2,190 + ≈ CHF 74 = ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
+          <t>CHF 2,240 در ترم (≈ CHF 4,480/سال)</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>$5,500</t>
+          <t>$5,400</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با نمرات ممتاز (عملاً ۱۰٪ بالای کلاس)؛ هزینهٔ درخواست CHF 150؛ تا ۲ برنامه</t>
+          <t>کارشناسی CS/ریاضی/مهندسی با نمرات عالی</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>C1 / IELTS 7.0</t>
+          <t>مدرک زبان الزامی نیست</t>
         </is>
       </c>
       <c r="M38" s="4">
-        <f>8</f>
+        <f>22</f>
         <v/>
       </c>
       <c r="N38" s="12" t="inlineStr">
@@ -5216,17 +5218,17 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>بهترین دانشگاه قارهٔ اروپا؛ اپلای فقط ۱–۳۰ نوامبر ۲۰۲۶، پاسخ تا پایان مارس ۲۰۲۷، شروع ۲۰ سپتامبر ۲۰۲۷؛ با معدل ۱۵.۷۷ احتمال پذیرش کم</t>
+          <t>بسیار رقابتی؛ کارآموزی صنعتی جزو برنامه است</t>
         </is>
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/computer-science.html</t>
+          <t>https://www.epfl.ch/education/master/programs/data-science/</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5243,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ETH Zürich + EPFL</t>
+          <t>ETH Zürich</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -5256,12 +5258,12 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>MSc Cyber Security (مشترک ETH–EPFL؛ یک سال در هر کدام)</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -5271,7 +5273,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ ETH: ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
+          <t>CHF 2,190 + ≈ CHF 74 = ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -5281,7 +5283,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با نمرات ممتاز؛ پیش‌زمینهٔ ریاضی/سیستم قوی</t>
+          <t>کارشناسی CS با نمرات ممتاز (عملاً ۱۰٪ بالای کلاس)؛ هزینهٔ درخواست CHF 150؛ تا ۲ برنامه</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -5300,17 +5302,17 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>قوی‌ترین ارشد امنیت اروپا؛ همان پنجرهٔ نوامبر ETH؛ Reach</t>
+          <t>بهترین دانشگاه قارهٔ اروپا؛ اپلای فقط ۱–۳۰ نوامبر ۲۰۲۶، پاسخ تا پایان مارس ۲۰۲۷، شروع ۲۰ سپتامبر ۲۰۲۷؛ با معدل ۱۵.۷۷ احتمال پذیرش کم</t>
         </is>
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/cyber-security.html</t>
+          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/computer-science.html</t>
         </is>
       </c>
     </row>
@@ -5320,82 +5322,81 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Universität Stuttgart</t>
+          <t>ETH Zürich + EPFL</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
+          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,350</t>
+          <t>خیلی گران — CHF 1,900–2,500</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Computer Science (انگلیسی، بدون NC)</t>
+          <t>MSc Cyber Security (مشترک ETH–EPFL؛ یک سال در هر کدام)</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + ≈ €200 سهم ترم = ≈ €3,400/سال</t>
+          <t>شهریهٔ ETH: ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>$3,900</t>
+          <t>$5,500</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
+          <t>کارشناسی CS با نمرات ممتاز؛ پیش‌زمینهٔ ریاضی/سیستم قوی</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1)</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="N40" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>C1 / IELTS 7.0</t>
+        </is>
+      </c>
+      <c r="M40" s="4">
+        <f>8</f>
+        <v/>
+      </c>
+      <c r="N40" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ بادن-وورتمبرگ برای غیر-EU</t>
+          <t>قوی‌ترین ارشد امنیت اروپا؛ همان پنجرهٔ نوامبر ETH؛ Reach</t>
         </is>
       </c>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/study/study-programs/</t>
+          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/cyber-security.html</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5426,12 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Information Technology (INFOTECH)</t>
+          <t>M.Sc. Computer Science (انگلیسی، بدون NC)</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -5440,7 +5441,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + سهم ترم ≈ €3,400/سال</t>
+          <t>€1,500 در ترم + ≈ €200 سهم ترم = ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5450,7 +5451,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی EE/CS/Computer Engineering؛ گزینش</t>
+          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -5470,17 +5471,17 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>گرایش‌های Embedded/Communication؛ Bosch و Daimler همان شهر</t>
+          <t>شهریهٔ بادن-وورتمبرگ برای غیر-EU</t>
         </is>
       </c>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>https://www.mygermanuniversity.com/master/information-technology-infotech/678</t>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/</t>
         </is>
       </c>
     </row>
@@ -5495,27 +5496,27 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>FAU Erlangen-Nürnberg</t>
+          <t>Universität Stuttgart</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
+          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €950–1,150</t>
+          <t>گران — €1,100–1,350</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Artificial Intelligence</t>
+          <t>M.Sc. Information Technology (INFOTECH)</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -5525,27 +5526,27 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>€4,000 در ترم برای غیر-EU از ترم تابستان ۲۰۲۷ (€8,000/سال) + €82 سهم ترم</t>
+          <t>€1,500 در ترم + سهم ترم ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>$9,300</t>
+          <t>$3,900</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بررسی ریزنمرات</t>
+          <t>کارشناسی EE/CS/Computer Engineering؛ گزینش</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 6.0)</t>
+          <t>7.0 (C1)</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>318</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
@@ -5555,17 +5556,17 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی اکتبر ۲۰۲۷ شما مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
+          <t>گرایش‌های Embedded/Communication؛ Bosch و Daimler همان شهر</t>
         </is>
       </c>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/artificial-intelligence-m-sc/</t>
+          <t>https://www.mygermanuniversity.com/master/information-technology-infotech/678</t>
         </is>
       </c>
     </row>
@@ -5595,12 +5596,12 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Autonomy Technologies</t>
+          <t>M.Sc. Artificial Intelligence</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -5610,17 +5611,17 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>€2,000 در ترم از تابستان ۲۰۲۷ (€4,000/سال) + €82 سهم ترم</t>
+          <t>€4,000 در ترم برای غیر-EU از ترم تابستان ۲۰۲۷ (€8,000/سال) + €82 سهم ترم</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>$4,700</t>
+          <t>$9,300</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط؛ آلمانی لازم نیست</t>
+          <t>کارشناسی CS/مرتبط؛ بررسی ریزنمرات</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -5640,17 +5641,17 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>رباتیک/خودران؛ ⚠️ مشمول شهریهٔ جدید FAU از ۲۰۲۷ (صفحهٔ رسمی شهریه، ۲۰۲۶)</t>
+          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی اکتبر ۲۰۲۷ شما مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
         </is>
       </c>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+          <t>https://www.fau.eu/degree-program/artificial-intelligence-m-sc/</t>
         </is>
       </c>
     </row>
@@ -5665,27 +5666,27 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>TU Darmstadt</t>
+          <t>FAU Erlangen-Nürnberg</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Darmstadt (دارمشتات) — ۲۵ دقیقه تا فرانکفورت</t>
+          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>متوسط — €950–1,150</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Distributed Software Systems (انگلیسی)</t>
+          <t>M.Sc. Autonomy Technologies</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -5695,47 +5696,47 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €300 سهم ترم (≈ €600/سال)</t>
+          <t>€2,000 در ترم از تابستان ۲۰۲۷ (€4,000/سال) + €82 سهم ترم</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$4,700</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با پیش‌نیازهای مشخص</t>
+          <t>کارشناسی مرتبط؛ آلمانی لازم نیست</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>≈ 7.0 (C1) — چک شود</t>
+          <t>B2 (IELTS 6.0)</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="N44" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>منطقهٔ Rhein-Main (SAP، Deutsche Bank، Software AG)</t>
+          <t>رباتیک/خودران؛ ⚠️ مشمول شهریهٔ جدید FAU از ۲۰۲۷ (صفحهٔ رسمی شهریه، ۲۰۲۶)</t>
         </is>
       </c>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>https://www.tu-darmstadt.de/studieren/</t>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
       </c>
     </row>
@@ -5750,27 +5751,27 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>TU Dresden</t>
+          <t>TU Darmstadt</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Dresden (درسدن) — «سیلیکون ساکسونی»</t>
+          <t>Darmstadt (دارمشتات) — ۲۵ دقیقه تا فرانکفورت</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €850–1,050</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Computer Science (انگلیسی)</t>
+          <t>M.Sc. Distributed Software Systems (انگلیسی)</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -5780,7 +5781,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €300 سهم ترم</t>
+          <t>€0 + ≈ €300 سهم ترم (≈ €600/سال)</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -5790,37 +5791,37 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارزیابی استعداد</t>
+          <t>کارشناسی CS با پیش‌نیازهای مشخص</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>≈ 7.0 (C1) — چک شود</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>Dresden ارزان‌ترین شهر جدول؛ GlobalFoundries/Infineon/Bosch</t>
+          <t>منطقهٔ Rhein-Main (SAP، Deutsche Bank، Software AG)</t>
         </is>
       </c>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de/studium/vor-dem-studium/studienangebot</t>
+          <t>https://www.tu-darmstadt.de/studieren/</t>
         </is>
       </c>
     </row>
@@ -5835,27 +5836,27 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Saarland University (UdS)</t>
+          <t>TU Dresden</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
+          <t>Dresden (درسدن) — «سیلیکون ساکسونی»</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>ارزان — €850–1,050</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Cybersecurity</t>
+          <t>M.Sc. Computer Science (انگلیسی)</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -5865,46 +5866,47 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €394 سهم ترم (≈ €790/سال)</t>
+          <t>€0 + ≈ €300 سهم ترم</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>$900</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS + اثبات دروس پایه + ۲ توصیه‌نامه؛ بدون NC</t>
+          <t>کارشناسی CS؛ ارزیابی استعداد</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1؛ MOI پذیرفته نمی‌شود)</t>
-        </is>
-      </c>
-      <c r="M46" s="4">
-        <f>588 (CS ≈ 251)</f>
-        <v/>
-      </c>
-      <c r="N46" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N46" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>CISPA — بهترین مرکز امنیت آلمان؛ IELTS 7 شرط سخت شماست</t>
+          <t>Dresden ارزان‌ترین شهر جدول؛ GlobalFoundries/Infineon/Bosch</t>
         </is>
       </c>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+          <t>https://tu-dresden.de/studium/vor-dem-studium/studienangebot</t>
         </is>
       </c>
     </row>
@@ -5934,12 +5936,12 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Data Science and Artificial Intelligence</t>
+          <t>M.Sc. Cybersecurity</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -5949,7 +5951,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €394 سهم ترم</t>
+          <t>€0 + ≈ €394 سهم ترم (≈ €790/سال)</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -5959,12 +5961,12 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
+          <t>کارشناسی CS + اثبات دروس پایه + ۲ توصیه‌نامه؛ بدون NC</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1)</t>
+          <t>7.0 (C1؛ MOI پذیرفته نمی‌شود)</t>
         </is>
       </c>
       <c r="M47" s="4">
@@ -5978,17 +5980,17 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>MPI Informatics و DFKI در همان کمپوس</t>
+          <t>CISPA — بهترین مرکز امنیت آلمان؛ IELTS 7 شرط سخت شماست</t>
         </is>
       </c>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/data-science.html</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
       </c>
     </row>
@@ -6003,27 +6005,27 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>TU Chemnitz</t>
+          <t>Saarland University (UdS)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Chemnitz (کمنیتس) — ساکسونی</t>
+          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €800–1,000</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Automotive Software Engineering</t>
+          <t>M.Sc. Data Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -6033,47 +6035,46 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €320 سهم ترم (≈ €640/سال)</t>
+          <t>€0 + ≈ €394 سهم ترم</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$900</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون محدودیت پذیرش</t>
+          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 5.5)</t>
-        </is>
-      </c>
-      <c r="M48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>7.0 (C1)</t>
+        </is>
+      </c>
+      <c r="M48" s="4">
+        <f>588 (CS ≈ 251)</f>
+        <v/>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>آسان‌ترین ورود؛ شهر ارزان؛ ولی صنعت خودرو ۲۰۲۴–۲۵ ضعیف و آلمانی در کارفرمایان محلی</t>
+          <t>MPI Informatics و DFKI در همان کمپوس</t>
         </is>
       </c>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>https://www.mygermanuniversity.com/master/automotive-software-engineering/91</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/data-science.html</t>
         </is>
       </c>
     </row>
@@ -6088,27 +6089,27 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Universität Passau</t>
+          <t>TU Chemnitz</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Passau (پاساو) — شهر کوچک، مرز اتریش</t>
+          <t>Chemnitz (کمنیتس) — ساکسونی</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>ارزان — €800–1,000</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Artificial Intelligence Engineering</t>
+          <t>M.Sc. Automotive Software Engineering</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -6118,22 +6119,22 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €100–200 سهم ترم</t>
+          <t>€0 + ≈ €320 سهم ترم (≈ €640/سال)</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.7 (معدل شما ≈ 2.3 ✓)؛ ۳۵ ECTS ریاضی + ۴۰ ECTS CS</t>
+          <t>کارشناسی CS/مرتبط؛ بدون محدودیت پذیرش</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>B2؛ + آلمانی A1 تا پایان سال اول (کلاس رایگان)</t>
+          <t>B2 (IELTS 5.5)</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -6148,17 +6149,17 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان؛ Passau رسماً اعلام کرده «فعلاً» شهریهٔ غیر-EU نمی‌گیرد (برخلاف FAU/TUM) ولی طبق قانون باواریا می‌تواند — قبل از اپلای چک کنید</t>
+          <t>آسان‌ترین ورود؛ شهر ارزان؛ ولی صنعت خودرو ۲۰۲۴–۲۵ ضعیف و آلمانی در کارفرمایان محلی</t>
         </is>
       </c>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+          <t>https://www.mygermanuniversity.com/master/automotive-software-engineering/91</t>
         </is>
       </c>
     </row>
@@ -6173,27 +6174,27 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Otto-von-Guericke-Universität (OVGU)</t>
+          <t>Universität Passau</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Magdeburg (ماگدبورگ) — ساکسونی-آنهالت</t>
+          <t>Passau (پاساو) — شهر کوچک، مرز اتریش</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €850–1,000</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Data and Knowledge Engineering</t>
+          <t>M.Sc. Artificial Intelligence Engineering</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -6203,22 +6204,22 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €311 سهم ترم</t>
+          <t>€0 + ≈ €100–200 سهم ترم</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$300</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.3 (معدل شما ≈ 2.27 — دقیقاً مرزی)؛ کارشناسی CS</t>
+          <t>معدل آلمانی ≤ 2.7 (معدل شما ≈ 2.3 ✓)؛ ۳۵ ECTS ریاضی + ۴۰ ECTS CS</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>6.0–7.0 (منابع متناقض؛ رسمی را چک کنید)</t>
+          <t>B2؛ + آلمانی A1 تا پایان سال اول (کلاس رایگان)</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -6226,20 +6227,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N50" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="inlineStr"/>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان؛ Passau رسماً اعلام کرده «فعلاً» شهریهٔ غیر-EU نمی‌گیرد (برخلاف FAU/TUM) ولی طبق قانون باواریا می‌تواند — قبل از اپلای چک کنید</t>
+        </is>
+      </c>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>https://www.dke.ovgu.de/</t>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
       </c>
     </row>
@@ -6254,27 +6259,27 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>TH Köln – Cologne Game Lab</t>
+          <t>Otto-von-Guericke-Universität (OVGU)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Köln / Cologne (کلن) — چهارمین شهر آلمان</t>
+          <t>Magdeburg (ماگدبورگ) — ساکسونی-آنهالت</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>ارزان — €850–1,000</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>M.A. Game Development and Research</t>
+          <t>M.Sc. Data and Knowledge Engineering</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -6284,47 +6289,43 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>€2,500 در ترم (غیر-EU) + €277 سهم ترم ≈ €5,550/سال</t>
+          <t>€0 + ≈ €311 سهم ترم</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>$6,300</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>هر کارشناسی + ≥ ۱۲ ماه سابقهٔ مرتبط + آزمون استعداد (مهلت ۳۱ مارس)</t>
+          <t>معدل آلمانی ≤ 2.3 (معدل شما ≈ 2.27 — دقیقاً مرزی)؛ کارشناسی CS</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>6.0–7.0 (منابع متناقض؛ رسمی را چک کنید)</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>— (UAS)</t>
-        </is>
-      </c>
-      <c r="N51" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
-        </is>
-      </c>
-      <c r="P51" s="4" t="inlineStr">
-        <is>
-          <t>معتبرترین مدرسهٔ بازی آلمان؛ ۷ ماه Unity + ۲ سال IT شما احتمالاً شرط ۱۲ ماه را می‌پوشاند — بپرسید</t>
-        </is>
-      </c>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+          <t>https://www.dke.ovgu.de/</t>
         </is>
       </c>
     </row>
@@ -6339,27 +6340,27 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Universität Siegen</t>
+          <t>TH Köln – Cologne Game Lab</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Siegen (زیگن) — شهر کوچک، NRW</t>
+          <t>Köln / Cologne (کلن) — چهارمین شهر آلمان</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Human Computer Interaction</t>
+          <t>M.A. Game Development and Research</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -6369,47 +6370,47 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €372 سهم ترم</t>
+          <t>€2,500 در ترم (غیر-EU) + €277 سهم ترم ≈ €5,550/سال</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>$800</t>
+          <t>$6,300</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.5؛ کارشناسی CS/IS/Design/Psychology</t>
+          <t>هر کارشناسی + ≥ ۱۲ ماه سابقهٔ مرتبط + آزمون استعداد (مهلت ۳۱ مارس)</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N52" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>شروع زمستان و تابستان؛ شهر کوچک</t>
+          <t>معتبرترین مدرسهٔ بازی آلمان؛ ۷ ماه Unity + ۲ سال IT شما احتمالاً شرط ۱۲ ماه را می‌پوشاند — بپرسید</t>
         </is>
       </c>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
       </c>
     </row>
@@ -6424,27 +6425,27 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Hochschule Bonn-Rhein-Sieg (H-BRS)</t>
+          <t>Universität Siegen</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Sankt Augustin (زانکت آگوستین) — حومهٔ Bonn</t>
+          <t>Siegen (زیگن) — شهر کوچک، NRW</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €950–1,200</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Autonomous Systems</t>
+          <t>M.Sc. Human Computer Interaction</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -6454,7 +6455,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>€0 + €349 سهم ترم</t>
+          <t>€0 + ≈ €372 سهم ترم</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6464,37 +6465,37 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.5؛ ۲۵ جای محدود؛ آزمون استعداد؛ uni-assist</t>
+          <t>معدل آلمانی ≤ 2.5؛ کارشناسی CS/IS/Design/Psychology</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>6.5 (B2+)</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>— (UAS)</t>
-        </is>
-      </c>
-      <c r="N53" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>رباتیک کاربردی با Fraunhofer؛ نزدیک Bonn/Köln</t>
+          <t>شروع زمستان و تابستان؛ شهر کوچک</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6510,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>RWTH Aachen</t>
+          <t>Hochschule Bonn-Rhein-Sieg (H-BRS)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Aachen (آخن) — مرز هلند/بلژیک</t>
+          <t>Sankt Augustin (زانکت آگوستین) — حومهٔ Bonn</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -6524,12 +6525,12 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Software Systems Engineering</t>
+          <t>M.Sc. Autonomous Systems</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -6539,7 +6540,7 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €330 سهم ترم</t>
+          <t>€0 + €349 سهم ترم</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -6549,37 +6550,37 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS، معدل ≥ ۶۵٪ (شما ۷۹٪ ✓)؛ ۲ درس پیشرفتهٔ سیستم؛ مهلت ۱ مارس</t>
+          <t>معدل آلمانی ≤ 2.5؛ ۲۵ جای محدود؛ آزمون استعداد؛ uni-assist</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 5.5)</t>
+          <t>6.5 (B2+)</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="N54" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>TU9؛ رقابتی — معدل شما حداقل را رد می‌کند ولی متقاضیان قوی‌ترند</t>
+          <t>رباتیک کاربردی با Fraunhofer؛ نزدیک Bonn/Köln</t>
         </is>
       </c>
       <c r="Q54" s="8" t="inlineStr">
         <is>
-          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
       </c>
     </row>
@@ -6594,27 +6595,27 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Universität Tübingen</t>
+          <t>RWTH Aachen</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Tübingen (توبینگن) — شهر دانشگاهی کوچک؛ Cyber Valley</t>
+          <t>Aachen (آخن) — مرز هلند/بلژیک</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>متوسط — €950–1,200</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Machine Learning</t>
+          <t>M.Sc. Software Systems Engineering</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -6624,27 +6625,28 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + ≈ €200 = ≈ €3,400/سال</t>
+          <t>€0 + ≈ €330 سهم ترم</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>$3,900</t>
+          <t>$800</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی؛ آزمون توانایی؛ مهلت ۳۰ آوریل</t>
+          <t>کارشناسی CS، معدل ≥ ۶۵٪ (شما ۷۹٪ ✓)؛ ۲ درس پیشرفتهٔ سیستم؛ مهلت ۱ مارس</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="M55" s="4">
-        <f>230</f>
-        <v/>
+          <t>B2 (IELTS 5.5)</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -6653,17 +6655,17 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>Cyber Valley — بهترین ML آلمان؛ پذیرش بسیار سخت</t>
+          <t>TU9؛ رقابتی — معدل شما حداقل را رد می‌کند ولی متقاضیان قوی‌ترند</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr">
         <is>
-          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
       </c>
     </row>
@@ -6678,27 +6680,27 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>TU München (TUM)</t>
+          <t>Universität Tübingen</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>München – Garching (مونیخ، کمپوس گارشینگ)</t>
+          <t>Tübingen (توبینگن) — شهر دانشگاهی کوچک؛ Cyber Valley</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,300–1,600</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Informatics</t>
+          <t>M.Sc. Machine Learning</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -6708,28 +6710,27 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>€6,000 در ترم برای غیر-EU (€12,000/سال) + €97</t>
+          <t>€1,500 در ترم + ≈ €200 = ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>$13,900</t>
+          <t>$3,900</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارزیابی استعداد؛ بسیار رقابتی</t>
+          <t>کارشناسی CS/ریاضی؛ آزمون توانایی؛ مهلت ۳۰ آوریل</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="inlineStr">
-        <is>
-          <t>≈ 25</t>
-        </is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M56" s="4">
+        <f>230</f>
+        <v/>
       </c>
       <c r="N56" s="12" t="inlineStr">
         <is>
@@ -6738,17 +6739,17 @@
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>⚠️ TUM از ۲۰۲۴ شهریهٔ غیر-EU می‌گیرد — دیگر «رایگان» نیست؛ Munich گران‌ترین شهر آلمان</t>
+          <t>Cyber Valley — بهترین ML آلمان؛ پذیرش بسیار سخت</t>
         </is>
       </c>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
       </c>
     </row>
@@ -6758,27 +6759,27 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>University of Twente (UT)</t>
+          <t>TU München (TUM)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
+          <t>München – Garching (مونیخ، کمپوس گارشینگ)</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,000–1,300</t>
+          <t>خیلی گران — €1,300–1,600</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (گرایش‌ها: Cyber Security، Data Science، Software Tech، ...)</t>
+          <t>M.Sc. Informatics</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -6793,17 +6794,17 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>€21,700</t>
+          <t>€6,000 در ترم برای غیر-EU (€12,000/سال) + €97</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>$24,700</t>
+          <t>$13,900</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>حداقل رسمی برای مدرک ایرانی ۱۵/۲۰</t>
+          <t>کارشناسی CS؛ ارزیابی استعداد؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -6813,12 +6814,12 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="N57" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>≈ 25</t>
+        </is>
+      </c>
+      <c r="N57" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -6828,12 +6829,12 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>⚠️ TUM از ۲۰۲۴ شهریهٔ غیر-EU می‌گیرد — دیگر «رایگان» نیست؛ Munich گران‌ترین شهر آلمان</t>
         </is>
       </c>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/computer-science/</t>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
       </c>
     </row>
@@ -6863,12 +6864,12 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded Systems</t>
+          <t>MSc Computer Science (گرایش‌ها: Cyber Security، Data Science، Software Tech، ...)</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -6888,7 +6889,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>CGPA ≥ ۷۰–۷۵٪؛ کارشناسی CS/EE/Computer Eng</t>
+          <t>حداقل رسمی برای مدرک ایرانی ۱۵/۲۰</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -6908,17 +6909,17 @@
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ مهلت غیر-EU ۱ مه</t>
+          <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/computer-science/</t>
         </is>
       </c>
     </row>
@@ -6948,12 +6949,12 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>MSc Interaction Technology</t>
+          <t>MSc Embedded Systems</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -6973,7 +6974,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط</t>
+          <t>CGPA ≥ ۷۰–۷۵٪؛ کارشناسی CS/EE/Computer Eng</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -6993,17 +6994,17 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>HCI فنی (نه طراحی صرف)</t>
+          <t>شهریهٔ رسمی 2026/27؛ مهلت غیر-EU ۱ مه</t>
         </is>
       </c>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/interaction-technology/</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
       </c>
     </row>
@@ -7018,27 +7019,27 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Radboud University</t>
+          <t>University of Twente (UT)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Nijmegen (نایمخن) — شرق هلند</t>
+          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,050–1,350</t>
+          <t>متوسط — €1,000–1,300</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>MSc Computing Science (گرایش‌ها: Cyber Security، Data Science، Software Science)</t>
+          <t>MSc Interaction Technology</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -7048,17 +7049,17 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
+          <t>€21,700</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>$22,500</t>
+          <t>$24,700</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با ریاضی/الگوریتم کافی</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -7068,7 +7069,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>223</t>
         </is>
       </c>
       <c r="N60" s="10" t="inlineStr">
@@ -7078,17 +7079,17 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>HCI فنی (نه طراحی صرف)</t>
         </is>
       </c>
       <c r="Q60" s="8" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/masters/computing-science</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/interaction-technology/</t>
         </is>
       </c>
     </row>
@@ -7118,12 +7119,12 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computing Science (گرایش‌ها: Cyber Security، Data Science، Software Science)</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -7143,7 +7144,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI/مرتبط</t>
+          <t>کارشناسی CS با ریاضی/الگوریتم کافی</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -7163,17 +7164,17 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>AI شناختی (Donders Institute)</t>
+          <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
       <c r="Q61" s="8" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/masters/artificial-intelligence</t>
+          <t>https://www.ru.nl/en/education/masters/computing-science</t>
         </is>
       </c>
     </row>
@@ -7188,27 +7189,27 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Leiden University</t>
+          <t>Radboud University</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Leiden (لایدن) — بین Den Haag و Amsterdam</t>
+          <t>Nijmegen (نایمخن) — شرق هلند</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>متوسط — €1,050–1,350</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (گرایش‌ها: Artificial Intelligence، Data Science، ...)</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>چندحوزه‌ای (انتخاب گرایش)</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -7218,17 +7219,17 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>€22,500</t>
+          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>$25,600</t>
+          <t>$22,500</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/AI/مرتبط</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -7238,27 +7239,27 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="N62" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ نزدیک Den Haag/Amsterdam</t>
+          <t>AI شناختی (Donders Institute)</t>
         </is>
       </c>
       <c r="Q62" s="8" t="inlineStr">
         <is>
-          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+          <t>https://www.ru.nl/en/education/masters/artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -7273,27 +7274,27 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>University of Groningen (RUG)</t>
+          <t>Leiden University</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Groningen (خرونینگن) — شمال هلند</t>
+          <t>Leiden (لایدن) — بین Den Haag و Amsterdam</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,050–1,350</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computer Science (گرایش‌ها: Artificial Intelligence، Data Science، ...)</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>چندحوزه‌ای (انتخاب گرایش)</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -7303,17 +7304,17 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>€24,900</t>
+          <t>€22,500</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>$28,400</t>
+          <t>$25,600</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی AI/CS با ریاضی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -7323,7 +7324,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N63" s="11" t="inlineStr">
@@ -7333,17 +7334,17 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ بورس ASML €5k</t>
+          <t>شهریهٔ رسمی 2026/27؛ نزدیک Den Haag/Amsterdam</t>
         </is>
       </c>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7374,12 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>MSc Computing Science</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -7388,17 +7389,17 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>≈ €21,400 (2025) → ≈ €22,500</t>
+          <t>€24,900</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>$25,600</t>
+          <t>$28,400</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی AI/CS با ریاضی</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -7411,20 +7412,24 @@
           <t>157</t>
         </is>
       </c>
-      <c r="N64" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="N64" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P64" s="4" t="inlineStr"/>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27؛ بورس ASML €5k</t>
+        </is>
+      </c>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/computing-science/?lang=en</t>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
       </c>
     </row>
@@ -7439,27 +7444,27 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Utrecht University</t>
+          <t>University of Groningen (RUG)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
+          <t>Groningen (خرونینگن) — شمال هلند</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>متوسط — €1,050–1,350</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>MSc Game and Media Technology</t>
+          <t>MSc Computing Science</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -7469,17 +7474,17 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>€25,306</t>
+          <t>≈ €21,400 (2025) → ≈ €22,500</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>$28,800</t>
+          <t>$25,600</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارشد پژوهشی گزینشی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -7489,27 +7494,23 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="N65" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="N65" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
-        </is>
-      </c>
-      <c r="P65" s="4" t="inlineStr">
-        <is>
-          <t>تنها ارشد پژوهشی بازی هلند؛ Utrecht قطب استودیوهای بازی</t>
-        </is>
-      </c>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr"/>
       <c r="Q65" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+          <t>https://www.rug.nl/masters/computing-science/?lang=en</t>
         </is>
       </c>
     </row>
@@ -7539,12 +7540,12 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Game and Media Technology</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -7564,7 +7565,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI؛ گزینشی</t>
+          <t>کارشناسی CS؛ ارشد پژوهشی گزینشی</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -7584,17 +7585,17 @@
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>همان باند شهریهٔ Utrecht 2026/27</t>
+          <t>تنها ارشد پژوهشی بازی هلند؛ Utrecht قطب استودیوهای بازی</t>
         </is>
       </c>
       <c r="Q66" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/artificial-intelligence</t>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
       </c>
     </row>
@@ -7609,47 +7610,47 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA)</t>
+          <t>Utrecht University</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Amsterdam (آمستردام)</t>
+          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,300–1,700</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering (۱ ساله!)</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>≈ €23,540</t>
+          <t>€25,306</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>$26,800</t>
+          <t>$28,800</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/AI؛ گزینشی</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -7659,27 +7660,27 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="N67" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="N67" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>تنها ارشد ۱ سالهٔ معتبر هلند → کل هزینه نصف؛ اما اجارهٔ Amsterdam €900–1,300</t>
+          <t>همان باند شهریهٔ Utrecht 2026/27</t>
         </is>
       </c>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>https://www.uva.nl/en/programmes/masters/software-engineering/software-engineering.html</t>
+          <t>https://www.uu.nl/en/masters/artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -7709,32 +7710,32 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Software Engineering (۱ ساله!)</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>≈ €26,000</t>
+          <t>≈ €23,540</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>$29,600</t>
+          <t>$26,800</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی AI/CS با ریاضی قوی؛ بسیار رقابتی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -7747,20 +7748,24 @@
           <t>60</t>
         </is>
       </c>
-      <c r="N68" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="N68" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
-        </is>
-      </c>
-      <c r="P68" s="4" t="inlineStr"/>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P68" s="4" t="inlineStr">
+        <is>
+          <t>تنها ارشد ۱ سالهٔ معتبر هلند → کل هزینه نصف؛ اما اجارهٔ Amsterdam €900–1,300</t>
+        </is>
+      </c>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>https://www.uva.nl/en/programmes/masters/artificial-intelligence/artificial-intelligence.html</t>
+          <t>https://www.uva.nl/en/programmes/masters/software-engineering/software-engineering.html</t>
         </is>
       </c>
     </row>
@@ -7775,27 +7780,27 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>TU Eindhoven (TU/e)</t>
+          <t>University of Amsterdam (UvA)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
+          <t>Amsterdam (آمستردام)</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,400</t>
+          <t>خیلی گران — €1,300–1,700</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science and Artificial Intelligence</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -7805,17 +7810,17 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
+          <t>≈ €26,000</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>$25,500</t>
+          <t>$29,600</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی؛ گزینش بر اساس معدل</t>
+          <t>کارشناسی AI/CS با ریاضی قوی؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -7825,7 +7830,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N69" s="12" t="inlineStr">
@@ -7835,17 +7840,13 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P69" s="4" t="inlineStr">
-        <is>
-          <t>Brainport (ASML، Philips، NXP)</t>
-        </is>
-      </c>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P69" s="4" t="inlineStr"/>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/graduate-school/master-data-science-and-artificial-intelligence</t>
+          <t>https://www.uva.nl/en/programmes/masters/artificial-intelligence/artificial-intelligence.html</t>
         </is>
       </c>
     </row>
@@ -7875,12 +7876,12 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded Systems</t>
+          <t>MSc Data Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -7900,7 +7901,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE؛ گزینش</t>
+          <t>کارشناسی CS/ریاضی؛ گزینش بر اساس معدل</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -7920,17 +7921,17 @@
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>ASML/NXP بزرگ‌ترین کارفرمایان Embedded اروپا</t>
+          <t>Brainport (ASML، Philips، NXP)</t>
         </is>
       </c>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/graduate-school/master-embedded-systems</t>
+          <t>https://www.tue.nl/en/education/graduate-school/master-data-science-and-artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -7945,27 +7946,27 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>TU Delft</t>
+          <t>TU Eindhoven (TU/e)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Delft (دلفت) — کنار Den Haag/Rotterdam</t>
+          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>گران — €1,100–1,400</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science / MSc Computer &amp; Embedded Systems Engineering</t>
+          <t>MSc Embedded Systems</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -7975,27 +7976,27 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>€22,290 (2025/26) → ≈ €23,000</t>
+          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>$26,200</t>
+          <t>$25,500</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>معدل ≥ ۷۵٪ / ۲۰٪ برتر</t>
+          <t>کارشناسی CS/EE؛ گزینش</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N71" s="12" t="inlineStr">
@@ -8005,17 +8006,17 @@
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>معتبرترین، ولی برای معدل ۱۵.۷۷ دور از دسترس</t>
+          <t>ASML/NXP بزرگ‌ترین کارفرمایان Embedded اروپا</t>
         </is>
       </c>
       <c r="Q71" s="8" t="inlineStr">
         <is>
-          <t>https://www.tudelft.nl/onderwijs/opleidingen/masters/cs/msc-computer-science</t>
+          <t>https://www.tue.nl/en/education/graduate-school/master-embedded-systems</t>
         </is>
       </c>
     </row>
@@ -8030,77 +8031,77 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Breda University of Applied Sciences (BUas)</t>
+          <t>TU Delft</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Breda (بردا) — جنوب هلند</t>
+          <t>Delft (دلفت) — کنار Den Haag/Rotterdam</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,000–1,300</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Master Game Technology (۱ ساله)</t>
+          <t>MSc Computer Science / MSc Computer &amp; Embedded Systems Engineering</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>≈ €15,200</t>
+          <t>€22,290 (2025/26) → ≈ €23,000</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>$17,300</t>
+          <t>$26,200</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی IT/برنامه‌نویسی/بازی + پیشنهاد پروژه</t>
+          <t>معدل ≥ ۷۵٪ / ۲۰٪ برتر</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>— (UAS)</t>
-        </is>
-      </c>
-      <c r="N72" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N72" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>برنامهٔ بازی BUas در اروپا شناخته‌شده است؛ مدرک UAS (نه پژوهشی)</t>
+          <t>معتبرترین، ولی برای معدل ۱۵.۷۷ دور از دسترس</t>
         </is>
       </c>
       <c r="Q72" s="8" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/breda-university-applied-sciences/postgrad/master-game-technology</t>
+          <t>https://www.tudelft.nl/onderwijs/opleidingen/masters/cs/msc-computer-science</t>
         </is>
       </c>
     </row>
@@ -8110,82 +8111,82 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Linköping University (LiU)</t>
+          <t>Breda University of Applied Sciences (BUas)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
+          <t>Breda (بردا) — جنوب هلند</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,500–12,500</t>
+          <t>متوسط — €1,000–1,300</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>Master Game Technology (۱ ساله)</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>SEK 166,000</t>
+          <t>≈ €15,200</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>$16,800</t>
+          <t>$17,300</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>گزینش بر اساس گروه معدل</t>
+          <t>کارشناسی IT/برنامه‌نویسی/بازی + پیشنهاد پروژه</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="N73" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>برنامهٔ بازی BUas در اروپا شناخته‌شده است؛ مدرک UAS (نه پژوهشی)</t>
         </is>
       </c>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>https://liu.se/en/education/program/6mics</t>
+          <t>https://www.topuniversities.com/universities/breda-university-applied-sciences/postgrad/master-game-technology</t>
         </is>
       </c>
     </row>
@@ -8215,12 +8216,12 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>MSc Statistics and Machine Learning</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -8230,7 +8231,7 @@
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 166,000 (همان باند)</t>
+          <t>SEK 166,000</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -8240,7 +8241,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی با ≥ ۳۰ واحد ریاضی/آمار + برنامه‌نویسی</t>
+          <t>گزینش بر اساس گروه معدل</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -8260,13 +8261,17 @@
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
-        </is>
-      </c>
-      <c r="P74" s="4" t="inlineStr"/>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P74" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی</t>
+        </is>
+      </c>
       <c r="Q74" s="8" t="inlineStr">
         <is>
-          <t>https://liu.se/en/education/program/f7msl</t>
+          <t>https://liu.se/en/education/program/6mics</t>
         </is>
       </c>
     </row>
@@ -8281,27 +8286,27 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Halmstad University</t>
+          <t>Linköping University (LiU)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Halmstad (هالمستاد) — غرب سوئد</t>
+          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,000–12,000</t>
+          <t>متوسط — SEK 10,500–12,500</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded and Intelligent Systems (120 cr)</t>
+          <t>MSc Statistics and Machine Learning</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -8311,17 +8316,17 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 151,000</t>
+          <t>≈ SEK 166,000 (همان باند)</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>$15,300</t>
+          <t>$16,800</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE</t>
+          <t>کارشناسی با ≥ ۳۰ واحد ریاضی/آمار + برنامه‌نویسی</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -8331,27 +8336,23 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
-        </is>
-      </c>
-      <c r="P75" s="4" t="inlineStr">
-        <is>
-          <t>Volvo/HMS در منطقه؛ بدون رتبهٔ QS</t>
-        </is>
-      </c>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="inlineStr"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>https://www.hh.se/english/education/programmes.html</t>
+          <t>https://liu.se/en/education/program/f7msl</t>
         </is>
       </c>
     </row>
@@ -8366,27 +8367,27 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Blekinge Institute of Technology (BTH)</t>
+          <t>Halmstad University</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Karlskrona (کارلسکرونا) — Ericsson، Telenor</t>
+          <t>Halmstad (هالمستاد) — غرب سوئد</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>ارزان — SEK 9,500–11,500</t>
+          <t>متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering (120 cr)</t>
+          <t>MSc Embedded and Intelligent Systems (120 cr)</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -8396,17 +8397,17 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>SEK 140,000</t>
+          <t>≈ SEK 151,000</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>$14,100</t>
+          <t>$15,300</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>≥ ۹۰ واحد CS/SE</t>
+          <t>کارشناسی CS/EE</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -8419,24 +8420,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N76" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>Ericsson و Telenor در Karlskrona؛ ⚠️ نسخهٔ ۶۰ واحدی از راه دور است</t>
+          <t>Volvo/HMS در منطقه؛ بدون رتبهٔ QS</t>
         </is>
       </c>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>https://www.bth.se/eng/programmes/</t>
+          <t>https://www.hh.se/english/education/programmes.html</t>
         </is>
       </c>
     </row>
@@ -8451,27 +8452,27 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>KTH Royal Institute of Technology</t>
+          <t>Blekinge Institute of Technology (BTH)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Stockholm (استکهلم)</t>
+          <t>Karlskrona (کارلسکرونا) — Ericsson، Telenor</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>گران — SEK 12,500–15,000</t>
+          <t>ارزان — SEK 9,500–11,500</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>MSc Machine Learning</t>
+          <t>MSc Software Engineering (120 cr)</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -8481,17 +8482,17 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 180,000–190,000 (کل دوره ≈ 360k–380k)</t>
+          <t>SEK 140,000</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>$18,200–19,200</t>
+          <t>$14,100</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی قوی؛ بسیار رقابتی</t>
+          <t>≥ ۹۰ واحد CS/SE</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -8501,27 +8502,27 @@
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="N77" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Stockholm گران (اتاق SEK 7–10k)؛ رقم دقیق روی kth.se فقط در سامانهٔ اپلای نمایش داده می‌شود</t>
+          <t>Ericsson و Telenor در Karlskrona؛ ⚠️ نسخهٔ ۶۰ واحدی از راه دور است</t>
         </is>
       </c>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+          <t>https://www.bth.se/eng/programmes/</t>
         </is>
       </c>
     </row>
@@ -8551,12 +8552,12 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>MSc Cybersecurity</t>
+          <t>MSc Machine Learning</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -8566,7 +8567,7 @@
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 180,000–190,000</t>
+          <t>≈ SEK 180,000–190,000 (کل دوره ≈ 360k–380k)</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -8576,7 +8577,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/ریاضی قوی؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -8596,13 +8597,17 @@
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
-        </is>
-      </c>
-      <c r="P78" s="4" t="inlineStr"/>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P78" s="4" t="inlineStr">
+        <is>
+          <t>Stockholm گران (اتاق SEK 7–10k)؛ رقم دقیق روی kth.se فقط در سامانهٔ اپلای نمایش داده می‌شود</t>
+        </is>
+      </c>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/cybersecurity</t>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8627,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Stockholm – Kista (استکهلم، شیستا؛ قطب ICT)</t>
+          <t>Stockholm (استکهلم)</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -8632,12 +8637,12 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering of Distributed Systems</t>
+          <t>MSc Cybersecurity</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -8647,7 +8652,7 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>SEK 180,000–190,000</t>
+          <t>≈ SEK 180,000–190,000</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -8670,24 +8675,20 @@
           <t>82</t>
         </is>
       </c>
-      <c r="N79" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+      <c r="N79" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
-        </is>
-      </c>
-      <c r="P79" s="4" t="inlineStr">
-        <is>
-          <t>Kista = قطب ICT سوئد (Ericsson)</t>
-        </is>
-      </c>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="inlineStr"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/software-engineering-of-distributed-systems</t>
+          <t>https://www.kth.se/en/studies/master/cybersecurity</t>
         </is>
       </c>
     </row>
@@ -8702,27 +8703,27 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Chalmers University of Technology</t>
+          <t>KTH Royal Institute of Technology</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+          <t>Stockholm – Kista (استکهلم، شیستا؛ قطب ICT)</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,500–13,500</t>
+          <t>گران — SEK 12,500–15,000</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science and AI</t>
+          <t>MSc Software Engineering of Distributed Systems</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -8732,17 +8733,17 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 175,000 (2026/27؛ 2025/26: 160,000)</t>
+          <t>SEK 180,000–190,000</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>$17,700</t>
+          <t>$18,200–19,200</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -8752,7 +8753,7 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N80" s="11" t="inlineStr">
@@ -8762,17 +8763,17 @@
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه؛ ⚠️ طبق صفحهٔ شهریهٔ Chalmers دانشگاه‌های سوئد فعلاً نمی‌توانند از ایران پول دریافت کنند (تحریم بانکی) — پرداخت از کشور ثالث</t>
+          <t>Kista = قطب ICT سوئد (Ericsson)</t>
         </is>
       </c>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/data-science-and-ai-msc/</t>
+          <t>https://www.kth.se/en/studies/master/software-engineering-of-distributed-systems</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8803,12 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering and Technology</t>
+          <t>MSc Data Science and AI</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -8817,7 +8818,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 175,000 (2026/27)</t>
+          <t>≈ SEK 175,000 (2026/27؛ 2025/26: 160,000)</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -8827,7 +8828,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE</t>
+          <t>کارشناسی CS/ریاضی</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -8840,20 +8841,24 @@
           <t>174</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="N81" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P81" s="4" t="inlineStr"/>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="inlineStr">
+        <is>
+          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه؛ ⚠️ طبق صفحهٔ شهریهٔ Chalmers دانشگاه‌های سوئد فعلاً نمی‌توانند از ایران پول دریافت کنند (تحریم بانکی) — پرداخت از کشور ثالث</t>
+        </is>
+      </c>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/software-engineering-and-technology-msc/</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/data-science-and-ai-msc/</t>
         </is>
       </c>
     </row>
@@ -8883,12 +8888,12 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>MSc Interaction Design and Technologies</t>
+          <t>MSc Software Engineering and Technology</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -8908,7 +8913,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/Design</t>
+          <t>کارشناسی CS/SE</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -8928,13 +8933,13 @@
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/interaction-design-and-technologies-msc/</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/software-engineering-and-technology-msc/</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8954,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>University of Gothenburg (مشترک با Chalmers)</t>
+          <t>Chalmers University of Technology</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -8964,12 +8969,12 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>MSc Game Design &amp; Technology</t>
+          <t>MSc Interaction Design and Technologies</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -8979,17 +8984,17 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>SEK 147,000 (ورودی ۲۰۲۷: کل دوره SEK 294,000 رسمی)</t>
+          <t>≈ SEK 175,000 (2026/27)</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>$14,800</t>
+          <t>$17,700</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/Design/Media</t>
+          <t>کارشناسی CS/Design</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -8999,7 +9004,7 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N83" s="10" t="inlineStr">
@@ -9009,17 +9014,13 @@
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
-        </is>
-      </c>
-      <c r="P83" s="4" t="inlineStr">
-        <is>
-          <t>Gothenburg: استودیوهای EA DICE/Ghost؛ بازار بازی ضعیف</t>
-        </is>
-      </c>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+        </is>
+      </c>
+      <c r="P83" s="4" t="inlineStr"/>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/interaction-design-and-technologies-msc/</t>
         </is>
       </c>
     </row>
@@ -9034,27 +9035,27 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Uppsala University</t>
+          <t>University of Gothenburg (مشترک با Chalmers)</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Uppsala (اوپسالا) — ۴۰ دقیقه تا استکهلم</t>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,000–13,000</t>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Game Design &amp; Technology</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -9064,17 +9065,17 @@
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 145,000–150,000</t>
+          <t>SEK 147,000 (ورودی ۲۰۲۷: کل دوره SEK 294,000 رسمی)</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>$14,600–15,200</t>
+          <t>$14,800</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/Design/Media</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -9084,27 +9085,27 @@
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="N84" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>رتبهٔ بالا با شهریهٔ پایین‌تر از KTH</t>
+          <t>Gothenburg: استودیوهای EA DICE/Ghost؛ بازار بازی ضعیف</t>
         </is>
       </c>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.se/en/study/programme/masters-programme-in-computer-science</t>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
       </c>
     </row>
@@ -9119,27 +9120,27 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Umeå University</t>
+          <t>Uppsala University</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Umeå (اومئو) — شمال سوئد</t>
+          <t>Uppsala (اوپسالا) — ۴۰ دقیقه تا استکهلم</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>ارزان تا متوسط — SEK 10,000–12,000</t>
+          <t>متوسط تا گران — SEK 11,000–13,000</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -9149,17 +9150,17 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>SEK 152,300</t>
+          <t>≈ SEK 145,000–150,000</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>$15,400</t>
+          <t>$14,600–15,200</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -9169,27 +9170,27 @@
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="N85" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N85" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>شمال سوئد، شهر دانشجویی ارزان؛ کل دوره SEK 304,600</t>
+          <t>رتبهٔ بالا با شهریهٔ پایین‌تر از KTH</t>
         </is>
       </c>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+          <t>https://www.uu.se/en/study/programme/masters-programme-in-computer-science</t>
         </is>
       </c>
     </row>
@@ -9204,27 +9205,27 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>University of Skövde</t>
+          <t>Umeå University</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Skövde (شوده) — Sweden Game Arena</t>
+          <t>Umeå (اومئو) — شمال سوئد</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>ارزان — SEK 9,500–11,500</t>
+          <t>ارزان تا متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science (120 cr)</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -9234,17 +9235,17 @@
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>SEK 135,000</t>
+          <t>SEK 152,300</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>$13,600</t>
+          <t>$15,400</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط</t>
+          <t>کارشناسی CS/ریاضی</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -9254,27 +9255,27 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N86" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>ارزان؛ Skövde قطب بازی سوئد (Sweden Game Arena)</t>
+          <t>شمال سوئد، شهر دانشجویی ارزان؛ کل دوره SEK 304,600</t>
         </is>
       </c>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>https://www.his.se/en/education/</t>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
       </c>
     </row>
@@ -9289,27 +9290,27 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Mälardalen University (MDU)</t>
+          <t>University of Skövde</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
+          <t>Skövde (شوده) — Sweden Game Arena</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,000–12,000</t>
+          <t>ارزان — SEK 9,500–11,500</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>MSc Intelligent Embedded Systems</t>
+          <t>MSc Data Science (120 cr)</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -9319,7 +9320,7 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 135,000</t>
+          <t>SEK 135,000</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -9329,7 +9330,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -9349,17 +9350,17 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>ABB و Westinghouse در Västerås؛ رقم 2024/25</t>
+          <t>ارزان؛ Skövde قطب بازی سوئد (Sweden Game Arena)</t>
         </is>
       </c>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>https://www.mdu.se/en/malardalen-university/education</t>
+          <t>https://www.his.se/en/education/</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9390,12 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering</t>
+          <t>MSc Intelligent Embedded Systems</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -9414,7 +9415,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE</t>
+          <t>کارشناسی CS/EE</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -9434,10 +9435,14 @@
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P88" s="4" t="inlineStr"/>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="inlineStr">
+        <is>
+          <t>ABB و Westinghouse در Västerås؛ رقم 2024/25</t>
+        </is>
+      </c>
       <c r="Q88" s="8" t="inlineStr">
         <is>
           <t>https://www.mdu.se/en/malardalen-university/education</t>
@@ -9450,27 +9455,27 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (AAU)</t>
+          <t>Mälardalen University (MDU)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
+          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–9,500</t>
+          <t>متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (IT)</t>
+          <t>MSc Software Engineering</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -9485,31 +9490,32 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>≈ €14,910 (2025/26: €7,455 در ترم؛ نرخ ۲۰۲۶ روی سایت AAU منتشر نشده — mastersportal: €15,340)</t>
+          <t>≈ SEK 135,000</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>$17,000–17,500</t>
+          <t>$13,600</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>رسمی: حداقل ۱۵۰ ECTS دروس مرتبط با CS (برنامه‌نویسی ۱۵، مهندسی نرم‌افزار ۵، الگوریتم ۵، پایگاه داده ۵، ریاضیات گسسته ۵)؛ از ورودی ۲۰۲۷ سابقهٔ کار و انگیزه‌نامه هم در رتبه‌بندی حساب می‌شود</t>
+          <t>کارشناسی CS/SE</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>6.5 (هر بخش ≥ 6.0)</t>
-        </is>
-      </c>
-      <c r="M89" s="4">
-        <f>329</f>
-        <v/>
-      </c>
-      <c r="N89" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -9517,14 +9523,10 @@
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P89" s="4" t="inlineStr">
-        <is>
-          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)؛ ظرفیت محدود</t>
-        </is>
-      </c>
+      <c r="P89" s="4" t="inlineStr"/>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+          <t>https://www.mdu.se/en/malardalen-university/education</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9556,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>MSc Software</t>
+          <t>MSc Computer Science (IT)</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -9569,7 +9571,7 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>≈ €14,910–15,340</t>
+          <t>≈ €14,910 (2025/26: €7,455 در ترم؛ نرخ ۲۰۲۶ روی سایت AAU منتشر نشده — mastersportal: €15,340)</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -9579,12 +9581,12 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی SE/CS</t>
+          <t>رسمی: حداقل ۱۵۰ ECTS دروس مرتبط با CS (برنامه‌نویسی ۱۵، مهندسی نرم‌افزار ۵، الگوریتم ۵، پایگاه داده ۵، ریاضیات گسسته ۵)؛ از ورودی ۲۰۲۷ سابقهٔ کار و انگیزه‌نامه هم در رتبه‌بندی حساب می‌شود</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5 (هر بخش ≥ 6.0)</t>
         </is>
       </c>
       <c r="M90" s="4">
@@ -9601,10 +9603,14 @@
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P90" s="4" t="inlineStr"/>
+      <c r="P90" s="4" t="inlineStr">
+        <is>
+          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)؛ ظرفیت محدود</t>
+        </is>
+      </c>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/software</t>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
         </is>
       </c>
     </row>
@@ -9624,22 +9630,22 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen – Sydhavn (کپنهاگ؛ کمپوس AAU)</t>
+          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 10,000–12,500</t>
+          <t>متوسط — DKK 8,000–9,500</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Cyber Security</t>
+          <t>MSc Software</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -9659,7 +9665,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE مرتبط؛ مهلت ۱ مارس</t>
+          <t>کارشناسی SE/CS</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -9678,17 +9684,13 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
-        </is>
-      </c>
-      <c r="P91" s="4" t="inlineStr">
-        <is>
-          <t>کمپوس کپنهاگ: اجاره بالاتر ولی بازار کار بزرگ</t>
-        </is>
-      </c>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P91" s="4" t="inlineStr"/>
       <c r="Q91" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/cyber-security/</t>
+          <t>https://www.en.aau.dk/education/master/software</t>
         </is>
       </c>
     </row>
@@ -9708,22 +9710,22 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Aalborg یا Copenhagen (هر دو کمپوس)</t>
+          <t>Copenhagen – Sydhavn (کپنهاگ؛ کمپوس AAU)</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>متوسط (Aalborg) تا خیلی گران (Copenhagen)</t>
+          <t>خیلی گران — DKK 10,000–12,500</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>MSc Medialogy</t>
+          <t>MSc Eng Cyber Security</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -9743,7 +9745,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط (Medialogy، CS، Media Tech)</t>
+          <t>کارشناسی CS/EE مرتبط؛ مهلت ۱ مارس</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -9762,17 +9764,17 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>تعامل، AR/VR، بازی؛ بین HCI و Game</t>
+          <t>کمپوس کپنهاگ: اجاره بالاتر ولی بازار کار بزرگ</t>
         </is>
       </c>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/medialogy-aal</t>
+          <t>https://www.en.aau.dk/education/master/cyber-security/</t>
         </is>
       </c>
     </row>
@@ -9787,27 +9789,27 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+          <t>Aalborg یا Copenhagen (هر دو کمپوس)</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–10,000</t>
+          <t>متوسط (Aalborg) تا خیلی گران (Copenhagen)</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Medialogy</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -9817,17 +9819,17 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>€17,300 (از ورودی سپتامبر ۲۰۲۶؛ قبلاً €13,900)</t>
+          <t>≈ €14,910–15,340</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>$19,700</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>≥ ۱۰۰ ECTS دروس CS؛ ظرفیت محدود + آزمون</t>
+          <t>کارشناسی مرتبط (Medialogy، CS، Media Tech)</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -9836,7 +9838,7 @@
         </is>
       </c>
       <c r="M93" s="4">
-        <f>283</f>
+        <f>329</f>
         <v/>
       </c>
       <c r="N93" s="10" t="inlineStr">
@@ -9846,17 +9848,17 @@
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>⚠️ افزایش شهریهٔ ۲۰۲۶ — جدول اصلی اصلاح شد</t>
+          <t>تعامل، AR/VR، بازی؛ بین HCI و Game</t>
         </is>
       </c>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
+          <t>https://www.en.aau.dk/education/master/medialogy-aal</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9888,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Software Engineering</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -9901,7 +9903,7 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>€17,300</t>
+          <t>€17,300 (از ورودی سپتامبر ۲۰۲۶؛ قبلاً €13,900)</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -9911,7 +9913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی SE/CS</t>
+          <t>≥ ۱۰۰ ECTS دروس CS؛ ظرفیت محدود + آزمون</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -9935,12 +9937,12 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>گرایش‌های Interactive Tech &amp; Games، Cyber-security &amp; Data Intelligence</t>
+          <t>⚠️ افزایش شهریهٔ ۲۰۲۶ — جدول اصلی اصلاح شد</t>
         </is>
       </c>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/softwareengineering</t>
+          <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
         </is>
       </c>
     </row>
@@ -9970,12 +9972,12 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Eng Software Engineering</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -9995,7 +9997,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI</t>
+          <t>کارشناسی SE/CS</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -10014,17 +10016,17 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>شروع سپتامبر و فوریه</t>
+          <t>گرایش‌های Interactive Tech &amp; Games، Cyber-security &amp; Data Intelligence</t>
         </is>
       </c>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/studyscience</t>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/softwareengineering</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10056,12 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Robot Systems</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -10079,7 +10081,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط (CS/EE/Mechatronics)</t>
+          <t>کارشناسی CS/AI</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -10098,17 +10100,17 @@
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>Odense Robotics cluster (Universal Robots، MiR)</t>
+          <t>شروع سپتامبر و فوریه</t>
         </is>
       </c>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
+          <t>https://www.sdu.dk/en/studyscience</t>
         </is>
       </c>
     </row>
@@ -10128,22 +10130,22 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Kolding (کولدینگ) — جنوب یوتلند</t>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>ارزان تا متوسط — DKK 7,500–9,000</t>
+          <t>متوسط — DKK 8,000–10,000</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science</t>
+          <t>MSc Eng Robot Systems</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -10163,7 +10165,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی با محتوای کمی/برنامه‌نویسی</t>
+          <t>کارشناسی مرتبط (CS/EE/Mechatronics)</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -10182,10 +10184,14 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P97" s="4" t="inlineStr"/>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="P97" s="4" t="inlineStr">
+        <is>
+          <t>Odense Robotics cluster (Universal Robots، MiR)</t>
+        </is>
+      </c>
       <c r="Q97" s="8" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
@@ -10203,27 +10209,27 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen (ITU)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen (کپنهاگ)</t>
+          <t>Kolding (کولدینگ) — جنوب یوتلند</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 10,000–12,500</t>
+          <t>ارزان تا متوسط — DKK 7,500–9,000</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>MSc Games — track Game Technology</t>
+          <t>MSc Data Science</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -10233,17 +10239,17 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>€16,500 (€8,250 در ترم؛ ورودی ۲۰۲۶ — رسمی)</t>
+          <t>€17,300</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>$18,800</t>
+          <t>$19,700</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>برای track فنی: کارشناسی CS</t>
+          <t>کارشناسی با محتوای کمی/برنامه‌نویسی</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -10251,10 +10257,9 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M98" s="4" t="inlineStr">
-        <is>
-          <t>— (تخصصی)</t>
-        </is>
+      <c r="M98" s="4">
+        <f>283</f>
+        <v/>
       </c>
       <c r="N98" s="10" t="inlineStr">
         <is>
@@ -10263,17 +10268,13 @@
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
-        </is>
-      </c>
-      <c r="P98" s="4" t="inlineStr">
-        <is>
-          <t>شناخته‌شده‌ترین ارشد بازی اسکاندیناوی؛ Copenhagen (IO Interactive، Unity Copenhagen)</t>
-        </is>
-      </c>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P98" s="4" t="inlineStr"/>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10304,12 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Games — track Game Technology</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -10318,7 +10319,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>€16,500 (€8,250 در ترم)</t>
+          <t>€16,500 (€8,250 در ترم؛ ورودی ۲۰۲۶ — رسمی)</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -10328,7 +10329,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE با برنامه‌نویسی قابل توجه</t>
+          <t>برای track فنی: کارشناسی CS</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -10348,12 +10349,12 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌تر از DTU/KU در کپنهاگ؛ رقم قدیمی €13,400 (پورتال studyindenmark) منسوخ است</t>
+          <t>شناخته‌شده‌ترین ارشد بازی اسکاندیناوی؛ Copenhagen (IO Interactive، Unity Copenhagen)</t>
         </is>
       </c>
       <c r="Q99" s="8" t="inlineStr">
@@ -10388,12 +10389,12 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -10413,7 +10414,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط با داده/CS</t>
+          <t>کارشناسی CS/SE با برنامه‌نویسی قابل توجه</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -10433,10 +10434,14 @@
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P100" s="4" t="inlineStr"/>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P100" s="4" t="inlineStr">
+        <is>
+          <t>ارزان‌تر از DTU/KU در کپنهاگ؛ رقم قدیمی €13,400 (پورتال studyindenmark) منسوخ است</t>
+        </is>
+      </c>
       <c r="Q100" s="8" t="inlineStr">
         <is>
           <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
@@ -10454,27 +10459,27 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Technical University of Denmark (DTU)</t>
+          <t>IT University of Copenhagen (ITU)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+          <t>Copenhagen (کپنهاگ)</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 9,500–12,000</t>
+          <t>خیلی گران — DKK 10,000–12,500</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Human-Centered Artificial Intelligence</t>
+          <t>MSc Data Science</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -10484,17 +10489,17 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>€15,000</t>
+          <t>€16,500 (€8,250 در ترم)</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>$17,100</t>
+          <t>$18,800</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>ظرفیت محدود؛ امتیازدهی: معدل ۶۰٪ + سابقهٔ کار ۱۰٪</t>
+          <t>کارشناسی مرتبط با داده/CS</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -10504,27 +10509,23 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="N101" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>— (تخصصی)</t>
+        </is>
+      </c>
+      <c r="N101" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
-        </is>
-      </c>
-      <c r="P101" s="4" t="inlineStr">
-        <is>
-          <t>معدل ۱۵.۷۷ در رقابت DTU ضعیف است</t>
-        </is>
-      </c>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr"/>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/human-centered-artificial-intelligence</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
@@ -10554,12 +10555,12 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Autonomous Systems</t>
+          <t>MSc Eng Human-Centered Artificial Intelligence</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -10579,7 +10580,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>۸۰–۹۰ ECTS دروس مرتبط؛ ظرفیت محدود</t>
+          <t>ظرفیت محدود؛ امتیازدهی: معدل ۶۰٪ + سابقهٔ کار ۱۰٪</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -10599,13 +10600,17 @@
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
-        </is>
-      </c>
-      <c r="P102" s="4" t="inlineStr"/>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P102" s="4" t="inlineStr">
+        <is>
+          <t>معدل ۱۵.۷۷ در رقابت DTU ضعیف است</t>
+        </is>
+      </c>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/human-centered-artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -10635,12 +10640,12 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Computer Science and Engineering</t>
+          <t>MSc Eng Autonomous Systems</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -10660,7 +10665,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>ظرفیت محدود؛ گزینش با معدل</t>
+          <t>۸۰–۹۰ ECTS دروس مرتبط؛ ظرفیت محدود</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -10680,13 +10685,13 @@
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr"/>
       <c r="Q103" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/computer-science-and-engineering</t>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
       </c>
     </row>
@@ -10701,131 +10706,212 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
+          <t>Technical University of Denmark (DTU)</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 9,500–12,000</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>€15,000</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>ظرفیت محدود؛ گزینش با معدل</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N104" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P104" s="4" t="inlineStr"/>
+      <c r="Q104" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/computer-science-and-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
           <t>Aarhus University (AU)</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>Aarhus (آرهوس) — دومین شهر دانمارک</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>گران — DKK 9,000–11,000</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="H105" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr">
+      <c r="I105" s="4" t="inlineStr">
         <is>
           <t>€17,300</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr">
+      <c r="J105" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="K104" s="4" t="inlineStr">
+      <c r="K105" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS با واحدهای مشخص</t>
         </is>
       </c>
-      <c r="L104" s="4" t="inlineStr">
+      <c r="L105" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="M104" s="4" t="inlineStr">
+      <c r="M105" s="4" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="N104" s="11" t="inlineStr">
+      <c r="N105" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="O104" s="4" t="inlineStr">
+      <c r="O105" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P104" s="4" t="inlineStr">
+      <c r="P105" s="4" t="inlineStr">
         <is>
           <t>Aarhus: دومین شهر، ارزان‌تر از کپنهاگ</t>
         </is>
       </c>
-      <c r="Q104" s="8" t="inlineStr">
+      <c r="Q105" s="8" t="inlineStr">
         <is>
           <t>https://masters.au.dk/computerscience</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="34" customHeight="1">
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>راهنما: هر ردیف یک برنامهٔ انگلیسی‌زبان است. Safe/Target/Reach نسبت به معدل ۱۵.۷۷/۲۰ (≈ 2:2 بریتانیا / ≈ 2.3 آلمانی / ≈ ۷۹٪) و IELTS ≈ 7 سنجیده شده و پیش‌بینی پذیرش نیست. «≈» یعنی رقم از منبع ثانویه یا سال قبل است — قبل از اقدام صفحهٔ رسمی را چک کنید.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="34" customHeight="1">
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>شهریهٔ دلاری با نرخ نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21 و گرد شده به $100. برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 ملاک است (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪؛ TU/e و Surrey و Gothenburg همین حالا رسمی‌اند). آلمان: عدد فقط سهم ترم (Semesterbeitrag) است که بلیت حمل‌ونقل را هم شامل می‌شود.</t>
+          <t>راهنما: هر ردیف یک برنامهٔ انگلیسی‌زبان است. Safe/Target/Reach نسبت به معدل ۱۵.۷۷/۲۰ (≈ 2:2 بریتانیا / ≈ 2.3 آلمانی / ≈ ۷۹٪) و IELTS ≈ 7 سنجیده شده و پیش‌بینی پذیرش نیست. «≈» یعنی رقم از منبع ثانویه یا سال قبل است — قبل از اقدام صفحهٔ رسمی را چک کنید.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="34" customHeight="1">
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>امتیاز بازار کار (۱–۵) ارزیابی من بر پایهٔ منابع شیت «حوزه‌ها و بازار کار» است، نه آمار رسمی؛ برای هر برنامه فقط حوزه را نشان می‌دهد، نه کیفیت آن دانشگاه.</t>
+          <t>شهریهٔ دلاری با نرخ نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21 و گرد شده به $100. برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 ملاک است (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪؛ TU/e و Surrey و Gothenburg همین حالا رسمی‌اند). آلمان: عدد فقط سهم ترم (Semesterbeitrag) است که بلیت حمل‌ونقل را هم شامل می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="34" customHeight="1">
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>ستون «هزینهٔ زندگی شهر» برآورد تقریبی هزینهٔ ماهانهٔ دانشجو با اجارهٔ اتاق در همان شهر است (سازگار با ردیف ۶ جدول اصلی)؛ برچسب‌ها: ارزان / متوسط / گران / خیلی گران. برای مقایسهٔ کشورها همچنان ردیف‌های ۶–۸ جدول اصلی معیار است.</t>
+          <t>امتیاز بازار کار (۱–۵) ارزیابی من بر پایهٔ منابع شیت «حوزه‌ها و بازار کار» است، نه آمار رسمی؛ برای هر برنامه فقط حوزه را نشان می‌دهد، نه کیفیت آن دانشگاه.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="34" customHeight="1">
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>بازبینی صحت اعداد (۲۷ سپتامبر ۲۰۲۶): ≈۷۰٪ شهریه‌ها مستقیماً از صفحهٔ رسمی 2026/27 است؛ ردیف‌های «≈» از منبع ثانویه یا سال قبل‌اند. اصلاح‌های این بازبینی: FAU از تابستان ۲۰۲۷ شهریه می‌گیرد (AI/CS €4,000/ترم)؛ ITU €16,500 (نه €13,400)؛ Radboud €19,714 رسمی؛ Chalmers ≈ SEK 175k (نه 160k)؛ KTH ≈ 180–190k؛ AAU شرط ≥ ۱۵۰ ECTS؛ Surrey Cyber ورودی ۲۰۲۷؛ Newcastle Games 2:2؛ Sheffield AI ≈ £32.9–34.3k. رتبه‌بندی Safe/Target/Reach، امتیاز بازار و ردهٔ هزینهٔ شهر ارزیابی‌اند، نه دادهٔ رسمی.</t>
+          <t>ستون «هزینهٔ زندگی شهر» برآورد تقریبی هزینهٔ ماهانهٔ دانشجو با اجارهٔ اتاق در همان شهر است (سازگار با ردیف ۶ جدول اصلی)؛ برچسب‌ها: ارزان / متوسط / گران / خیلی گران. برای مقایسهٔ کشورها همچنان ردیف‌های ۶–۸ جدول اصلی معیار است.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="34" customHeight="1">
       <c r="B111" s="13" t="inlineStr">
         <is>
+          <t>بازبینی صحت اعداد (۲۷ سپتامبر ۲۰۲۶): ≈۷۰٪ شهریه‌ها مستقیماً از صفحهٔ رسمی 2026/27 است؛ ردیف‌های «≈» از منبع ثانویه یا سال قبل‌اند. اصلاح‌های این بازبینی: FAU از تابستان ۲۰۲۷ شهریه می‌گیرد (AI/CS €4,000/ترم)؛ ITU €16,500 (نه €13,400)؛ Radboud €19,714 رسمی؛ Chalmers ≈ SEK 175k (نه 160k)؛ KTH ≈ 180–190k؛ AAU شرط ≥ ۱۵۰ ECTS؛ Surrey Cyber ورودی ۲۰۲۷؛ Newcastle Games 2:2؛ Sheffield AI ≈ £32.9–34.3k. رتبه‌بندی Safe/Target/Reach، امتیاز بازار و ردهٔ هزینهٔ شهر ارزیابی‌اند، نه دادهٔ رسمی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="34" customHeight="1">
+      <c r="B112" s="13" t="inlineStr">
+        <is>
           <t>حذف‌شده‌ها: Essex MSc Computer Games (برای 2025/26 و 2026/27 تعلیق شده)، Hull AI &amp; Data Science (سه رقم متناقض شهریه)، UCD/TCD (2:1 و ≈ €30k → Reach، بررسی نشد)، KU Copenhagen (شهریه تأیید نشد)؛ ایرلند (۱۲ برنامه) به خواست شما در سپتامبر ۲۰۲۶ کامل حذف و ۱۳ برنامهٔ سوئیس جایگزین شد. سوئیس: شهریه‌های ETH، EPFL، UZH، USI، ZHAW و HSLU از صفحات رسمی 2026/27؛ Bern، Fribourg و Basel از مراجع ثانویه (≈) — و یادتان باشد در سوئیس شهریه عدد کوچک است، هزینهٔ زندگی (CHF 1,400–2,500/ماه) و تمکن CHF 21,000 عدد اصلی‌اند.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q104"/>
+  <autoFilter ref="A1:Q105"/>
   <mergeCells count="6">
     <mergeCell ref="B111:Q111"/>
     <mergeCell ref="B107:Q107"/>
     <mergeCell ref="B108:Q108"/>
     <mergeCell ref="B110:Q110"/>
-    <mergeCell ref="B106:Q106"/>
     <mergeCell ref="B109:Q109"/>
+    <mergeCell ref="B112:Q112"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
@@ -10931,6 +11017,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q105" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11444,7 +11531,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>فرم بورس UTS Twente (۱۵ اکتبر)، سوئد universityadmissions.se (۱۶ اکتبر — تا ۴ برنامه با یک درخواست، SEK 900). پورتال‌های سوئیس (USI، Bern، Basel، UZH، ZHAW، HSLU) از حدود اکتبر–ژانویه برای پاییز ۲۰۲۷ باز می‌شوند.</t>
+          <t>فرم بورس UTS Twente (۱۵ اکتبر)، سوئد universityadmissions.se (۱۶ اکتبر — تا ۴ برنامه با یک درخواست، SEK 900). پورتال‌های سوئیس (USI، Neuchâtel، Fribourg، Bern، Basel، UZH، ZHAW، HSLU) از حدود اکتبر–ژانویه برای پاییز ۲۰۲۷ باز می‌شوند.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11714,7 +11801,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>انگلستان rolling است ولی زود اپلای کنید: بورس‌ها (Brunel، Northumbria) و ظرفیت‌ها زود پر می‌شود. سوئیس: پرونده‌های USI (Informatics / AI / Software &amp; Data Eng)، Bern، Basel، HSLU و ZHAW را همین ماه‌ها بفرستید تا قبل از مهلت ۳۰ آوریل بررسی شوند؛ ریزنمرات و دانشنامه باید ترجمهٔ رسمی/تأییدشده باشند.</t>
+          <t>انگلستان rolling است ولی زود اپلای کنید: بورس‌ها (Brunel، Northumbria) و ظرفیت‌ها زود پر می‌شود. سوئیس: پرونده‌های USI (Informatics / AI / Software &amp; Data Eng)، Neuchâtel/Bern، Basel و ZHAW را همین ماه‌ها بفرستید تا قبل از مهلت ۳۰ آوریل بررسی شوند (HSLU: ویزایی‌ها تا ۱ آوریل)؛ ریزنمرات و دانشنامه باید ترجمهٔ رسمی/تأییدشده باشند.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11763,12 +11850,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>هلند، آلمان</t>
+          <t>هلند، آلمان، سوئیس</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Radboud غیر-EU (اپلای اصلی)؛ بورس UTS Twente؛ پنجرهٔ Passau AI Engineering باز می‌شود (۱ آوریل – ۳۱ می).</t>
+          <t>Radboud غیر-EU (اپلای اصلی)؛ بورس UTS Twente؛ HSLU Applied Data Science &amp; AI — مهلت رسمی متقاضیان ویزا (Swiss/EU تا ۱ ژوئن)؛ پنجرهٔ Passau AI Engineering باز می‌شود (۱ آوریل – ۳۱ می).</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11849,7 +11936,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>USI (Informatics / AI / Software &amp; Data Engineering — مهلت غیر-EU)، Bern (Joint MSc CS؛ ویزایی‌ها مهلت دیرهنگام ندارند)، Basel، ZHAW MSE (پایان آوریل)؛ HSLU ≈ همین حدود (چک شود). پاسخ‌ها می–ژوئن؛ بلافاصله وقت ویزای D را در سفارت تهران بگیرید — تصمیم با ادارهٔ مهاجرت کانتون، ۸–۱۲ هفته؛ برای Ticino/Bern/Fribourg/Lucerne قبلش نوع مدرک تمکن قابل قبول را بپرسید.</t>
+          <t>USI (Informatics / AI / Software &amp; Data Engineering — مهلت غیر-EU)، Neuchâtel و Bern (Joint MSc CS؛ Neuchâtel: خارجی‌ها تا ۳۱ مارس بفرستند؛ ویزایی‌ها مهلت دیرهنگام ندارند)، Basel (رسمی)، ZHAW MSE (پایان آوریل)؛ HSLU زودتر است: ۱ آوریل. پاسخ‌ها می–ژوئن؛ بلافاصله وقت ویزای D را در سفارت تهران بگیرید — تصمیم با ادارهٔ مهاجرت کانتون، ۸–۱۲ هفته؛ برای Ticino/Neuchâtel/Fribourg/Bern/Lucerne قبلش نوع مدرک تمکن قابل قبول را بپرسید.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11984,7 +12071,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Twente/Radboud اتاق رزروشده برای بین‌المللی‌ها (مهلت‌دار)؛ Linköping یک پیشنهاد اتاق برای شهریه‌پردازها؛ آلمان لیست Studierendenwerk بلافاصله بعد از پذیرش؛ انگلستان خوابگاه دانشگاه زود پر می‌شود؛ سوئیس: WOKO/Juwo زوریخ و FMEL لوزان لیست انتظار طولانی — روز پذیرش ثبت‌نام کنید؛ Lugano/Fribourg/Bern/Lucerne آسان‌تر.</t>
+          <t>Twente/Radboud اتاق رزروشده برای بین‌المللی‌ها (مهلت‌دار)؛ Linköping یک پیشنهاد اتاق برای شهریه‌پردازها؛ آلمان لیست Studierendenwerk بلافاصله بعد از پذیرش؛ انگلستان خوابگاه دانشگاه زود پر می‌شود؛ سوئیس: WOKO/Juwo زوریخ و FMEL لوزان لیست انتظار طولانی — روز پذیرش ثبت‌نام کنید؛ Lugano/Fribourg/Neuchâtel/Bern/Lucerne آسان‌تر.</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12068,7 +12155,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>آلمان $27–36k  &lt;  انگلستان $38–65k (۱ سال)  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k. سوئیس گسترده‌ترین بازه را دارد: $35–84k — Bern/Fribourg (۱.۵ سال) $35–47k کنار انگلستان، UZH $45–58k، HSLU $53–64k، USI/EPFL $60–75k، ETH $66–84k کنار هلند</t>
+          <t>آلمان $27–36k  &lt;  انگلستان $38–65k (۱ سال)  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k. سوئیس گسترده‌ترین بازه را دارد: $35–84k — Neuchâtel/Fribourg (۱.۵ سال) $35–47k کنار انگلستان، Bern $39–51k، UZH $45–58k، HSLU $53–64k، USI/EPFL $60–75k، ETH $66–84k کنار هلند</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12191,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ = سوئیس ۱۸ › دانمارک ۱۶.  با حذف ایرلند، هیچ کشوری هر سه معیار را با هم نمی‌دهد: آلمان ارزان‌ترین (ولی آلمانی)، انگلستان تنها گزینهٔ کاملاً انگلیسی (ولی گران و بازار جونیور ضعیف)، سوئیس بالاترین حقوق (ولی گران‌ترین زندگی، ۶ ماه فرصت کار، زبان محلی برای PR). پیشنهاد: ۲ برنامه آلمان (Stuttgart + Passau/Saarland) + ۲ برنامه سوئیس با شانس واقعی (USI Lugano + HSLU یا Bern/Fribourg) + ۱–۲ گزینهٔ ارزان انگلستان (Teesside/Northumbria) به‌عنوان مسیر تماماً انگلیسی؛ ETH/EPFL فقط اگر حاضرید CHF 150 را برای یک شانس کم خرج کنید. تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در بهار ۲۰۲۷.</t>
+          <t>آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ = سوئیس ۱۸ › دانمارک ۱۶.  با حذف ایرلند، هیچ کشوری هر سه معیار را با هم نمی‌دهد: آلمان ارزان‌ترین (ولی آلمانی)، انگلستان تنها گزینهٔ کاملاً انگلیسی (ولی گران و بازار جونیور ضعیف)، سوئیس بالاترین حقوق (ولی گران‌ترین زندگی، ۶ ماه فرصت کار، زبان محلی برای PR). پیشنهاد: ۲ برنامه آلمان (Stuttgart + Passau/Saarland) + ۲ برنامه سوئیس با شانس واقعی (USI Lugano + HSLU یا Joint MSc CS در Neuchâtel/Fribourg) + ۱–۲ گزینهٔ ارزان انگلستان (Teesside/Northumbria) به‌عنوان مسیر تماماً انگلیسی؛ ETH/EPFL فقط اگر حاضرید CHF 150 را برای یک شانس کم خرج کنید. تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در بهار ۲۰۲۷.</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12215,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>اکتبر ۲۰۲۶: نظام‌وظیفه + رزرو IELTS خارج از ایران + مدارک · ۱۶ اکتبر: باز شدن سوئد · ۱–۳۰ نوامبر: پنجرهٔ ETH (Reach) · نوامبر–دسامبر: IELTS + VPD uni-assist · ۱۵ دسامبر: دور اول EPFL · ۱۵ ژانویه ۲۰۲۷: مهلت سوئد / AAU / Stuttgart · ۱ فوریه: مدارک سوئد + SDU · ۲۸ فوریه: UZH و Fribourg (ویزایی‌ها) · فوریه–مارس: انگلستان + پرونده‌های سوئیس · ۱ آوریل: Radboud · ۳۰ آوریل: USI / Bern / Basel / ZHAW · ۱ می: Twente · ۳۱ می: Passau · می–ژوئن: پول (سوئیس CHF 21,000 + شهریه) + ویزا یا برنامهٔ B · اوت–اکتبر: شروع (سوئیس اواسط سپتامبر).</t>
+          <t>اکتبر ۲۰۲۶: نظام‌وظیفه + رزرو IELTS خارج از ایران + مدارک · ۱۶ اکتبر: باز شدن سوئد · ۱–۳۰ نوامبر: پنجرهٔ ETH (Reach) · نوامبر–دسامبر: IELTS + VPD uni-assist · ۱۵ دسامبر: دور اول EPFL · ۱۵ ژانویه ۲۰۲۷: مهلت سوئد / AAU / Stuttgart · ۱ فوریه: مدارک سوئد + SDU · ۲۸ فوریه: UZH و Fribourg (ویزایی‌ها) · فوریه–مارس: انگلستان + پرونده‌های سوئیس · ۱ آوریل: Radboud + HSLU (ویزایی‌ها) · ۳۰ آوریل: USI / Neuchâtel / Bern / Basel / ZHAW · ۱ می: Twente · ۳۱ می: Passau · می–ژوئن: پول (سوئیس CHF 21,000 + شهریه) + ویزا یا برنامهٔ B · اوت–اکتبر: شروع (سوئیس اواسط سپتامبر).</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B150"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12832,1186 +12919,1282 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Bern شهریه CHF 750 + 200 خارجی (≈)؛ Fribourg CHF 870 + 115، مهلت ویزایی ۲۸ فوریه (≈)</t>
+          <t>سوئیس – Bern شهریه از پاییز ۲۰۲۶: CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها + 34 + 25 در ترم (رسمی)</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>https://www.mastersportal.com/studies/12191/computer-science.html</t>
+          <t>https://www.unibe.ch/studies/organizational_matters/renewal_of_semester_registration/fees/index_eng.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Bern: مهلت ۳۰ آوریل؛ ویزایی‌ها از مهلت دیرهنگام محروم‌اند (راهنمای ۲۰۲۶)</t>
+          <t>سوئیس – Joint MSc CS (Bern/Neuchâtel/Fribourg) FAQ رسمی: بدون آزمون زبان (B2 توصیه)، شرط کارشناسی CS یا معادل با حداکثر ۶۰ ECTS تکمیلی، مهلت‌های دیرهنگام</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>https://www.libertify.com/universities/university-of-bern-international-admissions-guide/</t>
+          <t>https://mcs.unibnf.ch/faq/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
+          <t>سوئیس – Neuchâtel شهریهٔ خارجی‌ها CHF 790/ترم (رسمی)</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
+          <t>https://www.unine.ch/admission/taxes-universitaires/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
+          <t>سوئیس – Neuchâtel مهلت ارشد ۳۰ آوریل؛ خارجی‌ها یک ماه زودتر؛ هزینهٔ پرونده CHF 100 (رسمی)</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
+          <t>https://www.unine.ch/admission/admission-master/delais-et-frais-dinscription-pour-les-masters/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
+          <t>سوئیس – Fribourg شهریهٔ خارجی‌ها CHF 870 + 115 = 985/ترم (رسمی)</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
+          <t>https://www.unifr.ch/studies/en/organisation/administrative-services-unifr-students/university-fees/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
+          <t>سوئیس – Fribourg مهلت ارشد با مدرک خارجی: ویزایی‌ها ۱–۲۸ فوریه، بقیه تا ۳۰ آوریل (رسمی)</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
+          <t>https://www.unifr.ch/studies/en/admission/admission-master/admission-master-foreign.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
+          <t>سوئیس – Basel MSc CS: 90 ECTS، انگلیسی، مهلت ۳۰ آوریل / ۳۰ نوامبر (رسمی)</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
+          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
+          <t>سوئیس – Basel شهریه CHF 850/ترم برای همه + CHF 100 هزینهٔ درخواست (Uni Info 2026/27)</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
+          <t>https://www.unibas.ch/dam/jcr:28672e66-8562-4988-9e38-b1c944ed22bf/COMPUTER%20SCIENCE%202026.2026-02-05-09-53-32.pdf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
+          <t>سوئیس – HSLU MSc Applied Data Science and AI (نام جدید): مهلت ویزایی‌ها ۱ آوریل، CHF 1,300/ترم خارجی، CHF 250 درخواست، 120 ECTS (رسمی)</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
+          <t>سوئیس – USI مهلت‌های 2026/27: غیر-EU ۳۰ آوریل؛ هزینهٔ پرونده CHF 100 برای مدارک خارج از کنوانسیون لیسبون (رسمی)</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
+          <t>https://www.usi.ch/en/education/master/informatics/application</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
+          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
+          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
+          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
+          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
+          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
+          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
+          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
+          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
+          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
+          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
+          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
+          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
+          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
+          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
+          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
+          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
+          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
+          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
+          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
         </is>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
+          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
+          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
+          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
+          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
+          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
+          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
+          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
+          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
         </is>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
+          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
+          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
+          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
+          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
         </is>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
+          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
+          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
+          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
+          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
         </is>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
+          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
+          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
         </is>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
+          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
+          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
+          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
+          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
+          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
+          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
+          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – وضعیت VAC تهران</t>
+          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
         </is>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – TU Dresden</t>
+          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
         </is>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Stuttgart</t>
+          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
+          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Newcastle 149</t>
+          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
         </is>
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
+          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – York =158</t>
+          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
         </is>
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/about/rankings/</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Leicester =314</t>
+          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
         </is>
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/university-leicester</t>
+          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Essex =438</t>
+          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
         </is>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/essex-university</t>
+          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Northumbria =528</t>
+          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
         </is>
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
+          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Brunel</t>
+          <t>بریتانیا – وضعیت VAC تهران</t>
         </is>
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
+          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – سایر</t>
+          <t>QS WUR 2027 – TU Dresden</t>
         </is>
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/world-university-rankings</t>
+          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
+          <t>QS WUR 2027 – Stuttgart</t>
         </is>
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
+          <t>QS WUR 2027 – Newcastle 149</t>
         </is>
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>https://www.xe.com/</t>
+          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
+          <t>QS WUR 2027 – York =158</t>
         </is>
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
+          <t>https://www.york.ac.uk/about/rankings/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
+          <t>QS WUR 2027 – Leicester =314</t>
         </is>
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
+          <t>https://www.topuniversities.com/universities/university-leicester</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
+          <t>QS WUR 2027 – Essex =438</t>
         </is>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>https://www.isc2.org/research</t>
+          <t>https://www.topuniversities.com/universities/essex-university</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
+          <t>QS WUR 2027 – Northumbria =528</t>
         </is>
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
+          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
+          <t>QS WUR 2027 – Brunel</t>
         </is>
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
+          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
+          <t>QS WUR 2027 – سایر</t>
         </is>
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
+          <t>https://www.topuniversities.com/world-university-rankings</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
+          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
         </is>
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
+          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+          <t>https://www.xe.com/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
+          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
         </is>
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Siegen MSc HCI (DAAD)</t>
+          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
         </is>
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
+          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
         </is>
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+          <t>https://www.isc2.org/research</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>آلمان – RWTH MSc Software Systems Engineering</t>
+          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
         </is>
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
+          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
         </is>
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
+          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
         </is>
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
+          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
         </is>
       </c>
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
+          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
         </is>
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>هلند – Leiden CS 2026/27: €22,500</t>
+          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
         </is>
       </c>
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>هلند – Groningen AI 2026/27: €24,900</t>
+          <t>آلمان – Siegen MSc HCI (DAAD)</t>
         </is>
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
+          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
         </is>
       </c>
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
+          <t>آلمان – RWTH MSc Software Systems Engineering</t>
         </is>
       </c>
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
+          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
         </is>
       </c>
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
+          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
         </is>
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Umeå AI: SEK 152,300</t>
+          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
         </is>
       </c>
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
+          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
         </is>
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>https://www.study.eu/best-universities/sweden</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
+          <t>هلند – Leiden CS 2026/27: €22,500</t>
         </is>
       </c>
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
+          <t>هلند – Groningen AI 2026/27: €24,900</t>
         </is>
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
+          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
         </is>
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus CS €17,300</t>
+          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
         </is>
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>https://masters.au.dk/computerscience</t>
+          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
+          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
         </is>
       </c>
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
+          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
         </is>
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
+          <t>سوئد – Umeå AI: SEK 152,300</t>
         </is>
       </c>
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
+          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
         </is>
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
+          <t>https://www.study.eu/best-universities/sweden</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
+          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
         </is>
       </c>
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
+          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
         </is>
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
+          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
+          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
         </is>
       </c>
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – NTU QS 2027 =639</t>
+          <t>دانمارک – Aarhus CS €17,300</t>
         </is>
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
+          <t>https://masters.au.dk/computerscience</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
+          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
         </is>
       </c>
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
+          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
+          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
         </is>
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
+          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
+          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
         </is>
       </c>
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
+          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
+          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
         </is>
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
+          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
         </is>
       </c>
       <c r="B136" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
+          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
         </is>
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
+          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
         </is>
       </c>
       <c r="B138" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+          <t>انگلستان – NTU QS 2027 =639</t>
         </is>
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
         </is>
       </c>
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
         </is>
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
         </is>
       </c>
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>https://zandienglish.ir/toefl-in-iran/</t>
+          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
         </is>
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
         </is>
       </c>
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
         </is>
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
         </is>
       </c>
       <c r="B146" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
         </is>
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
         </is>
       </c>
       <c r="B148" s="16" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
         </is>
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
+          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>https://zandienglish.ir/toefl-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
           <t>هلند – Twente: مهلت غیر-EEA ۱ می ۲۰۲۷؛ بورس UTS ۱۵ اکتبر ۲۰۲۶ – ۱ آوریل ۲۰۲۷</t>
         </is>
       </c>
-      <c r="B150" s="16" t="inlineStr">
+      <c r="B158" s="16" t="inlineStr">
         <is>
           <t>https://collegedunia.com/netherlands/university/749-university-of-twente-enschede/admission</t>
         </is>
@@ -14168,6 +14351,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId157"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -875,46 +875,124 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>۵ب</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>بورس / تخفیف شهریهٔ واقعاً در دسترسِ شما (غیر-EU، معدل ۱۵.۷۷ ≈ ۷۹٪، ورودی ۲۰۲۷)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>شهریه‌ای نیست که تخفیف بخورد؛ بورس ارشد هم عملاً نیست:
+• Deutschlandstipendium: €300/ماه، بعد از ثبت‌نام، ≈ ۱–۳٪ دانشجویان
+• DAAD برای ارشد معمولی CS بورس ندارد (فقط فهرست توسعه‌محور EPOS)
+• Stuttgart (BW): قانون اجازهٔ معافیت حداکثر ۵٪ «استعدادهای ویژه» از €1,500/ترم را می‌دهد — سالانه اعلام می‌شود؛ FAU هنوز طرح معافیت برای شهریهٔ جدید نداده
+اثر روی هزینهٔ شما: ≈ صفر (از قبل ارزان‌ترین است)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>• NL Scholarship (سابقاً Holland): €5,000 یک‌بار در سال اول، از طریق دانشگاه‌های عضو؛ مهلت ۱ فوریه یا ۱ می (بسته به دانشگاه) — با معدل شما شدنی‌ترین
+• UTS Twente: €3,000–22,000/سال فقط برای «بهترین‌ها» (۱۵ اکتبر – ۱ آوریل) → Reach
+• Radboud Scholarship Programme: شهریه تا سطح EU (≈ €2,600) + ویزا/بیمه؛ ۳۱ ژانویه؛ بسیار رقابتی → Reach
+• TU/e ALSP، Utrecht/Leiden/UvA Excellence: ۱۰٪ بالای کلاس → نه
+اثر: حداکثر −€5k از $75–90k</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>قوی‌ترین کشور جدول، ولی درهای اصلی برای معدل ۷۹٪ نیمه‌باز است:
+• LiU: معمولاً ۵۰٪ شهریه، فقط اگر LiU اولویت ۱ باشد؛ ⚠️ از ۲۰۲۶ فقط GPA ≥ 3.5/4 یا «first/high second class» — معدل شما (≈ 3.1/4) احتمالاً زیر خط
+• Chalmers IPOET ۷۵٪ (≈ ۳۵ بورس؛ فرم جدا تا ۱۵ ژانویه): حداقل معدل ۸۰٪ — شما ۷۸.۹٪ = دقیقاً زیر خط
+• KTH Scholarship: شهریهٔ کامل، چند ده نفر، ۱ دسامبر – ۱۵ ژانویه → Reach
+• Halmstad ۲۵٪/۵۰٪ (پنجرهٔ ≈ ۹–۲۵ فوریه) و MDU تا ۱۰۰٪ (اولویت ۱؛ معدود) — واقع‌بینانه‌ترین‌ها برای شما
+• ⚠️ بورس دولتی SI: ایران جزو ۳۴ کشور واجد شرایط نیست
+اثر: با ۵۰٪ در Halmstad/MDU کل دوره از $54–65k به ≈ $40–48k می‌رسد — نزدیک به انگلستان</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Danish Government Scholarship = معافیت شهریه (+ گاهی کمک‌هزینه) که خودِ دانشگاه از سهمیهٔ دولتی می‌دهد؛ فرم جدا ندارد — همهٔ غیر-EUها خودکار بررسی می‌شوند:
+• AAU: ≈ ۱۵ بورس/سال = معافیت کامل + DKK 11,225/ماه (۲۰۲۶)
+• SDU: فقط بعضی ارشدهای مهندسی، معافیت کامل، معدود
+• ITU/DTU/Aarhus: تعداد کم، رقابتی
+شانس واقعی با معدل ۷۹٪: پایین؛ روی آن برنامه نریزید (خود AAU هم همین را می‌گوید)
+اثر روی برنامه‌ریزی: صفر مگر برنده شوید</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>• ETH Excellence (ESOP): معافیت + CHF 12,000/ترم؛ ≈ ۶۰ بورس؛ فقط ۱۰٪ بالای کلاس؛ همراه اپلای ۱–۳۰ نوامبر → با معدل شما نه
+• EPFL Excellence Fellowship: ≈ CHF 16,000/سال؛ درصد بالای کلاس → نه
+• USI: ۶۰ بورس یک‌بارهٔ CHF 4,000 (= نصف شهریهٔ سال اول) برای معدل ≥ ۸۰/۱۰۰ — شما ۷۸.۹ → مرزی؛ + ۲۰ بورس سال دوم برای بهترینِ هر برنامه
+• Neuchâtel/Fribourg/Bern/Basel/UZH/ZHAW/HSLU: بورس ارشد برای خارجی‌ها ندارند (کمک کانتونی فقط برای مقیم‌ها)
+• بورس دولت سوئیس (ESKAS): فقط دکترا/پژوهش
+اثر: ≈ صفر (مسئلهٔ سوئیس هزینهٔ زندگی است، نه شهریه)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>تخفیف‌های خودکار دانشگاهی (بدون فرم) — همین‌ها واقعی‌اند:
+• Essex: جدول کشوری؛ ایران با ≥ ۱۴/۲۰ → £4,500 تخفیف شهریه (شما واجد شرایط؛ جدول ۲۰۲۵–۲۶ — نسخهٔ ۲۰۲۶–۲۷ را چک کنید)
+• Teesside Global Excellence: £2,000 (صلاحدیدی؛ پیشنهاد تا ۳۰ آوریل)
+• Brunel VC Award: £6,000 فقط با معادل 2:1 (+ ودیعهٔ £5,000) — برای ایران معمولاً ≥ ۱۶/۲۰؛ برای شما مرزی، از پذیرش بپرسید
+• Northumbria £3,000: فقط فهرست کشوری/ادامه‌تحصیلی‌های داخل UK — ایران نه
+• Leicester/York: بورس‌های بین‌المللی محدود و رقابتی
+• ❌ Chevening: ۲ سال کار *بعد از* مدرک + تعهد بازگشت ۲ ساله — با فارغ‌التحصیلی ۲۰۲۶ و هدف مهاجرت نمی‌خواند · ❌ GREAT: ایران در فهرست نیست · ❌ Commonwealth
+اثر: Essex −$6k، Teesside −$2.6k از $38–65k</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>liu.se (Scholarships؛ شرط جدید ۲۰۲۶)؛ chalmers.se (IPOET ≥ ۸۰٪)؛ hh.se؛ mdu.se؛ si.se (۳۴ کشور)؛ NL Scholarship (Nuffic/studyinnl)؛ utwente.nl؛ ru.nl؛ en.aau.dk (Finance and fees: ≈ ۱۵ بورس، DKK 11,225/ماه)؛ sdu.dk؛ ethz.ch (ESOP)؛ epfl.ch؛ usi.ch / Fondazione per le Facoltà di Lugano؛ essex.ac.uk؛ tees.ac.uk؛ brunel.ac.uk؛ northumbria.ac.uk؛ chevening.org (Eligibility)؛ deutschlandstipendium.de — ⚠️ مبالغ چرخهٔ ۲۰۲۶/۲۷؛ برای ۲۰۲۷/۲۸ موقع اپلای دوباره ببینید. این ردیف امتیاز ردیف ۲۸ را عوض نمی‌کند (امتیازها با قیمت کامل حساب شده‌اند)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>۶</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>هزینه زندگی ماهانه واقعی دانشجو (و حداقل قانونی ویزا ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>€950–1,250 (Dresden/Erlangen ارزان‌تر؛ Stuttgart/Darmstadt گران‌تر)
 حداقل حساب مسدود: €992/ماه</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>€1,100–1,500 در Enschede/Nijmegen
 حداقل IND: €1,130.77/ماه</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SEK 10,700–13,000 (≈ €950–1,150)
 حداقل Migrationsverket: SEK 10,656/ماه</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>DKK 8,000–10,000 (≈ €1,070–1,340) در Aalborg/Odense
 حداقل SIRI: DKK 7,426/ماه</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Zürich: CHF 1,900–2,500 (≈ $2,300–3,000؛ اتاق WOKO CHF 500–900، اتاق خصوصی 800–1,200) · Lausanne: CHF 1,700–2,200
 Bern/Basel/Lucerne: CHF 1,550–2,100 · Lugano/Fribourg/Neuchâtel: CHF 1,350–1,800
 حداقل رسمی: CHF 21,000 در سال (Basel: 24,000)؛ کانتون زوریخ فقط حساب بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم سوئیس را می‌پذیرد</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>شمال انگلستان (Middlesbrough/Newcastle): £950–1,250
 Leicester/Colchester/York: £1,000–1,350
@@ -922,1077 +1000,1077 @@
 حداقل ویزا: £1,171 / £1,529 در ماه (× ۹)؛ از ۳۰ نوامبر ۲۰۲۶: £1,203 / £1,570</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (HC 584)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>۷</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>هزینه سال اول = شهریه + ۱۲ ماه زندگی (دلار)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>$13,000–18,000 (Stuttgart تا $20,500؛ FAU از ۲۰۲۷ تا ≈ $26,000)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>$37,500–45,000</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>$27,000–32,500</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>$31,500–38,000</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>$23,000–42,000 (Neuchâtel/Fribourg $23–31k · Lucerne $26–32k · Bern $27–35k · Lugano/Lausanne $30–37k · Zürich $30–42k)</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>$38,000–65,000 (Teesside $38–42k · Northumbria $44–48k · Leicester/Essex $48–54k · Brunel/London $55–61k · York $60–65k)</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>محاسبه از ردیف‌های ۴ و ۶؛ بدون بلیت، ویزا، بیمه، ودیعه (۱۰–۱۵٪ اضافه کنید)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>۸</t>
+          <t>۷</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>هزینه کل تا فارغ‌التحصیلی (شهریه × سال‌ها + زندگی) — مهم‌ترین عدد مالی</t>
+          <t>هزینه سال اول = شهریه + ۱۲ ماه زندگی (دلار)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$27,000–36,000 (۲ سال؛ Stuttgart تا $41,000؛ FAU از ۲۰۲۷ تا ≈ $53,000) — ارزان‌ترین</t>
+          <t>$13,000–18,000 (Stuttgart تا $20,500؛ FAU از ۲۰۲۷ تا ≈ $26,000)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>$75,000–90,000 (۲ سال) — گران‌ترین</t>
+          <t>$37,500–45,000</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>$54,000–65,000 (۲ سال)</t>
+          <t>$27,000–32,500</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>$63,000–76,000 (۲ سال)</t>
+          <t>$31,500–38,000</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>$35,000–84,000 (Neuchâtel/Fribourg ۱.۵ سال $35–47k · Bern $39–51k · UZH $45–58k · HSLU $53–64k · USI/EPFL $60–75k · ETH $66–84k) — بعد از هلند گران‌ترین؛ شهریه ناچیز است، هزینهٔ زندگی همه‌چیز را تعیین می‌کند</t>
+          <t>$23,000–42,000 (Neuchâtel/Fribourg $23–31k · Lucerne $26–32k · Bern $27–35k · Lugano/Lausanne $30–37k · Zürich $30–42k)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>$38,000–65,000 (۱ سال)</t>
+          <t>$38,000–65,000 (Teesside $38–42k · Northumbria $44–48k · Leicester/Essex $48–54k · Brunel/London $55–61k · York $60–65k)</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>محاسبه؛ جدول اول فقط سال اول را مقایسه کرده بود</t>
+          <t>محاسبه از ردیف‌های ۴ و ۶؛ بدون بلیت، ویزا، بیمه، ودیعه (۱۰–۱۵٪ اضافه کنید)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>۹</t>
+          <t>۸</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>سازگاری با بودجه $32,000 در سال</t>
+          <t>هزینه کل تا فارغ‌التحصیلی (شهریه × سال‌ها + زندگی) — مهم‌ترین عدد مالی</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>✅ کاملاً (حتی Stuttgart)</t>
+          <t>$27,000–36,000 (۲ سال؛ Stuttgart تا $41,000؛ FAU از ۲۰۲۷ تا ≈ $53,000) — ارزان‌ترین</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>❌ کسری $5,500–13,000 در هر سال</t>
+          <t>$75,000–90,000 (۲ سال) — گران‌ترین</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>✅ (Linköping دقیقاً مرزی)</t>
+          <t>$54,000–65,000 (۲ سال)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ مرزی؛ AAU تقریباً در بودجه، SDU کسری تا ≈ $6,000 در سال</t>
+          <t>$63,000–76,000 (۲ سال)</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ فقط Neuchâtel/Fribourg (و با صرفه‌جویی Lucerne/Lugano) در بودجه؛ Zürich/Lausanne کسری $1,000–10,000 در سال؛ کار دانشجویی در ۶ ماه اول ممنوع → سال اول تماماً از جیب</t>
+          <t>$35,000–84,000 (Neuchâtel/Fribourg ۱.۵ سال $35–47k · Bern $39–51k · UZH $45–58k · HSLU $53–64k · USI/EPFL $60–75k · ETH $66–84k) — بعد از هلند گران‌ترین؛ شهریه ناچیز است، هزینهٔ زندگی همه‌چیز را تعیین می‌کند</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>❌ کسری $6,000–33,000 (کمترین: Teesside ≈ $6–10k؛ Northumbria ≈ $12–16k)</t>
+          <t>$38,000–65,000 (۱ سال)</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>محاسبه از ردیف ۷</t>
+          <t>محاسبه؛ جدول اول فقط سال اول را مقایسه کرده بود</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>۱۰</t>
+          <t>۹</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>مسکن در بدو ورود</t>
+          <t>سازگاری با بودجه $32,000 در سال</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه Studierendenwerk با لیست انتظار؛ Stuttgart و Darmstadt سخت، Dresden و Erlangen آسان‌تر. بلافاصله بعد از پذیرش ثبت‌نام کنید.</t>
+          <t>✅ کاملاً (حتی Stuttgart)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>کمبود شدید ملی؛ ولی Twente (کمپوس) و Radboud/SSH&amp; اتاق رزروشده برای بین‌المللی‌ها دارند — مهلت را از دست ندهید.</t>
+          <t>❌ کسری $5,500–13,000 در هر سال</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>تضمین سراسری نیست: Linköping به شهریه‌پردازها یک پیشنهاد اتاق برای سال اول می‌دهد؛ Halmstad تضمین ندارد؛ BTH تأیید نشد.</t>
+          <t>✅ (Linköping دقیقاً مرزی)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>دفتر اسکان بین‌المللی AAU/SDU؛ Aalborg و Odense نسبتاً در دسترس.</t>
+          <t>⚠️ مرزی؛ AAU تقریباً در بودجه، SDU کسری تا ≈ $6,000 در سال</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Zürich بحرانی: WOKO/Juwo (CHF 500–900) لیست انتظار ۳–۱۲ ماه، بازار خصوصی بسیار رقابتی؛ Lausanne خوابگاه‌های FMEL (زود پر می‌شود)؛ Lugano/Fribourg/Neuchâtel/Bern/Lucerne آسان‌تر و ارزان‌تر (CHF 500–800). روز دریافت پذیرش ثبت‌نام کنید.</t>
+          <t>⚠️ فقط Neuchâtel/Fribourg (و با صرفه‌جویی Lucerne/Lugano) در بودجه؛ Zürich/Lausanne کسری $1,000–10,000 در سال؛ کار دانشجویی در ۶ ماه اول ممنوع → سال اول تماماً از جیب</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>معمولاً تضمین خوابگاه سال اول برای بین‌المللی‌ها اگر تا مهلت درخواست دهید.</t>
+          <t>❌ کسری $6,000–33,000 (کمترین: Teesside ≈ $6–10k؛ Northumbria ≈ $12–16k)</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>سایت دانشگاه‌ها؛ hh.se (Find Accommodation)؛ liu.se</t>
+          <t>محاسبه از ردیف ۷</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>۱۱</t>
+          <t>۱۰</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>سقف قانونی کار دانشجویی</t>
+          <t>مسکن در بدو ورود</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>۱۴۰ روز کامل یا ۲۸۰ نیم‌روز در سال (Werkstudent تا ۲۰ ساعت/هفته در ترم)</t>
+          <t>خوابگاه Studierendenwerk با لیست انتظار؛ Stuttgart و Darmstadt سخت، Dresden و Erlangen آسان‌تر. بلافاصله بعد از پذیرش ثبت‌نام کنید.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>۱۶ ساعت/هفته (کارفرما TWV می‌گیرد) یا تمام‌وقت در ژوئن–اوت</t>
+          <t>کمبود شدید ملی؛ ولی Twente (کمپوس) و Radboud/SSH&amp; اتاق رزروشده برای بین‌المللی‌ها دارند — مهلت را از دست ندهید.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>از ۱۱ ژوئن ۲۰۲۶: حداکثر ۱۵ ساعت/هفته در ترم؛ ژوئن–اوت بدون سقف. تخلف = لغو اقامت. + حداقل پیشرفت تحصیلی ۳۷.۵ واحد سال اول / ۴۵ واحد بعد</t>
+          <t>تضمین سراسری نیست: Linköping به شهریه‌پردازها یک پیشنهاد اتاق برای سال اول می‌دهد؛ Halmstad تضمین ندارد؛ BTH تأیید نشد.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>۹۰ ساعت/ماه (سپتامبر–مه) + تمام‌وقت ژوئن–اوت</t>
+          <t>دفتر اسکان بین‌المللی AAU/SDU؛ Aalborg و Odense نسبتاً در دسترس.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>غیر-EU: ۶ ماه اول هیچ؛ بعد از آن ۱۵ ساعت/هفته در ترم و تمام‌وقت در تعطیلات؛ کارفرما باید مجوز کانتونی بگیرد؛ کل دورهٔ تحصیل در سوئیس حداکثر ۸ سال</t>
+          <t>Zürich بحرانی: WOKO/Juwo (CHF 500–900) لیست انتظار ۳–۱۲ ماه، بازار خصوصی بسیار رقابتی؛ Lausanne خوابگاه‌های FMEL (زود پر می‌شود)؛ Lugano/Fribourg/Neuchâtel/Bern/Lucerne آسان‌تر و ارزان‌تر (CHF 500–800). روز دریافت پذیرش ثبت‌نام کنید.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>۲۰ ساعت/هفته در ترم؛ تمام‌وقت در تعطیلات</t>
+          <t>معمولاً تضمین خوابگاه سال اول برای بین‌المللی‌ها اگر تا مهلت درخواست دهید.</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se (خبر ۲۵ مه ۲۰۲۶)؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk</t>
+          <t>سایت دانشگاه‌ها؛ hh.se (Find Accommodation)؛ liu.se</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>۱۲</t>
+          <t>۱۱</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>درآمد واقع‌بینانه کار حین تحصیل (ناخالص، ماهانه)</t>
+          <t>سقف قانونی کار دانشجویی</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>€1,000–1,600 (Werkstudent فنی €15–20/ساعت؛ برای رشته شما فراوان)</t>
+          <t>۱۴۰ روز کامل یا ۲۸۰ نیم‌روز در سال (Werkstudent تا ۲۰ ساعت/هفته در ترم)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>تا ≈ €1,000 (۱۶ ساعت × €14.71)؛ یافتن کارفرمای TWV‌گیر سخت</t>
+          <t>۱۶ ساعت/هفته (کارفرما TWV می‌گیرد) یا تمام‌وقت در ژوئن–اوت</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>€300–800 (سقف ۱۵ ساعت؛ کار برای غیرسوئدی‌زبان کمیاب)</t>
+          <t>از ۱۱ ژوئن ۲۰۲۶: حداکثر ۱۵ ساعت/هفته در ترم؛ ژوئن–اوت بدون سقف. تخلف = لغو اقامت. + حداقل پیشرفت تحصیلی ۳۷.۵ واحد سال اول / ۴۵ واحد بعد</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>DKK 8,000–12,000 (€1,070–1,600) اگر کار پیدا شود؛ اکثر کارهای خدماتی دانمارکی می‌خواهند</t>
+          <t>۹۰ ساعت/ماه (سپتامبر–مه) + تمام‌وقت ژوئن–اوت</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>بعد از ماه ششم: ≈ CHF 1,300–1,800 (۱۵ ساعت × CHF 22–28؛ دستیاری آموزشی/پژوهشی در ETH/UZH/ZHAW رایج)</t>
+          <t>غیر-EU: ۶ ماه اول هیچ؛ بعد از آن ۱۵ ساعت/هفته در ترم و تمام‌وقت در تعطیلات؛ کارفرما باید مجوز کانتونی بگیرد؛ کل دورهٔ تحصیل در سوئیس حداکثر ۸ سال</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>تا ≈ £1,100 (۲۰ ساعت × £12.71)</t>
+          <t>۲۰ ساعت/هفته در ترم؛ تمام‌وقت در تعطیلات</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>حداقل دستمزدهای ۲۰۲۶؛ برآورد. درآمد دانشجویی را در تأمین مالی ویزا حساب نکنید.</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se (خبر ۲۵ مه ۲۰۲۶)؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>۱۳</t>
+          <t>۱۲</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>زبان محیط کار فنی (IT)</t>
+          <t>درآمد واقع‌بینانه کار حین تحصیل (ناخالص، ماهانه)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی در استارتاپ‌ها/شرکت‌های بزرگ (Berlin، Munich، Hamburg) کافی؛ اکثر آگهی‌های IT آلمانی B2 می‌خواهند → بدون آلمانی حدود نیمی از بازار بسته است.</t>
+          <t>€1,000–1,600 (Werkstudent فنی €15–20/ساعت؛ برای رشته شما فراوان)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی در tech رایج و کافی؛ نه ۱۰۰٪.</t>
+          <t>تا ≈ €1,000 (۱۶ ساعت × €14.71)؛ یافتن کارفرمای TWV‌گیر سخت</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی در tech رایج (Stockholm، Göteborg)؛ بازار ۲۰۲۴–۲۶ ضعیف (بیکاری ≈ ۹٪).</t>
+          <t>€300–800 (سقف ۱۵ ساعت؛ کار برای غیرسوئدی‌زبان کمیاب)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی برای بخشی از نقش‌های IT در Copenhagen/Aarhus کافی؛ برای اکثر نقش‌ها دانمارکی B1–B2 ترجیح دارد؛ در Aalborg/Odense سخت‌تر.</t>
+          <t>DKK 8,000–12,000 (€1,070–1,600) اگر کار پیدا شود؛ اکثر کارهای خدماتی دانمارکی می‌خواهند</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Zürich: انگلیسی در Big Tech (Google ≈ ۵ هزار نفر، Microsoft، Meta، Apple، Nvidia، OpenAI/Anthropic)، بانک‌ها و استارتاپ‌های ETH کافی؛ Lausanne/Geneva: انگلیسی + فرانسه؛ SMEهای آلمانی‌زبان و Lugano (ایتالیایی) زبان محلی می‌خواهند → بدون آلمانی/فرانسه ≈ نیمی از بازار بسته</t>
+          <t>بعد از ماه ششم: ≈ CHF 1,300–1,800 (۱۵ ساعت × CHF 22–28؛ دستیاری آموزشی/پژوهشی در ETH/UZH/ZHAW رایج)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>۱۰۰٪ انگلیسی؛ بازار جونیور ۲۰۲۵–۲۶ بسیار رقابتی.</t>
+          <t>تا ≈ £1,100 (۲۰ ساعت × £12.71)</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>workindenmark.dk؛ آگهی‌های StepStone/LinkedIn؛ ارزیابی</t>
+          <t>حداقل دستمزدهای ۲۰۲۶؛ برآورد. درآمد دانشجویی را در تأمین مالی ویزا حساب نکنید.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>۱۴</t>
+          <t>۱۳</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>زبان برای امور اداری و زندگی روزمره</t>
+          <t>زبان محیط کار فنی (IT)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>قانوناً برای تحصیل لازم نیست؛ عملاً A2–B1 (اداره اتباع، اجاره، بیمه، مالیات).</t>
+          <t>انگلیسی در استارتاپ‌ها/شرکت‌های بزرگ (Berlin، Munich، Hamburg) کافی؛ اکثر آگهی‌های IT آلمانی B2 می‌خواهند → بدون آلمانی حدود نیمی از بازار بسته است.</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی کافی؛ نامه‌های رسمی هلندی.</t>
+          <t>انگلیسی در tech رایج و کافی؛ نه ۱۰۰٪.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی کافی.</t>
+          <t>انگلیسی در tech رایج (Stockholm، Göteborg)؛ بازار ۲۰۲۴–۲۶ ضعیف (بیکاری ≈ ۹٪).</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی روزمره کافی؛ سامانه‌ها و نامه‌ها دانمارکی.</t>
+          <t>انگلیسی برای بخشی از نقش‌های IT در Copenhagen/Aarhus کافی؛ برای اکثر نقش‌ها دانمارکی B1–B2 ترجیح دارد؛ در Aalborg/Odense سخت‌تر.</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>رسمی: آلمانی / فرانسه / ایتالیایی بسته به کانتون؛ نامه‌های ادارهٔ مهاجرت، بیمه، اجاره و مالیات به زبان محلی؛ انگلیسی در زوریخ/ژنو/لوزان برای روزمره کافی است، ولی سوئیسی‌آلمانی (گویش) در محیط اجتماعی مانع است</t>
+          <t>Zürich: انگلیسی در Big Tech (Google ≈ ۵ هزار نفر، Microsoft، Meta، Apple، Nvidia، OpenAI/Anthropic)، بانک‌ها و استارتاپ‌های ETH کافی؛ Lausanne/Geneva: انگلیسی + فرانسه؛ SMEهای آلمانی‌زبان و Lugano (ایتالیایی) زبان محلی می‌خواهند → بدون آلمانی/فرانسه ≈ نیمی از بازار بسته</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی.</t>
+          <t>۱۰۰٪ انگلیسی؛ بازار جونیور ۲۰۲۵–۲۶ بسیار رقابتی.</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>تجربه عمومی؛ ارزیابی</t>
+          <t>workindenmark.dk؛ آگهی‌های StepStone/LinkedIn؛ ارزیابی</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>۱۵</t>
+          <t>۱۴</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>مجوز اقامت پس از تحصیل برای جست‌وجوی کار</t>
+          <t>زبان برای امور اداری و زندگی روزمره</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>۱۸ ماه (§20 AufenthG) — هر کاری مجاز</t>
+          <t>قانوناً برای تحصیل لازم نیست؛ عملاً A2–B1 (اداره اتباع، اجاره، بیمه، مالیات).</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>۱۲ ماه (zoekjaar) — تا ۳ سال بعد از مدرک قابل درخواست؛ €254</t>
+          <t>انگلیسی کافی؛ نامه‌های رسمی هلندی.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>۱۲ ماه — با اثبات تمکن SEK 10,656/ماه برای کل دوره</t>
+          <t>انگلیسی کافی.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>۳ سال، خودکار همراه مجوز تحصیلی برای ارشد state-approved (AAU/SDU) — تا گرفتن «مجوز کار نامحدود» فقط ۹۰ ساعت/ماه</t>
+          <t>انگلیسی روزمره کافی؛ سامانه‌ها و نامه‌ها دانمارکی.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>فقط ۶ ماه (مجوز L برای جست‌وجوی کار، مادهٔ ۲۱ بند ۳ FNIA) — کوتاه‌ترین در بین ۶ کشور؛ کار در این مدت تا ۱۵ ساعت/هفته</t>
+          <t>رسمی: آلمانی / فرانسه / ایتالیایی بسته به کانتون؛ نامه‌های ادارهٔ مهاجرت، بیمه، اجاره و مالیات به زبان محلی؛ انگلیسی در زوریخ/ژنو/لوزان برای روزمره کافی است، ولی سوئیسی‌آلمانی (گویش) در محیط اجتماعی مانع است</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>۱۸ ماه Graduate visa برای درخواست‌های از ۱ ژانویه ۲۰۲۷ — £937 + IHS £1,035/سال</t>
+          <t>انگلیسی.</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (Statement of Changes ۱۴ اکتبر ۲۰۲۵)</t>
+          <t>تجربه عمومی؛ ارزیابی</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>۱۵</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>مجوز اقامت پس از تحصیل برای جست‌وجوی کار</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>۱۸ ماه (§20 AufenthG) — هر کاری مجاز</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>۱۲ ماه (zoekjaar) — تا ۳ سال بعد از مدرک قابل درخواست؛ €254</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>۱۲ ماه — با اثبات تمکن SEK 10,656/ماه برای کل دوره</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>۳ سال، خودکار همراه مجوز تحصیلی برای ارشد state-approved (AAU/SDU) — تا گرفتن «مجوز کار نامحدود» فقط ۹۰ ساعت/ماه</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>فقط ۶ ماه (مجوز L برای جست‌وجوی کار، مادهٔ ۲۱ بند ۳ FNIA) — کوتاه‌ترین در بین ۶ کشور؛ کار در این مدت تا ۱۵ ساعت/هفته</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>۱۸ ماه Graduate visa برای درخواست‌های از ۱ ژانویه ۲۰۲۷ — £937 + IHS £1,035/سال</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (Statement of Changes ۱۴ اکتبر ۲۰۲۵)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>۱۶</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>حداقل حقوق برای ویزای کار (سطوح ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>بلوکارت: €50,700 عمومی / €45,934.20 برای IT و تازه‌فارغ‌التحصیلان (تا ۳ سال بعد از مدرک)
 مجوز کار §18b برای فارغ‌التحصیلان آلمان: بدون کف ثابت</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>HSM کاهش‌یافته برای فارغ‌التحصیلان هلند (تا ۳ سال): €3,122/ماه بدون حق تعطیلات ≈ €40,500/سال
 زیر ۳۰ سال عادی: €4,357/ماه</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>SEK 34,470/ماه (۹۰٪ میانه؛ از ۱۶ ژوئن ۲۰۲۶)
 فارغ‌التحصیلان سوئد که از داخل درخواست دهند: ۷۵٪ = SEK 28,725/ماه
 هر ژوئن به‌روز می‌شود</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Positive List (مشاغل IT): کف ثابت ندارد (حقوق مطابق استاندارد دانمارکی)
 Pay Limit: DKK 552,000 · Supplementary: DKK 446,000</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>کف عددی ندارد ولی حقوق باید «متعارف محل/رشته» باشد. فارغ‌التحصیل سوئیس از «اولویت داخلی/EU» معاف است اگر شغل «منفعت علمی/اقتصادی بالا» داشته باشد؛ ⚠️ ولی سهمیهٔ سالانهٔ اتباع غیر-EU (۲۰۲۶: ۴,۵۰۰ مجوز B + ۴,۰۰۰ L؛ معمولاً ≈ ۶۵–۷۰٪ مصرف می‌شود) شامل شما هم می‌شود — طرح معافیت فارغ‌التحصیلان (22.067) از ۲۰۲۳ در پارلمان متوقف مانده</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Skilled Worker: بالاترینِ £41,700 و نرخ شغل؛ نرخ SOC 2134 (توسعه‌دهنده) = £54,700
 تازه‌کار (حداکثر ۴ سال): ۷۰٪ = £38,290
 + انگلیسی B2 (از ۸ ژانویه ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch (Art. 21 FNIA)؛ gov.uk Appendix Skilled Occupations</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>۱۷</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>حقوق ورودی جونیور توسعه‌دهنده (ناخالص سالانه، ۲۰۲۶)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>€48,000–55,000 (با ارشد ≈ €55k)</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>€40,000–50,000 (Amsterdam بالاتر)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>SEK 420,000–540,000 (35–45 هزار در ماه)</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>DKK 500,000–540,000 (IDA 2026: تازه‌فارغ‌التحصیل ≈ DKK 43,800/ماه با بازنشستگی)</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>CHF 85,000–105,000 (≈ $103–127k؛ میانهٔ Glassdoor زوریخ CHF 92k؛ ETH/EPFL 90–118k؛ Big Tech CHF 110–165k) — بالاترین در بین ۶ کشور</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>£28,000–35,000 خارج لندن (Manchester/Leeds/Newcastle)؛ London £32,000–45,000 — اغلب زیر کف اسپانسری £38,290</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>StepStone؛ Glassdoor؛ IDA؛ Reed — برآورد بازار، نه آمار رسمی</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>۱۸</t>
+          <t>۱۷</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>خالص ماهانه تقریبی (بعد از مالیات)</t>
+          <t>حقوق ورودی جونیور توسعه‌دهنده (ناخالص سالانه، ۲۰۲۶)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>€2,700–3,000</t>
+          <t>€48,000–55,000 (با ارشد ≈ €55k)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>€2,700–3,100 (بدون قاعده ۳۰٪)</t>
+          <t>€40,000–50,000 (Amsterdam بالاتر)</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>€2,500–2,900 (SEK 29–33 هزار)</t>
+          <t>SEK 420,000–540,000 (35–45 هزار در ماه)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>€3,300–3,700 (DKK 25–27.5 هزار)</t>
+          <t>DKK 500,000–540,000 (IDA 2026: تازه‌فارغ‌التحصیل ≈ DKK 43,800/ماه با بازنشستگی)</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>≈ CHF 5,700–6,700 (مالیات + بیمه‌های اجتماعی ≈ ۲۰–۲۵٪ برای مجرد در زوریخ)؛ بیمهٔ درمانی اجباری CHF 350–450/ماه جداگانه از جیب</t>
+          <t>CHF 85,000–105,000 (≈ $103–127k؛ میانهٔ Glassdoor زوریخ CHF 92k؛ ETH/EPFL 90–118k؛ Big Tech CHF 110–165k) — بالاترین در بین ۶ کشور</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>£2,000–2,500</t>
+          <t>£28,000–35,000 خارج لندن (Manchester/Leeds/Newcastle)؛ London £32,000–45,000 — اغلب زیر کف اسپانسری £38,290</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>ماشین‌حساب‌های مالیاتی ۲۰۲۶ (کلاس مالیاتی مجرد)</t>
+          <t>StepStone؛ Glassdoor؛ IDA؛ Reed — برآورد بازار، نه آمار رسمی</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>۱۹</t>
+          <t>۱۸</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>پس‌انداز ماهانه تخمینی جونیور (خالص − هزینه زندگی یک نفر شاغل)</t>
+          <t>خالص ماهانه تقریبی (بعد از مالیات)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>€1,000–1,500</t>
+          <t>€2,700–3,000</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>€700–1,200</t>
+          <t>€2,700–3,100 (بدون قاعده ۳۰٪)</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>€900–1,400</t>
+          <t>€2,500–2,900 (SEK 29–33 هزار)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>€1,100–1,600</t>
+          <t>€3,300–3,700 (DKK 25–27.5 هزار)</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>CHF 1,500–3,000 (≈ $1,800–3,600) در زوریخ (استودیو CHF 1,400–1,900 + بیمه ≈ 400) — بیشترین پس‌انداز مطلق بین ۶ کشور، اگر شغل بگیرید</t>
+          <t>≈ CHF 5,700–6,700 (مالیات + بیمه‌های اجتماعی ≈ ۲۰–۲۵٪ برای مجرد در زوریخ)؛ بیمهٔ درمانی اجباری CHF 350–450/ماه جداگانه از جیب</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>£400–900</t>
+          <t>£2,000–2,500</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>برآورد؛ هزینه زندگی شاغل: DE €1,400–1,700 · NL €1,700–2,100 · SE €1,300–1,600 · DK €1,900–2,300 · CH CHF 3,200–3,800 · UK £1,300–1,700</t>
+          <t>ماشین‌حساب‌های مالیاتی ۲۰۲۶ (کلاس مالیاتی مجرد)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>۲۰</t>
+          <t>۱۹</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>اقامت دائم (PR) — زمان و شرط اصلی</t>
+          <t>پس‌انداز ماهانه تخمینی جونیور (خالص − هزینه زندگی یک نفر شاغل)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>۲ سال کار برای فارغ‌التحصیل آلمان با B1 (§18c)؛ بلوکارت: ۲۱ ماه با B1 / ۲۷ ماه با A1</t>
+          <t>€1,000–1,500</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>۵ سال اقامت قانونی (سال‌های تحصیل نصف حساب می‌شود) + inburgering</t>
+          <t>€700–1,200</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>۴ سال مجوز کار در ۷ سال اخیر + خودکفایی (تحصیل حساب نمی‌شود)</t>
+          <t>€900–1,400</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>۸ سال (یا ۴ سال با هر ۴ شرط تکمیلی) + ۳.۵ سال کار تمام‌وقت در ۴ سال اخیر</t>
+          <t>€1,100–1,600</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>اجازهٔ اقامت C: برای ایرانی‌ها ۱۰ سال (۵ سال آخر پیوسته با B)؛ سال‌های دانشجویی فقط اگر بعدش ۲ سال پیوسته اجازهٔ B داشته باشید حساب می‌شود؛ C زودهنگام ۵ ساله فقط با «ادغام موفق» و B1 شفاهی به صلاحدید کانتون — سخت‌ترین مسیر در بین ۶ کشور</t>
+          <t>CHF 1,500–3,000 (≈ $1,800–3,600) در زوریخ (استودیو CHF 1,400–1,900 + بیمه ≈ 400) — بیشترین پس‌انداز مطلق بین ۶ کشور، اگر شغل بگیرید</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>فعلاً ۵ سال Skilled Worker (Graduate visa حساب نمی‌شود)؛ طرح Earned Settlement با پایه ۱۰ سال در دستور کار دولت (تا سپتامبر ۲۰۲۶ قانون نشده)</t>
+          <t>£400–900</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk / Home Affairs Committee</t>
+          <t>برآورد؛ هزینه زندگی شاغل: DE €1,400–1,700 · NL €1,700–2,100 · SE €1,300–1,600 · DK €1,900–2,300 · CH CHF 3,200–3,800 · UK £1,300–1,700</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>۲۱</t>
+          <t>۲۰</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>آزمون زبان محلی برای PR</t>
+          <t>اقامت دائم (PR) — زمان و شرط اصلی</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>B1 آلمانی (A1 فقط با بلوکارت ۲۷ ماهه)</t>
+          <t>۲ سال کار برای فارغ‌التحصیل آلمان با B1 (§18c)؛ بلوکارت: ۲۱ ماه با B1 / ۲۷ ماه با A1</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>A2 فعلی → B1 (تصمیم کابینه، فوریه ۲۰۲۶)</t>
+          <t>۵ سال اقامت قانونی (سال‌های تحصیل نصف حساب می‌شود) + inburgering</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>هیچ (برای PR)</t>
+          <t>۴ سال مجوز کار در ۷ سال اخیر + خودکفایی (تحصیل حساب نمی‌شود)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Prøve i Dansk 2 (≈ B1) برای مسیر ۸ ساله؛ PD3 (≈ B2) برای مسیر ۴ ساله</t>
+          <t>۸ سال (یا ۴ سال با هر ۴ شرط تکمیلی) + ۳.۵ سال کار تمام‌وقت در ۴ سال اخیر</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>A2 شفاهی + A1 کتبی زبان محلی (آزمون fide) برای C ۱۰ ساله؛ B1 شفاهی برای C زودهنگام ۵ ساله → بدون زبان سوم PR نمی‌گیرید</t>
+          <t>اجازهٔ اقامت C: برای ایرانی‌ها ۱۰ سال (۵ سال آخر پیوسته با B)؛ سال‌های دانشجویی فقط اگر بعدش ۲ سال پیوسته اجازهٔ B داشته باشید حساب می‌شود؛ C زودهنگام ۵ ساله فقط با «ادغام موفق» و B1 شفاهی به صلاحدید کانتون — سخت‌ترین مسیر در بین ۶ کشور</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>انگلیسی B2 از ۲۶ مارس ۲۰۲۷ + آزمون Life in the UK (زبان سوم نیست)</t>
+          <t>فعلاً ۵ سال Skilled Worker (Graduate visa حساب نمی‌شود)؛ طرح Earned Settlement با پایه ۱۰ سال در دستور کار دولت (تا سپتامبر ۲۰۲۶ قانون نشده)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>BAMF؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (HC 1691)</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk / Home Affairs Committee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>۲۲</t>
+          <t>۲۱</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>شهروندی (جدا از PR)</t>
+          <t>آزمون زبان محلی برای PR</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>۵ سال + B1 + آزمون تابعیت (تحصیل حساب می‌شود)</t>
+          <t>B1 آلمانی (A1 فقط با بلوکارت ۲۷ ماهه)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>۵ سال + inburgering (A2 → B1)</t>
+          <t>A2 فعلی → B1 (تصمیم کابینه، فوریه ۲۰۲۶)</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>از ۶ ژوئن ۲۰۲۶: ۸ سال + آزمون مدنی + آزمون زبان (از اکتبر ۲۰۲۷) + کف درآمد</t>
+          <t>هیچ (برای PR)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>۹ سال + PD3 + آزمون تابعیت + اشتغال ۳.۵ سال از ۴ سال</t>
+          <t>Prøve i Dansk 2 (≈ B1) برای مسیر ۸ ساله؛ PD3 (≈ B2) برای مسیر ۴ ساله</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>۱۰ سال اقامت (سال‌های ۸ تا ۱۸ سالگی دوبرابر) + اجازهٔ C + B1 شفاهی / A2 کتبی + شرایط کانتون و شهرداری (۲–۵ سال اقامت محلی) — سخت‌ترین در اروپا</t>
+          <t>A2 شفاهی + A1 کتبی زبان محلی (آزمون fide) برای C ۱۰ ساله؛ B1 شفاهی برای C زودهنگام ۵ ساله → بدون زبان سوم PR نمی‌گیرید</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>ILR + ۱۲ ماه؛ B1/B2 + Life in the UK</t>
+          <t>انگلیسی B2 از ۲۶ مارس ۲۰۲۷ + آزمون Life in the UK (زبان سوم نیست)</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>قوانین تابعیت ۲۰۲۶؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch</t>
+          <t>BAMF؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (HC 1691)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>۲۳</t>
+          <t>۲۲</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>فرایند ویزا برای پاسپورت ایرانی — وضعیت سپتامبر ۲۰۲۶ (بسیار متغیر)</t>
+          <t>شهروندی (جدا از PR)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>سفارت تهران در «حالت اضطراری»؛ بخش ویزا به روی مراجعان عادی بسته. TLScontact از ۱۵ ژوئیه ۲۰۲۶ لیست انتظار دانشجویی باز کرده ولی وقت نمی‌دهد. صدور ویزا: ۴۶هزار (۲۰۲۴) → ۲۳هزار (۲۰۲۵) → ≈ ۱٬۳۰۰ اوایل ۲۰۲۶. ارجاع موردی به ایروان/استانبول. حتی در شرایط عادی لیست انتظار ۶–۱۸ ماه.</t>
+          <t>۵ سال + B1 + آزمون تابعیت (تحصیل حساب می‌شود)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه درخواست را در IND ثبت می‌کند (TEV) ✓؛ ولی سفارت هلند موقتاً به باکو منتقل شده و MVV در ایران صادر نمی‌شود.</t>
+          <t>۵ سال + inburgering (A2 → B1)</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>درخواست آنلاین در Migrationsverket؛ بررسی دیجیتال پاسپورت؛ سفارت تهران فعلاً بیومتریک/کارت اقامت نمی‌گیرد (ژوئیه ۲۰۲۶).</t>
+          <t>از ۶ ژوئن ۲۰۲۶: ۸ سال + آزمون مدنی + آزمون زبان (از اکتبر ۲۰۲۷) + کف درآمد</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>«در حال حاضر امکان درخواست از ایران وجود ندارد» (سفارت دانمارک، ۲۰۲۶) — باید از SIRI بخواهید پرونده به نمایندگی دیگری در منطقه برود؛ بیومتریک ظرف ۱۴ روز.</t>
+          <t>۹ سال + PD3 + آزمون تابعیت + اشتغال ۳.۵ سال از ۴ سال</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>سفارت سوئیس در تهران باز است: ویزای D (تحصیلی) با وقت قبلی پذیرفته می‌شود، ویزای C فعلاً خیر (اطلاعیهٔ ۳۰ ژانویه ۲۰۲۶؛ در جنگ ژوئن ۲۰۲۵ دو هفته بسته بود). تصمیم را ادارهٔ مهاجرت کانتون می‌گیرد: ۸–۱۲ هفته؛ ETH تأییدیهٔ ثبت‌نام برای ویزا را از می ۲۰۲۷ می‌دهد. ⚠️ گلوگاه اصلی: اثبات تمکن (ردیف ۲۵).</t>
+          <t>۱۰ سال اقامت (سال‌های ۸ تا ۱۸ سالگی دوبرابر) + اجازهٔ C + B1 شفاهی / A2 کتبی + شرایط کانتون و شهرداری (۲–۵ سال اقامت محلی) — سخت‌ترین در اروپا</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>درخواست آنلاین gov.uk + بیومتریک در VAC؛ VFS تهران در ۲۰۲۶ متناوباً بسته/باز شده؛ می‌توان از VAC کشور ثالث اقدام کرد. «قانون ۲۸ روز» مربوط به تمکن مالی است، نه VFS.</t>
+          <t>ILR + ۱۲ ماه؛ B1/B2 + Life in the UK</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>visas-de.tlscontact.com؛ netherlandsworldwide.nl؛ swedenabroad.se؛ iran.um.dk؛ eda.admin.ch/tehran؛ gov.uk — برنامه B: اقدام از ترکیه/ارمنستان/امارات</t>
+          <t>قوانین تابعیت ۲۰۲۶؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>۲۳</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>فرایند ویزا برای پاسپورت ایرانی — وضعیت سپتامبر ۲۰۲۶ (بسیار متغیر)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>سفارت تهران در «حالت اضطراری»؛ بخش ویزا به روی مراجعان عادی بسته. TLScontact از ۱۵ ژوئیه ۲۰۲۶ لیست انتظار دانشجویی باز کرده ولی وقت نمی‌دهد. صدور ویزا: ۴۶هزار (۲۰۲۴) → ۲۳هزار (۲۰۲۵) → ≈ ۱٬۳۰۰ اوایل ۲۰۲۶. ارجاع موردی به ایروان/استانبول. حتی در شرایط عادی لیست انتظار ۶–۱۸ ماه.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>دانشگاه درخواست را در IND ثبت می‌کند (TEV) ✓؛ ولی سفارت هلند موقتاً به باکو منتقل شده و MVV در ایران صادر نمی‌شود.</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>درخواست آنلاین در Migrationsverket؛ بررسی دیجیتال پاسپورت؛ سفارت تهران فعلاً بیومتریک/کارت اقامت نمی‌گیرد (ژوئیه ۲۰۲۶).</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>«در حال حاضر امکان درخواست از ایران وجود ندارد» (سفارت دانمارک، ۲۰۲۶) — باید از SIRI بخواهید پرونده به نمایندگی دیگری در منطقه برود؛ بیومتریک ظرف ۱۴ روز.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>سفارت سوئیس در تهران باز است: ویزای D (تحصیلی) با وقت قبلی پذیرفته می‌شود، ویزای C فعلاً خیر (اطلاعیهٔ ۳۰ ژانویه ۲۰۲۶؛ در جنگ ژوئن ۲۰۲۵ دو هفته بسته بود). تصمیم را ادارهٔ مهاجرت کانتون می‌گیرد: ۸–۱۲ هفته؛ ETH تأییدیهٔ ثبت‌نام برای ویزا را از می ۲۰۲۷ می‌دهد. ⚠️ گلوگاه اصلی: اثبات تمکن (ردیف ۲۵).</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>درخواست آنلاین gov.uk + بیومتریک در VAC؛ VFS تهران در ۲۰۲۶ متناوباً بسته/باز شده؛ می‌توان از VAC کشور ثالث اقدام کرد. «قانون ۲۸ روز» مربوط به تمکن مالی است، نه VFS.</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>visas-de.tlscontact.com؛ netherlandsworldwide.nl؛ swedenabroad.se؛ iran.um.dk؛ eda.admin.ch/tehran؛ gov.uk — برنامه B: اقدام از ترکیه/ارمنستان/امارات</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>۲۴</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>نمره انگلیسی برنامه‌های هدف</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>TU Darmstadt، TU Dresden، Stuttgart: C1 / IELTS 7.0 (Dresden: هر بخش ≥ B2)
 FAU (AI): B2 / IELTS 6.5</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>IELTS 6.5 (هر بخش ≥ 6.0)</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>IELTS 6.5 (هر بخش ≥ 5.5)</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>IELTS 6.5</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>USI: B2 در ورود (IELTS 5.5–6.5) و C1 تا فارغ‌التحصیلی · HSLU: C1 (B2 مشروط) · Joint MSc CS (Neuchâtel/Fribourg/Bern): بدون آزمون زبان — B2 توصیه (FAQ رسمی) · ZHAW: B2–C1 · UZH و ETH: C1 / IELTS 7.0 · EPFL: مدرک زبان الزامی نیست</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>IELTS 6.0–6.5</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>سایت برنامه‌ها — ⚠️ IELTS از ۳۱ ژانویه ۲۰۲۶ و TOEFL از ۱۴۰۵ در ایران برگزار نمی‌شوند؛ آزمون را در استانبول/ایروان/دبی/تفلیس بدهید (نتیجهٔ کامپیوتری ۳–۵ روزه). برای مهلت ۱۵ ژانویهٔ ۲۰۲۷ (سوئد/دانمارک/Stuttgart) نتیجه باید تا اوایل ژانویه در دست باشد</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>۲۵</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>تمکن مالی ویزا (۲۰۲۶) و نکته تحریمی</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>حساب مسدود €11,904 (€992 × ۱۲). Fintiba ساکنان ایران را نمی‌پذیرد؛ Expatrio/Coracle را هنگام اقدام بررسی کنید. انتقال پول فقط از مسیر کشور ثالث/صرافی (۳–۶٪ هزینه).</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>€13,569 (€1,130.77 × ۱۲) + شهریه؛ معمولاً به حساب دانشگاه واریز می‌شود.</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>SEK 10,656 × ماه‌های مجوز (سال اول ≈ SEK 128,000) + قسط اول شهریه.</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>پرداخت شهریه ترم اول به‌عنوان تمکن پذیرفته می‌شود (در غیر این‌صورت DKK 7,426/ماه).</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>CHF 21,000 برای هر سال (Basel 24,000) + شهریه؛ برای هر تمدید سالانه دوباره. زوریخ: فقط حساب بانک سوئیسی/شعبهٔ سوئیسی به نام خودتان (حساب والدین پذیرفته نیست) یا ضامن مقیم سوئیس (B/C)؛ بانک‌های سوئیس برای ساکنان ایران حساب باز نمی‌کنند → عملاً از تهران فقط با ضامن، یا کانتون‌های انعطاف‌پذیرتر (تیچینو، فریبورگ، نوشاتل، برن، لوسرن — قبل از اقدام از دفتر بین‌الملل دانشگاه تأیید بگیرید). انتقال پول فقط از مسیر کشور ثالث.</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>شهریه + £1,171 × ۹ = £10,539 خارج لندن / £13,761 لندن؛ از ۳۰ نوامبر ۲۰۲۶: £10,827 / £14,130؛ ۲۸ روز متوالی در حساب؛ + ویزای دانشجویی £524 + IHS با نرخ دانشجویی £776/سال (برای ۱۶ ماه اقامت ≈ £1,164).</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (HC 584). افتتاح حساب بانکی برای ایرانی‌ها در همه‌جا کندتر است (آلمان و هلند بیشترین گزارش مشکل).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>۲۶</t>
+          <t>۲۵</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>بازار کار برای جونیورِ فقط‌انگلیسی‌زبان (ارزیابی، ۱–۵ ستاره)</t>
+          <t>تمکن مالی ویزا (۲۰۲۶) و نکته تحریمی</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>⭐⭐⭐ تقاضا و حقوق بالا؛ بدون آلمانی نیمی از بازار بسته</t>
+          <t>حساب مسدود €11,904 (€992 × ۱۲). Fintiba ساکنان ایران را نمی‌پذیرد؛ Expatrio/Coracle را هنگام اقدام بررسی کنید. انتقال پول فقط از مسیر کشور ثالث/صرافی (۳–۶٪ هزینه).</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐ انگلیسی‌دوست‌ترین بازار قاره؛ کف HSM فارغ‌التحصیل دست‌یافتنی</t>
+          <t>€13,569 (€1,130.77 × ۱۲) + شهریه؛ معمولاً به حساب دانشگاه واریز می‌شود.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>⭐⭐ بازار ۲۰۲۴–۲۶ ضعیف؛ شبکه محلی مهم</t>
+          <t>SEK 10,656 × ماه‌های مجوز (سال اول ≈ SEK 128,000) + قسط اول شهریه.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>⭐⭐ بدون دانمارکی محدود؛ خارج از Copenhagen سخت</t>
+          <t>پرداخت شهریه ترم اول به‌عنوان تمکن پذیرفته می‌شود (در غیر این‌صورت DKK 7,426/ماه).</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>⭐⭐⭐ بالاترین حقوق اروپا و هاب Big Tech در زوریخ؛ ولی برای غیر-EU فقط ۶ ماه فرصت، سهمیه و شرط «منفعت اقتصادی بالا» → عملاً فقط شرکت‌های بزرگ/اسپین‌آف‌های ETH اسپانسر می‌شوند؛ رقابت با فارغ‌التحصیلان ETH/EPFL و EU؛ بازار ۲۰۲۶ گزینشی‌تر</t>
+          <t>CHF 21,000 برای هر سال (Basel 24,000) + شهریه؛ برای هر تمدید سالانه دوباره. زوریخ: فقط حساب بانک سوئیسی/شعبهٔ سوئیسی به نام خودتان (حساب والدین پذیرفته نیست) یا ضامن مقیم سوئیس (B/C)؛ بانک‌های سوئیس برای ساکنان ایران حساب باز نمی‌کنند → عملاً از تهران فقط با ضامن، یا کانتون‌های انعطاف‌پذیرتر (تیچینو، فریبورگ، نوشاتل، برن، لوسرن — قبل از اقدام از دفتر بین‌الملل دانشگاه تأیید بگیرید). انتقال پول فقط از مسیر کشور ثالث.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>⭐⭐ بازار جونیور اشباع؛ اسپانسری £38,290+ برای جونیور نادر؛ بعد از ۱۸ ماه باید ویزای کار داشت</t>
+          <t>شهریه + £1,171 × ۹ = £10,539 خارج لندن / £13,761 لندن؛ از ۳۰ نوامبر ۲۰۲۶: £10,827 / £14,130؛ ۲۸ روز متوالی در حساب؛ + ویزای دانشجویی £524 + IHS با نرخ دانشجویی £776/سال (برای ۱۶ ماه اقامت ≈ £1,164).</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>ارزیابی بر اساس ردیف‌های ۱۳، ۱۵، ۱۶، ۱۷</t>
+          <t>make-it-in-germany.com؛ ind.nl؛ migrationsverket.se؛ nyidanmark.dk؛ sem.admin.ch؛ gov.uk (HC 584). افتتاح حساب بانکی برای ایرانی‌ها در همه‌جا کندتر است (آلمان و هلند بیشترین گزارش مشکل).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>۲۷</t>
+          <t>۲۶</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>جهت‌گیری سیاست‌های مهاجرتی ۲۰۲۵–۲۶ (ریسک تغییر تا ۲۰۲۸)</t>
+          <t>بازار کار برای جونیورِ فقط‌انگلیسی‌زبان (ارزیابی، ۱–۵ ستاره)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>متوسط: قوانین کار پایدار؛ تابعیت ۳ ساله حذف شد</t>
+          <t>⭐⭐⭐ تقاضا و حقوق بالا؛ بدون آلمانی نیمی از بازار بسته</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>متوسط: B1 برای PR/تابعیت؛ WIB فقط کارشناسی انگلیسی را هدف گرفته (ارشد امن)</t>
+          <t>⭐⭐⭐⭐ انگلیسی‌دوست‌ترین بازار قاره؛ کف HSM فارغ‌التحصیل دست‌یافتنی</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>بالا: شهروندی ۸ سال، کف حقوق ۹۰٪ میانه، سقف کار ۱۵ ساعت، تبدیل اقامت تحصیلی به کاری فقط بعد از ≥ ۲ ترم</t>
+          <t>⭐⭐ بازار ۲۰۲۴–۲۶ ضعیف؛ شبکه محلی مهم</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>متوسط–بالا: سخت‌گیرانه ولی پایدار</t>
+          <t>⭐⭐ بدون دانمارکی محدود؛ خارج از Copenhagen سخت</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>متوسط: ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ رد شد (۵۴.۸٪ نه)؛ ولی بستهٔ صرفه‌جویی EP27 (۲۰۲۷–۲۹) → احتمال افزایش دوبارهٔ شهریهٔ ETH/EPFL برای خارجی‌ها؛ سهمیهٔ غیر-EU ثابت (۸,۵۰۰)؛ بستهٔ قراردادهای جدید با EU (Bilaterals III) در راه رفراندوم</t>
+          <t>⭐⭐⭐ بالاترین حقوق اروپا و هاب Big Tech در زوریخ؛ ولی برای غیر-EU فقط ۶ ماه فرصت، سهمیه و شرط «منفعت اقتصادی بالا» → عملاً فقط شرکت‌های بزرگ/اسپین‌آف‌های ETH اسپانسر می‌شوند؛ رقابت با فارغ‌التحصیلان ETH/EPFL و EU؛ بازار ۲۰۲۶ گزینشی‌تر</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>بسیار بالا: Graduate visa ۱۸ ماه، B2، طرح PR ۱۰ ساله، عوارض £925/دانشجو/سال از اوت ۲۰۲۸ فقط برای دانشگاه‌های انگلستان — دورهٔ یک‌سالهٔ شما (سپتامبر ۲۰۲۷ تا سپتامبر ۲۰۲۸) عملاً از آن رد می‌شود، ولی بعضی دانشگاه‌ها ممکن است از ۲۰۲۷ در شهریه پیش‌خور کنند</t>
+          <t>⭐⭐ بازار جونیور اشباع؛ اسپانسری £38,290+ برای جونیور نادر؛ بعد از ۱۸ ماه باید ویزای کار داشت</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>قوانین و لوایح ۲۰۲۵–۲۶</t>
+          <t>ارزیابی بر اساس ردیف‌های ۱۳، ۱۵، ۱۶، ۱۷</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>۲۷</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>جهت‌گیری سیاست‌های مهاجرتی ۲۰۲۵–۲۶ (ریسک تغییر تا ۲۰۲۸)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>متوسط: قوانین کار پایدار؛ تابعیت ۳ ساله حذف شد</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>متوسط: B1 برای PR/تابعیت؛ WIB فقط کارشناسی انگلیسی را هدف گرفته (ارشد امن)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>بالا: شهروندی ۸ سال، کف حقوق ۹۰٪ میانه، سقف کار ۱۵ ساعت، تبدیل اقامت تحصیلی به کاری فقط بعد از ≥ ۲ ترم</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>متوسط–بالا: سخت‌گیرانه ولی پایدار</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>متوسط: ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ رد شد (۵۴.۸٪ نه)؛ ولی بستهٔ صرفه‌جویی EP27 (۲۰۲۷–۲۹) → احتمال افزایش دوبارهٔ شهریهٔ ETH/EPFL برای خارجی‌ها؛ سهمیهٔ غیر-EU ثابت (۸,۵۰۰)؛ بستهٔ قراردادهای جدید با EU (Bilaterals III) در راه رفراندوم</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>بسیار بالا: Graduate visa ۱۸ ماه، B2، طرح PR ۱۰ ساله، عوارض £925/دانشجو/سال از اوت ۲۰۲۸ فقط برای دانشگاه‌های انگلستان — دورهٔ یک‌سالهٔ شما (سپتامبر ۲۰۲۷ تا سپتامبر ۲۰۲۸) عملاً از آن رد می‌شود، ولی بعضی دانشگاه‌ها ممکن است از ۲۰۲۷ در شهریه پیش‌خور کنند</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>قوانین و لوایح ۲۰۲۵–۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>۲۸</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>امتیاز برای ۳ معیار شما (هر کدام از ۱۰): هزینه کل / زندگی و کار فقط با انگلیسی / بازار کار و حقوق</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>10 / 4 / 8 = ۲۲</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>2 / 8 / 8 = ۱۸</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>6 / 8 / 5 = ۱۹</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>4 / 6 / 6 = ۱۶</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>5 / 6 / 7 = ۱۸</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>5 / 10 / 4 = ۱۹</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>وزن برابر. اگر «هزینه» وزن بیشتری دارد و B1 آلمانی را می‌پذیرید → آلمان؛ اگر «انگلیسی» وزن بیشتری دارد → انگلستان (کامل) و بعد هلند/سوئد؛ اگر «حقوق» وزن بیشتری دارد → سوئیس، به شرط پذیرش ریسک پنجرهٔ ۶ ماههٔ کار و هزینهٔ زندگی. سوئیس: هزینه ۵ (شهریه ناچیز ولی زندگی گران‌ترین)، انگلیسی ۶ (تحصیل و Big Tech انگلیسی، اداری/PR زبان محلی)، بازار ۷ (بالاترین حقوق، ولی دسترسی محدود برای غیر-EU). انگلستان با گزینه‌های ارزان شمال (Teesside/Northumbria) ۱۹ (هم‌امتیاز سوئد) ولی هنوز از بودجهٔ سالانه $32k بیرون است.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>تاریخ راستی‌آزمایی: ۲۷ سپتامبر ۲۰۲۶ (۵ مهر ۱۴۰۵). نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>همه ارقام سطح 2026/27 و از منابع رسمی (شیت «منابع»)؛ برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 را بگیرید (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪). ردیف‌های ۱۳، ۱۴، ۱۷–۱۹، ۲۶ برآورد/ارزیابی هستند و در ستون منبع مشخص شده‌اند.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
+          <t>همه ارقام سطح 2026/27 و از منابع رسمی (شیت «منابع»)؛ برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 را بگیرید (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪). ردیف‌های ۱۳، ۱۴، ۱۷–۱۹، ۲۶ برآورد/ارزیابی هستند و در ستون منبع مشخص شده‌اند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
           <t>جدول اولیه (Table.xlsx) برای مقایسه دست‌نخورده مانده است.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>شیت «برنامه‌ها»: ≈۱۰۰ برنامهٔ انگلیسی‌زبان در ۸ حوزهٔ کامپیوتری (نه فقط CS) برای هر ۶ کشور؛ شیت «حوزه‌ها و بازار کار»: کدام حوزه برای شما بازار و پذیرش بهتری دارد.</t>
         </is>
@@ -12239,7 +12317,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>• هزینه کل دوره اضافه شد (هلند از «نیاز به تأمین سال دوم» به گران‌ترین گزینه تبدیل شد)
+          <t>• ردیف ۵ب (بورس/تخفیف شهریهٔ واقعاً در دسترس شما) اضافه شد — ۲۸ سپتامبر ۲۰۲۶؛ امتیازها را عوض نمی‌کند
+• هزینه کل دوره اضافه شد (هلند از «نیاز به تأمین سال دوم» به گران‌ترین گزینه تبدیل شد)
 • فقط انگلستان (به خواست شما): Strathclyde و Swansea حذف شدند؛ گزینه‌ها Teesside £17,000 · Northumbria £21,500 · Leicester £24,250 · Essex £24,675 · Brunel £24,795 · York £32,900؛ Graduate visa ۱۸ ماه؛ کف اسپانسری £54,700 / £38,290؛ طرح PR ۱۰ ساله؛ عوارض £925 از ۲۰۲۸ شامل همهٔ گزینه‌ها
 • کف حقوق ۲۰۲۶ همه کشورها به‌روز شد (آلمان €50,700/€45,934؛ هلند €3,122/ماه؛ سوئد SEK 34,470)
 • ایرلند به خواست شما به‌کلی حذف و سوئیس جایگزین شد (سپتامبر ۲۰۲۶): شهریه‌های 2026/27 ETH/EPFL/UZH/USI/ZHAW/HSLU، تمکن CHF 21,000، ۶ ماه جست‌وجوی کار، سهمیهٔ غیر-EU، اجازهٔ C ۱۰ ساله، حقوق جونیور CHF 85–105k، سفارت تهران (ویزای D فعال)
@@ -12297,7 +12376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B158"/>
+  <dimension ref="A1:B173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12787,1414 +12866,1594 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – ETH: تاریخ‌های اپلای ارشد پاییز ۲۰۲۷ (۱–۳۰ نوامبر ۲۰۲۶؛ پاسخ تا پایان مارس؛ شروع ۲۰ سپتامبر ۲۰۲۷)</t>
+          <t>بورس – LiU International Scholarship: معمولاً ۵۰٪؛ شرط جدید ۲۰۲۶ (GPA ≥ 3.5/4 یا first/high second class)؛ فقط اولویت ۱</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>https://ethz.ch/en/studies/master/application/dates.html</t>
+          <t>https://liu.se/en/article/scholarships</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EPFL: شهریه CHF 2,240/ترم برای خارجی‌های غیرمقیم از پاییز ۲۰۲۵ (CHF 780 برای بقیه)</t>
+          <t>بورس – Chalmers: بورس‌های شهریه‌پردازها (IPOET ۷۵٪ با حداقل معدل ۸۰٪، Avancez)</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/education/studies/en/rules-and-procedures/study-taxes/tuition-fee-other-fees/</t>
+          <t>https://www.chalmers.se/en/education/application-and-admission/scholarships-for-fee-paying-students/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EPFL: پنجره‌های اپلای ارشد (۱۵ دسامبر / ۳۱ مارس؛ یک برنامه در سال)</t>
+          <t>بورس – Halmstad University Scholarship ۲۵٪/۵۰٪ برای غیر-EU (ثانویه؛ hh.se را چک کنید)</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/education/admission/admission-2/master-admission-criteria-application/online-application/</t>
+          <t>https://www.mastersportal.com/scholarships/10077/halmstad-university-scholarships.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – UZH: شهریه CHF 720 + 100 (خارجی، ارشد) + 59؛ هزینهٔ درخواست CHF 150</t>
+          <t>بورس – MDU: بورس تا ۱۰۰٪ شهریه برای متقاضیان اولویت ۱ (ثانویه؛ mdu.se را چک کنید)</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>https://www.uzh.ch/en/studies/application/fees.html</t>
+          <t>https://daadscholarship.com/malardalen-university-scholarships-2026-to-study-for-free-in-sweden/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – UZH: مهلت ویزایی‌ها ۲۸ فوریه / بدون ویزا ۳۰ آوریل (پاییز)</t>
+          <t>بورس – SI Scholarship for Global Professionals: ۳۴ کشور واجد شرایط — ایران نیست (رسمی)</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>https://www.oec.uzh.ch/en/studies/general/admission/master/faq-master-admission.html</t>
+          <t>https://si.se/en/apply/scholarships/swedish-institute-scholarships-for-global-professionals/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI MSc Informatics: CHF 4,000/ترم غیرمقیم، B2 در ورود → C1، مهلت غیر-EU ۳۰ آوریل</t>
+          <t>بورس – NL Scholarship (سابقاً Holland Scholarship): €5,000 سال اول برای غیر-EEA، از طریق دانشگاه‌های عضو</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>https://www.usi.ch/en/education/master/informatics</t>
+          <t>https://www.mastersportal.com/scholarships/988/holland-scholarship-for-non-eea-international-students.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI MSc Artificial Intelligence: CHF 4,000/ترم، IELTS 6.5</t>
+          <t>بورس – AAU: ≈ ۱۵ بورس دولتی در سال، معافیت شهریه + DKK 11,225/ماه (۲۰۲۶)، بررسی خودکار (رسمی)</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/usi-universita-della-svizzera-italiana/postgrad/master-science-artificial-intelligence</t>
+          <t>https://www.en.aau.dk/education/apply/master/finance-and-fees</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – swissuniversities: شهریهٔ دانشگاه‌های علوم کاربردی 2026–27 (ZHAW 1,220؛ HSLU 1,300؛ OST 1,500؛ FHNW 1,000–5,000)</t>
+          <t>بورس – ETH Excellence Scholarship &amp; Opportunity Programme: CHF 12,000/ترم + معافیت؛ ۱۰٪ بالای کلاس؛ ۱–۳۰ نوامبر</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>https://www.swissuniversities.ch/en/themen/lehre-studium/information-on-studies/tuition-fees/tuition-fees-at-uas</t>
+          <t>https://ethz.ch/en/studies/financial/scholarships/excellencescholarship.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – ZHAW MSE: انگلیسی، 90 ECTS، پروفایل‌های CS/Data Science/Cyber، معدل A/B، مهلت پایان آوریل</t>
+          <t>بورس – USI: بورس‌های Fondazione per le Facoltà di Lugano (CHF 4,000؛ سال اول با معدل ≥ ۸۰/۱۰۰؛ سال دوم بهترینِ هر برنامه) — خبر رسمی USI</t>
         </is>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
+          <t>https://www.eco.usi.ch/en/feeds/9861</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – HSLU MSc Applied Information &amp; Data Science: C1 (B2 مشروط)، آلمانی لازم نیست، هر کارشناسی</t>
+          <t>بورس – Essex Academic Excellence International Masters Scholarship: جدول کشوری (ایران ۱۴/۲۰ → £4,500؛ جدول ۲۰۲۵–۲۶)</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/haeufig-gestellte-fragen/</t>
+          <t>https://www.essex.ac.uk/scholarships</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Bern: Swiss Joint MSc Computer Science (90 ECTS، انگلیسی، شرط کارشناسی CS)</t>
+          <t>بورس – Teesside Global Excellence Scholarship £2,000 (پیشنهاد تا ۳۰ آوریل؛ رسمی)</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
+          <t>https://www.tees.ac.uk/sections/international/global_excellence_scholarship.cfm</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Bern شهریه از پاییز ۲۰۲۶: CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها + 34 + 25 در ترم (رسمی)</t>
+          <t>بورس – Brunel Vice-Chancellor's Postgraduate International Excellence Award £6,000 (حداقل 2:1؛ ودیعهٔ £5,000)</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>https://www.unibe.ch/studies/organizational_matters/renewal_of_semester_registration/fees/index_eng.html</t>
+          <t>https://www.brunel.ac.uk/scholarships</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Joint MSc CS (Bern/Neuchâtel/Fribourg) FAQ رسمی: بدون آزمون زبان (B2 توصیه)، شرط کارشناسی CS یا معادل با حداکثر ۶۰ ECTS تکمیلی، مهلت‌های دیرهنگام</t>
+          <t>بورس – Northumbria PGT International Scholarship £3,000: فهرست کشوری/ادامه‌تحصیلی‌های داخل UK — ایران نیست</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>https://mcs.unibnf.ch/faq/</t>
+          <t>https://www.mastersportal.com/scholarships/3890/pgt-international-scholarships.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Neuchâtel شهریهٔ خارجی‌ها CHF 790/ترم (رسمی)</t>
+          <t>بورس – Chevening eligibility (رسمی): ۲ سال کار بعد از مدرک کارشناسی + تعهد بازگشت ۲ ساله؛ مهلت ۶ اکتبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>https://www.unine.ch/admission/taxes-universitaires/</t>
+          <t>https://www.chevening.org/resource-hub/guidance/eligibility/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Neuchâtel مهلت ارشد ۳۰ آوریل؛ خارجی‌ها یک ماه زودتر؛ هزینهٔ پرونده CHF 100 (رسمی)</t>
+          <t>بورس – Deutschlandstipendium €300/ماه (رسمی)</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>https://www.unine.ch/admission/admission-master/delais-et-frais-dinscription-pour-les-masters/</t>
+          <t>https://www.deutschlandstipendium.de/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Fribourg شهریهٔ خارجی‌ها CHF 870 + 115 = 985/ترم (رسمی)</t>
+          <t>سوئیس – ETH: تاریخ‌های اپلای ارشد پاییز ۲۰۲۷ (۱–۳۰ نوامبر ۲۰۲۶؛ پاسخ تا پایان مارس؛ شروع ۲۰ سپتامبر ۲۰۲۷)</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>https://www.unifr.ch/studies/en/organisation/administrative-services-unifr-students/university-fees/</t>
+          <t>https://ethz.ch/en/studies/master/application/dates.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Fribourg مهلت ارشد با مدرک خارجی: ویزایی‌ها ۱–۲۸ فوریه، بقیه تا ۳۰ آوریل (رسمی)</t>
+          <t>سوئیس – EPFL: شهریه CHF 2,240/ترم برای خارجی‌های غیرمقیم از پاییز ۲۰۲۵ (CHF 780 برای بقیه)</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>https://www.unifr.ch/studies/en/admission/admission-master/admission-master-foreign.html</t>
+          <t>https://www.epfl.ch/education/studies/en/rules-and-procedures/study-taxes/tuition-fee-other-fees/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Basel MSc CS: 90 ECTS، انگلیسی، مهلت ۳۰ آوریل / ۳۰ نوامبر (رسمی)</t>
+          <t>سوئیس – EPFL: پنجره‌های اپلای ارشد (۱۵ دسامبر / ۳۱ مارس؛ یک برنامه در سال)</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
+          <t>https://www.epfl.ch/education/admission/admission-2/master-admission-criteria-application/online-application/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Basel شهریه CHF 850/ترم برای همه + CHF 100 هزینهٔ درخواست (Uni Info 2026/27)</t>
+          <t>سوئیس – UZH: شهریه CHF 720 + 100 (خارجی، ارشد) + 59؛ هزینهٔ درخواست CHF 150</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>https://www.unibas.ch/dam/jcr:28672e66-8562-4988-9e38-b1c944ed22bf/COMPUTER%20SCIENCE%202026.2026-02-05-09-53-32.pdf</t>
+          <t>https://www.uzh.ch/en/studies/application/fees.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – HSLU MSc Applied Data Science and AI (نام جدید): مهلت ویزایی‌ها ۱ آوریل، CHF 1,300/ترم خارجی، CHF 250 درخواست، 120 ECTS (رسمی)</t>
+          <t>سوئیس – UZH: مهلت ویزایی‌ها ۲۸ فوریه / بدون ویزا ۳۰ آوریل (پاییز)</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
+          <t>https://www.oec.uzh.ch/en/studies/general/admission/master/faq-master-admission.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI مهلت‌های 2026/27: غیر-EU ۳۰ آوریل؛ هزینهٔ پرونده CHF 100 برای مدارک خارج از کنوانسیون لیسبون (رسمی)</t>
+          <t>سوئیس – USI MSc Informatics: CHF 4,000/ترم غیرمقیم، B2 در ورود → C1، مهلت غیر-EU ۳۰ آوریل</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>https://www.usi.ch/en/education/master/informatics/application</t>
+          <t>https://www.usi.ch/en/education/master/informatics</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
+          <t>سوئیس – USI MSc Artificial Intelligence: CHF 4,000/ترم، IELTS 6.5</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
+          <t>https://www.topuniversities.com/universities/usi-universita-della-svizzera-italiana/postgrad/master-science-artificial-intelligence</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
+          <t>سوئیس – swissuniversities: شهریهٔ دانشگاه‌های علوم کاربردی 2026–27 (ZHAW 1,220؛ HSLU 1,300؛ OST 1,500؛ FHNW 1,000–5,000)</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
+          <t>https://www.swissuniversities.ch/en/themen/lehre-studium/information-on-studies/tuition-fees/tuition-fees-at-uas</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
+          <t>سوئیس – ZHAW MSE: انگلیسی، 90 ECTS، پروفایل‌های CS/Data Science/Cyber، معدل A/B، مهلت پایان آوریل</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
+          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
+          <t>سوئیس – HSLU MSc Applied Information &amp; Data Science: C1 (B2 مشروط)، آلمانی لازم نیست، هر کارشناسی</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/haeufig-gestellte-fragen/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
+          <t>سوئیس – Bern: Swiss Joint MSc Computer Science (90 ECTS، انگلیسی، شرط کارشناسی CS)</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
+          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
+          <t>سوئیس – Bern شهریه از پاییز ۲۰۲۶: CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها + 34 + 25 در ترم (رسمی)</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
+          <t>https://www.unibe.ch/studies/organizational_matters/renewal_of_semester_registration/fees/index_eng.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
+          <t>سوئیس – Joint MSc CS (Bern/Neuchâtel/Fribourg) FAQ رسمی: بدون آزمون زبان (B2 توصیه)، شرط کارشناسی CS یا معادل با حداکثر ۶۰ ECTS تکمیلی، مهلت‌های دیرهنگام</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
+          <t>https://mcs.unibnf.ch/faq/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
+          <t>سوئیس – Neuchâtel شهریهٔ خارجی‌ها CHF 790/ترم (رسمی)</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
+          <t>https://www.unine.ch/admission/taxes-universitaires/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
+          <t>سوئیس – Neuchâtel مهلت ارشد ۳۰ آوریل؛ خارجی‌ها یک ماه زودتر؛ هزینهٔ پرونده CHF 100 (رسمی)</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
+          <t>https://www.unine.ch/admission/admission-master/delais-et-frais-dinscription-pour-les-masters/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
+          <t>سوئیس – Fribourg شهریهٔ خارجی‌ها CHF 870 + 115 = 985/ترم (رسمی)</t>
         </is>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
+          <t>https://www.unifr.ch/studies/en/organisation/administrative-services-unifr-students/university-fees/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
+          <t>سوئیس – Fribourg مهلت ارشد با مدرک خارجی: ویزایی‌ها ۱–۲۸ فوریه، بقیه تا ۳۰ آوریل (رسمی)</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
+          <t>https://www.unifr.ch/studies/en/admission/admission-master/admission-master-foreign.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
+          <t>سوئیس – Basel MSc CS: 90 ECTS، انگلیسی، مهلت ۳۰ آوریل / ۳۰ نوامبر (رسمی)</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
+          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
+          <t>سوئیس – Basel شهریه CHF 850/ترم برای همه + CHF 100 هزینهٔ درخواست (Uni Info 2026/27)</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
+          <t>https://www.unibas.ch/dam/jcr:28672e66-8562-4988-9e38-b1c944ed22bf/COMPUTER%20SCIENCE%202026.2026-02-05-09-53-32.pdf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
+          <t>سوئیس – HSLU MSc Applied Data Science and AI (نام جدید): مهلت ویزایی‌ها ۱ آوریل، CHF 1,300/ترم خارجی، CHF 250 درخواست، 120 ECTS (رسمی)</t>
         </is>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
+          <t>سوئیس – USI مهلت‌های 2026/27: غیر-EU ۳۰ آوریل؛ هزینهٔ پرونده CHF 100 برای مدارک خارج از کنوانسیون لیسبون (رسمی)</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
+          <t>https://www.usi.ch/en/education/master/informatics/application</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
+          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
         </is>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
+          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
+          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
+          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
+          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
         </is>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
+          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
+          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
         </is>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
+          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
+          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
         </is>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
+          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
+          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
+          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
+          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
         </is>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
+          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
+          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
         </is>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
+          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
+          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
+          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
+          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
+          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
+          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
         </is>
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
+          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
+          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
         </is>
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
+          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
+          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
         </is>
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
+          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
+          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
         </is>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
+          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
+          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
         </is>
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
+          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – وضعیت VAC تهران</t>
+          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
         </is>
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
+          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – TU Dresden</t>
+          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
         </is>
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
+          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Stuttgart</t>
+          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
         </is>
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
+          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Newcastle 149</t>
+          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
         </is>
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
+          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – York =158</t>
+          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/about/rankings/</t>
+          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Leicester =314</t>
+          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
         </is>
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/university-leicester</t>
+          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Essex =438</t>
+          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/essex-university</t>
+          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Northumbria =528</t>
+          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
         </is>
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Brunel</t>
+          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
         </is>
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – سایر</t>
+          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
         </is>
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/world-university-rankings</t>
+          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
+          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
         </is>
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
+          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
         </is>
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>https://www.xe.com/</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
+          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
         </is>
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
+          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
+          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
         </is>
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
+          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
+          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
         </is>
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>https://www.isc2.org/research</t>
+          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
+          <t>بریتانیا – وضعیت VAC تهران</t>
         </is>
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
+          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
+          <t>QS WUR 2027 – TU Dresden</t>
         </is>
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
+          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
+          <t>QS WUR 2027 – Stuttgart</t>
         </is>
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
+          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
+          <t>QS WUR 2027 – Newcastle 149</t>
         </is>
       </c>
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
+          <t>QS WUR 2027 – York =158</t>
         </is>
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+          <t>https://www.york.ac.uk/about/rankings/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
+          <t>QS WUR 2027 – Leicester =314</t>
         </is>
       </c>
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+          <t>https://www.topuniversities.com/universities/university-leicester</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Siegen MSc HCI (DAAD)</t>
+          <t>QS WUR 2027 – Essex =438</t>
         </is>
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+          <t>https://www.topuniversities.com/universities/essex-university</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
+          <t>QS WUR 2027 – Northumbria =528</t>
         </is>
       </c>
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>آلمان – RWTH MSc Software Systems Engineering</t>
+          <t>QS WUR 2027 – Brunel</t>
         </is>
       </c>
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
+          <t>QS WUR 2027 – سایر</t>
         </is>
       </c>
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+          <t>https://www.topuniversities.com/world-university-rankings</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
+          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
         </is>
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
+          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+          <t>https://www.xe.com/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
+          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
         </is>
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>هلند – Leiden CS 2026/27: €22,500</t>
+          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
         </is>
       </c>
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>هلند – Groningen AI 2026/27: €24,900</t>
+          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
         </is>
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+          <t>https://www.isc2.org/research</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
+          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
         </is>
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
+          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
         </is>
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
+          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
+          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
         </is>
       </c>
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
+          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
         </is>
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Umeå AI: SEK 152,300</t>
+          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
         </is>
       </c>
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
+          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
         </is>
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>https://www.study.eu/best-universities/sweden</t>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
+          <t>آلمان – Siegen MSc HCI (DAAD)</t>
         </is>
       </c>
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
+          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
         </is>
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
+          <t>آلمان – RWTH MSc Software Systems Engineering</t>
         </is>
       </c>
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus CS €17,300</t>
+          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
         </is>
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>https://masters.au.dk/computerscience</t>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
+          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
         </is>
       </c>
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
+          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
         </is>
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
+          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
         </is>
       </c>
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
+          <t>هلند – Leiden CS 2026/27: €22,500</t>
         </is>
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
+          <t>هلند – Groningen AI 2026/27: €24,900</t>
         </is>
       </c>
       <c r="B136" s="16" t="inlineStr">
         <is>
-          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
+          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
         </is>
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
+          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
         </is>
       </c>
       <c r="B138" s="16" t="inlineStr">
         <is>
-          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
+          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – NTU QS 2027 =639</t>
+          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
         </is>
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
+          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
         </is>
       </c>
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
+          <t>سوئد – Umeå AI: SEK 152,300</t>
         </is>
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
+          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
         </is>
       </c>
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
+          <t>https://www.study.eu/best-universities/sweden</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
+          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
         </is>
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
+          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
         </is>
       </c>
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
+          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
         </is>
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
+          <t>دانمارک – Aarhus CS €17,300</t>
         </is>
       </c>
       <c r="B146" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+          <t>https://masters.au.dk/computerscience</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
         </is>
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
         </is>
       </c>
       <c r="B148" s="16" t="inlineStr">
         <is>
-          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
         </is>
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
         </is>
       </c>
       <c r="B150" s="16" t="inlineStr">
         <is>
-          <t>https://zandienglish.ir/toefl-in-iran/</t>
+          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
         </is>
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
         </is>
       </c>
       <c r="B152" s="16" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
         </is>
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+          <t>انگلستان – NTU QS 2027 =639</t>
         </is>
       </c>
       <c r="B154" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
         </is>
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
         </is>
       </c>
       <c r="B156" s="16" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
         </is>
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
+          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t>https://zandienglish.ir/toefl-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
           <t>هلند – Twente: مهلت غیر-EEA ۱ می ۲۰۲۷؛ بورس UTS ۱۵ اکتبر ۲۰۲۶ – ۱ آوریل ۲۰۲۷</t>
         </is>
       </c>
-      <c r="B158" s="16" t="inlineStr">
+      <c r="B173" s="16" t="inlineStr">
         <is>
           <t>https://collegedunia.com/netherlands/university/749-university-of-twente-enschede/admission</t>
         </is>
@@ -14359,6 +14618,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -15,7 +15,7 @@
     <sheet name="منابع" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2087,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q112"/>
+  <dimension ref="A1:Q118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4305,81 +4305,81 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>سوئیس</t>
+          <t>انگلستان</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>USI – Università della Svizzera italiana</t>
+          <t>Imperial College London (Russell Group)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
+          <t>London – مرکز (South Kensington / Bloomsbury / Strand؛ Imperial، UCL، KCL)</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,400–1,800</t>
+          <t>خیلی گران — £1,600–1,900 (برآورد خود Imperial: £16.4–17k برای ۹ ماه)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>MSc Informatics (گرایش‌ها: Artificial Intelligence، Software Development، Systems…)</t>
+          <t>MSc Computing (Artificial Intelligence and Machine Learning) / MSc Computing</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>CHF 4,000 در ترم برای غیرمقیم سوئیس (CHF 8,000/سال)</t>
+          <t>£46,000 (2026/27 رسمی؛ 2027/28 هنوز اعلام نشده)</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>$9,700</t>
+          <t>$61,000</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ فارغ‌التحصیل UAS با ۳۰–۶۰ ECTS تکمیلی؛ بررسی موردی</t>
+          <t>First-class honours در رشته‌ای با محتوای قابل توجه Computing — برای مدرک ایرانی ≥ ۱۷–۱۸/۲۰ → با ۱۵.۷۷ رسماً واجد شرایط نیستید</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>B2 در ورود (IELTS 5.5) → C1 (7.0) تا فارغ‌التحصیلی</t>
+          <t>7.0 (higher requirement؛ هر بخش ≥ 6.5)</t>
         </is>
       </c>
       <c r="M27" s="4">
-        <f>456</f>
+        <f>2</f>
         <v/>
       </c>
-      <c r="N27" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>کم‌شرط‌ترین ورود سوئیس؛ Lugano ارزان‌ترین شهر دانشگاهی سوئیس؛ مهلت غیر-EU ۳۰ آوریل ۲۰۲۷؛ زبان شهر ایتالیایی</t>
+          <t>QS 2027 #2 · LEO: میانهٔ درآمد فارغ‌التحصیلان Computing پنج سال بعد £79,600 · دورهای ۲۰۲۷: ۶ ژانویه / ۱۰ مارس / ۲۸ آوریل · Imperial Inspires £15,000 (رقابتی) · ❌ عملاً بسته برای معدل شما</t>
         </is>
       </c>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>https://www.usi.ch/en/education/master/informatics</t>
+          <t>https://www.imperial.ac.uk/study/courses/postgraduate-taught/computing-artificial-intelligence-msc/</t>
         </is>
       </c>
     </row>
@@ -4389,81 +4389,81 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>سوئیس</t>
+          <t>انگلستان</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>USI – Università della Svizzera italiana</t>
+          <t>UCL – University College London (Russell Group)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
+          <t>London – مرکز (South Kensington / Bloomsbury / Strand؛ Imperial، UCL، KCL)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,400–1,800</t>
+          <t>خیلی گران — £1,600–1,900 (برآورد خود Imperial: £16.4–17k برای ۹ ماه)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence (با IDSIA)</t>
+          <t>MSc Software Systems Engineering / MSc Machine Learning (MSc Computer Science تبدیلی است و برای فارغ‌التحصیل CS باز نیست)</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>CHF 4,000 در ترم برای غیرمقیم (CHF 8,000/سال)</t>
+          <t>≈ £42,700–46,700 (2026/27؛ MSc Computer Science رسماً £42,700)</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>$9,700</t>
+          <t>$56,600–61,900</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط با ریاضی و برنامه‌نویسی قوی؛ بررسی موردی</t>
+          <t>2:1 (upper second) — جدول تطبیق ایرانِ UCL را نتوانستم رسمی تأیید کنم (معمولاً ۱۵–۱۶/۲۰)؛ ریاضی قوی؛ هزینهٔ درخواست £90؛ ودیعهٔ ۱۰٪ شهریه</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>6.5 (B2؛ C1 تا پایان دوره)</t>
+          <t>7.0 (Level 2؛ هر بخش ≥ 6.5)</t>
         </is>
       </c>
       <c r="M28" s="4">
-        <f>456</f>
+        <f>9</f>
         <v/>
       </c>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="N28" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>اولین ارشد AI سوئیس؛ IDSIA (آزمایشگاه Schmidhuber/LSTM)؛ رقابتی‌تر از Informatics</t>
+          <t>QS 2027 #9 · High Fliers 2026: پنجمین دانشگاه هدف کارفرمایان بزرگ · لندن گران‌ترین زندگی · با ۱۵.۷۷ مرزی-پایین</t>
         </is>
       </c>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t>https://www.usi.ch/en/education/master/artificial-intelligence</t>
+          <t>https://www.ucl.ac.uk/prospective-students/graduate/taught-degrees/computer-science-msc-2026</t>
         </is>
       </c>
     </row>
@@ -4473,81 +4473,81 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>سوئیس</t>
+          <t>انگلستان</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>USI – Università della Svizzera italiana</t>
+          <t>King's College London (Russell Group)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
+          <t>London – مرکز (South Kensington / Bloomsbury / Strand؛ Imperial، UCL، KCL)</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,400–1,800</t>
+          <t>خیلی گران — £1,600–1,900 (برآورد خود Imperial: £16.4–17k برای ۹ ماه)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>MSc Software and Data Engineering</t>
+          <t>MSc Advanced Computing / MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>CHF 4,000 در ترم برای غیرمقیم (CHF 8,000/سال)</t>
+          <t>£40,450 (2026)</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>$9,700</t>
+          <t>$53,600</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط</t>
+          <t>«high 2:1» = ۶۵٪ — جدول رسمی KCL برای ایران: ۱۷/۲۰ (2:1 معمولی = ۱۵/۲۰، First = ۱۸/۲۰) → با ۱۵.۷۷ زیر خط، مگر با سابقهٔ کار قابل توجه</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>B2 → C1</t>
+          <t>7.0 (هر بخش ≥ 6.5)</t>
         </is>
       </c>
       <c r="M29" s="4">
-        <f>456</f>
+        <f>31</f>
         <v/>
       </c>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>ترکیب مهندسی نرم‌افزار + مهندسی داده (Data Engineering — همان توصیهٔ شیت حوزه‌ها)؛ کم‌رقابت‌تر از AI</t>
+          <t>QS 2027 ≈ 31 · Strand، مرکز لندن · نیاز به ۱۷/۲۰ یعنی «high 2:1» — سابقهٔ کار ۲ ساله ممکن است جبران کند (خود KCL این را می‌گوید)، ولی امیدوار نباشید</t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>https://www.usi.ch/en/education/master/software-and-data-engineering</t>
+          <t>https://www.kcl.ac.uk/study-legacy/postgraduate/apply/entry-requirements/international</t>
         </is>
       </c>
     </row>
@@ -4557,82 +4557,81 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>سوئیس</t>
+          <t>انگلستان</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Hochschule Luzern (HSLU)</t>
+          <t>University of Warwick (Russell Group)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Lucerne / Luzern (لوسرن) — مرکز سوئیس، ۴۵ دقیقه تا زوریخ</t>
+          <t>Coventry (کاونتری) — کمپوس Warwick؛ میدلندز</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,550–1,950</t>
+          <t>متوسط — £1,000–1,250</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>MSc Applied Data Science and AI (نام جدید از اوت ۲۰۲۶؛ قبلاً Applied Information and Data Science)</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS؛ معمولاً ۴ ترم، قابل تمدید تا ۸)</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>CHF 1,300 در ترم (خارجی) + ≈ CHF 275 هزینهٔ جانبی ≈ CHF 3,150/سال؛ هزینهٔ درخواست CHF 250</t>
+          <t>£37,460 (2026 entry)</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>$3,800</t>
+          <t>$49,600</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>هر کارشناسی (دانشگاه یا UAS)؛ آزمون انگلیسی + آزمون استعداد HSLU</t>
+          <t>2:1 — جدول رسمی Warwick برای ایران: 1st = ۱۷/۲۰، 2:1 = ۱۵/۲۰، 2:2 = ۱۳/۲۰ → ۱۵.۷۷ ✓ (پذیرش PGT ≈ ۲۲٪، رقابتی)</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>C1 (B2 مشروط)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+          <t>7.0 (اکثر PGT؛ بعضی 6.5)</t>
+        </is>
+      </c>
+      <c r="M30" s="4">
+        <f>69</f>
+        <v/>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>«باز برای تغییر رشته‌ای‌ها»، کاربردی و مدیریتی؛ ترکیبی (حضوری/آنلاین)؛ آلمانی لازم نیست؛ شروع سپتامبر/فوریه؛ ⚠️ مهلت ویزایی‌ها ۱ آوریل ۲۰۲۷ (رسمی؛ Swiss/EU تا ۱ ژوئن)</t>
+          <t>QS 2027 ≈ 69 · High Fliers 2026: چهارمین دانشگاه هدف کارفرمایان · Coventry ارزان‌تر از لندن · هزینهٔ درخواست £75، ودیعهٔ £2,500 · واقع‌بینانه‌ترین «برند بزرگ» برای معدل شما</t>
         </is>
       </c>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
+          <t>https://warwick.ac.uk/study/international/countryinformation/middleeast/iran/</t>
         </is>
       </c>
     </row>
@@ -4642,81 +4641,81 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>سوئیس</t>
+          <t>انگلستان</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>University of Bern</t>
+          <t>University of Bristol (Russell Group)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Bern (برن) — پایتخت؛ آلمانی‌زبان</t>
+          <t>Bristol (بریستول) — جنوب غرب؛ قطب فناوری/هوافضا</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,600–2,000</t>
+          <t>گران — £1,200–1,450</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Swiss Joint MSc Computer Science (Bern / Neuchâtel / Fribourg)</t>
+          <t>MSc Data Science (برای فارغ‌التحصیل CS/مهندسی؛ MSc Computer Science بریستول تبدیلی است)</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>۱.۵ سال (90 ECTS)</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها (از پاییز ۲۰۲۶) + 34 + 25 = CHF 2,609 در ترم (≈ CHF 5,200/سال)</t>
+          <t>£37,900 (2027/28 رسمی — ورودی سپتامبر ۲۰۲۷)</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>$6,300</t>
+          <t>$50,200</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی Computer Science یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی — دروس تکمیلی ممکن است آلمانی/فرانسه باشند)</t>
+          <t>«strong 2:1 (۶۵٪+)» در CS/مهندسی/علوم عددی؛ صفحهٔ ایرانِ بریستول: کارشناسی ۴ ساله از دانشگاه مورد تأیید با حداقل ۱۵/۲۰ → ۱۵.۷۷ حداقل را رد می‌کند ولی «strong» نیست</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
+          <t>6.5 (Profile E) — چک شود</t>
         </is>
       </c>
       <c r="M31" s="4">
-        <f>191</f>
+        <f>54</f>
         <v/>
       </c>
-      <c r="N31" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>⚠️ شهریهٔ خارجی‌ها از پاییز ۲۰۲۶ سه‌برابر شد (رسمی unibe.ch) → همان مدرک مشترک را از Neuchâtel (CHF 790/ترم) یا Fribourg (CHF 985/ترم) بگیرید؛ مهلت ۳۰ آوریل — ویزایی‌ها مهلت دیرهنگام ندارند</t>
+          <t>QS 2027 ≈ 54 · LEO: میانهٔ Computing پنج سال بعد £70,300 · High Fliers: پنجم (۲۰۲۵) · Think Big Scholarship (رقابتی) · با ۱۵.۷۷ Reach</t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
+          <t>https://www.bristol.ac.uk/study/postgraduate/taught/msc-data-science/</t>
         </is>
       </c>
     </row>
@@ -4726,27 +4725,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>سوئیس</t>
+          <t>انگلستان</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>University of Neuchâtel</t>
+          <t>Durham University (Russell Group)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Neuchâtel (نوشاتل) — فرانسه‌زبان؛ کنار دریاچه؛ ۳۵ دقیقه تا برن</t>
+          <t>Durham (دورهام) — شمال شرق؛ ۱۵ دقیقه تا نیوکاسل</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — CHF 1,350–1,750</t>
+          <t>ارزان تا متوسط — £950–1,200</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Swiss Joint MSc Computer Science (ثبت‌نام در Neuchâtel)</t>
+          <t>MSc Advanced Computer Science (و MSc Data Science)</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -4756,33 +4755,32 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>۱.۵ سال (90 ECTS)</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>CHF 790 در ترم (خارجی؛ شامل همهٔ هزینه‌ها) = CHF 1,580/سال</t>
+          <t>£34,500 (2026 entry)</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>$1,900</t>
+          <t>$45,700</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی)</t>
+          <t>2:1 در CS — جدول رسمی Durham برای ایران: 1st ≥ ۱۷/۲۰، 2:1 = ۱۴–۱۶/۲۰، 2:2 = ۱۲–۱۳/۲۰ (دانشگاه باید در فهرست Ecctis باشد) → ۱۵.۷۷ ✓</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>6.5 (هر بخش ≥ 6.0)</t>
+        </is>
+      </c>
+      <c r="M32" s="4">
+        <f>94</f>
+        <v/>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
@@ -4796,12 +4794,12 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌ترین شهریهٔ سوئیس؛ همان مدرک مشترک Bern/Fribourg (دروس در سه شهر، بلیت قطار جبران می‌شود)؛ مهلت ۳۰ آوریل (خارجی‌ها: تا ۳۱ مارس بفرستید)؛ هزینهٔ پرونده CHF 100 از شهریه کم می‌شود؛ شهر فرانسه‌زبان</t>
+          <t>QS 2027 ≈ 94 · High Fliers 2025: دهم · ارزان‌ترین شهر بین این شش · ارزان‌ترین Russell Group این فهرست بعد از York/Newcastle · شروع سپتامبر ۲۰۲۶ اعلام شده؛ ۲۰۲۷ مشابه</t>
         </is>
       </c>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>https://mcs.unibnf.ch/</t>
+          <t>https://www.durham.ac.uk/study/courses/advanced-computer-science-g5t609/</t>
         </is>
       </c>
     </row>
@@ -4816,22 +4814,22 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>University of Fribourg</t>
+          <t>USI – Università della Svizzera italiana</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Fribourg (فریبورگ) — دوزبانه (آلمانی/فرانسه)</t>
+          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,450–1,800</t>
+          <t>گران — CHF 1,400–1,800</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Swiss Joint MSc Computer Science (ثبت‌نام در Fribourg)</t>
+          <t>MSc Informatics (گرایش‌ها: Artificial Intelligence، Software Development، Systems…)</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -4841,31 +4839,31 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>۱.۵ سال (90 ECTS)</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>CHF 870 + 115 = CHF 985 در ترم (خارجی؛ رسمی) = CHF 1,970/سال</t>
+          <t>CHF 4,000 در ترم برای غیرمقیم سوئیس (CHF 8,000/سال)</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>$2,400</t>
+          <t>$9,700</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی)</t>
+          <t>کارشناسی CS/مرتبط؛ فارغ‌التحصیل UAS با ۳۰–۶۰ ECTS تکمیلی؛ بررسی موردی</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
+          <t>B2 در ورود (IELTS 5.5) → C1 (7.0) تا فارغ‌التحصیلی</t>
         </is>
       </c>
       <c r="M33" s="4">
-        <f>670</f>
+        <f>456</f>
         <v/>
       </c>
       <c r="N33" s="10" t="inlineStr">
@@ -4880,12 +4878,12 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>همان برنامهٔ مشترک Bern/Neuchâtel؛ شهر دوزبانه و ارزان‌تر؛ ⚠️ مهلت ویزایی‌ها ۱–۲۸ فوریه ۲۰۲۷ (رسمی unifr.ch)</t>
+          <t>کم‌شرط‌ترین ورود سوئیس؛ Lugano ارزان‌ترین شهر دانشگاهی سوئیس؛ مهلت غیر-EU ۳۰ آوریل ۲۰۲۷؛ زبان شهر ایتالیایی</t>
         </is>
       </c>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>https://www.unifr.ch/inf/en/</t>
+          <t>https://www.usi.ch/en/education/master/informatics</t>
         </is>
       </c>
     </row>
@@ -4900,76 +4898,76 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>University of Basel</t>
+          <t>USI – Università della Svizzera italiana</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Basel (بازل) — Roche، Novartis؛ مرز آلمان/فرانسه</t>
+          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>گران — CHF 1,600–2,100</t>
+          <t>گران — CHF 1,400–1,800</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Artificial Intelligence (با IDSIA)</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>۱.۵ سال (90 ECTS)</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>CHF 850 در ترم (برای همه؛ بدون اضافهٔ خارجی‌ها — رسمی 2026/27) = CHF 1,700/سال</t>
+          <t>CHF 4,000 در ترم برای غیرمقیم (CHF 8,000/سال)</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>$2,100</t>
+          <t>$9,700</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS یا معادل با نمرات خوب؛ بررسی فردی</t>
+          <t>کارشناسی CS/مرتبط با ریاضی و برنامه‌نویسی قوی؛ بررسی موردی</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>B2–C1 (چک شود)</t>
+          <t>6.5 (B2؛ C1 تا پایان دوره)</t>
         </is>
       </c>
       <c r="M34" s="4">
-        <f>150</f>
+        <f>456</f>
         <v/>
       </c>
-      <c r="N34" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>رتبهٔ ۱۵۰؛ 90 ECTS انگلیسی؛ هزینهٔ درخواست CHF 100؛ ⚠️ کانتون Basel تمکن CHF 24,000/سال می‌خواهد؛ مهلت ۳۰ آوریل (رسمی)</t>
+          <t>اولین ارشد AI سوئیس؛ IDSIA (آزمایشگاه Schmidhuber/LSTM)؛ رقابتی‌تر از Informatics</t>
         </is>
       </c>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
+          <t>https://www.usi.ch/en/education/master/artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -4984,76 +4982,76 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>University of Zurich (UZH)</t>
+          <t>USI – Università della Svizzera italiana</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
+          <t>Lugano (لوگانو) — تیچینو، ایتالیایی‌زبان؛ IDSIA؛ ارزان‌ترین شهر دانشگاهی سوئیس</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,900–2,500</t>
+          <t>گران — CHF 1,400–1,800</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>MSc Informatics (گرایش‌ها: Software Systems، Data Science، People-Oriented Computing…)</t>
+          <t>MSc Software and Data Engineering</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>۱.۵–۲ سال (90/120 ECTS)</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>CHF 720 + 100 (خارجی) + 59 = CHF 879 در ترم (≈ CHF 1,760/سال)</t>
+          <t>CHF 4,000 در ترم برای غیرمقیم (CHF 8,000/سال)</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>$2,100</t>
+          <t>$9,700</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی Informatics/CS با نمرات بسیار خوب؛ فقط یک درخواست در هر ترم؛ هزینهٔ درخواست CHF 150</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>C1 / IELTS 7.0</t>
+          <t>B2 → C1</t>
         </is>
       </c>
       <c r="M35" s="4">
-        <f>98</f>
+        <f>456</f>
         <v/>
       </c>
-      <c r="N35" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>⚠️ مهلت ویزایی‌ها ۲۸ فوریه ۲۰۲۷ (بدون ویزا ۳۰ آوریل)؛ کانتون زوریخ: تمکن CHF 21,000 فقط در بانک سوئیسی به نام خودتان</t>
+          <t>ترکیب مهندسی نرم‌افزار + مهندسی داده (Data Engineering — همان توصیهٔ شیت حوزه‌ها)؛ کم‌رقابت‌تر از AI</t>
         </is>
       </c>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>https://www.ifi.uzh.ch/en/studies/master.html</t>
+          <t>https://www.usi.ch/en/education/master/software-and-data-engineering</t>
         </is>
       </c>
     </row>
@@ -5068,77 +5066,77 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>ZHAW School of Engineering</t>
+          <t>Hochschule Luzern (HSLU)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Zürich / Winterthur (زوریخ / وینترتور؛ کمپوس‌های ZHAW)</t>
+          <t>Lucerne / Luzern (لوسرن) — مرکز سوئیس، ۴۵ دقیقه تا زوریخ</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,800–2,400</t>
+          <t>گران — CHF 1,550–1,950</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>MSc in Engineering (MSE) — پروفایل Computer Science / Data Science / Information &amp; Cyber Security</t>
+          <t>MSc Applied Data Science and AI (نام جدید از اوت ۲۰۲۶؛ قبلاً Applied Information and Data Science)</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>چندحوزه‌ای (انتخاب گرایش)</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>۱.۵ سال (90 ECTS؛ پاره‌وقت تا ۳ سال)</t>
+          <t>۲ سال (120 ECTS؛ معمولاً ۴ ترم، قابل تمدید تا ۸)</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>CHF 1,220 در ترم (خارجی) + CHF 60 ≈ CHF 2,560/سال</t>
+          <t>CHF 1,300 در ترم (خارجی) + ≈ CHF 275 هزینهٔ جانبی ≈ CHF 3,150/سال؛ هزینهٔ درخواست CHF 250</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>$3,100</t>
+          <t>$3,800</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی با نمرات A یا B (≈ یک‌سوم بالای کلاس) — گواهی رتبهٔ کلاسی از سمنان بگیرید</t>
+          <t>هر کارشناسی (دانشگاه یا UAS)؛ آزمون انگلیسی + آزمون استعداد HSLU</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>B2–C1</t>
+          <t>C1 (B2 مشروط)</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>851–900</t>
-        </is>
-      </c>
-      <c r="N36" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>کاربردی و پروژه‌محور (کار در مؤسسات ZHAW، اغلب با حقوق دستیاری)؛ مهلت پایان آوریل؛ کانتون زوریخ (تمکن در بانک سوئیسی)</t>
+          <t>«باز برای تغییر رشته‌ای‌ها»، کاربردی و مدیریتی؛ ترکیبی (حضوری/آنلاین)؛ آلمانی لازم نیست؛ شروع سپتامبر/فوریه؛ ⚠️ مهلت ویزایی‌ها ۱ آوریل ۲۰۲۷ (رسمی؛ Swiss/EU تا ۱ ژوئن)</t>
         </is>
       </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
         </is>
       </c>
     </row>
@@ -5153,22 +5151,22 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>EPFL</t>
+          <t>University of Bern</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Lausanne (لوزان) — کنار دریاچهٔ ژنو؛ فرانسه‌زبان؛ EPFL</t>
+          <t>Bern (برن) — پایتخت؛ آلمانی‌زبان</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,700–2,200</t>
+          <t>گران — CHF 1,600–2,000</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>Swiss Joint MSc Computer Science (Bern / Neuchâtel / Fribourg)</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -5178,36 +5176,36 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۱.۵ سال (90 ECTS)</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>CHF 2,240 در ترم برای خارجی‌های غیرمقیم (از پاییز ۲۰۲۵؛ ≈ CHF 4,480/سال)</t>
+          <t>CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها (از پاییز ۲۰۲۶) + 34 + 25 = CHF 2,609 در ترم (≈ CHF 5,200/سال)</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>$5,400</t>
+          <t>$6,300</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با نمرات عالی (بالای کلاس)؛ فقط یک برنامه در سال</t>
+          <t>کارشناسی Computer Science یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی — دروس تکمیلی ممکن است آلمانی/فرانسه باشند)</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>مدرک زبان الزامی نیست (C1 عملاً لازم)</t>
+          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
         </is>
       </c>
       <c r="M37" s="4">
-        <f>22</f>
+        <f>191</f>
         <v/>
       </c>
-      <c r="N37" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -5217,12 +5215,12 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>دور اول ۱۵ دسامبر ۲۰۲۶ (توصیه برای ویزایی‌ها؛ پاسخ اوایل آوریل)، دور دوم ۳۱ مارس ۲۰۲۷؛ ⚠️ احتمال افزایش دوبارهٔ شهریه (EP27)</t>
+          <t>⚠️ شهریهٔ خارجی‌ها از پاییز ۲۰۲۶ سه‌برابر شد (رسمی unibe.ch) → همان مدرک مشترک را از Neuchâtel (CHF 790/ترم) یا Fribourg (CHF 985/ترم) بگیرید؛ مهلت ۳۰ آوریل — ویزایی‌ها مهلت دیرهنگام ندارند</t>
         </is>
       </c>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/education/master/programs/computer-science/</t>
+          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
         </is>
       </c>
     </row>
@@ -5237,76 +5235,77 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>EPFL</t>
+          <t>University of Neuchâtel</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Lausanne (لوزان) — کنار دریاچهٔ ژنو؛ فرانسه‌زبان؛ EPFL</t>
+          <t>Neuchâtel (نوشاتل) — فرانسه‌زبان؛ کنار دریاچه؛ ۳۵ دقیقه تا برن</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,700–2,200</t>
+          <t>متوسط تا گران — CHF 1,350–1,750</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science</t>
+          <t>Swiss Joint MSc Computer Science (ثبت‌نام در Neuchâtel)</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۱.۵ سال (90 ECTS)</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>CHF 2,240 در ترم (≈ CHF 4,480/سال)</t>
+          <t>CHF 790 در ترم (خارجی؛ شامل همهٔ هزینه‌ها) = CHF 1,580/سال</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>$5,400</t>
+          <t>$1,900</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی/مهندسی با نمرات عالی</t>
+          <t>کارشناسی CS یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی)</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>مدرک زبان الزامی نیست</t>
-        </is>
-      </c>
-      <c r="M38" s="4">
-        <f>22</f>
-        <v/>
-      </c>
-      <c r="N38" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>بسیار رقابتی؛ کارآموزی صنعتی جزو برنامه است</t>
+          <t>ارزان‌ترین شهریهٔ سوئیس؛ همان مدرک مشترک Bern/Fribourg (دروس در سه شهر، بلیت قطار جبران می‌شود)؛ مهلت ۳۰ آوریل (خارجی‌ها: تا ۳۱ مارس بفرستید)؛ هزینهٔ پرونده CHF 100 از شهریه کم می‌شود؛ شهر فرانسه‌زبان</t>
         </is>
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/education/master/programs/data-science/</t>
+          <t>https://mcs.unibnf.ch/</t>
         </is>
       </c>
     </row>
@@ -5321,22 +5320,22 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ETH Zürich</t>
+          <t>University of Fribourg</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
+          <t>Fribourg (فریبورگ) — دوزبانه (آلمانی/فرانسه)</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,900–2,500</t>
+          <t>گران — CHF 1,450–1,800</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>Swiss Joint MSc Computer Science (ثبت‌نام در Fribourg)</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -5346,36 +5345,36 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۱.۵ سال (90 ECTS)</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>CHF 2,190 + ≈ CHF 74 = ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
+          <t>CHF 870 + 115 = CHF 985 در ترم (خارجی؛ رسمی) = CHF 1,970/سال</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>$5,500</t>
+          <t>$2,400</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با نمرات ممتاز (عملاً ۱۰٪ بالای کلاس)؛ هزینهٔ درخواست CHF 150؛ تا ۲ برنامه</t>
+          <t>کارشناسی CS یا معادل (بررسی موردی؛ حداکثر ۶۰ ECTS تکمیلی)</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>C1 / IELTS 7.0</t>
+          <t>بدون آزمون (B2 توصیه — FAQ رسمی)</t>
         </is>
       </c>
       <c r="M39" s="4">
-        <f>8</f>
+        <f>670</f>
         <v/>
       </c>
-      <c r="N39" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -5385,12 +5384,12 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>بهترین دانشگاه قارهٔ اروپا؛ اپلای فقط ۱–۳۰ نوامبر ۲۰۲۶، پاسخ تا پایان مارس ۲۰۲۷، شروع ۲۰ سپتامبر ۲۰۲۷؛ با معدل ۱۵.۷۷ احتمال پذیرش کم</t>
+          <t>همان برنامهٔ مشترک Bern/Neuchâtel؛ شهر دوزبانه و ارزان‌تر؛ ⚠️ مهلت ویزایی‌ها ۱–۲۸ فوریه ۲۰۲۷ (رسمی unifr.ch)</t>
         </is>
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/computer-science.html</t>
+          <t>https://www.unifr.ch/inf/en/</t>
         </is>
       </c>
     </row>
@@ -5405,76 +5404,76 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>ETH Zürich + EPFL</t>
+          <t>University of Basel</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
+          <t>Basel (بازل) — Roche، Novartis؛ مرز آلمان/فرانسه</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — CHF 1,900–2,500</t>
+          <t>گران — CHF 1,600–2,100</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>MSc Cyber Security (مشترک ETH–EPFL؛ یک سال در هر کدام)</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>۲ سال (120 ECTS)</t>
+          <t>۱.۵ سال (90 ECTS)</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ ETH: ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
+          <t>CHF 850 در ترم (برای همه؛ بدون اضافهٔ خارجی‌ها — رسمی 2026/27) = CHF 1,700/سال</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>$5,500</t>
+          <t>$2,100</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با نمرات ممتاز؛ پیش‌زمینهٔ ریاضی/سیستم قوی</t>
+          <t>کارشناسی CS یا معادل با نمرات خوب؛ بررسی فردی</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>C1 / IELTS 7.0</t>
+          <t>B2–C1 (چک شود)</t>
         </is>
       </c>
       <c r="M40" s="4">
-        <f>8</f>
+        <f>150</f>
         <v/>
       </c>
-      <c r="N40" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="N40" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>قوی‌ترین ارشد امنیت اروپا؛ همان پنجرهٔ نوامبر ETH؛ Reach</t>
+          <t>رتبهٔ ۱۵۰؛ 90 ECTS انگلیسی؛ هزینهٔ درخواست CHF 100؛ ⚠️ کانتون Basel تمکن CHF 24,000/سال می‌خواهد؛ مهلت ۳۰ آوریل (رسمی)</t>
         </is>
       </c>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/cyber-security.html</t>
+          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
         </is>
       </c>
     </row>
@@ -5484,27 +5483,27 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Universität Stuttgart</t>
+          <t>University of Zurich (UZH)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
+          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,350</t>
+          <t>خیلی گران — CHF 1,900–2,500</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Computer Science (انگلیسی، بدون NC)</t>
+          <t>MSc Informatics (گرایش‌ها: Software Systems، Data Science، People-Oriented Computing…)</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -5514,37 +5513,36 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۱.۵–۲ سال (90/120 ECTS)</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + ≈ €200 سهم ترم = ≈ €3,400/سال</t>
+          <t>CHF 720 + 100 (خارجی) + 59 = CHF 879 در ترم (≈ CHF 1,760/سال)</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>$3,900</t>
+          <t>$2,100</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
+          <t>کارشناسی Informatics/CS با نمرات بسیار خوب؛ فقط یک درخواست در هر ترم؛ هزینهٔ درخواست CHF 150</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1)</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="N41" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>C1 / IELTS 7.0</t>
+        </is>
+      </c>
+      <c r="M41" s="4">
+        <f>98</f>
+        <v/>
+      </c>
+      <c r="N41" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -5554,12 +5552,12 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ بادن-وورتمبرگ برای غیر-EU</t>
+          <t>⚠️ مهلت ویزایی‌ها ۲۸ فوریه ۲۰۲۷ (بدون ویزا ۳۰ آوریل)؛ کانتون زوریخ: تمکن CHF 21,000 فقط در بانک سوئیسی به نام خودتان</t>
         </is>
       </c>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/study/study-programs/</t>
+          <t>https://www.ifi.uzh.ch/en/studies/master.html</t>
         </is>
       </c>
     </row>
@@ -5569,82 +5567,82 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Universität Stuttgart</t>
+          <t>ZHAW School of Engineering</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
+          <t>Zürich / Winterthur (زوریخ / وینترتور؛ کمپوس‌های ZHAW)</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,350</t>
+          <t>خیلی گران — CHF 1,800–2,400</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Information Technology (INFOTECH)</t>
+          <t>MSc in Engineering (MSE) — پروفایل Computer Science / Data Science / Information &amp; Cyber Security</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>چندحوزه‌ای (انتخاب گرایش)</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۱.۵ سال (90 ECTS؛ پاره‌وقت تا ۳ سال)</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + سهم ترم ≈ €3,400/سال</t>
+          <t>CHF 1,220 در ترم (خارجی) + CHF 60 ≈ CHF 2,560/سال</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>$3,900</t>
+          <t>$3,100</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی EE/CS/Computer Engineering؛ گزینش</t>
+          <t>کارشناسی با نمرات A یا B (≈ یک‌سوم بالای کلاس) — گواهی رتبهٔ کلاسی از سمنان بگیرید</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1)</t>
+          <t>B2–C1</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="N42" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>851–900</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>گرایش‌های Embedded/Communication؛ Bosch و Daimler همان شهر</t>
+          <t>کاربردی و پروژه‌محور (کار در مؤسسات ZHAW، اغلب با حقوق دستیاری)؛ مهلت پایان آوریل؛ کانتون زوریخ (تمکن در بانک سوئیسی)</t>
         </is>
       </c>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>https://www.mygermanuniversity.com/master/information-technology-infotech/678</t>
+          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
         </is>
       </c>
     </row>
@@ -5654,82 +5652,81 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>FAU Erlangen-Nürnberg</t>
+          <t>EPFL</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
+          <t>Lausanne (لوزان) — کنار دریاچهٔ ژنو؛ فرانسه‌زبان؛ EPFL</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €950–1,150</t>
+          <t>خیلی گران — CHF 1,700–2,200</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Artificial Intelligence</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>€4,000 در ترم برای غیر-EU از ترم تابستان ۲۰۲۷ (€8,000/سال) + €82 سهم ترم</t>
+          <t>CHF 2,240 در ترم برای خارجی‌های غیرمقیم (از پاییز ۲۰۲۵؛ ≈ CHF 4,480/سال)</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>$9,300</t>
+          <t>$5,400</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بررسی ریزنمرات</t>
+          <t>کارشناسی CS با نمرات عالی (بالای کلاس)؛ فقط یک برنامه در سال</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 6.0)</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="N43" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>مدرک زبان الزامی نیست (C1 عملاً لازم)</t>
+        </is>
+      </c>
+      <c r="M43" s="4">
+        <f>22</f>
+        <v/>
+      </c>
+      <c r="N43" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی اکتبر ۲۰۲۷ شما مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
+          <t>دور اول ۱۵ دسامبر ۲۰۲۶ (توصیه برای ویزایی‌ها؛ پاسخ اوایل آوریل)، دور دوم ۳۱ مارس ۲۰۲۷؛ ⚠️ احتمال افزایش دوبارهٔ شهریه (EP27)</t>
         </is>
       </c>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/artificial-intelligence-m-sc/</t>
+          <t>https://www.epfl.ch/education/master/programs/computer-science/</t>
         </is>
       </c>
     </row>
@@ -5739,82 +5736,81 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>FAU Erlangen-Nürnberg</t>
+          <t>EPFL</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
+          <t>Lausanne (لوزان) — کنار دریاچهٔ ژنو؛ فرانسه‌زبان؛ EPFL</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €950–1,150</t>
+          <t>خیلی گران — CHF 1,700–2,200</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Autonomy Technologies</t>
+          <t>MSc Data Science</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>€2,000 در ترم از تابستان ۲۰۲۷ (€4,000/سال) + €82 سهم ترم</t>
+          <t>CHF 2,240 در ترم (≈ CHF 4,480/سال)</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>$4,700</t>
+          <t>$5,400</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط؛ آلمانی لازم نیست</t>
+          <t>کارشناسی CS/ریاضی/مهندسی با نمرات عالی</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 6.0)</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="N44" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>مدرک زبان الزامی نیست</t>
+        </is>
+      </c>
+      <c r="M44" s="4">
+        <f>22</f>
+        <v/>
+      </c>
+      <c r="N44" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>رباتیک/خودران؛ ⚠️ مشمول شهریهٔ جدید FAU از ۲۰۲۷ (صفحهٔ رسمی شهریه، ۲۰۲۶)</t>
+          <t>بسیار رقابتی؛ کارآموزی صنعتی جزو برنامه است</t>
         </is>
       </c>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+          <t>https://www.epfl.ch/education/master/programs/data-science/</t>
         </is>
       </c>
     </row>
@@ -5824,82 +5820,81 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>TU Darmstadt</t>
+          <t>ETH Zürich</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Darmstadt (دارمشتات) — ۲۵ دقیقه تا فرانکفورت</t>
+          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>خیلی گران — CHF 1,900–2,500</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Distributed Software Systems (انگلیسی)</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €300 سهم ترم (≈ €600/سال)</t>
+          <t>CHF 2,190 + ≈ CHF 74 = ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$5,500</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با پیش‌نیازهای مشخص</t>
+          <t>کارشناسی CS با نمرات ممتاز (عملاً ۱۰٪ بالای کلاس)؛ هزینهٔ درخواست CHF 150؛ تا ۲ برنامه</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>≈ 7.0 (C1) — چک شود</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="N45" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>C1 / IELTS 7.0</t>
+        </is>
+      </c>
+      <c r="M45" s="4">
+        <f>8</f>
+        <v/>
+      </c>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>منطقهٔ Rhein-Main (SAP، Deutsche Bank، Software AG)</t>
+          <t>بهترین دانشگاه قارهٔ اروپا؛ اپلای فقط ۱–۳۰ نوامبر ۲۰۲۶، پاسخ تا پایان مارس ۲۰۲۷، شروع ۲۰ سپتامبر ۲۰۲۷؛ با معدل ۱۵.۷۷ احتمال پذیرش کم</t>
         </is>
       </c>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>https://www.tu-darmstadt.de/studieren/</t>
+          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/computer-science.html</t>
         </is>
       </c>
     </row>
@@ -5909,63 +5904,62 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>آلمان</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>TU Dresden</t>
+          <t>ETH Zürich + EPFL</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Dresden (درسدن) — «سیلیکون ساکسونی»</t>
+          <t>Zürich (زوریخ) — Google، UBS، ETH؛ گران‌ترین شهر دانشگاهی اروپا</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €850–1,050</t>
+          <t>خیلی گران — CHF 1,900–2,500</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Computer Science (انگلیسی)</t>
+          <t>MSc Cyber Security (مشترک ETH–EPFL؛ یک سال در هر کدام)</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۲ سال (120 ECTS)</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €300 سهم ترم</t>
+          <t>شهریهٔ ETH: ≈ CHF 2,264 در ترم (≈ CHF 4,530/سال)</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$5,500</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارزیابی استعداد</t>
+          <t>کارشناسی CS با نمرات ممتاز؛ پیش‌زمینهٔ ریاضی/سیستم قوی</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
+          <t>C1 / IELTS 7.0</t>
+        </is>
+      </c>
+      <c r="M46" s="4">
+        <f>8</f>
+        <v/>
       </c>
       <c r="N46" s="12" t="inlineStr">
         <is>
@@ -5974,17 +5968,17 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>Dresden ارزان‌ترین شهر جدول؛ GlobalFoundries/Infineon/Bosch</t>
+          <t>قوی‌ترین ارشد امنیت اروپا؛ همان پنجرهٔ نوامبر ETH؛ Reach</t>
         </is>
       </c>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de/studium/vor-dem-studium/studienangebot</t>
+          <t>https://ethz.ch/en/studies/master/degree-programmes/engineering-sciences/cyber-security.html</t>
         </is>
       </c>
     </row>
@@ -5999,27 +5993,27 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Saarland University (UdS)</t>
+          <t>Universität Stuttgart</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
+          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>گران — €1,100–1,350</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Cybersecurity</t>
+          <t>M.Sc. Computer Science (انگلیسی، بدون NC)</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -6029,27 +6023,28 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €394 سهم ترم (≈ €790/سال)</t>
+          <t>€1,500 در ترم + ≈ €200 سهم ترم = ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>$900</t>
+          <t>$3,900</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS + اثبات دروس پایه + ۲ توصیه‌نامه؛ بدون NC</t>
+          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>7.0 (C1؛ MOI پذیرفته نمی‌شود)</t>
-        </is>
-      </c>
-      <c r="M47" s="4">
-        <f>588 (CS ≈ 251)</f>
-        <v/>
+          <t>7.0 (C1)</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
       </c>
       <c r="N47" s="10" t="inlineStr">
         <is>
@@ -6058,17 +6053,17 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>CISPA — بهترین مرکز امنیت آلمان؛ IELTS 7 شرط سخت شماست</t>
+          <t>شهریهٔ بادن-وورتمبرگ برای غیر-EU</t>
         </is>
       </c>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/</t>
         </is>
       </c>
     </row>
@@ -6083,27 +6078,27 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Saarland University (UdS)</t>
+          <t>Universität Stuttgart</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
+          <t>Stuttgart (اشتوتگارت) — Bosch، Mercedes، Porsche</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>گران — €1,100–1,350</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Data Science and Artificial Intelligence</t>
+          <t>M.Sc. Information Technology (INFOTECH)</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -6113,17 +6108,17 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €394 سهم ترم</t>
+          <t>€1,500 در ترم + سهم ترم ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>$900</t>
+          <t>$3,900</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
+          <t>کارشناسی EE/CS/Computer Engineering؛ گزینش</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -6131,9 +6126,10 @@
           <t>7.0 (C1)</t>
         </is>
       </c>
-      <c r="M48" s="4">
-        <f>588 (CS ≈ 251)</f>
-        <v/>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
       </c>
       <c r="N48" s="10" t="inlineStr">
         <is>
@@ -6142,17 +6138,17 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>MPI Informatics و DFKI در همان کمپوس</t>
+          <t>گرایش‌های Embedded/Communication؛ Bosch و Daimler همان شهر</t>
         </is>
       </c>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/data-science.html</t>
+          <t>https://www.mygermanuniversity.com/master/information-technology-infotech/678</t>
         </is>
       </c>
     </row>
@@ -6167,27 +6163,27 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>TU Chemnitz</t>
+          <t>FAU Erlangen-Nürnberg</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Chemnitz (کمنیتس) — ساکسونی</t>
+          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €800–1,000</t>
+          <t>متوسط — €950–1,150</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Automotive Software Engineering</t>
+          <t>M.Sc. Artificial Intelligence</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -6197,47 +6193,47 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €320 سهم ترم (≈ €640/سال)</t>
+          <t>€4,000 در ترم برای غیر-EU از ترم تابستان ۲۰۲۷ (€8,000/سال) + €82 سهم ترم</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$9,300</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط؛ بدون محدودیت پذیرش</t>
+          <t>کارشناسی CS/مرتبط؛ بررسی ریزنمرات</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>B2 (IELTS 5.5)</t>
+          <t>B2 (IELTS 6.0)</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>آسان‌ترین ورود؛ شهر ارزان؛ ولی صنعت خودرو ۲۰۲۴–۲۵ ضعیف و آلمانی در کارفرمایان محلی</t>
+          <t>⚠️ FAU طبق BayHIG §13 از تابستان ۲۰۲۷ برای ورودی‌های جدید غیر-EU شهریه می‌گیرد (AI و CS: €4,000/ترم) — ورودی اکتبر ۲۰۲۷ شما مشمول است؛ دیگر «رایگان» نیست. Siemens/adidas/Schaeffler در منطقه</t>
         </is>
       </c>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>https://www.mygermanuniversity.com/master/automotive-software-engineering/91</t>
+          <t>https://www.fau.eu/degree-program/artificial-intelligence-m-sc/</t>
         </is>
       </c>
     </row>
@@ -6252,27 +6248,27 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Universität Passau</t>
+          <t>FAU Erlangen-Nürnberg</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Passau (پاساو) — شهر کوچک، مرز اتریش</t>
+          <t>Erlangen / Nürnberg (ارلانگن / نورنبرگ) — Siemens</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €900–1,100</t>
+          <t>متوسط — €950–1,150</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Artificial Intelligence Engineering</t>
+          <t>M.Sc. Autonomy Technologies</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -6282,47 +6278,47 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €100–200 سهم ترم</t>
+          <t>€2,000 در ترم از تابستان ۲۰۲۷ (€4,000/سال) + €82 سهم ترم</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>$4,700</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.7 (معدل شما ≈ 2.3 ✓)؛ ۳۵ ECTS ریاضی + ۴۰ ECTS CS</t>
+          <t>کارشناسی مرتبط؛ آلمانی لازم نیست</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>B2؛ + آلمانی A1 تا پایان سال اول (کلاس رایگان)</t>
+          <t>B2 (IELTS 6.0)</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N50" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان؛ Passau رسماً اعلام کرده «فعلاً» شهریهٔ غیر-EU نمی‌گیرد (برخلاف FAU/TUM) ولی طبق قانون باواریا می‌تواند — قبل از اپلای چک کنید</t>
+          <t>رباتیک/خودران؛ ⚠️ مشمول شهریهٔ جدید FAU از ۲۰۲۷ (صفحهٔ رسمی شهریه، ۲۰۲۶)</t>
         </is>
       </c>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
       </c>
     </row>
@@ -6337,27 +6333,27 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Otto-von-Guericke-Universität (OVGU)</t>
+          <t>TU Darmstadt</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Magdeburg (ماگدبورگ) — ساکسونی-آنهالت</t>
+          <t>Darmstadt (دارمشتات) — ۲۵ دقیقه تا فرانکفورت</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>ارزان — €850–1,000</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Data and Knowledge Engineering</t>
+          <t>M.Sc. Distributed Software Systems (انگلیسی)</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -6367,7 +6363,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €311 سهم ترم</t>
+          <t>€0 + ≈ €300 سهم ترم (≈ €600/سال)</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6377,33 +6373,37 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.3 (معدل شما ≈ 2.27 — دقیقاً مرزی)؛ کارشناسی CS</t>
+          <t>کارشناسی CS با پیش‌نیازهای مشخص</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>6.0–7.0 (منابع متناقض؛ رسمی را چک کنید)</t>
+          <t>≈ 7.0 (C1) — چک شود</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P51" s="4" t="inlineStr"/>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>منطقهٔ Rhein-Main (SAP، Deutsche Bank، Software AG)</t>
+        </is>
+      </c>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>https://www.dke.ovgu.de/</t>
+          <t>https://www.tu-darmstadt.de/studieren/</t>
         </is>
       </c>
     </row>
@@ -6418,27 +6418,27 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>TH Köln – Cologne Game Lab</t>
+          <t>TU Dresden</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Köln / Cologne (کلن) — چهارمین شهر آلمان</t>
+          <t>Dresden (درسدن) — «سیلیکون ساکسونی»</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>ارزان — €850–1,050</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>M.A. Game Development and Research</t>
+          <t>M.Sc. Computer Science (انگلیسی)</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>€2,500 در ترم (غیر-EU) + €277 سهم ترم ≈ €5,550/سال</t>
+          <t>€0 + ≈ €300 سهم ترم</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>$6,300</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>هر کارشناسی + ≥ ۱۲ ماه سابقهٔ مرتبط + آزمون استعداد (مهلت ۳۱ مارس)</t>
+          <t>کارشناسی CS؛ ارزیابی استعداد</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>— (UAS)</t>
-        </is>
-      </c>
-      <c r="N52" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N52" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>معتبرترین مدرسهٔ بازی آلمان؛ ۷ ماه Unity + ۲ سال IT شما احتمالاً شرط ۱۲ ماه را می‌پوشاند — بپرسید</t>
+          <t>Dresden ارزان‌ترین شهر جدول؛ GlobalFoundries/Infineon/Bosch</t>
         </is>
       </c>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+          <t>https://tu-dresden.de/studium/vor-dem-studium/studienangebot</t>
         </is>
       </c>
     </row>
@@ -6503,12 +6503,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Universität Siegen</t>
+          <t>Saarland University (UdS)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Siegen (زیگن) — شهر کوچک، NRW</t>
+          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Human Computer Interaction</t>
+          <t>M.Sc. Cybersecurity</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -6533,47 +6533,46 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €372 سهم ترم</t>
+          <t>€0 + ≈ €394 سهم ترم (≈ €790/سال)</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>$800</t>
+          <t>$900</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.5؛ کارشناسی CS/IS/Design/Psychology</t>
+          <t>کارشناسی CS + اثبات دروس پایه + ۲ توصیه‌نامه؛ بدون NC</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>7.0 (C1؛ MOI پذیرفته نمی‌شود)</t>
+        </is>
+      </c>
+      <c r="M53" s="4">
+        <f>588 (CS ≈ 251)</f>
+        <v/>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>شروع زمستان و تابستان؛ شهر کوچک</t>
+          <t>CISPA — بهترین مرکز امنیت آلمان؛ IELTS 7 شرط سخت شماست</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
       </c>
     </row>
@@ -6588,27 +6587,27 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Hochschule Bonn-Rhein-Sieg (H-BRS)</t>
+          <t>Saarland University (UdS)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Sankt Augustin (زانکت آگوستین) — حومهٔ Bonn</t>
+          <t>Saarbrücken (زاربروکن) — مرز فرانسه؛ CISPA/DFKI</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €950–1,200</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Autonomous Systems</t>
+          <t>M.Sc. Data Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -6618,28 +6617,27 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>€0 + €349 سهم ترم</t>
+          <t>€0 + ≈ €394 سهم ترم</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>$800</t>
+          <t>$900</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>معدل آلمانی ≤ 2.5؛ ۲۵ جای محدود؛ آزمون استعداد؛ uni-assist</t>
+          <t>کارشناسی CS/مرتبط؛ بدون NC</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>6.5 (B2+)</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
-        <is>
-          <t>— (UAS)</t>
-        </is>
+          <t>7.0 (C1)</t>
+        </is>
+      </c>
+      <c r="M54" s="4">
+        <f>588 (CS ≈ 251)</f>
+        <v/>
       </c>
       <c r="N54" s="10" t="inlineStr">
         <is>
@@ -6648,17 +6646,17 @@
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>رباتیک کاربردی با Fraunhofer؛ نزدیک Bonn/Köln</t>
+          <t>MPI Informatics و DFKI در همان کمپوس</t>
         </is>
       </c>
       <c r="Q54" s="8" t="inlineStr">
         <is>
-          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/data-science.html</t>
         </is>
       </c>
     </row>
@@ -6673,27 +6671,27 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>RWTH Aachen</t>
+          <t>TU Chemnitz</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Aachen (آخن) — مرز هلند/بلژیک</t>
+          <t>Chemnitz (کمنیتس) — ساکسونی</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €950–1,200</t>
+          <t>ارزان — €800–1,000</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Software Systems Engineering</t>
+          <t>M.Sc. Automotive Software Engineering</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -6703,17 +6701,17 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>€0 + ≈ €330 سهم ترم</t>
+          <t>€0 + ≈ €320 سهم ترم (≈ €640/سال)</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>$800</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS، معدل ≥ ۶۵٪ (شما ۷۹٪ ✓)؛ ۲ درس پیشرفتهٔ سیستم؛ مهلت ۱ مارس</t>
+          <t>کارشناسی CS/مرتبط؛ بدون محدودیت پذیرش</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -6723,27 +6721,27 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="N55" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>TU9؛ رقابتی — معدل شما حداقل را رد می‌کند ولی متقاضیان قوی‌ترند</t>
+          <t>آسان‌ترین ورود؛ شهر ارزان؛ ولی صنعت خودرو ۲۰۲۴–۲۵ ضعیف و آلمانی در کارفرمایان محلی</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr">
         <is>
-          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+          <t>https://www.mygermanuniversity.com/master/automotive-software-engineering/91</t>
         </is>
       </c>
     </row>
@@ -6758,22 +6756,22 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Universität Tübingen</t>
+          <t>Universität Passau</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Tübingen (توبینگن) — شهر دانشگاهی کوچک؛ Cyber Valley</t>
+          <t>Passau (پاساو) — شهر کوچک، مرز اتریش</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,050–1,300</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Machine Learning</t>
+          <t>M.Sc. Artificial Intelligence Engineering</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -6788,31 +6786,32 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>€1,500 در ترم + ≈ €200 = ≈ €3,400/سال</t>
+          <t>€0 + ≈ €100–200 سهم ترم</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>$3,900</t>
+          <t>$300</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی؛ آزمون توانایی؛ مهلت ۳۰ آوریل</t>
+          <t>معدل آلمانی ≤ 2.7 (معدل شما ≈ 2.3 ✓)؛ ۳۵ ECTS ریاضی + ۴۰ ECTS CS</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="M56" s="4">
-        <f>230</f>
-        <v/>
-      </c>
-      <c r="N56" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>B2؛ + آلمانی A1 تا پایان سال اول (کلاس رایگان)</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -6822,12 +6821,12 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>Cyber Valley — بهترین ML آلمان؛ پذیرش بسیار سخت</t>
+          <t>کاملاً انگلیسی؛ شهر کوچک و ارزان؛ Passau رسماً اعلام کرده «فعلاً» شهریهٔ غیر-EU نمی‌گیرد (برخلاف FAU/TUM) ولی طبق قانون باواریا می‌تواند — قبل از اپلای چک کنید</t>
         </is>
       </c>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
       </c>
     </row>
@@ -6842,27 +6841,27 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>TU München (TUM)</t>
+          <t>Otto-von-Guericke-Universität (OVGU)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>München – Garching (مونیخ، کمپوس گارشینگ)</t>
+          <t>Magdeburg (ماگدبورگ) — ساکسونی-آنهالت</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,300–1,600</t>
+          <t>ارزان — €850–1,000</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>M.Sc. Informatics</t>
+          <t>M.Sc. Data and Knowledge Engineering</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -6872,47 +6871,43 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>€6,000 در ترم برای غیر-EU (€12,000/سال) + €97</t>
+          <t>€0 + ≈ €311 سهم ترم</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>$13,900</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارزیابی استعداد؛ بسیار رقابتی</t>
+          <t>معدل آلمانی ≤ 2.3 (معدل شما ≈ 2.27 — دقیقاً مرزی)؛ کارشناسی CS</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0–7.0 (منابع متناقض؛ رسمی را چک کنید)</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>≈ 25</t>
-        </is>
-      </c>
-      <c r="N57" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P57" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ TUM از ۲۰۲۴ شهریهٔ غیر-EU می‌گیرد — دیگر «رایگان» نیست؛ Munich گران‌ترین شهر آلمان</t>
-        </is>
-      </c>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="inlineStr"/>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+          <t>https://www.dke.ovgu.de/</t>
         </is>
       </c>
     </row>
@@ -6922,32 +6917,32 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>University of Twente (UT)</t>
+          <t>TH Köln – Cologne Game Lab</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
+          <t>Köln / Cologne (کلن) — چهارمین شهر آلمان</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,000–1,300</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (گرایش‌ها: Cyber Security، Data Science، Software Tech، ...)</t>
+          <t>M.A. Game Development and Research</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -6957,27 +6952,27 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>€21,700</t>
+          <t>€2,500 در ترم (غیر-EU) + €277 سهم ترم ≈ €5,550/سال</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>$24,700</t>
+          <t>$6,300</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>حداقل رسمی برای مدرک ایرانی ۱۵/۲۰</t>
+          <t>هر کارشناسی + ≥ ۱۲ ماه سابقهٔ مرتبط + آزمون استعداد (مهلت ۳۱ مارس)</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>— (UAS)</t>
         </is>
       </c>
       <c r="N58" s="10" t="inlineStr">
@@ -6987,17 +6982,17 @@
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>معتبرترین مدرسهٔ بازی آلمان؛ ۷ ماه Unity + ۲ سال IT شما احتمالاً شرط ۱۲ ماه را می‌پوشاند — بپرسید</t>
         </is>
       </c>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/computer-science/</t>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
       </c>
     </row>
@@ -7007,32 +7002,32 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>University of Twente (UT)</t>
+          <t>Universität Siegen</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
+          <t>Siegen (زیگن) — شهر کوچک، NRW</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,000–1,300</t>
+          <t>متوسط — €900–1,100</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded Systems</t>
+          <t>M.Sc. Human Computer Interaction</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -7042,17 +7037,17 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>€21,700</t>
+          <t>€0 + ≈ €372 سهم ترم</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>$24,700</t>
+          <t>$800</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>CGPA ≥ ۷۰–۷۵٪؛ کارشناسی CS/EE/Computer Eng</t>
+          <t>معدل آلمانی ≤ 2.5؛ کارشناسی CS/IS/Design/Psychology</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -7062,27 +7057,27 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="N59" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ مهلت غیر-EU ۱ مه</t>
+          <t>شروع زمستان و تابستان؛ شهر کوچک</t>
         </is>
       </c>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
       </c>
     </row>
@@ -7092,32 +7087,32 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>University of Twente (UT)</t>
+          <t>Hochschule Bonn-Rhein-Sieg (H-BRS)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
+          <t>Sankt Augustin (زانکت آگوستین) — حومهٔ Bonn</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,000–1,300</t>
+          <t>متوسط — €950–1,200</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>MSc Interaction Technology</t>
+          <t>M.Sc. Autonomous Systems</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -7127,27 +7122,27 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>€21,700</t>
+          <t>€0 + €349 سهم ترم</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>$24,700</t>
+          <t>$800</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط</t>
+          <t>معدل آلمانی ≤ 2.5؛ ۲۵ جای محدود؛ آزمون استعداد؛ uni-assist</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5 (B2+)</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>— (UAS)</t>
         </is>
       </c>
       <c r="N60" s="10" t="inlineStr">
@@ -7157,17 +7152,17 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>HCI فنی (نه طراحی صرف)</t>
+          <t>رباتیک کاربردی با Fraunhofer؛ نزدیک Bonn/Köln</t>
         </is>
       </c>
       <c r="Q60" s="8" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/interaction-technology/</t>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
       </c>
     </row>
@@ -7177,27 +7172,27 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Radboud University</t>
+          <t>RWTH Aachen</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Nijmegen (نایمخن) — شرق هلند</t>
+          <t>Aachen (آخن) — مرز هلند/بلژیک</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,050–1,350</t>
+          <t>متوسط — €950–1,200</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>MSc Computing Science (گرایش‌ها: Cyber Security، Data Science، Software Science)</t>
+          <t>M.Sc. Software Systems Engineering</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -7212,32 +7207,32 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
+          <t>€0 + ≈ €330 سهم ترم</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>$22,500</t>
+          <t>$800</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS با ریاضی/الگوریتم کافی</t>
+          <t>کارشناسی CS، معدل ≥ ۶۵٪ (شما ۷۹٪ ✓)؛ ۲ درس پیشرفتهٔ سیستم؛ مهلت ۱ مارس</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>B2 (IELTS 5.5)</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="N61" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="N61" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -7247,12 +7242,12 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>TU9؛ رقابتی — معدل شما حداقل را رد می‌کند ولی متقاضیان قوی‌ترند</t>
         </is>
       </c>
       <c r="Q61" s="8" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/masters/computing-science</t>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
       </c>
     </row>
@@ -7262,27 +7257,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Radboud University</t>
+          <t>Universität Tübingen</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Nijmegen (نایمخن) — شرق هلند</t>
+          <t>Tübingen (توبینگن) — شهر دانشگاهی کوچک؛ Cyber Valley</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,050–1,350</t>
+          <t>گران — €1,050–1,300</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>M.Sc. Machine Learning</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -7297,32 +7292,31 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
+          <t>€1,500 در ترم + ≈ €200 = ≈ €3,400/سال</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>$22,500</t>
+          <t>$3,900</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI/مرتبط</t>
+          <t>کارشناسی CS/ریاضی؛ آزمون توانایی؛ مهلت ۳۰ آوریل</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="M62" s="4" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="N62" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M62" s="4">
+        <f>230</f>
+        <v/>
+      </c>
+      <c r="N62" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -7332,12 +7326,12 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>AI شناختی (Donders Institute)</t>
+          <t>Cyber Valley — بهترین ML آلمان؛ پذیرش بسیار سخت</t>
         </is>
       </c>
       <c r="Q62" s="8" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/masters/artificial-intelligence</t>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
       </c>
     </row>
@@ -7347,32 +7341,32 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>هلند</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Leiden University</t>
+          <t>TU München (TUM)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Leiden (لایدن) — بین Den Haag و Amsterdam</t>
+          <t>München – Garching (مونیخ، کمپوس گارشینگ)</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>خیلی گران — €1,300–1,600</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (گرایش‌ها: Artificial Intelligence، Data Science، ...)</t>
+          <t>M.Sc. Informatics</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>چندحوزه‌ای (انتخاب گرایش)</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -7382,17 +7376,17 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>€22,500</t>
+          <t>€6,000 در ترم برای غیر-EU (€12,000/سال) + €97</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>$25,600</t>
+          <t>$13,900</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS؛ ارزیابی استعداد؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -7402,27 +7396,27 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="N63" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>≈ 25</t>
+        </is>
+      </c>
+      <c r="N63" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ نزدیک Den Haag/Amsterdam</t>
+          <t>⚠️ TUM از ۲۰۲۴ شهریهٔ غیر-EU می‌گیرد — دیگر «رایگان» نیست؛ Munich گران‌ترین شهر آلمان</t>
         </is>
       </c>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
       </c>
     </row>
@@ -7437,27 +7431,27 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>University of Groningen (RUG)</t>
+          <t>University of Twente (UT)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Groningen (خرونینگن) — شمال هلند</t>
+          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,050–1,350</t>
+          <t>متوسط — €1,000–1,300</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computer Science (گرایش‌ها: Cyber Security، Data Science، Software Tech، ...)</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -7467,17 +7461,17 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>€24,900</t>
+          <t>€21,700</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>$28,400</t>
+          <t>$24,700</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی AI/CS با ریاضی</t>
+          <t>حداقل رسمی برای مدرک ایرانی ۱۵/۲۰</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -7487,27 +7481,27 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="N64" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>شهریهٔ رسمی 2026/27؛ بورس ASML €5k</t>
+          <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/computer-science/</t>
         </is>
       </c>
     </row>
@@ -7522,27 +7516,27 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>University of Groningen (RUG)</t>
+          <t>University of Twente (UT)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Groningen (خرونینگن) — شمال هلند</t>
+          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,050–1,350</t>
+          <t>متوسط — €1,000–1,300</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>MSc Computing Science</t>
+          <t>MSc Embedded Systems</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -7552,17 +7546,17 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>≈ €21,400 (2025) → ≈ €22,500</t>
+          <t>€21,700</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>$25,600</t>
+          <t>$24,700</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>CGPA ≥ ۷۰–۷۵٪؛ کارشناسی CS/EE/Computer Eng</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -7572,7 +7566,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>223</t>
         </is>
       </c>
       <c r="N65" s="10" t="inlineStr">
@@ -7582,13 +7576,17 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P65" s="4" t="inlineStr"/>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27؛ مهلت غیر-EU ۱ مه</t>
+        </is>
+      </c>
       <c r="Q65" s="8" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/computing-science/?lang=en</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
       </c>
     </row>
@@ -7603,27 +7601,27 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Utrecht University</t>
+          <t>University of Twente (UT)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
+          <t>Enschede (انسخده) — شرق هلند، مرز آلمان</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>متوسط — €1,000–1,300</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>MSc Game and Media Technology</t>
+          <t>MSc Interaction Technology</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -7633,17 +7631,17 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>€25,306</t>
+          <t>€21,700</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>$28,800</t>
+          <t>$24,700</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS؛ ارشد پژوهشی گزینشی</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -7653,27 +7651,27 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="N66" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>تنها ارشد پژوهشی بازی هلند؛ Utrecht قطب استودیوهای بازی</t>
+          <t>HCI فنی (نه طراحی صرف)</t>
         </is>
       </c>
       <c r="Q66" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/interaction-technology/</t>
         </is>
       </c>
     </row>
@@ -7688,27 +7686,27 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Utrecht University</t>
+          <t>Radboud University</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
+          <t>Nijmegen (نایمخن) — شرق هلند</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,200–1,500</t>
+          <t>متوسط — €1,050–1,350</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computing Science (گرایش‌ها: Cyber Security، Data Science، Software Science)</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -7718,17 +7716,17 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>€25,306</t>
+          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>$28,800</t>
+          <t>$22,500</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI؛ گزینشی</t>
+          <t>کارشناسی CS با ریاضی/الگوریتم کافی</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -7738,27 +7736,27 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="N67" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>همان باند شهریهٔ Utrecht 2026/27</t>
+          <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/artificial-intelligence</t>
+          <t>https://www.ru.nl/en/education/masters/computing-science</t>
         </is>
       </c>
     </row>
@@ -7773,47 +7771,47 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA)</t>
+          <t>Radboud University</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Amsterdam (آمستردام)</t>
+          <t>Nijmegen (نایمخن) — شرق هلند</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,300–1,700</t>
+          <t>متوسط — €1,050–1,350</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering (۱ ساله!)</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>≈ €23,540</t>
+          <t>€19,714 (2026/27 — نرخ رسمی دانشکدهٔ علوم)</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>$26,800</t>
+          <t>$22,500</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی CS/AI/مرتبط</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -7823,27 +7821,27 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="N68" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>تنها ارشد ۱ سالهٔ معتبر هلند → کل هزینه نصف؛ اما اجارهٔ Amsterdam €900–1,300</t>
+          <t>AI شناختی (Donders Institute)</t>
         </is>
       </c>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>https://www.uva.nl/en/programmes/masters/software-engineering/software-engineering.html</t>
+          <t>https://www.ru.nl/en/education/masters/artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -7858,27 +7856,27 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA)</t>
+          <t>Leiden University</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Amsterdam (آمستردام)</t>
+          <t>Leiden (لایدن) — بین Den Haag و Amsterdam</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — €1,300–1,700</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computer Science (گرایش‌ها: Artificial Intelligence، Data Science، ...)</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>چندحوزه‌ای (انتخاب گرایش)</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -7888,17 +7886,17 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>≈ €26,000</t>
+          <t>€22,500</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>$29,600</t>
+          <t>$25,600</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی AI/CS با ریاضی قوی؛ بسیار رقابتی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -7908,23 +7906,27 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="N69" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="N69" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
-        </is>
-      </c>
-      <c r="P69" s="4" t="inlineStr"/>
+          <t>4/5 — گرایش را بعد از ورود انتخاب می‌کنید؛ امتیاز بازار = گرایشی که برمی‌دارید</t>
+        </is>
+      </c>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>شهریهٔ رسمی 2026/27؛ نزدیک Den Haag/Amsterdam</t>
+        </is>
+      </c>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>https://www.uva.nl/en/programmes/masters/artificial-intelligence/artificial-intelligence.html</t>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
       </c>
     </row>
@@ -7939,27 +7941,27 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>TU Eindhoven (TU/e)</t>
+          <t>University of Groningen (RUG)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
+          <t>Groningen (خرونینگن) — شمال هلند</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,400</t>
+          <t>متوسط — €1,050–1,350</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science and Artificial Intelligence</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -7969,17 +7971,17 @@
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
+          <t>€24,900</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>$25,500</t>
+          <t>$28,400</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی؛ گزینش بر اساس معدل</t>
+          <t>کارشناسی AI/CS با ریاضی</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -7989,27 +7991,27 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="N70" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>Brainport (ASML، Philips، NXP)</t>
+          <t>شهریهٔ رسمی 2026/27؛ بورس ASML €5k</t>
         </is>
       </c>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/graduate-school/master-data-science-and-artificial-intelligence</t>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
       </c>
     </row>
@@ -8024,27 +8026,27 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>TU Eindhoven (TU/e)</t>
+          <t>University of Groningen (RUG)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
+          <t>Groningen (خرونینگن) — شمال هلند</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>گران — €1,100–1,400</t>
+          <t>متوسط — €1,050–1,350</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded Systems</t>
+          <t>MSc Computing Science</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -8054,17 +8056,17 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
+          <t>≈ €21,400 (2025) → ≈ €22,500</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>$25,500</t>
+          <t>$25,600</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE؛ گزینش</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -8074,27 +8076,23 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="N71" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
-        </is>
-      </c>
-      <c r="P71" s="4" t="inlineStr">
-        <is>
-          <t>ASML/NXP بزرگ‌ترین کارفرمایان Embedded اروپا</t>
-        </is>
-      </c>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="inlineStr"/>
       <c r="Q71" s="8" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/graduate-school/master-embedded-systems</t>
+          <t>https://www.rug.nl/masters/computing-science/?lang=en</t>
         </is>
       </c>
     </row>
@@ -8109,12 +8107,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>TU Delft</t>
+          <t>Utrecht University</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Delft (دلفت) — کنار Den Haag/Rotterdam</t>
+          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -8124,12 +8122,12 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science / MSc Computer &amp; Embedded Systems Engineering</t>
+          <t>MSc Game and Media Technology</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -8139,27 +8137,27 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>€22,290 (2025/26) → ≈ €23,000</t>
+          <t>€25,306</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>$26,200</t>
+          <t>$28,800</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>معدل ≥ ۷۵٪ / ۲۰٪ برتر</t>
+          <t>کارشناسی CS؛ ارشد پژوهشی گزینشی</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>113</t>
         </is>
       </c>
       <c r="N72" s="12" t="inlineStr">
@@ -8169,17 +8167,17 @@
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>معتبرترین، ولی برای معدل ۱۵.۷۷ دور از دسترس</t>
+          <t>تنها ارشد پژوهشی بازی هلند؛ Utrecht قطب استودیوهای بازی</t>
         </is>
       </c>
       <c r="Q72" s="8" t="inlineStr">
         <is>
-          <t>https://www.tudelft.nl/onderwijs/opleidingen/masters/cs/msc-computer-science</t>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
       </c>
     </row>
@@ -8194,77 +8192,77 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Breda University of Applied Sciences (BUas)</t>
+          <t>Utrecht University</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Breda (بردا) — جنوب هلند</t>
+          <t>Utrecht (اوترخت) — مرکز هلند؛ قطب استودیوهای بازی</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>متوسط — €1,000–1,300</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Master Game Technology (۱ ساله)</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>۱ سال</t>
+          <t>۲ سال</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>≈ €15,200</t>
+          <t>€25,306</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>$17,300</t>
+          <t>$28,800</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی IT/برنامه‌نویسی/بازی + پیشنهاد پروژه</t>
+          <t>کارشناسی CS/AI؛ گزینشی</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>— (UAS)</t>
-        </is>
-      </c>
-      <c r="N73" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="N73" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>برنامهٔ بازی BUas در اروپا شناخته‌شده است؛ مدرک UAS (نه پژوهشی)</t>
+          <t>همان باند شهریهٔ Utrecht 2026/27</t>
         </is>
       </c>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/breda-university-applied-sciences/postgrad/master-game-technology</t>
+          <t>https://www.uu.nl/en/masters/artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -8274,27 +8272,27 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Linköping University (LiU)</t>
+          <t>University of Amsterdam (UvA)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
+          <t>Amsterdam (آمستردام)</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,500–12,500</t>
+          <t>خیلی گران — €1,300–1,700</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Software Engineering (۱ ساله!)</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -8304,22 +8302,22 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>SEK 166,000</t>
+          <t>≈ €23,540</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>$16,800</t>
+          <t>$26,800</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>گزینش بر اساس گروه معدل</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -8329,12 +8327,12 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="N74" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N74" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
@@ -8344,12 +8342,12 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی</t>
+          <t>تنها ارشد ۱ سالهٔ معتبر هلند → کل هزینه نصف؛ اما اجارهٔ Amsterdam €900–1,300</t>
         </is>
       </c>
       <c r="Q74" s="8" t="inlineStr">
         <is>
-          <t>https://liu.se/en/education/program/6mics</t>
+          <t>https://www.uva.nl/en/programmes/masters/software-engineering/software-engineering.html</t>
         </is>
       </c>
     </row>
@@ -8359,27 +8357,27 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Linköping University (LiU)</t>
+          <t>University of Amsterdam (UvA)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
+          <t>Amsterdam (آمستردام)</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,500–12,500</t>
+          <t>خیلی گران — €1,300–1,700</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>MSc Statistics and Machine Learning</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -8394,17 +8392,17 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 166,000 (همان باند)</t>
+          <t>≈ €26,000</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>$16,800</t>
+          <t>$29,600</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی با ≥ ۳۰ واحد ریاضی/آمار + برنامه‌نویسی</t>
+          <t>کارشناسی AI/CS با ریاضی قوی؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -8414,12 +8412,12 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="N75" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N75" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -8430,7 +8428,7 @@
       <c r="P75" s="4" t="inlineStr"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>https://liu.se/en/education/program/f7msl</t>
+          <t>https://www.uva.nl/en/programmes/masters/artificial-intelligence/artificial-intelligence.html</t>
         </is>
       </c>
     </row>
@@ -8440,32 +8438,32 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Halmstad University</t>
+          <t>TU Eindhoven (TU/e)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Halmstad (هالمستاد) — غرب سوئد</t>
+          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,000–12,000</t>
+          <t>گران — €1,100–1,400</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>MSc Embedded and Intelligent Systems (120 cr)</t>
+          <t>MSc Data Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -8475,17 +8473,17 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 151,000</t>
+          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>$15,300</t>
+          <t>$25,500</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE</t>
+          <t>کارشناسی CS/ریاضی؛ گزینش بر اساس معدل</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -8495,27 +8493,27 @@
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="N76" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>Volvo/HMS در منطقه؛ بدون رتبهٔ QS</t>
+          <t>Brainport (ASML، Philips، NXP)</t>
         </is>
       </c>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>https://www.hh.se/english/education/programmes.html</t>
+          <t>https://www.tue.nl/en/education/graduate-school/master-data-science-and-artificial-intelligence</t>
         </is>
       </c>
     </row>
@@ -8525,32 +8523,32 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Blekinge Institute of Technology (BTH)</t>
+          <t>TU Eindhoven (TU/e)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Karlskrona (کارلسکرونا) — Ericsson، Telenor</t>
+          <t>Eindhoven (آیندهوون) — Brainport: ASML، Philips، NXP</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>ارزان — SEK 9,500–11,500</t>
+          <t>گران — €1,100–1,400</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering (120 cr)</t>
+          <t>MSc Embedded Systems</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -8560,17 +8558,17 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>SEK 140,000</t>
+          <t>€22,400 (2027/28 رسمی؛ 2026/27: €21,700)</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>$14,100</t>
+          <t>$25,500</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>≥ ۹۰ واحد CS/SE</t>
+          <t>کارشناسی CS/EE؛ گزینش</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -8580,27 +8578,27 @@
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="9" t="inlineStr">
-        <is>
-          <t>Safe/Target</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="N77" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Ericsson و Telenor در Karlskrona؛ ⚠️ نسخهٔ ۶۰ واحدی از راه دور است</t>
+          <t>ASML/NXP بزرگ‌ترین کارفرمایان Embedded اروپا</t>
         </is>
       </c>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>https://www.bth.se/eng/programmes/</t>
+          <t>https://www.tue.nl/en/education/graduate-school/master-embedded-systems</t>
         </is>
       </c>
     </row>
@@ -8610,32 +8608,32 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>KTH Royal Institute of Technology</t>
+          <t>TU Delft</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Stockholm (استکهلم)</t>
+          <t>Delft (دلفت) — کنار Den Haag/Rotterdam</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>گران — SEK 12,500–15,000</t>
+          <t>گران — €1,200–1,500</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>MSc Machine Learning</t>
+          <t>MSc Computer Science / MSc Computer &amp; Embedded Systems Engineering</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -8645,27 +8643,27 @@
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 180,000–190,000 (کل دوره ≈ 360k–380k)</t>
+          <t>€22,290 (2025/26) → ≈ €23,000</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>$18,200–19,200</t>
+          <t>$26,200</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی قوی؛ بسیار رقابتی</t>
+          <t>معدل ≥ ۷۵٪ / ۲۰٪ برتر</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N78" s="12" t="inlineStr">
@@ -8675,17 +8673,17 @@
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>Stockholm گران (اتاق SEK 7–10k)؛ رقم دقیق روی kth.se فقط در سامانهٔ اپلای نمایش داده می‌شود</t>
+          <t>معتبرترین، ولی برای معدل ۱۵.۷۷ دور از دسترس</t>
         </is>
       </c>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+          <t>https://www.tudelft.nl/onderwijs/opleidingen/masters/cs/msc-computer-science</t>
         </is>
       </c>
     </row>
@@ -8695,78 +8693,82 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>سوئد</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>KTH Royal Institute of Technology</t>
+          <t>Breda University of Applied Sciences (BUas)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Stockholm (استکهلم)</t>
+          <t>Breda (بردا) — جنوب هلند</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>گران — SEK 12,500–15,000</t>
+          <t>متوسط — €1,000–1,300</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>MSc Cybersecurity</t>
+          <t>Master Game Technology (۱ ساله)</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>۲ سال</t>
+          <t>۱ سال</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 180,000–190,000</t>
+          <t>≈ €15,200</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>$18,200–19,200</t>
+          <t>$17,300</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>کارشناسی IT/برنامه‌نویسی/بازی + پیشنهاد پروژه</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="N79" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+          <t>— (UAS)</t>
+        </is>
+      </c>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
-        </is>
-      </c>
-      <c r="P79" s="4" t="inlineStr"/>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>برنامهٔ بازی BUas در اروپا شناخته‌شده است؛ مدرک UAS (نه پژوهشی)</t>
+        </is>
+      </c>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/cybersecurity</t>
+          <t>https://www.topuniversities.com/universities/breda-university-applied-sciences/postgrad/master-game-technology</t>
         </is>
       </c>
     </row>
@@ -8781,27 +8783,27 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>KTH Royal Institute of Technology</t>
+          <t>Linköping University (LiU)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Stockholm – Kista (استکهلم، شیستا؛ قطب ICT)</t>
+          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>گران — SEK 12,500–15,000</t>
+          <t>متوسط — SEK 10,500–12,500</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering of Distributed Systems</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -8811,17 +8813,17 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>SEK 180,000–190,000</t>
+          <t>SEK 166,000</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>$18,200–19,200</t>
+          <t>$16,800</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS</t>
+          <t>گزینش بر اساس گروه معدل</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -8831,27 +8833,27 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="N80" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>Kista = قطب ICT سوئد (Ericsson)</t>
+          <t>گزینهٔ Target جدول اصلی</t>
         </is>
       </c>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/software-engineering-of-distributed-systems</t>
+          <t>https://liu.se/en/education/program/6mics</t>
         </is>
       </c>
     </row>
@@ -8866,27 +8868,27 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Chalmers University of Technology</t>
+          <t>Linköping University (LiU)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+          <t>Linköping (لینشوپینگ) — Saab، Ericsson</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,500–13,500</t>
+          <t>متوسط — SEK 10,500–12,500</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science and AI</t>
+          <t>MSc Statistics and Machine Learning</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -8896,17 +8898,17 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 175,000 (2026/27؛ 2025/26: 160,000)</t>
+          <t>≈ SEK 166,000 (همان باند)</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>$17,700</t>
+          <t>$16,800</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی</t>
+          <t>کارشناسی با ≥ ۳۰ واحد ریاضی/آمار + برنامه‌نویسی</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -8916,27 +8918,23 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="N81" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P81" s="4" t="inlineStr">
-        <is>
-          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه؛ ⚠️ طبق صفحهٔ شهریهٔ Chalmers دانشگاه‌های سوئد فعلاً نمی‌توانند از ایران پول دریافت کنند (تحریم بانکی) — پرداخت از کشور ثالث</t>
-        </is>
-      </c>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="inlineStr"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/data-science-and-ai-msc/</t>
+          <t>https://liu.se/en/education/program/f7msl</t>
         </is>
       </c>
     </row>
@@ -8951,27 +8949,27 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Chalmers University of Technology</t>
+          <t>Halmstad University</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+          <t>Halmstad (هالمستاد) — غرب سوئد</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,500–13,500</t>
+          <t>متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering and Technology</t>
+          <t>MSc Embedded and Intelligent Systems (120 cr)</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -8981,17 +8979,17 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 175,000 (2026/27)</t>
+          <t>≈ SEK 151,000</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>$17,700</t>
+          <t>$15,300</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE</t>
+          <t>کارشناسی CS/EE</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -9001,23 +8999,27 @@
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="N82" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P82" s="4" t="inlineStr"/>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="P82" s="4" t="inlineStr">
+        <is>
+          <t>Volvo/HMS در منطقه؛ بدون رتبهٔ QS</t>
+        </is>
+      </c>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/software-engineering-and-technology-msc/</t>
+          <t>https://www.hh.se/english/education/programmes.html</t>
         </is>
       </c>
     </row>
@@ -9032,27 +9034,27 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Chalmers University of Technology</t>
+          <t>Blekinge Institute of Technology (BTH)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+          <t>Karlskrona (کارلسکرونا) — Ericsson، Telenor</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,500–13,500</t>
+          <t>ارزان — SEK 9,500–11,500</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>MSc Interaction Design and Technologies</t>
+          <t>MSc Software Engineering (120 cr)</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -9062,17 +9064,17 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 175,000 (2026/27)</t>
+          <t>SEK 140,000</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>$17,700</t>
+          <t>$14,100</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/Design</t>
+          <t>≥ ۹۰ واحد CS/SE</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -9082,23 +9084,27 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="N83" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="9" t="inlineStr">
+        <is>
+          <t>Safe/Target</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
-        </is>
-      </c>
-      <c r="P83" s="4" t="inlineStr"/>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P83" s="4" t="inlineStr">
+        <is>
+          <t>Ericsson و Telenor در Karlskrona؛ ⚠️ نسخهٔ ۶۰ واحدی از راه دور است</t>
+        </is>
+      </c>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/find-masters-programme/interaction-design-and-technologies-msc/</t>
+          <t>https://www.bth.se/eng/programmes/</t>
         </is>
       </c>
     </row>
@@ -9113,27 +9119,27 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>University of Gothenburg (مشترک با Chalmers)</t>
+          <t>KTH Royal Institute of Technology</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
+          <t>Stockholm (استکهلم)</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,500–13,500</t>
+          <t>گران — SEK 12,500–15,000</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>MSc Game Design &amp; Technology</t>
+          <t>MSc Machine Learning</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -9143,17 +9149,17 @@
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>SEK 147,000 (ورودی ۲۰۲۷: کل دوره SEK 294,000 رسمی)</t>
+          <t>≈ SEK 180,000–190,000 (کل دوره ≈ 360k–380k)</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>$14,800</t>
+          <t>$18,200–19,200</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/Design/Media</t>
+          <t>کارشناسی CS/ریاضی قوی؛ بسیار رقابتی</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -9163,27 +9169,27 @@
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="N84" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N84" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>Gothenburg: استودیوهای EA DICE/Ghost؛ بازار بازی ضعیف</t>
+          <t>Stockholm گران (اتاق SEK 7–10k)؛ رقم دقیق روی kth.se فقط در سامانهٔ اپلای نمایش داده می‌شود</t>
         </is>
       </c>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
       </c>
     </row>
@@ -9198,27 +9204,27 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Uppsala University</t>
+          <t>KTH Royal Institute of Technology</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Uppsala (اوپسالا) — ۴۰ دقیقه تا استکهلم</t>
+          <t>Stockholm (استکهلم)</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>متوسط تا گران — SEK 11,000–13,000</t>
+          <t>گران — SEK 12,500–15,000</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Cybersecurity</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -9228,12 +9234,12 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 145,000–150,000</t>
+          <t>≈ SEK 180,000–190,000</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>$14,600–15,200</t>
+          <t>$18,200–19,200</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -9248,27 +9254,23 @@
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="N85" s="11" t="inlineStr">
-        <is>
-          <t>Target/Reach</t>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N85" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
-        </is>
-      </c>
-      <c r="P85" s="4" t="inlineStr">
-        <is>
-          <t>رتبهٔ بالا با شهریهٔ پایین‌تر از KTH</t>
-        </is>
-      </c>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="P85" s="4" t="inlineStr"/>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>https://www.uu.se/en/study/programme/masters-programme-in-computer-science</t>
+          <t>https://www.kth.se/en/studies/master/cybersecurity</t>
         </is>
       </c>
     </row>
@@ -9283,27 +9285,27 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Umeå University</t>
+          <t>KTH Royal Institute of Technology</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Umeå (اومئو) — شمال سوئد</t>
+          <t>Stockholm – Kista (استکهلم، شیستا؛ قطب ICT)</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>ارزان تا متوسط — SEK 10,000–12,000</t>
+          <t>گران — SEK 12,500–15,000</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Software Engineering of Distributed Systems</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>ابری / سیستم‌های توزیع‌شده / DevOps</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -9313,17 +9315,17 @@
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>SEK 152,300</t>
+          <t>SEK 180,000–190,000</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>$15,400</t>
+          <t>$18,200–19,200</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/ریاضی</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -9333,27 +9335,27 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="N86" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N86" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — تقاضای پایدار و کمتر مدرک‌محور؛ گواهی AWS/Azure کنار مدرک وزن زیادی دارد</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>شمال سوئد، شهر دانشجویی ارزان؛ کل دوره SEK 304,600</t>
+          <t>Kista = قطب ICT سوئد (Ericsson)</t>
         </is>
       </c>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+          <t>https://www.kth.se/en/studies/master/software-engineering-of-distributed-systems</t>
         </is>
       </c>
     </row>
@@ -9368,22 +9370,22 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>University of Skövde</t>
+          <t>Chalmers University of Technology</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Skövde (شوده) — Sweden Game Arena</t>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>ارزان — SEK 9,500–11,500</t>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science (120 cr)</t>
+          <t>MSc Data Science and AI</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -9398,17 +9400,17 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>SEK 135,000</t>
+          <t>≈ SEK 175,000 (2026/27؛ 2025/26: 160,000)</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>$13,600</t>
+          <t>$17,700</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/مرتبط</t>
+          <t>کارشناسی CS/ریاضی</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -9418,12 +9420,12 @@
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N87" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="N87" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -9433,12 +9435,12 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>ارزان؛ Skövde قطب بازی سوئد (Sweden Game Arena)</t>
+          <t>Volvo، Ericsson، Zenseact؛ مهلت ۱۵ ژانویه؛ ⚠️ طبق صفحهٔ شهریهٔ Chalmers دانشگاه‌های سوئد فعلاً نمی‌توانند از ایران پول دریافت کنند (تحریم بانکی) — پرداخت از کشور ثالث</t>
         </is>
       </c>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>https://www.his.se/en/education/</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/data-science-and-ai-msc/</t>
         </is>
       </c>
     </row>
@@ -9453,27 +9455,27 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Mälardalen University (MDU)</t>
+          <t>Chalmers University of Technology</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,000–12,000</t>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>MSc Intelligent Embedded Systems</t>
+          <t>MSc Software Engineering and Technology</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -9483,17 +9485,17 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 135,000</t>
+          <t>≈ SEK 175,000 (2026/27)</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>$13,600</t>
+          <t>$17,700</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE</t>
+          <t>کارشناسی CS/SE</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -9503,27 +9505,23 @@
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="N88" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
-        </is>
-      </c>
-      <c r="P88" s="4" t="inlineStr">
-        <is>
-          <t>ABB و Westinghouse در Västerås؛ رقم 2024/25</t>
-        </is>
-      </c>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="inlineStr"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>https://www.mdu.se/en/malardalen-university/education</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/software-engineering-and-technology-msc/</t>
         </is>
       </c>
     </row>
@@ -9538,27 +9536,27 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Mälardalen University (MDU)</t>
+          <t>Chalmers University of Technology</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>متوسط — SEK 10,000–12,000</t>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>MSc Software Engineering</t>
+          <t>MSc Interaction Design and Technologies</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -9568,17 +9566,17 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>≈ SEK 135,000</t>
+          <t>≈ SEK 175,000 (2026/27)</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>$13,600</t>
+          <t>$17,700</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE</t>
+          <t>کارشناسی CS/Design</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -9588,23 +9586,23 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>Safe</t>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr"/>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>https://www.mdu.se/en/malardalen-university/education</t>
+          <t>https://www.chalmers.se/en/education/find-masters-programme/interaction-design-and-technologies-msc/</t>
         </is>
       </c>
     </row>
@@ -9614,32 +9612,32 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (AAU)</t>
+          <t>University of Gothenburg (مشترک با Chalmers)</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
+          <t>Gothenburg / Göteborg (گوتنبرگ) — Volvo، Ericsson</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–9,500</t>
+          <t>متوسط تا گران — SEK 11,500–13,500</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science (IT)</t>
+          <t>MSc Game Design &amp; Technology</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>توسعه بازی</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -9649,27 +9647,28 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>≈ €14,910 (2025/26: €7,455 در ترم؛ نرخ ۲۰۲۶ روی سایت AAU منتشر نشده — mastersportal: €15,340)</t>
+          <t>SEK 147,000 (ورودی ۲۰۲۷: کل دوره SEK 294,000 رسمی)</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>$17,000–17,500</t>
+          <t>$14,800</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>رسمی: حداقل ۱۵۰ ECTS دروس مرتبط با CS (برنامه‌نویسی ۱۵، مهندسی نرم‌افزار ۵، الگوریتم ۵، پایگاه داده ۵، ریاضیات گسسته ۵)؛ از ورودی ۲۰۲۷ سابقهٔ کار و انگیزه‌نامه هم در رتبه‌بندی حساب می‌شود</t>
+          <t>کارشناسی CS/Design/Media</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>6.5 (هر بخش ≥ 6.0)</t>
-        </is>
-      </c>
-      <c r="M90" s="4">
-        <f>329</f>
-        <v/>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
       </c>
       <c r="N90" s="10" t="inlineStr">
         <is>
@@ -9678,17 +9677,17 @@
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)؛ ظرفیت محدود</t>
+          <t>Gothenburg: استودیوهای EA DICE/Ghost؛ بازار بازی ضعیف</t>
         </is>
       </c>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
       </c>
     </row>
@@ -9698,27 +9697,27 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (AAU)</t>
+          <t>Uppsala University</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
+          <t>Uppsala (اوپسالا) — ۴۰ دقیقه تا استکهلم</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–9,500</t>
+          <t>متوسط تا گران — SEK 11,000–13,000</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>MSc Software</t>
+          <t>MSc Computer Science</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -9733,17 +9732,17 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>≈ €14,910–15,340</t>
+          <t>≈ SEK 145,000–150,000</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>$17,000–17,500</t>
+          <t>$14,600–15,200</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی SE/CS</t>
+          <t>کارشناسی CS</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -9751,13 +9750,14 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M91" s="4">
-        <f>329</f>
-        <v/>
-      </c>
-      <c r="N91" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N91" s="11" t="inlineStr">
+        <is>
+          <t>Target/Reach</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -9765,10 +9765,14 @@
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P91" s="4" t="inlineStr"/>
+      <c r="P91" s="4" t="inlineStr">
+        <is>
+          <t>رتبهٔ بالا با شهریهٔ پایین‌تر از KTH</t>
+        </is>
+      </c>
       <c r="Q91" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/software</t>
+          <t>https://www.uu.se/en/study/programme/masters-programme-in-computer-science</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9782,32 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (AAU)</t>
+          <t>Umeå University</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen – Sydhavn (کپنهاگ؛ کمپوس AAU)</t>
+          <t>Umeå (اومئو) — شمال سوئد</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 10,000–12,500</t>
+          <t>ارزان تا متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Cyber Security</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>امنیت سایبری</t>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -9813,17 +9817,17 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>≈ €14,910–15,340</t>
+          <t>SEK 152,300</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>$17,000–17,500</t>
+          <t>$15,400</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/EE مرتبط؛ مهلت ۱ مارس</t>
+          <t>کارشناسی CS/ریاضی</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -9831,9 +9835,10 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M92" s="4">
-        <f>329</f>
-        <v/>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
       </c>
       <c r="N92" s="10" t="inlineStr">
         <is>
@@ -9842,17 +9847,17 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>کمپوس کپنهاگ: اجاره بالاتر ولی بازار کار بزرگ</t>
+          <t>شمال سوئد، شهر دانشجویی ارزان؛ کل دوره SEK 304,600</t>
         </is>
       </c>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/cyber-security/</t>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
       </c>
     </row>
@@ -9862,32 +9867,32 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Aalborg University (AAU)</t>
+          <t>University of Skövde</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Aalborg یا Copenhagen (هر دو کمپوس)</t>
+          <t>Skövde (شوده) — Sweden Game Arena</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>متوسط (Aalborg) تا خیلی گران (Copenhagen)</t>
+          <t>ارزان — SEK 9,500–11,500</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>MSc Medialogy</t>
+          <t>MSc Data Science (120 cr)</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>HCI / طراحی تعامل / UX</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -9897,17 +9902,17 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>≈ €14,910–15,340</t>
+          <t>SEK 135,000</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>$17,000–17,500</t>
+          <t>$13,600</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط (Medialogy، CS، Media Tech)</t>
+          <t>کارشناسی CS/مرتبط</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -9915,28 +9920,29 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M93" s="4">
-        <f>329</f>
-        <v/>
-      </c>
-      <c r="N93" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>تعامل، AR/VR، بازی؛ بین HCI و Game</t>
+          <t>ارزان؛ Skövde قطب بازی سوئد (Sweden Game Arena)</t>
         </is>
       </c>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/medialogy-aal</t>
+          <t>https://www.his.se/en/education/</t>
         </is>
       </c>
     </row>
@@ -9946,32 +9952,32 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU)</t>
+          <t>Mälardalen University (MDU)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–10,000</t>
+          <t>متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>MSc Computer Science</t>
+          <t>MSc Intelligent Embedded Systems</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -9981,17 +9987,17 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>€17,300 (از ورودی سپتامبر ۲۰۲۶؛ قبلاً €13,900)</t>
+          <t>≈ SEK 135,000</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>$19,700</t>
+          <t>$13,600</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>≥ ۱۰۰ ECTS دروس CS؛ ظرفیت محدود + آزمون</t>
+          <t>کارشناسی CS/EE</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -9999,28 +10005,29 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M94" s="4">
-        <f>283</f>
-        <v/>
-      </c>
-      <c r="N94" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>⚠️ افزایش شهریهٔ ۲۰۲۶ — جدول اصلی اصلاح شد</t>
+          <t>ABB و Westinghouse در Västerås؛ رقم 2024/25</t>
         </is>
       </c>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
+          <t>https://www.mdu.se/en/malardalen-university/education</t>
         </is>
       </c>
     </row>
@@ -10030,27 +10037,27 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>دانمارک</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU)</t>
+          <t>Mälardalen University (MDU)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+          <t>Västerås (وسترئوس) — ABB، Westinghouse؛ ۱ ساعت تا استکهلم</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–10,000</t>
+          <t>متوسط — SEK 10,000–12,000</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Software Engineering</t>
+          <t>MSc Software Engineering</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -10065,17 +10072,17 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>€17,300</t>
+          <t>≈ SEK 135,000</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>$19,700</t>
+          <t>$13,600</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی SE/CS</t>
+          <t>کارشناسی CS/SE</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -10083,13 +10090,14 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M95" s="4">
-        <f>283</f>
-        <v/>
-      </c>
-      <c r="N95" s="10" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>Safe</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -10097,14 +10105,10 @@
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P95" s="4" t="inlineStr">
-        <is>
-          <t>گرایش‌های Interactive Tech &amp; Games، Cyber-security &amp; Data Intelligence</t>
-        </is>
-      </c>
+      <c r="P95" s="4" t="inlineStr"/>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/softwareengineering</t>
+          <t>https://www.mdu.se/en/malardalen-university/education</t>
         </is>
       </c>
     </row>
@@ -10119,27 +10123,27 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–10,000</t>
+          <t>متوسط — DKK 8,000–9,500</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>MSc Artificial Intelligence</t>
+          <t>MSc Computer Science (IT)</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>هوش مصنوعی / یادگیری ماشین</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -10149,26 +10153,26 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>€17,300</t>
+          <t>≈ €14,910 (2025/26: €7,455 در ترم؛ نرخ ۲۰۲۶ روی سایت AAU منتشر نشده — mastersportal: €15,340)</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>$19,700</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/AI</t>
+          <t>رسمی: حداقل ۱۵۰ ECTS دروس مرتبط با CS (برنامه‌نویسی ۱۵، مهندسی نرم‌افزار ۵، الگوریتم ۵، پایگاه داده ۵، ریاضیات گسسته ۵)؛ از ورودی ۲۰۲۷ سابقهٔ کار و انگیزه‌نامه هم در رتبه‌بندی حساب می‌شود</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5 (هر بخش ≥ 6.0)</t>
         </is>
       </c>
       <c r="M96" s="4">
-        <f>283</f>
+        <f>329</f>
         <v/>
       </c>
       <c r="N96" s="10" t="inlineStr">
@@ -10178,17 +10182,17 @@
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>شروع سپتامبر و فوریه</t>
+          <t>گزینهٔ Target جدول اصلی؛ PBL (پروژه‌محور)؛ ظرفیت محدود</t>
         </is>
       </c>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/studyscience</t>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
         </is>
       </c>
     </row>
@@ -10203,27 +10207,27 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
+          <t>Aalborg (آلبورگ) — شمال یوتلند</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>متوسط — DKK 8,000–10,000</t>
+          <t>متوسط — DKK 8,000–9,500</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Robot Systems</t>
+          <t>MSc Software</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -10233,17 +10237,17 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>€17,300</t>
+          <t>≈ €14,910–15,340</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>$19,700</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط (CS/EE/Mechatronics)</t>
+          <t>کارشناسی SE/CS</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -10252,7 +10256,7 @@
         </is>
       </c>
       <c r="M97" s="4">
-        <f>283</f>
+        <f>329</f>
         <v/>
       </c>
       <c r="N97" s="10" t="inlineStr">
@@ -10262,17 +10266,13 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
-        </is>
-      </c>
-      <c r="P97" s="4" t="inlineStr">
-        <is>
-          <t>Odense Robotics cluster (Universal Robots، MiR)</t>
-        </is>
-      </c>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P97" s="4" t="inlineStr"/>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
+          <t>https://www.en.aau.dk/education/master/software</t>
         </is>
       </c>
     </row>
@@ -10287,27 +10287,27 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Kolding (کولدینگ) — جنوب یوتلند</t>
+          <t>Copenhagen – Sydhavn (کپنهاگ؛ کمپوس AAU)</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>ارزان تا متوسط — DKK 7,500–9,000</t>
+          <t>خیلی گران — DKK 10,000–12,500</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science</t>
+          <t>MSc Eng Cyber Security</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>امنیت سایبری</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -10317,17 +10317,17 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>€17,300</t>
+          <t>≈ €14,910–15,340</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>$19,700</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی با محتوای کمی/برنامه‌نویسی</t>
+          <t>کارشناسی CS/EE مرتبط؛ مهلت ۱ مارس</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="M98" s="4">
-        <f>283</f>
+        <f>329</f>
         <v/>
       </c>
       <c r="N98" s="10" t="inlineStr">
@@ -10346,13 +10346,17 @@
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P98" s="4" t="inlineStr"/>
+          <t>4/5 — کمبود ساختاری (Bitkom: جزو ۳ کمبود اصلی آلمان)؛ اما ۳۱٪ تیم‌ها هیچ نیروی جونیور ندارند → کارآموزی/گواهی لازم است</t>
+        </is>
+      </c>
+      <c r="P98" s="4" t="inlineStr">
+        <is>
+          <t>کمپوس کپنهاگ: اجاره بالاتر ولی بازار کار بزرگ</t>
+        </is>
+      </c>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
+          <t>https://www.en.aau.dk/education/master/cyber-security/</t>
         </is>
       </c>
     </row>
@@ -10367,27 +10371,27 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen (ITU)</t>
+          <t>Aalborg University (AAU)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen (کپنهاگ)</t>
+          <t>Aalborg یا Copenhagen (هر دو کمپوس)</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 10,000–12,500</t>
+          <t>متوسط (Aalborg) تا خیلی گران (Copenhagen)</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>MSc Games — track Game Technology</t>
+          <t>MSc Medialogy</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>توسعه بازی</t>
+          <t>HCI / طراحی تعامل / UX</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -10397,17 +10401,17 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>€16,500 (€8,250 در ترم؛ ورودی ۲۰۲۶ — رسمی)</t>
+          <t>≈ €14,910–15,340</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>$18,800</t>
+          <t>$17,000–17,500</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>برای track فنی: کارشناسی CS</t>
+          <t>کارشناسی مرتبط (Medialogy، CS، Media Tech)</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -10415,10 +10419,9 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M99" s="4" t="inlineStr">
-        <is>
-          <t>— (تخصصی)</t>
-        </is>
+      <c r="M99" s="4">
+        <f>329</f>
+        <v/>
       </c>
       <c r="N99" s="10" t="inlineStr">
         <is>
@@ -10427,17 +10430,17 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+          <t>2/5 — آگهی‌های UX/UXR از ۲۰۲۲ حدود ۷۰٪ کم شده و از ۲۰۲۳ ثابت مانده؛ رقابت شدید، حقوق شروع کمتر از توسعه‌دهنده</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>شناخته‌شده‌ترین ارشد بازی اسکاندیناوی؛ Copenhagen (IO Interactive، Unity Copenhagen)</t>
+          <t>تعامل، AR/VR، بازی؛ بین HCI و Game</t>
         </is>
       </c>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://www.en.aau.dk/education/master/medialogy-aal</t>
         </is>
       </c>
     </row>
@@ -10452,17 +10455,17 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen (ITU)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen (کپنهاگ)</t>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 10,000–12,500</t>
+          <t>متوسط — DKK 8,000–10,000</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -10482,17 +10485,17 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>€16,500 (€8,250 در ترم)</t>
+          <t>€17,300 (از ورودی سپتامبر ۲۰۲۶؛ قبلاً €13,900)</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>$18,800</t>
+          <t>$19,700</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی CS/SE با برنامه‌نویسی قابل توجه</t>
+          <t>≥ ۱۰۰ ECTS دروس CS؛ ظرفیت محدود + آزمون</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -10500,10 +10503,9 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M100" s="4" t="inlineStr">
-        <is>
-          <t>— (تخصصی)</t>
-        </is>
+      <c r="M100" s="4">
+        <f>283</f>
+        <v/>
       </c>
       <c r="N100" s="10" t="inlineStr">
         <is>
@@ -10517,12 +10519,12 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌تر از DTU/KU در کپنهاگ؛ رقم قدیمی €13,400 (پورتال studyindenmark) منسوخ است</t>
+          <t>⚠️ افزایش شهریهٔ ۲۰۲۶ — جدول اصلی اصلاح شد</t>
         </is>
       </c>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
         </is>
       </c>
     </row>
@@ -10537,27 +10539,27 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen (ITU)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen (کپنهاگ)</t>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 10,000–12,500</t>
+          <t>متوسط — DKK 8,000–10,000</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>MSc Data Science</t>
+          <t>MSc Eng Software Engineering</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>علم داده / تحلیل داده</t>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -10567,17 +10569,17 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>€16,500 (€8,250 در ترم)</t>
+          <t>€17,300</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>$18,800</t>
+          <t>$19,700</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>کارشناسی مرتبط با داده/CS</t>
+          <t>کارشناسی SE/CS</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -10585,10 +10587,9 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M101" s="4" t="inlineStr">
-        <is>
-          <t>— (تخصصی)</t>
-        </is>
+      <c r="M101" s="4">
+        <f>283</f>
+        <v/>
       </c>
       <c r="N101" s="10" t="inlineStr">
         <is>
@@ -10597,13 +10598,17 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
-        </is>
-      </c>
-      <c r="P101" s="4" t="inlineStr"/>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>گرایش‌های Interactive Tech &amp; Games، Cyber-security &amp; Data Intelligence</t>
+        </is>
+      </c>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/softwareengineering</t>
         </is>
       </c>
     </row>
@@ -10618,22 +10623,22 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Technical University of Denmark (DTU)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 9,500–12,000</t>
+          <t>متوسط — DKK 8,000–10,000</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Human-Centered Artificial Intelligence</t>
+          <t>MSc Artificial Intelligence</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -10648,17 +10653,17 @@
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>€15,000</t>
+          <t>€17,300</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>$17,100</t>
+          <t>$19,700</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>ظرفیت محدود؛ امتیازدهی: معدل ۶۰٪ + سابقهٔ کار ۱۰٪</t>
+          <t>کارشناسی CS/AI</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -10666,14 +10671,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M102" s="4" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="N102" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="M102" s="4">
+        <f>283</f>
+        <v/>
+      </c>
+      <c r="N102" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O102" s="4" t="inlineStr">
@@ -10683,12 +10687,12 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>معدل ۱۵.۷۷ در رقابت DTU ضعیف است</t>
+          <t>شروع سپتامبر و فوریه</t>
         </is>
       </c>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/human-centered-artificial-intelligence</t>
+          <t>https://www.sdu.dk/en/studyscience</t>
         </is>
       </c>
     </row>
@@ -10703,22 +10707,22 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Technical University of Denmark (DTU)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+          <t>Odense (اودنسه) — سومین شهر؛ خوشهٔ رباتیک</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 9,500–12,000</t>
+          <t>متوسط — DKK 8,000–10,000</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Autonomous Systems</t>
+          <t>MSc Eng Robot Systems</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -10733,17 +10737,17 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>€15,000</t>
+          <t>€17,300</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>$17,100</t>
+          <t>$19,700</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>۸۰–۹۰ ECTS دروس مرتبط؛ ظرفیت محدود</t>
+          <t>کارشناسی مرتبط (CS/EE/Mechatronics)</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -10751,14 +10755,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M103" s="4" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="N103" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="M103" s="4">
+        <f>283</f>
+        <v/>
+      </c>
+      <c r="N103" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O103" s="4" t="inlineStr">
@@ -10766,10 +10769,14 @@
           <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
         </is>
       </c>
-      <c r="P103" s="4" t="inlineStr"/>
+      <c r="P103" s="4" t="inlineStr">
+        <is>
+          <t>Odense Robotics cluster (Universal Robots، MiR)</t>
+        </is>
+      </c>
       <c r="Q103" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
         </is>
       </c>
     </row>
@@ -10784,27 +10791,27 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Technical University of Denmark (DTU)</t>
+          <t>University of Southern Denmark (SDU)</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+          <t>Kolding (کولدینگ) — جنوب یوتلند</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>خیلی گران — DKK 9,500–12,000</t>
+          <t>ارزان تا متوسط — DKK 7,500–9,000</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>MSc Eng Computer Science and Engineering</t>
+          <t>MSc Data Science</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+          <t>علم داده / تحلیل داده</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -10814,17 +10821,17 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>€15,000</t>
+          <t>€17,300</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>$17,100</t>
+          <t>$19,700</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>ظرفیت محدود؛ گزینش با معدل</t>
+          <t>کارشناسی با محتوای کمی/برنامه‌نویسی</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -10832,25 +10839,24 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="M104" s="4" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="N104" s="12" t="inlineStr">
-        <is>
-          <t>Reach</t>
+      <c r="M104" s="4">
+        <f>283</f>
+        <v/>
+      </c>
+      <c r="N104" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
         </is>
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/computer-science-and-engineering</t>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/alle-kandidatuddannelser</t>
         </is>
       </c>
     </row>
@@ -10865,131 +10871,629 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
+          <t>IT University of Copenhagen (ITU)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Copenhagen (کپنهاگ)</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 10,000–12,500</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>MSc Games — track Game Technology</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>توسعه بازی</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>€16,500 (€8,250 در ترم؛ ورودی ۲۰۲۶ — رسمی)</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>$18,800</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>برای track فنی: کارشناسی CS</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M105" s="4" t="inlineStr">
+        <is>
+          <t>— (تخصصی)</t>
+        </is>
+      </c>
+      <c r="N105" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t>2/5 — ≈۴۵ هزار اخراج ۲۰۲۲–۲۰۲۵؛ ۲۶٪ توسعه‌دهندگان اروپایی حداقل یک‌بار اخراج شده‌اند؛ حقوق برنامه‌نویس Unity تا ۵۰٪ افت — سابقهٔ Unity شما مزیت ورود است، نه تضمین</t>
+        </is>
+      </c>
+      <c r="P105" s="4" t="inlineStr">
+        <is>
+          <t>شناخته‌شده‌ترین ارشد بازی اسکاندیناوی؛ Copenhagen (IO Interactive، Unity Copenhagen)</t>
+        </is>
+      </c>
+      <c r="Q105" s="8" t="inlineStr">
+        <is>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>IT University of Copenhagen (ITU)</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Copenhagen (کپنهاگ)</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 10,000–12,500</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>MSc Computer Science</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>€16,500 (€8,250 در ترم)</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>$18,800</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی CS/SE با برنامه‌نویسی قابل توجه</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M106" s="4" t="inlineStr">
+        <is>
+          <t>— (تخصصی)</t>
+        </is>
+      </c>
+      <c r="N106" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P106" s="4" t="inlineStr">
+        <is>
+          <t>ارزان‌تر از DTU/KU در کپنهاگ؛ رقم قدیمی €13,400 (پورتال studyindenmark) منسوخ است</t>
+        </is>
+      </c>
+      <c r="Q106" s="8" t="inlineStr">
+        <is>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>IT University of Copenhagen (ITU)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Copenhagen (کپنهاگ)</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 10,000–12,500</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>MSc Data Science</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>علم داده / تحلیل داده</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>€16,500 (€8,250 در ترم)</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>$18,800</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>کارشناسی مرتبط با داده/CS</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M107" s="4" t="inlineStr">
+        <is>
+          <t>— (تخصصی)</t>
+        </is>
+      </c>
+      <c r="N107" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>3/5 — بازار ارشد/سینیور خوب، ولی سطح جونیور اشباع (ده‌ها هزار فارغ‌التحصیل مشابه)؛ Data Engineer کم‌رقابت‌تر از Data Scientist</t>
+        </is>
+      </c>
+      <c r="P107" s="4" t="inlineStr"/>
+      <c r="Q107" s="8" t="inlineStr">
+        <is>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Technical University of Denmark (DTU)</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 9,500–12,000</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Human-Centered Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>هوش مصنوعی / یادگیری ماشین</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>€15,000</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>ظرفیت محدود؛ امتیازدهی: معدل ۶۰٪ + سابقهٔ کار ۱۰٪</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N108" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>5/5 — داغ‌ترین بازار؛ «AI Engineer» سریع‌ترین‌رشد (LinkedIn 2026)؛ ولی برنامه‌های ریاضی‌محور (Tübingen، UvA، KTH) بسیار رقابتی‌اند</t>
+        </is>
+      </c>
+      <c r="P108" s="4" t="inlineStr">
+        <is>
+          <t>معدل ۱۵.۷۷ در رقابت DTU ضعیف است</t>
+        </is>
+      </c>
+      <c r="Q108" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/human-centered-artificial-intelligence</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Technical University of Denmark (DTU)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 9,500–12,000</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>سیستم‌های نهفته / رباتیک / خودران</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>€15,000</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>۸۰–۹۰ ECTS دروس مرتبط؛ ظرفیت محدود</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M109" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — در آلمان و سوئد قوی (خودرو، Bosch، ABB، Ericsson)؛ ولی کارفرمایان صنعتی خارج از شهرهای بزرگ اغلب آلمانی/سوئدی می‌خواهند</t>
+        </is>
+      </c>
+      <c r="P109" s="4" t="inlineStr"/>
+      <c r="Q109" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Technical University of Denmark (DTU)</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Kgs. Lyngby (لینگبی) — ۱۵ کیلومتری کپنهاگ</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>خیلی گران — DKK 9,500–12,000</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>MSc Eng Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>۲ سال</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>€15,000</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>$17,100</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>ظرفیت محدود؛ گزینش با معدل</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N110" s="12" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
+        </is>
+      </c>
+      <c r="P110" s="4" t="inlineStr"/>
+      <c r="Q110" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/computer-science-and-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>دانمارک</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
           <t>Aarhus University (AU)</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>Aarhus (آرهوس) — دومین شهر دانمارک</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>گران — DKK 9,000–11,000</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>MSc Computer Science</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr">
+      <c r="G111" s="4" t="inlineStr">
         <is>
           <t>مهندسی نرم‌افزار / علوم کامپیوتر</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>۲ سال</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr">
+      <c r="I111" s="4" t="inlineStr">
         <is>
           <t>€17,300</t>
         </is>
       </c>
-      <c r="J105" s="4" t="inlineStr">
+      <c r="J111" s="4" t="inlineStr">
         <is>
           <t>$19,700</t>
         </is>
       </c>
-      <c r="K105" s="4" t="inlineStr">
+      <c r="K111" s="4" t="inlineStr">
         <is>
           <t>کارشناسی CS با واحدهای مشخص</t>
         </is>
       </c>
-      <c r="L105" s="4" t="inlineStr">
+      <c r="L111" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="M105" s="4" t="inlineStr">
+      <c r="M111" s="4" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="N105" s="11" t="inlineStr">
+      <c r="N111" s="11" t="inlineStr">
         <is>
           <t>Target/Reach</t>
         </is>
       </c>
-      <c r="O105" s="4" t="inlineStr">
+      <c r="O111" s="4" t="inlineStr">
         <is>
           <t>4/5 — بیشترین حجم آگهی در هر ۶ کشور؛ ورود جونیور از ۲۰۲۳ سخت‌تر شده — سابقهٔ کار شما مزیت است</t>
         </is>
       </c>
-      <c r="P105" s="4" t="inlineStr">
+      <c r="P111" s="4" t="inlineStr">
         <is>
           <t>Aarhus: دومین شهر، ارزان‌تر از کپنهاگ</t>
         </is>
       </c>
-      <c r="Q105" s="8" t="inlineStr">
+      <c r="Q111" s="8" t="inlineStr">
         <is>
           <t>https://masters.au.dk/computerscience</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="34" customHeight="1">
-      <c r="B107" s="13" t="inlineStr">
+    <row r="113" ht="34" customHeight="1">
+      <c r="B113" s="13" t="inlineStr">
         <is>
           <t>راهنما: هر ردیف یک برنامهٔ انگلیسی‌زبان است. Safe/Target/Reach نسبت به معدل ۱۵.۷۷/۲۰ (≈ 2:2 بریتانیا / ≈ 2.3 آلمانی / ≈ ۷۹٪) و IELTS ≈ 7 سنجیده شده و پیش‌بینی پذیرش نیست. «≈» یعنی رقم از منبع ثانویه یا سال قبل است — قبل از اقدام صفحهٔ رسمی را چک کنید.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="34" customHeight="1">
-      <c r="B108" s="13" t="inlineStr">
+    <row r="114" ht="34" customHeight="1">
+      <c r="B114" s="13" t="inlineStr">
         <is>
           <t>شهریهٔ دلاری با نرخ نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21 و گرد شده به $100. برای ورودی سپتامبر ۲۰۲۷ نرخ 2027/28 ملاک است (تا بهار ۲۰۲۷ منتشر می‌شود؛ فعلاً +۳–۵٪؛ TU/e و Surrey و Gothenburg همین حالا رسمی‌اند). آلمان: عدد فقط سهم ترم (Semesterbeitrag) است که بلیت حمل‌ونقل را هم شامل می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="34" customHeight="1">
-      <c r="B109" s="13" t="inlineStr">
+    <row r="115" ht="34" customHeight="1">
+      <c r="B115" s="13" t="inlineStr">
         <is>
           <t>امتیاز بازار کار (۱–۵) ارزیابی من بر پایهٔ منابع شیت «حوزه‌ها و بازار کار» است، نه آمار رسمی؛ برای هر برنامه فقط حوزه را نشان می‌دهد، نه کیفیت آن دانشگاه.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="34" customHeight="1">
-      <c r="B110" s="13" t="inlineStr">
+    <row r="116" ht="34" customHeight="1">
+      <c r="B116" s="13" t="inlineStr">
         <is>
           <t>ستون «هزینهٔ زندگی شهر» برآورد تقریبی هزینهٔ ماهانهٔ دانشجو با اجارهٔ اتاق در همان شهر است (سازگار با ردیف ۶ جدول اصلی)؛ برچسب‌ها: ارزان / متوسط / گران / خیلی گران. برای مقایسهٔ کشورها همچنان ردیف‌های ۶–۸ جدول اصلی معیار است.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="34" customHeight="1">
-      <c r="B111" s="13" t="inlineStr">
+    <row r="117" ht="34" customHeight="1">
+      <c r="B117" s="13" t="inlineStr">
         <is>
           <t>بازبینی صحت اعداد (۲۷ سپتامبر ۲۰۲۶): ≈۷۰٪ شهریه‌ها مستقیماً از صفحهٔ رسمی 2026/27 است؛ ردیف‌های «≈» از منبع ثانویه یا سال قبل‌اند. اصلاح‌های این بازبینی: FAU از تابستان ۲۰۲۷ شهریه می‌گیرد (AI/CS €4,000/ترم)؛ ITU €16,500 (نه €13,400)؛ Radboud €19,714 رسمی؛ Chalmers ≈ SEK 175k (نه 160k)؛ KTH ≈ 180–190k؛ AAU شرط ≥ ۱۵۰ ECTS؛ Surrey Cyber ورودی ۲۰۲۷؛ Newcastle Games 2:2؛ Sheffield AI ≈ £32.9–34.3k. رتبه‌بندی Safe/Target/Reach، امتیاز بازار و ردهٔ هزینهٔ شهر ارزیابی‌اند، نه دادهٔ رسمی.</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="34" customHeight="1">
-      <c r="B112" s="13" t="inlineStr">
+    <row r="118" ht="34" customHeight="1">
+      <c r="B118" s="13" t="inlineStr">
         <is>
           <t>حذف‌شده‌ها: Essex MSc Computer Games (برای 2025/26 و 2026/27 تعلیق شده)، Hull AI &amp; Data Science (سه رقم متناقض شهریه)، UCD/TCD (2:1 و ≈ €30k → Reach، بررسی نشد)، KU Copenhagen (شهریه تأیید نشد)؛ ایرلند (۱۲ برنامه) به خواست شما در سپتامبر ۲۰۲۶ کامل حذف و ۱۳ برنامهٔ سوئیس جایگزین شد. سوئیس: شهریه‌های ETH، EPFL، UZH، USI، ZHAW و HSLU از صفحات رسمی 2026/27؛ Bern، Fribourg و Basel از مراجع ثانویه (≈) — و یادتان باشد در سوئیس شهریه عدد کوچک است، هزینهٔ زندگی (CHF 1,400–2,500/ماه) و تمکن CHF 21,000 عدد اصلی‌اند.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q105"/>
+  <autoFilter ref="A1:Q111"/>
   <mergeCells count="6">
-    <mergeCell ref="B111:Q111"/>
-    <mergeCell ref="B107:Q107"/>
-    <mergeCell ref="B108:Q108"/>
-    <mergeCell ref="B110:Q110"/>
-    <mergeCell ref="B109:Q109"/>
-    <mergeCell ref="B112:Q112"/>
+    <mergeCell ref="B115:Q115"/>
+    <mergeCell ref="B114:Q114"/>
+    <mergeCell ref="B118:Q118"/>
+    <mergeCell ref="B113:Q113"/>
+    <mergeCell ref="B116:Q116"/>
+    <mergeCell ref="B117:Q117"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
@@ -11096,6 +11600,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12376,7 +12886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B173"/>
+  <dimension ref="A1:B184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12866,1594 +13376,1726 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>بورس – LiU International Scholarship: معمولاً ۵۰٪؛ شرط جدید ۲۰۲۶ (GPA ≥ 3.5/4 یا first/high second class)؛ فقط اولویت ۱</t>
+          <t>Russell Group – فهرست رسمی ۲۴ عضو (۲۰ در انگلستان)</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>https://liu.se/en/article/scholarships</t>
+          <t>https://russellgroup.ac.uk/about/our-universities/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>بورس – Chalmers: بورس‌های شهریه‌پردازها (IPOET ۷۵٪ با حداقل معدل ۸۰٪، Avancez)</t>
+          <t>انگلستان – Warwick: جدول رسمی تطبیق مدرک ایرانی (1st ۱۷/۲۰، 2:1 ۱۵/۲۰، 2:2 ۱۳/۲۰)</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>https://www.chalmers.se/en/education/application-and-admission/scholarships-for-fee-paying-students/</t>
+          <t>https://warwick.ac.uk/study/international/countryinformation/middleeast/iran/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>بورس – Halmstad University Scholarship ۲۵٪/۵۰٪ برای غیر-EU (ثانویه؛ hh.se را چک کنید)</t>
+          <t>انگلستان – Durham MSc Advanced Computer Science: £34,500 (2026)؛ جدول ایران (2:1 = ۱۴–۱۶/۲۰؛ Ecctis)</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>https://www.mastersportal.com/scholarships/10077/halmstad-university-scholarships.html</t>
+          <t>https://www.durham.ac.uk/study/courses/advanced-computer-science-g5t609/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>بورس – MDU: بورس تا ۱۰۰٪ شهریه برای متقاضیان اولویت ۱ (ثانویه؛ mdu.se را چک کنید)</t>
+          <t>انگلستان – KCL: جدول رسمی ایران (First ۱۸، high 2:1 ۱۷، 2:1 ۱۵، high 2:2 ۱۳ از ۲۰)؛ Advanced Computing high 2:1، £40,450 (2026)</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>https://daadscholarship.com/malardalen-university-scholarships-2026-to-study-for-free-in-sweden/</t>
+          <t>https://www.kcl.ac.uk/study-legacy/postgraduate/apply/entry-requirements/international</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>بورس – SI Scholarship for Global Professionals: ۳۴ کشور واجد شرایط — ایران نیست (رسمی)</t>
+          <t>انگلستان – Imperial MSc Computing (AI &amp; ML): First-class؛ £46,000 (2026/27)</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>https://si.se/en/apply/scholarships/swedish-institute-scholarships-for-global-professionals/</t>
+          <t>https://www.imperial.ac.uk/study/courses/postgraduate-taught/computing-artificial-intelligence-msc/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>بورس – NL Scholarship (سابقاً Holland Scholarship): €5,000 سال اول برای غیر-EEA، از طریق دانشگاه‌های عضو</t>
+          <t>انگلستان – UCL MSc Computer Science (تبدیلی): £42,700 (2026/27)، 2:1 در رشتهٔ غیر CS</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>https://www.mastersportal.com/scholarships/988/holland-scholarship-for-non-eea-international-students.html</t>
+          <t>https://www.ucl.ac.uk/prospective-students/graduate/taught-degrees/computer-science-msc-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>بورس – AAU: ≈ ۱۵ بورس دولتی در سال، معافیت شهریه + DKK 11,225/ماه (۲۰۲۶)، بررسی خودکار (رسمی)</t>
+          <t>انگلستان – Bristol MSc Data Science: £37,900 (سپتامبر ۲۰۲۷)، strong 2:1 (۶۵٪)</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/apply/master/finance-and-fees</t>
+          <t>https://www.bristol.ac.uk/study/postgraduate/taught/msc-data-science/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>بورس – ETH Excellence Scholarship &amp; Opportunity Programme: CHF 12,000/ترم + معافیت؛ ۱۰٪ بالای کلاس؛ ۱–۳۰ نوامبر</t>
+          <t>انگلستان – Bristol صفحهٔ ایران: کارشناسی ۴ ساله با حداقل ۱۵/۲۰ از دانشگاه مورد تأیید</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>https://ethz.ch/en/studies/financial/scholarships/excellencescholarship.html</t>
+          <t>https://www.bristol.ac.uk/international/countries/iran.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>بورس – USI: بورس‌های Fondazione per le Facoltà di Lugano (CHF 4,000؛ سال اول با معدل ≥ ۸۰/۱۰۰؛ سال دوم بهترینِ هر برنامه) — خبر رسمی USI</t>
+          <t>انگلستان – High Fliers «The Graduate Market in 2026»: دانشگاه‌های هدف کارفرمایان (Manchester، Birmingham، Nottingham، Warwick، UCL)؛ استخدام فارغ‌التحصیل در پایین‌ترین سطح از ۲۰۱۲</t>
         </is>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>https://www.eco.usi.ch/en/feeds/9861</t>
+          <t>https://www.manchester.ac.uk/about/news/university-of-manchester-tops-uk-rankings-for-graduate-employer-interest/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>بورس – Essex Academic Excellence International Masters Scholarship: جدول کشوری (ایران ۱۴/۲۰ → £4,500؛ جدول ۲۰۲۵–۲۶)</t>
+          <t>انگلستان – LEO (DfE) درآمد ۵ سال بعد: Imperial Computing £79,600؛ Bristol Computing £70,300؛ میانهٔ کل بخش ≈ £31–34k (ثانویه: unilens/campusquant)</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>https://www.essex.ac.uk/scholarships</t>
+          <t>https://unilens.co.uk/insights/highest-graduate-earnings-uk-universities-2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>بورس – Teesside Global Excellence Scholarship £2,000 (پیشنهاد تا ۳۰ آوریل؛ رسمی)</t>
+          <t>انگلستان – Appendix ATAS: ارشد آموزشی CS/AI نیاز به ATAS ندارد (فقط پژوهشی/PhD در CS و ارشد آموزشی فیزیک/مواد/مکانیک/هوافضا/شیمی)</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>https://www.tees.ac.uk/sections/international/global_excellence_scholarship.cfm</t>
+          <t>https://www.gov.uk/guidance/immigration-rules/immigration-rules-appendix-atas-academic-technology-approval-scheme-atas</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>بورس – Brunel Vice-Chancellor's Postgraduate International Excellence Award £6,000 (حداقل 2:1؛ ودیعهٔ £5,000)</t>
+          <t>بورس – LiU International Scholarship: معمولاً ۵۰٪؛ شرط جدید ۲۰۲۶ (GPA ≥ 3.5/4 یا first/high second class)؛ فقط اولویت ۱</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>https://www.brunel.ac.uk/scholarships</t>
+          <t>https://liu.se/en/article/scholarships</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>بورس – Northumbria PGT International Scholarship £3,000: فهرست کشوری/ادامه‌تحصیلی‌های داخل UK — ایران نیست</t>
+          <t>بورس – Chalmers: بورس‌های شهریه‌پردازها (IPOET ۷۵٪ با حداقل معدل ۸۰٪، Avancez)</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>https://www.mastersportal.com/scholarships/3890/pgt-international-scholarships.html</t>
+          <t>https://www.chalmers.se/en/education/application-and-admission/scholarships-for-fee-paying-students/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>بورس – Chevening eligibility (رسمی): ۲ سال کار بعد از مدرک کارشناسی + تعهد بازگشت ۲ ساله؛ مهلت ۶ اکتبر ۲۰۲۶</t>
+          <t>بورس – Halmstad University Scholarship ۲۵٪/۵۰٪ برای غیر-EU (ثانویه؛ hh.se را چک کنید)</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>https://www.chevening.org/resource-hub/guidance/eligibility/</t>
+          <t>https://www.mastersportal.com/scholarships/10077/halmstad-university-scholarships.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>بورس – Deutschlandstipendium €300/ماه (رسمی)</t>
+          <t>بورس – MDU: بورس تا ۱۰۰٪ شهریه برای متقاضیان اولویت ۱ (ثانویه؛ mdu.se را چک کنید)</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>https://www.deutschlandstipendium.de/</t>
+          <t>https://daadscholarship.com/malardalen-university-scholarships-2026-to-study-for-free-in-sweden/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – ETH: تاریخ‌های اپلای ارشد پاییز ۲۰۲۷ (۱–۳۰ نوامبر ۲۰۲۶؛ پاسخ تا پایان مارس؛ شروع ۲۰ سپتامبر ۲۰۲۷)</t>
+          <t>بورس – SI Scholarship for Global Professionals: ۳۴ کشور واجد شرایط — ایران نیست (رسمی)</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>https://ethz.ch/en/studies/master/application/dates.html</t>
+          <t>https://si.se/en/apply/scholarships/swedish-institute-scholarships-for-global-professionals/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EPFL: شهریه CHF 2,240/ترم برای خارجی‌های غیرمقیم از پاییز ۲۰۲۵ (CHF 780 برای بقیه)</t>
+          <t>بورس – NL Scholarship (سابقاً Holland Scholarship): €5,000 سال اول برای غیر-EEA، از طریق دانشگاه‌های عضو</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/education/studies/en/rules-and-procedures/study-taxes/tuition-fee-other-fees/</t>
+          <t>https://www.mastersportal.com/scholarships/988/holland-scholarship-for-non-eea-international-students.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EPFL: پنجره‌های اپلای ارشد (۱۵ دسامبر / ۳۱ مارس؛ یک برنامه در سال)</t>
+          <t>بورس – AAU: ≈ ۱۵ بورس دولتی در سال، معافیت شهریه + DKK 11,225/ماه (۲۰۲۶)، بررسی خودکار (رسمی)</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/education/admission/admission-2/master-admission-criteria-application/online-application/</t>
+          <t>https://www.en.aau.dk/education/apply/master/finance-and-fees</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – UZH: شهریه CHF 720 + 100 (خارجی، ارشد) + 59؛ هزینهٔ درخواست CHF 150</t>
+          <t>بورس – ETH Excellence Scholarship &amp; Opportunity Programme: CHF 12,000/ترم + معافیت؛ ۱۰٪ بالای کلاس؛ ۱–۳۰ نوامبر</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>https://www.uzh.ch/en/studies/application/fees.html</t>
+          <t>https://ethz.ch/en/studies/financial/scholarships/excellencescholarship.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – UZH: مهلت ویزایی‌ها ۲۸ فوریه / بدون ویزا ۳۰ آوریل (پاییز)</t>
+          <t>بورس – USI: بورس‌های Fondazione per le Facoltà di Lugano (CHF 4,000؛ سال اول با معدل ≥ ۸۰/۱۰۰؛ سال دوم بهترینِ هر برنامه) — خبر رسمی USI</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>https://www.oec.uzh.ch/en/studies/general/admission/master/faq-master-admission.html</t>
+          <t>https://www.eco.usi.ch/en/feeds/9861</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI MSc Informatics: CHF 4,000/ترم غیرمقیم، B2 در ورود → C1، مهلت غیر-EU ۳۰ آوریل</t>
+          <t>بورس – Essex Academic Excellence International Masters Scholarship: جدول کشوری (ایران ۱۴/۲۰ → £4,500؛ جدول ۲۰۲۵–۲۶)</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>https://www.usi.ch/en/education/master/informatics</t>
+          <t>https://www.essex.ac.uk/scholarships</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI MSc Artificial Intelligence: CHF 4,000/ترم، IELTS 6.5</t>
+          <t>بورس – Teesside Global Excellence Scholarship £2,000 (پیشنهاد تا ۳۰ آوریل؛ رسمی)</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/usi-universita-della-svizzera-italiana/postgrad/master-science-artificial-intelligence</t>
+          <t>https://www.tees.ac.uk/sections/international/global_excellence_scholarship.cfm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – swissuniversities: شهریهٔ دانشگاه‌های علوم کاربردی 2026–27 (ZHAW 1,220؛ HSLU 1,300؛ OST 1,500؛ FHNW 1,000–5,000)</t>
+          <t>بورس – Brunel Vice-Chancellor's Postgraduate International Excellence Award £6,000 (حداقل 2:1؛ ودیعهٔ £5,000)</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>https://www.swissuniversities.ch/en/themen/lehre-studium/information-on-studies/tuition-fees/tuition-fees-at-uas</t>
+          <t>https://www.brunel.ac.uk/scholarships</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – ZHAW MSE: انگلیسی، 90 ECTS، پروفایل‌های CS/Data Science/Cyber، معدل A/B، مهلت پایان آوریل</t>
+          <t>بورس – Northumbria PGT International Scholarship £3,000: فهرست کشوری/ادامه‌تحصیلی‌های داخل UK — ایران نیست</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
+          <t>https://www.mastersportal.com/scholarships/3890/pgt-international-scholarships.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – HSLU MSc Applied Information &amp; Data Science: C1 (B2 مشروط)، آلمانی لازم نیست، هر کارشناسی</t>
+          <t>بورس – Chevening eligibility (رسمی): ۲ سال کار بعد از مدرک کارشناسی + تعهد بازگشت ۲ ساله؛ مهلت ۶ اکتبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/haeufig-gestellte-fragen/</t>
+          <t>https://www.chevening.org/resource-hub/guidance/eligibility/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Bern: Swiss Joint MSc Computer Science (90 ECTS، انگلیسی، شرط کارشناسی CS)</t>
+          <t>بورس – Deutschlandstipendium €300/ماه (رسمی)</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
+          <t>https://www.deutschlandstipendium.de/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Bern شهریه از پاییز ۲۰۲۶: CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها + 34 + 25 در ترم (رسمی)</t>
+          <t>سوئیس – ETH: تاریخ‌های اپلای ارشد پاییز ۲۰۲۷ (۱–۳۰ نوامبر ۲۰۲۶؛ پاسخ تا پایان مارس؛ شروع ۲۰ سپتامبر ۲۰۲۷)</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>https://www.unibe.ch/studies/organizational_matters/renewal_of_semester_registration/fees/index_eng.html</t>
+          <t>https://ethz.ch/en/studies/master/application/dates.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Joint MSc CS (Bern/Neuchâtel/Fribourg) FAQ رسمی: بدون آزمون زبان (B2 توصیه)، شرط کارشناسی CS یا معادل با حداکثر ۶۰ ECTS تکمیلی، مهلت‌های دیرهنگام</t>
+          <t>سوئیس – EPFL: شهریه CHF 2,240/ترم برای خارجی‌های غیرمقیم از پاییز ۲۰۲۵ (CHF 780 برای بقیه)</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>https://mcs.unibnf.ch/faq/</t>
+          <t>https://www.epfl.ch/education/studies/en/rules-and-procedures/study-taxes/tuition-fee-other-fees/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Neuchâtel شهریهٔ خارجی‌ها CHF 790/ترم (رسمی)</t>
+          <t>سوئیس – EPFL: پنجره‌های اپلای ارشد (۱۵ دسامبر / ۳۱ مارس؛ یک برنامه در سال)</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>https://www.unine.ch/admission/taxes-universitaires/</t>
+          <t>https://www.epfl.ch/education/admission/admission-2/master-admission-criteria-application/online-application/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Neuchâtel مهلت ارشد ۳۰ آوریل؛ خارجی‌ها یک ماه زودتر؛ هزینهٔ پرونده CHF 100 (رسمی)</t>
+          <t>سوئیس – UZH: شهریه CHF 720 + 100 (خارجی، ارشد) + 59؛ هزینهٔ درخواست CHF 150</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>https://www.unine.ch/admission/admission-master/delais-et-frais-dinscription-pour-les-masters/</t>
+          <t>https://www.uzh.ch/en/studies/application/fees.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Fribourg شهریهٔ خارجی‌ها CHF 870 + 115 = 985/ترم (رسمی)</t>
+          <t>سوئیس – UZH: مهلت ویزایی‌ها ۲۸ فوریه / بدون ویزا ۳۰ آوریل (پاییز)</t>
         </is>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>https://www.unifr.ch/studies/en/organisation/administrative-services-unifr-students/university-fees/</t>
+          <t>https://www.oec.uzh.ch/en/studies/general/admission/master/faq-master-admission.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Fribourg مهلت ارشد با مدرک خارجی: ویزایی‌ها ۱–۲۸ فوریه، بقیه تا ۳۰ آوریل (رسمی)</t>
+          <t>سوئیس – USI MSc Informatics: CHF 4,000/ترم غیرمقیم، B2 در ورود → C1، مهلت غیر-EU ۳۰ آوریل</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>https://www.unifr.ch/studies/en/admission/admission-master/admission-master-foreign.html</t>
+          <t>https://www.usi.ch/en/education/master/informatics</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Basel MSc CS: 90 ECTS، انگلیسی، مهلت ۳۰ آوریل / ۳۰ نوامبر (رسمی)</t>
+          <t>سوئیس – USI MSc Artificial Intelligence: CHF 4,000/ترم، IELTS 6.5</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
+          <t>https://www.topuniversities.com/universities/usi-universita-della-svizzera-italiana/postgrad/master-science-artificial-intelligence</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Basel شهریه CHF 850/ترم برای همه + CHF 100 هزینهٔ درخواست (Uni Info 2026/27)</t>
+          <t>سوئیس – swissuniversities: شهریهٔ دانشگاه‌های علوم کاربردی 2026–27 (ZHAW 1,220؛ HSLU 1,300؛ OST 1,500؛ FHNW 1,000–5,000)</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>https://www.unibas.ch/dam/jcr:28672e66-8562-4988-9e38-b1c944ed22bf/COMPUTER%20SCIENCE%202026.2026-02-05-09-53-32.pdf</t>
+          <t>https://www.swissuniversities.ch/en/themen/lehre-studium/information-on-studies/tuition-fees/tuition-fees-at-uas</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – HSLU MSc Applied Data Science and AI (نام جدید): مهلت ویزایی‌ها ۱ آوریل، CHF 1,300/ترم خارجی، CHF 250 درخواست، 120 ECTS (رسمی)</t>
+          <t>سوئیس – ZHAW MSE: انگلیسی، 90 ECTS، پروفایل‌های CS/Data Science/Cyber، معدل A/B، مهلت پایان آوریل</t>
         </is>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
+          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI مهلت‌های 2026/27: غیر-EU ۳۰ آوریل؛ هزینهٔ پرونده CHF 100 برای مدارک خارج از کنوانسیون لیسبون (رسمی)</t>
+          <t>سوئیس – HSLU MSc Applied Information &amp; Data Science: C1 (B2 مشروط)، آلمانی لازم نیست، هر کارشناسی</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>https://www.usi.ch/en/education/master/informatics/application</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/haeufig-gestellte-fragen/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
+          <t>سوئیس – Bern: Swiss Joint MSc Computer Science (90 ECTS، انگلیسی، شرط کارشناسی CS)</t>
         </is>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
+          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
+          <t>سوئیس – Bern شهریه از پاییز ۲۰۲۶: CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها + 34 + 25 در ترم (رسمی)</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
+          <t>https://www.unibe.ch/studies/organizational_matters/renewal_of_semester_registration/fees/index_eng.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
+          <t>سوئیس – Joint MSc CS (Bern/Neuchâtel/Fribourg) FAQ رسمی: بدون آزمون زبان (B2 توصیه)، شرط کارشناسی CS یا معادل با حداکثر ۶۰ ECTS تکمیلی، مهلت‌های دیرهنگام</t>
         </is>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
+          <t>https://mcs.unibnf.ch/faq/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
+          <t>سوئیس – Neuchâtel شهریهٔ خارجی‌ها CHF 790/ترم (رسمی)</t>
         </is>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
+          <t>https://www.unine.ch/admission/taxes-universitaires/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
+          <t>سوئیس – Neuchâtel مهلت ارشد ۳۰ آوریل؛ خارجی‌ها یک ماه زودتر؛ هزینهٔ پرونده CHF 100 (رسمی)</t>
         </is>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
+          <t>https://www.unine.ch/admission/admission-master/delais-et-frais-dinscription-pour-les-masters/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
+          <t>سوئیس – Fribourg شهریهٔ خارجی‌ها CHF 870 + 115 = 985/ترم (رسمی)</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
+          <t>https://www.unifr.ch/studies/en/organisation/administrative-services-unifr-students/university-fees/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
+          <t>سوئیس – Fribourg مهلت ارشد با مدرک خارجی: ویزایی‌ها ۱–۲۸ فوریه، بقیه تا ۳۰ آوریل (رسمی)</t>
         </is>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
+          <t>https://www.unifr.ch/studies/en/admission/admission-master/admission-master-foreign.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
+          <t>سوئیس – Basel MSc CS: 90 ECTS، انگلیسی، مهلت ۳۰ آوریل / ۳۰ نوامبر (رسمی)</t>
         </is>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
+          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
+          <t>سوئیس – Basel شهریه CHF 850/ترم برای همه + CHF 100 هزینهٔ درخواست (Uni Info 2026/27)</t>
         </is>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
+          <t>https://www.unibas.ch/dam/jcr:28672e66-8562-4988-9e38-b1c944ed22bf/COMPUTER%20SCIENCE%202026.2026-02-05-09-53-32.pdf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
+          <t>سوئیس – HSLU MSc Applied Data Science and AI (نام جدید): مهلت ویزایی‌ها ۱ آوریل، CHF 1,300/ترم خارجی، CHF 250 درخواست، 120 ECTS (رسمی)</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
+          <t>سوئیس – USI مهلت‌های 2026/27: غیر-EU ۳۰ آوریل؛ هزینهٔ پرونده CHF 100 برای مدارک خارج از کنوانسیون لیسبون (رسمی)</t>
         </is>
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
+          <t>https://www.usi.ch/en/education/master/informatics/application</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
+          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
         </is>
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
+          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
+          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
         </is>
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
+          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
+          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
         </is>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
+          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
+          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
         </is>
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
+          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
+          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
         </is>
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
+          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
+          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
         </is>
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
+          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
+          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
         </is>
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
+          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
+          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
         </is>
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
+          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
+          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
+          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
+          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
         </is>
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
+          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
+          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
         </is>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
+          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
+          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
         </is>
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
+          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
+          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
         </is>
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
+          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
+          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
         </is>
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
+          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
+          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
         </is>
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
+          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
+          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
         </is>
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
+          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
+          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
         </is>
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
+          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
+          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
         </is>
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
+          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
+          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
         </is>
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
+          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – وضعیت VAC تهران</t>
+          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
         </is>
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
+          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – TU Dresden</t>
+          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
         </is>
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
+          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Stuttgart</t>
+          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
+          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Newcastle 149</t>
+          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
         </is>
       </c>
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – York =158</t>
+          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
         </is>
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/about/rankings/</t>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Leicester =314</t>
+          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
         </is>
       </c>
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/university-leicester</t>
+          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Essex =438</t>
+          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
         </is>
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/essex-university</t>
+          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Northumbria =528</t>
+          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
         </is>
       </c>
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Brunel</t>
+          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
         </is>
       </c>
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
+          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – سایر</t>
+          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
         </is>
       </c>
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/world-university-rankings</t>
+          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
+          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
         </is>
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
+          <t>بریتانیا – وضعیت VAC تهران</t>
         </is>
       </c>
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>https://www.xe.com/</t>
+          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
+          <t>QS WUR 2027 – TU Dresden</t>
         </is>
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
+          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
+          <t>QS WUR 2027 – Stuttgart</t>
         </is>
       </c>
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
+          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
+          <t>QS WUR 2027 – Newcastle 149</t>
         </is>
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>https://www.isc2.org/research</t>
+          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
+          <t>QS WUR 2027 – York =158</t>
         </is>
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
+          <t>https://www.york.ac.uk/about/rankings/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
+          <t>QS WUR 2027 – Leicester =314</t>
         </is>
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
+          <t>https://www.topuniversities.com/universities/university-leicester</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
+          <t>QS WUR 2027 – Essex =438</t>
         </is>
       </c>
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
+          <t>https://www.topuniversities.com/universities/essex-university</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
+          <t>QS WUR 2027 – Northumbria =528</t>
         </is>
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
+          <t>QS WUR 2027 – Brunel</t>
         </is>
       </c>
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
+          <t>QS WUR 2027 – سایر</t>
         </is>
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+          <t>https://www.topuniversities.com/world-university-rankings</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Siegen MSc HCI (DAAD)</t>
+          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
         </is>
       </c>
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
+          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
         </is>
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+          <t>https://www.xe.com/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>آلمان – RWTH MSc Software Systems Engineering</t>
+          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
         </is>
       </c>
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
+          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
         </is>
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
+          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
         </is>
       </c>
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+          <t>https://www.isc2.org/research</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
+          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
         </is>
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
+          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
         </is>
       </c>
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>هلند – Leiden CS 2026/27: €22,500</t>
+          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
         </is>
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>هلند – Groningen AI 2026/27: €24,900</t>
+          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
         </is>
       </c>
       <c r="B136" s="16" t="inlineStr">
         <is>
-          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
+          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
         </is>
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
+          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
         </is>
       </c>
       <c r="B138" s="16" t="inlineStr">
         <is>
-          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
+          <t>آلمان – Siegen MSc HCI (DAAD)</t>
         </is>
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
+          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
         </is>
       </c>
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Umeå AI: SEK 152,300</t>
+          <t>آلمان – RWTH MSc Software Systems Engineering</t>
         </is>
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
+          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
         </is>
       </c>
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>https://www.study.eu/best-universities/sweden</t>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
+          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
         </is>
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
+          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
         </is>
       </c>
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
+          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
         </is>
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus CS €17,300</t>
+          <t>هلند – Leiden CS 2026/27: €22,500</t>
         </is>
       </c>
       <c r="B146" s="16" t="inlineStr">
         <is>
-          <t>https://masters.au.dk/computerscience</t>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
+          <t>هلند – Groningen AI 2026/27: €24,900</t>
         </is>
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
+          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
         </is>
       </c>
       <c r="B148" s="16" t="inlineStr">
         <is>
-          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
+          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
         </is>
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
+          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
+          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
         </is>
       </c>
       <c r="B150" s="16" t="inlineStr">
         <is>
-          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
+          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
         </is>
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
+          <t>سوئد – Umeå AI: SEK 152,300</t>
         </is>
       </c>
       <c r="B152" s="16" t="inlineStr">
         <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
+          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
         </is>
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
+          <t>https://www.study.eu/best-universities/sweden</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – NTU QS 2027 =639</t>
+          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
         </is>
       </c>
       <c r="B154" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
+          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
         </is>
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
+          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
+          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
         </is>
       </c>
       <c r="B156" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
+          <t>دانمارک – Aarhus CS €17,300</t>
         </is>
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
+          <t>https://masters.au.dk/computerscience</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
+          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
         </is>
       </c>
       <c r="B158" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
+          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
         </is>
       </c>
       <c r="B159" s="16" t="inlineStr">
         <is>
-          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
+          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
         </is>
       </c>
       <c r="B160" s="16" t="inlineStr">
         <is>
-          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
+          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
         </is>
       </c>
       <c r="B161" s="16" t="inlineStr">
         <is>
-          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
         </is>
       </c>
       <c r="B162" s="16" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
         </is>
       </c>
       <c r="B163" s="16" t="inlineStr">
         <is>
-          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
         </is>
       </c>
       <c r="B164" s="16" t="inlineStr">
         <is>
-          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+          <t>انگلستان – NTU QS 2027 =639</t>
         </is>
       </c>
       <c r="B165" s="16" t="inlineStr">
         <is>
-          <t>https://zandienglish.ir/toefl-in-iran/</t>
+          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
         </is>
       </c>
       <c r="B166" s="16" t="inlineStr">
         <is>
-          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
         </is>
       </c>
       <c r="B167" s="16" t="inlineStr">
         <is>
-          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
         </is>
       </c>
       <c r="B168" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
         </is>
       </c>
       <c r="B169" s="16" t="inlineStr">
         <is>
-          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
         </is>
       </c>
       <c r="B170" s="16" t="inlineStr">
         <is>
-          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
         </is>
       </c>
       <c r="B171" s="16" t="inlineStr">
         <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
         </is>
       </c>
       <c r="B172" s="16" t="inlineStr">
         <is>
-          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
+          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>https://zandienglish.ir/toefl-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+        </is>
+      </c>
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+        </is>
+      </c>
+      <c r="B179" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+        </is>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+        </is>
+      </c>
+      <c r="B181" s="16" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+        </is>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+        </is>
+      </c>
+      <c r="B183" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
           <t>هلند – Twente: مهلت غیر-EEA ۱ می ۲۰۲۷؛ بورس UTS ۱۵ اکتبر ۲۰۲۶ – ۱ آوریل ۲۰۲۷</t>
         </is>
       </c>
-      <c r="B173" s="16" t="inlineStr">
+      <c r="B184" s="16" t="inlineStr">
         <is>
           <t>https://collegedunia.com/netherlands/university/749-university-of-twente-enschede/admission</t>
         </is>
@@ -14633,6 +15275,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B184" r:id="rId183"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -11,8 +11,9 @@
     <sheet name="برنامه‌ها" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="حوزه‌ها و بازار کار" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="برنامهٔ زمانی ۲۰۲۷" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="جمع‌بندی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="منابع" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="خوابگاه و مسکن" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="جمع‌بندی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="منابع" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه‌ها'!$A$1:$Q$111</definedName>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +50,7 @@
       <sz val="9"/>
       <u val="single"/>
     </font>
+    <font/>
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
@@ -123,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
@@ -168,7 +170,10 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12716,166 +12721,1596 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="130" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>موضوع</t>
+          <t>کشور</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>جمع‌بندی</t>
+          <t>چه کسی خوابگاه می‌دهد؟</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>تضمین برای دانشجوی ارشد بین‌المللی؟</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>هزینه‌اش داخل شهریه است؟</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>اجارهٔ خوابگاه (ماهانه، معمولاً با قبوض)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>غذا (catered)؟</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>اگر خوابگاه نشد: اتاق/خانهٔ خصوصی (ماهانه)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>زمان اقدام، ودیعه، ضامن — نکات ایرانی‌ها</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>منبع</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>رتبه‌بندی هزینه کل تا فارغ‌التحصیلی</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>آلمان 🇩🇪</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>آلمان $27–36k  &lt;  انگلستان $38–65k (۱ سال)  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k. سوئیس گسترده‌ترین بازه را دارد: $35–84k — Neuchâtel/Fribourg (۱.۵ سال) $35–47k کنار انگلستان، Bern $39–51k، UZH $45–58k، HSLU $53–64k، USI/EPFL $60–75k، ETH $66–84k کنار هلند</t>
+          <t>Studierendenwerk (نهاد عمومی هر شهر)؛ خودِ دانشگاه خوابگاه ندارد. ۱,۷۰۰ خوابگاه / ≈ ۱۹۶ هزار جا در کل کشور</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>❌ هیچ تضمینی؛ لیست انتظار. Stuttgart: معمولاً ۶–۸ ماه برای ترم زمستان · Darmstadt/Aachen سخت · Dresden، Chemnitz، Magdeburg، Passau، Saarbrücken راحت‌تر. بلافاصله بعد از پذیرش (قبل از ویزا) در لیست بنویسید</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>❌ جدا (شهریه‌ای هم نیست)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>میانگین ملی ≈ €306–330 با همهٔ قبوض (DSW) · Stuttgart میانگین €345 (بازهٔ €229–500) · شرق آلمان €220–330</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>❌ بدون غذا؛ Mensa ناهار €3–5</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>اتاق در WG: Stuttgart/Darmstadt/Aachen/Erlangen €450–700 · Dresden/Chemnitz/Magdeburg/Passau/Saarbrücken €280–450 · آپارتمان یک‌خوابه €600–1,000</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>ودیعهٔ ۲–۳ اجاره · بدون آدرس رسمی (Anmeldung) کارت اقامت نمی‌گیرید → قبل از پرواز حداقل اقامت موقت رزرو کنید · WGهای خصوصی معمولاً SCHUFA نمی‌خواهند ولی مصاحبهٔ ویدئویی و گواهی حساب مسدود کمک می‌کند</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>studierendenwerke.de؛ studierendenwerk-stuttgart.de؛ hdm-stuttgart.de</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>فقط با انگلیسی (تحصیل + کار + اداری + اقامت)</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>هلند 🇳🇱</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>انگلستان کامل؛ هلند و سوئد برای زندگی/کار خوب ولی برای اقامت دائم/تابعیت زبان می‌خواهند (هلند B1 در راه، سوئد آزمون تابعیت)؛ سوئیس: تحصیل و Big Tech زوریخ انگلیسی، ولی اداری به زبان کانتون و PR/تابعیت با A2–B1 زبان محلی (۱۰ سال)؛ دانمارک و آلمان بدون زبان محلی هم بازار کار و هم PR محدود.</t>
+          <t>دانشگاه‌ها خوابگاه ندارند؛ با شرکت‌های مسکن دانشجویی (SSH، Roomspot/De Veste، Vestide، Plaza) تعدادی اتاق «رزرو» می‌کنند</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>❌ نه. Twente: پیشنهاد اتاق برای دانشجویان ویزایی از طریق Roomspot، اول‌آمده‌اول‌گرفته · Radboud: «کمک مسکن» با فرم PAS تا ۱ ژوئن، اتاق مبلهٔ €370–650، بدون تضمین · Utrecht: استودیوهای رزروشدهٔ ارشد در ۲۸ می ۲۰۲۶ همه تمام شد · UvA/Delft/Leiden: قرعه‌کشی</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>❌ جدا</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Enschede/Nijmegen €370–650 · Eindhoven/Utrecht €500–870 (Utrecht Plaza: €868 با قبوض) · Amsterdam/Delft/Leiden €700–1,100</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>اتاق €500–900 · استودیو €900–1,400 · بحران ملی مسکن؛ بدون اتاق ثبت‌نام BSN و بانک هم گیر می‌کند</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>بعضی ارائه‌دهنده‌ها ۳ ماه اجاره پیش می‌گیرند · ودیعه ۱–۲ ماه (Utrecht: €1,306) · قرارداد ۱۲ ماههٔ غیرقابل فسخ · کلاهبرداری آنلاین زیاد: فقط از کانال دانشگاه/SSH</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>ru.nl؛ sshn.nl؛ uu.nl؛ utwente.nl (issuu)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>بازار کار و حقوق جونیور</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>سوئد 🇸🇪</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>حقوق ناخالص: سوئیس (CHF 85–105k) ≫ دانمارک &gt; آلمان &gt; هلند ≈ سوئد &gt; انگلستان. دسترسی برای جونیورِ فقط‌انگلیسی: هلند &gt; آلمان ≈ سوئیس (فقط شرکت‌های بزرگ، ۶ ماه فرصت) &gt; سوئد ≈ دانمارک ≈ انگلستان.</t>
+          <t>شرکت‌های مسکن دانشجویی/شهرداری (SGS گوتنبرگ، SSSB استکهلم، Studentbostäder لینشوپینگ…)؛ بعضی دانشگاه‌ها برای «شهریه‌پردازها» سهمیه دارند</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>✅ Uppsala: تضمین رسمی برای شهریه‌پردازها · LiU: یک پیشنهاد اتاق برای سال اول · KTH/Stockholm University: ❌ · Halmstad: «تضمین نمی‌کند» · Chalmers/MDU/BTH/Skövde: سهمیه یا صف — بلافاصله بعد از پرداخت شهریه اقدام کنید</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>❌ جدا</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>اتاق کریدوری SEK 3,500–6,500 (Stockholm 4,500–8,000؛ Linköping/Halmstad/Västerås/Karlskrona/Skövde ارزان‌تر)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>اتاق SEK 5,000–8,000 · آپارتمان کوچک SEK 8,000–13,000 · در استکهلم/گوتنبرگ بدون صف چندساله تقریباً غیرممکن</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>بدون شمارهٔ ملی (personnummer) اجارهٔ خصوصی سخت است؛ اجارهٔ دست‌دوم (andrahand) رایج و پرکلاهبرداری · ودیعه معمولاً ۱ ماه</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>uu.se؛ liu.se؛ hh.se؛ su.se</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>نتیجه با وزن برابر برای ۳ معیار</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>دانمارک 🇩🇰</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ = سوئیس ۱۸ › دانمارک ۱۶.  با حذف ایرلند، هیچ کشوری هر سه معیار را با هم نمی‌دهد: آلمان ارزان‌ترین (ولی آلمانی)، انگلستان تنها گزینهٔ کاملاً انگلیسی (ولی گران و بازار جونیور ضعیف)، سوئیس بالاترین حقوق (ولی گران‌ترین زندگی، ۶ ماه فرصت کار، زبان محلی برای PR). پیشنهاد: ۲ برنامه آلمان (Stuttgart + Passau/Saarland) + ۲ برنامه سوئیس با شانس واقعی (USI Lugano + HSLU یا Joint MSc CS در Neuchâtel/Fribourg) + ۱–۲ گزینهٔ ارزان انگلستان (Teesside/Northumbria) به‌عنوان مسیر تماماً انگلیسی؛ ETH/EPFL فقط اگر حاضرید CHF 150 را برای یک شانس کم خرج کنید. تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در بهار ۲۰۲۷.</t>
+          <t>دفتر مسکن بین‌الملل دانشگاه (AAU، SDU، AU) + خوابگاه‌های kollegium و شرکت‌های عمومی (KKIK/CIU در کپنهاگ)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>AAU Aalborg: «تقریباً ۱۰۰٪» (دفتر مسکن بین‌الملل، ۲۲۰+ واحد مبله) · AAU Copenhagen: ❌ صریحاً «بدون تضمین» · SDU Odense: کمک، بدون تضمین · ITU/DTU/KU کپنهاگ: ❌</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>❌ جدا</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Aalborg DKK 3,200–4,700 (میانگین 3,950؛ اینترنت/آب/گرمایش/برق داخل) · Odense DKK 3,500–5,500 · Copenhagen DKK 3,500–6,000 (KKIK/CIU) تا 5,000–9,000 (خوابگاه خصوصی/co-living)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Aalborg/Odense اتاق DKK 3,500–5,000 · Copenhagen آپارتمان از DKK 7,000+</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>AAU اجاره را سه‌ماهه می‌گیرد · ودیعه تا ۳ ماه · کمک‌هزینهٔ مسکن دولتی برای دانشجوی بین‌المللی ممنوع (گرفتنش = لغو اقامت)</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>en.aau.dk؛ sdu.dk</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ریسک شماره یک</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>سوئیس 🇨🇭</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>دسترسی به سفارت‌ها از داخل ایران (ردیف ۲۳): در سپتامبر ۲۰۲۶ فقط سوئیس (ویزای D با وقت قبلی) و تا حدی سوئد (آنلاین) از تهران قابل اقدام‌اند؛ آلمان، هلند، دانمارک و انگلستان خدمات عادی ندارند. برای سوئیس گلوگاه به‌جای سفارت، اثبات تمکن CHF 21,000 در بانک سوئیسی (کانتون زوریخ) است. از الان هزینه «برنامه B» (اقدام از ترکیه/ارمنستان/امارات) را در بودجه ببینید.</t>
+          <t>تعاونی‌های خوابگاه (WOKO/Juwo زوریخ، FMEL لوزان، خوابگاه‌های USI لوگانو، WoVe بازل، StuWo برن…)؛ دانشگاه فقط معرفی می‌کند</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>❌ هیچ‌جا. زوریخ لیست انتظار ۳–۱۲ ماه — روز پذیرش ثبت‌نام کنید · لوزان FMEL زود پر می‌شود · لوگانو/فریبورگ/نوشاتل/برن/لوسرن آسان‌تر</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>❌ جدا</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>WOKO زوریخ CHF 480–900 · FMEL ≈ CHF 500–900 · USI/Bern/Fribourg/Neuchâtel/Luzern ≈ CHF 450–800</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>❌ (Mensa ناهار CHF 7–12)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>اتاق در WG: زوریخ CHF 700–1,200، بقیه CHF 600–900 · استودیو CHF 1,200–1,800</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>ودیعهٔ ۲–۳ ماه · اجارهٔ خصوصی زوریخ اغلب گواهی عدم بدهی (Betreibungsauszug) + ضامن یا بیمهٔ ودیعه می‌خواهد · اجازهٔ اقامت به آدرس ثبت‌شده وابسته است</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>woko.ch؛ fmel.ch؛ برآوردهای ردیف ۱۰ جدول اصلی</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>برنامه زمانی ورودی سپتامبر ۲۰۲۷ (فشرده — جزئیات در شیت «برنامهٔ زمانی ۲۰۲۷»)</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>انگلستان 🇬🇧</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>اکتبر ۲۰۲۶: نظام‌وظیفه + رزرو IELTS خارج از ایران + مدارک · ۱۶ اکتبر: باز شدن سوئد · ۱–۳۰ نوامبر: پنجرهٔ ETH (Reach) · نوامبر–دسامبر: IELTS + VPD uni-assist · ۱۵ دسامبر: دور اول EPFL · ۱۵ ژانویه ۲۰۲۷: مهلت سوئد / AAU / Stuttgart · ۱ فوریه: مدارک سوئد + SDU · ۲۸ فوریه: UZH و Fribourg (ویزایی‌ها) · فوریه–مارس: انگلستان + پرونده‌های سوئیس · ۱ آوریل: Radboud + HSLU (ویزایی‌ها) · ۳۰ آوریل: USI / Neuchâtel / Bern / Basel / ZHAW · ۱ می: Twente · ۳۱ می: Passau · می–ژوئن: پول (سوئیس CHF 21,000 + شهریه) + ویزا یا برنامهٔ B · اوت–اکتبر: شروع (سوئیس اواسط سپتامبر).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>سه پیش‌نیاز عملی ورودی ۲۰۲۷</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>(۱) آزمون زبان: IELTS و TOEFL در ایران برگزار نمی‌شوند → سفر به ترکیه/ارمنستان/امارات/گرجستان تا دسامبر ۲۰۲۶. (۲) نظام‌وظیفه: بدون کارت/معافیت، خروج تحصیلی فقط با مجوز سخا + وثیقهٔ ۲۰۰ میلیون تومان + پذیرش از دانشگاه مورد تأیید وزارت علوم. (۳) نقدینگی: شهریه/تمکن سال اول باید تا می–ژوئن ۲۰۲۷ قابل انتقال باشد (SDU یک سال کامل پیش‌پرداخت). اگر یکی از این سه تا ژانویه ۲۰۲۷ حل نشود، هدف واقع‌بینانه سوئیس (USI/Bern/Basel/ZHAW تا ۳۰ آوریل)، انگلستان، هلند و آلمان با مهلت‌های بهار ۲۰۲۷ است — یا ورودی ۲۰۲۸. برای سوئیس علاوه بر این سه، «ضامن مقیم یا حساب بانکی قابل قبول کانتون» پیش‌نیاز چهارم است.</t>
+          <t>خودِ دانشگاه (halls) + خوابگاه‌های خصوصی PBSA (Unite، iQ، Student Roost…)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>✅ در بسیاری از دانشگاه‌ها برای ارشد، اگر تا مهلت اقدام کنید: York (تا ۳۱ ژوئیه)، Essex (برای کل دوره)، Brunel (همهٔ دانشجویان جدید؛ مهلت ۱۵ مارس!)، Teesside/Northumbria/Newcastle/Sheffield/Lancaster معمولاً بله (تأیید کنید) · ❌ Imperial، UCL، KCL، Durham (کالج‌ها برای PG بدون تضمین)، Warwick محدود</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>❌ همیشه جدا؛ قرارداد ۴۰–۵۱ هفته؛ قبوض و اینترنت داخل</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>شمال: Northumbria £94–158/هفته (رسمی) · Teesside ≈ £95–140 · Newcastle £118–240 (رسمی) · York £186–224 (رسمی؛ ۵۱ هفته = £9.5–11.4k/سال) · Durham PG ≈ £183–200 self-catered · جنوب/لندن: Essex ≈ £115–200 · Brunel ≈ £150–240 · UCL/KCL ≈ £190–350 · Imperial £210–410. یعنی ماهانه ≈ £400–700 شمال، £650–1,000 جنوب، £900–1,800 لندن</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>✅ «catered halls» وجود دارد ولی عمدتاً برای سال اول کارشناسی. برای ارشد: Durham (کالج‌های catered: صبحانه+ناهار+شام فقط در هفته‌های ترم ≈ ۳۰ هفته؛ ≈ £262/هفته = £10.2k/سال؛ سهم غذا ≈ £3,087) · Northumbria گزینهٔ catered دارد · York، Essex، Brunel، Newcastle، Teesside برای PG فقط self-catered</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>اتاق در خانهٔ مشترک: شمال £450–650/ماه · Colchester/Coventry/York £550–750 · لندن £900–1,400 · PBSA خصوصی £140–290/هفته شمال، £270–450 لندن</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>مزیت بزرگ برای ایرانی: خوابگاه دانشگاه ضامن بریتانیایی نمی‌خواهد (اجارهٔ خصوصی معمولاً ضامن UK یا ۶–۱۲ ماه پیش‌پرداخت؛ خدمات ضامن ≈ £138/ماه) · پیش‌پرداخت £250–500 (Brunel £350/£450) · UCL طرح ضامن دانشگاهی £50 دارد؛ Imperial فقط برای UG/PhD</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>york.ac.uk؛ essex.ac.uk؛ brunel.ac.uk؛ ncl.ac.uk؛ northumbria.ac.uk؛ durham.ac.uk؛ palatinate.org.uk</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>تغییرات اصلی نسبت به جدول اول</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>• ردیف ۵ب (بورس/تخفیف شهریهٔ واقعاً در دسترس شما) اضافه شد — ۲۸ سپتامبر ۲۰۲۶؛ امتیازها را عوض نمی‌کند
-• هزینه کل دوره اضافه شد (هلند از «نیاز به تأمین سال دوم» به گران‌ترین گزینه تبدیل شد)
-• فقط انگلستان (به خواست شما): Strathclyde و Swansea حذف شدند؛ گزینه‌ها Teesside £17,000 · Northumbria £21,500 · Leicester £24,250 · Essex £24,675 · Brunel £24,795 · York £32,900؛ Graduate visa ۱۸ ماه؛ کف اسپانسری £54,700 / £38,290؛ طرح PR ۱۰ ساله؛ عوارض £925 از ۲۰۲۸ شامل همهٔ گزینه‌ها
-• کف حقوق ۲۰۲۶ همه کشورها به‌روز شد (آلمان €50,700/€45,934؛ هلند €3,122/ماه؛ سوئد SEK 34,470)
-• ایرلند به خواست شما به‌کلی حذف و سوئیس جایگزین شد (سپتامبر ۲۰۲۶): شهریه‌های 2026/27 ETH/EPFL/UZH/USI/ZHAW/HSLU، تمکن CHF 21,000، ۶ ماه جست‌وجوی کار، سهمیهٔ غیر-EU، اجازهٔ C ۱۰ ساله، حقوق جونیور CHF 85–105k، سفارت تهران (ویزای D فعال)
-• سوئد: کار دانشجویی ۱۵ ساعت/هفته (ژوئن ۲۰۲۶)؛ شهروندی ۸ سال؛ «BTH یک‌ساله» حذف شد؛ خوابگاه فقط LiU
-• QS 2027؛ شهریه‌های واقعی 2026/27؛ «۷۵٪ قبولی» حذف شد
-• «۱۰۰٪ انگلیسی» برای هلند/سوئد/دانمارک تعدیل شد؛ دانمارک PD2/PD3 تفکیک شد
-• ردیف ویزا برای وضعیت ۲۰۲۶ بازنویسی شد؛ ردیف‌های IELTS، تمکن مالی، پس‌انداز، شهروندی و امتیاز اضافه شد</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>دانشگاه</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>کشور / شهر</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>خوابگاه یا کمک دانشگاه</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>تضمین برای ارشد؟</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>اجاره (ماهانه ≈)</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>غذا؟</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>مهلت / نکته</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>منبع</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>چرا «انگلستان» و نه «بریتانیا»</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Universität Stuttgart</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>به خواست شما فقط دانشگاه‌های انگلستان مقایسه شده‌اند. قوانین ویزا، کار و اقامت در کل بریتانیا یکسان است؛ سه تفاوت عملی: (۱) ارزان‌ترین گزینه‌های انگلستان (Teesside £17,000، Northumbria £21,500) از Swansea/Strathclyde ارزان‌ترند → کل دوره از $48–71k به $38–65k رسید؛ (۲) عوارض £925 به ازای هر دانشجو از اوت ۲۰۲۸ فقط دانشگاه‌های انگلستان را می‌گیرد — یعنی همهٔ گزینه‌های شما؛ (۳) بازار کار فناوری بریتانیا عملاً در انگلستان است (London، Manchester، Cambridge، Bristol، Leeds) — حذف اسکاتلند/ولز به فرصت شغلی لطمه نمی‌زند. برای شهریهٔ کمتر باید رتبهٔ پایین‌تر را بپذیرید: Teesside/Chester بدون رتبه QS، Northumbria ≈ ۵۲۸، Essex ≈ ۴۳۸؛ York (۱۵۸) و Newcastle (۱۴۹) تقریباً دوبرابر گران‌ترند.</t>
-        </is>
-      </c>
+          <t>آلمان / Stuttgart</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Studierendenwerk Stuttgart (۳۵ مجموعه، ۷,۲۰۰ جا)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>❌ لیست انتظار ۶–۸ ماه</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>€229–500 (میانگین €345) با قبوض</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>همان روز پذیرش ثبت‌نام؛ Esslingen/Göppingen زودتر خالی می‌شود</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>studierendenwerk-stuttgart.de</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>نکته پروفایل</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Uni Passau / Saarland / TU Dresden / Chemnitz / OVGU</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>معدل (۱۵.۷۷ طبق جدول اول؛ ۱۵.۷۰ طبق نقد دوم — تفاوتی در نتیجه ندارد) برای همه برنامه‌های بالا بالاتر از حداقل است. مهم‌تر از معدل، تطابق ریزنمرات با پیش‌نیازها (ریاضی، الگوریتم، CS نظری) و SOP با تکیه بر ۲ سال سابقه کار + بازی‌سازی + پروژه‌های گیت‌هاب است.</t>
-        </is>
-      </c>
+          <t>آلمان / شهرهای ارزان</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Studierendenwerk محلی</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>❌ ولی معمولاً ظرفیت هست</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>€220–380 با قبوض (≈)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>شهرهای کوچک/شرقی: بدون بحران؛ WG خصوصی €280–450</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>studierendenwerke.de (≈)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>اعداد را چگونه بخوانم</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TU Darmstadt / RWTH Aachen / FAU Erlangen</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>مبالغ سطح 2026/27 هستند؛ نرخ 2027/28 (سال ورود شما) بین اکتبر ۲۰۲۶ تا بهار ۲۰۲۷ منتشر می‌شود — جایی که رسمی بود (TU/e €22,400، Surrey £26,900، Gothenburg SEK 294k کل) در جدول آمده؛ برای بقیه فعلاً ۳–۵٪ اضافه کنید. نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21</t>
+          <t>آلمان / شهرهای گران</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Studierendenwerk محلی</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>❌ صف طولانی</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>€300–450 با قبوض (≈)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>WG خصوصی €450–700؛ زودتر از همه اقدام کنید</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>studierendenwerke.de (≈)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>هلند / Enschede</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>اتاق‌های کمپوس و شهر از طریق Roomspot (اول‌آمده‌اول‌گرفته)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>پیشنهاد برای دانشجویان ویزایی اگر زود اقدام کنند</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>€300–800</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>بلافاصله بعد از پذیرش در Roomspot ثبت‌نام کنید</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>utwente.nl (issuu)</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Radboud University</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>هلند / Nijmegen</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>میانجی‌گری دانشگاه + SSH&amp; (اتاق‌های مبله برای کل دوره)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>❌ «کمک، نه تضمین»</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>€370–650</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>فرم PAS تا ۱ ژوئن؛ پیشنهادها می–ژوئیه؛ گاهی ۳ ماه پیش‌پرداخت</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>ru.nl؛ sshn.nl</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Utrecht / TU Eindhoven / UvA / Delft / Leiden</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>هلند / شهرهای بزرگ</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>اتاق‌های رزروشده با SSH/Plaza/Vestide؛ قرعه‌کشی یا اول‌آمده</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>❌ (Utrecht ۲۰۲۶: ۲۸ می تمام شد)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>€650–1,100 (Utrecht استودیو €868 با قبوض)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>ودیعه ≈ ۲ ماه (Utrecht €1,306)؛ قرارداد ۱۲ ماههٔ ثابت</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>uu.nl</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Uppsala University</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>سوئد / Uppsala</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Housing Office دانشگاه</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>✅ تضمین رسمی برای شهریه‌پردازها</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>SEK 3,500–6,100</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>شهریه را تا مهلت بپردازید و به‌موقع درخواست دهید</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>uu.se</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Linköping University</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>سوئد / Linköping</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>یک پیشنهاد اتاق برای سال اول (Studentbostäder)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>✅ یک پیشنهاد (نه انتخاب)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>SEK 3,500–5,500 (≈)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>بعد از پرداخت شهریه؛ رد کنید = از دست می‌رود</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>liu.se</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>KTH / Chalmers</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>سوئد / Stockholm / Göteborg</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>KTH Accommodation (محدود)؛ Chalmers از طریق SGS برای شهریه‌پردازها</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>❌ KTH بدون تضمین؛ Chalmers سهمیه (چک شود)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>SEK 4,500–8,000</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>SSSB استکهلم صف ۶–۱۸ ماه؛ Plan B لازم</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>su.se؛ leapscholar (≈)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Halmstad / MDU / BTH / Skövde</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>سوئد / شهرهای کوچک</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>معرفی به شرکت‌های مسکن شهرداری</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>❌ Halmstad صریحاً «تضمین نمی‌کند»؛ بقیه صف</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>SEK 3,500–5,500 (≈)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>شهرهای کوچک: معمولاً ظرف چند هفته پیدا می‌شود</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>hh.se (≈)</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Aalborg University (Aalborg)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک / Aalborg</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>International Accommodation Office؛ ۲۲۰+ واحد مبله</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>✅ «تقریباً ۱۰۰٪»</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>DKK 3,200–4,700 (میانگین 3,950) با اینترنت/آب/گرمایش/برق</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>اجاره سه‌ماهه؛ ثبت‌نام studieboligaalborg.dk ۱ ژوئیه – ۳۱ اوت</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>en.aau.dk؛ findunirooms</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>AAU Copenhagen / ITU / DTU / KU</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک / Copenhagen</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>راهنمایی؛ KKIK/CIU؛ خوابگاه‌های خصوصی</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>❌ صریحاً بدون تضمین</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>DKK 3,500–6,000 (KKIK/CIU) · 5,000–9,000 خوابگاه/co-living · آپارتمان 7,000+</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>«سخت‌ترین بازار اروپا» (خود AAU)؛ ۶ ماه قبل شروع کنید</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>en.aau.dk</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SDU Odense</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک / Odense</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>SDU Housing (کمک با kollegium)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>❌ کمک، بدون تضمین</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>DKK 3,500–5,500 (≈)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Odense خیلی ارزان‌تر از کپنهاگ</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>sdu.dk (≈)</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ETH Zürich / UZH / ZHAW</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس / Zürich</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>WOKO، Juwo (تعاونی‌ها)؛ دانشگاه فقط معرفی می‌کند</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>❌ لیست انتظار ۳–۱۲ ماه</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>CHF 480–900؛ WG خصوصی 700–1,200</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>روز پذیرش در WOKO ثبت‌نام کنید؛ اجارهٔ خصوصی: ضامن/بیمهٔ ودیعه</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>woko.ch</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس / Lausanne</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>FMEL (بنیاد خوابگاه‌های لوزان)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>❌ زود پر می‌شود</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 500–900</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>بلافاصله بعد از پذیرش دور اول (مارس)</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>fmel.ch (≈)</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>USI / Bern / Fribourg / Neuchâtel / Basel / HSLU</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس / شهرهای کوچک‌تر</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه‌های دانشجویی محلی + معرفی دانشگاه</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>❌ ولی بازار آسان‌تر از زوریخ</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 450–800؛ WG 600–900</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>لوگانو/فریبورگ/نوشاتل ارزان‌ترین سوئیس</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Teesside University</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه دانشگاه + PBSA خصوصی</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>معمولاً بله برای دانشجویان جدید (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>≈ £95–140/هفته (≈ £410–610/ماه) با قبوض؛ PBSA از £138/هفته</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>❌ (PG)</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>ارزان‌ترین شهر جدول انگلستان</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>tees.ac.uk (≈)</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Northumbria University</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / Newcastle</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه دانشگاه</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>معمولاً بله (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>£94.19–158.31/هفته با قبوض (رسمی) = £410–690/ماه</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>✅ گزینهٔ catered دارد</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>حداقل زندگی ≈ £1,015/ماه (خود دانشگاه)</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>northumbria.ac.uk</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / Newcastle</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه‌های دانشگاه (Bowsden Court، Grand Hotel، Bernicia…)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>برای PG جدید معمولاً بله (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>£117.60–239.75/هفته (رسمی 2026/27)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>❌ (PG)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Bowsden Court برای PG/خانواده</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>University of York</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / York</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس (Wentworth Graduate College، Halifax)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>✅ تضمین PG اگر تا ۳۱ ژوئیه اقدام کنید</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>£186–224/هفته × ۵۱ هفته = £9,486–11,424/سال (رسمی 2026/27)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>❌ (PG self-catered)</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>پیشنهاد بدون قید ویزا تا ۷ اوت</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>york.ac.uk</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>University of Essex</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / Colchester</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>✅ تضمین برای PG برای کل دوره (اکتبر: مهلت ≈ ۱۲ سپتامبر؛ ژانویه: ۳۰ نوامبر)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>≈ £115–200/هفته (چک شود)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>ورود زودهنگام رایگان برای ورودی ژانویه</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>essex.ac.uk</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Brunel University London</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / Uxbridge</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>✅ تضمین برای همهٔ دانشجویان جدید — مهلت ۱۵ مارس ۲۰۲۶ برای 2026/27</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>≈ £150–240/هفته (چک شود)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت £350 (اتاق) / £450 (استودیو)</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>brunel.ac.uk</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Warwick / Sheffield / Lancaster / Leicester</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / شهرهای متوسط</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه دانشگاه</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sheffield/Lancaster معمولاً بله برای PG؛ Warwick محدود (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>≈ £125–210/هفته</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>❌ (PG)</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>اتاق خصوصی £550–750/ماه</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Durham University</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / Durham</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>کالج‌ها (۱۷ کالج؛ Ustinov فقط PG)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>❌ PG بدون تضمین؛ کالج‌ها بعد از پذیرش تماس می‌گیرند</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>PG self-catered ≈ £183–200/هفته (۳۹ هفته £7,146–7,801، 25/26) · catered £262/هفته (£10,233/سال)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>✅ کالج‌های catered (۳ وعده در ترم) — عمدتاً کارشناسی؛ بعضی کالج‌ها برای PG هم</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>سهم غذا ≈ £3,087/سال؛ اجارهٔ خصوصی از £190/هفته</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>durham.ac.uk؛ palatinate.org.uk</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>University of Bristol</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / Bristol</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه دانشگاه (catered و self-catered)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>PG: محدود (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>≈ £150–260/هفته</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>✅ catered halls (عمدتاً UG)</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>بریستول یکی از گران‌ترین شهرهای خارج لندن</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>UCL / King's College London</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / London</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه‌های دانشگاه و بین‌دانشگاهی</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>❌ PG بدون تضمین</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>≈ £190–350/هفته (£820–1,500/ماه)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>❌ (PG)</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>UCL طرح ضامن اجاره £50 (سقف £1,517/ماه)</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>harveywjames (≈)</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Imperial College London</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان / London</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه (Beit، Holbein…) + GradPad</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>❌ PG بدون تضمین</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>£210–410/هفته (۲۰۲۶) = £900–1,800/ماه؛ خانهٔ مشترک £180–450/هفته</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>❌ (PG)</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>طرح ضامن اجاره فقط UG/PhD؛ برآورد خود Imperial برای زندگی: £16.4–17k / ۹ ماه</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>harveywjames؛ ukfreshersguide (≈)</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>پاسخ کوتاه به «انگلیس خوابگاه با ناهار و شام می‌دهد»: بله، «catered halls» وجود دارد (معمولاً صبحانه + شام، در Durham سه وعده)، ولی (۱) تقریباً همه‌جا فقط برای سال اول کارشناسی است و برای ارشد فقط چند جا (Durham، Northumbria، بعضی کالج‌های Bristol)، (۲) فقط در هفته‌های ترم (≈ ۳۰ هفته) غذا می‌دهند، (۳) هیچ‌جا داخل شهریه نیست — Durham ≈ £3,087 در سال برای غذا جدا می‌گیرد و اجارهٔ catered ≈ £262/هفته است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>• در هیچ‌یک از ۶ کشور خوابگاه داخل شهریه نیست. ارزان‌ترین خوابگاه‌ها: آلمان (€230–450 با قبوض) و شهرهای کوچک سوئد/دانمارک؛ گران‌ترین: لندن (£900–1,800/ماه) و زوریخ (CHF 700–1,200 اتاق).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>• تضمین واقعی برای دانشجوی ارشد بین‌المللی فقط در: Uppsala، LiU (یک پیشنهاد)، AAU Aalborg، و دانشگاه‌های انگلستان با مهلت (York ۳۱ ژوئیه، Essex، Brunel ۱۵ مارس، احتمالاً Teesside/Northumbria/Newcastle/Sheffield/Lancaster). آلمان، هلند، سوئیس و لندن: هیچ تضمینی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>• برای ایرانی‌ها: خوابگاه دانشگاه در انگلستان ضامن بریتانیایی نمی‌خواهد — اجارهٔ خصوصی می‌خواهد (یا ۶–۱۲ ماه پیش‌پرداخت). در هلند/سوئیس/آلمان ودیعهٔ ۲–۳ ماه + گاهی پیش‌پرداخت ۳ ماه را در «نقد روز صفر» حساب کنید. آدرس ثبت‌شده در آلمان (Anmeldung)، هلند (BSN) و سوئیس شرط گرفتن کارت اقامت/بانک است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>• اعداد «رسمی» از صفحهٔ دانشگاه (۲۰۲۶/۲۷) و اعداد با «≈» برآورد از منابع ثانویه‌اند؛ اجاره‌ها هر سال ۳–۸٪ بالا می‌رود.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A38:I38"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12886,7 +14321,177 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B184"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>موضوع</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>جمع‌بندی</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>رتبه‌بندی هزینه کل تا فارغ‌التحصیلی</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>آلمان $27–36k  &lt;  انگلستان $38–65k (۱ سال)  &lt;  سوئد $54–65k  &lt;  دانمارک $63–76k  &lt;  هلند $75–90k. سوئیس گسترده‌ترین بازه را دارد: $35–84k — Neuchâtel/Fribourg (۱.۵ سال) $35–47k کنار انگلستان، Bern $39–51k، UZH $45–58k، HSLU $53–64k، USI/EPFL $60–75k، ETH $66–84k کنار هلند</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>فقط با انگلیسی (تحصیل + کار + اداری + اقامت)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان کامل؛ هلند و سوئد برای زندگی/کار خوب ولی برای اقامت دائم/تابعیت زبان می‌خواهند (هلند B1 در راه، سوئد آزمون تابعیت)؛ سوئیس: تحصیل و Big Tech زوریخ انگلیسی، ولی اداری به زبان کانتون و PR/تابعیت با A2–B1 زبان محلی (۱۰ سال)؛ دانمارک و آلمان بدون زبان محلی هم بازار کار و هم PR محدود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>بازار کار و حقوق جونیور</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>حقوق ناخالص: سوئیس (CHF 85–105k) ≫ دانمارک &gt; آلمان &gt; هلند ≈ سوئد &gt; انگلستان. دسترسی برای جونیورِ فقط‌انگلیسی: هلند &gt; آلمان ≈ سوئیس (فقط شرکت‌های بزرگ، ۶ ماه فرصت) &gt; سوئد ≈ دانمارک ≈ انگلستان.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>نتیجه با وزن برابر برای ۳ معیار</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>آلمان ۲۲ › سوئد ۱۹ = انگلستان ۱۹ › هلند ۱۸ = سوئیس ۱۸ › دانمارک ۱۶.  با حذف ایرلند، هیچ کشوری هر سه معیار را با هم نمی‌دهد: آلمان ارزان‌ترین (ولی آلمانی)، انگلستان تنها گزینهٔ کاملاً انگلیسی (ولی گران و بازار جونیور ضعیف)، سوئیس بالاترین حقوق (ولی گران‌ترین زندگی، ۶ ماه فرصت کار، زبان محلی برای PR). پیشنهاد: ۲ برنامه آلمان (Stuttgart + Passau/Saarland) + ۲ برنامه سوئیس با شانس واقعی (USI Lugano + HSLU یا Joint MSc CS در Neuchâtel/Fribourg) + ۱–۲ گزینهٔ ارزان انگلستان (Teesside/Northumbria) به‌عنوان مسیر تماماً انگلیسی؛ ETH/EPFL فقط اگر حاضرید CHF 150 را برای یک شانس کم خرج کنید. تصمیم نهایی با پذیرش/بورس و وضعیت سفارت‌ها در بهار ۲۰۲۷.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ریسک شماره یک</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>دسترسی به سفارت‌ها از داخل ایران (ردیف ۲۳): در سپتامبر ۲۰۲۶ فقط سوئیس (ویزای D با وقت قبلی) و تا حدی سوئد (آنلاین) از تهران قابل اقدام‌اند؛ آلمان، هلند، دانمارک و انگلستان خدمات عادی ندارند. برای سوئیس گلوگاه به‌جای سفارت، اثبات تمکن CHF 21,000 در بانک سوئیسی (کانتون زوریخ) است. از الان هزینه «برنامه B» (اقدام از ترکیه/ارمنستان/امارات) را در بودجه ببینید.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>برنامه زمانی ورودی سپتامبر ۲۰۲۷ (فشرده — جزئیات در شیت «برنامهٔ زمانی ۲۰۲۷»)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>اکتبر ۲۰۲۶: نظام‌وظیفه + رزرو IELTS خارج از ایران + مدارک · ۱۶ اکتبر: باز شدن سوئد · ۱–۳۰ نوامبر: پنجرهٔ ETH (Reach) · نوامبر–دسامبر: IELTS + VPD uni-assist · ۱۵ دسامبر: دور اول EPFL · ۱۵ ژانویه ۲۰۲۷: مهلت سوئد / AAU / Stuttgart · ۱ فوریه: مدارک سوئد + SDU · ۲۸ فوریه: UZH و Fribourg (ویزایی‌ها) · فوریه–مارس: انگلستان + پرونده‌های سوئیس · ۱ آوریل: Radboud + HSLU (ویزایی‌ها) · ۳۰ آوریل: USI / Neuchâtel / Bern / Basel / ZHAW · ۱ می: Twente · ۳۱ می: Passau · می–ژوئن: پول (سوئیس CHF 21,000 + شهریه) + ویزا یا برنامهٔ B · اوت–اکتبر: شروع (سوئیس اواسط سپتامبر).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>سه پیش‌نیاز عملی ورودی ۲۰۲۷</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>(۱) آزمون زبان: IELTS و TOEFL در ایران برگزار نمی‌شوند → سفر به ترکیه/ارمنستان/امارات/گرجستان تا دسامبر ۲۰۲۶. (۲) نظام‌وظیفه: بدون کارت/معافیت، خروج تحصیلی فقط با مجوز سخا + وثیقهٔ ۲۰۰ میلیون تومان + پذیرش از دانشگاه مورد تأیید وزارت علوم. (۳) نقدینگی: شهریه/تمکن سال اول باید تا می–ژوئن ۲۰۲۷ قابل انتقال باشد (SDU یک سال کامل پیش‌پرداخت). اگر یکی از این سه تا ژانویه ۲۰۲۷ حل نشود، هدف واقع‌بینانه سوئیس (USI/Bern/Basel/ZHAW تا ۳۰ آوریل)، انگلستان، هلند و آلمان با مهلت‌های بهار ۲۰۲۷ است — یا ورودی ۲۰۲۸. برای سوئیس علاوه بر این سه، «ضامن مقیم یا حساب بانکی قابل قبول کانتون» پیش‌نیاز چهارم است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>تغییرات اصلی نسبت به جدول اول</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>• ردیف ۵ب (بورس/تخفیف شهریهٔ واقعاً در دسترس شما) اضافه شد — ۲۸ سپتامبر ۲۰۲۶؛ امتیازها را عوض نمی‌کند
+• هزینه کل دوره اضافه شد (هلند از «نیاز به تأمین سال دوم» به گران‌ترین گزینه تبدیل شد)
+• فقط انگلستان (به خواست شما): Strathclyde و Swansea حذف شدند؛ گزینه‌ها Teesside £17,000 · Northumbria £21,500 · Leicester £24,250 · Essex £24,675 · Brunel £24,795 · York £32,900؛ Graduate visa ۱۸ ماه؛ کف اسپانسری £54,700 / £38,290؛ طرح PR ۱۰ ساله؛ عوارض £925 از ۲۰۲۸ شامل همهٔ گزینه‌ها
+• کف حقوق ۲۰۲۶ همه کشورها به‌روز شد (آلمان €50,700/€45,934؛ هلند €3,122/ماه؛ سوئد SEK 34,470)
+• ایرلند به خواست شما به‌کلی حذف و سوئیس جایگزین شد (سپتامبر ۲۰۲۶): شهریه‌های 2026/27 ETH/EPFL/UZH/USI/ZHAW/HSLU، تمکن CHF 21,000، ۶ ماه جست‌وجوی کار، سهمیهٔ غیر-EU، اجازهٔ C ۱۰ ساله، حقوق جونیور CHF 85–105k، سفارت تهران (ویزای D فعال)
+• سوئد: کار دانشجویی ۱۵ ساعت/هفته (ژوئن ۲۰۲۶)؛ شهروندی ۸ سال؛ «BTH یک‌ساله» حذف شد؛ خوابگاه فقط LiU
+• QS 2027؛ شهریه‌های واقعی 2026/27؛ «۷۵٪ قبولی» حذف شد
+• «۱۰۰٪ انگلیسی» برای هلند/سوئد/دانمارک تعدیل شد؛ دانمارک PD2/PD3 تفکیک شد
+• ردیف ویزا برای وضعیت ۲۰۲۶ بازنویسی شد؛ ردیف‌های IELTS، تمکن مالی، پس‌انداز، شهروندی و امتیاز اضافه شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>چرا «انگلستان» و نه «بریتانیا»</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>به خواست شما فقط دانشگاه‌های انگلستان مقایسه شده‌اند. قوانین ویزا، کار و اقامت در کل بریتانیا یکسان است؛ سه تفاوت عملی: (۱) ارزان‌ترین گزینه‌های انگلستان (Teesside £17,000، Northumbria £21,500) از Swansea/Strathclyde ارزان‌ترند → کل دوره از $48–71k به $38–65k رسید؛ (۲) عوارض £925 به ازای هر دانشجو از اوت ۲۰۲۸ فقط دانشگاه‌های انگلستان را می‌گیرد — یعنی همهٔ گزینه‌های شما؛ (۳) بازار کار فناوری بریتانیا عملاً در انگلستان است (London، Manchester، Cambridge، Bristol، Leeds) — حذف اسکاتلند/ولز به فرصت شغلی لطمه نمی‌زند. برای شهریهٔ کمتر باید رتبهٔ پایین‌تر را بپذیرید: Teesside/Chester بدون رتبه QS، Northumbria ≈ ۵۲۸، Essex ≈ ۴۳۸؛ York (۱۵۸) و Newcastle (۱۴۹) تقریباً دوبرابر گران‌ترند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>نکته پروفایل</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>معدل (۱۵.۷۷ طبق جدول اول؛ ۱۵.۷۰ طبق نقد دوم — تفاوتی در نتیجه ندارد) برای همه برنامه‌های بالا بالاتر از حداقل است. مهم‌تر از معدل، تطابق ریزنمرات با پیش‌نیازها (ریاضی، الگوریتم، CS نظری) و SOP با تکیه بر ۲ سال سابقه کار + بازی‌سازی + پروژه‌های گیت‌هاب است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>اعداد را چگونه بخوانم</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>مبالغ سطح 2026/27 هستند؛ نرخ 2027/28 (سال ورود شما) بین اکتبر ۲۰۲۶ تا بهار ۲۰۲۷ منتشر می‌شود — جایی که رسمی بود (TU/e €22,400، Surrey £26,900، Gothenburg SEK 294k کل) در جدول آمده؛ برای بقیه فعلاً ۳–۵٪ اضافه کنید. نرخ تبدیل ۲۷ سپتامبر ۲۰۲۶: €1 = $1.14 · £1 = $1.325 · $1 ≈ SEK 9.9 · $1 ≈ DKK 6.55 · CHF 1 = $1.21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12911,7 +14516,7 @@
           <t>آلمان – EU Blue Card 2026 (€50,700 / €45,934.20)</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/visa-residence/types/eu-blue-card</t>
         </is>
@@ -12923,7 +14528,7 @@
           <t>آلمان – Sperrkonto €992/ماه (2026)</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/study-training/study/financing</t>
         </is>
@@ -12935,7 +14540,7 @@
           <t>آلمان – Niederlassungserlaubnis §18c (فارغ‌التحصیلان، ۲ سال، B1)</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>https://www.make-it-in-germany.com/en/visa-residence/living-permanently/permanent-residence</t>
         </is>
@@ -12947,7 +14552,7 @@
           <t>آلمان – Stuttgart MSc Computer Science (انگلیسی، IELTS 7، €1,500/ترم)</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc./</t>
         </is>
@@ -12959,7 +14564,7 @@
           <t>آلمان – FAU MSc Artificial Intelligence (انگلیسی، B2)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>https://www.ai.study.fau.eu/prospective-students/living-studying-in-germany/language-proficiency/</t>
         </is>
@@ -12971,7 +14576,7 @@
           <t>آلمان – TU Darmstadt MSc Computer Science</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>https://www.informatik.tu-darmstadt.de/studium_fb20/im_studium/studiengaenge_liste/computer_science_msc.en.jsp</t>
         </is>
@@ -12983,7 +14588,7 @@
           <t>آلمان – TU Dresden MSc Computer Science admission</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>https://tu-dresden.de/ing/informatik/studium/studienangebot/master-studiengaenge/m-sc-computer-science/admission?set_language=en</t>
         </is>
@@ -12995,7 +14600,7 @@
           <t>آلمان – TLScontact Tehran (لیست انتظار دانشجویی)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>https://visas-de.tlscontact.com/en-us/country/ir/vac/irTHR2de</t>
         </is>
@@ -13007,7 +14612,7 @@
           <t>آلمان – وضعیت سفارت تهران (Iran International، اوت ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>https://www.iranintl.com/en/202608115899</t>
         </is>
@@ -13019,7 +14624,7 @@
           <t>آلمان – Fintiba: ساکنان ایران پذیرفته نمی‌شوند</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>https://www.simplegermany.com/best-blocked-account-germany/</t>
         </is>
@@ -13031,7 +14636,7 @@
           <t>آلمان – حقوق توسعه‌دهنده (StepStone)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>https://www.stepstone.de/gehalt/Software-Entwickler-in.html</t>
         </is>
@@ -13043,7 +14648,7 @@
           <t>هلند – IND مبالغ ۲۰۲۶ (HSM €3,122 / €4,357؛ دانشجو €1,130.77)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>https://ind.nl/en/required-amounts-income-requirements</t>
         </is>
@@ -13055,7 +14660,7 @@
           <t>هلند – Twente شهریه 2026/27 €21,700</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/computer-science/finance/</t>
         </is>
@@ -13067,7 +14672,7 @@
           <t>هلند – Twente حداقل معدل برای مدرک ایرانی (۱۵/۲۰)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/education/master/programmes/european-studies/admission/international/</t>
         </is>
@@ -13079,7 +14684,7 @@
           <t>هلند – Twente QS 2027 = 223</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/about-us/impact-ambitions/rankings/</t>
         </is>
@@ -13091,7 +14696,7 @@
           <t>هلند – Radboud شهریهٔ رسمی 2026/27 غیر-EEA €19,714 (Data Science and AI؛ دانشکدهٔ علوم)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>https://www.ru.nl/en/education/masters/data-science-and-ai/tuition</t>
         </is>
@@ -13103,7 +14708,7 @@
           <t>هلند – MVV در ایران (سفارت در باکو)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>https://www.netherlandsworldwide.nl/visa-the-netherlands/mvv-long-stay/apply-iran</t>
         </is>
@@ -13115,7 +14720,7 @@
           <t>هلند – B1 برای PR/تابعیت (تصمیم کابینه ۲۰۲۶)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>https://thedutchdaily.nl/dutch-citizenship-b1-language-requirement-confirmed-2026/</t>
         </is>
@@ -13127,7 +14732,7 @@
           <t>سوئد – قوانین جدید اقامت تحصیلی از ۱۱ ژوئن ۲۰۲۶ (۱۵ ساعت/هفته)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/nyheter/news-archive/2026-05-25-new-rules-for-residence-permits-for-studies-in-higher-education.html</t>
         </is>
@@ -13139,7 +14744,7 @@
           <t>سوئد – قوانین جدید مجوز کار از ۱ ژوئن ۲۰۲۶ (SEK 34,470)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/nyheter/news-archive/2026-04-17-new-rules-for-work-permits-from-1-june-2026.html</t>
         </is>
@@ -13151,7 +14756,7 @@
           <t>سوئد – گروه‌های معاف (فارغ‌التحصیلان ۷۵٪)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>https://eiglaw.com/sweden-publishes-exempt-occupations-for-new-salary-rule/</t>
         </is>
@@ -13163,7 +14768,7 @@
           <t>سوئد – مجوز ۱۲ ماهه جست‌وجوی کار و تمکن SEK 10,656</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>https://www.migrationsverket.se/en/you-want-to-extend/study/look-for-work-after-completing-your-studies-in-sweden.html</t>
         </is>
@@ -13175,7 +14780,7 @@
           <t>سوئد – Linköping MSc CS شهریه SEK 332,000 (کل)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>https://liu.se/en/education/program/6mics</t>
         </is>
@@ -13187,7 +14792,7 @@
           <t>سوئد – BTH MSc Software Engineering 120 credits (SEK 70,000/ترم)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>https://www.bth.se/english/education/programmes/masters-programme-in-software-engineering-120-credits</t>
         </is>
@@ -13199,7 +14804,7 @@
           <t>سوئد – BTH برنامه ۶۰ واحدی (از راه دور، نیمه‌وقت، ۲ سال سابقه)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>https://www.bth.se/english/education/programmes/masters-programme-in-software-engineering-60-credits</t>
         </is>
@@ -13211,7 +14816,7 @@
           <t>سوئد – Halmstad MSc Information Technology شهریه</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>https://www.mastersportal.com/studies/22787/information-technology.html</t>
         </is>
@@ -13223,7 +14828,7 @@
           <t>سوئد – Halmstad مسکن (بدون تضمین)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>https://www.hh.se/english/education/student-life/find-accommodation.html</t>
         </is>
@@ -13235,7 +14840,7 @@
           <t>سوئد – شهروندی ۸ ساله از ژوئن ۲۰۲۶</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>https://www.imidaily.com/europe/sweden-passes-law-curtailing-naturalization-8-year-wait-income-floor/</t>
         </is>
@@ -13247,7 +14852,7 @@
           <t>سوئد – اطلاعیه مهاجرتی سفارت تهران</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>https://www.swedenabroad.se/globalassets/ambassader/iran-teheran/documents/migration-issues/new-folder/english-versin.pdf</t>
         </is>
@@ -13259,7 +14864,7 @@
           <t>دانمارک – Pay Limit Scheme 2026</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/pl-PL/You-want-to-apply/Work/Pay-limit-scheme</t>
         </is>
@@ -13271,7 +14876,7 @@
           <t>دانمارک – برنامه‌های آموزش عالی: ۹۰ ساعت/ماه، ۶ ماه یا ۳ سال جست‌وجوی کار</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/en-GB/You-want-to-apply/Study/Higher-Education</t>
         </is>
@@ -13283,7 +14888,7 @@
           <t>دانمارک – مجوز ۳ ساله جست‌وجوی کار</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/de-DE/You-want-to-apply/Study/Study---job-seeking/Study---3-years-job-seeking</t>
         </is>
@@ -13295,7 +14900,7 @@
           <t>دانمارک – اقامت دائم</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>https://www.nyidanmark.dk/de-DE/You-want-to-apply/Permanent-residence-permit/Permanent-residence</t>
         </is>
@@ -13307,7 +14912,7 @@
           <t>دانمارک – تمکن DKK 7,426 (2026)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>https://nyidanmark.dk/en-GB/Words-and-concepts/SIRI/Self-support---SIRI</t>
         </is>
@@ -13319,7 +14924,7 @@
           <t>دانمارک – AAU Computer Science (IT) شهریه €7,455/ترم</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>https://studyindenmark.dk/portal/aalborg-university-aau/aalborg/computer-science-it-msc</t>
         </is>
@@ -13331,7 +14936,7 @@
           <t>دانمارک – SDU شهریهٔ رسمی از ورودی ۲۰۲۶: Science/Engineering €17,300 در سال</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/fees_and_funding/tuition</t>
         </is>
@@ -13343,7 +14948,7 @@
           <t>دانمارک – SDU MSc Computer Science (ظرفیت محدود، €17,300)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi/adgangskrav</t>
         </is>
@@ -13355,7 +14960,7 @@
           <t>دانمارک – سفارت تهران (درخواست از ایران ممکن نیست)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>https://iran.um.dk/en</t>
         </is>
@@ -13367,7 +14972,7 @@
           <t>دانمارک – IDA حقوق شروع ۲۰۲۶</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>https://studerende.ida.dk/snart-nyuddannet/loen/softwareingenioer-loen-saa-meget-kommer-du-til-at-tjene/</t>
         </is>
@@ -13376,1726 +14981,1942 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Russell Group – فهرست رسمی ۲۴ عضو (۲۰ در انگلستان)</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>https://russellgroup.ac.uk/about/our-universities/</t>
+          <t>مسکن – DSW: میانگین اجارهٔ خوابگاه Studierendenwerk ≈ €306 با قبوض؛ ۱,۷۰۰ خوابگاه / ۱۹۶ هزار جا</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>https://www.studierendenwerke.de/en/topics/accomodation/accommodation-and-studies</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Warwick: جدول رسمی تطبیق مدرک ایرانی (1st ۱۷/۲۰، 2:1 ۱۵/۲۰، 2:2 ۱۳/۲۰)</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>https://warwick.ac.uk/study/international/countryinformation/middleeast/iran/</t>
+          <t>مسکن – Studierendenwerk Stuttgart: €229–399 با قبوض، لیست انتظار معمول ۶–۸ ماه (اطلاعیهٔ رسمی)</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>https://www.studierendenwerk-stuttgart.de/ueber-uns/presse/pressemitteilungen/mitteilung/wohnraum-fuer-studierende-in-der-hochschulregion-stuttgart</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Durham MSc Advanced Computer Science: £34,500 (2026)؛ جدول ایران (2:1 = ۱۴–۱۶/۲۰؛ Ecctis)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>https://www.durham.ac.uk/study/courses/advanced-computer-science-g5t609/</t>
+          <t>مسکن – Radboud: کمک مسکن (فرم PAS تا ۱ ژوئن)، بدون تضمین، گاهی ۳ ماه پیش‌پرداخت</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/students/international-students/housing/housing-options/apply-for-help-with-housing</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – KCL: جدول رسمی ایران (First ۱۸، high 2:1 ۱۷، 2:1 ۱۵، high 2:2 ۱۳ از ۲۰)؛ Advanced Computing high 2:1، £40,450 (2026)</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>https://www.kcl.ac.uk/study-legacy/postgraduate/apply/entry-requirements/international</t>
+          <t>مسکن – Radboud بروشور 2026–27: اتاق مبلهٔ €370–650؛ زندگی €1,100–1,200</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>https://www.timeshighereducation.com/cms-academic/sites/default/files/institution_downloads/2025-08/OM_BAMA_intbrochure_2026-2027_interactieve_3.pdf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Imperial MSc Computing (AI &amp; ML): First-class؛ £46,000 (2026/27)</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>https://www.imperial.ac.uk/study/courses/postgraduate-taught/computing-artificial-intelligence-msc/</t>
+          <t>مسکن – Utrecht: استودیوهای رزروشدهٔ ارشد €868 با قبوض، ودیعه €1,306؛ ۲۸ می ۲۰۲۶ تمام شد</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uu.nl/en/education/welcome-to-utrecht/prepare-your-stay/arrange-housing/ways-to-find-housing/uu-reserved-accommodation-progamme/reserved-accommodation-for-masters-sep-26/reserved-housing-plaza</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – UCL MSc Computer Science (تبدیلی): £42,700 (2026/27)، 2:1 در رشتهٔ غیر CS</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>https://www.ucl.ac.uk/prospective-students/graduate/taught-degrees/computer-science-msc-2026</t>
+          <t>مسکن – Twente: اجاره €300–800؛ Roomspot؛ پیشنهاد برای دانشجویان ویزایی اول‌آمده‌اول‌گرفته</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>https://issuu.com/utwente/docs/master_programmes_university_of_twente/s/16597294</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Bristol MSc Data Science: £37,900 (سپتامبر ۲۰۲۷)، strong 2:1 (۶۵٪)</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>https://www.bristol.ac.uk/study/postgraduate/taught/msc-data-science/</t>
+          <t>مسکن – Uppsala: تضمین رسمی خوابگاه برای شهریه‌پردازها</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uu.se/en/study/masters-studies/living-in-sweden/housing</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Bristol صفحهٔ ایران: کارشناسی ۴ ساله با حداقل ۱۵/۲۰ از دانشگاه مورد تأیید</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>https://www.bristol.ac.uk/international/countries/iran.html</t>
+          <t>مسکن – Stockholm University: بدون تضمین؛ ≈ ۶۰۰ واحد برای بین‌المللی‌ها</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>https://medarbetare.su.se/en/education/first-and-second-level/internationalisation-for-students/housing-for-international-students</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – High Fliers «The Graduate Market in 2026»: دانشگاه‌های هدف کارفرمایان (Manchester، Birmingham، Nottingham، Warwick، UCL)؛ استخدام فارغ‌التحصیل در پایین‌ترین سطح از ۲۰۱۲</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>https://www.manchester.ac.uk/about/news/university-of-manchester-tops-uk-rankings-for-graduate-employer-interest/</t>
+          <t>مسکن – AAU Copenhagen: صریحاً بدون تضمین؛ KKIK/CIU DKK 3,500–6,000؛ خوابگاه 5,000–9,000</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/living-in-denmark/accommodation/international-students-in-copenhagen</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – LEO (DfE) درآمد ۵ سال بعد: Imperial Computing £79,600؛ Bristol Computing £70,300؛ میانهٔ کل بخش ≈ £31–34k (ثانویه: unilens/campusquant)</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>https://unilens.co.uk/insights/highest-graduate-earnings-uk-universities-2026</t>
+          <t>مسکن – AAU Aalborg: دفتر مسکن بین‌الملل، ۲۲۰+ واحد مبله، «تقریباً ۱۰۰٪ تضمین»، DKK 3,200–4,700 (ثانویه + بروشور AAU)</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>https://www.findunirooms.com/denmark/aalborg-university/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Appendix ATAS: ارشد آموزشی CS/AI نیاز به ATAS ندارد (فقط پژوهشی/PhD در CS و ارشد آموزشی فیزیک/مواد/مکانیک/هوافضا/شیمی)</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/guidance/immigration-rules/immigration-rules-appendix-atas-academic-technology-approval-scheme-atas</t>
+          <t>مسکن – York: تضمین PG تا ۳۱ ژوئیه؛ اجارهٔ 2026/27 £186–224/هفته (۵۱ هفته)</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/study/accommodation/postgraduate/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>بورس – LiU International Scholarship: معمولاً ۵۰٪؛ شرط جدید ۲۰۲۶ (GPA ≥ 3.5/4 یا first/high second class)؛ فقط اولویت ۱</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>https://liu.se/en/article/scholarships</t>
+          <t>مسکن – Essex: تضمین خوابگاه PG برای کل دوره با اقدام تا مهلت</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>https://www.essex.ac.uk/life/accommodation/apply/new-students/postgraduate</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>بورس – Chalmers: بورس‌های شهریه‌پردازها (IPOET ۷۵٪ با حداقل معدل ۸۰٪، Avancez)</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>https://www.chalmers.se/en/education/application-and-admission/scholarships-for-fee-paying-students/</t>
+          <t>مسکن – Brunel: تضمین برای همهٔ دانشجویان جدید؛ مهلت ۱۵ مارس ۲۰۲۶؛ پیش‌پرداخت £350/£450</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>https://www.brunel.ac.uk/life/accommodation/how-to-apply</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>بورس – Halmstad University Scholarship ۲۵٪/۵۰٪ برای غیر-EU (ثانویه؛ hh.se را چک کنید)</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>https://www.mastersportal.com/scholarships/10077/halmstad-university-scholarships.html</t>
+          <t>مسکن – Newcastle: فهرست خوابگاه‌های PG 2026/27 (£117.60–239.75/هفته)</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ncl.ac.uk/accommodation/university/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>بورس – MDU: بورس تا ۱۰۰٪ شهریه برای متقاضیان اولویت ۱ (ثانویه؛ mdu.se را چک کنید)</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>https://daadscholarship.com/malardalen-university-scholarships-2026-to-study-for-free-in-sweden/</t>
+          <t>مسکن – Northumbria: خوابگاه £94.19–158.31/هفته با قبوض؛ catered و self-catered؛ حداقل زندگی £1,015/ماه</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/postgraduate-study/pg-info-new/postgraduate-study-living-costs/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>بورس – SI Scholarship for Global Professionals: ۳۴ کشور واجد شرایط — ایران نیست (رسمی)</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>https://si.se/en/apply/scholarships/swedish-institute-scholarships-for-global-professionals/</t>
+          <t>مسکن – Durham: catered فقط برای کارشناسی (University College)؛ PG self-catered؛ راهنمای کالج PG</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>https://www.durham.ac.uk/colleges-and-student-experience/colleges/university/accommodation/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>بورس – NL Scholarship (سابقاً Holland Scholarship): €5,000 سال اول برای غیر-EEA، از طریق دانشگاه‌های عضو</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>https://www.mastersportal.com/scholarships/988/holland-scholarship-for-non-eea-international-students.html</t>
+          <t>مسکن – Durham قیمت 25/26: catered £10,233/سال، self-catered £7,146–7,801 (۳۹ هفته)، سهم غذا £3,087</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>https://www.palatinate.org.uk/college-accommodation-prices-increase-by-5/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>بورس – AAU: ≈ ۱۵ بورس دولتی در سال، معافیت شهریه + DKK 11,225/ماه (۲۰۲۶)، بررسی خودکار (رسمی)</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>https://www.en.aau.dk/education/apply/master/finance-and-fees</t>
+          <t>مسکن – Imperial: PG بدون تضمین؛ خوابگاه £210–410/هفته (۲۰۲۶)؛ طرح ضامن اجاره فقط UG/PhD؛ UCL طرح ضامن £50</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>https://www.harveywjames.com/news-imperial-college-rent-guarantee-scheme-london</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>بورس – ETH Excellence Scholarship &amp; Opportunity Programme: CHF 12,000/ترم + معافیت؛ ۱۰٪ بالای کلاس؛ ۱–۳۰ نوامبر</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>https://ethz.ch/en/studies/financial/scholarships/excellencescholarship.html</t>
+          <t>Russell Group – فهرست رسمی ۲۴ عضو (۲۰ در انگلستان)</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>https://russellgroup.ac.uk/about/our-universities/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>بورس – USI: بورس‌های Fondazione per le Facoltà di Lugano (CHF 4,000؛ سال اول با معدل ≥ ۸۰/۱۰۰؛ سال دوم بهترینِ هر برنامه) — خبر رسمی USI</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>https://www.eco.usi.ch/en/feeds/9861</t>
+          <t>انگلستان – Warwick: جدول رسمی تطبیق مدرک ایرانی (1st ۱۷/۲۰، 2:1 ۱۵/۲۰، 2:2 ۱۳/۲۰)</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>https://warwick.ac.uk/study/international/countryinformation/middleeast/iran/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>بورس – Essex Academic Excellence International Masters Scholarship: جدول کشوری (ایران ۱۴/۲۰ → £4,500؛ جدول ۲۰۲۵–۲۶)</t>
-        </is>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>https://www.essex.ac.uk/scholarships</t>
+          <t>انگلستان – Durham MSc Advanced Computer Science: £34,500 (2026)؛ جدول ایران (2:1 = ۱۴–۱۶/۲۰؛ Ecctis)</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>https://www.durham.ac.uk/study/courses/advanced-computer-science-g5t609/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>بورس – Teesside Global Excellence Scholarship £2,000 (پیشنهاد تا ۳۰ آوریل؛ رسمی)</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>https://www.tees.ac.uk/sections/international/global_excellence_scholarship.cfm</t>
+          <t>انگلستان – KCL: جدول رسمی ایران (First ۱۸، high 2:1 ۱۷، 2:1 ۱۵، high 2:2 ۱۳ از ۲۰)؛ Advanced Computing high 2:1، £40,450 (2026)</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/study-legacy/postgraduate/apply/entry-requirements/international</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>بورس – Brunel Vice-Chancellor's Postgraduate International Excellence Award £6,000 (حداقل 2:1؛ ودیعهٔ £5,000)</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>https://www.brunel.ac.uk/scholarships</t>
+          <t>انگلستان – Imperial MSc Computing (AI &amp; ML): First-class؛ £46,000 (2026/27)</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>https://www.imperial.ac.uk/study/courses/postgraduate-taught/computing-artificial-intelligence-msc/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>بورس – Northumbria PGT International Scholarship £3,000: فهرست کشوری/ادامه‌تحصیلی‌های داخل UK — ایران نیست</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>https://www.mastersportal.com/scholarships/3890/pgt-international-scholarships.html</t>
+          <t>انگلستان – UCL MSc Computer Science (تبدیلی): £42,700 (2026/27)، 2:1 در رشتهٔ غیر CS</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/prospective-students/graduate/taught-degrees/computer-science-msc-2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>بورس – Chevening eligibility (رسمی): ۲ سال کار بعد از مدرک کارشناسی + تعهد بازگشت ۲ ساله؛ مهلت ۶ اکتبر ۲۰۲۶</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>https://www.chevening.org/resource-hub/guidance/eligibility/</t>
+          <t>انگلستان – Bristol MSc Data Science: £37,900 (سپتامبر ۲۰۲۷)، strong 2:1 (۶۵٪)</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/study/postgraduate/taught/msc-data-science/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>بورس – Deutschlandstipendium €300/ماه (رسمی)</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>https://www.deutschlandstipendium.de/</t>
+          <t>انگلستان – Bristol صفحهٔ ایران: کارشناسی ۴ ساله با حداقل ۱۵/۲۰ از دانشگاه مورد تأیید</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/international/countries/iran.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – ETH: تاریخ‌های اپلای ارشد پاییز ۲۰۲۷ (۱–۳۰ نوامبر ۲۰۲۶؛ پاسخ تا پایان مارس؛ شروع ۲۰ سپتامبر ۲۰۲۷)</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
-        <is>
-          <t>https://ethz.ch/en/studies/master/application/dates.html</t>
+          <t>انگلستان – High Fliers «The Graduate Market in 2026»: دانشگاه‌های هدف کارفرمایان (Manchester، Birmingham، Nottingham، Warwick، UCL)؛ استخدام فارغ‌التحصیل در پایین‌ترین سطح از ۲۰۱۲</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>https://www.manchester.ac.uk/about/news/university-of-manchester-tops-uk-rankings-for-graduate-employer-interest/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EPFL: شهریه CHF 2,240/ترم برای خارجی‌های غیرمقیم از پاییز ۲۰۲۵ (CHF 780 برای بقیه)</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>https://www.epfl.ch/education/studies/en/rules-and-procedures/study-taxes/tuition-fee-other-fees/</t>
+          <t>انگلستان – LEO (DfE) درآمد ۵ سال بعد: Imperial Computing £79,600؛ Bristol Computing £70,300؛ میانهٔ کل بخش ≈ £31–34k (ثانویه: unilens/campusquant)</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>https://unilens.co.uk/insights/highest-graduate-earnings-uk-universities-2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EPFL: پنجره‌های اپلای ارشد (۱۵ دسامبر / ۳۱ مارس؛ یک برنامه در سال)</t>
-        </is>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>https://www.epfl.ch/education/admission/admission-2/master-admission-criteria-application/online-application/</t>
+          <t>انگلستان – Appendix ATAS: ارشد آموزشی CS/AI نیاز به ATAS ندارد (فقط پژوهشی/PhD در CS و ارشد آموزشی فیزیک/مواد/مکانیک/هوافضا/شیمی)</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/guidance/immigration-rules/immigration-rules-appendix-atas-academic-technology-approval-scheme-atas</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – UZH: شهریه CHF 720 + 100 (خارجی، ارشد) + 59؛ هزینهٔ درخواست CHF 150</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>https://www.uzh.ch/en/studies/application/fees.html</t>
+          <t>بورس – LiU International Scholarship: معمولاً ۵۰٪؛ شرط جدید ۲۰۲۶ (GPA ≥ 3.5/4 یا first/high second class)؛ فقط اولویت ۱</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>https://liu.se/en/article/scholarships</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – UZH: مهلت ویزایی‌ها ۲۸ فوریه / بدون ویزا ۳۰ آوریل (پاییز)</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>https://www.oec.uzh.ch/en/studies/general/admission/master/faq-master-admission.html</t>
+          <t>بورس – Chalmers: بورس‌های شهریه‌پردازها (IPOET ۷۵٪ با حداقل معدل ۸۰٪، Avancez)</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>https://www.chalmers.se/en/education/application-and-admission/scholarships-for-fee-paying-students/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI MSc Informatics: CHF 4,000/ترم غیرمقیم، B2 در ورود → C1، مهلت غیر-EU ۳۰ آوریل</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>https://www.usi.ch/en/education/master/informatics</t>
+          <t>بورس – Halmstad University Scholarship ۲۵٪/۵۰٪ برای غیر-EU (ثانویه؛ hh.se را چک کنید)</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mastersportal.com/scholarships/10077/halmstad-university-scholarships.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI MSc Artificial Intelligence: CHF 4,000/ترم، IELTS 6.5</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/usi-universita-della-svizzera-italiana/postgrad/master-science-artificial-intelligence</t>
+          <t>بورس – MDU: بورس تا ۱۰۰٪ شهریه برای متقاضیان اولویت ۱ (ثانویه؛ mdu.se را چک کنید)</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>https://daadscholarship.com/malardalen-university-scholarships-2026-to-study-for-free-in-sweden/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – swissuniversities: شهریهٔ دانشگاه‌های علوم کاربردی 2026–27 (ZHAW 1,220؛ HSLU 1,300؛ OST 1,500؛ FHNW 1,000–5,000)</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>https://www.swissuniversities.ch/en/themen/lehre-studium/information-on-studies/tuition-fees/tuition-fees-at-uas</t>
+          <t>بورس – SI Scholarship for Global Professionals: ۳۴ کشور واجد شرایط — ایران نیست (رسمی)</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>https://si.se/en/apply/scholarships/swedish-institute-scholarships-for-global-professionals/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – ZHAW MSE: انگلیسی، 90 ECTS، پروفایل‌های CS/Data Science/Cyber، معدل A/B، مهلت پایان آوریل</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
+          <t>بورس – NL Scholarship (سابقاً Holland Scholarship): €5,000 سال اول برای غیر-EEA، از طریق دانشگاه‌های عضو</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mastersportal.com/scholarships/988/holland-scholarship-for-non-eea-international-students.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – HSLU MSc Applied Information &amp; Data Science: C1 (B2 مشروط)، آلمانی لازم نیست، هر کارشناسی</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/haeufig-gestellte-fragen/</t>
+          <t>بورس – AAU: ≈ ۱۵ بورس دولتی در سال، معافیت شهریه + DKK 11,225/ماه (۲۰۲۶)، بررسی خودکار (رسمی)</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/apply/master/finance-and-fees</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Bern: Swiss Joint MSc Computer Science (90 ECTS، انگلیسی، شرط کارشناسی CS)</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="inlineStr">
-        <is>
-          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
+          <t>بورس – ETH Excellence Scholarship &amp; Opportunity Programme: CHF 12,000/ترم + معافیت؛ ۱۰٪ بالای کلاس؛ ۱–۳۰ نوامبر</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>https://ethz.ch/en/studies/financial/scholarships/excellencescholarship.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Bern شهریه از پاییز ۲۰۲۶: CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها + 34 + 25 در ترم (رسمی)</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="inlineStr">
-        <is>
-          <t>https://www.unibe.ch/studies/organizational_matters/renewal_of_semester_registration/fees/index_eng.html</t>
+          <t>بورس – USI: بورس‌های Fondazione per le Facoltà di Lugano (CHF 4,000؛ سال اول با معدل ≥ ۸۰/۱۰۰؛ سال دوم بهترینِ هر برنامه) — خبر رسمی USI</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>https://www.eco.usi.ch/en/feeds/9861</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Joint MSc CS (Bern/Neuchâtel/Fribourg) FAQ رسمی: بدون آزمون زبان (B2 توصیه)، شرط کارشناسی CS یا معادل با حداکثر ۶۰ ECTS تکمیلی، مهلت‌های دیرهنگام</t>
-        </is>
-      </c>
-      <c r="B79" s="16" t="inlineStr">
-        <is>
-          <t>https://mcs.unibnf.ch/faq/</t>
+          <t>بورس – Essex Academic Excellence International Masters Scholarship: جدول کشوری (ایران ۱۴/۲۰ → £4,500؛ جدول ۲۰۲۵–۲۶)</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>https://www.essex.ac.uk/scholarships</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Neuchâtel شهریهٔ خارجی‌ها CHF 790/ترم (رسمی)</t>
-        </is>
-      </c>
-      <c r="B80" s="16" t="inlineStr">
-        <is>
-          <t>https://www.unine.ch/admission/taxes-universitaires/</t>
+          <t>بورس – Teesside Global Excellence Scholarship £2,000 (پیشنهاد تا ۳۰ آوریل؛ رسمی)</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>https://www.tees.ac.uk/sections/international/global_excellence_scholarship.cfm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Neuchâtel مهلت ارشد ۳۰ آوریل؛ خارجی‌ها یک ماه زودتر؛ هزینهٔ پرونده CHF 100 (رسمی)</t>
-        </is>
-      </c>
-      <c r="B81" s="16" t="inlineStr">
-        <is>
-          <t>https://www.unine.ch/admission/admission-master/delais-et-frais-dinscription-pour-les-masters/</t>
+          <t>بورس – Brunel Vice-Chancellor's Postgraduate International Excellence Award £6,000 (حداقل 2:1؛ ودیعهٔ £5,000)</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>https://www.brunel.ac.uk/scholarships</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Fribourg شهریهٔ خارجی‌ها CHF 870 + 115 = 985/ترم (رسمی)</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="inlineStr">
-        <is>
-          <t>https://www.unifr.ch/studies/en/organisation/administrative-services-unifr-students/university-fees/</t>
+          <t>بورس – Northumbria PGT International Scholarship £3,000: فهرست کشوری/ادامه‌تحصیلی‌های داخل UK — ایران نیست</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mastersportal.com/scholarships/3890/pgt-international-scholarships.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Fribourg مهلت ارشد با مدرک خارجی: ویزایی‌ها ۱–۲۸ فوریه، بقیه تا ۳۰ آوریل (رسمی)</t>
-        </is>
-      </c>
-      <c r="B83" s="16" t="inlineStr">
-        <is>
-          <t>https://www.unifr.ch/studies/en/admission/admission-master/admission-master-foreign.html</t>
+          <t>بورس – Chevening eligibility (رسمی): ۲ سال کار بعد از مدرک کارشناسی + تعهد بازگشت ۲ ساله؛ مهلت ۶ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>https://www.chevening.org/resource-hub/guidance/eligibility/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Basel MSc CS: 90 ECTS، انگلیسی، مهلت ۳۰ آوریل / ۳۰ نوامبر (رسمی)</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
+          <t>بورس – Deutschlandstipendium €300/ماه (رسمی)</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>https://www.deutschlandstipendium.de/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Basel شهریه CHF 850/ترم برای همه + CHF 100 هزینهٔ درخواست (Uni Info 2026/27)</t>
-        </is>
-      </c>
-      <c r="B85" s="16" t="inlineStr">
-        <is>
-          <t>https://www.unibas.ch/dam/jcr:28672e66-8562-4988-9e38-b1c944ed22bf/COMPUTER%20SCIENCE%202026.2026-02-05-09-53-32.pdf</t>
+          <t>سوئیس – ETH: تاریخ‌های اپلای ارشد پاییز ۲۰۲۷ (۱–۳۰ نوامبر ۲۰۲۶؛ پاسخ تا پایان مارس؛ شروع ۲۰ سپتامبر ۲۰۲۷)</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>https://ethz.ch/en/studies/master/application/dates.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – HSLU MSc Applied Data Science and AI (نام جدید): مهلت ویزایی‌ها ۱ آوریل، CHF 1,300/ترم خارجی، CHF 250 درخواست، 120 ECTS (رسمی)</t>
-        </is>
-      </c>
-      <c r="B86" s="16" t="inlineStr">
-        <is>
-          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
+          <t>سوئیس – EPFL: شهریه CHF 2,240/ترم برای خارجی‌های غیرمقیم از پاییز ۲۰۲۵ (CHF 780 برای بقیه)</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>https://www.epfl.ch/education/studies/en/rules-and-procedures/study-taxes/tuition-fee-other-fees/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – USI مهلت‌های 2026/27: غیر-EU ۳۰ آوریل؛ هزینهٔ پرونده CHF 100 برای مدارک خارج از کنوانسیون لیسبون (رسمی)</t>
-        </is>
-      </c>
-      <c r="B87" s="16" t="inlineStr">
-        <is>
-          <t>https://www.usi.ch/en/education/master/informatics/application</t>
+          <t>سوئیس – EPFL: پنجره‌های اپلای ارشد (۱۵ دسامبر / ۳۱ مارس؛ یک برنامه در سال)</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>https://www.epfl.ch/education/admission/admission-2/master-admission-criteria-application/online-application/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
-        </is>
-      </c>
-      <c r="B88" s="16" t="inlineStr">
-        <is>
-          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
+          <t>سوئیس – UZH: شهریه CHF 720 + 100 (خارجی، ارشد) + 59؛ هزینهٔ درخواست CHF 150</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uzh.ch/en/studies/application/fees.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
-        </is>
-      </c>
-      <c r="B89" s="16" t="inlineStr">
-        <is>
-          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
+          <t>سوئیس – UZH: مهلت ویزایی‌ها ۲۸ فوریه / بدون ویزا ۳۰ آوریل (پاییز)</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>https://www.oec.uzh.ch/en/studies/general/admission/master/faq-master-admission.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
-        </is>
-      </c>
-      <c r="B90" s="16" t="inlineStr">
-        <is>
-          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
+          <t>سوئیس – USI MSc Informatics: CHF 4,000/ترم غیرمقیم، B2 در ورود → C1، مهلت غیر-EU ۳۰ آوریل</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>https://www.usi.ch/en/education/master/informatics</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
-        </is>
-      </c>
-      <c r="B91" s="16" t="inlineStr">
-        <is>
-          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
+          <t>سوئیس – USI MSc Artificial Intelligence: CHF 4,000/ترم، IELTS 6.5</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/usi-universita-della-svizzera-italiana/postgrad/master-science-artificial-intelligence</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
+          <t>سوئیس – swissuniversities: شهریهٔ دانشگاه‌های علوم کاربردی 2026–27 (ZHAW 1,220؛ HSLU 1,300؛ OST 1,500؛ FHNW 1,000–5,000)</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>https://www.swissuniversities.ch/en/themen/lehre-studium/information-on-studies/tuition-fees/tuition-fees-at-uas</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
-        </is>
-      </c>
-      <c r="B93" s="16" t="inlineStr">
-        <is>
-          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
+          <t>سوئیس – ZHAW MSE: انگلیسی، 90 ECTS، پروفایل‌های CS/Data Science/Cyber، معدل A/B، مهلت پایان آوریل</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>https://www.zhaw.ch/en/engineering/study/masters-degree-programme</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
-        </is>
-      </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
+          <t>سوئیس – HSLU MSc Applied Information &amp; Data Science: C1 (B2 مشروط)، آلمانی لازم نیست، هر کارشناسی</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-information-and-data-science/haeufig-gestellte-fragen/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
-        </is>
-      </c>
-      <c r="B95" s="16" t="inlineStr">
-        <is>
-          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
+          <t>سوئیس – Bern: Swiss Joint MSc Computer Science (90 ECTS، انگلیسی، شرط کارشناسی CS)</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>https://www.philnat.unibe.ch/studies/study_programs/master_s_in_computer_science/index_eng.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
+          <t>سوئیس – Bern شهریه از پاییز ۲۰۲۶: CHF 850 + 1,700 اضافهٔ غیرسوئیسی‌ها + 34 + 25 در ترم (رسمی)</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>https://www.unibe.ch/studies/organizational_matters/renewal_of_semester_registration/fees/index_eng.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
-        </is>
-      </c>
-      <c r="B97" s="16" t="inlineStr">
-        <is>
-          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
+          <t>سوئیس – Joint MSc CS (Bern/Neuchâtel/Fribourg) FAQ رسمی: بدون آزمون زبان (B2 توصیه)، شرط کارشناسی CS یا معادل با حداکثر ۶۰ ECTS تکمیلی، مهلت‌های دیرهنگام</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>https://mcs.unibnf.ch/faq/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
-        </is>
-      </c>
-      <c r="B98" s="16" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
+          <t>سوئیس – Neuchâtel شهریهٔ خارجی‌ها CHF 790/ترم (رسمی)</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>https://www.unine.ch/admission/taxes-universitaires/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
-        </is>
-      </c>
-      <c r="B99" s="16" t="inlineStr">
-        <is>
-          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
+          <t>سوئیس – Neuchâtel مهلت ارشد ۳۰ آوریل؛ خارجی‌ها یک ماه زودتر؛ هزینهٔ پرونده CHF 100 (رسمی)</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>https://www.unine.ch/admission/admission-master/delais-et-frais-dinscription-pour-les-masters/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
+          <t>سوئیس – Fribourg شهریهٔ خارجی‌ها CHF 870 + 115 = 985/ترم (رسمی)</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>https://www.unifr.ch/studies/en/organisation/administrative-services-unifr-students/university-fees/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
-        </is>
-      </c>
-      <c r="B101" s="16" t="inlineStr">
-        <is>
-          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
+          <t>سوئیس – Fribourg مهلت ارشد با مدرک خارجی: ویزایی‌ها ۱–۲۸ فوریه، بقیه تا ۳۰ آوریل (رسمی)</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>https://www.unifr.ch/studies/en/admission/admission-master/admission-master-foreign.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
+          <t>سوئیس – Basel MSc CS: 90 ECTS، انگلیسی، مهلت ۳۰ آوریل / ۳۰ نوامبر (رسمی)</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>https://dmi.unibas.ch/en/studies/computer-science/masters/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
-        </is>
-      </c>
-      <c r="B103" s="16" t="inlineStr">
-        <is>
-          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
+          <t>سوئیس – Basel شهریه CHF 850/ترم برای همه + CHF 100 هزینهٔ درخواست (Uni Info 2026/27)</t>
+        </is>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>https://www.unibas.ch/dam/jcr:28672e66-8562-4988-9e38-b1c944ed22bf/COMPUTER%20SCIENCE%202026.2026-02-05-09-53-32.pdf</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
-        </is>
-      </c>
-      <c r="B104" s="16" t="inlineStr">
-        <is>
-          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
+          <t>سوئیس – HSLU MSc Applied Data Science and AI (نام جدید): مهلت ویزایی‌ها ۱ آوریل، CHF 1,300/ترم خارجی، CHF 250 درخواست، 120 ECTS (رسمی)</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>https://www.hslu.ch/en/lucerne-school-of-business/degree-programmes/master/applied-data-science-and-ai/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
-        </is>
-      </c>
-      <c r="B105" s="16" t="inlineStr">
-        <is>
-          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
+          <t>سوئیس – USI مهلت‌های 2026/27: غیر-EU ۳۰ آوریل؛ هزینهٔ پرونده CHF 100 برای مدارک خارج از کنوانسیون لیسبون (رسمی)</t>
+        </is>
+      </c>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>https://www.usi.ch/en/education/master/informatics/application</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
-        </is>
-      </c>
-      <c r="B106" s="16" t="inlineStr">
-        <is>
-          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
+          <t>سوئیس – SEM FAQ: ۶ ماه جست‌وجوی کار برای فارغ‌التحصیلان؛ اولویت داخلی/EU؛ سهمیه</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>https://www.sem.admin.ch/sem/en/home/themen/arbeit/faq.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
-        </is>
-      </c>
-      <c r="B107" s="16" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
+          <t>سوئیس – سهمیهٔ ۲۰۲۶ اتباع غیر-EU: ۴,۵۰۰ B + ۴,۰۰۰ L؛ شرایط FNIA</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>https://goldblum.ch/knowledgebase/residence-permit-in-switzerland-obtain/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="inlineStr">
-        <is>
-          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
+          <t>سوئیس – Art. 21(3) FNIA: معافیت از آزمون بازار کار ولی نه از سهمیه؛ طرح 22.067 اجرا نشده</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>https://vshcherbakov.com/2025/06/26/Path-to-working-permit-for-Swiss-graduates/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
+          <t>سوئیس – اقامت تحصیلی ۲۰۲۶: CHF 21,000/سال، ۱۵ ساعت کار بعد از ۶ ماه، پردازش ۸–۱۲ هفته</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>https://www.study-abroad.org/blog/ch-student-visa-guide/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="inlineStr">
-        <is>
-          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
+          <t>سوئیس – کانتون زوریخ: تمکن فقط در بانک مستقر در سوئیس به نام خودتان یا ضامن مقیم (راهنمای ZHAW)</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>https://www.zhaw.ch/storage/sml/master/msc-bf-pie-information-for-international-students.pdf</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
-        </is>
-      </c>
-      <c r="B111" s="16" t="inlineStr">
-        <is>
-          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
+          <t>سوئیس – تفاوت کانتون‌ها: Basel CHF 24,000؛ زوریخ حساب سوئیسی</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>https://gradpilot.com/news/switzerland-student-visa-motivation-letter-canton-guide</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
-        </is>
-      </c>
-      <c r="B112" s="16" t="inlineStr">
-        <is>
-          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
+          <t>سوئیس – اجازهٔ C: ۱۰ سال برای اتباع کشور ثالث، A2 شفاهی/A1 کتبی؛ ۵ سال با B1</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>https://relofinder.ch/blog/swiss-c-permit-permanent-residence-2026-guide/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
-        </is>
-      </c>
-      <c r="B113" s="16" t="inlineStr">
-        <is>
-          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
+          <t>سوئیس – اجازهٔ C: احتساب سال‌های تحصیل و شرایط ادغام</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>https://www.richmondchambers.ch/post/swiss-c-permit-eligibility-required-years-of-residence-integration-expectations-and-fast-track-pa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="inlineStr">
-        <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
+          <t>سوئیس – سفارت تهران: ویزای D با وقت قبلی، ویزای C فعلاً نه (۳۰ ژانویه ۲۰۲۶)</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>https://www.eda.admin.ch/countries/iran/en/home.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="inlineStr">
-        <is>
-          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
+          <t>سوئیس – حقوق مهندس نرم‌افزار ۲۰۲۶ (جونیور CHF 85–105k؛ خالص زوریخ)</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>https://whatisthesalary.com/it-salaries/software-engineer-salary-in-switzerland/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
-        </is>
-      </c>
-      <c r="B116" s="16" t="inlineStr">
-        <is>
-          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
+          <t>سوئیس – Glassdoor: میانهٔ Junior Software Engineer زوریخ CHF 92k</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Salaries/z%C3%BCrich-junior-software-engineer-salary-SRCH_IL.0,6_IC3297851_KO7,31.htm</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
-        </is>
-      </c>
-      <c r="B117" s="16" t="inlineStr">
-        <is>
-          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
+          <t>سوئیس – بازهٔ حقوق زوریخ ۲۰۲۶ بر اساس نوع کارفرما</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>https://upreer.ch/en/salaries/software-engineer-salary-zurich/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>بریتانیا – وضعیت VAC تهران</t>
-        </is>
-      </c>
-      <c r="B118" s="16" t="inlineStr">
-        <is>
-          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
+          <t>سوئیس – هزینهٔ زندگی زوریخ CHF 2,000–2,200/ماه (UZH)</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>https://www.msfinance.uzh.ch/en/studyinginzurich/accommodation.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – TU Dresden</t>
-        </is>
-      </c>
-      <c r="B119" s="16" t="inlineStr">
-        <is>
-          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
+          <t>سوئیس – QS 2027: ETH 8، EPFL 22، UZH 98، Basel 150، Bern 191، USI 456، Fribourg 670، ZHAW 851–900</t>
+        </is>
+      </c>
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>https://www.iamexpat.ch/education/education-news/eth-zurich-makes-top-universities-world</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Stuttgart</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="inlineStr">
-        <is>
-          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
+          <t>سوئیس – رد ابتکار «سوئیس ۱۰ میلیونی» SVP در ۱۴ ژوئن ۲۰۲۶ (۵۴.۸٪ نه)</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>https://www.tagesanzeiger.ch/10-millionen-schweiz-resultate-der-svp-initiative-im-ticker-935664202454</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Newcastle 149</t>
-        </is>
-      </c>
-      <c r="B121" s="16" t="inlineStr">
-        <is>
-          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
+          <t>سوئیس – EP27: کاهش ۷۸ میلیون فرانک بودجهٔ ETH؛ سناریوی چهاربرابر شدن شهریهٔ خارجی‌ها</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>https://www.efd.admin.ch/de/entlastungspaket-27</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – York =158</t>
-        </is>
-      </c>
-      <c r="B122" s="16" t="inlineStr">
-        <is>
-          <t>https://www.york.ac.uk/about/rankings/</t>
+          <t>سوئیس – بازار IT ۲۰۲۶: استخدام گزینشی‌تر، بیکاری ≈ ۳.۲٪، کمبود ساختاری ICT</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>https://capiwell.ch/swiss-it-labour-market-2026-specialised-skills-slower-growth-and-new-openings-for-start-ups/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Leicester =314</t>
-        </is>
-      </c>
-      <c r="B123" s="16" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/university-leicester</t>
+          <t>نرخ CHF/USD ۲۷ سپتامبر ۲۰۲۶ (1.207)</t>
+        </is>
+      </c>
+      <c r="B123" s="17" t="inlineStr">
+        <is>
+          <t>https://www.xe.com/en-us/currencyconverter/convert/?Amount=1&amp;From=CHF&amp;To=USD</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Essex =438</t>
-        </is>
-      </c>
-      <c r="B124" s="16" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/essex-university</t>
+          <t>بریتانیا – Graduate visa ۱۸ ماه (از ژانویه ۲۰۲۷)</t>
+        </is>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
+        <is>
+          <t>https://students.leeds.ac.uk/visa-information-after-studies/doc/graduate-visas</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Northumbria =528</t>
-        </is>
-      </c>
-      <c r="B125" s="16" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
+          <t>بریتانیا – HC 584 (۳ سپتامبر ۲۰۲۶): تمکن £1,570 / £1,203 از ۳۰ نوامبر ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="B125" s="17" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/statement-of-changes-to-the-immigration-rules-hc-584-3-september-2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – Brunel</t>
-        </is>
-      </c>
-      <c r="B126" s="16" t="inlineStr">
-        <is>
-          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
+          <t>بریتانیا – Skilled Worker نرخ شغل SOC 2134 £54,700</t>
+        </is>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
+          <t>https://withrowan.co.uk/guides/skilled-worker-software-engineers</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>QS WUR 2027 – سایر</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/world-university-rankings</t>
+          <t>بریتانیا – Earned Settlement (وضعیت سپتامبر ۲۰۲۶)</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ukimmigration.law/earned-settlement-ilr-uk-plans/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr">
-        <is>
-          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
+          <t>انگلستان – Teesside MSc Computer Science 2026-27: £17,000، 2:2، IELTS 6.0</t>
+        </is>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t>https://www.tees.ac.uk/postgraduate_courses/computing_&amp;_cyber_security/msc_computer_science.cfm</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
-        </is>
-      </c>
-      <c r="B129" s="16" t="inlineStr">
-        <is>
-          <t>https://www.xe.com/</t>
+          <t>انگلستان – Northumbria MSc Advanced Computer Science 2026/27: £21,500، 2:2</t>
+        </is>
+      </c>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>https://www.northumbria.ac.uk/study-at-northumbria/courses/msc-advanced-computer-science-dtfava6/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
-        </is>
-      </c>
-      <c r="B130" s="16" t="inlineStr">
-        <is>
-          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
+          <t>انگلستان – Leicester MSc Advanced Computer Science سپتامبر ۲۰۲۶: £24,250، 2:1</t>
+        </is>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t>https://le.ac.uk/courses/advanced-computer-science-msc/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
-        </is>
-      </c>
-      <c r="B131" s="16" t="inlineStr">
-        <is>
-          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
+          <t>انگلستان – Essex MSc Advanced Computer Science 2026: £24,675، 2:2 (شامل Computer Engineering)</t>
+        </is>
+      </c>
+      <c r="B131" s="17" t="inlineStr">
+        <is>
+          <t>https://www.essex.ac.uk/courses/pg00435/1/msc-advanced-computer-science</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
-        </is>
-      </c>
-      <c r="B132" s="16" t="inlineStr">
-        <is>
-          <t>https://www.isc2.org/research</t>
+          <t>انگلستان – York MSc Advanced Computer Science 2026/27: £32,900، 2:2، IELTS 6.5</t>
+        </is>
+      </c>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-advanced-computer-science/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
-        </is>
-      </c>
-      <c r="B133" s="16" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
+          <t>انگلستان – Chester MSc Advanced Computer Science 2026/27: £15,500 (کف قیمت انگلستان)</t>
+        </is>
+      </c>
+      <c r="B133" s="17" t="inlineStr">
+        <is>
+          <t>https://www.chester.ac.uk/study/course-search/advanced-computer-science-msc/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
-        </is>
-      </c>
-      <c r="B134" s="16" t="inlineStr">
-        <is>
-          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
+          <t>بریتانیا – Brunel MSc AI 2026/27 £24,795</t>
+        </is>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t>https://www.brunel.ac.uk/study/courses/artificial-intelligence-msc</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
-        </is>
-      </c>
-      <c r="B135" s="16" t="inlineStr">
-        <is>
-          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
+          <t>بریتانیا – عوارض £925 به ازای هر دانشجوی بین‌المللی (انگلستان، از 2028-29)</t>
+        </is>
+      </c>
+      <c r="B135" s="17" t="inlineStr">
+        <is>
+          <t>https://www.researchprofessionalnews.com/rr-news-uk-politics-2025-11-international-levy-to-be-flat-fee-of-925-per-student/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
-        </is>
-      </c>
-      <c r="B136" s="16" t="inlineStr">
-        <is>
-          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
+          <t>بریتانیا – وضعیت VAC تهران</t>
+        </is>
+      </c>
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>https://livingintehran.com/2026/02/03/tehran-diplomatic-update-recent-embassy-reopenings-current-status-feb-2026/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
-        </is>
-      </c>
-      <c r="B137" s="16" t="inlineStr">
-        <is>
-          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
+          <t>QS WUR 2027 – TU Dresden</t>
+        </is>
+      </c>
+      <c r="B137" s="17" t="inlineStr">
+        <is>
+          <t>https://tu-dresden.de/tu-dresden/newsportal/news/qs-ranking-2027-tud-gehoert-erneut-zu-den-zehn-besten-universitaeten-deutschlands-und-baut-internationalen-erfolg-weiter-aus</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
-        </is>
-      </c>
-      <c r="B138" s="16" t="inlineStr">
-        <is>
-          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
+          <t>QS WUR 2027 – Stuttgart</t>
+        </is>
+      </c>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/university/news/all/QS-World-University-Rankings-2027-The-University-of-Stuttgart-is-recognized-for-its-strong-research-performance-and-commitment-to-sustainability/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Siegen MSc HCI (DAAD)</t>
-        </is>
-      </c>
-      <c r="B139" s="16" t="inlineStr">
-        <is>
-          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
+          <t>QS WUR 2027 – Newcastle 149</t>
+        </is>
+      </c>
+      <c r="B139" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ncl.ac.uk/press/articles/latest/2026/06/qs2027/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="inlineStr">
-        <is>
-          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
+          <t>QS WUR 2027 – York =158</t>
+        </is>
+      </c>
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/about/rankings/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>آلمان – RWTH MSc Software Systems Engineering</t>
-        </is>
-      </c>
-      <c r="B141" s="16" t="inlineStr">
-        <is>
-          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
+          <t>QS WUR 2027 – Leicester =314</t>
+        </is>
+      </c>
+      <c r="B141" s="17" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/university-leicester</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
-        </is>
-      </c>
-      <c r="B142" s="16" t="inlineStr">
-        <is>
-          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
+          <t>QS WUR 2027 – Essex =438</t>
+        </is>
+      </c>
+      <c r="B142" s="17" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/essex-university</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
-        </is>
-      </c>
-      <c r="B143" s="16" t="inlineStr">
-        <is>
-          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
+          <t>QS WUR 2027 – Northumbria =528</t>
+        </is>
+      </c>
+      <c r="B143" s="17" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/northumbria-university-newcastle</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="inlineStr">
-        <is>
-          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
+          <t>QS WUR 2027 – Brunel</t>
+        </is>
+      </c>
+      <c r="B144" s="17" t="inlineStr">
+        <is>
+          <t>https://students.brunel.ac.uk/campus-news/brunel-climbs-global-qs-rankings-after-strong-year-for-research-and-graduate-outcomes</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
-        </is>
-      </c>
-      <c r="B145" s="16" t="inlineStr">
-        <is>
-          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
+          <t>QS WUR 2027 – سایر</t>
+        </is>
+      </c>
+      <c r="B145" s="17" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/world-university-rankings</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>هلند – Leiden CS 2026/27: €22,500</t>
-        </is>
-      </c>
-      <c r="B146" s="16" t="inlineStr">
-        <is>
-          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
+          <t>حداقل دستمزد ۲۰۲۶ هلند (€14.71)</t>
+        </is>
+      </c>
+      <c r="B146" s="17" t="inlineStr">
+        <is>
+          <t>https://arlettipartners.com/new-increase-in-the-dutch-minimum-hourly-wage-from-january-1st-2026/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>هلند – Groningen AI 2026/27: €24,900</t>
-        </is>
-      </c>
-      <c r="B147" s="16" t="inlineStr">
-        <is>
-          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
+          <t>نرخ ارز (xe.com، ۲۷ سپتامبر ۲۰۲۶)</t>
+        </is>
+      </c>
+      <c r="B147" s="17" t="inlineStr">
+        <is>
+          <t>https://www.xe.com/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="inlineStr">
-        <is>
-          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
+          <t>بازار کار – LinkedIn/WEF ژانویه ۲۰۲۶: ۱.۳ میلیون شغل جدید AI؛ AI Engineer سریع‌ترین‌رشد</t>
+        </is>
+      </c>
+      <c r="B148" s="17" t="inlineStr">
+        <is>
+          <t>https://www.weforum.org/stories/jobs-and-the-future-of-work/ai-has-already-added-1-3-million-new-jobs-according-to-linkedin-data/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
-        </is>
-      </c>
-      <c r="B149" s="16" t="inlineStr">
-        <is>
-          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
+          <t>بازار کار – Bitkom 2025: ۱۰۹ هزار جای خالی IT در آلمان، ۷.۷ ماه زمان پرکردن</t>
+        </is>
+      </c>
+      <c r="B149" s="17" t="inlineStr">
+        <is>
+          <t>https://www.bitkom.org/Bitkom/Publikationen/Der-Arbeitsmarkt-fuer-IT-Fachkraefte</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="inlineStr">
-        <is>
-          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
+          <t>بازار کار – ISC2 Cybersecurity Workforce Study 2024/2025 (حذف عدد کمبود؛ کمبود بودجه دلیل اول؛ ۳۱٪ تیم‌ها بدون جونیور)</t>
+        </is>
+      </c>
+      <c r="B150" s="17" t="inlineStr">
+        <is>
+          <t>https://www.isc2.org/research</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
-        </is>
-      </c>
-      <c r="B151" s="16" t="inlineStr">
-        <is>
-          <t>https://www.kth.se/en/studies/master/machine-learning</t>
+          <t>بازار کار – اخراج‌های صنعت بازی ۲۰۲۲–۲۰۲۶ (≈۴۵ هزار؛ افت حقوق Unity)</t>
+        </is>
+      </c>
+      <c r="B151" s="17" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2022%E2%80%932026_video_game_industry_layoffs</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Umeå AI: SEK 152,300</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="inlineStr">
-        <is>
-          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
+          <t>بازار کار – آگهی‌های UX/UXR (Indeed تا Q4 2025)</t>
+        </is>
+      </c>
+      <c r="B152" s="17" t="inlineStr">
+        <is>
+          <t>https://www.thevoiceofuser.com/everyone-knows-the-uxr-hiring-market-is-bad-how-bad-is-it-though/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
-        </is>
-      </c>
-      <c r="B153" s="16" t="inlineStr">
-        <is>
-          <t>https://www.study.eu/best-universities/sweden</t>
+          <t>بازار کار – اشباع جونیور علم داده ۲۰۲۶</t>
+        </is>
+      </c>
+      <c r="B153" s="17" t="inlineStr">
+        <is>
+          <t>https://research.com/advice/are-too-many-students-choosing-data-science-oversaturation-competition-hiring-reality</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
-        </is>
-      </c>
-      <c r="B154" s="16" t="inlineStr">
-        <is>
-          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
+          <t>آلمان – Saarland MSc Cybersecurity (C1، بدون شهریه)</t>
+        </is>
+      </c>
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uni-saarland.de/en/study/programmes/master/cybersecurity.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
-        </is>
-      </c>
-      <c r="B155" s="16" t="inlineStr">
-        <is>
-          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
+          <t>آلمان – Passau MSc AI Engineering (B2، معدل ≤ 2.7، A1 آلمانی سال اول)</t>
+        </is>
+      </c>
+      <c r="B155" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/msc-ai-eng</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
-        </is>
-      </c>
-      <c r="B156" s="16" t="inlineStr">
-        <is>
-          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
+          <t>آلمان – Cologne Game Lab MA Game Development &amp; Research (€2,500/ترم غیر-EU)</t>
+        </is>
+      </c>
+      <c r="B156" s="17" t="inlineStr">
+        <is>
+          <t>https://colognegamelab.de/study-programs/post-graduate-programs/game-development-research-ma/faqs/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus CS €17,300</t>
-        </is>
-      </c>
-      <c r="B157" s="16" t="inlineStr">
-        <is>
-          <t>https://masters.au.dk/computerscience</t>
+          <t>آلمان – Siegen MSc HCI (DAAD)</t>
+        </is>
+      </c>
+      <c r="B157" s="17" t="inlineStr">
+        <is>
+          <t>https://www2.daad.de/deutschland/studienangebote/international-programmes/en/detail/4686/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
-        </is>
-      </c>
-      <c r="B158" s="16" t="inlineStr">
-        <is>
-          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
+          <t>آلمان – H-BRS MSc Autonomous Systems (B2+)</t>
+        </is>
+      </c>
+      <c r="B158" s="17" t="inlineStr">
+        <is>
+          <t>https://www.h-brs.de/en/inf/admission-application-master-autonomous-systems</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
-        </is>
-      </c>
-      <c r="B159" s="16" t="inlineStr">
-        <is>
-          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
+          <t>آلمان – RWTH MSc Software Systems Engineering</t>
+        </is>
+      </c>
+      <c r="B159" s="17" t="inlineStr">
+        <is>
+          <t>https://sc.informatik.rwth-aachen.de/en/studium/master/sse/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
-        </is>
-      </c>
-      <c r="B160" s="16" t="inlineStr">
-        <is>
-          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
+          <t>آلمان – Tübingen MSc Machine Learning (IELTS 7، €1,500/ترم)</t>
+        </is>
+      </c>
+      <c r="B160" s="17" t="inlineStr">
+        <is>
+          <t>https://uni-tuebingen.de/fakultaeten/mathematisch-naturwissenschaftliche-fakultaet/fachbereiche/informatik/studium/studierende/lehre-studienorganisation/studiengaenge/machine-learning/admission-and-application/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
-        </is>
-      </c>
-      <c r="B161" s="16" t="inlineStr">
-        <is>
-          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
+          <t>آلمان – TUM Informatics: €6,000 در ترم برای غیر-EU</t>
+        </is>
+      </c>
+      <c r="B161" s="17" t="inlineStr">
+        <is>
+          <t>https://www.tum.de/en/studies/degree-programs/detail/informatics-master-of-science-msc</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
-        </is>
-      </c>
-      <c r="B162" s="16" t="inlineStr">
-        <is>
-          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
+          <t>آلمان – FAU Autonomy Technologies (B2، IELTS 6.0)</t>
+        </is>
+      </c>
+      <c r="B162" s="17" t="inlineStr">
+        <is>
+          <t>https://www.fau.eu/degree-program/autonomy-technologies-m-sc/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
-        </is>
-      </c>
-      <c r="B163" s="16" t="inlineStr">
-        <is>
-          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
+          <t>هلند – Twente Embedded Systems 2026/27: €21,700</t>
+        </is>
+      </c>
+      <c r="B163" s="17" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/education/master/programmes/embedded-systems/finance/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
-        </is>
-      </c>
-      <c r="B164" s="16" t="inlineStr">
-        <is>
-          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
+          <t>هلند – Leiden CS 2026/27: €22,500</t>
+        </is>
+      </c>
+      <c r="B164" s="17" t="inlineStr">
+        <is>
+          <t>https://www.universiteitleiden.nl/en/education/study-programmes/master/computer-science/artificial-intelligence/admission-and-application/tuition-fees</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – NTU QS 2027 =639</t>
-        </is>
-      </c>
-      <c r="B165" s="16" t="inlineStr">
-        <is>
-          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
+          <t>هلند – Groningen AI 2026/27: €24,900</t>
+        </is>
+      </c>
+      <c r="B165" s="17" t="inlineStr">
+        <is>
+          <t>https://www.rug.nl/masters/artificial-intelligence/?lang=en</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
-        </is>
-      </c>
-      <c r="B166" s="16" t="inlineStr">
-        <is>
-          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
+          <t>هلند – Utrecht Game &amp; Media Technology 2026/27: €25,306</t>
+        </is>
+      </c>
+      <c r="B166" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uu.nl/en/masters/game-and-media-technology</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
-        </is>
-      </c>
-      <c r="B167" s="16" t="inlineStr">
-        <is>
-          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
+          <t>هلند – QS 2027 فهرست دانشگاه‌های هلند</t>
+        </is>
+      </c>
+      <c r="B167" s="17" t="inlineStr">
+        <is>
+          <t>https://dub.uu.nl/en/news/dutch-universities-fall-global-qs-rankings</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
-        </is>
-      </c>
-      <c r="B168" s="16" t="inlineStr">
-        <is>
-          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
+          <t>سوئد – Gothenburg Game Design &amp; Technology: SEK 290,000 کل</t>
+        </is>
+      </c>
+      <c r="B168" s="17" t="inlineStr">
+        <is>
+          <t>https://www.gu.se/en/study-gothenburg/game-design-technology-masters-programme-n2gdt</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
-        </is>
-      </c>
-      <c r="B169" s="16" t="inlineStr">
-        <is>
-          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+          <t>سوئد – KTH Machine Learning: ≈ SEK 180,000–190,000 (کل دوره 360k طبق راهنمای ۲۰۲۶؛ kth.se رقم را فقط در سامانه نشان می‌دهد)</t>
+        </is>
+      </c>
+      <c r="B169" s="17" t="inlineStr">
+        <is>
+          <t>https://www.kth.se/en/studies/master/machine-learning</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
-        </is>
-      </c>
-      <c r="B170" s="16" t="inlineStr">
-        <is>
-          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+          <t>سوئد – Umeå AI: SEK 152,300</t>
+        </is>
+      </c>
+      <c r="B170" s="17" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/master/masters-programme-in-artificial-intelligence/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
-        </is>
-      </c>
-      <c r="B171" s="16" t="inlineStr">
-        <is>
-          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+          <t>سوئد – QS 2027 فهرست دانشگاه‌های سوئد</t>
+        </is>
+      </c>
+      <c r="B171" s="17" t="inlineStr">
+        <is>
+          <t>https://www.study.eu/best-universities/sweden</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
-        </is>
-      </c>
-      <c r="B172" s="16" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+          <t>دانمارک – ITU شهریهٔ رسمی ورودی ۲۰۲۶: €8,250 در ترم = €16,500 در سال (رقم قدیمی €6,700 منسوخ)</t>
+        </is>
+      </c>
+      <c r="B172" s="17" t="inlineStr">
+        <is>
+          <t>https://en.itu.dk/Programmes/MSc-Programmes/Applying-to-a-MSc-programme/Non-EU-EOES</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
-        </is>
-      </c>
-      <c r="B173" s="16" t="inlineStr">
-        <is>
-          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+          <t>دانمارک – AAU Cyber Security / Medialogy €7,455 در ترم</t>
+        </is>
+      </c>
+      <c r="B173" s="17" t="inlineStr">
+        <is>
+          <t>https://studyindenmark.dk/portal/aalborg-university-aau/copenhagen/cyber-security-msc-in-engineering</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
-        </is>
-      </c>
-      <c r="B174" s="16" t="inlineStr">
-        <is>
-          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+          <t>دانمارک – DTU €15,000 (Human-Centered AI / Autonomous Systems)</t>
+        </is>
+      </c>
+      <c r="B174" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dtu.dk/english/education/graduate/msc-programmes/autonomous-systems/prerequisites</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
-        </is>
-      </c>
-      <c r="B175" s="16" t="inlineStr">
-        <is>
-          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+          <t>دانمارک – Aarhus CS €17,300</t>
+        </is>
+      </c>
+      <c r="B175" s="17" t="inlineStr">
+        <is>
+          <t>https://masters.au.dk/computerscience</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
-        </is>
-      </c>
-      <c r="B176" s="16" t="inlineStr">
-        <is>
-          <t>https://zandienglish.ir/toefl-in-iran/</t>
+          <t>دانمارک – QS 2027 فهرست دانشگاه‌های دانمارک</t>
+        </is>
+      </c>
+      <c r="B176" s="17" t="inlineStr">
+        <is>
+          <t>https://leapscholar.com/blog/top-universities-in-denmark/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
-        </is>
-      </c>
-      <c r="B177" s="16" t="inlineStr">
-        <is>
-          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+          <t>انگلستان – Goldsmiths MSc Computer Games Programming £22,000</t>
+        </is>
+      </c>
+      <c r="B177" s="17" t="inlineStr">
+        <is>
+          <t>https://www.gold.ac.uk/pg/msc-computer-games-programming/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
-        </is>
-      </c>
-      <c r="B178" s="16" t="inlineStr">
-        <is>
-          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+          <t>انگلستان – Royal Holloway MSc Information &amp; Cyber Security £25,500</t>
+        </is>
+      </c>
+      <c r="B178" s="17" t="inlineStr">
+        <is>
+          <t>https://www.royalholloway.ac.uk/studying-here/postgraduate/information-security/information-and-cyber-security/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
-        </is>
-      </c>
-      <c r="B179" s="16" t="inlineStr">
-        <is>
-          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+          <t>انگلستان – Kent MSc Cyber Security (NCSC)</t>
+        </is>
+      </c>
+      <c r="B179" s="17" t="inlineStr">
+        <is>
+          <t>https://www.kent.ac.uk/courses/postgraduate/1225/cyber-security</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
-        </is>
-      </c>
-      <c r="B180" s="16" t="inlineStr">
-        <is>
-          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+          <t>انگلستان – MMU MSc Cyber Security £21,000</t>
+        </is>
+      </c>
+      <c r="B180" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mmu.ac.uk/study/postgraduate/course/msc-cyber-security</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
-        </is>
-      </c>
-      <c r="B181" s="16" t="inlineStr">
-        <is>
-          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+          <t>انگلستان – York MSc Human-Centred Interactive Technologies £32,900</t>
+        </is>
+      </c>
+      <c r="B181" s="17" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk/study/postgraduate-taught/courses/msc-human-centred-interactive-technologies/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
-        </is>
-      </c>
-      <c r="B182" s="16" t="inlineStr">
-        <is>
-          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+          <t>انگلستان – Lancaster MSc Cyber Security £30,000</t>
+        </is>
+      </c>
+      <c r="B182" s="17" t="inlineStr">
+        <is>
+          <t>https://www.lancaster.ac.uk/study/postgraduate/postgraduate-courses/cyber-security-msc/2026/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
-        </is>
-      </c>
-      <c r="B183" s="16" t="inlineStr">
-        <is>
-          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+          <t>انگلستان – NTU QS 2027 =639</t>
+        </is>
+      </c>
+      <c r="B183" s="17" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/uk/university/862-nottingham-trent-university-nottingham/ranking</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
+          <t>آلمان – FAU: شهریهٔ غیر-EU از ترم تابستان ۲۰۲۷ (AI/CS €4,000، Autonomy Tech €2,000 در ترم؛ BayHIG §13)</t>
+        </is>
+      </c>
+      <c r="B184" s="17" t="inlineStr">
+        <is>
+          <t>https://www.fau.eu/studying/international-students/application-and-enrollment-for-international-applicants/tuition-fees-for-students-from-non-eu-states/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau: «فعلاً» بدون شهریه برای غیر-EU (اعلام رسمی)</t>
+        </is>
+      </c>
+      <c r="B185" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/study/news/news/no-tuition-fees-for-international-students-at-the-university-of-passau</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – Aarhus نرخ رسمی 2026/27: Computer Science / Data Science / Computer Engineering €17,300</t>
+        </is>
+      </c>
+      <c r="B186" s="17" t="inlineStr">
+        <is>
+          <t>https://masters.au.dk/tuitionfees/current-tuition-fee-rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU Computer Science (IT): شرط رسمی ≥ ۱۵۰ ECTS دروس CS؛ معیار رتبه‌بندی ۲۰۲۷ شامل سابقهٔ کار</t>
+        </is>
+      </c>
+      <c r="B187" s="17" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/master/computer-science-it</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – Chalmers شهریهٔ استاندارد 2026/27 ≈ SEK 175,000 (collegedunia به نقل از صفحهٔ شهریهٔ Chalmers)</t>
+        </is>
+      </c>
+      <c r="B188" s="17" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/sweden/university/769-chalmers-university-of-technology-gothenburg/programs?stream_id=48&amp;degree_type=Master</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Surrey MSc Cyber Security ورودی ۲۰۲۷: £25,900 (فوریه) / £26,900 (سپتامبر)</t>
+        </is>
+      </c>
+      <c r="B189" s="17" t="inlineStr">
+        <is>
+          <t>https://www.surrey.ac.uk/postgraduate/cyber-security-msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان – Newcastle MSc Computer Game Engineering £32,300، شرط 2:2 (QS TopUniversities)</t>
+        </is>
+      </c>
+      <c r="B190" s="17" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/newcastle-university/postgrad/msc-computer-game-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>هلند – TU/e شهریهٔ رسمی 2026/27 €21,700 (2027/28: €22,400)</t>
+        </is>
+      </c>
+      <c r="B191" s="17" t="inlineStr">
+        <is>
+          <t>https://www.tue.nl/en/education/become-a-tue-student/tuition-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف برگزاری IELTS در ایران از ۳۱ ژانویه ۲۰۲۶ (اعلام IDP)</t>
+        </is>
+      </c>
+      <c r="B192" s="17" t="inlineStr">
+        <is>
+          <t>https://wanaen.com/ielts-testing-to-be-suspended-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وضعیت IELTS شهریور ۱۴۰۵: در ایران برگزار نمی‌شود؛ آزمون در کشور دیگر</t>
+        </is>
+      </c>
+      <c r="B193" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jahantahsil.com/%D8%A2%D8%B2%D9%85%D9%88%D9%86-%D8%A2%DB%8C%D9%84%D8%AA%D8%B3-ielts-%DA%86%DB%8C%D8%B3%D8%AA-%D9%88-%DA%A9%D8%AC%D8%A7-%D8%A8%D8%B1%DA%AF%D8%B2%D8%A7%D8%B1-%D9%85%DB%8C%D8%B4%D9%88%D8%AF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>ایران – توقف TOEFL در ایران (وضعیت شهریور ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B194" s="17" t="inlineStr">
+        <is>
+          <t>https://zandienglish.ir/toefl-in-iran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>ایران – وثیقهٔ خروج تحصیلی مشمولان ۲۰۰ میلیون تومان (سامانهٔ سخا، تیر ۱۴۰۵)</t>
+        </is>
+      </c>
+      <c r="B195" s="17" t="inlineStr">
+        <is>
+          <t>https://www.zoomit.ir/iran-news/464136-exit-permit-bond-sakha-1405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>سوئد – تاریخ‌های کلیدی ورودی پاییز ۲۰۲۷ (۱۶ اکتبر – ۱۵ ژانویه؛ مدارک ۱ فوریه؛ دور دوم ۱۵ آوریل)</t>
+        </is>
+      </c>
+      <c r="B196" s="17" t="inlineStr">
+        <is>
+          <t>https://www.umu.se/en/education/application-and-admission/key-dates-and-deadlines/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Stuttgart MSc CS: بازهٔ اپلای ترم زمستان ۱۵ نوامبر – ۱۵ ژانویه؛ انگلیسی C1</t>
+        </is>
+      </c>
+      <c r="B197" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/en/study/study-programs/Computer-Science-M.Sc.-00001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>آلمان – Passau: بازهٔ اپلای AI Engineering ۱ آوریل – ۳۱ می</t>
+        </is>
+      </c>
+      <c r="B198" s="17" t="inlineStr">
+        <is>
+          <t>https://www.uni-passau.de/en/apply/apply-with-intl-qualifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – AAU: مهلت شهریه‌پردازها ۱۵ ژانویه (EU: ۱ مارس)؛ پورتال از اواسط دسامبر</t>
+        </is>
+      </c>
+      <c r="B199" s="17" t="inlineStr">
+        <is>
+          <t>https://www.en.aau.dk/education/apply/master/how-and-when-to-apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>دانمارک – SDU Computer Science: مهلت غیر-EU ۱ فوریه؛ شهریه یک سال پیش‌پرداخت</t>
+        </is>
+      </c>
+      <c r="B200" s="17" t="inlineStr">
+        <is>
+          <t>https://www.sdu.dk/en/uddannelse/kandidat/datalogi</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>هلند – Radboud: مهلت غیر-EU ۱ آوریل، بورس ۳۱ ژانویه، ثبت‌نام ۱ ژوئن</t>
+        </is>
+      </c>
+      <c r="B201" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/en/education/application-and-admission/application-procedure-masters/deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
           <t>هلند – Twente: مهلت غیر-EEA ۱ می ۲۰۲۷؛ بورس UTS ۱۵ اکتبر ۲۰۲۶ – ۱ آوریل ۲۰۲۷</t>
         </is>
       </c>
-      <c r="B184" s="16" t="inlineStr">
+      <c r="B202" s="17" t="inlineStr">
         <is>
           <t>https://collegedunia.com/netherlands/university/749-university-of-twente-enschede/admission</t>
         </is>
@@ -15286,6 +17107,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId201"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -12721,7 +12721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14268,48 +14268,524 @@
       </c>
       <c r="I36" s="4" t="n"/>
     </row>
-    <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="14" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>شهر / کشور</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>خوابگاه استاندارد (حمام مشترک) — سالانه</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>خوابگاه en-suite — سالانه</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>اتاق در خانهٔ مشترک خصوصی — سالانه (+ قبوض ≈ £80/ماه)</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>en-suite در برابر اتاق خصوصی</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>استاندارد در برابر en-suite (پول حمام اختصاصی)</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>نکته</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="n"/>
+      <c r="I38" s="1" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Newcastle / Middlesbrough (Northumbria، Newcastle، Teesside)</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>£94–118/هفته × ۵۱ = £4,800–6,000 (رسمی Northumbria £94.19، Newcastle £117.60)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>£140–190/هفته × ۵۱ = £7,100–9,700</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>£450–650/ماه × ۱۲ + £960 = £6,400–8,800 (+ ضامن ≈ £1,650 اگر لازم شود)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>≈ برابر (−£1,000 تا +£1,700)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>استاندارد £2,300–3,700 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>ارزان‌ترین راه واقعی: اتاق استاندارد ۵۱ هفته‌ای ≈ £4,900 با همهٔ قبوض</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>York (اعداد رسمی PG 2026/27)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>£186 × ۵۱ = £9,486</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>£206 × ۵۱ = £10,506</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>£550–750/ماه × ۱۲ + £960 = £7,560–9,960</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>❌ en-suite £500–2,900 گران‌تر از اتاق خصوصی</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>استاندارد £1,020 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>York خوابگاه گران دارد؛ مزیتش تضمین و بی‌ضامنی است، نه قیمت</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Colchester (Essex)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>≈ £115–140 × ۴۰–۵۱ = £4,600–7,100</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>≈ £160–200 × ۴۰–۵۱ = £6,400–10,200</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>£550–700/ماه × ۱۲ + £960 = £7,560–9,360</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>≈ برابر</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>استاندارد £1,800–3,000 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>قرارداد ۴۰ هفته‌ای برای ارشد ۱۲ ماهه کافی نیست → ۸–۱۲ هفتهٔ تابستان جدا</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Uxbridge (Brunel) — غرب لندن</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>≈ £150–170 × ۴۰–۵۰ = £6,000–8,500</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>≈ £190–240 × ۴۰–۵۰ = £7,600–12,000</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>£900–1,200/ماه × ۱۲ + £1,200 = £12,000–15,600</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>✅ en-suite £2,000–5,000 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>استاندارد £1,600–3,500 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>در لندن و حومه خوابگاه دانشگاه واقعاً می‌صرفد + تضمین Brunel (مهلت ۱۵ مارس)</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Durham (کالج، PG self-catered)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>£183 × ۳۹ = £7,146 + ۱۳ هفته تابستان ≈ £1,950 = £9,100</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>£200 × ۳۹ = £7,801 + تابستان ≈ £1,950 = £9,750</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>£550–700/ماه × ۱۲ + £960 = £7,560–9,360</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>≈ برابر تا £2,000 گران‌تر</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>استاندارد £650 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>قرارداد ۳۹ هفته‌ای دورهام برای ارشد ۱۲ ماهه مشکل‌ساز است</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>London مرکز (UCL / KCL / Imperial)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>£210–250 × ۴۰–۵۱ = £8,400–12,750</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>£260–350 × ۴۰–۵۱ = £10,400–17,850</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>£1,000–1,400/ماه × ۱۲ + £1,200 = £13,200–18,000 (+ ضامن)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>✅ £0–3,000 ارزان‌تر (اگر گیرتان بیاید — PG بدون تضمین)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>استاندارد £2,000–5,000 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>در لندن هر دو گران‌اند؛ تفاوت اصلی «ضامن نخواستن» خوابگاه است</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>آلمان (Studierendenwerk در برابر WG)</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>€230–450/ماه با قبوض = €2,800–5,400</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>— (خوابگاه‌های آلمان معمولاً حمام مشترک یا آپارتمان تک‌نفره)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>€450–700 + €80 قبوض = €6,400–9,400</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>✅ خوابگاه €1,500–4,500 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>بزرگ‌ترین صرفه‌جویی نسبی — ولی لیست انتظار</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>هلند (اتاق رزروشده در برابر بازار)</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>€370–650 = €4,400–7,800</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>€600–1,000 = €7,200–12,000</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>✅ €1,500–4,000 ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>اتاق رزروشده فقط سال اول و بدون تضمین</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>سوئد (کریدوری در برابر خصوصی)</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>SEK 3,500–6,500 = SEK 42–78k</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>SEK 5,000–8,000 (+ برق) = SEK 62–100k</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>✅ SEK 15–25k ارزان‌تر (≈ $1,500–2,500)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Uppsala/LiU تضمین؛ استکهلم صف</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>دانمارک (kollegium در برابر خصوصی)</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>DKK 3,200–4,700 = DKK 38–56k</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>DKK 4,500–7,000 = DKK 54–84k</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>✅ DKK 15–30k ارزان‌تر (≈ $2,300–4,600)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Aalborg تضمین؛ کپنهاگ نه</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>سوئیس (WOKO/FMEL در برابر WG)</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>CHF 480–900 = CHF 5,800–10,800</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>CHF 700–1,200 = CHF 8,400–14,400</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>✅ CHF 2,500–5,000 ارزان‌تر (≈ $3,000–6,000)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>بزرگ‌ترین صرفه‌جویی مطلق — ولی زوریخ ۳–۱۲ ماه صف</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>پاسخ کوتاه به «انگلیس خوابگاه با ناهار و شام می‌دهد»: بله، «catered halls» وجود دارد (معمولاً صبحانه + شام، در Durham سه وعده)، ولی (۱) تقریباً همه‌جا فقط برای سال اول کارشناسی است و برای ارشد فقط چند جا (Durham، Northumbria، بعضی کالج‌های Bristol)، (۲) فقط در هفته‌های ترم (≈ ۳۰ هفته) غذا می‌دهند، (۳) هیچ‌جا داخل شهریه نیست — Durham ≈ £3,087 در سال برای غذا جدا می‌گیرد و اجارهٔ catered ≈ £262/هفته است.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>• در هیچ‌یک از ۶ کشور خوابگاه داخل شهریه نیست. ارزان‌ترین خوابگاه‌ها: آلمان (€230–450 با قبوض) و شهرهای کوچک سوئد/دانمارک؛ گران‌ترین: لندن (£900–1,800/ماه) و زوریخ (CHF 700–1,200 اتاق).</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>• تضمین واقعی برای دانشجوی ارشد بین‌المللی فقط در: Uppsala، LiU (یک پیشنهاد)، AAU Aalborg، و دانشگاه‌های انگلستان با مهلت (York ۳۱ ژوئیه، Essex، Brunel ۱۵ مارس، احتمالاً Teesside/Northumbria/Newcastle/Sheffield/Lancaster). آلمان، هلند، سوئیس و لندن: هیچ تضمینی.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>• برای ایرانی‌ها: خوابگاه دانشگاه در انگلستان ضامن بریتانیایی نمی‌خواهد — اجارهٔ خصوصی می‌خواهد (یا ۶–۱۲ ماه پیش‌پرداخت). در هلند/سوئیس/آلمان ودیعهٔ ۲–۳ ماه + گاهی پیش‌پرداخت ۳ ماه را در «نقد روز صفر» حساب کنید. آدرس ثبت‌شده در آلمان (Anmeldung)، هلند (BSN) و سوئیس شرط گرفتن کارت اقامت/بانک است.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>• اعداد «رسمی» از صفحهٔ دانشگاه (۲۰۲۶/۲۷) و اعداد با «≈» برآورد از منابع ثانویه‌اند؛ اجاره‌ها هر سال ۳–۸٪ بالا می‌رود.</t>
         </is>
       </c>
     </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>• en-suite در برابر اتاق خصوصی (جدول سوم): در شمال انگلستان و York خوابگاه en-suite تقریباً هم‌قیمت یا حتی گران‌تر از اتاق در خانهٔ مشترک است؛ صرفه‌جویی واقعی از (۱) اتاق استاندارد با حمام مشترک (£1,000–3,700 در سال کمتر از en-suite) و (۲) نخواستن ضامن/پیش‌پرداخت و قبوض ثابت می‌آید. در لندن، حومهٔ لندن و در آلمان/سوئیس/هلند/سوئد/دانمارک خوابگاه واقعاً ارزان‌تر از بازار است.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A38:I38"/>
+  <mergeCells count="6">
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Table_final.xlsx
+++ b/Table_final.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
@@ -168,6 +168,15 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -12721,7 +12730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13067,42 +13076,42 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>دانشگاه</t>
+          <t>شهر</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>کشور / شهر</t>
+          <t>کشور</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>خوابگاه یا کمک دانشگاه</t>
+          <t>دانشگاه(های) شیت برنامه‌ها</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>تضمین برای ارشد؟</t>
+          <t>چه کسی خوابگاه می‌دهد</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>اجاره (ماهانه ≈)</t>
+          <t>شانس گرفتن خوابگاه برای ارشد بین‌المللی (⭐ تا ⭐⭐⭐⭐⭐) و زمان</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>غذا؟</t>
+          <t>اجارهٔ خوابگاه / ماه</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>مهلت / نکته</t>
+          <t>اتاق خصوصی / ماه</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>منبع</t>
+          <t>اعتبار عدد و منبع</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -13110,42 +13119,42 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
           <t>Universität Stuttgart</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>آلمان / Stuttgart</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Studierendenwerk Stuttgart (۳۵ مجموعه، ۷,۲۰۰ جا)</t>
-        </is>
-      </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>❌ لیست انتظار ۶–۸ ماه</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>€229–500 (میانگین €345) با قبوض</t>
+          <t>Studierendenwerk Stuttgart</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — لیست انتظار معمول ۶–۸ ماه برای ترم زمستان؛ Esslingen/Göppingen/Ludwigsburg زودتر</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>€229–500 با قبوض (میانگین €345)</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>همان روز پذیرش ثبت‌نام؛ Esslingen/Göppingen زودتر خالی می‌شود</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>studierendenwerk-stuttgart.de</t>
+          <t>WG €593 (MLP 2025)</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>رسمی (Studierendenwerk، MLP)</t>
         </is>
       </c>
       <c r="I10" s="4" t="n"/>
@@ -13153,42 +13162,42 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Uni Passau / Saarland / TU Dresden / Chemnitz / OVGU</t>
+          <t>Erlangen</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>آلمان / شهرهای ارزان</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Studierendenwerk محلی</t>
+          <t>FAU</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>❌ ولی معمولاً ظرفیت هست</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>€220–380 با قبوض (≈)</t>
+          <t>Studierendenwerk Erlangen-Nürnberg</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط — ۱–۲ ترم انتظار ممکن؛ Nürnberg هم گزینه</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €280–420</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>شهرهای کوچک/شرقی: بدون بحران؛ WG خصوصی €280–450</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>studierendenwerke.de (≈)</t>
+          <t>≈ €450–520</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
         </is>
       </c>
       <c r="I11" s="4" t="n"/>
@@ -13196,42 +13205,42 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TU Darmstadt / RWTH Aachen / FAU Erlangen</t>
+          <t>Darmstadt</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>آلمان / شهرهای گران</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Studierendenwerk محلی</t>
+          <t>TU Darmstadt</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>❌ صف طولانی</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>€300–450 با قبوض (≈)</t>
+          <t>Studierendenwerk Darmstadt</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — تقاضای بالا (فرانکفورت نزدیک)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €280–450</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>WG خصوصی €450–700؛ زودتر از همه اقدام کنید</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>studierendenwerke.de (≈)</t>
+          <t>WG €483 (MLP 2025)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I12" s="4" t="n"/>
@@ -13239,42 +13248,42 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Dresden</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>هلند / Enschede</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>اتاق‌های کمپوس و شهر از طریق Roomspot (اول‌آمده‌اول‌گرفته)</t>
+          <t>TU Dresden</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>پیشنهاد برای دانشجویان ویزایی اگر زود اقدام کنند</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>€300–800</t>
+          <t>Studentenwerk Dresden (ذخیرهٔ بزرگ)</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — معمولاً ظرف چند هفته تا یک ترم</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €250–380</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>بلافاصله بعد از پذیرش در Roomspot ثبت‌نام کنید</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>utwente.nl (issuu)</t>
+          <t>WG €435 (MLP 2025)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I13" s="4" t="n"/>
@@ -13282,42 +13291,42 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Radboud University</t>
+          <t>Saarbrücken</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>هلند / Nijmegen</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>میانجی‌گری دانشگاه + SSH&amp; (اتاق‌های مبله برای کل دوره)</t>
+          <t>Saarland University</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>❌ «کمک، نه تضمین»</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>€370–650</t>
+          <t>Studentenwerk Saarland</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €250–380</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>فرم PAS تا ۱ ژوئن؛ پیشنهادها می–ژوئیه؛ گاهی ۳ ماه پیش‌پرداخت</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>ru.nl؛ sshn.nl</t>
+          <t>WG €480 (MLP 2025)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I14" s="4" t="n"/>
@@ -13325,42 +13334,42 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Utrecht / TU Eindhoven / UvA / Delft / Leiden</t>
+          <t>Chemnitz</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>هلند / شهرهای بزرگ</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>اتاق‌های رزروشده با SSH/Plaza/Vestide؛ قرعه‌کشی یا اول‌آمده</t>
+          <t>TU Chemnitz</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>❌ (Utrecht ۲۰۲۶: ۲۸ می تمام شد)</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>€650–1,100 (Utrecht استودیو €868 با قبوض)</t>
+          <t>Studentenwerk Chemnitz-Zwickau</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ تقریباً همیشه جا هست</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €200–300</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>ودیعه ≈ ۲ ماه (Utrecht €1,306)؛ قرارداد ۱۲ ماههٔ ثابت</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>uu.nl</t>
+          <t>WG €274 (MLP 2025) — ارزان‌ترین آلمان</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I15" s="4" t="n"/>
@@ -13368,42 +13377,42 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Uppsala University</t>
+          <t>Passau</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>سوئد / Uppsala</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Housing Office دانشگاه</t>
+          <t>Universität Passau</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>✅ تضمین رسمی برای شهریه‌پردازها</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>SEK 3,500–6,100</t>
+          <t>Studierendenwerk Niederbayern/Oberpfalz</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — شهر کوچک، ظرفیت نسبتاً خوب</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €260–380</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>شهریه را تا مهلت بپردازید و به‌موقع درخواست دهید</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>uu.se</t>
+          <t>≈ €380–450</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
         </is>
       </c>
       <c r="I16" s="4" t="n"/>
@@ -13411,42 +13420,42 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Linköping University</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>سوئد / Linköping</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>یک پیشنهاد اتاق برای سال اول (Studentbostäder)</t>
+          <t>OVGU</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>✅ یک پیشنهاد (نه انتخاب)</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>SEK 3,500–5,500 (≈)</t>
+          <t>Studentenwerk Magdeburg</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ تقریباً همیشه جا هست</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €220–320</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>بعد از پرداخت شهریه؛ رد کنید = از دست می‌رود</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>liu.se</t>
+          <t>WG €339 (MLP 2025)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I17" s="4" t="n"/>
@@ -13454,42 +13463,42 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>KTH / Chalmers</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>سوئد / Stockholm / Göteborg</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>KTH Accommodation (محدود)؛ Chalmers از طریق SGS برای شهریه‌پردازها</t>
+          <t>TH Köln</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>❌ KTH بدون تضمین؛ Chalmers سهمیه (چک شود)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>SEK 4,500–8,000</t>
+          <t>Kölner Studierendenwerk</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — شهر بزرگ، صف طولانی</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €300–450</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>SSSB استکهلم صف ۶–۱۸ ماه؛ Plan B لازم</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>su.se؛ leapscholar (≈)</t>
+          <t>WG €641 (MLP 2025)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I18" s="4" t="n"/>
@@ -13497,42 +13506,42 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Halmstad / MDU / BTH / Skövde</t>
+          <t>Siegen</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>سوئد / شهرهای کوچک</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>معرفی به شرکت‌های مسکن شهرداری</t>
+          <t>Universität Siegen</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>❌ Halmstad صریحاً «تضمین نمی‌کند»؛ بقیه صف</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>SEK 3,500–5,500 (≈)</t>
+          <t>Studierendenwerk Siegen</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €250–350</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>شهرهای کوچک: معمولاً ظرف چند هفته پیدا می‌شود</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>hh.se (≈)</t>
+          <t>≈ €330–400</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
         </is>
       </c>
       <c r="I19" s="4" t="n"/>
@@ -13540,42 +13549,42 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Aalborg University (Aalborg)</t>
+          <t>Sankt Augustin</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>دانمارک / Aalborg</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>International Accommodation Office؛ ۲۲۰+ واحد مبله</t>
+          <t>H-BRS</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>✅ «تقریباً ۱۰۰٪»</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>DKK 3,200–4,700 (میانگین 3,950) با اینترنت/آب/گرمایش/برق</t>
+          <t>Studierendenwerk Bonn</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط (منطقهٔ بن)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €300–400</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>اجاره سه‌ماهه؛ ثبت‌نام studieboligaalborg.dk ۱ ژوئیه – ۳۱ اوت</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>en.aau.dk؛ findunirooms</t>
+          <t>≈ €450–520</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
         </is>
       </c>
       <c r="I20" s="4" t="n"/>
@@ -13583,42 +13592,42 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>AAU Copenhagen / ITU / DTU / KU</t>
+          <t>Aachen</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>دانمارک / Copenhagen</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>راهنمایی؛ KKIK/CIU؛ خوابگاه‌های خصوصی</t>
+          <t>RWTH</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>❌ صریحاً بدون تضمین</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>DKK 3,500–6,000 (KKIK/CIU) · 5,000–9,000 خوابگاه/co-living · آپارتمان 7,000+</t>
+          <t>Studierendenwerk Aachen</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط — ۱–۲ ترم انتظار رایج</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €280–420</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>«سخت‌ترین بازار اروپا» (خود AAU)؛ ۶ ماه قبل شروع کنید</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>en.aau.dk</t>
+          <t>WG €483 (MLP 2025)</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I21" s="4" t="n"/>
@@ -13626,42 +13635,42 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>SDU Odense</t>
+          <t>Tübingen</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>دانمارک / Odense</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>SDU Housing (کمک با kollegium)</t>
+          <t>Universität Tübingen</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>❌ کمک، بدون تضمین</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>DKK 3,500–5,500 (≈)</t>
+          <t>Studierendenwerk Tübingen-Hohenheim</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط — شهر کوچک و پرتقاضا</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €300–450</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Odense خیلی ارزان‌تر از کپنهاگ</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>sdu.dk (≈)</t>
+          <t>WG €464 (MLP 2025)</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I22" s="4" t="n"/>
@@ -13669,42 +13678,42 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ETH Zürich / UZH / ZHAW</t>
+          <t>München</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>سوئیس / Zürich</t>
+          <t>آلمان</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>WOKO، Juwo (تعاونی‌ها)؛ دانشگاه فقط معرفی می‌کند</t>
+          <t>TUM / LMU</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>❌ لیست انتظار ۳–۱۲ ماه</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>CHF 480–900؛ WG خصوصی 700–1,200</t>
+          <t>Studierendenwerk München</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>⭐ خیلی کم — انتظار ۲–۴ ترم</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €350–500</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>روز پذیرش در WOKO ثبت‌نام کنید؛ اجارهٔ خصوصی: ضامن/بیمهٔ ودیعه</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>woko.ch</t>
+          <t>WG €790 (MLP 2025) — گران‌ترین آلمان</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>MLP رسمی؛ خوابگاه برآورد</t>
         </is>
       </c>
       <c r="I23" s="4" t="n"/>
@@ -13712,42 +13721,42 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>EPFL</t>
+          <t>Enschede</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>سوئیس / Lausanne</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>FMEL (بنیاد خوابگاه‌های لوزان)</t>
+          <t>University of Twente</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>❌ زود پر می‌شود</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>≈ CHF 500–900</t>
+          <t>Roomspot / کمپوس UT</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — پیشنهاد برای دانشجویان ویزایی (اول‌آمده)؛ خارج از فهرست شهرهای پرفشار Kences</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>€300–800 (UT)</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>بلافاصله بعد از پذیرش دور اول (مارس)</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>fmel.ch (≈)</t>
+          <t>≈ €397 میانگین (Kamernet Q1 2025) — ارزان‌ترین هلند</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>رسمی/ثانویه</t>
         </is>
       </c>
       <c r="I24" s="4" t="n"/>
@@ -13755,42 +13764,42 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>USI / Bern / Fribourg / Neuchâtel / Basel / HSLU</t>
+          <t>Nijmegen</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>سوئیس / شهرهای کوچک‌تر</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه‌های دانشجویی محلی + معرفی دانشگاه</t>
+          <t>Radboud</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>❌ ولی بازار آسان‌تر از زوریخ</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>≈ CHF 450–800؛ WG 600–900</t>
+          <t>میانجی‌گری Radboud + SSH&amp;</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط — فرم PAS تا ۱ ژوئن، پیشنهاد می–ژوئیه، بدون تضمین؛ Kences: فشار بالا</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>€370–650 مبله</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>لوگانو/فریبورگ/نوشاتل ارزان‌ترین سوئیس</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>برآورد</t>
+          <t>≈ €500–650</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>رسمی (ru.nl)</t>
         </is>
       </c>
       <c r="I25" s="4" t="n"/>
@@ -13798,42 +13807,42 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Teesside University</t>
+          <t>Leiden</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / Middlesbrough</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه دانشگاه + PBSA خصوصی</t>
+          <t>Leiden University</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>معمولاً بله برای دانشجویان جدید (تأیید کنید)</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>≈ £95–140/هفته (≈ £410–610/ماه) با قبوض؛ PBSA از £138/هفته</t>
+          <t>DUWO (اتاق‌های رزروشده، قرعه)</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — فشار بالا (Kences)؛ اجاره ۱۸٪ در یک سال بالا رفت</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>❌ (PG)</t>
+          <t>≈ €500–800</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌ترین شهر جدول انگلستان</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>tees.ac.uk (≈)</t>
+          <t>≈ €600–900</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>برآورد + Kences/Kamernet</t>
         </is>
       </c>
       <c r="I26" s="4" t="n"/>
@@ -13841,42 +13850,42 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Northumbria University</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / Newcastle</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه دانشگاه</t>
+          <t>University of Groningen</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>معمولاً بله (تأیید کنید)</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>£94.19–158.31/هفته با قبوض (رسمی) = £410–690/ماه</t>
+          <t>SSH Short Stay (رزرو)</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط — «میانهٔ جدول» Kences</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>✅ گزینهٔ catered دارد</t>
+          <t>≈ €450–700</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>حداقل زندگی ≈ £1,015/ماه (خود دانشگاه)</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>northumbria.ac.uk</t>
+          <t>€515 میانگین (Kences)</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Kences رسمی</t>
         </is>
       </c>
       <c r="I27" s="4" t="n"/>
@@ -13884,42 +13893,42 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Newcastle University</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / Newcastle</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه‌های دانشگاه (Bowsden Court، Grand Hotel، Bernicia…)</t>
+          <t>Utrecht University</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>برای PG جدید معمولاً بله (تأیید کنید)</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>£117.60–239.75/هفته (رسمی 2026/27)</t>
+          <t>استودیوهای رزروشده (Plaza/SSH)</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>⭐ خیلی کم — بیشترین فشار هلند (Kences نوامبر ۲۰۲۵)؛ رزروها ۲۸ می ۲۰۲۶ تمام شد</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>❌ (PG)</t>
+          <t>€868 با قبوض (رزروشده)</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Bowsden Court برای PG/خانواده</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>ncl.ac.uk</t>
+          <t>≈ €600–900</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>رسمی (uu.nl)</t>
         </is>
       </c>
       <c r="I28" s="4" t="n"/>
@@ -13927,42 +13936,42 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>University of York</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / York</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه کمپوس (Wentworth Graduate College، Halifax)</t>
+          <t>UvA / VU</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>✅ تضمین PG اگر تا ۳۱ ژوئیه اقدام کنید</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>£186–224/هفته × ۵۱ هفته = £9,486–11,424/سال (رسمی 2026/27)</t>
+          <t>اتاق‌های رزروشده (قرعه؛ فقط سال اول)</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>⭐ خیلی کم — بدترین بازار هلند</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>❌ (PG self-catered)</t>
+          <t>≈ €650–1,000</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>پیشنهاد بدون قید ویزا تا ۷ اوت</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>york.ac.uk</t>
+          <t>≈ €650 (Kences) تا €979 (Kamernet)</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Kences/Kamernet</t>
         </is>
       </c>
       <c r="I29" s="4" t="n"/>
@@ -13970,42 +13979,42 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>University of Essex</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / Colchester</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه کمپوس</t>
+          <t>TU/e</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>✅ تضمین برای PG برای کل دوره (اکتبر: مهلت ≈ ۱۲ سپتامبر؛ ژانویه: ۳۰ نوامبر)</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>≈ £115–200/هفته (چک شود)</t>
+          <t>Vestide / Holland2Stay (محدود)</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — فشار بالا (Kences)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €500–800</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>ورود زودهنگام رایگان برای ورودی ژانویه</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>essex.ac.uk</t>
+          <t>≈ €550–800</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>برآورد + Kences</t>
         </is>
       </c>
       <c r="I30" s="4" t="n"/>
@@ -14013,42 +14022,42 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Brunel University London</t>
+          <t>Delft</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / Uxbridge</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه کمپوس</t>
+          <t>TU Delft</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>✅ تضمین برای همهٔ دانشجویان جدید — مهلت ۱۵ مارس ۲۰۲۶ برای 2026/27</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>≈ £150–240/هفته (چک شود)</t>
+          <t>DUWO (رزرو، قرعه)</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — فشار بالا؛ برنامهٔ ۳,۵۰۰ اتاق شهر شکست خورد (۲۷۹ ساخته شد)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>≈ €500–800</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>پیش‌پرداخت £350 (اتاق) / £450 (استودیو)</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>brunel.ac.uk</t>
+          <t>≈ €600–900</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Kences/Delta</t>
         </is>
       </c>
       <c r="I31" s="4" t="n"/>
@@ -14056,40 +14065,40 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Warwick / Sheffield / Lancaster / Leicester</t>
+          <t>Breda</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / شهرهای متوسط</t>
+          <t>هلند</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه دانشگاه</t>
+          <t>BUas</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Sheffield/Lancaster معمولاً بله برای PG؛ Warwick محدود (تأیید کنید)</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>≈ £125–210/هفته</t>
+          <t>معرفی BUas + بازار</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>❌ (PG)</t>
+          <t>≈ €450–650</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>اتاق خصوصی £550–750/ماه</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
+          <t>≈ €500–650</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>برآورد</t>
         </is>
@@ -14099,42 +14108,42 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Durham University</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / Durham</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>کالج‌ها (۱۷ کالج؛ Ustinov فقط PG)</t>
+          <t>LiU</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>❌ PG بدون تضمین؛ کالج‌ها بعد از پذیرش تماس می‌گیرند</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>PG self-catered ≈ £183–200/هفته (۳۹ هفته £7,146–7,801، 25/26) · catered £262/هفته (£10,233/سال)</t>
+          <t>Studentbostäder + یک پیشنهاد LiU برای شهریه‌پردازها</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ — SFS «سبز» ۲۰۲۴ و ۲۰۲۵ + پیشنهاد دانشگاه</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>✅ کالج‌های catered (۳ وعده در ترم) — عمدتاً کارشناسی؛ بعضی کالج‌ها برای PG هم</t>
+          <t>SEK 3,500–5,500</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>سهم غذا ≈ £3,087/سال؛ اجارهٔ خصوصی از £190/هفته</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>durham.ac.uk؛ palatinate.org.uk</t>
+          <t>SEK 5,000–7,000</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>SFS رسمی؛ liu.se</t>
         </is>
       </c>
       <c r="I33" s="4" t="n"/>
@@ -14142,42 +14151,42 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>University of Bristol</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / Bristol</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه دانشگاه (catered و self-catered)</t>
+          <t>Halmstad University</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>PG: محدود (تأیید کنید)</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>≈ £150–260/هفته</t>
+          <t>شرکت‌های شهری؛ دانشگاه «تضمین نمی‌کند»</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — SFS «قرمز» ۲۰۲۳ و ۲۰۲۴</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>✅ catered halls (عمدتاً UG)</t>
+          <t>SEK 3,500–5,500</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>بریستول یکی از گران‌ترین شهرهای خارج لندن</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>برآورد</t>
+          <t>SEK 5,000–7,000</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>SFS رسمی؛ hh.se</t>
         </is>
       </c>
       <c r="I34" s="4" t="n"/>
@@ -14185,42 +14194,42 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>UCL / King's College London</t>
+          <t>Karlskrona</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / London</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه‌های دانشگاه و بین‌دانشگاهی</t>
+          <t>BTH</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>❌ PG بدون تضمین</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>≈ £190–350/هفته (£820–1,500/ماه)</t>
+          <t>Karlskronahem + معرفی BTH</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — SFS «سبز» ۲۰۲۴ (زرد ۲۰۲۳)</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>❌ (PG)</t>
+          <t>SEK 3,500–5,000</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>UCL طرح ضامن اجاره £50 (سقف £1,517/ماه)</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>harveywjames (≈)</t>
+          <t>SEK 4,500–6,500</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>SFS رسمی</t>
         </is>
       </c>
       <c r="I35" s="4" t="n"/>
@@ -14228,551 +14237,3389 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Imperial College London</t>
+          <t>Stockholm / Kista</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>انگلستان / London</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>خوابگاه (Beit، Holbein…) + GradPad</t>
+          <t>KTH</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>❌ PG بدون تضمین</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>£210–410/هفته (۲۰۲۶) = £900–1,800/ماه؛ خانهٔ مشترک £180–450/هفته</t>
+          <t>SSSB (صف) + KTH Accommodation (محدود، بدون تضمین)</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>⭐ خیلی کم — SFS «قرمز» هر سال؛ صف SSSB ۶–۱۸ ماه</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>❌ (PG)</t>
+          <t>SEK 4,500–8,000</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>طرح ضامن اجاره فقط UG/PhD؛ برآورد خود Imperial برای زندگی: £16.4–17k / ۹ ماه</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>harveywjames؛ ukfreshersguide (≈)</t>
+          <t>SEK 7,000–11,000</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>SFS رسمی؛ su.se</t>
         </is>
       </c>
       <c r="I36" s="4" t="n"/>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Gothenburg</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Chalmers / GU</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>SGS (اولویت شهریه‌پردازهای Chalmers — چک شود)</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — SFS «قرمز» هر سال</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>SEK 4,000–6,500</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>SEK 6,000–9,000</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>SFS رسمی</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="n"/>
+    </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>شهر / کشور</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>خوابگاه استاندارد (حمام مشترک) — سالانه</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>خوابگاه en-suite — سالانه</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>اتاق در خانهٔ مشترک خصوصی — سالانه (+ قبوض ≈ £80/ماه)</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>en-suite در برابر اتاق خصوصی</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>استاندارد در برابر en-suite (پول حمام اختصاصی)</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>نکته</t>
-        </is>
-      </c>
-      <c r="H38" s="1" t="n"/>
-      <c r="I38" s="1" t="n"/>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>سوئد</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Uppsala University</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Housing Office دانشگاه</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ برای شهریه‌پردازها (تضمین رسمی) — با اینکه SFS شهر را «قرمز» می‌داند</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>SEK 3,500–6,100</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>SEK 6,000–8,500</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>uu.se رسمی؛ SFS</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Newcastle / Middlesbrough (Northumbria، Newcastle، Teesside)</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>£94–118/هفته × ۵۱ = £4,800–6,000 (رسمی Northumbria £94.19، Newcastle £117.60)</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>£140–190/هفته × ۵۱ = £7,100–9,700</t>
+          <t>Umeå University</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>£450–650/ماه × ۱۲ + £960 = £6,400–8,800 (+ ضامن ≈ £1,650 اگر لازم شود)</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>≈ برابر (−£1,000 تا +£1,700)</t>
+          <t>Bostaden (صف) + پیشنهاد دانشگاه به شهریه‌پردازها (چک شود)</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط — SFS «قرمز» ۲۰۲۴، «زرد» ۲۰۲۳</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>استاندارد £2,300–3,700 ارزان‌تر</t>
+          <t>SEK 3,500–5,500</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>ارزان‌ترین راه واقعی: اتاق استاندارد ۵۱ هفته‌ای ≈ £4,900 با همهٔ قبوض</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n"/>
+          <t>SEK 5,000–7,000</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>SFS رسمی</t>
+        </is>
+      </c>
       <c r="I39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>York (اعداد رسمی PG 2026/27)</t>
+          <t>Skövde</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>£186 × ۵۱ = £9,486</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>£206 × ۵۱ = £10,506</t>
+          <t>University of Skövde</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>£550–750/ماه × ۱۲ + £960 = £7,560–9,960</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>❌ en-suite £500–2,900 گران‌تر از اتاق خصوصی</t>
+          <t>Skövdebostäder</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — SFS «سبز» ۲۰۲۴ (قرمز ۲۰۲۳؛ ولی اتاق موقت همیشه آسان)</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>استاندارد £1,020 ارزان‌تر</t>
+          <t>SEK 3,300–4,800</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>York خوابگاه گران دارد؛ مزیتش تضمین و بی‌ضامنی است، نه قیمت</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n"/>
+          <t>SEK 4,500–6,000</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>SFS رسمی</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Colchester (Essex)</t>
+          <t>Västerås</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>≈ £115–140 × ۴۰–۵۱ = £4,600–7,100</t>
+          <t>سوئد</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>≈ £160–200 × ۴۰–۵۱ = £6,400–10,200</t>
+          <t>MDU</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>£550–700/ماه × ۱۲ + £960 = £7,560–9,360</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>≈ برابر</t>
+          <t>Bostad Västerås + تضمین شهرداری برای دانشجویان جدید</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ — SFS «سبز» هر سال؛ تضمین شهری</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>استاندارد £1,800–3,000 ارزان‌تر</t>
+          <t>SEK 3,500–5,500</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>قرارداد ۴۰ هفته‌ای برای ارشد ۱۲ ماهه کافی نیست → ۸–۱۲ هفتهٔ تابستان جدا</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n"/>
+          <t>SEK 5,000–7,000</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>SFS رسمی</t>
+        </is>
+      </c>
       <c r="I41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Uxbridge (Brunel) — غرب لندن</t>
+          <t>Aalborg</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>≈ £150–170 × ۴۰–۵۰ = £6,000–8,500</t>
+          <t>دانمارک</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>≈ £190–240 × ۴۰–۵۰ = £7,600–12,000</t>
+          <t>AAU</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>£900–1,200/ماه × ۱۲ + £1,200 = £12,000–15,600</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>✅ en-suite £2,000–5,000 ارزان‌تر</t>
+          <t>International Accommodation Office (۲۲۰+ واحد مبله)</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ «تقریباً ۱۰۰٪»</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>استاندارد £1,600–3,500 ارزان‌تر</t>
+          <t>DKK 3,200–4,700 با اینترنت/آب/گرمایش/برق</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>در لندن و حومه خوابگاه دانشگاه واقعاً می‌صرفد + تضمین Brunel (مهلت ۱۵ مارس)</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n"/>
+          <t>DKK 3,500–5,000</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>AAU رسمی/ثانویه</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Durham (کالج، PG self-catered)</t>
+          <t>Copenhagen (AAU CPH، ITU، KU)</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>£183 × ۳۹ = £7,146 + ۱۳ هفته تابستان ≈ £1,950 = £9,100</t>
+          <t>دانمارک</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>£200 × ۳۹ = £7,801 + تابستان ≈ £1,950 = £9,750</t>
+          <t>AAU Copenhagen / ITU</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>£550–700/ماه × ۱۲ + £960 = £7,560–9,360</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>≈ برابر تا £2,000 گران‌تر</t>
+          <t>راهنمایی؛ KKIK/CIU؛ خوابگاه خصوصی</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>⭐ خیلی کم — خود AAU: «سخت‌ترین بازار اروپا»، بدون تضمین</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>استاندارد £650 ارزان‌تر</t>
+          <t>DKK 3,500–6,000 (KKIK/CIU) · 5,000–9,000 خوابگاه خصوصی</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>قرارداد ۳۹ هفته‌ای دورهام برای ارشد ۱۲ ماهه مشکل‌ساز است</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="n"/>
+          <t>DKK 6,000–9,000 (آپارتمان از 7,000)</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>en.aau.dk رسمی</t>
+        </is>
+      </c>
       <c r="I43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>London مرکز (UCL / KCL / Imperial)</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>£210–250 × ۴۰–۵۱ = £8,400–12,750</t>
+          <t>دانمارک</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>£260–350 × ۴۰–۵۱ = £10,400–17,850</t>
+          <t>DTU</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>£1,000–1,400/ماه × ۱۲ + £1,200 = £13,200–18,000 (+ ضامن)</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>✅ £0–3,000 ارزان‌تر (اگر گیرتان بیاید — PG بدون تضمین)</t>
+          <t>DTU Housing (Campus Village محدود)</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>استاندارد £2,000–5,000 ارزان‌تر</t>
+          <t>≈ DKK 4,000–6,500</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>در لندن هر دو گران‌اند؛ تفاوت اصلی «ضامن نخواستن» خوابگاه است</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n"/>
+          <t>≈ DKK 6,000–8,500</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>آلمان (Studierendenwerk در برابر WG)</t>
+          <t>Odense</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>€230–450/ماه با قبوض = €2,800–5,400</t>
+          <t>دانمارک</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>— (خوابگاه‌های آلمان معمولاً حمام مشترک یا آپارتمان تک‌نفره)</t>
+          <t>SDU</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>€450–700 + €80 قبوض = €6,400–9,400</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>✅ خوابگاه €1,500–4,500 ارزان‌تر</t>
+          <t>SDU Housing + kollegium</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — کمک فعال، ظرفیت خوب</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≈ DKK 3,500–5,500</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>بزرگ‌ترین صرفه‌جویی نسبی — ولی لیست انتظار</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="n"/>
+          <t>≈ DKK 4,000–6,000</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
       <c r="I45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>هلند (اتاق رزروشده در برابر بازار)</t>
+          <t>Kolding</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>€370–650 = €4,400–7,800</t>
+          <t>دانمارک</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SDU Kolding</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>€600–1,000 = €7,200–12,000</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>✅ €1,500–4,000 ارزان‌تر</t>
+          <t>SDU Housing</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≈ DKK 3,000–4,500</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>اتاق رزروشده فقط سال اول و بدون تضمین</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="n"/>
+          <t>≈ DKK 3,500–5,500</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>سوئد (کریدوری در برابر خصوصی)</t>
+          <t>Aarhus</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>SEK 3,500–6,500 = SEK 42–78k</t>
+          <t>دانمارک</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aarhus University</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>SEK 5,000–8,000 (+ برق) = SEK 62–100k</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>✅ SEK 15–25k ارزان‌تر (≈ $1,500–2,500)</t>
+          <t>AU Housing (پیشنهاد به بین‌المللی‌ها)</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط — بازار تنگ ولی دانشگاه پیشنهاد می‌دهد</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≈ DKK 3,500–6,000</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Uppsala/LiU تضمین؛ استکهلم صف</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="n"/>
+          <t>≈ DKK 5,000–7,500</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
       <c r="I47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>دانمارک (kollegium در برابر خصوصی)</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>DKK 3,200–4,700 = DKK 38–56k</t>
+          <t>سوئیس</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ETH، UZH</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>DKK 4,500–7,000 = DKK 54–84k</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>✅ DKK 15–30k ارزان‌تر (≈ $2,300–4,600)</t>
+          <t>WOKO، Juwo (تعاونی)</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>⭐ خیلی کم — لیست انتظار ۳–۱۲ ماه؛ روز پذیرش ثبت‌نام کنید</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CHF 480–900</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Aalborg تضمین؛ کپنهاگ نه</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="n"/>
+          <t>CHF 700–1,200</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>woko.ch؛ برآورد</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>ZHAW</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>WOKO Winterthur / بازار</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — کمی بهتر از زوریخ</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 500–800</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>CHF 650–1,000</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>FMEL</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐ کم — زود پر می‌شود؛ بلافاصله بعد از پذیرش دور اول</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 500–900</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>CHF 700–1,000</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>University of Bern</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>StuWo Bern / بازار</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 500–750</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>CHF 650–900</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>University of Basel</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>WoVe Basel / بازار</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 500–800</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>CHF 650–950</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Fribourg</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>University of Fribourg</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Apartis / معرفی دانشگاه</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 450–700</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>CHF 600–800</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Neuchâtel</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>University of Neuchâtel</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Alfen / معرفی دانشگاه</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 450–700</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>CHF 550–800</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>USI</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه‌های USI + سرویس مسکن دانشگاه</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 500–800</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>CHF 600–900</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>سوئیس</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>HSLU</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>معرفی HSLU / بازار</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>≈ CHF 500–800</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>CHF 650–900</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Teesside</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه دانشگاه + PBSA فراوان</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — معمولاً برای همهٔ ورودی‌ها جا هست (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>≈ £95–140/هفته = £410–610/ماه</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>£450–550</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>برآورد؛ PBSA از £138/هفته</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Northumbria، Newcastle University</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه‌های هر دو دانشگاه</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — ذخیرهٔ بزرگ (تأیید تضمین PG)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Northumbria £94–158/هفته · Newcastle £118–240/هفته (رسمی) = £410–1,040/ماه</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>£500–650</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>NTU</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه NTU</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>≈ £130–200/هفته</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>£500–650</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>MMU (و University of Manchester)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه دانشگاه</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا — University of Manchester رسماً به هر PG بین‌المللی برای کل دوره تضمین می‌دهد (اقدام تا ۳۱ اوت)؛ MMU تأیید کنید</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>≈ £140–220/هفته</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>£550–750</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>manchester.ac.uk رسمی؛ MMU برآورد</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Essex</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ تضمین برای PG برای کل دوره (اقدام تا مهلت)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>≈ £115–200/هفته</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>£550–700</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>essex.ac.uk رسمی (تضمین)؛ قیمت برآورد</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>University of Leicester</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه دانشگاه</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>≈ £130–200/هفته</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>£500–650</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>London – Uxbridge</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Brunel</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ تضمین برای همهٔ دانشجویان جدید — مهلت ۱۵ مارس</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>≈ £150–240/هفته</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>£900–1,200</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>brunel.ac.uk رسمی (تضمین)؛ قیمت برآورد</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Egham</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Royal Holloway</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>≈ £150–230/هفته</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>£750–950</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>London – New Cross</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Goldsmiths</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه محدود</t>
+        </is>
+      </c>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ متوسط</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>≈ £190–300/هفته</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>£900–1,300</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Canterbury</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>≈ £130–210/هفته</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>£550–700</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Surrey</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>≈ £150–230/هفته</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>£750–950</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>University of York</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه کمپوس (Wentworth، Halifax)</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ تضمین PG — اقدام تا ۳۱ ژوئیه</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>£186–224/هفته × ۵۱ هفته (رسمی 2026/27)</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>£550–750</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>york.ac.uk رسمی</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Lancaster University</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>کالج‌های کمپوس</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>≈ £125–190/هفته</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>£500–650</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>برآورد</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Sheffield</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>انگلستان</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه دانشگاه (ذخیرهٔ بزرگ)</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ بالا (تأیید کنید)</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+     